--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="14_{A1B3B906-E661-414D-BCC5-34D6B6413D4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{94F2B126-0C5A-4B7D-9B0B-8CA76E01F0FA}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="14_{A1B3B906-E661-414D-BCC5-34D6B6413D4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{8696725A-FD65-4510-83C1-53C433FC3300}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notas" sheetId="1" r:id="rId1"/>
@@ -26,14 +26,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'extrato 2024'!$A$1:$C$187</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CR$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CS$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9111" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9147" uniqueCount="393">
   <si>
     <t>Jogador</t>
   </si>
@@ -3477,7 +3477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CR83"/>
+  <dimension ref="A1:CS83"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
@@ -3502,10 +3502,10 @@
     <col min="50" max="58" width="9.54296875" customWidth="1"/>
     <col min="59" max="65" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
-    <col min="67" max="90" width="11" customWidth="1"/>
+    <col min="67" max="91" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3773,27 +3773,30 @@
       <c r="CK1" s="1">
         <v>46085</v>
       </c>
-      <c r="CL1" s="1"/>
-      <c r="CM1" t="s">
+      <c r="CL1" s="1">
+        <v>46092</v>
+      </c>
+      <c r="CM1" s="1"/>
+      <c r="CN1" t="s">
         <v>57</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>58</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
         <v>59</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CQ1" t="s">
         <v>62</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>386</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4058,31 +4061,34 @@
       <c r="CK2">
         <v>6.5</v>
       </c>
-      <c r="CM2">
-        <f>COUNT(B2:CK2)</f>
-        <v>82</v>
-      </c>
-      <c r="CN2" s="18">
-        <f>AVERAGE(B2:CK2)</f>
-        <v>6.0426829268292686</v>
-      </c>
-      <c r="CO2">
-        <f t="shared" ref="CO2" si="0">IF(CM2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
+      <c r="CL2">
+        <v>5.5</v>
+      </c>
+      <c r="CN2">
+        <f>COUNT(B2:CL2)</f>
+        <v>83</v>
+      </c>
+      <c r="CO2" s="18">
+        <f>AVERAGE(B2:CL2)</f>
+        <v>6.0361445783132526</v>
+      </c>
+      <c r="CP2">
+        <f t="shared" ref="CP2" si="0">IF(CN2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
         <v>1.2512468149547391</v>
       </c>
-      <c r="CP2">
-        <v>1</v>
-      </c>
       <c r="CQ2">
+        <v>1</v>
+      </c>
+      <c r="CR2">
         <f>COUNT(CG2:CJ2)</f>
         <v>4</v>
       </c>
-      <c r="CR2">
-        <f t="shared" ref="CR2" si="1">IF(CP2=0,CQ2,0)</f>
+      <c r="CS2">
+        <f t="shared" ref="CS2" si="1">IF(CQ2=0,CR2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4350,31 +4356,31 @@
       <c r="CK3">
         <v>5</v>
       </c>
-      <c r="CM3">
+      <c r="CN3">
         <f>COUNT(B3:CK3)</f>
         <v>79</v>
       </c>
-      <c r="CN3" s="18">
+      <c r="CO3" s="18">
         <f>AVERAGE(B3:CK3)</f>
         <v>5.6518987341772151</v>
       </c>
-      <c r="CO3">
-        <f t="shared" ref="CO3:CO66" si="2">IF(CM3&gt;1,_xlfn.STDEV.S(B3:CF3),"")</f>
+      <c r="CP3">
+        <f t="shared" ref="CP3:CP66" si="2">IF(CN3&gt;1,_xlfn.STDEV.S(B3:CF3),"")</f>
         <v>1.0518094984498128</v>
       </c>
-      <c r="CP3">
-        <v>1</v>
-      </c>
       <c r="CQ3">
-        <f t="shared" ref="CQ3:CQ66" si="3">COUNT(CG3:CJ3)</f>
+        <v>1</v>
+      </c>
+      <c r="CR3">
+        <f t="shared" ref="CR3:CR66" si="3">COUNT(CG3:CJ3)</f>
         <v>4</v>
       </c>
-      <c r="CR3">
-        <f t="shared" ref="CR3:CR66" si="4">IF(CP3=0,CQ3,0)</f>
+      <c r="CS3">
+        <f t="shared" ref="CS3:CS66" si="4">IF(CQ3=0,CR3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4636,31 +4642,31 @@
       <c r="CI4">
         <v>5.5</v>
       </c>
-      <c r="CM4">
-        <f t="shared" ref="CM4:CM66" si="5">COUNT(B4:CI4)</f>
+      <c r="CN4">
+        <f t="shared" ref="CN4:CN66" si="5">COUNT(B4:CI4)</f>
         <v>72</v>
       </c>
-      <c r="CN4" s="18">
-        <f t="shared" ref="CN4:CN66" si="6">AVERAGE(B4:CI4)</f>
+      <c r="CO4" s="18">
+        <f t="shared" ref="CO4:CO66" si="6">AVERAGE(B4:CI4)</f>
         <v>5.708333333333333</v>
       </c>
-      <c r="CO4">
+      <c r="CP4">
         <f t="shared" si="2"/>
         <v>0.96435844595057774</v>
       </c>
-      <c r="CP4">
-        <v>1</v>
-      </c>
       <c r="CQ4">
+        <v>1</v>
+      </c>
+      <c r="CR4">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CR4">
+      <c r="CS4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -4910,31 +4916,31 @@
       <c r="CE5">
         <v>5</v>
       </c>
-      <c r="CM5">
+      <c r="CN5">
         <f t="shared" si="5"/>
         <v>68</v>
       </c>
-      <c r="CN5" s="18">
+      <c r="CO5" s="18">
         <f t="shared" si="6"/>
         <v>6.4191176470588234</v>
       </c>
-      <c r="CO5">
+      <c r="CP5">
         <f t="shared" si="2"/>
         <v>1.1769245721961776</v>
       </c>
-      <c r="CP5">
+      <c r="CQ5">
         <v>0</v>
       </c>
-      <c r="CQ5">
+      <c r="CR5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR5">
+      <c r="CS5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -5187,31 +5193,31 @@
       <c r="CI6">
         <v>5.5</v>
       </c>
-      <c r="CM6">
+      <c r="CN6">
         <f t="shared" si="5"/>
         <v>67</v>
       </c>
-      <c r="CN6" s="18">
+      <c r="CO6" s="18">
         <f t="shared" si="6"/>
         <v>5.9701492537313436</v>
       </c>
-      <c r="CO6">
+      <c r="CP6">
         <f t="shared" si="2"/>
         <v>0.96648378625350351</v>
       </c>
-      <c r="CP6">
+      <c r="CQ6">
         <v>0</v>
       </c>
-      <c r="CQ6">
+      <c r="CR6">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CR6">
+      <c r="CS6">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -5473,31 +5479,34 @@
       <c r="CK7">
         <v>6</v>
       </c>
-      <c r="CM7">
-        <f>COUNT(B7:CK7)</f>
-        <v>69</v>
-      </c>
-      <c r="CN7" s="18">
-        <f>AVERAGE(B7:CK7)</f>
-        <v>6.6231884057971016</v>
-      </c>
-      <c r="CO7">
+      <c r="CL7">
+        <v>6</v>
+      </c>
+      <c r="CN7">
+        <f>COUNT(B7:CL7)</f>
+        <v>70</v>
+      </c>
+      <c r="CO7" s="18">
+        <f>AVERAGE(B7:CL7)</f>
+        <v>6.6142857142857139</v>
+      </c>
+      <c r="CP7">
         <f t="shared" si="2"/>
         <v>0.9419445925236869</v>
       </c>
-      <c r="CP7">
-        <v>1</v>
-      </c>
       <c r="CQ7">
+        <v>1</v>
+      </c>
+      <c r="CR7">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CR7">
+      <c r="CS7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -5762,31 +5771,34 @@
       <c r="CK8">
         <v>6.5</v>
       </c>
-      <c r="CM8">
-        <f>COUNT(B8:CK8)</f>
-        <v>69</v>
-      </c>
-      <c r="CN8" s="18">
-        <f>AVERAGE(B8:CK8)</f>
-        <v>6.6086956521739131</v>
-      </c>
-      <c r="CO8">
+      <c r="CL8">
+        <v>6.5</v>
+      </c>
+      <c r="CN8">
+        <f>COUNT(B8:CL8)</f>
+        <v>70</v>
+      </c>
+      <c r="CO8" s="18">
+        <f>AVERAGE(B8:CL8)</f>
+        <v>6.6071428571428568</v>
+      </c>
+      <c r="CP8">
         <f t="shared" si="2"/>
         <v>1.0570846156365068</v>
       </c>
-      <c r="CP8">
-        <v>1</v>
-      </c>
       <c r="CQ8">
+        <v>1</v>
+      </c>
+      <c r="CR8">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CR8">
+      <c r="CS8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -6051,31 +6063,34 @@
       <c r="CK9">
         <v>6.5</v>
       </c>
-      <c r="CM9">
-        <f>COUNT(B9:CK9)</f>
-        <v>70</v>
-      </c>
-      <c r="CN9" s="18">
-        <f>AVERAGE(B9:CK9)</f>
-        <v>7.2928571428571427</v>
-      </c>
-      <c r="CO9">
+      <c r="CL9">
+        <v>5.5</v>
+      </c>
+      <c r="CN9">
+        <f>COUNT(B9:CL9)</f>
+        <v>71</v>
+      </c>
+      <c r="CO9" s="18">
+        <f>AVERAGE(B9:CL9)</f>
+        <v>7.267605633802817</v>
+      </c>
+      <c r="CP9">
         <f t="shared" si="2"/>
         <v>1.1294250579557983</v>
       </c>
-      <c r="CP9">
-        <v>1</v>
-      </c>
       <c r="CQ9">
+        <v>1</v>
+      </c>
+      <c r="CR9">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CR9">
+      <c r="CS9">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -6334,31 +6349,31 @@
       <c r="CK10">
         <v>5.5</v>
       </c>
-      <c r="CM10">
+      <c r="CN10">
         <f t="shared" si="5"/>
         <v>62</v>
       </c>
-      <c r="CN10" s="18">
+      <c r="CO10" s="18">
         <f t="shared" si="6"/>
         <v>5.717741935483871</v>
       </c>
-      <c r="CO10">
+      <c r="CP10">
         <f t="shared" si="2"/>
         <v>1.3617531291315086</v>
       </c>
-      <c r="CP10">
-        <v>1</v>
-      </c>
       <c r="CQ10">
+        <v>1</v>
+      </c>
+      <c r="CR10">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CR10">
+      <c r="CS10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6617,31 +6632,34 @@
       <c r="CH11">
         <v>6.5</v>
       </c>
-      <c r="CM11">
+      <c r="CL11">
+        <v>6.5</v>
+      </c>
+      <c r="CN11">
         <f t="shared" si="5"/>
         <v>59</v>
       </c>
-      <c r="CN11" s="18">
+      <c r="CO11" s="18">
         <f t="shared" si="6"/>
         <v>6.6779661016949152</v>
       </c>
-      <c r="CO11">
+      <c r="CP11">
         <f t="shared" si="2"/>
         <v>1.0072574989410263</v>
       </c>
-      <c r="CP11">
-        <v>1</v>
-      </c>
       <c r="CQ11">
+        <v>1</v>
+      </c>
+      <c r="CR11">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="CR11">
+      <c r="CS11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -6903,31 +6921,34 @@
       <c r="CK12">
         <v>7</v>
       </c>
-      <c r="CM12">
-        <f>COUNT(B12:CK12)</f>
-        <v>55</v>
-      </c>
-      <c r="CN12" s="18">
-        <f>AVERAGE(B12:CK12)</f>
-        <v>5.4818181818181815</v>
-      </c>
-      <c r="CO12">
+      <c r="CL12">
+        <v>5.5</v>
+      </c>
+      <c r="CN12">
+        <f>COUNT(B12:CL12)</f>
+        <v>56</v>
+      </c>
+      <c r="CO12" s="18">
+        <f>AVERAGE(B12:CL12)</f>
+        <v>5.4821428571428568</v>
+      </c>
+      <c r="CP12">
         <f t="shared" si="2"/>
         <v>1.0254583642020354</v>
       </c>
-      <c r="CP12">
-        <v>1</v>
-      </c>
       <c r="CQ12">
+        <v>1</v>
+      </c>
+      <c r="CR12">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="CR12">
+      <c r="CS12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -7192,31 +7213,34 @@
       <c r="CK13">
         <v>6</v>
       </c>
-      <c r="CM13">
-        <f>COUNT(B13:CK13)</f>
-        <v>53</v>
-      </c>
-      <c r="CN13" s="18">
-        <f>AVERAGE(B13:CK13)</f>
-        <v>6.3867924528301883</v>
-      </c>
-      <c r="CO13">
+      <c r="CL13">
+        <v>6</v>
+      </c>
+      <c r="CN13">
+        <f>COUNT(B13:CL13)</f>
+        <v>54</v>
+      </c>
+      <c r="CO13" s="18">
+        <f>AVERAGE(B13:CL13)</f>
+        <v>6.3796296296296298</v>
+      </c>
+      <c r="CP13">
         <f t="shared" si="2"/>
         <v>1.1769469323774333</v>
       </c>
-      <c r="CP13">
-        <v>1</v>
-      </c>
       <c r="CQ13">
+        <v>1</v>
+      </c>
+      <c r="CR13">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CR13">
+      <c r="CS13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -7466,31 +7490,31 @@
       <c r="CF14">
         <v>5.5</v>
       </c>
-      <c r="CM14">
+      <c r="CN14">
         <f t="shared" si="5"/>
         <v>47</v>
       </c>
-      <c r="CN14" s="18">
+      <c r="CO14" s="18">
         <f t="shared" si="6"/>
         <v>4.4255319148936172</v>
       </c>
-      <c r="CO14">
+      <c r="CP14">
         <f t="shared" si="2"/>
         <v>1.3391217246854428</v>
       </c>
-      <c r="CP14">
-        <v>1</v>
-      </c>
       <c r="CQ14">
+        <v>1</v>
+      </c>
+      <c r="CR14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR14">
+      <c r="CS14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -7758,31 +7782,34 @@
       <c r="CK15">
         <v>5</v>
       </c>
-      <c r="CM15">
-        <f>COUNT(B15:CK15)</f>
-        <v>45</v>
-      </c>
-      <c r="CN15" s="18">
-        <f>AVERAGE(B15:CK15)</f>
-        <v>6.0666666666666664</v>
-      </c>
-      <c r="CO15">
+      <c r="CL15">
+        <v>6</v>
+      </c>
+      <c r="CN15">
+        <f>COUNT(B15:CL15)</f>
+        <v>46</v>
+      </c>
+      <c r="CO15" s="18">
+        <f>AVERAGE(B15:CL15)</f>
+        <v>6.0652173913043477</v>
+      </c>
+      <c r="CP15">
         <f t="shared" si="2"/>
         <v>0.9573434129174403</v>
       </c>
-      <c r="CP15">
-        <v>1</v>
-      </c>
       <c r="CQ15">
+        <v>1</v>
+      </c>
+      <c r="CR15">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CR15">
+      <c r="CS15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -8047,31 +8074,34 @@
       <c r="CK16">
         <v>5.5</v>
       </c>
-      <c r="CM16">
-        <f>COUNT(B16:CK16)</f>
-        <v>43</v>
-      </c>
-      <c r="CN16" s="18">
-        <f>AVERAGE(B16:CK16)</f>
-        <v>4.9883720930232558</v>
-      </c>
-      <c r="CO16">
+      <c r="CL16">
+        <v>6</v>
+      </c>
+      <c r="CN16">
+        <f>COUNT(B16:CL16)</f>
+        <v>44</v>
+      </c>
+      <c r="CO16" s="18">
+        <f>AVERAGE(B16:CL16)</f>
+        <v>5.0113636363636367</v>
+      </c>
+      <c r="CP16">
         <f t="shared" si="2"/>
         <v>1.0645089158214895</v>
       </c>
-      <c r="CP16">
-        <v>1</v>
-      </c>
       <c r="CQ16">
+        <v>1</v>
+      </c>
+      <c r="CR16">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CR16">
+      <c r="CS16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -8324,31 +8354,31 @@
       <c r="CK17">
         <v>6.5</v>
       </c>
-      <c r="CM17">
+      <c r="CN17">
         <f t="shared" si="5"/>
         <v>36</v>
       </c>
-      <c r="CN17" s="18">
+      <c r="CO17" s="18">
         <f t="shared" si="6"/>
         <v>5.7361111111111107</v>
       </c>
-      <c r="CO17">
+      <c r="CP17">
         <f t="shared" si="2"/>
         <v>0.92956296268047622</v>
       </c>
-      <c r="CP17">
-        <v>1</v>
-      </c>
       <c r="CQ17">
+        <v>1</v>
+      </c>
+      <c r="CR17">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CR17">
+      <c r="CS17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -8601,31 +8631,34 @@
       <c r="CK18">
         <v>6</v>
       </c>
-      <c r="CM18">
+      <c r="CL18">
+        <v>6</v>
+      </c>
+      <c r="CN18">
         <f t="shared" si="5"/>
         <v>36</v>
       </c>
-      <c r="CN18" s="18">
+      <c r="CO18" s="18">
         <f t="shared" si="6"/>
         <v>5.6111111111111107</v>
       </c>
-      <c r="CO18">
+      <c r="CP18">
         <f t="shared" si="2"/>
         <v>1.0098256776095882</v>
       </c>
-      <c r="CP18">
-        <v>1</v>
-      </c>
       <c r="CQ18">
+        <v>1</v>
+      </c>
+      <c r="CR18">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="CR18">
+      <c r="CS18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -8887,31 +8920,31 @@
       <c r="CJ19">
         <v>5.5</v>
       </c>
-      <c r="CM19">
+      <c r="CN19">
         <f>COUNT(B19:CJ19)</f>
         <v>37</v>
       </c>
-      <c r="CN19" s="18">
+      <c r="CO19" s="18">
         <f>AVERAGE(B19:CJ19)</f>
         <v>5.2027027027027026</v>
       </c>
-      <c r="CO19">
+      <c r="CP19">
         <f t="shared" si="2"/>
         <v>1.3241383031954423</v>
       </c>
-      <c r="CP19">
-        <v>1</v>
-      </c>
       <c r="CQ19">
+        <v>1</v>
+      </c>
+      <c r="CR19">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CR19">
+      <c r="CS19">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>367</v>
       </c>
@@ -9158,31 +9191,31 @@
       <c r="CJ20">
         <v>6</v>
       </c>
-      <c r="CM20">
+      <c r="CN20">
         <f t="shared" si="5"/>
         <v>55</v>
       </c>
-      <c r="CN20" s="18">
+      <c r="CO20" s="18">
         <f t="shared" si="6"/>
         <v>6.3181818181818183</v>
       </c>
-      <c r="CO20">
+      <c r="CP20">
         <f t="shared" si="2"/>
         <v>1.1213885273224193</v>
       </c>
-      <c r="CP20">
+      <c r="CQ20">
         <v>0</v>
       </c>
-      <c r="CQ20">
+      <c r="CR20">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="CR20">
+      <c r="CS20">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -9426,31 +9459,31 @@
       <c r="CF21">
         <v>5.5</v>
       </c>
-      <c r="CM21">
+      <c r="CN21">
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="CN21" s="18">
+      <c r="CO21" s="18">
         <f t="shared" si="6"/>
         <v>5.6923076923076925</v>
       </c>
-      <c r="CO21">
+      <c r="CP21">
         <f t="shared" si="2"/>
         <v>0.84687340856573534</v>
       </c>
-      <c r="CP21">
+      <c r="CQ21">
         <v>0</v>
       </c>
-      <c r="CQ21">
+      <c r="CR21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR21">
+      <c r="CS21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -9694,31 +9727,31 @@
       <c r="CK22">
         <v>5.5</v>
       </c>
-      <c r="CM22">
+      <c r="CN22">
         <f t="shared" si="5"/>
         <v>38</v>
       </c>
-      <c r="CN22" s="18">
+      <c r="CO22" s="18">
         <f t="shared" si="6"/>
         <v>6.1578947368421053</v>
       </c>
-      <c r="CO22">
+      <c r="CP22">
         <f t="shared" si="2"/>
         <v>1.0973263770680928</v>
       </c>
-      <c r="CP22">
+      <c r="CQ22">
         <v>0</v>
       </c>
-      <c r="CQ22">
+      <c r="CR22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR22">
+      <c r="CS22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -9965,31 +9998,31 @@
       <c r="CI23">
         <v>5</v>
       </c>
-      <c r="CM23">
+      <c r="CN23">
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="CN23" s="18">
+      <c r="CO23" s="18">
         <f t="shared" si="6"/>
         <v>5.4</v>
       </c>
-      <c r="CO23">
+      <c r="CP23">
         <f t="shared" si="2"/>
         <v>0.71728150235677346</v>
       </c>
-      <c r="CP23">
+      <c r="CQ23">
         <v>0</v>
       </c>
-      <c r="CQ23">
+      <c r="CR23">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CR23">
+      <c r="CS23">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -10251,31 +10284,34 @@
       <c r="CK24">
         <v>6</v>
       </c>
-      <c r="CM24">
-        <f>COUNT(B24:CK24)</f>
-        <v>27</v>
-      </c>
-      <c r="CN24" s="18">
-        <f>AVERAGE(B24:CK24)</f>
-        <v>6.333333333333333</v>
-      </c>
-      <c r="CO24">
+      <c r="CL24">
+        <v>7.5</v>
+      </c>
+      <c r="CN24">
+        <f>COUNT(B24:CL24)</f>
+        <v>28</v>
+      </c>
+      <c r="CO24" s="18">
+        <f>AVERAGE(B24:CL24)</f>
+        <v>6.375</v>
+      </c>
+      <c r="CP24">
         <f t="shared" si="2"/>
         <v>0.90960483309014595</v>
       </c>
-      <c r="CP24">
-        <v>1</v>
-      </c>
       <c r="CQ24">
+        <v>1</v>
+      </c>
+      <c r="CR24">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CR24">
+      <c r="CS24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -10516,31 +10552,31 @@
       <c r="CB25" t="s">
         <v>26</v>
       </c>
-      <c r="CM25">
+      <c r="CN25">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="CN25" s="18">
+      <c r="CO25" s="18">
         <f t="shared" si="6"/>
         <v>5.7894736842105265</v>
       </c>
-      <c r="CO25">
+      <c r="CP25">
         <f t="shared" si="2"/>
         <v>1.3674366679797902</v>
       </c>
-      <c r="CP25">
+      <c r="CQ25">
         <v>0</v>
       </c>
-      <c r="CQ25">
+      <c r="CR25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR25">
+      <c r="CS25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>346</v>
       </c>
@@ -10781,31 +10817,31 @@
       <c r="CB26" t="s">
         <v>26</v>
       </c>
-      <c r="CM26">
+      <c r="CN26">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="CN26" s="18">
+      <c r="CO26" s="18">
         <f t="shared" si="6"/>
         <v>5.9444444444444446</v>
       </c>
-      <c r="CO26">
+      <c r="CP26">
         <f t="shared" si="2"/>
         <v>0.72535769855270305</v>
       </c>
-      <c r="CP26">
+      <c r="CQ26">
         <v>0</v>
       </c>
-      <c r="CQ26">
+      <c r="CR26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR26">
+      <c r="CS26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -11046,31 +11082,31 @@
       <c r="CB27" t="s">
         <v>26</v>
       </c>
-      <c r="CM27">
+      <c r="CN27">
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="CN27" s="18">
+      <c r="CO27" s="18">
         <f t="shared" si="6"/>
         <v>5.3235294117647056</v>
       </c>
-      <c r="CO27">
+      <c r="CP27">
         <f t="shared" si="2"/>
         <v>1.3456083251473603</v>
       </c>
-      <c r="CP27">
+      <c r="CQ27">
         <v>0</v>
       </c>
-      <c r="CQ27">
+      <c r="CR27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR27">
+      <c r="CS27">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -11311,31 +11347,31 @@
       <c r="CB28" t="s">
         <v>26</v>
       </c>
-      <c r="CM28">
+      <c r="CN28">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="CN28" s="18">
+      <c r="CO28" s="18">
         <f t="shared" si="6"/>
         <v>4.53125</v>
       </c>
-      <c r="CO28">
+      <c r="CP28">
         <f t="shared" si="2"/>
         <v>1.5434674167816653</v>
       </c>
-      <c r="CP28">
+      <c r="CQ28">
         <v>0</v>
       </c>
-      <c r="CQ28">
+      <c r="CR28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR28">
+      <c r="CS28">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -11576,31 +11612,34 @@
       <c r="CB29" t="s">
         <v>26</v>
       </c>
-      <c r="CM29">
+      <c r="CL29">
+        <v>6.5</v>
+      </c>
+      <c r="CN29">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="CN29" s="18">
+      <c r="CO29" s="18">
         <f t="shared" si="6"/>
         <v>6.65625</v>
       </c>
-      <c r="CO29">
+      <c r="CP29">
         <f t="shared" si="2"/>
         <v>0.74651970279870483</v>
       </c>
-      <c r="CP29">
+      <c r="CQ29">
         <v>0</v>
       </c>
-      <c r="CQ29">
+      <c r="CR29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR29">
+      <c r="CS29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -11841,31 +11880,31 @@
       <c r="CB30">
         <v>5.5</v>
       </c>
-      <c r="CM30">
+      <c r="CN30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="CN30" s="18">
+      <c r="CO30" s="18">
         <f t="shared" si="6"/>
         <v>3.8666666666666667</v>
       </c>
-      <c r="CO30">
+      <c r="CP30">
         <f t="shared" si="2"/>
         <v>2.3563490726929555</v>
       </c>
-      <c r="CP30">
+      <c r="CQ30">
         <v>0</v>
       </c>
-      <c r="CQ30">
+      <c r="CR30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR30">
+      <c r="CS30">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -12112,31 +12151,34 @@
       <c r="CI31">
         <v>4</v>
       </c>
-      <c r="CM31">
+      <c r="CL31">
+        <v>5.5</v>
+      </c>
+      <c r="CN31">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="CN31" s="18">
+      <c r="CO31" s="18">
         <f t="shared" si="6"/>
         <v>4.8214285714285712</v>
       </c>
-      <c r="CO31">
+      <c r="CP31">
         <f t="shared" si="2"/>
         <v>0.89335151148745728</v>
       </c>
-      <c r="CP31">
+      <c r="CQ31">
         <v>0</v>
       </c>
-      <c r="CQ31">
+      <c r="CR31">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CR31">
+      <c r="CS31">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -12377,31 +12419,31 @@
       <c r="CB32" t="s">
         <v>26</v>
       </c>
-      <c r="CM32">
+      <c r="CN32">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="CN32" s="18">
+      <c r="CO32" s="18">
         <f t="shared" si="6"/>
         <v>7.3461538461538458</v>
       </c>
-      <c r="CO32">
+      <c r="CP32">
         <f t="shared" si="2"/>
         <v>1.5191090506255012</v>
       </c>
-      <c r="CP32">
+      <c r="CQ32">
         <v>0</v>
       </c>
-      <c r="CQ32">
+      <c r="CR32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR32">
+      <c r="CS32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -12642,31 +12684,31 @@
       <c r="CB33" t="s">
         <v>26</v>
       </c>
-      <c r="CM33">
+      <c r="CN33">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="CN33" s="18">
+      <c r="CO33" s="18">
         <f t="shared" si="6"/>
         <v>4.6818181818181817</v>
       </c>
-      <c r="CO33">
+      <c r="CP33">
         <f t="shared" si="2"/>
         <v>0.81463879335344846</v>
       </c>
-      <c r="CP33">
+      <c r="CQ33">
         <v>0</v>
       </c>
-      <c r="CQ33">
+      <c r="CR33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR33">
+      <c r="CS33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -12910,31 +12952,31 @@
       <c r="CC34">
         <v>6</v>
       </c>
-      <c r="CM34">
+      <c r="CN34">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="CN34" s="18">
+      <c r="CO34" s="18">
         <f t="shared" si="6"/>
         <v>8.4499999999999993</v>
       </c>
-      <c r="CO34">
+      <c r="CP34">
         <f t="shared" si="2"/>
         <v>1.1890705987824657</v>
       </c>
-      <c r="CP34">
+      <c r="CQ34">
         <v>0</v>
       </c>
-      <c r="CQ34">
+      <c r="CR34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR34">
+      <c r="CS34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>343</v>
       </c>
@@ -13178,31 +13220,34 @@
       <c r="CK35">
         <v>6</v>
       </c>
-      <c r="CM35">
+      <c r="CL35">
+        <v>5.5</v>
+      </c>
+      <c r="CN35">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="CN35" s="18">
+      <c r="CO35" s="18">
         <f t="shared" si="6"/>
         <v>4.125</v>
       </c>
-      <c r="CO35">
+      <c r="CP35">
         <f t="shared" si="2"/>
         <v>1.7677669529663689</v>
       </c>
-      <c r="CP35">
+      <c r="CQ35">
         <v>0</v>
       </c>
-      <c r="CQ35">
+      <c r="CR35">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR35">
+      <c r="CS35">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>340</v>
       </c>
@@ -13443,31 +13488,34 @@
       <c r="CB36" t="s">
         <v>26</v>
       </c>
-      <c r="CM36">
+      <c r="CL36">
+        <v>6</v>
+      </c>
+      <c r="CN36">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CN36" s="18">
+      <c r="CO36" s="18">
         <f t="shared" si="6"/>
         <v>5.7142857142857144</v>
       </c>
-      <c r="CO36">
+      <c r="CP36">
         <f t="shared" si="2"/>
         <v>0.56694670951384085</v>
       </c>
-      <c r="CP36">
+      <c r="CQ36">
         <v>0</v>
       </c>
-      <c r="CQ36">
+      <c r="CR36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR36">
+      <c r="CS36">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>376</v>
       </c>
@@ -13708,31 +13756,31 @@
       <c r="CB37" t="s">
         <v>26</v>
       </c>
-      <c r="CM37">
+      <c r="CN37">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CN37" s="18">
+      <c r="CO37" s="18">
         <f t="shared" si="6"/>
         <v>5.7857142857142856</v>
       </c>
-      <c r="CO37">
+      <c r="CP37">
         <f t="shared" si="2"/>
         <v>0.4879500364742666</v>
       </c>
-      <c r="CP37">
+      <c r="CQ37">
         <v>0</v>
       </c>
-      <c r="CQ37">
+      <c r="CR37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR37">
+      <c r="CS37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>81</v>
       </c>
@@ -13991,31 +14039,34 @@
       <c r="CK38">
         <v>6.5</v>
       </c>
-      <c r="CM38">
-        <f>COUNT(B38:CK38)</f>
-        <v>10</v>
-      </c>
-      <c r="CN38" s="18">
-        <f>AVERAGE(B38:CK38)</f>
-        <v>6.45</v>
-      </c>
-      <c r="CO38">
+      <c r="CL38">
+        <v>6.5</v>
+      </c>
+      <c r="CN38">
+        <f>COUNT(B38:CL38)</f>
+        <v>11</v>
+      </c>
+      <c r="CO38" s="18">
+        <f>AVERAGE(B38:CL38)</f>
+        <v>6.4545454545454541</v>
+      </c>
+      <c r="CP38">
         <f t="shared" si="2"/>
         <v>0.90829510622924903</v>
       </c>
-      <c r="CP38">
-        <v>1</v>
-      </c>
       <c r="CQ38">
+        <v>1</v>
+      </c>
+      <c r="CR38">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CR38">
+      <c r="CS38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>378</v>
       </c>
@@ -14268,31 +14319,31 @@
       <c r="CK39">
         <v>5</v>
       </c>
-      <c r="CM39">
+      <c r="CN39">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="CN39" s="18">
+      <c r="CO39" s="18">
         <f t="shared" si="6"/>
         <v>5.166666666666667</v>
       </c>
-      <c r="CO39">
+      <c r="CP39">
         <f t="shared" si="2"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="CP39">
+      <c r="CQ39">
         <v>0</v>
       </c>
-      <c r="CQ39">
+      <c r="CR39">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="CR39">
+      <c r="CS39">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -14536,31 +14587,31 @@
       <c r="CH40">
         <v>6.5</v>
       </c>
-      <c r="CM40">
+      <c r="CN40">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CN40" s="18">
+      <c r="CO40" s="18">
         <f t="shared" si="6"/>
         <v>7.8</v>
       </c>
-      <c r="CO40">
+      <c r="CP40">
         <f t="shared" si="2"/>
         <v>1.0307764064044151</v>
       </c>
-      <c r="CP40">
+      <c r="CQ40">
         <v>0</v>
       </c>
-      <c r="CQ40">
+      <c r="CR40">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CR40">
+      <c r="CS40">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -14801,31 +14852,31 @@
       <c r="CB41" t="s">
         <v>26</v>
       </c>
-      <c r="CM41">
+      <c r="CN41">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CN41" s="18">
+      <c r="CO41" s="18">
         <f t="shared" si="6"/>
         <v>5.625</v>
       </c>
-      <c r="CO41">
+      <c r="CP41">
         <f t="shared" si="2"/>
         <v>0.9464847243000456</v>
       </c>
-      <c r="CP41">
+      <c r="CQ41">
         <v>0</v>
       </c>
-      <c r="CQ41">
+      <c r="CR41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR41">
+      <c r="CS41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>54</v>
       </c>
@@ -15066,31 +15117,31 @@
       <c r="CB42" t="s">
         <v>26</v>
       </c>
-      <c r="CM42">
+      <c r="CN42">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CN42" s="18">
+      <c r="CO42" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CO42">
+      <c r="CP42">
         <f t="shared" si="2"/>
         <v>1.0408329997330663</v>
       </c>
-      <c r="CP42">
+      <c r="CQ42">
         <v>0</v>
       </c>
-      <c r="CQ42">
+      <c r="CR42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR42">
+      <c r="CS42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -15331,31 +15382,31 @@
       <c r="CB43" t="s">
         <v>26</v>
       </c>
-      <c r="CM43">
+      <c r="CN43">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CN43" s="18">
+      <c r="CO43" s="18">
         <f t="shared" si="6"/>
         <v>1.375</v>
       </c>
-      <c r="CO43">
+      <c r="CP43">
         <f t="shared" si="2"/>
         <v>1.8874586088176875</v>
       </c>
-      <c r="CP43">
+      <c r="CQ43">
         <v>0</v>
       </c>
-      <c r="CQ43">
+      <c r="CR43">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR43">
+      <c r="CS43">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>344</v>
       </c>
@@ -15596,31 +15647,31 @@
       <c r="CB44" t="s">
         <v>26</v>
       </c>
-      <c r="CM44">
+      <c r="CN44">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CN44" s="18">
+      <c r="CO44" s="18">
         <f t="shared" si="6"/>
         <v>4.625</v>
       </c>
-      <c r="CO44">
+      <c r="CP44">
         <f t="shared" si="2"/>
         <v>1.4361406616345072</v>
       </c>
-      <c r="CP44">
+      <c r="CQ44">
         <v>0</v>
       </c>
-      <c r="CQ44">
+      <c r="CR44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR44">
+      <c r="CS44">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>361</v>
       </c>
@@ -15861,31 +15912,31 @@
       <c r="CB45" t="s">
         <v>26</v>
       </c>
-      <c r="CM45">
+      <c r="CN45">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CN45" s="18">
+      <c r="CO45" s="18">
         <f t="shared" si="6"/>
         <v>6.25</v>
       </c>
-      <c r="CO45">
+      <c r="CP45">
         <f t="shared" si="2"/>
         <v>0.8660254037844386</v>
       </c>
-      <c r="CP45">
+      <c r="CQ45">
         <v>0</v>
       </c>
-      <c r="CQ45">
+      <c r="CR45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR45">
+      <c r="CS45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>43</v>
       </c>
@@ -16126,31 +16177,31 @@
       <c r="CB46" t="s">
         <v>26</v>
       </c>
-      <c r="CM46">
+      <c r="CN46">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CN46" s="18">
+      <c r="CO46" s="18">
         <f t="shared" si="6"/>
         <v>2.875</v>
       </c>
-      <c r="CO46">
+      <c r="CP46">
         <f t="shared" si="2"/>
         <v>2.7801378862687129</v>
       </c>
-      <c r="CP46">
+      <c r="CQ46">
         <v>0</v>
       </c>
-      <c r="CQ46">
+      <c r="CR46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR46">
+      <c r="CS46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -16391,31 +16442,31 @@
       <c r="CB47" t="s">
         <v>26</v>
       </c>
-      <c r="CM47">
+      <c r="CN47">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CN47" s="18">
+      <c r="CO47" s="18">
         <f t="shared" si="6"/>
         <v>3.375</v>
       </c>
-      <c r="CO47">
+      <c r="CP47">
         <f t="shared" si="2"/>
         <v>0.47871355387816905</v>
       </c>
-      <c r="CP47">
+      <c r="CQ47">
         <v>0</v>
       </c>
-      <c r="CQ47">
+      <c r="CR47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR47">
+      <c r="CS47">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -16656,31 +16707,31 @@
       <c r="CB48" t="s">
         <v>26</v>
       </c>
-      <c r="CM48">
+      <c r="CN48">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CN48" s="18">
+      <c r="CO48" s="18">
         <f t="shared" si="6"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="CO48">
+      <c r="CP48">
         <f t="shared" si="2"/>
         <v>1.4433756729740652</v>
       </c>
-      <c r="CP48">
+      <c r="CQ48">
         <v>0</v>
       </c>
-      <c r="CQ48">
+      <c r="CR48">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR48">
+      <c r="CS48">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -16921,31 +16972,31 @@
       <c r="CB49" t="s">
         <v>26</v>
       </c>
-      <c r="CM49">
+      <c r="CN49">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CN49" s="18">
+      <c r="CO49" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CO49">
+      <c r="CP49">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-      <c r="CP49">
+      <c r="CQ49">
         <v>0</v>
       </c>
-      <c r="CQ49">
+      <c r="CR49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR49">
+      <c r="CS49">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -17186,31 +17237,31 @@
       <c r="CB50" t="s">
         <v>26</v>
       </c>
-      <c r="CM50">
+      <c r="CN50">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CN50" s="18">
+      <c r="CO50" s="18">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="CO50">
+      <c r="CP50">
         <f t="shared" si="2"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CP50">
+      <c r="CQ50">
         <v>0</v>
       </c>
-      <c r="CQ50">
+      <c r="CR50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR50">
+      <c r="CS50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>362</v>
       </c>
@@ -17454,31 +17505,31 @@
       <c r="CD51">
         <v>5.5</v>
       </c>
-      <c r="CM51">
+      <c r="CN51">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CN51" s="18">
+      <c r="CO51" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CO51">
+      <c r="CP51">
         <f t="shared" si="2"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CP51">
+      <c r="CQ51">
         <v>0</v>
       </c>
-      <c r="CQ51">
+      <c r="CR51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR51">
+      <c r="CS51">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>364</v>
       </c>
@@ -17719,31 +17770,34 @@
       <c r="CB52" t="s">
         <v>26</v>
       </c>
-      <c r="CM52">
+      <c r="CL52">
+        <v>6.5</v>
+      </c>
+      <c r="CN52">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CN52" s="18">
+      <c r="CO52" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="CO52">
+      <c r="CP52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CP52">
+      <c r="CQ52">
         <v>0</v>
       </c>
-      <c r="CQ52">
+      <c r="CR52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR52">
+      <c r="CS52">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -17984,31 +18038,31 @@
       <c r="CB53" t="s">
         <v>26</v>
       </c>
-      <c r="CM53">
+      <c r="CN53">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CN53" s="18">
+      <c r="CO53" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CO53">
+      <c r="CP53">
         <f t="shared" si="2"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CP53">
+      <c r="CQ53">
         <v>0</v>
       </c>
-      <c r="CQ53">
+      <c r="CR53">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR53">
+      <c r="CS53">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>339</v>
       </c>
@@ -18249,31 +18303,31 @@
       <c r="CB54" t="s">
         <v>26</v>
       </c>
-      <c r="CM54">
+      <c r="CN54">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CN54" s="18">
+      <c r="CO54" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CO54">
+      <c r="CP54">
         <f t="shared" si="2"/>
         <v>2.4748737341529163</v>
       </c>
-      <c r="CP54">
+      <c r="CQ54">
         <v>0</v>
       </c>
-      <c r="CQ54">
+      <c r="CR54">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR54">
+      <c r="CS54">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>342</v>
       </c>
@@ -18517,31 +18571,31 @@
       <c r="CJ55">
         <v>5.5</v>
       </c>
-      <c r="CM55">
+      <c r="CN55">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CN55" s="18">
+      <c r="CO55" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CO55">
+      <c r="CP55">
         <f t="shared" si="2"/>
         <v>2.1213203435596424</v>
       </c>
-      <c r="CP55">
+      <c r="CQ55">
         <v>0</v>
       </c>
-      <c r="CQ55">
+      <c r="CR55">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CR55">
+      <c r="CS55">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>369</v>
       </c>
@@ -18782,31 +18836,31 @@
       <c r="CB56" t="s">
         <v>26</v>
       </c>
-      <c r="CM56">
+      <c r="CN56">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CN56" s="18">
+      <c r="CO56" s="18">
         <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
-      <c r="CO56">
+      <c r="CP56">
         <f t="shared" si="2"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="CP56">
+      <c r="CQ56">
         <v>0</v>
       </c>
-      <c r="CQ56">
+      <c r="CR56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR56">
+      <c r="CS56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>52</v>
       </c>
@@ -19050,31 +19104,31 @@
       <c r="CG57">
         <v>6</v>
       </c>
-      <c r="CM57">
+      <c r="CN57">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CN57" s="18">
+      <c r="CO57" s="18">
         <f t="shared" si="6"/>
         <v>5.666666666666667</v>
       </c>
-      <c r="CO57">
+      <c r="CP57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CP57">
+      <c r="CQ57">
         <v>0</v>
       </c>
-      <c r="CQ57">
+      <c r="CR57">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CR57">
+      <c r="CS57">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>368</v>
       </c>
@@ -19318,31 +19372,31 @@
       <c r="CG58">
         <v>6</v>
       </c>
-      <c r="CM58">
+      <c r="CN58">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CN58" s="18">
+      <c r="CO58" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CO58">
+      <c r="CP58">
         <f t="shared" si="2"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CP58">
+      <c r="CQ58">
         <v>0</v>
       </c>
-      <c r="CQ58">
+      <c r="CR58">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CR58">
+      <c r="CS58">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>379</v>
       </c>
@@ -19583,31 +19637,31 @@
       <c r="CB59" t="s">
         <v>26</v>
       </c>
-      <c r="CM59">
+      <c r="CN59">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CN59" s="18">
+      <c r="CO59" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CO59">
+      <c r="CP59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CP59">
+      <c r="CQ59">
         <v>0</v>
       </c>
-      <c r="CQ59">
+      <c r="CR59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR59">
+      <c r="CS59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>391</v>
       </c>
@@ -19854,31 +19908,31 @@
       <c r="CH60">
         <v>7</v>
       </c>
-      <c r="CM60">
+      <c r="CN60">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CN60" s="18">
+      <c r="CO60" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CO60" t="e">
+      <c r="CP60" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CP60">
+      <c r="CQ60">
         <v>0</v>
       </c>
-      <c r="CQ60">
+      <c r="CR60">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CR60">
+      <c r="CS60">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>86</v>
       </c>
@@ -20119,31 +20173,31 @@
       <c r="CB61" t="s">
         <v>26</v>
       </c>
-      <c r="CM61">
+      <c r="CN61">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CN61" s="18">
+      <c r="CO61" s="18">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="CO61" t="str">
+      <c r="CP61" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="CP61">
+      <c r="CQ61">
         <v>0</v>
       </c>
-      <c r="CQ61">
+      <c r="CR61">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR61">
+      <c r="CS61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>77</v>
       </c>
@@ -20384,31 +20438,31 @@
       <c r="CB62" t="s">
         <v>26</v>
       </c>
-      <c r="CM62">
+      <c r="CN62">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CN62" s="18">
+      <c r="CO62" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CO62" t="str">
+      <c r="CP62" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="CP62">
+      <c r="CQ62">
         <v>0</v>
       </c>
-      <c r="CQ62">
+      <c r="CR62">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR62">
+      <c r="CS62">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>353</v>
       </c>
@@ -20649,31 +20703,31 @@
       <c r="CB63" t="s">
         <v>26</v>
       </c>
-      <c r="CM63">
+      <c r="CN63">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CN63" s="18">
+      <c r="CO63" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CO63" t="str">
+      <c r="CP63" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="CP63">
+      <c r="CQ63">
         <v>0</v>
       </c>
-      <c r="CQ63">
+      <c r="CR63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR63">
+      <c r="CS63">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>80</v>
       </c>
@@ -20914,31 +20968,31 @@
       <c r="CB64" t="s">
         <v>26</v>
       </c>
-      <c r="CM64">
+      <c r="CN64">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CN64" s="18">
+      <c r="CO64" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CO64" t="str">
+      <c r="CP64" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="CP64">
+      <c r="CQ64">
         <v>0</v>
       </c>
-      <c r="CQ64">
+      <c r="CR64">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR64">
+      <c r="CS64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>47</v>
       </c>
@@ -21179,31 +21233,31 @@
       <c r="CB65" t="s">
         <v>26</v>
       </c>
-      <c r="CM65">
+      <c r="CN65">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CN65" s="18">
+      <c r="CO65" s="18">
         <f t="shared" si="6"/>
         <v>3.5</v>
       </c>
-      <c r="CO65" t="str">
+      <c r="CP65" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="CP65">
+      <c r="CQ65">
         <v>0</v>
       </c>
-      <c r="CQ65">
+      <c r="CR65">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CR65">
+      <c r="CS65">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>389</v>
       </c>
@@ -21447,31 +21501,31 @@
       <c r="CH66">
         <v>5</v>
       </c>
-      <c r="CM66">
+      <c r="CN66">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CN66" s="18">
+      <c r="CO66" s="18">
         <f t="shared" si="6"/>
         <v>4.25</v>
       </c>
-      <c r="CO66" t="e">
+      <c r="CP66" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CP66">
+      <c r="CQ66">
         <v>0</v>
       </c>
-      <c r="CQ66">
+      <c r="CR66">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CR66">
+      <c r="CS66">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -21712,31 +21766,31 @@
       <c r="CB67" t="s">
         <v>26</v>
       </c>
-      <c r="CM67">
-        <f t="shared" ref="CM67:CM82" si="7">COUNT(B67:CI67)</f>
-        <v>1</v>
-      </c>
-      <c r="CN67" s="18">
-        <f t="shared" ref="CN67:CN82" si="8">AVERAGE(B67:CI67)</f>
+      <c r="CN67">
+        <f t="shared" ref="CN67:CN82" si="7">COUNT(B67:CI67)</f>
+        <v>1</v>
+      </c>
+      <c r="CO67" s="18">
+        <f t="shared" ref="CO67:CO82" si="8">AVERAGE(B67:CI67)</f>
         <v>3</v>
       </c>
-      <c r="CO67" t="str">
-        <f t="shared" ref="CO67:CO82" si="9">IF(CM67&gt;1,_xlfn.STDEV.S(B67:CF67),"")</f>
+      <c r="CP67" t="str">
+        <f t="shared" ref="CP67:CP82" si="9">IF(CN67&gt;1,_xlfn.STDEV.S(B67:CF67),"")</f>
         <v/>
       </c>
-      <c r="CP67">
+      <c r="CQ67">
         <v>0</v>
       </c>
-      <c r="CQ67">
-        <f t="shared" ref="CQ67:CQ83" si="10">COUNT(CG67:CJ67)</f>
+      <c r="CR67">
+        <f t="shared" ref="CR67:CR83" si="10">COUNT(CG67:CJ67)</f>
         <v>0</v>
       </c>
-      <c r="CR67">
-        <f t="shared" ref="CR67:CR82" si="11">IF(CP67=0,CQ67,0)</f>
+      <c r="CS67">
+        <f t="shared" ref="CS67:CS82" si="11">IF(CQ67=0,CR67,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>345</v>
       </c>
@@ -21986,31 +22040,34 @@
       <c r="CK68">
         <v>3.5</v>
       </c>
-      <c r="CM68">
+      <c r="CL68">
+        <v>5.5</v>
+      </c>
+      <c r="CN68">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="CN68" s="18">
+      <c r="CO68" s="18">
         <f t="shared" si="8"/>
         <v>4.25</v>
       </c>
-      <c r="CO68" t="e">
+      <c r="CP68" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CP68">
+      <c r="CQ68">
         <v>0</v>
       </c>
-      <c r="CQ68">
+      <c r="CR68">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="CR68">
+      <c r="CS68">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>347</v>
       </c>
@@ -22251,31 +22308,31 @@
       <c r="CB69" t="s">
         <v>26</v>
       </c>
-      <c r="CM69">
+      <c r="CN69">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN69" s="18">
+      <c r="CO69" s="18">
         <f t="shared" si="8"/>
         <v>6.5</v>
       </c>
-      <c r="CO69" t="str">
+      <c r="CP69" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP69">
+      <c r="CQ69">
         <v>0</v>
       </c>
-      <c r="CQ69">
+      <c r="CR69">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR69">
+      <c r="CS69">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>350</v>
       </c>
@@ -22516,31 +22573,31 @@
       <c r="CB70" t="s">
         <v>26</v>
       </c>
-      <c r="CM70">
+      <c r="CN70">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN70" s="18">
+      <c r="CO70" s="18">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="CO70" t="str">
+      <c r="CP70" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP70">
+      <c r="CQ70">
         <v>0</v>
       </c>
-      <c r="CQ70">
+      <c r="CR70">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR70">
+      <c r="CS70">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>351</v>
       </c>
@@ -22781,31 +22838,31 @@
       <c r="CB71" t="s">
         <v>26</v>
       </c>
-      <c r="CM71">
+      <c r="CN71">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN71" s="18">
+      <c r="CO71" s="18">
         <f t="shared" si="8"/>
         <v>6.5</v>
       </c>
-      <c r="CO71" t="str">
+      <c r="CP71" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP71">
+      <c r="CQ71">
         <v>0</v>
       </c>
-      <c r="CQ71">
+      <c r="CR71">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR71">
+      <c r="CS71">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>352</v>
       </c>
@@ -23046,31 +23103,31 @@
       <c r="CB72" t="s">
         <v>26</v>
       </c>
-      <c r="CM72">
+      <c r="CN72">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN72" s="18">
+      <c r="CO72" s="18">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="CO72" t="str">
+      <c r="CP72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP72">
+      <c r="CQ72">
         <v>0</v>
       </c>
-      <c r="CQ72">
+      <c r="CR72">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR72">
+      <c r="CS72">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>354</v>
       </c>
@@ -23311,31 +23368,31 @@
       <c r="CB73" t="s">
         <v>26</v>
       </c>
-      <c r="CM73">
+      <c r="CN73">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN73" s="18">
+      <c r="CO73" s="18">
         <f t="shared" si="8"/>
         <v>5.5</v>
       </c>
-      <c r="CO73" t="str">
+      <c r="CP73" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP73">
+      <c r="CQ73">
         <v>0</v>
       </c>
-      <c r="CQ73">
+      <c r="CR73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR73">
+      <c r="CS73">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>365</v>
       </c>
@@ -23576,31 +23633,31 @@
       <c r="CB74" t="s">
         <v>26</v>
       </c>
-      <c r="CM74">
+      <c r="CN74">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN74" s="18">
+      <c r="CO74" s="18">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="CO74" t="str">
+      <c r="CP74" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP74">
+      <c r="CQ74">
         <v>0</v>
       </c>
-      <c r="CQ74">
+      <c r="CR74">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR74">
+      <c r="CS74">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>366</v>
       </c>
@@ -23841,31 +23898,31 @@
       <c r="CB75" t="s">
         <v>26</v>
       </c>
-      <c r="CM75">
+      <c r="CN75">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN75" s="18">
+      <c r="CO75" s="18">
         <f t="shared" si="8"/>
         <v>2.5</v>
       </c>
-      <c r="CO75" t="str">
+      <c r="CP75" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP75">
+      <c r="CQ75">
         <v>0</v>
       </c>
-      <c r="CQ75">
+      <c r="CR75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR75">
+      <c r="CS75">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>374</v>
       </c>
@@ -24106,31 +24163,31 @@
       <c r="CB76" t="s">
         <v>26</v>
       </c>
-      <c r="CM76">
+      <c r="CN76">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN76" s="18">
+      <c r="CO76" s="18">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="CO76" t="str">
+      <c r="CP76" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP76">
+      <c r="CQ76">
         <v>0</v>
       </c>
-      <c r="CQ76">
+      <c r="CR76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR76">
+      <c r="CS76">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>375</v>
       </c>
@@ -24371,31 +24428,31 @@
       <c r="CB77" t="s">
         <v>26</v>
       </c>
-      <c r="CM77">
+      <c r="CN77">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN77" s="18">
+      <c r="CO77" s="18">
         <f t="shared" si="8"/>
         <v>5.5</v>
       </c>
-      <c r="CO77" t="str">
+      <c r="CP77" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP77">
+      <c r="CQ77">
         <v>0</v>
       </c>
-      <c r="CQ77">
+      <c r="CR77">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR77">
+      <c r="CS77">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>377</v>
       </c>
@@ -24636,31 +24693,31 @@
       <c r="CB78" t="s">
         <v>26</v>
       </c>
-      <c r="CM78">
+      <c r="CN78">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN78" s="18">
+      <c r="CO78" s="18">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="CO78" t="str">
+      <c r="CP78" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP78">
+      <c r="CQ78">
         <v>0</v>
       </c>
-      <c r="CQ78">
+      <c r="CR78">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR78">
+      <c r="CS78">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>381</v>
       </c>
@@ -24901,31 +24958,31 @@
       <c r="CB79" t="s">
         <v>26</v>
       </c>
-      <c r="CM79">
+      <c r="CN79">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN79" s="18">
+      <c r="CO79" s="18">
         <f t="shared" si="8"/>
         <v>5.5</v>
       </c>
-      <c r="CO79" t="str">
+      <c r="CP79" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP79">
+      <c r="CQ79">
         <v>0</v>
       </c>
-      <c r="CQ79">
+      <c r="CR79">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR79">
+      <c r="CS79">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>382</v>
       </c>
@@ -25166,31 +25223,31 @@
       <c r="CB80" t="s">
         <v>26</v>
       </c>
-      <c r="CM80">
+      <c r="CN80">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN80" s="18">
+      <c r="CO80" s="18">
         <f t="shared" si="8"/>
         <v>5.5</v>
       </c>
-      <c r="CO80" t="str">
+      <c r="CP80" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP80">
+      <c r="CQ80">
         <v>0</v>
       </c>
-      <c r="CQ80">
+      <c r="CR80">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CR80">
+      <c r="CS80">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>388</v>
       </c>
@@ -25440,31 +25497,31 @@
       <c r="CJ81">
         <v>7</v>
       </c>
-      <c r="CM81">
+      <c r="CN81">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="CN81" s="18">
+      <c r="CO81" s="18">
         <f t="shared" si="8"/>
         <v>6.5</v>
       </c>
-      <c r="CO81" t="e">
+      <c r="CP81" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CP81">
+      <c r="CQ81">
         <v>0</v>
       </c>
-      <c r="CQ81">
+      <c r="CR81">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="CR81">
+      <c r="CS81">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>390</v>
       </c>
@@ -25708,31 +25765,31 @@
       <c r="CH82">
         <v>7.5</v>
       </c>
-      <c r="CM82">
+      <c r="CN82">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CN82" s="18">
+      <c r="CO82" s="18">
         <f t="shared" si="8"/>
         <v>7.5</v>
       </c>
-      <c r="CO82" t="str">
+      <c r="CP82" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CP82">
+      <c r="CQ82">
         <v>0</v>
       </c>
-      <c r="CQ82">
+      <c r="CR82">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR82">
+      <c r="CS82">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>392</v>
       </c>
@@ -25976,37 +26033,37 @@
       <c r="CI83">
         <v>7</v>
       </c>
-      <c r="CM83">
-        <f t="shared" ref="CM83" si="12">COUNT(B83:CI83)</f>
-        <v>1</v>
-      </c>
-      <c r="CN83" s="18">
-        <f t="shared" ref="CN83" si="13">AVERAGE(B83:CI83)</f>
+      <c r="CN83">
+        <f t="shared" ref="CN83" si="12">COUNT(B83:CI83)</f>
+        <v>1</v>
+      </c>
+      <c r="CO83" s="18">
+        <f t="shared" ref="CO83" si="13">AVERAGE(B83:CI83)</f>
         <v>7</v>
       </c>
-      <c r="CO83" t="str">
-        <f t="shared" ref="CO83" si="14">IF(CM83&gt;1,_xlfn.STDEV.S(B83:CF83),"")</f>
+      <c r="CP83" t="str">
+        <f t="shared" ref="CP83" si="14">IF(CN83&gt;1,_xlfn.STDEV.S(B83:CF83),"")</f>
         <v/>
       </c>
-      <c r="CP83">
+      <c r="CQ83">
         <v>0</v>
       </c>
-      <c r="CQ83">
+      <c r="CR83">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR83">
-        <f t="shared" ref="CR83" si="15">IF(CP83=0,CQ83,0)</f>
+      <c r="CS83">
+        <f t="shared" ref="CS83" si="15">IF(CQ83=0,CR83,0)</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CR83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
-    <sortState ref="A2:CR80">
-      <sortCondition descending="1" ref="CP1:CP80"/>
+  <autoFilter ref="A1:CS83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
+    <sortState ref="A2:CS80">
+      <sortCondition descending="1" ref="CQ1:CQ80"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="CM2:CM83">
+  <conditionalFormatting sqref="CN2:CN83">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -26018,7 +26075,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CO2:CO83">
+  <conditionalFormatting sqref="CP2:CP83">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -26030,7 +26087,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CM2:CM83">
+  <conditionalFormatting sqref="CN2:CN83">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -26042,7 +26099,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CN2:CN83">
+  <conditionalFormatting sqref="CO2:CO83">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
@@ -26054,7 +26111,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CN2:CN83">
+  <conditionalFormatting sqref="CO2:CO83">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
@@ -26066,7 +26123,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CM2:CM83">
+  <conditionalFormatting sqref="CN2:CN83">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -26078,7 +26135,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CN2:CN83">
+  <conditionalFormatting sqref="CO2:CO83">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -26090,7 +26147,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL79">
+  <conditionalFormatting sqref="CM2:CM79">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -26102,7 +26159,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL67">
+  <conditionalFormatting sqref="CM2:CM67">
     <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
@@ -26114,7 +26171,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL67">
+  <conditionalFormatting sqref="CM2:CM67">
     <cfRule type="colorScale" priority="127">
       <colorScale>
         <cfvo type="min"/>
@@ -26126,7 +26183,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL67">
+  <conditionalFormatting sqref="CM2:CM67">
     <cfRule type="colorScale" priority="129">
       <colorScale>
         <cfvo type="min"/>
@@ -26138,7 +26195,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:CK83">
+  <conditionalFormatting sqref="B2:CL83">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -31228,7 +31285,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X258"/>
+  <dimension ref="A1:X261"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -44048,6 +44105,156 @@
         <v>343</v>
       </c>
     </row>
+    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A259" s="14">
+        <v>46092</v>
+      </c>
+      <c r="B259" s="3">
+        <v>4</v>
+      </c>
+      <c r="C259" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E259" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="F259" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H259" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I259" s="9">
+        <v>6</v>
+      </c>
+      <c r="J259" s="10">
+        <v>2</v>
+      </c>
+      <c r="K259" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L259" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M259" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="N259" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="O259" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="P259" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A260" s="14">
+        <v>46092</v>
+      </c>
+      <c r="B260" s="3">
+        <v>3</v>
+      </c>
+      <c r="C260" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D260" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E260" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="F260" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G260" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H260" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I260" s="11">
+        <v>5</v>
+      </c>
+      <c r="J260" s="2">
+        <v>2</v>
+      </c>
+      <c r="K260" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L260" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M260" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N260" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="O260" s="61" t="s">
+        <v>343</v>
+      </c>
+      <c r="P260" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A261" s="14">
+        <v>46092</v>
+      </c>
+      <c r="B261" s="5">
+        <v>4</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G261" s="61" t="s">
+        <v>343</v>
+      </c>
+      <c r="H261" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I261" s="5">
+        <v>3</v>
+      </c>
+      <c r="J261" s="8">
+        <v>2</v>
+      </c>
+      <c r="K261" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L261" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M261" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="N261" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="O261" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="P261" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -44055,7 +44262,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:BR83"/>
+  <dimension ref="A1:BS83"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -44064,10 +44271,10 @@
     <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="70" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="71" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -44278,8 +44485,11 @@
       <c r="BR1" s="1">
         <v>46085</v>
       </c>
-    </row>
-    <row r="2" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS1" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -44328,8 +44538,11 @@
       <c r="BR2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -44337,7 +44550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -44375,12 +44588,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -44388,7 +44601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>364</v>
       </c>
@@ -44398,8 +44611,11 @@
       <c r="AQ7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -44407,7 +44623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>353</v>
       </c>
@@ -44415,22 +44631,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="11" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="13" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>362</v>
       </c>
@@ -44438,12 +44654,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -44493,7 +44709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -44531,7 +44747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>378</v>
       </c>
@@ -44542,7 +44758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -44556,7 +44772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -44609,7 +44825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -44695,7 +44911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>392</v>
       </c>
@@ -44703,7 +44919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -44749,8 +44965,11 @@
       <c r="BR22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>375</v>
       </c>
@@ -44758,7 +44977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -44913,7 +45132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>342</v>
       </c>
@@ -44930,17 +45149,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="28" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -44954,7 +45173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -45058,7 +45277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>361</v>
       </c>
@@ -45075,7 +45294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>390</v>
       </c>
@@ -45083,7 +45302,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>1</v>
       </c>
@@ -45214,7 +45433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>351</v>
       </c>
@@ -45222,7 +45441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -45358,8 +45577,11 @@
       <c r="BR34">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>381</v>
       </c>
@@ -45367,7 +45589,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -45486,7 +45708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -45494,7 +45716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>61</v>
       </c>
@@ -45502,7 +45724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>374</v>
       </c>
@@ -45510,7 +45732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -45628,8 +45850,11 @@
       <c r="BQ40">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -45637,7 +45862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -45657,7 +45882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -45665,7 +45890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>368</v>
       </c>
@@ -45679,7 +45904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>345</v>
       </c>
@@ -45689,8 +45914,11 @@
       <c r="BR45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>343</v>
       </c>
@@ -45700,8 +45928,11 @@
       <c r="BR46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>344</v>
       </c>
@@ -45715,7 +45946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -45846,7 +46077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -45902,12 +46133,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="51" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -45924,12 +46155,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="53" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -46038,8 +46269,11 @@
       <c r="BR53">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>369</v>
       </c>
@@ -46047,7 +46281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>388</v>
       </c>
@@ -46061,7 +46295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -46072,7 +46306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>340</v>
       </c>
@@ -46095,17 +46329,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="59" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -46200,12 +46434,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>81</v>
       </c>
@@ -46227,8 +46461,11 @@
       <c r="BR62">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -46251,12 +46488,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="65" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>22</v>
       </c>
@@ -46287,8 +46524,11 @@
       <c r="BE65">
         <v>6</v>
       </c>
-    </row>
-    <row r="66" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>376</v>
       </c>
@@ -46311,7 +46551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>44</v>
       </c>
@@ -46364,7 +46604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>379</v>
       </c>
@@ -46375,7 +46615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -46392,12 +46632,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="71" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>82</v>
       </c>
@@ -46537,7 +46777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>49</v>
       </c>
@@ -46545,12 +46785,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="74" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -46564,7 +46804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -46727,8 +46967,11 @@
       <c r="BR75">
         <v>3</v>
       </c>
-    </row>
-    <row r="76" spans="1:70" x14ac:dyDescent="0.35">
+      <c r="BS75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>45</v>
       </c>
@@ -46739,7 +46982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>367</v>
       </c>
@@ -46813,7 +47056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>352</v>
       </c>
@@ -46821,12 +47064,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:70" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="80" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -46840,7 +47083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:67" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>86</v>
       </c>
@@ -46848,7 +47091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -47020,8 +47263,11 @@
       <c r="BO82">
         <v>3</v>
       </c>
-    </row>
-    <row r="83" spans="1:67" hidden="1" x14ac:dyDescent="0.35">
+      <c r="BS82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>47</v>
       </c>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="14_{A1B3B906-E661-414D-BCC5-34D6B6413D4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{8696725A-FD65-4510-83C1-53C433FC3300}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="14_{A1B3B906-E661-414D-BCC5-34D6B6413D4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{AA1386FF-E535-4F2F-9B22-22C1377FBFB3}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,14 +26,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'extrato 2024'!$A$1:$C$187</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CS$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CU$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9147" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9215" uniqueCount="393">
   <si>
     <t>Jogador</t>
   </si>
@@ -1981,7 +1981,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2090,6 +2090,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3477,7 +3480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CS83"/>
+  <dimension ref="A1:CU83"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
@@ -3502,10 +3505,10 @@
     <col min="50" max="58" width="9.54296875" customWidth="1"/>
     <col min="59" max="65" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
-    <col min="67" max="91" width="11" customWidth="1"/>
+    <col min="67" max="93" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3776,27 +3779,33 @@
       <c r="CL1" s="1">
         <v>46092</v>
       </c>
-      <c r="CM1" s="1"/>
-      <c r="CN1" t="s">
+      <c r="CM1" s="1">
+        <v>46099</v>
+      </c>
+      <c r="CN1" s="1">
+        <v>46106</v>
+      </c>
+      <c r="CO1" s="1"/>
+      <c r="CP1" t="s">
         <v>57</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CQ1" t="s">
         <v>58</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CR1" t="s">
         <v>59</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CS1" t="s">
         <v>62</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CT1" t="s">
         <v>386</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CU1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4064,31 +4073,37 @@
       <c r="CL2">
         <v>5.5</v>
       </c>
+      <c r="CM2">
+        <v>5.5</v>
+      </c>
       <c r="CN2">
-        <f>COUNT(B2:CL2)</f>
-        <v>83</v>
-      </c>
-      <c r="CO2" s="18">
-        <f>AVERAGE(B2:CL2)</f>
-        <v>6.0361445783132526</v>
+        <v>6</v>
       </c>
       <c r="CP2">
-        <f t="shared" ref="CP2" si="0">IF(CN2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
+        <f>COUNT(B2:CN2)</f>
+        <v>85</v>
+      </c>
+      <c r="CQ2" s="18">
+        <f>AVERAGE(B2:CN2)</f>
+        <v>6.0294117647058822</v>
+      </c>
+      <c r="CR2">
+        <f t="shared" ref="CR2" si="0">IF(CP2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
         <v>1.2512468149547391</v>
       </c>
-      <c r="CQ2">
-        <v>1</v>
-      </c>
-      <c r="CR2">
+      <c r="CS2">
+        <v>1</v>
+      </c>
+      <c r="CT2">
         <f>COUNT(CG2:CJ2)</f>
         <v>4</v>
       </c>
-      <c r="CS2">
-        <f t="shared" ref="CS2" si="1">IF(CQ2=0,CR2,0)</f>
+      <c r="CU2">
+        <f t="shared" ref="CU2" si="1">IF(CS2=0,CT2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4356,31 +4371,37 @@
       <c r="CK3">
         <v>5</v>
       </c>
+      <c r="CM3">
+        <v>6</v>
+      </c>
       <c r="CN3">
+        <v>5.5</v>
+      </c>
+      <c r="CP3">
         <f>COUNT(B3:CK3)</f>
         <v>79</v>
       </c>
-      <c r="CO3" s="18">
+      <c r="CQ3" s="18">
         <f>AVERAGE(B3:CK3)</f>
         <v>5.6518987341772151</v>
       </c>
-      <c r="CP3">
-        <f t="shared" ref="CP3:CP66" si="2">IF(CN3&gt;1,_xlfn.STDEV.S(B3:CF3),"")</f>
+      <c r="CR3">
+        <f t="shared" ref="CR3:CR66" si="2">IF(CP3&gt;1,_xlfn.STDEV.S(B3:CF3),"")</f>
         <v>1.0518094984498128</v>
       </c>
-      <c r="CQ3">
-        <v>1</v>
-      </c>
-      <c r="CR3">
-        <f t="shared" ref="CR3:CR66" si="3">COUNT(CG3:CJ3)</f>
+      <c r="CS3">
+        <v>1</v>
+      </c>
+      <c r="CT3">
+        <f t="shared" ref="CT3:CT66" si="3">COUNT(CG3:CJ3)</f>
         <v>4</v>
       </c>
-      <c r="CS3">
-        <f t="shared" ref="CS3:CS66" si="4">IF(CQ3=0,CR3,0)</f>
+      <c r="CU3">
+        <f t="shared" ref="CU3:CU66" si="4">IF(CS3=0,CT3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4642,31 +4663,31 @@
       <c r="CI4">
         <v>5.5</v>
       </c>
-      <c r="CN4">
-        <f t="shared" ref="CN4:CN66" si="5">COUNT(B4:CI4)</f>
+      <c r="CP4">
+        <f t="shared" ref="CP4:CP66" si="5">COUNT(B4:CI4)</f>
         <v>72</v>
       </c>
-      <c r="CO4" s="18">
-        <f t="shared" ref="CO4:CO66" si="6">AVERAGE(B4:CI4)</f>
+      <c r="CQ4" s="18">
+        <f t="shared" ref="CQ4:CQ66" si="6">AVERAGE(B4:CI4)</f>
         <v>5.708333333333333</v>
       </c>
-      <c r="CP4">
+      <c r="CR4">
         <f t="shared" si="2"/>
         <v>0.96435844595057774</v>
       </c>
-      <c r="CQ4">
-        <v>1</v>
-      </c>
-      <c r="CR4">
+      <c r="CS4">
+        <v>1</v>
+      </c>
+      <c r="CT4">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CS4">
+      <c r="CU4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -4916,31 +4937,31 @@
       <c r="CE5">
         <v>5</v>
       </c>
-      <c r="CN5">
+      <c r="CP5">
         <f t="shared" si="5"/>
         <v>68</v>
       </c>
-      <c r="CO5" s="18">
+      <c r="CQ5" s="18">
         <f t="shared" si="6"/>
         <v>6.4191176470588234</v>
       </c>
-      <c r="CP5">
+      <c r="CR5">
         <f t="shared" si="2"/>
         <v>1.1769245721961776</v>
       </c>
-      <c r="CQ5">
+      <c r="CS5">
         <v>0</v>
       </c>
-      <c r="CR5">
+      <c r="CT5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS5">
+      <c r="CU5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -5193,31 +5214,31 @@
       <c r="CI6">
         <v>5.5</v>
       </c>
-      <c r="CN6">
+      <c r="CP6">
         <f t="shared" si="5"/>
         <v>67</v>
       </c>
-      <c r="CO6" s="18">
+      <c r="CQ6" s="18">
         <f t="shared" si="6"/>
         <v>5.9701492537313436</v>
       </c>
-      <c r="CP6">
+      <c r="CR6">
         <f t="shared" si="2"/>
         <v>0.96648378625350351</v>
       </c>
-      <c r="CQ6">
+      <c r="CS6">
         <v>0</v>
       </c>
-      <c r="CR6">
+      <c r="CT6">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CS6">
+      <c r="CU6">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -5483,30 +5504,33 @@
         <v>6</v>
       </c>
       <c r="CN7">
+        <v>6</v>
+      </c>
+      <c r="CP7">
         <f>COUNT(B7:CL7)</f>
         <v>70</v>
       </c>
-      <c r="CO7" s="18">
+      <c r="CQ7" s="18">
         <f>AVERAGE(B7:CL7)</f>
         <v>6.6142857142857139</v>
       </c>
-      <c r="CP7">
+      <c r="CR7">
         <f t="shared" si="2"/>
         <v>0.9419445925236869</v>
       </c>
-      <c r="CQ7">
-        <v>1</v>
-      </c>
-      <c r="CR7">
+      <c r="CS7">
+        <v>1</v>
+      </c>
+      <c r="CT7">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CS7">
+      <c r="CU7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -5774,31 +5798,31 @@
       <c r="CL8">
         <v>6.5</v>
       </c>
-      <c r="CN8">
+      <c r="CP8">
         <f>COUNT(B8:CL8)</f>
         <v>70</v>
       </c>
-      <c r="CO8" s="18">
+      <c r="CQ8" s="18">
         <f>AVERAGE(B8:CL8)</f>
         <v>6.6071428571428568</v>
       </c>
-      <c r="CP8">
+      <c r="CR8">
         <f t="shared" si="2"/>
         <v>1.0570846156365068</v>
       </c>
-      <c r="CQ8">
-        <v>1</v>
-      </c>
-      <c r="CR8">
+      <c r="CS8">
+        <v>1</v>
+      </c>
+      <c r="CT8">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CS8">
+      <c r="CU8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -6066,31 +6090,31 @@
       <c r="CL9">
         <v>5.5</v>
       </c>
-      <c r="CN9">
+      <c r="CP9">
         <f>COUNT(B9:CL9)</f>
         <v>71</v>
       </c>
-      <c r="CO9" s="18">
+      <c r="CQ9" s="18">
         <f>AVERAGE(B9:CL9)</f>
         <v>7.267605633802817</v>
       </c>
-      <c r="CP9">
+      <c r="CR9">
         <f t="shared" si="2"/>
         <v>1.1294250579557983</v>
       </c>
-      <c r="CQ9">
-        <v>1</v>
-      </c>
-      <c r="CR9">
+      <c r="CS9">
+        <v>1</v>
+      </c>
+      <c r="CT9">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CS9">
+      <c r="CU9">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -6349,31 +6373,37 @@
       <c r="CK10">
         <v>5.5</v>
       </c>
+      <c r="CM10">
+        <v>7</v>
+      </c>
       <c r="CN10">
+        <v>7.5</v>
+      </c>
+      <c r="CP10">
         <f t="shared" si="5"/>
         <v>62</v>
       </c>
-      <c r="CO10" s="18">
+      <c r="CQ10" s="18">
         <f t="shared" si="6"/>
         <v>5.717741935483871</v>
       </c>
-      <c r="CP10">
+      <c r="CR10">
         <f t="shared" si="2"/>
         <v>1.3617531291315086</v>
       </c>
-      <c r="CQ10">
-        <v>1</v>
-      </c>
-      <c r="CR10">
+      <c r="CS10">
+        <v>1</v>
+      </c>
+      <c r="CT10">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CS10">
+      <c r="CU10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6635,31 +6665,37 @@
       <c r="CL11">
         <v>6.5</v>
       </c>
+      <c r="CM11">
+        <v>6.5</v>
+      </c>
       <c r="CN11">
+        <v>7</v>
+      </c>
+      <c r="CP11">
         <f t="shared" si="5"/>
         <v>59</v>
       </c>
-      <c r="CO11" s="18">
+      <c r="CQ11" s="18">
         <f t="shared" si="6"/>
         <v>6.6779661016949152</v>
       </c>
-      <c r="CP11">
+      <c r="CR11">
         <f t="shared" si="2"/>
         <v>1.0072574989410263</v>
       </c>
-      <c r="CQ11">
-        <v>1</v>
-      </c>
-      <c r="CR11">
+      <c r="CS11">
+        <v>1</v>
+      </c>
+      <c r="CT11">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="CS11">
+      <c r="CU11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -6924,31 +6960,37 @@
       <c r="CL12">
         <v>5.5</v>
       </c>
+      <c r="CM12">
+        <v>6</v>
+      </c>
       <c r="CN12">
-        <f>COUNT(B12:CL12)</f>
-        <v>56</v>
-      </c>
-      <c r="CO12" s="18">
-        <f>AVERAGE(B12:CL12)</f>
-        <v>5.4821428571428568</v>
+        <v>6.5</v>
       </c>
       <c r="CP12">
+        <f>COUNT(B12:CN12)</f>
+        <v>58</v>
+      </c>
+      <c r="CQ12" s="18">
+        <f>AVERAGE(B12:CN12)</f>
+        <v>5.5086206896551726</v>
+      </c>
+      <c r="CR12">
         <f t="shared" si="2"/>
         <v>1.0254583642020354</v>
       </c>
-      <c r="CQ12">
-        <v>1</v>
-      </c>
-      <c r="CR12">
+      <c r="CS12">
+        <v>1</v>
+      </c>
+      <c r="CT12">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="CS12">
+      <c r="CU12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -7216,31 +7258,37 @@
       <c r="CL13">
         <v>6</v>
       </c>
+      <c r="CM13">
+        <v>6</v>
+      </c>
       <c r="CN13">
-        <f>COUNT(B13:CL13)</f>
-        <v>54</v>
-      </c>
-      <c r="CO13" s="18">
-        <f>AVERAGE(B13:CL13)</f>
-        <v>6.3796296296296298</v>
+        <v>5.5</v>
       </c>
       <c r="CP13">
+        <f>COUNT(B13:CN13)</f>
+        <v>56</v>
+      </c>
+      <c r="CQ13" s="18">
+        <f>AVERAGE(B13:CN13)</f>
+        <v>6.3571428571428568</v>
+      </c>
+      <c r="CR13">
         <f t="shared" si="2"/>
         <v>1.1769469323774333</v>
       </c>
-      <c r="CQ13">
-        <v>1</v>
-      </c>
-      <c r="CR13">
+      <c r="CS13">
+        <v>1</v>
+      </c>
+      <c r="CT13">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CS13">
+      <c r="CU13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -7490,31 +7538,31 @@
       <c r="CF14">
         <v>5.5</v>
       </c>
-      <c r="CN14">
+      <c r="CP14">
         <f t="shared" si="5"/>
         <v>47</v>
       </c>
-      <c r="CO14" s="18">
+      <c r="CQ14" s="18">
         <f t="shared" si="6"/>
         <v>4.4255319148936172</v>
       </c>
-      <c r="CP14">
+      <c r="CR14">
         <f t="shared" si="2"/>
         <v>1.3391217246854428</v>
       </c>
-      <c r="CQ14">
-        <v>1</v>
-      </c>
-      <c r="CR14">
+      <c r="CS14">
+        <v>1</v>
+      </c>
+      <c r="CT14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS14">
+      <c r="CU14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -7786,30 +7834,33 @@
         <v>6</v>
       </c>
       <c r="CN15">
+        <v>6</v>
+      </c>
+      <c r="CP15">
         <f>COUNT(B15:CL15)</f>
         <v>46</v>
       </c>
-      <c r="CO15" s="18">
+      <c r="CQ15" s="18">
         <f>AVERAGE(B15:CL15)</f>
         <v>6.0652173913043477</v>
       </c>
-      <c r="CP15">
+      <c r="CR15">
         <f t="shared" si="2"/>
         <v>0.9573434129174403</v>
       </c>
-      <c r="CQ15">
-        <v>1</v>
-      </c>
-      <c r="CR15">
+      <c r="CS15">
+        <v>1</v>
+      </c>
+      <c r="CT15">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CS15">
+      <c r="CU15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -8077,31 +8128,31 @@
       <c r="CL16">
         <v>6</v>
       </c>
-      <c r="CN16">
+      <c r="CP16">
         <f>COUNT(B16:CL16)</f>
         <v>44</v>
       </c>
-      <c r="CO16" s="18">
+      <c r="CQ16" s="18">
         <f>AVERAGE(B16:CL16)</f>
         <v>5.0113636363636367</v>
       </c>
-      <c r="CP16">
+      <c r="CR16">
         <f t="shared" si="2"/>
         <v>1.0645089158214895</v>
       </c>
-      <c r="CQ16">
-        <v>1</v>
-      </c>
-      <c r="CR16">
+      <c r="CS16">
+        <v>1</v>
+      </c>
+      <c r="CT16">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CS16">
+      <c r="CU16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -8355,30 +8406,33 @@
         <v>6.5</v>
       </c>
       <c r="CN17">
+        <v>5.5</v>
+      </c>
+      <c r="CP17">
         <f t="shared" si="5"/>
         <v>36</v>
       </c>
-      <c r="CO17" s="18">
+      <c r="CQ17" s="18">
         <f t="shared" si="6"/>
         <v>5.7361111111111107</v>
       </c>
-      <c r="CP17">
+      <c r="CR17">
         <f t="shared" si="2"/>
         <v>0.92956296268047622</v>
       </c>
-      <c r="CQ17">
-        <v>1</v>
-      </c>
-      <c r="CR17">
+      <c r="CS17">
+        <v>1</v>
+      </c>
+      <c r="CT17">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CS17">
+      <c r="CU17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -8634,31 +8688,37 @@
       <c r="CL18">
         <v>6</v>
       </c>
+      <c r="CM18">
+        <v>6.5</v>
+      </c>
       <c r="CN18">
+        <v>6.5</v>
+      </c>
+      <c r="CP18">
         <f t="shared" si="5"/>
         <v>36</v>
       </c>
-      <c r="CO18" s="18">
+      <c r="CQ18" s="18">
         <f t="shared" si="6"/>
         <v>5.6111111111111107</v>
       </c>
-      <c r="CP18">
+      <c r="CR18">
         <f t="shared" si="2"/>
         <v>1.0098256776095882</v>
       </c>
-      <c r="CQ18">
-        <v>1</v>
-      </c>
-      <c r="CR18">
+      <c r="CS18">
+        <v>1</v>
+      </c>
+      <c r="CT18">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="CS18">
+      <c r="CU18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -8920,31 +8980,34 @@
       <c r="CJ19">
         <v>5.5</v>
       </c>
-      <c r="CN19">
+      <c r="CM19">
+        <v>5.5</v>
+      </c>
+      <c r="CP19">
         <f>COUNT(B19:CJ19)</f>
         <v>37</v>
       </c>
-      <c r="CO19" s="18">
+      <c r="CQ19" s="18">
         <f>AVERAGE(B19:CJ19)</f>
         <v>5.2027027027027026</v>
       </c>
-      <c r="CP19">
+      <c r="CR19">
         <f t="shared" si="2"/>
         <v>1.3241383031954423</v>
       </c>
-      <c r="CQ19">
-        <v>1</v>
-      </c>
-      <c r="CR19">
+      <c r="CS19">
+        <v>1</v>
+      </c>
+      <c r="CT19">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CS19">
+      <c r="CU19">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>367</v>
       </c>
@@ -9192,30 +9255,33 @@
         <v>6</v>
       </c>
       <c r="CN20">
+        <v>6</v>
+      </c>
+      <c r="CP20">
         <f t="shared" si="5"/>
         <v>55</v>
       </c>
-      <c r="CO20" s="18">
+      <c r="CQ20" s="18">
         <f t="shared" si="6"/>
         <v>6.3181818181818183</v>
       </c>
-      <c r="CP20">
+      <c r="CR20">
         <f t="shared" si="2"/>
         <v>1.1213885273224193</v>
       </c>
-      <c r="CQ20">
+      <c r="CS20">
         <v>0</v>
       </c>
-      <c r="CR20">
+      <c r="CT20">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="CS20">
+      <c r="CU20">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -9459,31 +9525,31 @@
       <c r="CF21">
         <v>5.5</v>
       </c>
-      <c r="CN21">
+      <c r="CP21">
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="CO21" s="18">
+      <c r="CQ21" s="18">
         <f t="shared" si="6"/>
         <v>5.6923076923076925</v>
       </c>
-      <c r="CP21">
+      <c r="CR21">
         <f t="shared" si="2"/>
         <v>0.84687340856573534</v>
       </c>
-      <c r="CQ21">
+      <c r="CS21">
         <v>0</v>
       </c>
-      <c r="CR21">
+      <c r="CT21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS21">
+      <c r="CU21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -9727,31 +9793,31 @@
       <c r="CK22">
         <v>5.5</v>
       </c>
-      <c r="CN22">
+      <c r="CP22">
         <f t="shared" si="5"/>
         <v>38</v>
       </c>
-      <c r="CO22" s="18">
+      <c r="CQ22" s="18">
         <f t="shared" si="6"/>
         <v>6.1578947368421053</v>
       </c>
-      <c r="CP22">
+      <c r="CR22">
         <f t="shared" si="2"/>
         <v>1.0973263770680928</v>
       </c>
-      <c r="CQ22">
+      <c r="CS22">
         <v>0</v>
       </c>
-      <c r="CR22">
+      <c r="CT22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS22">
+      <c r="CU22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -9999,30 +10065,33 @@
         <v>5</v>
       </c>
       <c r="CN23">
+        <v>6</v>
+      </c>
+      <c r="CP23">
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="CO23" s="18">
+      <c r="CQ23" s="18">
         <f t="shared" si="6"/>
         <v>5.4</v>
       </c>
-      <c r="CP23">
+      <c r="CR23">
         <f t="shared" si="2"/>
         <v>0.71728150235677346</v>
       </c>
-      <c r="CQ23">
+      <c r="CS23">
         <v>0</v>
       </c>
-      <c r="CR23">
+      <c r="CT23">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CS23">
+      <c r="CU23">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -10287,31 +10356,37 @@
       <c r="CL24">
         <v>7.5</v>
       </c>
+      <c r="CM24">
+        <v>7.5</v>
+      </c>
       <c r="CN24">
-        <f>COUNT(B24:CL24)</f>
-        <v>28</v>
-      </c>
-      <c r="CO24" s="18">
-        <f>AVERAGE(B24:CL24)</f>
-        <v>6.375</v>
+        <v>6</v>
       </c>
       <c r="CP24">
+        <f>COUNT(B24:CN24)</f>
+        <v>30</v>
+      </c>
+      <c r="CQ24" s="18">
+        <f>AVERAGE(B24:CN24)</f>
+        <v>6.4</v>
+      </c>
+      <c r="CR24">
         <f t="shared" si="2"/>
         <v>0.90960483309014595</v>
       </c>
-      <c r="CQ24">
-        <v>1</v>
-      </c>
-      <c r="CR24">
+      <c r="CS24">
+        <v>1</v>
+      </c>
+      <c r="CT24">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CS24">
+      <c r="CU24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -10552,31 +10627,31 @@
       <c r="CB25" t="s">
         <v>26</v>
       </c>
-      <c r="CN25">
+      <c r="CP25">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="CO25" s="18">
+      <c r="CQ25" s="18">
         <f t="shared" si="6"/>
         <v>5.7894736842105265</v>
       </c>
-      <c r="CP25">
+      <c r="CR25">
         <f t="shared" si="2"/>
         <v>1.3674366679797902</v>
       </c>
-      <c r="CQ25">
+      <c r="CS25">
         <v>0</v>
       </c>
-      <c r="CR25">
+      <c r="CT25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS25">
+      <c r="CU25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>346</v>
       </c>
@@ -10817,31 +10892,31 @@
       <c r="CB26" t="s">
         <v>26</v>
       </c>
-      <c r="CN26">
+      <c r="CP26">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="CO26" s="18">
+      <c r="CQ26" s="18">
         <f t="shared" si="6"/>
         <v>5.9444444444444446</v>
       </c>
-      <c r="CP26">
+      <c r="CR26">
         <f t="shared" si="2"/>
         <v>0.72535769855270305</v>
       </c>
-      <c r="CQ26">
+      <c r="CS26">
         <v>0</v>
       </c>
-      <c r="CR26">
+      <c r="CT26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS26">
+      <c r="CU26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -11082,31 +11157,31 @@
       <c r="CB27" t="s">
         <v>26</v>
       </c>
-      <c r="CN27">
+      <c r="CP27">
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="CO27" s="18">
+      <c r="CQ27" s="18">
         <f t="shared" si="6"/>
         <v>5.3235294117647056</v>
       </c>
-      <c r="CP27">
+      <c r="CR27">
         <f t="shared" si="2"/>
         <v>1.3456083251473603</v>
       </c>
-      <c r="CQ27">
+      <c r="CS27">
         <v>0</v>
       </c>
-      <c r="CR27">
+      <c r="CT27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS27">
+      <c r="CU27">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -11347,31 +11422,31 @@
       <c r="CB28" t="s">
         <v>26</v>
       </c>
-      <c r="CN28">
+      <c r="CP28">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="CO28" s="18">
+      <c r="CQ28" s="18">
         <f t="shared" si="6"/>
         <v>4.53125</v>
       </c>
-      <c r="CP28">
+      <c r="CR28">
         <f t="shared" si="2"/>
         <v>1.5434674167816653</v>
       </c>
-      <c r="CQ28">
+      <c r="CS28">
         <v>0</v>
       </c>
-      <c r="CR28">
+      <c r="CT28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS28">
+      <c r="CU28">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -11615,31 +11690,37 @@
       <c r="CL29">
         <v>6.5</v>
       </c>
+      <c r="CM29">
+        <v>7.5</v>
+      </c>
       <c r="CN29">
+        <v>6</v>
+      </c>
+      <c r="CP29">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="CO29" s="18">
+      <c r="CQ29" s="18">
         <f t="shared" si="6"/>
         <v>6.65625</v>
       </c>
-      <c r="CP29">
+      <c r="CR29">
         <f t="shared" si="2"/>
         <v>0.74651970279870483</v>
       </c>
-      <c r="CQ29">
+      <c r="CS29">
         <v>0</v>
       </c>
-      <c r="CR29">
+      <c r="CT29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS29">
+      <c r="CU29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -11880,31 +11961,31 @@
       <c r="CB30">
         <v>5.5</v>
       </c>
-      <c r="CN30">
+      <c r="CP30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="CO30" s="18">
+      <c r="CQ30" s="18">
         <f t="shared" si="6"/>
         <v>3.8666666666666667</v>
       </c>
-      <c r="CP30">
+      <c r="CR30">
         <f t="shared" si="2"/>
         <v>2.3563490726929555</v>
       </c>
-      <c r="CQ30">
+      <c r="CS30">
         <v>0</v>
       </c>
-      <c r="CR30">
+      <c r="CT30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS30">
+      <c r="CU30">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -12154,31 +12235,31 @@
       <c r="CL31">
         <v>5.5</v>
       </c>
-      <c r="CN31">
+      <c r="CP31">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="CO31" s="18">
+      <c r="CQ31" s="18">
         <f t="shared" si="6"/>
         <v>4.8214285714285712</v>
       </c>
-      <c r="CP31">
+      <c r="CR31">
         <f t="shared" si="2"/>
         <v>0.89335151148745728</v>
       </c>
-      <c r="CQ31">
+      <c r="CS31">
         <v>0</v>
       </c>
-      <c r="CR31">
+      <c r="CT31">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CS31">
+      <c r="CU31">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -12419,31 +12500,31 @@
       <c r="CB32" t="s">
         <v>26</v>
       </c>
-      <c r="CN32">
+      <c r="CP32">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="CO32" s="18">
+      <c r="CQ32" s="18">
         <f t="shared" si="6"/>
         <v>7.3461538461538458</v>
       </c>
-      <c r="CP32">
+      <c r="CR32">
         <f t="shared" si="2"/>
         <v>1.5191090506255012</v>
       </c>
-      <c r="CQ32">
+      <c r="CS32">
         <v>0</v>
       </c>
-      <c r="CR32">
+      <c r="CT32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS32">
+      <c r="CU32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -12684,31 +12765,31 @@
       <c r="CB33" t="s">
         <v>26</v>
       </c>
-      <c r="CN33">
+      <c r="CP33">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="CO33" s="18">
+      <c r="CQ33" s="18">
         <f t="shared" si="6"/>
         <v>4.6818181818181817</v>
       </c>
-      <c r="CP33">
+      <c r="CR33">
         <f t="shared" si="2"/>
         <v>0.81463879335344846</v>
       </c>
-      <c r="CQ33">
+      <c r="CS33">
         <v>0</v>
       </c>
-      <c r="CR33">
+      <c r="CT33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS33">
+      <c r="CU33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -12952,31 +13033,31 @@
       <c r="CC34">
         <v>6</v>
       </c>
-      <c r="CN34">
+      <c r="CP34">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="CO34" s="18">
+      <c r="CQ34" s="18">
         <f t="shared" si="6"/>
         <v>8.4499999999999993</v>
       </c>
-      <c r="CP34">
+      <c r="CR34">
         <f t="shared" si="2"/>
         <v>1.1890705987824657</v>
       </c>
-      <c r="CQ34">
+      <c r="CS34">
         <v>0</v>
       </c>
-      <c r="CR34">
+      <c r="CT34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS34">
+      <c r="CU34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>343</v>
       </c>
@@ -13223,31 +13304,34 @@
       <c r="CL35">
         <v>5.5</v>
       </c>
-      <c r="CN35">
+      <c r="CM35">
+        <v>6.5</v>
+      </c>
+      <c r="CP35">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="CO35" s="18">
+      <c r="CQ35" s="18">
         <f t="shared" si="6"/>
         <v>4.125</v>
       </c>
-      <c r="CP35">
+      <c r="CR35">
         <f t="shared" si="2"/>
         <v>1.7677669529663689</v>
       </c>
-      <c r="CQ35">
+      <c r="CS35">
         <v>0</v>
       </c>
-      <c r="CR35">
+      <c r="CT35">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS35">
+      <c r="CU35">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>340</v>
       </c>
@@ -13491,31 +13575,31 @@
       <c r="CL36">
         <v>6</v>
       </c>
-      <c r="CN36">
+      <c r="CP36">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CO36" s="18">
+      <c r="CQ36" s="18">
         <f t="shared" si="6"/>
         <v>5.7142857142857144</v>
       </c>
-      <c r="CP36">
+      <c r="CR36">
         <f t="shared" si="2"/>
         <v>0.56694670951384085</v>
       </c>
-      <c r="CQ36">
+      <c r="CS36">
         <v>0</v>
       </c>
-      <c r="CR36">
+      <c r="CT36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS36">
+      <c r="CU36">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>376</v>
       </c>
@@ -13757,30 +13841,33 @@
         <v>26</v>
       </c>
       <c r="CN37">
+        <v>6</v>
+      </c>
+      <c r="CP37">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CO37" s="18">
+      <c r="CQ37" s="18">
         <f t="shared" si="6"/>
         <v>5.7857142857142856</v>
       </c>
-      <c r="CP37">
+      <c r="CR37">
         <f t="shared" si="2"/>
         <v>0.4879500364742666</v>
       </c>
-      <c r="CQ37">
+      <c r="CS37">
         <v>0</v>
       </c>
-      <c r="CR37">
+      <c r="CT37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS37">
+      <c r="CU37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>81</v>
       </c>
@@ -14042,31 +14129,37 @@
       <c r="CL38">
         <v>6.5</v>
       </c>
+      <c r="CM38">
+        <v>6</v>
+      </c>
       <c r="CN38">
-        <f>COUNT(B38:CL38)</f>
-        <v>11</v>
-      </c>
-      <c r="CO38" s="18">
-        <f>AVERAGE(B38:CL38)</f>
-        <v>6.4545454545454541</v>
+        <v>6.5</v>
       </c>
       <c r="CP38">
+        <f>COUNT(B38:CN38)</f>
+        <v>13</v>
+      </c>
+      <c r="CQ38" s="18">
+        <f>AVERAGE(B38:CN38)</f>
+        <v>6.4230769230769234</v>
+      </c>
+      <c r="CR38">
         <f t="shared" si="2"/>
         <v>0.90829510622924903</v>
       </c>
-      <c r="CQ38">
-        <v>1</v>
-      </c>
-      <c r="CR38">
+      <c r="CS38">
+        <v>1</v>
+      </c>
+      <c r="CT38">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CS38">
+      <c r="CU38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>378</v>
       </c>
@@ -14319,31 +14412,37 @@
       <c r="CK39">
         <v>5</v>
       </c>
+      <c r="CM39">
+        <v>5</v>
+      </c>
       <c r="CN39">
+        <v>5</v>
+      </c>
+      <c r="CP39">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="CO39" s="18">
+      <c r="CQ39" s="18">
         <f t="shared" si="6"/>
         <v>5.166666666666667</v>
       </c>
-      <c r="CP39">
+      <c r="CR39">
         <f t="shared" si="2"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="CQ39">
+      <c r="CS39">
         <v>0</v>
       </c>
-      <c r="CR39">
+      <c r="CT39">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="CS39">
+      <c r="CU39">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -14587,31 +14686,31 @@
       <c r="CH40">
         <v>6.5</v>
       </c>
-      <c r="CN40">
+      <c r="CP40">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CO40" s="18">
+      <c r="CQ40" s="18">
         <f t="shared" si="6"/>
         <v>7.8</v>
       </c>
-      <c r="CP40">
+      <c r="CR40">
         <f t="shared" si="2"/>
         <v>1.0307764064044151</v>
       </c>
-      <c r="CQ40">
+      <c r="CS40">
         <v>0</v>
       </c>
-      <c r="CR40">
+      <c r="CT40">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CS40">
+      <c r="CU40">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -14852,31 +14951,31 @@
       <c r="CB41" t="s">
         <v>26</v>
       </c>
-      <c r="CN41">
+      <c r="CP41">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CO41" s="18">
+      <c r="CQ41" s="18">
         <f t="shared" si="6"/>
         <v>5.625</v>
       </c>
-      <c r="CP41">
+      <c r="CR41">
         <f t="shared" si="2"/>
         <v>0.9464847243000456</v>
       </c>
-      <c r="CQ41">
+      <c r="CS41">
         <v>0</v>
       </c>
-      <c r="CR41">
+      <c r="CT41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS41">
+      <c r="CU41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>54</v>
       </c>
@@ -15117,31 +15216,31 @@
       <c r="CB42" t="s">
         <v>26</v>
       </c>
-      <c r="CN42">
+      <c r="CP42">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CO42" s="18">
+      <c r="CQ42" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CP42">
+      <c r="CR42">
         <f t="shared" si="2"/>
         <v>1.0408329997330663</v>
       </c>
-      <c r="CQ42">
+      <c r="CS42">
         <v>0</v>
       </c>
-      <c r="CR42">
+      <c r="CT42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS42">
+      <c r="CU42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -15382,31 +15481,31 @@
       <c r="CB43" t="s">
         <v>26</v>
       </c>
-      <c r="CN43">
+      <c r="CP43">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CO43" s="18">
+      <c r="CQ43" s="18">
         <f t="shared" si="6"/>
         <v>1.375</v>
       </c>
-      <c r="CP43">
+      <c r="CR43">
         <f t="shared" si="2"/>
         <v>1.8874586088176875</v>
       </c>
-      <c r="CQ43">
+      <c r="CS43">
         <v>0</v>
       </c>
-      <c r="CR43">
+      <c r="CT43">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS43">
+      <c r="CU43">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>344</v>
       </c>
@@ -15647,31 +15746,31 @@
       <c r="CB44" t="s">
         <v>26</v>
       </c>
-      <c r="CN44">
+      <c r="CP44">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CO44" s="18">
+      <c r="CQ44" s="18">
         <f t="shared" si="6"/>
         <v>4.625</v>
       </c>
-      <c r="CP44">
+      <c r="CR44">
         <f t="shared" si="2"/>
         <v>1.4361406616345072</v>
       </c>
-      <c r="CQ44">
+      <c r="CS44">
         <v>0</v>
       </c>
-      <c r="CR44">
+      <c r="CT44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS44">
+      <c r="CU44">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>361</v>
       </c>
@@ -15912,31 +16011,31 @@
       <c r="CB45" t="s">
         <v>26</v>
       </c>
-      <c r="CN45">
+      <c r="CP45">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CO45" s="18">
+      <c r="CQ45" s="18">
         <f t="shared" si="6"/>
         <v>6.25</v>
       </c>
-      <c r="CP45">
+      <c r="CR45">
         <f t="shared" si="2"/>
         <v>0.8660254037844386</v>
       </c>
-      <c r="CQ45">
+      <c r="CS45">
         <v>0</v>
       </c>
-      <c r="CR45">
+      <c r="CT45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS45">
+      <c r="CU45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>43</v>
       </c>
@@ -16177,31 +16276,31 @@
       <c r="CB46" t="s">
         <v>26</v>
       </c>
-      <c r="CN46">
+      <c r="CP46">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CO46" s="18">
+      <c r="CQ46" s="18">
         <f t="shared" si="6"/>
         <v>2.875</v>
       </c>
-      <c r="CP46">
+      <c r="CR46">
         <f t="shared" si="2"/>
         <v>2.7801378862687129</v>
       </c>
-      <c r="CQ46">
+      <c r="CS46">
         <v>0</v>
       </c>
-      <c r="CR46">
+      <c r="CT46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS46">
+      <c r="CU46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -16442,31 +16541,34 @@
       <c r="CB47" t="s">
         <v>26</v>
       </c>
-      <c r="CN47">
+      <c r="CM47">
+        <v>5.5</v>
+      </c>
+      <c r="CP47">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CO47" s="18">
+      <c r="CQ47" s="18">
         <f t="shared" si="6"/>
         <v>3.375</v>
       </c>
-      <c r="CP47">
+      <c r="CR47">
         <f t="shared" si="2"/>
         <v>0.47871355387816905</v>
       </c>
-      <c r="CQ47">
+      <c r="CS47">
         <v>0</v>
       </c>
-      <c r="CR47">
+      <c r="CT47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS47">
+      <c r="CU47">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -16707,31 +16809,31 @@
       <c r="CB48" t="s">
         <v>26</v>
       </c>
-      <c r="CN48">
+      <c r="CP48">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CO48" s="18">
+      <c r="CQ48" s="18">
         <f t="shared" si="6"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="CP48">
+      <c r="CR48">
         <f t="shared" si="2"/>
         <v>1.4433756729740652</v>
       </c>
-      <c r="CQ48">
+      <c r="CS48">
         <v>0</v>
       </c>
-      <c r="CR48">
+      <c r="CT48">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS48">
+      <c r="CU48">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -16972,31 +17074,31 @@
       <c r="CB49" t="s">
         <v>26</v>
       </c>
-      <c r="CN49">
+      <c r="CP49">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CO49" s="18">
+      <c r="CQ49" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CP49">
+      <c r="CR49">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-      <c r="CQ49">
+      <c r="CS49">
         <v>0</v>
       </c>
-      <c r="CR49">
+      <c r="CT49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS49">
+      <c r="CU49">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -17237,31 +17339,31 @@
       <c r="CB50" t="s">
         <v>26</v>
       </c>
-      <c r="CN50">
+      <c r="CP50">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CO50" s="18">
+      <c r="CQ50" s="18">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="CP50">
+      <c r="CR50">
         <f t="shared" si="2"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CQ50">
+      <c r="CS50">
         <v>0</v>
       </c>
-      <c r="CR50">
+      <c r="CT50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS50">
+      <c r="CU50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>362</v>
       </c>
@@ -17505,31 +17607,31 @@
       <c r="CD51">
         <v>5.5</v>
       </c>
-      <c r="CN51">
+      <c r="CP51">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CO51" s="18">
+      <c r="CQ51" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CP51">
+      <c r="CR51">
         <f t="shared" si="2"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CQ51">
+      <c r="CS51">
         <v>0</v>
       </c>
-      <c r="CR51">
+      <c r="CT51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS51">
+      <c r="CU51">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>364</v>
       </c>
@@ -17773,31 +17875,37 @@
       <c r="CL52">
         <v>6.5</v>
       </c>
+      <c r="CM52">
+        <v>5.5</v>
+      </c>
       <c r="CN52">
+        <v>6</v>
+      </c>
+      <c r="CP52">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CO52" s="18">
+      <c r="CQ52" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="CP52">
+      <c r="CR52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CQ52">
+      <c r="CS52">
         <v>0</v>
       </c>
-      <c r="CR52">
+      <c r="CT52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS52">
+      <c r="CU52">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -18038,31 +18146,31 @@
       <c r="CB53" t="s">
         <v>26</v>
       </c>
-      <c r="CN53">
+      <c r="CP53">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CO53" s="18">
+      <c r="CQ53" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CP53">
+      <c r="CR53">
         <f t="shared" si="2"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CQ53">
+      <c r="CS53">
         <v>0</v>
       </c>
-      <c r="CR53">
+      <c r="CT53">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS53">
+      <c r="CU53">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>339</v>
       </c>
@@ -18303,31 +18411,31 @@
       <c r="CB54" t="s">
         <v>26</v>
       </c>
-      <c r="CN54">
+      <c r="CP54">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CO54" s="18">
+      <c r="CQ54" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CP54">
+      <c r="CR54">
         <f t="shared" si="2"/>
         <v>2.4748737341529163</v>
       </c>
-      <c r="CQ54">
+      <c r="CS54">
         <v>0</v>
       </c>
-      <c r="CR54">
+      <c r="CT54">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS54">
+      <c r="CU54">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>342</v>
       </c>
@@ -18571,31 +18679,31 @@
       <c r="CJ55">
         <v>5.5</v>
       </c>
-      <c r="CN55">
+      <c r="CP55">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CO55" s="18">
+      <c r="CQ55" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CP55">
+      <c r="CR55">
         <f t="shared" si="2"/>
         <v>2.1213203435596424</v>
       </c>
-      <c r="CQ55">
+      <c r="CS55">
         <v>0</v>
       </c>
-      <c r="CR55">
+      <c r="CT55">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CS55">
+      <c r="CU55">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>369</v>
       </c>
@@ -18836,31 +18944,31 @@
       <c r="CB56" t="s">
         <v>26</v>
       </c>
-      <c r="CN56">
+      <c r="CP56">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CO56" s="18">
+      <c r="CQ56" s="18">
         <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
-      <c r="CP56">
+      <c r="CR56">
         <f t="shared" si="2"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="CQ56">
+      <c r="CS56">
         <v>0</v>
       </c>
-      <c r="CR56">
+      <c r="CT56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS56">
+      <c r="CU56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>52</v>
       </c>
@@ -19104,31 +19212,31 @@
       <c r="CG57">
         <v>6</v>
       </c>
-      <c r="CN57">
+      <c r="CP57">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CO57" s="18">
+      <c r="CQ57" s="18">
         <f t="shared" si="6"/>
         <v>5.666666666666667</v>
       </c>
-      <c r="CP57">
+      <c r="CR57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CQ57">
+      <c r="CS57">
         <v>0</v>
       </c>
-      <c r="CR57">
+      <c r="CT57">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CS57">
+      <c r="CU57">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>368</v>
       </c>
@@ -19372,31 +19480,31 @@
       <c r="CG58">
         <v>6</v>
       </c>
-      <c r="CN58">
+      <c r="CP58">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CO58" s="18">
+      <c r="CQ58" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CP58">
+      <c r="CR58">
         <f t="shared" si="2"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CQ58">
+      <c r="CS58">
         <v>0</v>
       </c>
-      <c r="CR58">
+      <c r="CT58">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CS58">
+      <c r="CU58">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>379</v>
       </c>
@@ -19637,31 +19745,31 @@
       <c r="CB59" t="s">
         <v>26</v>
       </c>
-      <c r="CN59">
+      <c r="CP59">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CO59" s="18">
+      <c r="CQ59" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CP59">
+      <c r="CR59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CQ59">
+      <c r="CS59">
         <v>0</v>
       </c>
-      <c r="CR59">
+      <c r="CT59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS59">
+      <c r="CU59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>391</v>
       </c>
@@ -19908,31 +20016,31 @@
       <c r="CH60">
         <v>7</v>
       </c>
-      <c r="CN60">
+      <c r="CP60">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CO60" s="18">
+      <c r="CQ60" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CP60" t="e">
+      <c r="CR60" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CQ60">
+      <c r="CS60">
         <v>0</v>
       </c>
-      <c r="CR60">
+      <c r="CT60">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CS60">
+      <c r="CU60">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>86</v>
       </c>
@@ -20173,31 +20281,31 @@
       <c r="CB61" t="s">
         <v>26</v>
       </c>
-      <c r="CN61">
+      <c r="CP61">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CO61" s="18">
+      <c r="CQ61" s="18">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="CP61" t="str">
+      <c r="CR61" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="CQ61">
+      <c r="CS61">
         <v>0</v>
       </c>
-      <c r="CR61">
+      <c r="CT61">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS61">
+      <c r="CU61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>77</v>
       </c>
@@ -20438,31 +20546,31 @@
       <c r="CB62" t="s">
         <v>26</v>
       </c>
-      <c r="CN62">
+      <c r="CP62">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CO62" s="18">
+      <c r="CQ62" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CP62" t="str">
+      <c r="CR62" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="CQ62">
+      <c r="CS62">
         <v>0</v>
       </c>
-      <c r="CR62">
+      <c r="CT62">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS62">
+      <c r="CU62">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>353</v>
       </c>
@@ -20703,31 +20811,31 @@
       <c r="CB63" t="s">
         <v>26</v>
       </c>
-      <c r="CN63">
+      <c r="CP63">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CO63" s="18">
+      <c r="CQ63" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CP63" t="str">
+      <c r="CR63" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="CQ63">
+      <c r="CS63">
         <v>0</v>
       </c>
-      <c r="CR63">
+      <c r="CT63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS63">
+      <c r="CU63">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>80</v>
       </c>
@@ -20968,31 +21076,31 @@
       <c r="CB64" t="s">
         <v>26</v>
       </c>
-      <c r="CN64">
+      <c r="CP64">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CO64" s="18">
+      <c r="CQ64" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CP64" t="str">
+      <c r="CR64" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="CQ64">
+      <c r="CS64">
         <v>0</v>
       </c>
-      <c r="CR64">
+      <c r="CT64">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS64">
+      <c r="CU64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>47</v>
       </c>
@@ -21233,31 +21341,31 @@
       <c r="CB65" t="s">
         <v>26</v>
       </c>
-      <c r="CN65">
+      <c r="CP65">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CO65" s="18">
+      <c r="CQ65" s="18">
         <f t="shared" si="6"/>
         <v>3.5</v>
       </c>
-      <c r="CP65" t="str">
+      <c r="CR65" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="CQ65">
+      <c r="CS65">
         <v>0</v>
       </c>
-      <c r="CR65">
+      <c r="CT65">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CS65">
+      <c r="CU65">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>389</v>
       </c>
@@ -21501,31 +21609,31 @@
       <c r="CH66">
         <v>5</v>
       </c>
-      <c r="CN66">
+      <c r="CP66">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CO66" s="18">
+      <c r="CQ66" s="18">
         <f t="shared" si="6"/>
         <v>4.25</v>
       </c>
-      <c r="CP66" t="e">
+      <c r="CR66" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CQ66">
+      <c r="CS66">
         <v>0</v>
       </c>
-      <c r="CR66">
+      <c r="CT66">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="CS66">
+      <c r="CU66">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -21766,31 +21874,31 @@
       <c r="CB67" t="s">
         <v>26</v>
       </c>
-      <c r="CN67">
-        <f t="shared" ref="CN67:CN82" si="7">COUNT(B67:CI67)</f>
-        <v>1</v>
-      </c>
-      <c r="CO67" s="18">
-        <f t="shared" ref="CO67:CO82" si="8">AVERAGE(B67:CI67)</f>
+      <c r="CP67">
+        <f t="shared" ref="CP67:CP82" si="7">COUNT(B67:CI67)</f>
+        <v>1</v>
+      </c>
+      <c r="CQ67" s="18">
+        <f t="shared" ref="CQ67:CQ82" si="8">AVERAGE(B67:CI67)</f>
         <v>3</v>
       </c>
-      <c r="CP67" t="str">
-        <f t="shared" ref="CP67:CP82" si="9">IF(CN67&gt;1,_xlfn.STDEV.S(B67:CF67),"")</f>
+      <c r="CR67" t="str">
+        <f t="shared" ref="CR67:CR82" si="9">IF(CP67&gt;1,_xlfn.STDEV.S(B67:CF67),"")</f>
         <v/>
       </c>
-      <c r="CQ67">
+      <c r="CS67">
         <v>0</v>
       </c>
-      <c r="CR67">
-        <f t="shared" ref="CR67:CR83" si="10">COUNT(CG67:CJ67)</f>
+      <c r="CT67">
+        <f t="shared" ref="CT67:CT83" si="10">COUNT(CG67:CJ67)</f>
         <v>0</v>
       </c>
-      <c r="CS67">
-        <f t="shared" ref="CS67:CS82" si="11">IF(CQ67=0,CR67,0)</f>
+      <c r="CU67">
+        <f t="shared" ref="CU67:CU82" si="11">IF(CS67=0,CT67,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>345</v>
       </c>
@@ -22043,31 +22151,34 @@
       <c r="CL68">
         <v>5.5</v>
       </c>
-      <c r="CN68">
+      <c r="CM68">
+        <v>5.5</v>
+      </c>
+      <c r="CP68">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="CO68" s="18">
+      <c r="CQ68" s="18">
         <f t="shared" si="8"/>
         <v>4.25</v>
       </c>
-      <c r="CP68" t="e">
+      <c r="CR68" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CQ68">
+      <c r="CS68">
         <v>0</v>
       </c>
-      <c r="CR68">
+      <c r="CT68">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="CS68">
+      <c r="CU68">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>347</v>
       </c>
@@ -22308,31 +22419,31 @@
       <c r="CB69" t="s">
         <v>26</v>
       </c>
-      <c r="CN69">
+      <c r="CP69">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO69" s="18">
+      <c r="CQ69" s="18">
         <f t="shared" si="8"/>
         <v>6.5</v>
       </c>
-      <c r="CP69" t="str">
+      <c r="CR69" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ69">
+      <c r="CS69">
         <v>0</v>
       </c>
-      <c r="CR69">
+      <c r="CT69">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS69">
+      <c r="CU69">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>350</v>
       </c>
@@ -22573,31 +22684,31 @@
       <c r="CB70" t="s">
         <v>26</v>
       </c>
-      <c r="CN70">
+      <c r="CP70">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO70" s="18">
+      <c r="CQ70" s="18">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="CP70" t="str">
+      <c r="CR70" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ70">
+      <c r="CS70">
         <v>0</v>
       </c>
-      <c r="CR70">
+      <c r="CT70">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS70">
+      <c r="CU70">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>351</v>
       </c>
@@ -22838,31 +22949,31 @@
       <c r="CB71" t="s">
         <v>26</v>
       </c>
-      <c r="CN71">
+      <c r="CP71">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO71" s="18">
+      <c r="CQ71" s="18">
         <f t="shared" si="8"/>
         <v>6.5</v>
       </c>
-      <c r="CP71" t="str">
+      <c r="CR71" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ71">
+      <c r="CS71">
         <v>0</v>
       </c>
-      <c r="CR71">
+      <c r="CT71">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS71">
+      <c r="CU71">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>352</v>
       </c>
@@ -23103,31 +23214,31 @@
       <c r="CB72" t="s">
         <v>26</v>
       </c>
-      <c r="CN72">
+      <c r="CP72">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO72" s="18">
+      <c r="CQ72" s="18">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="CP72" t="str">
+      <c r="CR72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ72">
+      <c r="CS72">
         <v>0</v>
       </c>
-      <c r="CR72">
+      <c r="CT72">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS72">
+      <c r="CU72">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>354</v>
       </c>
@@ -23368,31 +23479,31 @@
       <c r="CB73" t="s">
         <v>26</v>
       </c>
-      <c r="CN73">
+      <c r="CP73">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO73" s="18">
+      <c r="CQ73" s="18">
         <f t="shared" si="8"/>
         <v>5.5</v>
       </c>
-      <c r="CP73" t="str">
+      <c r="CR73" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ73">
+      <c r="CS73">
         <v>0</v>
       </c>
-      <c r="CR73">
+      <c r="CT73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS73">
+      <c r="CU73">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>365</v>
       </c>
@@ -23633,31 +23744,31 @@
       <c r="CB74" t="s">
         <v>26</v>
       </c>
-      <c r="CN74">
+      <c r="CP74">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO74" s="18">
+      <c r="CQ74" s="18">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="CP74" t="str">
+      <c r="CR74" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ74">
+      <c r="CS74">
         <v>0</v>
       </c>
-      <c r="CR74">
+      <c r="CT74">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS74">
+      <c r="CU74">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>366</v>
       </c>
@@ -23898,31 +24009,31 @@
       <c r="CB75" t="s">
         <v>26</v>
       </c>
-      <c r="CN75">
+      <c r="CP75">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO75" s="18">
+      <c r="CQ75" s="18">
         <f t="shared" si="8"/>
         <v>2.5</v>
       </c>
-      <c r="CP75" t="str">
+      <c r="CR75" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ75">
+      <c r="CS75">
         <v>0</v>
       </c>
-      <c r="CR75">
+      <c r="CT75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS75">
+      <c r="CU75">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>374</v>
       </c>
@@ -24163,31 +24274,31 @@
       <c r="CB76" t="s">
         <v>26</v>
       </c>
-      <c r="CN76">
+      <c r="CP76">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO76" s="18">
+      <c r="CQ76" s="18">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="CP76" t="str">
+      <c r="CR76" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ76">
+      <c r="CS76">
         <v>0</v>
       </c>
-      <c r="CR76">
+      <c r="CT76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS76">
+      <c r="CU76">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>375</v>
       </c>
@@ -24428,31 +24539,31 @@
       <c r="CB77" t="s">
         <v>26</v>
       </c>
-      <c r="CN77">
+      <c r="CP77">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO77" s="18">
+      <c r="CQ77" s="18">
         <f t="shared" si="8"/>
         <v>5.5</v>
       </c>
-      <c r="CP77" t="str">
+      <c r="CR77" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ77">
+      <c r="CS77">
         <v>0</v>
       </c>
-      <c r="CR77">
+      <c r="CT77">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS77">
+      <c r="CU77">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>377</v>
       </c>
@@ -24693,31 +24804,31 @@
       <c r="CB78" t="s">
         <v>26</v>
       </c>
-      <c r="CN78">
+      <c r="CP78">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO78" s="18">
+      <c r="CQ78" s="18">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="CP78" t="str">
+      <c r="CR78" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ78">
+      <c r="CS78">
         <v>0</v>
       </c>
-      <c r="CR78">
+      <c r="CT78">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS78">
+      <c r="CU78">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>381</v>
       </c>
@@ -24958,31 +25069,31 @@
       <c r="CB79" t="s">
         <v>26</v>
       </c>
-      <c r="CN79">
+      <c r="CP79">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO79" s="18">
+      <c r="CQ79" s="18">
         <f t="shared" si="8"/>
         <v>5.5</v>
       </c>
-      <c r="CP79" t="str">
+      <c r="CR79" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ79">
+      <c r="CS79">
         <v>0</v>
       </c>
-      <c r="CR79">
+      <c r="CT79">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS79">
+      <c r="CU79">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>382</v>
       </c>
@@ -25223,31 +25334,31 @@
       <c r="CB80" t="s">
         <v>26</v>
       </c>
-      <c r="CN80">
+      <c r="CP80">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO80" s="18">
+      <c r="CQ80" s="18">
         <f t="shared" si="8"/>
         <v>5.5</v>
       </c>
-      <c r="CP80" t="str">
+      <c r="CR80" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ80">
+      <c r="CS80">
         <v>0</v>
       </c>
-      <c r="CR80">
+      <c r="CT80">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CS80">
+      <c r="CU80">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>388</v>
       </c>
@@ -25497,31 +25608,31 @@
       <c r="CJ81">
         <v>7</v>
       </c>
-      <c r="CN81">
+      <c r="CP81">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="CO81" s="18">
+      <c r="CQ81" s="18">
         <f t="shared" si="8"/>
         <v>6.5</v>
       </c>
-      <c r="CP81" t="e">
+      <c r="CR81" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CQ81">
+      <c r="CS81">
         <v>0</v>
       </c>
-      <c r="CR81">
+      <c r="CT81">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="CS81">
+      <c r="CU81">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>390</v>
       </c>
@@ -25765,31 +25876,31 @@
       <c r="CH82">
         <v>7.5</v>
       </c>
-      <c r="CN82">
+      <c r="CP82">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="CO82" s="18">
+      <c r="CQ82" s="18">
         <f t="shared" si="8"/>
         <v>7.5</v>
       </c>
-      <c r="CP82" t="str">
+      <c r="CR82" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="CQ82">
+      <c r="CS82">
         <v>0</v>
       </c>
-      <c r="CR82">
+      <c r="CT82">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS82">
+      <c r="CU82">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:97" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>392</v>
       </c>
@@ -26033,37 +26144,37 @@
       <c r="CI83">
         <v>7</v>
       </c>
-      <c r="CN83">
-        <f t="shared" ref="CN83" si="12">COUNT(B83:CI83)</f>
-        <v>1</v>
-      </c>
-      <c r="CO83" s="18">
-        <f t="shared" ref="CO83" si="13">AVERAGE(B83:CI83)</f>
+      <c r="CP83">
+        <f t="shared" ref="CP83" si="12">COUNT(B83:CI83)</f>
+        <v>1</v>
+      </c>
+      <c r="CQ83" s="18">
+        <f t="shared" ref="CQ83" si="13">AVERAGE(B83:CI83)</f>
         <v>7</v>
       </c>
-      <c r="CP83" t="str">
-        <f t="shared" ref="CP83" si="14">IF(CN83&gt;1,_xlfn.STDEV.S(B83:CF83),"")</f>
+      <c r="CR83" t="str">
+        <f t="shared" ref="CR83" si="14">IF(CP83&gt;1,_xlfn.STDEV.S(B83:CF83),"")</f>
         <v/>
       </c>
-      <c r="CQ83">
+      <c r="CS83">
         <v>0</v>
       </c>
-      <c r="CR83">
+      <c r="CT83">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS83">
-        <f t="shared" ref="CS83" si="15">IF(CQ83=0,CR83,0)</f>
+      <c r="CU83">
+        <f t="shared" ref="CU83" si="15">IF(CS83=0,CT83,0)</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CS83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
-    <sortState ref="A2:CS80">
-      <sortCondition descending="1" ref="CQ1:CQ80"/>
+  <autoFilter ref="A1:CU83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
+    <sortState ref="A2:CU80">
+      <sortCondition descending="1" ref="CS1:CS80"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="CN2:CN83">
+  <conditionalFormatting sqref="CP2:CP83">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -26075,7 +26186,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP83">
+  <conditionalFormatting sqref="CR2:CR83">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -26087,7 +26198,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CN2:CN83">
+  <conditionalFormatting sqref="CP2:CP83">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -26099,7 +26210,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CO2:CO83">
+  <conditionalFormatting sqref="CQ2:CQ83">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
@@ -26111,7 +26222,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CO2:CO83">
+  <conditionalFormatting sqref="CQ2:CQ83">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
@@ -26123,7 +26234,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CN2:CN83">
+  <conditionalFormatting sqref="CP2:CP83">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -26135,7 +26246,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CO2:CO83">
+  <conditionalFormatting sqref="CQ2:CQ83">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -26147,7 +26258,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CM2:CM79">
+  <conditionalFormatting sqref="CO2:CO79">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -26159,7 +26270,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CM2:CM67">
+  <conditionalFormatting sqref="CO2:CO67">
     <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
@@ -26171,7 +26282,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CM2:CM67">
+  <conditionalFormatting sqref="CO2:CO67">
     <cfRule type="colorScale" priority="127">
       <colorScale>
         <cfvo type="min"/>
@@ -26183,7 +26294,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CM2:CM67">
+  <conditionalFormatting sqref="CO2:CO67">
     <cfRule type="colorScale" priority="129">
       <colorScale>
         <cfvo type="min"/>
@@ -26195,7 +26306,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:CL83">
+  <conditionalFormatting sqref="B2:CN83">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -31285,7 +31396,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X261"/>
+  <dimension ref="A1:X267"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -44255,6 +44366,298 @@
         <v>48</v>
       </c>
     </row>
+    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A262" s="14">
+        <v>46099</v>
+      </c>
+      <c r="B262" s="3">
+        <v>3</v>
+      </c>
+      <c r="C262" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E262" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F262" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H262" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="I262" s="9">
+        <v>1</v>
+      </c>
+      <c r="J262" s="10">
+        <v>6</v>
+      </c>
+      <c r="K262" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L262" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="M262" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N262" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="O262" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="P262" s="10"/>
+    </row>
+    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A263" s="14">
+        <v>46099</v>
+      </c>
+      <c r="B263" s="3">
+        <v>4</v>
+      </c>
+      <c r="C263" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D263" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="E263" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F263" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G263" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H263" s="10"/>
+      <c r="I263" s="11">
+        <v>3</v>
+      </c>
+      <c r="J263" s="2">
+        <v>4</v>
+      </c>
+      <c r="K263" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L263" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M263" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N263" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O263" s="61" t="s">
+        <v>378</v>
+      </c>
+      <c r="P263" s="2"/>
+    </row>
+    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A264" s="14">
+        <v>46099</v>
+      </c>
+      <c r="B264" s="5">
+        <v>4</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G264" s="61" t="s">
+        <v>378</v>
+      </c>
+      <c r="H264" s="2"/>
+      <c r="I264" s="5">
+        <v>4</v>
+      </c>
+      <c r="J264" s="8">
+        <v>4</v>
+      </c>
+      <c r="K264" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L264" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M264" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="N264" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="O264" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="P264" s="8" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A265" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B265" s="62">
+        <v>4</v>
+      </c>
+      <c r="C265" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E265" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F265" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H265" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I265" s="9">
+        <v>3</v>
+      </c>
+      <c r="J265" s="10">
+        <v>3</v>
+      </c>
+      <c r="K265" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L265" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M265" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="N265" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="O265" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P265" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A266" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B266" s="62">
+        <v>4</v>
+      </c>
+      <c r="C266" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D266" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E266" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F266" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G266" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H266" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I266" s="11">
+        <v>5</v>
+      </c>
+      <c r="J266" s="2">
+        <v>1</v>
+      </c>
+      <c r="K266" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L266" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M266" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="N266" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="O266" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="P266" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A267" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B267" s="62">
+        <v>3</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F267" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="G267" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="H267" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="I267" s="5">
+        <v>6</v>
+      </c>
+      <c r="J267" s="8">
+        <v>2</v>
+      </c>
+      <c r="K267" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L267" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M267" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="N267" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="O267" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P267" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -44262,7 +44665,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:BS83"/>
+  <dimension ref="A1:BU83"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -44271,10 +44674,10 @@
     <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="71" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="73" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -44488,8 +44891,14 @@
       <c r="BS1" s="1">
         <v>46092</v>
       </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BT1" s="1">
+        <v>46099</v>
+      </c>
+      <c r="BU1" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -44542,7 +44951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -44550,7 +44959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -44588,12 +44997,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:73" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -44601,7 +45010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>364</v>
       </c>
@@ -44614,8 +45023,11 @@
       <c r="BS7">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BU7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -44623,7 +45035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>353</v>
       </c>
@@ -44631,22 +45043,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:73" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="11" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="13" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>362</v>
       </c>
@@ -44654,12 +45066,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:73" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -44709,7 +45121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -44747,7 +45159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>378</v>
       </c>
@@ -44758,7 +45170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -44772,7 +45184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -44824,8 +45236,11 @@
       <c r="BP19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BU19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -44910,8 +45325,11 @@
       <c r="BR20">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BU20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>392</v>
       </c>
@@ -44919,7 +45337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -44968,8 +45386,14 @@
       <c r="BS22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BT22">
+        <v>3</v>
+      </c>
+      <c r="BU22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>375</v>
       </c>
@@ -44977,7 +45401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -45132,7 +45556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>342</v>
       </c>
@@ -45149,17 +45573,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:73" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="28" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -45173,7 +45597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -45277,7 +45701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>361</v>
       </c>
@@ -45294,7 +45718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>390</v>
       </c>
@@ -45302,7 +45726,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>1</v>
       </c>
@@ -45433,7 +45857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>351</v>
       </c>
@@ -45441,7 +45865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -45581,7 +46005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>381</v>
       </c>
@@ -45589,7 +46013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -45708,7 +46132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -45716,7 +46140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>61</v>
       </c>
@@ -45724,7 +46148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>374</v>
       </c>
@@ -45732,7 +46156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -45854,7 +46278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -45862,7 +46286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -45882,7 +46306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -45890,7 +46314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>368</v>
       </c>
@@ -45904,7 +46328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>345</v>
       </c>
@@ -45917,8 +46341,11 @@
       <c r="BS45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BT45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>343</v>
       </c>
@@ -45931,8 +46358,11 @@
       <c r="BS46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BT46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>344</v>
       </c>
@@ -45946,7 +46376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -46076,8 +46506,11 @@
       <c r="BR48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BT48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -46132,13 +46565,16 @@
       <c r="BK49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BT49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="51" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -46155,12 +46591,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:73" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="53" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -46272,8 +46708,11 @@
       <c r="BS53">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BU53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>369</v>
       </c>
@@ -46281,7 +46720,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>388</v>
       </c>
@@ -46295,7 +46734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -46305,8 +46744,11 @@
       <c r="BF56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BT56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>340</v>
       </c>
@@ -46329,17 +46771,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="59" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -46434,12 +46876,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>81</v>
       </c>
@@ -46464,8 +46906,11 @@
       <c r="BS62">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BU62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -46488,12 +46933,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:73" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="65" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>22</v>
       </c>
@@ -46527,8 +46972,14 @@
       <c r="BS65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BT65">
+        <v>1</v>
+      </c>
+      <c r="BU65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>376</v>
       </c>
@@ -46551,7 +47002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>44</v>
       </c>
@@ -46604,7 +47055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>379</v>
       </c>
@@ -46615,7 +47066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -46632,12 +47083,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:73" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="71" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>82</v>
       </c>
@@ -46776,8 +47227,11 @@
       <c r="BN71">
         <v>3</v>
       </c>
-    </row>
-    <row r="72" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="BU71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>49</v>
       </c>
@@ -46785,12 +47239,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="74" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -46804,7 +47258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -46971,7 +47425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>45</v>
       </c>
@@ -46982,7 +47436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>367</v>
       </c>
@@ -47055,8 +47509,11 @@
       <c r="BI77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+      <c r="BU77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:73" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>352</v>
       </c>
@@ -47064,12 +47521,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:73" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="80" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -47083,7 +47540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:73" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>86</v>
       </c>
@@ -47091,7 +47548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -47266,8 +47723,14 @@
       <c r="BS82">
         <v>3</v>
       </c>
-    </row>
-    <row r="83" spans="1:71" hidden="1" x14ac:dyDescent="0.35">
+      <c r="BT82">
+        <v>4</v>
+      </c>
+      <c r="BU82">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:73" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>47</v>
       </c>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/95416d5ad4be8d97/Documentos antigo/Projetos_jl/Streamlit/Dashboard Pelada/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{FD2634B1-9EDE-486E-AE13-243F5EFAB489}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notas" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="artilharia total" sheetId="3" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'extrato 2024'!$A$1:$C$187</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CV$83</definedName>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9253" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9254" uniqueCount="394">
   <si>
     <t>Jogador</t>
   </si>
@@ -28947,9 +28947,7 @@
       </c>
       <c r="V7" s="19"/>
       <c r="W7" s="19"/>
-      <c r="X7" s="19">
-        <v>24.84</v>
-      </c>
+      <c r="X7" s="19"/>
       <c r="Y7" s="19"/>
       <c r="Z7" t="s">
         <v>372</v>
@@ -29460,7 +29458,7 @@
       <c r="V15" s="19">
         <v>78.34</v>
       </c>
-      <c r="W15" s="21">
+      <c r="W15" s="19">
         <v>96.34</v>
       </c>
     </row>
@@ -29992,7 +29990,7 @@
       <c r="T26" s="22"/>
       <c r="U26" s="22"/>
       <c r="V26" s="19"/>
-      <c r="W26" s="21">
+      <c r="W26" s="19">
         <v>48.17</v>
       </c>
       <c r="X26" s="19"/>
@@ -30205,7 +30203,7 @@
         <v>96.34</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>49</v>
       </c>
@@ -30223,7 +30221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>343</v>
       </c>
@@ -30254,8 +30252,11 @@
       <c r="W34" s="19">
         <v>96.34</v>
       </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X34">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -30279,7 +30280,7 @@
       </c>
       <c r="W35" s="19"/>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -30299,7 +30300,7 @@
       </c>
       <c r="L36" s="19"/>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>55</v>
       </c>
@@ -30347,11 +30348,11 @@
       <c r="T37" s="19">
         <v>90.34</v>
       </c>
-      <c r="W37" s="21">
+      <c r="W37" s="19">
         <v>24.09</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>53</v>
       </c>
@@ -30367,7 +30368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>56</v>
       </c>
@@ -30423,7 +30424,7 @@
         <v>96.34</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>60</v>
       </c>
@@ -30445,7 +30446,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -30461,7 +30462,7 @@
       <c r="H41" s="19"/>
       <c r="I41" s="19"/>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>66</v>
       </c>
@@ -30512,7 +30513,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>63</v>
       </c>
@@ -30547,11 +30548,11 @@
       <c r="V43" s="19">
         <v>27</v>
       </c>
-      <c r="W43" s="21">
+      <c r="W43" s="19">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>68</v>
       </c>
@@ -30595,7 +30596,7 @@
       </c>
       <c r="S44" s="19"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>77</v>
       </c>
@@ -30609,7 +30610,7 @@
       <c r="H45" s="19"/>
       <c r="I45" s="19"/>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A46" s="31" t="s">
         <v>353</v>
       </c>
@@ -30626,7 +30627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>81</v>
       </c>
@@ -30653,11 +30654,11 @@
       <c r="V47" s="19">
         <v>78.34</v>
       </c>
-      <c r="W47" s="21">
+      <c r="W47" s="19">
         <v>96.34</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>388</v>
       </c>
@@ -31501,8 +31502,8 @@
         <v>1972.28</v>
       </c>
       <c r="W87" s="23">
-        <f>4*27+85.84*11</f>
-        <v>1052.24</v>
+        <f>5*27+85.84*13.75</f>
+        <v>1315.3</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.35">
@@ -31592,7 +31593,7 @@
       </c>
       <c r="W88" s="24">
         <f t="shared" ref="W88" si="9">W87/W86</f>
-        <v>0.56761553358255268</v>
+        <v>0.70951941697819088</v>
       </c>
     </row>
   </sheetData>
@@ -45022,7 +45023,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:BV83"/>
+  <dimension ref="A1:BV84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -45375,1356 +45376,1344 @@
     </row>
     <row r="7" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>364</v>
-      </c>
-      <c r="AH7">
-        <v>3</v>
-      </c>
-      <c r="AQ7">
-        <v>2</v>
-      </c>
-      <c r="BS7">
-        <v>3</v>
-      </c>
-      <c r="BU7">
-        <v>2</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
+        <v>364</v>
+      </c>
+      <c r="AH8">
+        <v>3</v>
+      </c>
+      <c r="AQ8">
+        <v>2</v>
+      </c>
+      <c r="BS8">
+        <v>3</v>
+      </c>
+      <c r="BU8">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>353</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>347</v>
-      </c>
-    </row>
-    <row r="11" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>382</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>362</v>
       </c>
-      <c r="BK13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="BK14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
-      <c r="K15">
-        <v>3</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
-      <c r="V15">
-        <v>1</v>
-      </c>
-      <c r="AE15">
-        <v>1</v>
-      </c>
-      <c r="AF15">
-        <v>1</v>
-      </c>
-      <c r="AH15">
-        <v>2</v>
-      </c>
-      <c r="AT15">
-        <v>1</v>
-      </c>
-      <c r="BA15">
-        <v>1</v>
-      </c>
-      <c r="BH15">
-        <v>1</v>
-      </c>
-      <c r="BM15">
-        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>1</v>
       </c>
       <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="P16">
-        <v>1</v>
-      </c>
-      <c r="S16">
-        <v>1</v>
-      </c>
-      <c r="W16">
-        <v>1</v>
-      </c>
-      <c r="Z16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <v>3</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="AE16">
+        <v>1</v>
+      </c>
+      <c r="AF16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
         <v>2</v>
       </c>
-      <c r="AA16">
-        <v>0.5</v>
-      </c>
-      <c r="AK16">
-        <v>1</v>
-      </c>
-      <c r="AR16">
-        <v>2</v>
-      </c>
-      <c r="AX16">
+      <c r="AT16">
+        <v>1</v>
+      </c>
+      <c r="BA16">
+        <v>1</v>
+      </c>
+      <c r="BH16">
+        <v>1</v>
+      </c>
+      <c r="BM16">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>378</v>
-      </c>
-      <c r="BL17">
-        <v>1</v>
-      </c>
-      <c r="BR17">
+        <v>14</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>2</v>
+      </c>
+      <c r="AA17">
+        <v>0.5</v>
+      </c>
+      <c r="AK17">
+        <v>1</v>
+      </c>
+      <c r="AR17">
+        <v>2</v>
+      </c>
+      <c r="AX17">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
-      <c r="V18">
-        <v>2</v>
+        <v>378</v>
+      </c>
+      <c r="BL18">
+        <v>1</v>
+      </c>
+      <c r="BR18">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>54</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="I19">
         <v>3</v>
       </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="T19">
-        <v>1</v>
-      </c>
-      <c r="W19">
-        <v>1</v>
-      </c>
-      <c r="X19">
-        <v>1</v>
-      </c>
-      <c r="Y19">
-        <v>1</v>
-      </c>
-      <c r="Z19">
-        <v>1</v>
-      </c>
-      <c r="AA19">
-        <v>1</v>
-      </c>
-      <c r="AC19">
-        <v>1</v>
-      </c>
-      <c r="AD19">
-        <v>1</v>
-      </c>
-      <c r="AH19">
-        <v>1</v>
-      </c>
-      <c r="AI19">
-        <v>1</v>
-      </c>
-      <c r="BA19">
-        <v>3</v>
-      </c>
-      <c r="BG19">
-        <v>1</v>
-      </c>
-      <c r="BP19">
-        <v>1</v>
-      </c>
-      <c r="BU19">
+      <c r="V19">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>66</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
       </c>
       <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>1</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AD20">
+        <v>1</v>
+      </c>
+      <c r="AH20">
+        <v>1</v>
+      </c>
+      <c r="AI20">
+        <v>1</v>
+      </c>
+      <c r="BA20">
+        <v>3</v>
+      </c>
+      <c r="BG20">
+        <v>1</v>
+      </c>
+      <c r="BP20">
+        <v>1</v>
+      </c>
+      <c r="BU20">
         <v>2</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>3</v>
-      </c>
-      <c r="N20">
-        <v>2</v>
-      </c>
-      <c r="O20">
-        <v>2</v>
-      </c>
-      <c r="P20">
-        <v>1</v>
-      </c>
-      <c r="S20">
-        <v>2</v>
-      </c>
-      <c r="V20">
-        <v>4</v>
-      </c>
-      <c r="W20">
-        <v>6</v>
-      </c>
-      <c r="X20">
-        <v>3</v>
-      </c>
-      <c r="AB20">
-        <v>1</v>
-      </c>
-      <c r="AC20">
-        <v>2</v>
-      </c>
-      <c r="AD20">
-        <v>3</v>
-      </c>
-      <c r="AE20">
-        <v>1</v>
-      </c>
-      <c r="AH20">
-        <v>4</v>
-      </c>
-      <c r="AI20">
-        <v>5</v>
-      </c>
-      <c r="AK20">
-        <v>1</v>
-      </c>
-      <c r="AL20">
-        <v>1</v>
-      </c>
-      <c r="AN20">
-        <v>2</v>
-      </c>
-      <c r="AU20">
-        <v>4</v>
-      </c>
-      <c r="AV20">
-        <v>1</v>
-      </c>
-      <c r="AX20">
-        <v>1</v>
-      </c>
-      <c r="BH20">
-        <v>1</v>
-      </c>
-      <c r="BI20">
-        <v>2</v>
-      </c>
-      <c r="BK20">
-        <v>2</v>
-      </c>
-      <c r="BQ20">
-        <v>2</v>
-      </c>
-      <c r="BR20">
-        <v>3</v>
-      </c>
-      <c r="BU20">
-        <v>1</v>
-      </c>
-      <c r="BV20">
-        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>391</v>
-      </c>
-      <c r="BP21">
+        <v>84</v>
+      </c>
+      <c r="I21">
         <v>2</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>3</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+      <c r="O21">
+        <v>2</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>2</v>
+      </c>
+      <c r="V21">
+        <v>4</v>
+      </c>
+      <c r="W21">
+        <v>6</v>
+      </c>
+      <c r="X21">
+        <v>3</v>
+      </c>
+      <c r="AB21">
+        <v>1</v>
+      </c>
+      <c r="AC21">
+        <v>2</v>
+      </c>
+      <c r="AD21">
+        <v>3</v>
+      </c>
+      <c r="AE21">
+        <v>1</v>
+      </c>
+      <c r="AH21">
+        <v>4</v>
+      </c>
+      <c r="AI21">
+        <v>5</v>
+      </c>
+      <c r="AK21">
+        <v>1</v>
+      </c>
+      <c r="AL21">
+        <v>1</v>
+      </c>
+      <c r="AN21">
+        <v>2</v>
+      </c>
+      <c r="AU21">
+        <v>4</v>
+      </c>
+      <c r="AV21">
+        <v>1</v>
+      </c>
+      <c r="AX21">
+        <v>1</v>
+      </c>
+      <c r="BH21">
+        <v>1</v>
+      </c>
+      <c r="BI21">
+        <v>2</v>
+      </c>
+      <c r="BK21">
+        <v>2</v>
+      </c>
+      <c r="BQ21">
+        <v>2</v>
+      </c>
+      <c r="BR21">
+        <v>3</v>
+      </c>
+      <c r="BU21">
+        <v>1</v>
+      </c>
+      <c r="BV21">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="H22">
+        <v>391</v>
+      </c>
+      <c r="BP22">
         <v>2</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="AK22">
-        <v>1</v>
-      </c>
-      <c r="AL22">
-        <v>4</v>
-      </c>
-      <c r="AO22">
-        <v>2</v>
-      </c>
-      <c r="AR22">
-        <v>3</v>
-      </c>
-      <c r="AS22">
-        <v>2</v>
-      </c>
-      <c r="AT22">
-        <v>1</v>
-      </c>
-      <c r="AY22">
-        <v>1</v>
-      </c>
-      <c r="BE22">
-        <v>2</v>
-      </c>
-      <c r="BF22">
-        <v>1</v>
-      </c>
-      <c r="BI22">
-        <v>2</v>
-      </c>
-      <c r="BR22">
-        <v>1</v>
-      </c>
-      <c r="BS22">
-        <v>1</v>
-      </c>
-      <c r="BT22">
-        <v>3</v>
-      </c>
-      <c r="BU22">
-        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>375</v>
-      </c>
-      <c r="AW23">
+        <v>15</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="AK23">
+        <v>1</v>
+      </c>
+      <c r="AL23">
+        <v>4</v>
+      </c>
+      <c r="AO23">
+        <v>2</v>
+      </c>
+      <c r="AR23">
+        <v>3</v>
+      </c>
+      <c r="AS23">
+        <v>2</v>
+      </c>
+      <c r="AT23">
+        <v>1</v>
+      </c>
+      <c r="AY23">
+        <v>1</v>
+      </c>
+      <c r="BE23">
+        <v>2</v>
+      </c>
+      <c r="BF23">
+        <v>1</v>
+      </c>
+      <c r="BI23">
+        <v>2</v>
+      </c>
+      <c r="BR23">
+        <v>1</v>
+      </c>
+      <c r="BS23">
+        <v>1</v>
+      </c>
+      <c r="BT23">
+        <v>3</v>
+      </c>
+      <c r="BU23">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24">
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <v>2</v>
-      </c>
-      <c r="M24">
-        <v>2</v>
-      </c>
-      <c r="N24">
-        <v>6</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <v>3</v>
-      </c>
-      <c r="R24">
-        <v>1</v>
-      </c>
-      <c r="S24">
-        <v>1</v>
-      </c>
-      <c r="T24">
-        <v>3</v>
-      </c>
-      <c r="U24">
-        <v>3</v>
-      </c>
-      <c r="V24">
-        <v>6</v>
-      </c>
-      <c r="W24">
-        <v>2</v>
-      </c>
-      <c r="X24">
-        <v>3</v>
-      </c>
-      <c r="Y24">
-        <v>1</v>
-      </c>
-      <c r="Z24">
-        <v>3.5</v>
-      </c>
-      <c r="AA24">
-        <v>3.5</v>
-      </c>
-      <c r="AB24">
-        <v>3</v>
-      </c>
-      <c r="AC24">
-        <v>1</v>
-      </c>
-      <c r="AE24">
-        <v>10</v>
-      </c>
-      <c r="AF24">
-        <v>3</v>
-      </c>
-      <c r="AG24">
-        <v>3</v>
-      </c>
-      <c r="AH24">
-        <v>2</v>
-      </c>
-      <c r="AJ24">
-        <v>3</v>
-      </c>
-      <c r="AK24">
-        <v>3</v>
-      </c>
-      <c r="AL24">
-        <v>5</v>
-      </c>
-      <c r="AN24">
-        <v>1</v>
-      </c>
-      <c r="AO24">
-        <v>6</v>
-      </c>
-      <c r="AP24">
-        <v>4</v>
-      </c>
-      <c r="AQ24">
-        <v>3</v>
-      </c>
-      <c r="AR24">
-        <v>4</v>
-      </c>
-      <c r="AS24">
-        <v>2</v>
-      </c>
-      <c r="AT24">
-        <v>4</v>
-      </c>
-      <c r="AU24">
-        <v>4</v>
-      </c>
-      <c r="AV24">
-        <v>6</v>
+        <v>375</v>
       </c>
       <c r="AW24">
         <v>1</v>
-      </c>
-      <c r="AY24">
-        <v>4</v>
-      </c>
-      <c r="AZ24">
-        <v>1</v>
-      </c>
-      <c r="BA24">
-        <v>3</v>
-      </c>
-      <c r="BC24">
-        <v>5</v>
-      </c>
-      <c r="BD24">
-        <v>2</v>
-      </c>
-      <c r="BE24">
-        <v>3</v>
-      </c>
-      <c r="BF24">
-        <v>3</v>
-      </c>
-      <c r="BG24">
-        <v>3</v>
-      </c>
-      <c r="BH24">
-        <v>1</v>
-      </c>
-      <c r="BI24">
-        <v>5</v>
-      </c>
-      <c r="BJ24">
-        <v>1</v>
-      </c>
-      <c r="BK24">
-        <v>1</v>
-      </c>
-      <c r="BL24">
-        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>2</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25">
+        <v>6</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>3</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <v>3</v>
+      </c>
+      <c r="U25">
+        <v>3</v>
+      </c>
+      <c r="V25">
+        <v>6</v>
+      </c>
+      <c r="W25">
+        <v>2</v>
+      </c>
+      <c r="X25">
+        <v>3</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <v>3.5</v>
+      </c>
+      <c r="AA25">
+        <v>3.5</v>
+      </c>
+      <c r="AB25">
+        <v>3</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AE25">
+        <v>10</v>
+      </c>
+      <c r="AF25">
+        <v>3</v>
+      </c>
+      <c r="AG25">
+        <v>3</v>
+      </c>
+      <c r="AH25">
+        <v>2</v>
+      </c>
+      <c r="AJ25">
+        <v>3</v>
+      </c>
+      <c r="AK25">
+        <v>3</v>
+      </c>
+      <c r="AL25">
+        <v>5</v>
+      </c>
+      <c r="AN25">
+        <v>1</v>
+      </c>
+      <c r="AO25">
+        <v>6</v>
+      </c>
+      <c r="AP25">
+        <v>4</v>
+      </c>
+      <c r="AQ25">
+        <v>3</v>
+      </c>
+      <c r="AR25">
+        <v>4</v>
+      </c>
+      <c r="AS25">
+        <v>2</v>
+      </c>
+      <c r="AT25">
+        <v>4</v>
+      </c>
+      <c r="AU25">
+        <v>4</v>
+      </c>
+      <c r="AV25">
+        <v>6</v>
+      </c>
+      <c r="AW25">
+        <v>1</v>
+      </c>
+      <c r="AY25">
+        <v>4</v>
+      </c>
+      <c r="AZ25">
+        <v>1</v>
+      </c>
+      <c r="BA25">
+        <v>3</v>
+      </c>
+      <c r="BC25">
+        <v>5</v>
+      </c>
+      <c r="BD25">
+        <v>2</v>
+      </c>
+      <c r="BE25">
+        <v>3</v>
+      </c>
+      <c r="BF25">
+        <v>3</v>
+      </c>
+      <c r="BG25">
+        <v>3</v>
+      </c>
+      <c r="BH25">
+        <v>1</v>
+      </c>
+      <c r="BI25">
+        <v>5</v>
+      </c>
+      <c r="BJ25">
+        <v>1</v>
+      </c>
+      <c r="BK25">
+        <v>1</v>
+      </c>
+      <c r="BL25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>342</v>
       </c>
-      <c r="T25">
+      <c r="T26">
         <v>4</v>
       </c>
-      <c r="AH25">
-        <v>1</v>
-      </c>
-      <c r="AK25">
-        <v>1</v>
-      </c>
-      <c r="BQ25">
+      <c r="AH26">
+        <v>1</v>
+      </c>
+      <c r="AK26">
+        <v>1</v>
+      </c>
+      <c r="BQ26">
         <v>2</v>
       </c>
-      <c r="BV25">
+      <c r="BV26">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="27" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="28" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>12</v>
-      </c>
-      <c r="N28">
-        <v>2</v>
-      </c>
-      <c r="U28">
-        <v>1</v>
-      </c>
-      <c r="AI28">
-        <v>1</v>
+        <v>388</v>
       </c>
     </row>
     <row r="29" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>3</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29">
-        <v>3</v>
-      </c>
-      <c r="P29">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="N29">
+        <v>2</v>
       </c>
       <c r="U29">
-        <v>3</v>
-      </c>
-      <c r="W29">
-        <v>1</v>
-      </c>
-      <c r="AD29">
-        <v>1</v>
-      </c>
-      <c r="AF29">
-        <v>1</v>
-      </c>
-      <c r="AH29">
         <v>1</v>
       </c>
       <c r="AI29">
         <v>1</v>
-      </c>
-      <c r="AJ29">
-        <v>2</v>
-      </c>
-      <c r="AO29">
-        <v>2</v>
-      </c>
-      <c r="AP29">
-        <v>2</v>
-      </c>
-      <c r="AQ29">
-        <v>4</v>
-      </c>
-      <c r="AR29">
-        <v>2</v>
-      </c>
-      <c r="AT29">
-        <v>1</v>
-      </c>
-      <c r="AU29">
-        <v>2</v>
-      </c>
-      <c r="AV29">
-        <v>1</v>
-      </c>
-      <c r="AW29">
-        <v>1</v>
-      </c>
-      <c r="AX29">
-        <v>1</v>
-      </c>
-      <c r="AZ29">
-        <v>2</v>
-      </c>
-      <c r="BA29">
-        <v>2</v>
-      </c>
-      <c r="BB29">
-        <v>1</v>
-      </c>
-      <c r="BD29">
-        <v>2</v>
-      </c>
-      <c r="BE29">
-        <v>3</v>
-      </c>
-      <c r="BF29">
-        <v>1</v>
-      </c>
-      <c r="BG29">
-        <v>1</v>
-      </c>
-      <c r="BJ29">
-        <v>1</v>
-      </c>
-      <c r="BK29">
-        <v>1</v>
-      </c>
-      <c r="BL29">
-        <v>1</v>
-      </c>
-      <c r="BM29">
-        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>361</v>
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>3</v>
+      </c>
+      <c r="P30">
+        <v>3</v>
+      </c>
+      <c r="U30">
+        <v>3</v>
+      </c>
+      <c r="W30">
+        <v>1</v>
       </c>
       <c r="AD30">
+        <v>1</v>
+      </c>
+      <c r="AF30">
+        <v>1</v>
+      </c>
+      <c r="AH30">
+        <v>1</v>
+      </c>
+      <c r="AI30">
+        <v>1</v>
+      </c>
+      <c r="AJ30">
         <v>2</v>
       </c>
-      <c r="AM30">
+      <c r="AO30">
+        <v>2</v>
+      </c>
+      <c r="AP30">
+        <v>2</v>
+      </c>
+      <c r="AQ30">
+        <v>4</v>
+      </c>
+      <c r="AR30">
+        <v>2</v>
+      </c>
+      <c r="AT30">
         <v>1</v>
       </c>
       <c r="AU30">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AV30">
+        <v>1</v>
+      </c>
+      <c r="AW30">
+        <v>1</v>
+      </c>
+      <c r="AX30">
+        <v>1</v>
+      </c>
+      <c r="AZ30">
+        <v>2</v>
+      </c>
+      <c r="BA30">
+        <v>2</v>
+      </c>
+      <c r="BB30">
+        <v>1</v>
+      </c>
+      <c r="BD30">
+        <v>2</v>
+      </c>
+      <c r="BE30">
+        <v>3</v>
       </c>
       <c r="BF30">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="BG30">
+        <v>1</v>
+      </c>
+      <c r="BJ30">
+        <v>1</v>
+      </c>
+      <c r="BK30">
+        <v>1</v>
+      </c>
+      <c r="BL30">
+        <v>1</v>
+      </c>
+      <c r="BM30">
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>389</v>
-      </c>
-      <c r="BO31">
+        <v>361</v>
+      </c>
+      <c r="AD31">
+        <v>2</v>
+      </c>
+      <c r="AM31">
+        <v>1</v>
+      </c>
+      <c r="AU31">
+        <v>1</v>
+      </c>
+      <c r="BF31">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32">
+        <v>389</v>
+      </c>
+      <c r="BO32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
         <v>2</v>
       </c>
-      <c r="I32">
+      <c r="I33">
         <v>2</v>
       </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-      <c r="K32">
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
         <v>2</v>
       </c>
-      <c r="L32">
-        <v>1</v>
-      </c>
-      <c r="M32">
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
         <v>2</v>
       </c>
-      <c r="N32">
-        <v>1</v>
-      </c>
-      <c r="O32">
-        <v>1</v>
-      </c>
-      <c r="P32">
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>1</v>
+      </c>
+      <c r="P33">
         <v>2</v>
       </c>
-      <c r="R32">
-        <v>1</v>
-      </c>
-      <c r="T32">
-        <v>1</v>
-      </c>
-      <c r="U32">
+      <c r="R33">
+        <v>1</v>
+      </c>
+      <c r="T33">
+        <v>1</v>
+      </c>
+      <c r="U33">
         <v>2</v>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <v>2</v>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <v>2</v>
       </c>
-      <c r="AD32">
-        <v>1</v>
-      </c>
-      <c r="AH32">
-        <v>1</v>
-      </c>
-      <c r="AJ32">
-        <v>1</v>
-      </c>
-      <c r="AN32">
+      <c r="AD33">
+        <v>1</v>
+      </c>
+      <c r="AH33">
+        <v>1</v>
+      </c>
+      <c r="AJ33">
+        <v>1</v>
+      </c>
+      <c r="AN33">
         <v>2</v>
       </c>
-      <c r="AO32">
-        <v>1</v>
-      </c>
-      <c r="AP32">
+      <c r="AO33">
+        <v>1</v>
+      </c>
+      <c r="AP33">
         <v>2</v>
       </c>
-      <c r="AQ32">
-        <v>1</v>
-      </c>
-      <c r="AS32">
+      <c r="AQ33">
+        <v>1</v>
+      </c>
+      <c r="AS33">
         <v>2</v>
       </c>
-      <c r="AW32">
-        <v>1</v>
-      </c>
-      <c r="AX32">
-        <v>1</v>
-      </c>
-      <c r="AY32">
+      <c r="AW33">
+        <v>1</v>
+      </c>
+      <c r="AX33">
+        <v>1</v>
+      </c>
+      <c r="AY33">
         <v>2</v>
       </c>
-      <c r="AZ32">
+      <c r="AZ33">
         <v>2</v>
       </c>
-      <c r="BA32">
-        <v>1</v>
-      </c>
-      <c r="BB32">
+      <c r="BA33">
+        <v>1</v>
+      </c>
+      <c r="BB33">
         <v>2</v>
       </c>
-      <c r="BC32">
+      <c r="BC33">
         <v>4</v>
       </c>
-      <c r="BD32">
-        <v>1</v>
-      </c>
-      <c r="BE32">
-        <v>1</v>
-      </c>
-      <c r="BG32">
+      <c r="BD33">
+        <v>1</v>
+      </c>
+      <c r="BE33">
+        <v>1</v>
+      </c>
+      <c r="BG33">
         <v>2</v>
       </c>
-      <c r="BH32">
+      <c r="BH33">
         <v>3</v>
       </c>
-      <c r="BJ32">
-        <v>1</v>
-      </c>
-      <c r="BM32">
+      <c r="BJ33">
+        <v>1</v>
+      </c>
+      <c r="BM33">
         <v>3</v>
       </c>
-      <c r="BN32">
-        <v>1</v>
-      </c>
-      <c r="BP32">
-        <v>1</v>
-      </c>
-      <c r="BR32">
+      <c r="BN33">
+        <v>1</v>
+      </c>
+      <c r="BP33">
+        <v>1</v>
+      </c>
+      <c r="BR33">
         <v>3</v>
       </c>
-      <c r="BV32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="BV33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>351</v>
       </c>
-      <c r="Z33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="G34">
-        <v>2</v>
-      </c>
-      <c r="H34">
-        <v>2</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
-      </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-      <c r="K34">
-        <v>2</v>
-      </c>
-      <c r="L34">
-        <v>5</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="O34">
-        <v>4</v>
-      </c>
-      <c r="P34">
-        <v>1</v>
-      </c>
-      <c r="Q34">
-        <v>2</v>
-      </c>
-      <c r="T34">
-        <v>6</v>
-      </c>
-      <c r="X34">
-        <v>2</v>
-      </c>
-      <c r="Y34">
-        <v>2</v>
-      </c>
       <c r="Z34">
         <v>1</v>
-      </c>
-      <c r="AA34">
-        <v>1</v>
-      </c>
-      <c r="AB34">
-        <v>1</v>
-      </c>
-      <c r="AC34">
-        <v>3</v>
-      </c>
-      <c r="AF34">
-        <v>4</v>
-      </c>
-      <c r="AI34">
-        <v>1</v>
-      </c>
-      <c r="AL34">
-        <v>1</v>
-      </c>
-      <c r="AN34">
-        <v>1</v>
-      </c>
-      <c r="AR34">
-        <v>2</v>
-      </c>
-      <c r="AS34">
-        <v>3</v>
-      </c>
-      <c r="AT34">
-        <v>1</v>
-      </c>
-      <c r="AW34">
-        <v>2</v>
-      </c>
-      <c r="AX34">
-        <v>5</v>
-      </c>
-      <c r="AY34">
-        <v>3</v>
-      </c>
-      <c r="AZ34">
-        <v>1</v>
-      </c>
-      <c r="BA34">
-        <v>3</v>
-      </c>
-      <c r="BB34">
-        <v>2</v>
-      </c>
-      <c r="BD34">
-        <v>3</v>
-      </c>
-      <c r="BF34">
-        <v>3</v>
-      </c>
-      <c r="BG34">
-        <v>4</v>
-      </c>
-      <c r="BH34">
-        <v>3</v>
-      </c>
-      <c r="BI34">
-        <v>2</v>
-      </c>
-      <c r="BJ34">
-        <v>1</v>
-      </c>
-      <c r="BL34">
-        <v>1</v>
-      </c>
-      <c r="BM34">
-        <v>2</v>
-      </c>
-      <c r="BN34">
-        <v>1</v>
-      </c>
-      <c r="BP34">
-        <v>1</v>
-      </c>
-      <c r="BQ34">
-        <v>2</v>
-      </c>
-      <c r="BR34">
-        <v>3</v>
-      </c>
-      <c r="BS34">
-        <v>2</v>
-      </c>
-      <c r="BV34">
-        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>381</v>
+        <v>9</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
+      </c>
+      <c r="L35">
+        <v>5</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <v>4</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+      <c r="Q35">
+        <v>2</v>
+      </c>
+      <c r="T35">
+        <v>6</v>
+      </c>
+      <c r="X35">
+        <v>2</v>
+      </c>
+      <c r="Y35">
+        <v>2</v>
+      </c>
+      <c r="Z35">
+        <v>1</v>
+      </c>
+      <c r="AA35">
+        <v>1</v>
+      </c>
+      <c r="AB35">
+        <v>1</v>
+      </c>
+      <c r="AC35">
+        <v>3</v>
+      </c>
+      <c r="AF35">
+        <v>4</v>
+      </c>
+      <c r="AI35">
+        <v>1</v>
+      </c>
+      <c r="AL35">
+        <v>1</v>
+      </c>
+      <c r="AN35">
+        <v>1</v>
+      </c>
+      <c r="AR35">
+        <v>2</v>
+      </c>
+      <c r="AS35">
+        <v>3</v>
+      </c>
+      <c r="AT35">
+        <v>1</v>
+      </c>
+      <c r="AW35">
+        <v>2</v>
+      </c>
+      <c r="AX35">
+        <v>5</v>
+      </c>
+      <c r="AY35">
+        <v>3</v>
+      </c>
+      <c r="AZ35">
+        <v>1</v>
+      </c>
+      <c r="BA35">
+        <v>3</v>
+      </c>
+      <c r="BB35">
+        <v>2</v>
+      </c>
+      <c r="BD35">
+        <v>3</v>
+      </c>
+      <c r="BF35">
+        <v>3</v>
       </c>
       <c r="BG35">
+        <v>4</v>
+      </c>
+      <c r="BH35">
+        <v>3</v>
+      </c>
+      <c r="BI35">
         <v>2</v>
+      </c>
+      <c r="BJ35">
+        <v>1</v>
+      </c>
+      <c r="BL35">
+        <v>1</v>
+      </c>
+      <c r="BM35">
+        <v>2</v>
+      </c>
+      <c r="BN35">
+        <v>1</v>
+      </c>
+      <c r="BP35">
+        <v>1</v>
+      </c>
+      <c r="BQ35">
+        <v>2</v>
+      </c>
+      <c r="BR35">
+        <v>3</v>
+      </c>
+      <c r="BS35">
+        <v>2</v>
+      </c>
+      <c r="BV35">
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <v>2</v>
-      </c>
-      <c r="G36">
-        <v>2</v>
-      </c>
-      <c r="H36">
-        <v>4</v>
-      </c>
-      <c r="J36">
-        <v>2</v>
-      </c>
-      <c r="K36">
-        <v>2</v>
-      </c>
-      <c r="L36">
-        <v>1</v>
-      </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-      <c r="P36">
-        <v>1</v>
-      </c>
-      <c r="Q36">
-        <v>1</v>
-      </c>
-      <c r="R36">
-        <v>3</v>
-      </c>
-      <c r="S36">
-        <v>2</v>
-      </c>
-      <c r="T36">
-        <v>2</v>
-      </c>
-      <c r="U36">
-        <v>2</v>
-      </c>
-      <c r="W36">
-        <v>3</v>
-      </c>
-      <c r="X36">
-        <v>3</v>
-      </c>
-      <c r="Y36">
-        <v>2</v>
-      </c>
-      <c r="AA36">
-        <v>2</v>
-      </c>
-      <c r="AB36">
-        <v>2</v>
-      </c>
-      <c r="AC36">
-        <v>2</v>
-      </c>
-      <c r="AE36">
-        <v>2</v>
-      </c>
-      <c r="AF36">
-        <v>1</v>
-      </c>
-      <c r="AG36">
-        <v>2</v>
-      </c>
-      <c r="AJ36">
-        <v>4</v>
-      </c>
-      <c r="AK36">
-        <v>2</v>
-      </c>
-      <c r="AM36">
-        <v>1</v>
-      </c>
-      <c r="AN36">
-        <v>1</v>
-      </c>
-      <c r="AO36">
-        <v>1</v>
-      </c>
-      <c r="AP36">
-        <v>1</v>
-      </c>
-      <c r="AU36">
-        <v>1</v>
-      </c>
-      <c r="AV36">
-        <v>1</v>
-      </c>
-      <c r="AW36">
-        <v>2</v>
-      </c>
-      <c r="BA36">
-        <v>1</v>
-      </c>
-      <c r="BH36">
-        <v>2</v>
-      </c>
-      <c r="BJ36">
-        <v>2</v>
-      </c>
-      <c r="BK36">
-        <v>3</v>
-      </c>
-      <c r="BP36">
+        <v>381</v>
+      </c>
+      <c r="BG36">
         <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37">
+        <v>4</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37">
+        <v>2</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="Q37">
+        <v>1</v>
+      </c>
+      <c r="R37">
+        <v>3</v>
+      </c>
+      <c r="S37">
+        <v>2</v>
+      </c>
+      <c r="T37">
+        <v>2</v>
+      </c>
+      <c r="U37">
+        <v>2</v>
+      </c>
+      <c r="W37">
+        <v>3</v>
+      </c>
+      <c r="X37">
+        <v>3</v>
+      </c>
+      <c r="Y37">
+        <v>2</v>
+      </c>
+      <c r="AA37">
+        <v>2</v>
+      </c>
+      <c r="AB37">
+        <v>2</v>
+      </c>
+      <c r="AC37">
+        <v>2</v>
+      </c>
+      <c r="AE37">
+        <v>2</v>
+      </c>
+      <c r="AF37">
+        <v>1</v>
+      </c>
+      <c r="AG37">
+        <v>2</v>
+      </c>
+      <c r="AJ37">
+        <v>4</v>
+      </c>
+      <c r="AK37">
+        <v>2</v>
+      </c>
+      <c r="AM37">
+        <v>1</v>
+      </c>
+      <c r="AN37">
+        <v>1</v>
+      </c>
+      <c r="AO37">
+        <v>1</v>
+      </c>
+      <c r="AP37">
+        <v>1</v>
+      </c>
+      <c r="AU37">
+        <v>1</v>
+      </c>
+      <c r="AV37">
+        <v>1</v>
+      </c>
+      <c r="AW37">
+        <v>2</v>
+      </c>
+      <c r="BA37">
+        <v>1</v>
+      </c>
+      <c r="BH37">
+        <v>2</v>
+      </c>
+      <c r="BJ37">
+        <v>2</v>
+      </c>
+      <c r="BK37">
+        <v>3</v>
+      </c>
+      <c r="BP37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>80</v>
       </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="F38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>61</v>
       </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>374</v>
-      </c>
-      <c r="AW39">
-        <v>2</v>
+      <c r="D39">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40">
+        <v>374</v>
+      </c>
+      <c r="AW40">
         <v>2</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="F40">
-        <v>4</v>
-      </c>
-      <c r="G40">
-        <v>3</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
-      <c r="M40">
-        <v>2</v>
-      </c>
-      <c r="N40">
-        <v>3</v>
-      </c>
-      <c r="T40">
-        <v>1</v>
-      </c>
-      <c r="X40">
-        <v>1</v>
-      </c>
-      <c r="AA40">
-        <v>2</v>
-      </c>
-      <c r="AB40">
-        <v>2</v>
-      </c>
-      <c r="AC40">
-        <v>1</v>
-      </c>
-      <c r="AD40">
-        <v>2</v>
-      </c>
-      <c r="AE40">
-        <v>1</v>
-      </c>
-      <c r="AG40">
-        <v>1</v>
-      </c>
-      <c r="AH40">
-        <v>2</v>
-      </c>
-      <c r="AJ40">
-        <v>1</v>
-      </c>
-      <c r="AM40">
-        <v>4</v>
-      </c>
-      <c r="AN40">
-        <v>1</v>
-      </c>
-      <c r="AP40">
-        <v>1</v>
-      </c>
-      <c r="AR40">
-        <v>1</v>
-      </c>
-      <c r="AS40">
-        <v>1</v>
-      </c>
-      <c r="AT40">
-        <v>1</v>
-      </c>
-      <c r="AV40">
-        <v>1</v>
-      </c>
-      <c r="AZ40">
-        <v>2</v>
-      </c>
-      <c r="BA40">
-        <v>1</v>
-      </c>
-      <c r="BC40">
-        <v>3</v>
-      </c>
-      <c r="BD40">
-        <v>1</v>
-      </c>
-      <c r="BI40">
-        <v>1</v>
-      </c>
-      <c r="BJ40">
-        <v>1</v>
-      </c>
-      <c r="BK40">
-        <v>3</v>
-      </c>
-      <c r="BL40">
-        <v>2</v>
-      </c>
-      <c r="BM40">
-        <v>5</v>
-      </c>
-      <c r="BO40">
-        <v>1</v>
-      </c>
-      <c r="BP40">
-        <v>3</v>
-      </c>
-      <c r="BQ40">
-        <v>3</v>
-      </c>
-      <c r="BS40">
-        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ41">
+        <v>19</v>
+      </c>
+      <c r="B41">
         <v>2</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>2</v>
+      </c>
+      <c r="N41">
+        <v>3</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="AA41">
+        <v>2</v>
+      </c>
+      <c r="AB41">
+        <v>2</v>
+      </c>
+      <c r="AC41">
+        <v>1</v>
+      </c>
+      <c r="AD41">
+        <v>2</v>
+      </c>
+      <c r="AE41">
+        <v>1</v>
+      </c>
+      <c r="AG41">
+        <v>1</v>
+      </c>
+      <c r="AH41">
+        <v>2</v>
+      </c>
+      <c r="AJ41">
+        <v>1</v>
+      </c>
+      <c r="AM41">
+        <v>4</v>
+      </c>
+      <c r="AN41">
+        <v>1</v>
+      </c>
+      <c r="AP41">
+        <v>1</v>
+      </c>
+      <c r="AR41">
+        <v>1</v>
+      </c>
+      <c r="AS41">
+        <v>1</v>
+      </c>
+      <c r="AT41">
+        <v>1</v>
+      </c>
+      <c r="AV41">
+        <v>1</v>
+      </c>
+      <c r="AZ41">
+        <v>2</v>
+      </c>
+      <c r="BA41">
+        <v>1</v>
+      </c>
+      <c r="BC41">
+        <v>3</v>
+      </c>
+      <c r="BD41">
+        <v>1</v>
+      </c>
+      <c r="BI41">
+        <v>1</v>
+      </c>
+      <c r="BJ41">
+        <v>1</v>
+      </c>
+      <c r="BK41">
+        <v>3</v>
+      </c>
+      <c r="BL41">
+        <v>2</v>
+      </c>
+      <c r="BM41">
+        <v>5</v>
+      </c>
+      <c r="BO41">
+        <v>1</v>
+      </c>
+      <c r="BP41">
+        <v>3</v>
+      </c>
+      <c r="BQ41">
+        <v>3</v>
+      </c>
+      <c r="BS41">
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>68</v>
       </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="I42">
-        <v>1</v>
-      </c>
-      <c r="N42">
-        <v>1</v>
-      </c>
-      <c r="W42">
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="W43">
         <v>2</v>
       </c>
-      <c r="AQ42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="AQ43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>53</v>
       </c>
-      <c r="N43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>368</v>
-      </c>
-      <c r="AM44">
-        <v>5</v>
-      </c>
-      <c r="BB44">
-        <v>9</v>
-      </c>
-      <c r="BN44">
-        <v>2</v>
+      <c r="N44">
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>345</v>
-      </c>
-      <c r="U45">
-        <v>1</v>
-      </c>
-      <c r="BR45">
-        <v>1</v>
-      </c>
-      <c r="BS45">
-        <v>1</v>
-      </c>
-      <c r="BT45">
-        <v>1</v>
+        <v>368</v>
+      </c>
+      <c r="AM45">
+        <v>5</v>
+      </c>
+      <c r="BB45">
+        <v>9</v>
+      </c>
+      <c r="BN45">
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>343</v>
-      </c>
-      <c r="AN46">
+        <v>345</v>
+      </c>
+      <c r="U46">
         <v>1</v>
       </c>
       <c r="BR46">
@@ -46734,1404 +46723,1421 @@
         <v>1</v>
       </c>
       <c r="BT46">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>344</v>
-      </c>
-      <c r="X47">
-        <v>1</v>
-      </c>
-      <c r="Y47">
-        <v>2</v>
-      </c>
-      <c r="AF47">
-        <v>2</v>
+        <v>343</v>
+      </c>
+      <c r="AN47">
+        <v>1</v>
+      </c>
+      <c r="BR47">
+        <v>1</v>
+      </c>
+      <c r="BS47">
+        <v>1</v>
+      </c>
+      <c r="BT47">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48">
+        <v>344</v>
+      </c>
+      <c r="X48">
+        <v>1</v>
+      </c>
+      <c r="Y48">
         <v>2</v>
-      </c>
-      <c r="C48">
-        <v>3</v>
-      </c>
-      <c r="F48">
-        <v>2</v>
-      </c>
-      <c r="I48">
-        <v>2</v>
-      </c>
-      <c r="J48">
-        <v>2</v>
-      </c>
-      <c r="K48">
-        <v>1</v>
-      </c>
-      <c r="L48">
-        <v>1</v>
-      </c>
-      <c r="M48">
-        <v>1</v>
-      </c>
-      <c r="O48">
-        <v>2</v>
-      </c>
-      <c r="R48">
-        <v>3</v>
-      </c>
-      <c r="S48">
-        <v>1</v>
-      </c>
-      <c r="T48">
-        <v>1</v>
-      </c>
-      <c r="V48">
-        <v>1</v>
-      </c>
-      <c r="W48">
-        <v>3</v>
-      </c>
-      <c r="X48">
-        <v>1</v>
-      </c>
-      <c r="Y48">
-        <v>1</v>
-      </c>
-      <c r="Z48">
-        <v>1.5</v>
-      </c>
-      <c r="AC48">
-        <v>1</v>
-      </c>
-      <c r="AD48">
-        <v>2</v>
-      </c>
-      <c r="AE48">
-        <v>1</v>
       </c>
       <c r="AF48">
         <v>2</v>
       </c>
-      <c r="AH48">
-        <v>2</v>
-      </c>
-      <c r="AL48">
-        <v>3</v>
-      </c>
-      <c r="AP48">
-        <v>2</v>
-      </c>
-      <c r="AQ48">
-        <v>4</v>
-      </c>
-      <c r="AR48">
-        <v>3</v>
-      </c>
-      <c r="AS48">
-        <v>0.5</v>
-      </c>
-      <c r="AU48">
-        <v>2</v>
-      </c>
-      <c r="AV48">
-        <v>1</v>
-      </c>
-      <c r="BC48">
-        <v>1</v>
-      </c>
-      <c r="BD48">
-        <v>1</v>
-      </c>
-      <c r="BE48">
-        <v>7</v>
-      </c>
-      <c r="BH48">
-        <v>1</v>
-      </c>
-      <c r="BI48">
-        <v>1</v>
-      </c>
-      <c r="BJ48">
-        <v>3</v>
-      </c>
-      <c r="BK48">
-        <v>3</v>
-      </c>
-      <c r="BL48">
-        <v>1</v>
-      </c>
-      <c r="BM48">
-        <v>1</v>
-      </c>
-      <c r="BN48">
-        <v>4</v>
-      </c>
-      <c r="BP48">
-        <v>1</v>
-      </c>
-      <c r="BQ48">
-        <v>3</v>
-      </c>
-      <c r="BR48">
-        <v>1</v>
-      </c>
-      <c r="BT48">
-        <v>1</v>
-      </c>
-      <c r="BV48">
-        <v>1</v>
-      </c>
     </row>
     <row r="49" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B49">
+        <v>2</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="I49">
+        <v>2</v>
+      </c>
+      <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49">
         <v>1</v>
       </c>
       <c r="O49">
+        <v>2</v>
+      </c>
+      <c r="R49">
         <v>3</v>
       </c>
-      <c r="P49">
-        <v>1</v>
-      </c>
-      <c r="Q49">
+      <c r="S49">
+        <v>1</v>
+      </c>
+      <c r="T49">
+        <v>1</v>
+      </c>
+      <c r="V49">
+        <v>1</v>
+      </c>
+      <c r="W49">
+        <v>3</v>
+      </c>
+      <c r="X49">
+        <v>1</v>
+      </c>
+      <c r="Y49">
+        <v>1</v>
+      </c>
+      <c r="Z49">
+        <v>1.5</v>
+      </c>
+      <c r="AC49">
+        <v>1</v>
+      </c>
+      <c r="AD49">
         <v>2</v>
       </c>
-      <c r="AM49">
-        <v>1</v>
-      </c>
-      <c r="AN49">
-        <v>1</v>
+      <c r="AE49">
+        <v>1</v>
+      </c>
+      <c r="AF49">
+        <v>2</v>
+      </c>
+      <c r="AH49">
+        <v>2</v>
+      </c>
+      <c r="AL49">
+        <v>3</v>
       </c>
       <c r="AP49">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AQ49">
+        <v>4</v>
+      </c>
+      <c r="AR49">
+        <v>3</v>
       </c>
       <c r="AS49">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="AU49">
+        <v>2</v>
       </c>
       <c r="AV49">
         <v>1</v>
       </c>
-      <c r="AX49">
-        <v>5</v>
-      </c>
-      <c r="AY49">
-        <v>1</v>
-      </c>
-      <c r="BA49">
-        <v>2</v>
-      </c>
-      <c r="BB49">
+      <c r="BC49">
+        <v>1</v>
+      </c>
+      <c r="BD49">
+        <v>1</v>
+      </c>
+      <c r="BE49">
+        <v>7</v>
+      </c>
+      <c r="BH49">
+        <v>1</v>
+      </c>
+      <c r="BI49">
+        <v>1</v>
+      </c>
+      <c r="BJ49">
+        <v>3</v>
+      </c>
+      <c r="BK49">
+        <v>3</v>
+      </c>
+      <c r="BL49">
+        <v>1</v>
+      </c>
+      <c r="BM49">
+        <v>1</v>
+      </c>
+      <c r="BN49">
         <v>4</v>
       </c>
-      <c r="BE49">
+      <c r="BP49">
+        <v>1</v>
+      </c>
+      <c r="BQ49">
         <v>3</v>
       </c>
-      <c r="BF49">
-        <v>2</v>
-      </c>
-      <c r="BH49">
-        <v>3</v>
-      </c>
-      <c r="BK49">
+      <c r="BR49">
         <v>1</v>
       </c>
       <c r="BT49">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="BV49">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>377</v>
+        <v>46</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="O50">
+        <v>3</v>
+      </c>
+      <c r="P50">
+        <v>1</v>
+      </c>
+      <c r="Q50">
+        <v>2</v>
+      </c>
+      <c r="AM50">
+        <v>1</v>
+      </c>
+      <c r="AN50">
+        <v>1</v>
+      </c>
+      <c r="AP50">
+        <v>1</v>
+      </c>
+      <c r="AS50">
+        <v>1</v>
+      </c>
+      <c r="AV50">
+        <v>1</v>
+      </c>
+      <c r="AX50">
+        <v>5</v>
+      </c>
+      <c r="AY50">
+        <v>1</v>
+      </c>
+      <c r="BA50">
+        <v>2</v>
+      </c>
+      <c r="BB50">
+        <v>4</v>
+      </c>
+      <c r="BE50">
+        <v>3</v>
+      </c>
+      <c r="BF50">
+        <v>2</v>
+      </c>
+      <c r="BH50">
+        <v>3</v>
+      </c>
+      <c r="BK50">
+        <v>1</v>
+      </c>
+      <c r="BT50">
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="52" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>3</v>
       </c>
-      <c r="F51">
+      <c r="F52">
         <v>3</v>
       </c>
-      <c r="L51">
-        <v>1</v>
-      </c>
-      <c r="S51">
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="S52">
         <v>3</v>
       </c>
-      <c r="AH51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="AH52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>350</v>
-      </c>
-    </row>
-    <row r="53" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>56</v>
-      </c>
-      <c r="C53">
-        <v>3</v>
-      </c>
-      <c r="E53">
-        <v>2</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="G53">
-        <v>2</v>
-      </c>
-      <c r="I53">
-        <v>1</v>
-      </c>
-      <c r="J53">
-        <v>1</v>
-      </c>
-      <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="L53">
-        <v>1</v>
-      </c>
-      <c r="M53">
-        <v>1</v>
-      </c>
-      <c r="P53">
-        <v>1</v>
-      </c>
-      <c r="R53">
-        <v>1</v>
-      </c>
-      <c r="S53">
-        <v>4</v>
-      </c>
-      <c r="T53">
-        <v>1</v>
-      </c>
-      <c r="V53">
-        <v>1</v>
-      </c>
-      <c r="W53">
-        <v>2</v>
-      </c>
-      <c r="Z53">
-        <v>2</v>
-      </c>
-      <c r="AA53">
-        <v>1</v>
-      </c>
-      <c r="AB53">
-        <v>4</v>
-      </c>
-      <c r="AC53">
-        <v>1</v>
-      </c>
-      <c r="AD53">
-        <v>1</v>
-      </c>
-      <c r="AX53">
-        <v>1</v>
-      </c>
-      <c r="AY53">
-        <v>1</v>
-      </c>
-      <c r="AZ53">
-        <v>2</v>
-      </c>
-      <c r="BD53">
-        <v>1</v>
-      </c>
-      <c r="BF53">
-        <v>1</v>
-      </c>
-      <c r="BH53">
-        <v>1</v>
-      </c>
-      <c r="BI53">
-        <v>1</v>
-      </c>
-      <c r="BJ53">
-        <v>2</v>
-      </c>
-      <c r="BK53">
-        <v>1</v>
-      </c>
-      <c r="BL53">
-        <v>2</v>
-      </c>
-      <c r="BM53">
-        <v>2</v>
-      </c>
-      <c r="BN53">
-        <v>2</v>
-      </c>
-      <c r="BO53">
-        <v>1</v>
-      </c>
-      <c r="BP53">
-        <v>1</v>
-      </c>
-      <c r="BR53">
-        <v>1</v>
-      </c>
-      <c r="BS53">
-        <v>2</v>
-      </c>
-      <c r="BU53">
-        <v>2</v>
-      </c>
-      <c r="BV53">
-        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>369</v>
-      </c>
-      <c r="AN54">
+        <v>56</v>
+      </c>
+      <c r="C54">
         <v>3</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="P54">
+        <v>1</v>
+      </c>
+      <c r="R54">
+        <v>1</v>
+      </c>
+      <c r="S54">
+        <v>4</v>
+      </c>
+      <c r="T54">
+        <v>1</v>
+      </c>
+      <c r="V54">
+        <v>1</v>
+      </c>
+      <c r="W54">
+        <v>2</v>
+      </c>
+      <c r="Z54">
+        <v>2</v>
+      </c>
+      <c r="AA54">
+        <v>1</v>
+      </c>
+      <c r="AB54">
+        <v>4</v>
+      </c>
+      <c r="AC54">
+        <v>1</v>
+      </c>
+      <c r="AD54">
+        <v>1</v>
+      </c>
+      <c r="AX54">
+        <v>1</v>
+      </c>
+      <c r="AY54">
+        <v>1</v>
+      </c>
+      <c r="AZ54">
+        <v>2</v>
+      </c>
+      <c r="BD54">
+        <v>1</v>
+      </c>
+      <c r="BF54">
+        <v>1</v>
+      </c>
+      <c r="BH54">
+        <v>1</v>
+      </c>
+      <c r="BI54">
+        <v>1</v>
+      </c>
+      <c r="BJ54">
+        <v>2</v>
+      </c>
+      <c r="BK54">
+        <v>1</v>
+      </c>
+      <c r="BL54">
+        <v>2</v>
+      </c>
+      <c r="BM54">
+        <v>2</v>
+      </c>
+      <c r="BN54">
+        <v>2</v>
+      </c>
+      <c r="BO54">
+        <v>1</v>
+      </c>
+      <c r="BP54">
+        <v>1</v>
+      </c>
+      <c r="BR54">
+        <v>1</v>
+      </c>
+      <c r="BS54">
+        <v>2</v>
+      </c>
+      <c r="BU54">
+        <v>2</v>
+      </c>
+      <c r="BV54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>387</v>
-      </c>
-      <c r="BN55">
+        <v>369</v>
+      </c>
+      <c r="AN55">
         <v>3</v>
-      </c>
-      <c r="BO55">
-        <v>2</v>
-      </c>
-      <c r="BQ55">
-        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>60</v>
-      </c>
-      <c r="B56">
+        <v>387</v>
+      </c>
+      <c r="BN56">
+        <v>3</v>
+      </c>
+      <c r="BO56">
         <v>2</v>
       </c>
-      <c r="BF56">
-        <v>1</v>
-      </c>
-      <c r="BT56">
+      <c r="BQ56">
         <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q57">
-        <v>1</v>
-      </c>
-      <c r="U57">
-        <v>1</v>
-      </c>
-      <c r="W57">
-        <v>1</v>
-      </c>
-      <c r="X57">
-        <v>3</v>
-      </c>
-      <c r="Y57">
-        <v>1</v>
-      </c>
-      <c r="Z57">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="BF57">
+        <v>1</v>
+      </c>
+      <c r="BT57">
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>339</v>
+        <v>340</v>
+      </c>
+      <c r="Q58">
+        <v>1</v>
+      </c>
+      <c r="U58">
+        <v>1</v>
+      </c>
+      <c r="W58">
+        <v>1</v>
+      </c>
+      <c r="X58">
+        <v>3</v>
+      </c>
+      <c r="Y58">
+        <v>1</v>
+      </c>
+      <c r="Z58">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>339</v>
       </c>
     </row>
     <row r="60" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60">
-        <v>1</v>
-      </c>
-      <c r="F60">
-        <v>3</v>
-      </c>
-      <c r="G60">
-        <v>2</v>
-      </c>
-      <c r="H60">
-        <v>3</v>
-      </c>
-      <c r="J60">
-        <v>1</v>
-      </c>
-      <c r="K60">
-        <v>1</v>
-      </c>
-      <c r="M60">
-        <v>3</v>
-      </c>
-      <c r="N60">
-        <v>4</v>
-      </c>
-      <c r="X60">
-        <v>6</v>
-      </c>
-      <c r="Y60">
-        <v>5</v>
-      </c>
-      <c r="Z60">
-        <v>1</v>
-      </c>
-      <c r="AD60">
-        <v>2</v>
-      </c>
-      <c r="AG60">
-        <v>3</v>
-      </c>
-      <c r="AJ60">
-        <v>2</v>
-      </c>
-      <c r="AM60">
-        <v>2</v>
-      </c>
-      <c r="AO60">
-        <v>3</v>
-      </c>
-      <c r="AQ60">
-        <v>2</v>
-      </c>
-      <c r="AT60">
-        <v>1</v>
-      </c>
-      <c r="AU60">
-        <v>4</v>
-      </c>
-      <c r="AV60">
-        <v>2</v>
-      </c>
-      <c r="AX60">
-        <v>1</v>
-      </c>
-      <c r="AY60">
-        <v>2</v>
-      </c>
-      <c r="AZ60">
-        <v>1</v>
-      </c>
-      <c r="BA60">
-        <v>4</v>
-      </c>
-      <c r="BB60">
-        <v>2</v>
-      </c>
-      <c r="BH60">
-        <v>1</v>
-      </c>
-      <c r="BR60">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>21</v>
+        <v>55</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
+      <c r="H61">
+        <v>3</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="M61">
+        <v>3</v>
+      </c>
+      <c r="N61">
+        <v>4</v>
+      </c>
+      <c r="X61">
+        <v>6</v>
+      </c>
+      <c r="Y61">
+        <v>5</v>
+      </c>
+      <c r="Z61">
+        <v>1</v>
+      </c>
+      <c r="AD61">
+        <v>2</v>
+      </c>
+      <c r="AG61">
+        <v>3</v>
+      </c>
+      <c r="AJ61">
+        <v>2</v>
+      </c>
+      <c r="AM61">
+        <v>2</v>
+      </c>
+      <c r="AO61">
+        <v>3</v>
+      </c>
+      <c r="AQ61">
+        <v>2</v>
+      </c>
+      <c r="AT61">
+        <v>1</v>
+      </c>
+      <c r="AU61">
+        <v>4</v>
+      </c>
+      <c r="AV61">
+        <v>2</v>
+      </c>
+      <c r="AX61">
+        <v>1</v>
+      </c>
+      <c r="AY61">
+        <v>2</v>
+      </c>
+      <c r="AZ61">
+        <v>1</v>
+      </c>
+      <c r="BA61">
+        <v>4</v>
+      </c>
+      <c r="BB61">
+        <v>2</v>
+      </c>
+      <c r="BH61">
+        <v>1</v>
+      </c>
+      <c r="BR61">
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>81</v>
-      </c>
-      <c r="G62">
-        <v>3</v>
-      </c>
-      <c r="K62">
-        <v>1</v>
-      </c>
-      <c r="BG62">
-        <v>2</v>
-      </c>
-      <c r="BN62">
-        <v>4</v>
-      </c>
-      <c r="BP62">
-        <v>1</v>
-      </c>
-      <c r="BR62">
-        <v>2</v>
-      </c>
-      <c r="BS62">
-        <v>3</v>
-      </c>
-      <c r="BU62">
-        <v>3</v>
-      </c>
-      <c r="BV62">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
+        <v>81</v>
+      </c>
+      <c r="G63">
+        <v>3</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
+      </c>
+      <c r="BG63">
+        <v>2</v>
+      </c>
+      <c r="BN63">
+        <v>4</v>
+      </c>
+      <c r="BP63">
+        <v>1</v>
+      </c>
+      <c r="BR63">
+        <v>2</v>
+      </c>
+      <c r="BS63">
+        <v>3</v>
+      </c>
+      <c r="BU63">
+        <v>3</v>
+      </c>
+      <c r="BV63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>63</v>
       </c>
-      <c r="B63">
+      <c r="B64">
         <v>2</v>
       </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="AF63">
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="AF64">
         <v>2</v>
       </c>
-      <c r="AQ63">
+      <c r="AQ64">
         <v>3</v>
       </c>
-      <c r="BF63">
-        <v>1</v>
-      </c>
-      <c r="BM63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+      <c r="BF64">
+        <v>1</v>
+      </c>
+      <c r="BM64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="65" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y65">
-        <v>1</v>
-      </c>
-      <c r="AB65">
-        <v>2</v>
-      </c>
-      <c r="AD65">
-        <v>3</v>
-      </c>
-      <c r="AI65">
-        <v>1</v>
-      </c>
-      <c r="AR65">
-        <v>4</v>
-      </c>
-      <c r="AV65">
-        <v>3</v>
-      </c>
-      <c r="BA65">
-        <v>2</v>
-      </c>
-      <c r="BB65">
-        <v>5</v>
-      </c>
-      <c r="BE65">
-        <v>6</v>
-      </c>
-      <c r="BS65">
-        <v>1</v>
-      </c>
-      <c r="BT65">
-        <v>1</v>
-      </c>
-      <c r="BU65">
-        <v>2</v>
-      </c>
-      <c r="BV65">
-        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>376</v>
-      </c>
-      <c r="AU66">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="Y66">
+        <v>1</v>
+      </c>
+      <c r="AB66">
+        <v>2</v>
+      </c>
+      <c r="AD66">
+        <v>3</v>
+      </c>
+      <c r="AI66">
+        <v>1</v>
+      </c>
+      <c r="AR66">
+        <v>4</v>
       </c>
       <c r="AV66">
-        <v>1</v>
-      </c>
-      <c r="AW66">
         <v>3</v>
       </c>
-      <c r="AX66">
-        <v>1</v>
-      </c>
-      <c r="AZ66">
-        <v>1</v>
-      </c>
-      <c r="BC66">
+      <c r="BA66">
         <v>2</v>
+      </c>
+      <c r="BB66">
+        <v>5</v>
+      </c>
+      <c r="BE66">
+        <v>6</v>
+      </c>
+      <c r="BS66">
+        <v>1</v>
+      </c>
+      <c r="BT66">
+        <v>1</v>
+      </c>
+      <c r="BU66">
+        <v>2</v>
+      </c>
+      <c r="BV66">
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>44</v>
-      </c>
-      <c r="N67">
+        <v>376</v>
+      </c>
+      <c r="AU67">
+        <v>1</v>
+      </c>
+      <c r="AV67">
+        <v>1</v>
+      </c>
+      <c r="AW67">
         <v>3</v>
       </c>
-      <c r="S67">
+      <c r="AX67">
+        <v>1</v>
+      </c>
+      <c r="AZ67">
+        <v>1</v>
+      </c>
+      <c r="BC67">
         <v>2</v>
-      </c>
-      <c r="AG67">
-        <v>2</v>
-      </c>
-      <c r="AI67">
-        <v>1</v>
-      </c>
-      <c r="AP67">
-        <v>2</v>
-      </c>
-      <c r="AQ67">
-        <v>1</v>
-      </c>
-      <c r="AR67">
-        <v>3</v>
-      </c>
-      <c r="AW67">
-        <v>1</v>
-      </c>
-      <c r="BA67">
-        <v>1</v>
-      </c>
-      <c r="BE67">
-        <v>1</v>
-      </c>
-      <c r="BI67">
-        <v>2</v>
-      </c>
-      <c r="BL67">
-        <v>2</v>
-      </c>
-      <c r="BN67">
-        <v>2</v>
-      </c>
-      <c r="BO67">
-        <v>1</v>
-      </c>
-      <c r="BP67">
-        <v>1</v>
-      </c>
-      <c r="BR67">
-        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>379</v>
-      </c>
-      <c r="BF68">
-        <v>1</v>
-      </c>
-      <c r="BG68">
+        <v>44</v>
+      </c>
+      <c r="N68">
+        <v>3</v>
+      </c>
+      <c r="S68">
+        <v>2</v>
+      </c>
+      <c r="AG68">
+        <v>2</v>
+      </c>
+      <c r="AI68">
+        <v>1</v>
+      </c>
+      <c r="AP68">
+        <v>2</v>
+      </c>
+      <c r="AQ68">
+        <v>1</v>
+      </c>
+      <c r="AR68">
+        <v>3</v>
+      </c>
+      <c r="AW68">
+        <v>1</v>
+      </c>
+      <c r="BA68">
+        <v>1</v>
+      </c>
+      <c r="BE68">
+        <v>1</v>
+      </c>
+      <c r="BI68">
+        <v>2</v>
+      </c>
+      <c r="BL68">
+        <v>2</v>
+      </c>
+      <c r="BN68">
+        <v>2</v>
+      </c>
+      <c r="BO68">
+        <v>1</v>
+      </c>
+      <c r="BP68">
+        <v>1</v>
+      </c>
+      <c r="BR68">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
+        <v>379</v>
+      </c>
+      <c r="BF69">
+        <v>1</v>
+      </c>
+      <c r="BG69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>8</v>
       </c>
-      <c r="B69">
-        <v>1</v>
-      </c>
-      <c r="H69">
-        <v>1</v>
-      </c>
-      <c r="J69">
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="J70">
         <v>2</v>
       </c>
-      <c r="Q69">
+      <c r="Q70">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+    <row r="71" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>354</v>
-      </c>
-    </row>
-    <row r="71" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>82</v>
-      </c>
-      <c r="B71">
-        <v>2</v>
-      </c>
-      <c r="C71">
-        <v>2</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71">
-        <v>2</v>
-      </c>
-      <c r="F71">
-        <v>1</v>
-      </c>
-      <c r="G71">
-        <v>2</v>
-      </c>
-      <c r="H71">
-        <v>2</v>
-      </c>
-      <c r="I71">
-        <v>3</v>
-      </c>
-      <c r="J71">
-        <v>4</v>
-      </c>
-      <c r="L71">
-        <v>4</v>
-      </c>
-      <c r="M71">
-        <v>1</v>
-      </c>
-      <c r="N71">
-        <v>2</v>
-      </c>
-      <c r="O71">
-        <v>1</v>
-      </c>
-      <c r="P71">
-        <v>1</v>
-      </c>
-      <c r="Q71">
-        <v>1</v>
-      </c>
-      <c r="R71">
-        <v>3</v>
-      </c>
-      <c r="S71">
-        <v>3</v>
-      </c>
-      <c r="U71">
-        <v>3</v>
-      </c>
-      <c r="V71">
-        <v>1</v>
-      </c>
-      <c r="W71">
-        <v>3</v>
-      </c>
-      <c r="AC71">
-        <v>1</v>
-      </c>
-      <c r="AF71">
-        <v>1</v>
-      </c>
-      <c r="AH71">
-        <v>2</v>
-      </c>
-      <c r="AI71">
-        <v>3</v>
-      </c>
-      <c r="AJ71">
-        <v>1</v>
-      </c>
-      <c r="AK71">
-        <v>4</v>
-      </c>
-      <c r="AL71">
-        <v>3</v>
-      </c>
-      <c r="AN71">
-        <v>1</v>
-      </c>
-      <c r="AP71">
-        <v>2</v>
-      </c>
-      <c r="AT71">
-        <v>2</v>
-      </c>
-      <c r="AU71">
-        <v>3</v>
-      </c>
-      <c r="AV71">
-        <v>1</v>
-      </c>
-      <c r="AW71">
-        <v>1</v>
-      </c>
-      <c r="AX71">
-        <v>1</v>
-      </c>
-      <c r="AY71">
-        <v>1</v>
-      </c>
-      <c r="AZ71">
-        <v>2</v>
-      </c>
-      <c r="BC71">
-        <v>2</v>
-      </c>
-      <c r="BD71">
-        <v>1</v>
-      </c>
-      <c r="BF71">
-        <v>2</v>
-      </c>
-      <c r="BH71">
-        <v>3</v>
-      </c>
-      <c r="BI71">
-        <v>1</v>
-      </c>
-      <c r="BJ71">
-        <v>2</v>
-      </c>
-      <c r="BK71">
-        <v>3</v>
-      </c>
-      <c r="BM71">
-        <v>2</v>
-      </c>
-      <c r="BN71">
-        <v>3</v>
-      </c>
-      <c r="BU71">
-        <v>1</v>
-      </c>
-      <c r="BV71">
-        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>49</v>
+        <v>82</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
       </c>
       <c r="G72">
         <v>2</v>
       </c>
+      <c r="H72">
+        <v>2</v>
+      </c>
+      <c r="I72">
+        <v>3</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+      <c r="L72">
+        <v>4</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>2</v>
+      </c>
+      <c r="O72">
+        <v>1</v>
+      </c>
+      <c r="P72">
+        <v>1</v>
+      </c>
+      <c r="Q72">
+        <v>1</v>
+      </c>
+      <c r="R72">
+        <v>3</v>
+      </c>
+      <c r="S72">
+        <v>3</v>
+      </c>
+      <c r="U72">
+        <v>3</v>
+      </c>
+      <c r="V72">
+        <v>1</v>
+      </c>
+      <c r="W72">
+        <v>3</v>
+      </c>
+      <c r="AC72">
+        <v>1</v>
+      </c>
+      <c r="AF72">
+        <v>1</v>
+      </c>
+      <c r="AH72">
+        <v>2</v>
+      </c>
+      <c r="AI72">
+        <v>3</v>
+      </c>
+      <c r="AJ72">
+        <v>1</v>
+      </c>
+      <c r="AK72">
+        <v>4</v>
+      </c>
+      <c r="AL72">
+        <v>3</v>
+      </c>
+      <c r="AN72">
+        <v>1</v>
+      </c>
+      <c r="AP72">
+        <v>2</v>
+      </c>
+      <c r="AT72">
+        <v>2</v>
+      </c>
+      <c r="AU72">
+        <v>3</v>
+      </c>
+      <c r="AV72">
+        <v>1</v>
+      </c>
+      <c r="AW72">
+        <v>1</v>
+      </c>
+      <c r="AX72">
+        <v>1</v>
+      </c>
+      <c r="AY72">
+        <v>1</v>
+      </c>
+      <c r="AZ72">
+        <v>2</v>
+      </c>
+      <c r="BC72">
+        <v>2</v>
+      </c>
+      <c r="BD72">
+        <v>1</v>
+      </c>
+      <c r="BF72">
+        <v>2</v>
+      </c>
+      <c r="BH72">
+        <v>3</v>
+      </c>
+      <c r="BI72">
+        <v>1</v>
+      </c>
+      <c r="BJ72">
+        <v>2</v>
+      </c>
+      <c r="BK72">
+        <v>3</v>
+      </c>
+      <c r="BM72">
+        <v>2</v>
+      </c>
+      <c r="BN72">
+        <v>3</v>
+      </c>
+      <c r="BU72">
+        <v>1</v>
+      </c>
+      <c r="BV72">
+        <v>3</v>
+      </c>
     </row>
     <row r="73" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>385</v>
+        <v>49</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>85</v>
-      </c>
-      <c r="K74">
-        <v>4</v>
-      </c>
-      <c r="L74">
-        <v>2</v>
-      </c>
-      <c r="M74">
-        <v>5</v>
+        <v>385</v>
       </c>
     </row>
     <row r="75" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>5</v>
-      </c>
-      <c r="B75">
-        <v>1</v>
-      </c>
-      <c r="C75">
+        <v>85</v>
+      </c>
+      <c r="K75">
+        <v>4</v>
+      </c>
+      <c r="L75">
         <v>2</v>
       </c>
-      <c r="D75">
-        <v>2</v>
-      </c>
-      <c r="E75">
-        <v>3</v>
-      </c>
-      <c r="F75">
-        <v>2</v>
-      </c>
-      <c r="G75">
-        <v>3</v>
-      </c>
-      <c r="H75">
-        <v>1</v>
-      </c>
       <c r="M75">
-        <v>4</v>
-      </c>
-      <c r="N75">
-        <v>6</v>
-      </c>
-      <c r="P75">
-        <v>2</v>
-      </c>
-      <c r="Q75">
-        <v>1</v>
-      </c>
-      <c r="R75">
-        <v>2</v>
-      </c>
-      <c r="S75">
-        <v>3</v>
-      </c>
-      <c r="V75">
-        <v>2</v>
-      </c>
-      <c r="W75">
-        <v>1</v>
-      </c>
-      <c r="X75">
-        <v>1</v>
-      </c>
-      <c r="Y75">
-        <v>4</v>
-      </c>
-      <c r="Z75">
-        <v>5</v>
-      </c>
-      <c r="AA75">
-        <v>1</v>
-      </c>
-      <c r="AB75">
-        <v>3</v>
-      </c>
-      <c r="AC75">
-        <v>4</v>
-      </c>
-      <c r="AD75">
-        <v>3</v>
-      </c>
-      <c r="AE75">
-        <v>3</v>
-      </c>
-      <c r="AF75">
-        <v>2</v>
-      </c>
-      <c r="AG75">
-        <v>5</v>
-      </c>
-      <c r="AH75">
-        <v>7</v>
-      </c>
-      <c r="AI75">
-        <v>3</v>
-      </c>
-      <c r="AJ75">
-        <v>1</v>
-      </c>
-      <c r="AK75">
-        <v>1</v>
-      </c>
-      <c r="AL75">
-        <v>6</v>
-      </c>
-      <c r="AR75">
-        <v>3</v>
-      </c>
-      <c r="AS75">
-        <v>2</v>
-      </c>
-      <c r="AV75">
-        <v>2</v>
-      </c>
-      <c r="AW75">
-        <v>1</v>
-      </c>
-      <c r="AX75">
-        <v>4</v>
-      </c>
-      <c r="AY75">
-        <v>3</v>
-      </c>
-      <c r="AZ75">
-        <v>4</v>
-      </c>
-      <c r="BA75">
-        <v>5</v>
-      </c>
-      <c r="BB75">
-        <v>6</v>
-      </c>
-      <c r="BC75">
-        <v>2</v>
-      </c>
-      <c r="BD75">
-        <v>2</v>
-      </c>
-      <c r="BE75">
-        <v>7</v>
-      </c>
-      <c r="BG75">
-        <v>4</v>
-      </c>
-      <c r="BH75">
-        <v>3</v>
-      </c>
-      <c r="BI75">
-        <v>4</v>
-      </c>
-      <c r="BK75">
-        <v>1</v>
-      </c>
-      <c r="BL75">
-        <v>8</v>
-      </c>
-      <c r="BM75">
-        <v>4</v>
-      </c>
-      <c r="BN75">
-        <v>5</v>
-      </c>
-      <c r="BO75">
-        <v>3</v>
-      </c>
-      <c r="BP75">
-        <v>1</v>
-      </c>
-      <c r="BQ75">
-        <v>1</v>
-      </c>
-      <c r="BR75">
-        <v>3</v>
-      </c>
-      <c r="BS75">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>45</v>
-      </c>
-      <c r="K76">
-        <v>1</v>
-      </c>
-      <c r="BJ76">
+        <v>5</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+      <c r="D76">
+        <v>2</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76">
+        <v>3</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <v>4</v>
+      </c>
+      <c r="N76">
+        <v>6</v>
+      </c>
+      <c r="P76">
+        <v>2</v>
+      </c>
+      <c r="Q76">
+        <v>1</v>
+      </c>
+      <c r="R76">
+        <v>2</v>
+      </c>
+      <c r="S76">
+        <v>3</v>
+      </c>
+      <c r="V76">
+        <v>2</v>
+      </c>
+      <c r="W76">
+        <v>1</v>
+      </c>
+      <c r="X76">
+        <v>1</v>
+      </c>
+      <c r="Y76">
+        <v>4</v>
+      </c>
+      <c r="Z76">
+        <v>5</v>
+      </c>
+      <c r="AA76">
+        <v>1</v>
+      </c>
+      <c r="AB76">
+        <v>3</v>
+      </c>
+      <c r="AC76">
+        <v>4</v>
+      </c>
+      <c r="AD76">
+        <v>3</v>
+      </c>
+      <c r="AE76">
+        <v>3</v>
+      </c>
+      <c r="AF76">
+        <v>2</v>
+      </c>
+      <c r="AG76">
+        <v>5</v>
+      </c>
+      <c r="AH76">
+        <v>7</v>
+      </c>
+      <c r="AI76">
+        <v>3</v>
+      </c>
+      <c r="AJ76">
+        <v>1</v>
+      </c>
+      <c r="AK76">
+        <v>1</v>
+      </c>
+      <c r="AL76">
+        <v>6</v>
+      </c>
+      <c r="AR76">
+        <v>3</v>
+      </c>
+      <c r="AS76">
+        <v>2</v>
+      </c>
+      <c r="AV76">
+        <v>2</v>
+      </c>
+      <c r="AW76">
+        <v>1</v>
+      </c>
+      <c r="AX76">
+        <v>4</v>
+      </c>
+      <c r="AY76">
+        <v>3</v>
+      </c>
+      <c r="AZ76">
+        <v>4</v>
+      </c>
+      <c r="BA76">
+        <v>5</v>
+      </c>
+      <c r="BB76">
+        <v>6</v>
+      </c>
+      <c r="BC76">
+        <v>2</v>
+      </c>
+      <c r="BD76">
+        <v>2</v>
+      </c>
+      <c r="BE76">
+        <v>7</v>
+      </c>
+      <c r="BG76">
+        <v>4</v>
+      </c>
+      <c r="BH76">
+        <v>3</v>
+      </c>
+      <c r="BI76">
+        <v>4</v>
+      </c>
+      <c r="BK76">
+        <v>1</v>
+      </c>
+      <c r="BL76">
+        <v>8</v>
+      </c>
+      <c r="BM76">
+        <v>4</v>
+      </c>
+      <c r="BN76">
+        <v>5</v>
+      </c>
+      <c r="BO76">
+        <v>3</v>
+      </c>
+      <c r="BP76">
+        <v>1</v>
+      </c>
+      <c r="BQ76">
+        <v>1</v>
+      </c>
+      <c r="BR76">
+        <v>3</v>
+      </c>
+      <c r="BS76">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:74" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
+        <v>45</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="BJ77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>367</v>
       </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77">
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
         <v>3</v>
       </c>
-      <c r="O77">
+      <c r="O78">
         <v>2</v>
       </c>
-      <c r="P77">
+      <c r="P78">
         <v>2</v>
       </c>
-      <c r="Q77">
-        <v>1</v>
-      </c>
-      <c r="R77">
-        <v>1</v>
-      </c>
-      <c r="AD77">
-        <v>1</v>
-      </c>
-      <c r="AE77">
-        <v>1</v>
-      </c>
-      <c r="AG77">
-        <v>1</v>
-      </c>
-      <c r="AH77">
+      <c r="Q78">
+        <v>1</v>
+      </c>
+      <c r="R78">
+        <v>1</v>
+      </c>
+      <c r="AD78">
+        <v>1</v>
+      </c>
+      <c r="AE78">
+        <v>1</v>
+      </c>
+      <c r="AG78">
+        <v>1</v>
+      </c>
+      <c r="AH78">
         <v>2</v>
       </c>
-      <c r="AL77">
+      <c r="AL78">
         <v>3</v>
       </c>
-      <c r="AM77">
+      <c r="AM78">
         <v>2</v>
       </c>
-      <c r="AN77">
-        <v>1</v>
-      </c>
-      <c r="AO77">
-        <v>1</v>
-      </c>
-      <c r="AR77">
-        <v>1</v>
-      </c>
-      <c r="AS77">
-        <v>1</v>
-      </c>
-      <c r="AT77">
-        <v>1</v>
-      </c>
-      <c r="AV77">
-        <v>1</v>
-      </c>
-      <c r="AW77">
+      <c r="AN78">
+        <v>1</v>
+      </c>
+      <c r="AO78">
+        <v>1</v>
+      </c>
+      <c r="AR78">
+        <v>1</v>
+      </c>
+      <c r="AS78">
+        <v>1</v>
+      </c>
+      <c r="AT78">
+        <v>1</v>
+      </c>
+      <c r="AV78">
+        <v>1</v>
+      </c>
+      <c r="AW78">
         <v>2</v>
       </c>
-      <c r="BD77">
-        <v>1</v>
-      </c>
-      <c r="BF77">
-        <v>1</v>
-      </c>
-      <c r="BI77">
-        <v>1</v>
-      </c>
-      <c r="BU77">
+      <c r="BD78">
+        <v>1</v>
+      </c>
+      <c r="BF78">
+        <v>1</v>
+      </c>
+      <c r="BI78">
+        <v>1</v>
+      </c>
+      <c r="BU78">
         <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>352</v>
-      </c>
-      <c r="Z78">
-        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
+        <v>352</v>
+      </c>
+      <c r="Z79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="80" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+    <row r="81" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>17</v>
       </c>
-      <c r="F80">
+      <c r="F81">
         <v>2</v>
       </c>
-      <c r="J80">
-        <v>1</v>
-      </c>
-      <c r="K80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>86</v>
       </c>
-      <c r="K81">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="K82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>16</v>
       </c>
-      <c r="C82">
+      <c r="C83">
         <v>4</v>
       </c>
-      <c r="D82">
+      <c r="D83">
         <v>3</v>
       </c>
-      <c r="F82">
+      <c r="F83">
         <v>2</v>
       </c>
-      <c r="G82">
-        <v>5</v>
-      </c>
-      <c r="H82">
+      <c r="G83">
+        <v>5</v>
+      </c>
+      <c r="H83">
         <v>3</v>
       </c>
-      <c r="I82">
+      <c r="I83">
         <v>2</v>
       </c>
-      <c r="J82">
-        <v>5</v>
-      </c>
-      <c r="K82">
+      <c r="J83">
+        <v>5</v>
+      </c>
+      <c r="K83">
         <v>3</v>
       </c>
-      <c r="L82">
+      <c r="L83">
         <v>2</v>
       </c>
-      <c r="M82">
+      <c r="M83">
         <v>3</v>
       </c>
-      <c r="O82">
-        <v>5</v>
-      </c>
-      <c r="P82">
-        <v>5</v>
-      </c>
-      <c r="Q82">
+      <c r="O83">
+        <v>5</v>
+      </c>
+      <c r="P83">
+        <v>5</v>
+      </c>
+      <c r="Q83">
         <v>3</v>
       </c>
-      <c r="R82">
+      <c r="R83">
         <v>2</v>
       </c>
-      <c r="S82">
+      <c r="S83">
         <v>3</v>
       </c>
-      <c r="T82">
-        <v>1</v>
-      </c>
-      <c r="U82">
-        <v>1</v>
-      </c>
-      <c r="V82">
+      <c r="T83">
+        <v>1</v>
+      </c>
+      <c r="U83">
+        <v>1</v>
+      </c>
+      <c r="V83">
         <v>3</v>
       </c>
-      <c r="W82">
+      <c r="W83">
         <v>3</v>
       </c>
-      <c r="X82">
-        <v>5</v>
-      </c>
-      <c r="Y82">
+      <c r="X83">
+        <v>5</v>
+      </c>
+      <c r="Y83">
         <v>4</v>
       </c>
-      <c r="Z82">
-        <v>1</v>
-      </c>
-      <c r="AA82">
+      <c r="Z83">
+        <v>1</v>
+      </c>
+      <c r="AA83">
         <v>3</v>
       </c>
-      <c r="AC82">
-        <v>1</v>
-      </c>
-      <c r="AE82">
+      <c r="AC83">
+        <v>1</v>
+      </c>
+      <c r="AE83">
         <v>4</v>
       </c>
-      <c r="AF82">
+      <c r="AF83">
         <v>2</v>
       </c>
-      <c r="AG82">
+      <c r="AG83">
         <v>3</v>
       </c>
-      <c r="AH82">
+      <c r="AH83">
         <v>2</v>
       </c>
-      <c r="AI82">
+      <c r="AI83">
         <v>2</v>
       </c>
-      <c r="AJ82">
+      <c r="AJ83">
         <v>7</v>
       </c>
-      <c r="AK82">
+      <c r="AK83">
         <v>3</v>
       </c>
-      <c r="AL82">
-        <v>5</v>
-      </c>
-      <c r="AM82">
-        <v>1</v>
-      </c>
-      <c r="AN82">
+      <c r="AL83">
+        <v>5</v>
+      </c>
+      <c r="AM83">
+        <v>1</v>
+      </c>
+      <c r="AN83">
         <v>4</v>
       </c>
-      <c r="AO82">
+      <c r="AO83">
         <v>3</v>
       </c>
-      <c r="AP82">
+      <c r="AP83">
         <v>6</v>
       </c>
-      <c r="AQ82">
+      <c r="AQ83">
         <v>4</v>
       </c>
-      <c r="AR82">
-        <v>5</v>
-      </c>
-      <c r="AS82">
+      <c r="AR83">
+        <v>5</v>
+      </c>
+      <c r="AS83">
         <v>3</v>
       </c>
-      <c r="AT82">
+      <c r="AT83">
         <v>2</v>
       </c>
-      <c r="AU82">
+      <c r="AU83">
         <v>2</v>
       </c>
-      <c r="AW82">
+      <c r="AW83">
         <v>3</v>
       </c>
-      <c r="AY82">
-        <v>1</v>
-      </c>
-      <c r="AZ82">
+      <c r="AY83">
+        <v>1</v>
+      </c>
+      <c r="AZ83">
         <v>3</v>
       </c>
-      <c r="BB82">
+      <c r="BB83">
         <v>4</v>
       </c>
-      <c r="BC82">
+      <c r="BC83">
         <v>4</v>
       </c>
-      <c r="BD82">
+      <c r="BD83">
         <v>3</v>
       </c>
-      <c r="BF82">
+      <c r="BF83">
         <v>2</v>
       </c>
-      <c r="BG82">
+      <c r="BG83">
         <v>4</v>
       </c>
-      <c r="BH82">
-        <v>5</v>
-      </c>
-      <c r="BJ82">
+      <c r="BH83">
+        <v>5</v>
+      </c>
+      <c r="BJ83">
         <v>4</v>
       </c>
-      <c r="BK82">
+      <c r="BK83">
         <v>2</v>
       </c>
-      <c r="BL82">
+      <c r="BL83">
         <v>4</v>
       </c>
-      <c r="BM82">
-        <v>1</v>
-      </c>
-      <c r="BN82">
+      <c r="BM83">
+        <v>1</v>
+      </c>
+      <c r="BN83">
         <v>2</v>
       </c>
-      <c r="BO82">
+      <c r="BO83">
         <v>3</v>
       </c>
-      <c r="BS82">
+      <c r="BS83">
         <v>3</v>
       </c>
-      <c r="BT82">
+      <c r="BT83">
         <v>4</v>
       </c>
-      <c r="BU82">
+      <c r="BU83">
         <v>4</v>
       </c>
-      <c r="BV82">
+      <c r="BV83">
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+    <row r="84" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB83" xr:uid="{130C2564-D265-4C41-A3E0-02A62EDAC91D}">
-    <sortState ref="A2:AB83">
-      <sortCondition ref="A1:A83"/>
+  <autoFilter ref="A1:AB84" xr:uid="{130C2564-D265-4C41-A3E0-02A62EDAC91D}">
+    <sortState ref="A2:AB84">
+      <sortCondition ref="A1:A84"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{FD2634B1-9EDE-486E-AE13-243F5EFAB489}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3C1165B0-6E15-482B-A397-DF951961618B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,17 +23,17 @@
     <sheet name="artilharia total" sheetId="3" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'extrato 2024'!$A$1:$C$187</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CV$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CW$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9254" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9290" uniqueCount="397">
   <si>
     <t>Jogador</t>
   </si>
@@ -1215,6 +1215,15 @@
   </si>
   <si>
     <t>Bernardo Impactus</t>
+  </si>
+  <si>
+    <t>Joshua</t>
+  </si>
+  <si>
+    <t>Caio (Octavio)</t>
+  </si>
+  <si>
+    <t>Leo MJ</t>
   </si>
 </sst>
 </file>
@@ -3483,7 +3492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CV84"/>
+  <dimension ref="A1:CW87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
@@ -3508,10 +3517,10 @@
     <col min="50" max="58" width="9.54296875" customWidth="1"/>
     <col min="59" max="65" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
-    <col min="67" max="94" width="11" customWidth="1"/>
+    <col min="67" max="95" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3791,27 +3800,30 @@
       <c r="CO1" s="1">
         <v>46113</v>
       </c>
-      <c r="CP1" s="1"/>
-      <c r="CQ1" t="s">
+      <c r="CP1" s="1">
+        <v>46120</v>
+      </c>
+      <c r="CQ1" s="1"/>
+      <c r="CR1" t="s">
         <v>57</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>58</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>59</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>62</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>392</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4088,31 +4100,34 @@
       <c r="CO2">
         <v>6</v>
       </c>
-      <c r="CQ2">
-        <f>COUNT(B2:CO2)</f>
-        <v>86</v>
-      </c>
-      <c r="CR2" s="18">
-        <f>AVERAGE(B2:CO2)</f>
-        <v>6.0290697674418601</v>
-      </c>
-      <c r="CS2">
-        <f t="shared" ref="CS2:CS33" si="0">IF(CQ2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
+      <c r="CP2">
+        <v>7</v>
+      </c>
+      <c r="CR2">
+        <f>COUNT(B2:CP2)</f>
+        <v>87</v>
+      </c>
+      <c r="CS2" s="18">
+        <f>AVERAGE(B2:CP2)</f>
+        <v>6.0402298850574709</v>
+      </c>
+      <c r="CT2">
+        <f t="shared" ref="CT2:CT33" si="0">IF(CR2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
         <v>1.2512468149547391</v>
       </c>
-      <c r="CT2">
-        <v>1</v>
-      </c>
       <c r="CU2">
-        <f t="shared" ref="CU2:CU33" si="1">COUNT(CK2:CN2)</f>
+        <v>1</v>
+      </c>
+      <c r="CV2">
+        <f t="shared" ref="CV2:CV33" si="1">COUNT(CK2:CN2)</f>
         <v>4</v>
       </c>
-      <c r="CV2">
-        <f t="shared" ref="CV2:CV33" si="2">IF(CT2=0,CU2,0)</f>
+      <c r="CW2">
+        <f t="shared" ref="CW2:CW33" si="2">IF(CU2=0,CV2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4389,31 +4404,34 @@
       <c r="CO3">
         <v>6</v>
       </c>
-      <c r="CQ3">
+      <c r="CP3">
+        <v>6</v>
+      </c>
+      <c r="CR3">
         <f>COUNT(B3:CK3)</f>
         <v>79</v>
       </c>
-      <c r="CR3" s="18">
+      <c r="CS3" s="18">
         <f>AVERAGE(B3:CK3)</f>
         <v>5.6518987341772151</v>
       </c>
-      <c r="CS3">
+      <c r="CT3">
         <f t="shared" si="0"/>
         <v>1.0518094984498128</v>
       </c>
-      <c r="CT3">
-        <v>1</v>
-      </c>
       <c r="CU3">
+        <v>1</v>
+      </c>
+      <c r="CV3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CV3">
+      <c r="CW3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4675,31 +4693,31 @@
       <c r="CI4">
         <v>5.5</v>
       </c>
-      <c r="CQ4">
+      <c r="CR4">
         <f>COUNT(B4:CI4)</f>
         <v>72</v>
       </c>
-      <c r="CR4" s="18">
+      <c r="CS4" s="18">
         <f>AVERAGE(B4:CI4)</f>
         <v>5.708333333333333</v>
       </c>
-      <c r="CS4">
+      <c r="CT4">
         <f t="shared" si="0"/>
         <v>0.96435844595057774</v>
       </c>
-      <c r="CT4">
+      <c r="CU4">
         <v>0</v>
       </c>
-      <c r="CU4">
+      <c r="CV4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CV4">
+      <c r="CW4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -4967,31 +4985,31 @@
       <c r="CL5">
         <v>5.5</v>
       </c>
-      <c r="CQ5">
+      <c r="CR5">
         <f>COUNT(B5:CL5)</f>
         <v>71</v>
       </c>
-      <c r="CR5" s="18">
+      <c r="CS5" s="18">
         <f>AVERAGE(B5:CL5)</f>
         <v>7.267605633802817</v>
       </c>
-      <c r="CS5">
+      <c r="CT5">
         <f t="shared" si="0"/>
         <v>1.1294250579557983</v>
       </c>
-      <c r="CT5">
-        <v>1</v>
-      </c>
       <c r="CU5">
+        <v>1</v>
+      </c>
+      <c r="CV5">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CV5">
+      <c r="CW5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -5262,31 +5280,31 @@
       <c r="CO6">
         <v>6.5</v>
       </c>
-      <c r="CQ6">
+      <c r="CR6">
         <f>COUNT(B6:CL6)</f>
         <v>70</v>
       </c>
-      <c r="CR6" s="18">
+      <c r="CS6" s="18">
         <f>AVERAGE(B6:CL6)</f>
         <v>6.6142857142857139</v>
       </c>
-      <c r="CS6">
+      <c r="CT6">
         <f t="shared" si="0"/>
         <v>0.9419445925236869</v>
       </c>
-      <c r="CT6">
-        <v>1</v>
-      </c>
       <c r="CU6">
+        <v>1</v>
+      </c>
+      <c r="CV6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CV6">
+      <c r="CW6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5557,31 +5575,34 @@
       <c r="CO7">
         <v>7.5</v>
       </c>
-      <c r="CQ7">
+      <c r="CP7">
+        <v>6.5</v>
+      </c>
+      <c r="CR7">
         <f>COUNT(B7:CL7)</f>
         <v>70</v>
       </c>
-      <c r="CR7" s="18">
+      <c r="CS7" s="18">
         <f>AVERAGE(B7:CL7)</f>
         <v>6.6071428571428568</v>
       </c>
-      <c r="CS7">
+      <c r="CT7">
         <f t="shared" si="0"/>
         <v>1.0570846156365068</v>
       </c>
-      <c r="CT7">
-        <v>1</v>
-      </c>
       <c r="CU7">
+        <v>1</v>
+      </c>
+      <c r="CV7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CV7">
+      <c r="CW7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5831,31 +5852,31 @@
       <c r="CE8">
         <v>5</v>
       </c>
-      <c r="CQ8">
+      <c r="CR8">
         <f>COUNT(B8:CI8)</f>
         <v>68</v>
       </c>
-      <c r="CR8" s="18">
+      <c r="CS8" s="18">
         <f>AVERAGE(B8:CI8)</f>
         <v>6.4191176470588234</v>
       </c>
-      <c r="CS8">
+      <c r="CT8">
         <f t="shared" si="0"/>
         <v>1.1769245721961776</v>
       </c>
-      <c r="CT8">
+      <c r="CU8">
         <v>0</v>
       </c>
-      <c r="CU8">
+      <c r="CV8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CV8">
+      <c r="CW8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -6108,31 +6129,31 @@
       <c r="CI9">
         <v>5.5</v>
       </c>
-      <c r="CQ9">
+      <c r="CR9">
         <f>COUNT(B9:CI9)</f>
         <v>67</v>
       </c>
-      <c r="CR9" s="18">
+      <c r="CS9" s="18">
         <f>AVERAGE(B9:CI9)</f>
         <v>5.9701492537313436</v>
       </c>
-      <c r="CS9">
+      <c r="CT9">
         <f t="shared" si="0"/>
         <v>0.96648378625350351</v>
       </c>
-      <c r="CT9">
+      <c r="CU9">
         <v>0</v>
       </c>
-      <c r="CU9">
+      <c r="CV9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CV9">
+      <c r="CW9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -6400,31 +6421,34 @@
       <c r="CO10">
         <v>6</v>
       </c>
-      <c r="CQ10">
+      <c r="CP10">
+        <v>5.5</v>
+      </c>
+      <c r="CR10">
         <f>COUNT(B10:CI10)</f>
         <v>62</v>
       </c>
-      <c r="CR10" s="18">
+      <c r="CS10" s="18">
         <f>AVERAGE(B10:CI10)</f>
         <v>5.717741935483871</v>
       </c>
-      <c r="CS10">
+      <c r="CT10">
         <f t="shared" si="0"/>
         <v>1.3617531291315086</v>
       </c>
-      <c r="CT10">
-        <v>1</v>
-      </c>
       <c r="CU10">
+        <v>1</v>
+      </c>
+      <c r="CV10">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CV10">
+      <c r="CW10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6695,31 +6719,31 @@
       <c r="CO11">
         <v>6.5</v>
       </c>
-      <c r="CQ11">
+      <c r="CR11">
         <f>COUNT(B11:CI11)</f>
         <v>59</v>
       </c>
-      <c r="CR11" s="18">
+      <c r="CS11" s="18">
         <f>AVERAGE(B11:CI11)</f>
         <v>6.6779661016949152</v>
       </c>
-      <c r="CS11">
+      <c r="CT11">
         <f t="shared" si="0"/>
         <v>1.0072574989410263</v>
       </c>
-      <c r="CT11">
-        <v>1</v>
-      </c>
       <c r="CU11">
+        <v>1</v>
+      </c>
+      <c r="CV11">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CV11">
+      <c r="CW11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -6993,31 +7017,34 @@
       <c r="CO12">
         <v>6</v>
       </c>
-      <c r="CQ12">
-        <f>COUNT(B12:CO12)</f>
-        <v>59</v>
-      </c>
-      <c r="CR12" s="18">
-        <f>AVERAGE(B12:CO12)</f>
-        <v>5.5169491525423728</v>
-      </c>
-      <c r="CS12">
+      <c r="CP12">
+        <v>6</v>
+      </c>
+      <c r="CR12">
+        <f>COUNT(B12:CP12)</f>
+        <v>60</v>
+      </c>
+      <c r="CS12" s="18">
+        <f>AVERAGE(B12:CP12)</f>
+        <v>5.5250000000000004</v>
+      </c>
+      <c r="CT12">
         <f t="shared" si="0"/>
         <v>1.0254583642020354</v>
       </c>
-      <c r="CT12">
-        <v>1</v>
-      </c>
       <c r="CU12">
+        <v>1</v>
+      </c>
+      <c r="CV12">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CV12">
+      <c r="CW12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -7291,31 +7318,31 @@
       <c r="CN13">
         <v>5.5</v>
       </c>
-      <c r="CQ13">
+      <c r="CR13">
         <f>COUNT(B13:CN13)</f>
         <v>56</v>
       </c>
-      <c r="CR13" s="18">
+      <c r="CS13" s="18">
         <f>AVERAGE(B13:CN13)</f>
         <v>6.3571428571428568</v>
       </c>
-      <c r="CS13">
+      <c r="CT13">
         <f t="shared" si="0"/>
         <v>1.1769469323774333</v>
       </c>
-      <c r="CT13">
-        <v>1</v>
-      </c>
       <c r="CU13">
+        <v>1</v>
+      </c>
+      <c r="CV13">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CV13">
+      <c r="CW13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>367</v>
       </c>
@@ -7565,31 +7592,34 @@
       <c r="CN14">
         <v>6</v>
       </c>
-      <c r="CQ14">
+      <c r="CP14">
+        <v>5.5</v>
+      </c>
+      <c r="CR14">
         <f>COUNT(B14:CI14)</f>
         <v>55</v>
       </c>
-      <c r="CR14" s="18">
+      <c r="CS14" s="18">
         <f>AVERAGE(B14:CI14)</f>
         <v>6.3181818181818183</v>
       </c>
-      <c r="CS14">
+      <c r="CT14">
         <f t="shared" si="0"/>
         <v>1.1213885273224193</v>
       </c>
-      <c r="CT14">
+      <c r="CU14">
         <v>0</v>
       </c>
-      <c r="CU14">
+      <c r="CV14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CV14">
+      <c r="CW14">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -7833,31 +7863,31 @@
       <c r="CF15">
         <v>5.5</v>
       </c>
-      <c r="CQ15">
+      <c r="CR15">
         <f>COUNT(B15:CI15)</f>
         <v>52</v>
       </c>
-      <c r="CR15" s="18">
+      <c r="CS15" s="18">
         <f>AVERAGE(B15:CI15)</f>
         <v>5.6923076923076925</v>
       </c>
-      <c r="CS15">
+      <c r="CT15">
         <f t="shared" si="0"/>
         <v>0.84687340856573534</v>
       </c>
-      <c r="CT15">
+      <c r="CU15">
         <v>0</v>
       </c>
-      <c r="CU15">
+      <c r="CV15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CV15">
+      <c r="CW15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -8107,31 +8137,31 @@
       <c r="CF16">
         <v>5.5</v>
       </c>
-      <c r="CQ16">
+      <c r="CR16">
         <f>COUNT(B16:CI16)</f>
         <v>47</v>
       </c>
-      <c r="CR16" s="18">
+      <c r="CS16" s="18">
         <f>AVERAGE(B16:CI16)</f>
         <v>4.4255319148936172</v>
       </c>
-      <c r="CS16">
+      <c r="CT16">
         <f t="shared" si="0"/>
         <v>1.3391217246854428</v>
       </c>
-      <c r="CT16">
+      <c r="CU16">
         <v>0</v>
       </c>
-      <c r="CU16">
+      <c r="CV16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CV16">
+      <c r="CW16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>56</v>
       </c>
@@ -8408,31 +8438,34 @@
       <c r="CO17">
         <v>6</v>
       </c>
-      <c r="CQ17">
+      <c r="CP17">
+        <v>5.5</v>
+      </c>
+      <c r="CR17">
         <f>COUNT(B17:CL17)</f>
         <v>46</v>
       </c>
-      <c r="CR17" s="18">
+      <c r="CS17" s="18">
         <f>AVERAGE(B17:CL17)</f>
         <v>6.0652173913043477</v>
       </c>
-      <c r="CS17">
+      <c r="CT17">
         <f t="shared" si="0"/>
         <v>0.9573434129174403</v>
       </c>
-      <c r="CT17">
-        <v>1</v>
-      </c>
       <c r="CU17">
+        <v>1</v>
+      </c>
+      <c r="CV17">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CV17">
+      <c r="CW17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -8700,31 +8733,31 @@
       <c r="CL18">
         <v>6</v>
       </c>
-      <c r="CQ18">
+      <c r="CR18">
         <f>COUNT(B18:CL18)</f>
         <v>44</v>
       </c>
-      <c r="CR18" s="18">
+      <c r="CS18" s="18">
         <f>AVERAGE(B18:CL18)</f>
         <v>5.0113636363636367</v>
       </c>
-      <c r="CS18">
+      <c r="CT18">
         <f t="shared" si="0"/>
         <v>1.0645089158214895</v>
       </c>
-      <c r="CT18">
-        <v>1</v>
-      </c>
       <c r="CU18">
+        <v>1</v>
+      </c>
+      <c r="CV18">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CV18">
+      <c r="CW18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -8968,31 +9001,31 @@
       <c r="CK19">
         <v>5.5</v>
       </c>
-      <c r="CQ19">
+      <c r="CR19">
         <f>COUNT(B19:CI19)</f>
         <v>38</v>
       </c>
-      <c r="CR19" s="18">
+      <c r="CS19" s="18">
         <f>AVERAGE(B19:CI19)</f>
         <v>6.1578947368421053</v>
       </c>
-      <c r="CS19">
+      <c r="CT19">
         <f t="shared" si="0"/>
         <v>1.0973263770680928</v>
       </c>
-      <c r="CT19">
+      <c r="CU19">
         <v>0</v>
       </c>
-      <c r="CU19">
+      <c r="CV19">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CV19">
+      <c r="CW19">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -9257,31 +9290,31 @@
       <c r="CM20">
         <v>5.5</v>
       </c>
-      <c r="CQ20">
+      <c r="CR20">
         <f>COUNT(B20:CJ20)</f>
         <v>37</v>
       </c>
-      <c r="CR20" s="18">
+      <c r="CS20" s="18">
         <f>AVERAGE(B20:CJ20)</f>
         <v>5.2027027027027026</v>
       </c>
-      <c r="CS20">
+      <c r="CT20">
         <f t="shared" si="0"/>
         <v>1.3241383031954423</v>
       </c>
-      <c r="CT20">
+      <c r="CU20">
         <v>0</v>
       </c>
-      <c r="CU20">
+      <c r="CV20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CV20">
+      <c r="CW20">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -9540,31 +9573,31 @@
       <c r="CO21">
         <v>5.5</v>
       </c>
-      <c r="CQ21">
+      <c r="CR21">
         <f>COUNT(B21:CI21)</f>
         <v>36</v>
       </c>
-      <c r="CR21" s="18">
+      <c r="CS21" s="18">
         <f>AVERAGE(B21:CI21)</f>
         <v>5.7361111111111107</v>
       </c>
-      <c r="CS21">
+      <c r="CT21">
         <f t="shared" si="0"/>
         <v>0.92956296268047622</v>
       </c>
-      <c r="CT21">
-        <v>1</v>
-      </c>
       <c r="CU21">
+        <v>1</v>
+      </c>
+      <c r="CV21">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CV21">
+      <c r="CW21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -9829,31 +9862,34 @@
       <c r="CO22">
         <v>6</v>
       </c>
-      <c r="CQ22">
+      <c r="CP22">
+        <v>5.5</v>
+      </c>
+      <c r="CR22">
         <f>COUNT(B22:CI22)</f>
         <v>36</v>
       </c>
-      <c r="CR22" s="18">
+      <c r="CS22" s="18">
         <f>AVERAGE(B22:CI22)</f>
         <v>5.6111111111111107</v>
       </c>
-      <c r="CS22">
+      <c r="CT22">
         <f t="shared" si="0"/>
         <v>1.0098256776095882</v>
       </c>
-      <c r="CT22">
-        <v>1</v>
-      </c>
       <c r="CU22">
+        <v>1</v>
+      </c>
+      <c r="CV22">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CV22">
+      <c r="CW22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -10124,31 +10160,31 @@
       <c r="CN23">
         <v>6</v>
       </c>
-      <c r="CQ23">
+      <c r="CR23">
         <f>COUNT(B23:CN23)</f>
         <v>30</v>
       </c>
-      <c r="CR23" s="18">
+      <c r="CS23" s="18">
         <f>AVERAGE(B23:CN23)</f>
         <v>6.4</v>
       </c>
-      <c r="CS23">
+      <c r="CT23">
         <f t="shared" si="0"/>
         <v>0.90960483309014595</v>
       </c>
-      <c r="CT23">
-        <v>1</v>
-      </c>
       <c r="CU23">
+        <v>1</v>
+      </c>
+      <c r="CV23">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CV23">
+      <c r="CW23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -10398,31 +10434,31 @@
       <c r="CN24">
         <v>6</v>
       </c>
-      <c r="CQ24">
-        <f t="shared" ref="CQ24:CQ31" si="3">COUNT(B24:CI24)</f>
+      <c r="CR24">
+        <f t="shared" ref="CR24:CR31" si="3">COUNT(B24:CI24)</f>
         <v>25</v>
       </c>
-      <c r="CR24" s="18">
-        <f t="shared" ref="CR24:CR31" si="4">AVERAGE(B24:CI24)</f>
+      <c r="CS24" s="18">
+        <f t="shared" ref="CS24:CS31" si="4">AVERAGE(B24:CI24)</f>
         <v>5.4</v>
       </c>
-      <c r="CS24">
+      <c r="CT24">
         <f t="shared" si="0"/>
         <v>0.71728150235677346</v>
       </c>
-      <c r="CT24">
+      <c r="CU24">
         <v>0</v>
       </c>
-      <c r="CU24">
+      <c r="CV24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CV24">
+      <c r="CW24">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -10663,31 +10699,31 @@
       <c r="CB25" t="s">
         <v>26</v>
       </c>
-      <c r="CQ25">
+      <c r="CR25">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="CR25" s="18">
+      <c r="CS25" s="18">
         <f t="shared" si="4"/>
         <v>5.7894736842105265</v>
       </c>
-      <c r="CS25">
+      <c r="CT25">
         <f t="shared" si="0"/>
         <v>1.3674366679797902</v>
       </c>
-      <c r="CT25">
+      <c r="CU25">
         <v>0</v>
       </c>
-      <c r="CU25">
+      <c r="CV25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CV25">
+      <c r="CW25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>346</v>
       </c>
@@ -10928,31 +10964,31 @@
       <c r="CB26" t="s">
         <v>26</v>
       </c>
-      <c r="CQ26">
+      <c r="CR26">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="CR26" s="18">
+      <c r="CS26" s="18">
         <f t="shared" si="4"/>
         <v>5.9444444444444446</v>
       </c>
-      <c r="CS26">
+      <c r="CT26">
         <f t="shared" si="0"/>
         <v>0.72535769855270305</v>
       </c>
-      <c r="CT26">
+      <c r="CU26">
         <v>0</v>
       </c>
-      <c r="CU26">
+      <c r="CV26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CV26">
+      <c r="CW26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -11193,31 +11229,31 @@
       <c r="CB27" t="s">
         <v>26</v>
       </c>
-      <c r="CQ27">
+      <c r="CR27">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="CR27" s="18">
+      <c r="CS27" s="18">
         <f t="shared" si="4"/>
         <v>5.3235294117647056</v>
       </c>
-      <c r="CS27">
+      <c r="CT27">
         <f t="shared" si="0"/>
         <v>1.3456083251473603</v>
       </c>
-      <c r="CT27">
+      <c r="CU27">
         <v>0</v>
       </c>
-      <c r="CU27">
+      <c r="CV27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CV27">
+      <c r="CW27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -11458,31 +11494,31 @@
       <c r="CB28" t="s">
         <v>26</v>
       </c>
-      <c r="CQ28">
+      <c r="CR28">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="CR28" s="18">
+      <c r="CS28" s="18">
         <f t="shared" si="4"/>
         <v>4.53125</v>
       </c>
-      <c r="CS28">
+      <c r="CT28">
         <f t="shared" si="0"/>
         <v>1.5434674167816653</v>
       </c>
-      <c r="CT28">
+      <c r="CU28">
         <v>0</v>
       </c>
-      <c r="CU28">
+      <c r="CV28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CV28">
+      <c r="CW28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -11735,31 +11771,31 @@
       <c r="CO29">
         <v>6.5</v>
       </c>
-      <c r="CQ29">
+      <c r="CR29">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="CR29" s="18">
+      <c r="CS29" s="18">
         <f t="shared" si="4"/>
         <v>6.65625</v>
       </c>
-      <c r="CS29">
+      <c r="CT29">
         <f t="shared" si="0"/>
         <v>0.74651970279870483</v>
       </c>
-      <c r="CT29">
-        <v>1</v>
-      </c>
       <c r="CU29">
+        <v>1</v>
+      </c>
+      <c r="CV29">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CV29">
+      <c r="CW29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -12000,31 +12036,31 @@
       <c r="CB30">
         <v>5.5</v>
       </c>
-      <c r="CQ30">
+      <c r="CR30">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="CR30" s="18">
+      <c r="CS30" s="18">
         <f t="shared" si="4"/>
         <v>3.8666666666666667</v>
       </c>
-      <c r="CS30">
+      <c r="CT30">
         <f t="shared" si="0"/>
         <v>2.3563490726929555</v>
       </c>
-      <c r="CT30">
+      <c r="CU30">
         <v>0</v>
       </c>
-      <c r="CU30">
+      <c r="CV30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CV30">
+      <c r="CW30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -12274,31 +12310,34 @@
       <c r="CL31">
         <v>5.5</v>
       </c>
-      <c r="CQ31">
+      <c r="CP31">
+        <v>6</v>
+      </c>
+      <c r="CR31">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="CR31" s="18">
+      <c r="CS31" s="18">
         <f t="shared" si="4"/>
         <v>4.8214285714285712</v>
       </c>
-      <c r="CS31">
+      <c r="CT31">
         <f t="shared" si="0"/>
         <v>0.89335151148745728</v>
       </c>
-      <c r="CT31">
+      <c r="CU31">
         <v>0</v>
       </c>
-      <c r="CU31">
+      <c r="CV31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CV31">
+      <c r="CW31">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -12569,31 +12608,34 @@
       <c r="CO32">
         <v>6</v>
       </c>
-      <c r="CQ32">
-        <f>COUNT(B32:CO32)</f>
-        <v>14</v>
-      </c>
-      <c r="CR32" s="18">
-        <f>AVERAGE(B32:CO32)</f>
-        <v>6.3928571428571432</v>
-      </c>
-      <c r="CS32">
+      <c r="CP32">
+        <v>6</v>
+      </c>
+      <c r="CR32">
+        <f>COUNT(B32:CP32)</f>
+        <v>15</v>
+      </c>
+      <c r="CS32" s="18">
+        <f>AVERAGE(B32:CP32)</f>
+        <v>6.3666666666666663</v>
+      </c>
+      <c r="CT32">
         <f t="shared" si="0"/>
         <v>0.90829510622924903</v>
       </c>
-      <c r="CT32">
-        <v>1</v>
-      </c>
       <c r="CU32">
+        <v>1</v>
+      </c>
+      <c r="CV32">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CV32">
+      <c r="CW32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -12834,31 +12876,31 @@
       <c r="CB33" t="s">
         <v>26</v>
       </c>
-      <c r="CQ33">
-        <f t="shared" ref="CQ33:CQ64" si="5">COUNT(B33:CI33)</f>
+      <c r="CR33">
+        <f t="shared" ref="CR33:CR64" si="5">COUNT(B33:CI33)</f>
         <v>13</v>
       </c>
-      <c r="CR33" s="18">
-        <f t="shared" ref="CR33:CR64" si="6">AVERAGE(B33:CI33)</f>
+      <c r="CS33" s="18">
+        <f t="shared" ref="CS33:CS64" si="6">AVERAGE(B33:CI33)</f>
         <v>7.3461538461538458</v>
       </c>
-      <c r="CS33">
+      <c r="CT33">
         <f t="shared" si="0"/>
         <v>1.5191090506255012</v>
       </c>
-      <c r="CT33">
+      <c r="CU33">
         <v>0</v>
       </c>
-      <c r="CU33">
+      <c r="CV33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CV33">
+      <c r="CW33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -13099,31 +13141,31 @@
       <c r="CB34" t="s">
         <v>26</v>
       </c>
-      <c r="CQ34">
+      <c r="CR34">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="CR34" s="18">
+      <c r="CS34" s="18">
         <f t="shared" si="6"/>
         <v>4.6818181818181817</v>
       </c>
-      <c r="CS34">
-        <f t="shared" ref="CS34:CS65" si="7">IF(CQ34&gt;1,_xlfn.STDEV.S(B34:CF34),"")</f>
+      <c r="CT34">
+        <f t="shared" ref="CT34:CT65" si="7">IF(CR34&gt;1,_xlfn.STDEV.S(B34:CF34),"")</f>
         <v>0.81463879335344846</v>
       </c>
-      <c r="CT34">
+      <c r="CU34">
         <v>0</v>
       </c>
-      <c r="CU34">
-        <f t="shared" ref="CU34:CU65" si="8">COUNT(CK34:CN34)</f>
+      <c r="CV34">
+        <f t="shared" ref="CV34:CV65" si="8">COUNT(CK34:CN34)</f>
         <v>0</v>
       </c>
-      <c r="CV34">
-        <f t="shared" ref="CV34:CV65" si="9">IF(CT34=0,CU34,0)</f>
+      <c r="CW34">
+        <f t="shared" ref="CW34:CW65" si="9">IF(CU34=0,CV34,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>45</v>
       </c>
@@ -13367,31 +13409,31 @@
       <c r="CC35">
         <v>6</v>
       </c>
-      <c r="CQ35">
+      <c r="CR35">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="CR35" s="18">
+      <c r="CS35" s="18">
         <f t="shared" si="6"/>
         <v>8.4499999999999993</v>
       </c>
-      <c r="CS35">
+      <c r="CT35">
         <f t="shared" si="7"/>
         <v>1.1890705987824657</v>
       </c>
-      <c r="CT35">
+      <c r="CU35">
         <v>0</v>
       </c>
-      <c r="CU35">
+      <c r="CV35">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV35">
+      <c r="CW35">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>343</v>
       </c>
@@ -13644,31 +13686,31 @@
       <c r="CO36">
         <v>6</v>
       </c>
-      <c r="CQ36">
+      <c r="CR36">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="CR36" s="18">
+      <c r="CS36" s="18">
         <f t="shared" si="6"/>
         <v>4.125</v>
       </c>
-      <c r="CS36">
+      <c r="CT36">
         <f t="shared" si="7"/>
         <v>1.7677669529663689</v>
       </c>
-      <c r="CT36">
-        <v>1</v>
-      </c>
       <c r="CU36">
+        <v>1</v>
+      </c>
+      <c r="CV36">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CV36">
+      <c r="CW36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>340</v>
       </c>
@@ -13912,31 +13954,31 @@
       <c r="CL37">
         <v>6</v>
       </c>
-      <c r="CQ37">
+      <c r="CR37">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CR37" s="18">
+      <c r="CS37" s="18">
         <f t="shared" si="6"/>
         <v>5.7142857142857144</v>
       </c>
-      <c r="CS37">
+      <c r="CT37">
         <f t="shared" si="7"/>
         <v>0.56694670951384085</v>
       </c>
-      <c r="CT37">
+      <c r="CU37">
         <v>0</v>
       </c>
-      <c r="CU37">
+      <c r="CV37">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CV37">
+      <c r="CW37">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>376</v>
       </c>
@@ -14183,31 +14225,31 @@
       <c r="CO38">
         <v>5.5</v>
       </c>
-      <c r="CQ38">
+      <c r="CR38">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CR38" s="18">
+      <c r="CS38" s="18">
         <f t="shared" si="6"/>
         <v>5.7857142857142856</v>
       </c>
-      <c r="CS38">
+      <c r="CT38">
         <f t="shared" si="7"/>
         <v>0.4879500364742666</v>
       </c>
-      <c r="CT38">
+      <c r="CU38">
         <v>0</v>
       </c>
-      <c r="CU38">
+      <c r="CV38">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CV38">
+      <c r="CW38">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>378</v>
       </c>
@@ -14469,31 +14511,34 @@
       <c r="CO39">
         <v>5.5</v>
       </c>
-      <c r="CQ39">
+      <c r="CP39">
+        <v>6</v>
+      </c>
+      <c r="CR39">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="CR39" s="18">
+      <c r="CS39" s="18">
         <f t="shared" si="6"/>
         <v>5.166666666666667</v>
       </c>
-      <c r="CS39">
+      <c r="CT39">
         <f t="shared" si="7"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="CT39">
-        <v>1</v>
-      </c>
       <c r="CU39">
+        <v>1</v>
+      </c>
+      <c r="CV39">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CV39">
+      <c r="CW39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -14737,31 +14782,31 @@
       <c r="CH40">
         <v>6.5</v>
       </c>
-      <c r="CQ40">
+      <c r="CR40">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CR40" s="18">
+      <c r="CS40" s="18">
         <f t="shared" si="6"/>
         <v>7.8</v>
       </c>
-      <c r="CS40">
+      <c r="CT40">
         <f t="shared" si="7"/>
         <v>1.0307764064044151</v>
       </c>
-      <c r="CT40">
+      <c r="CU40">
         <v>0</v>
       </c>
-      <c r="CU40">
+      <c r="CV40">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV40">
+      <c r="CW40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>60</v>
       </c>
@@ -15005,31 +15050,31 @@
       <c r="CM41">
         <v>5.5</v>
       </c>
-      <c r="CQ41">
+      <c r="CR41">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CR41" s="18">
+      <c r="CS41" s="18">
         <f t="shared" si="6"/>
         <v>3.375</v>
       </c>
-      <c r="CS41">
+      <c r="CT41">
         <f t="shared" si="7"/>
         <v>0.47871355387816905</v>
       </c>
-      <c r="CT41">
+      <c r="CU41">
         <v>0</v>
       </c>
-      <c r="CU41">
+      <c r="CV41">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CV41">
+      <c r="CW41">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -15270,31 +15315,31 @@
       <c r="CB42" t="s">
         <v>26</v>
       </c>
-      <c r="CQ42">
+      <c r="CR42">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CR42" s="18">
+      <c r="CS42" s="18">
         <f t="shared" si="6"/>
         <v>5.625</v>
       </c>
-      <c r="CS42">
+      <c r="CT42">
         <f t="shared" si="7"/>
         <v>0.9464847243000456</v>
       </c>
-      <c r="CT42">
+      <c r="CU42">
         <v>0</v>
       </c>
-      <c r="CU42">
+      <c r="CV42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV42">
+      <c r="CW42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -15535,31 +15580,31 @@
       <c r="CB43" t="s">
         <v>26</v>
       </c>
-      <c r="CQ43">
+      <c r="CR43">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CR43" s="18">
+      <c r="CS43" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CS43">
+      <c r="CT43">
         <f t="shared" si="7"/>
         <v>1.0408329997330663</v>
       </c>
-      <c r="CT43">
+      <c r="CU43">
         <v>0</v>
       </c>
-      <c r="CU43">
+      <c r="CV43">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV43">
+      <c r="CW43">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -15800,31 +15845,31 @@
       <c r="CB44" t="s">
         <v>26</v>
       </c>
-      <c r="CQ44">
+      <c r="CR44">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CR44" s="18">
+      <c r="CS44" s="18">
         <f t="shared" si="6"/>
         <v>1.375</v>
       </c>
-      <c r="CS44">
+      <c r="CT44">
         <f t="shared" si="7"/>
         <v>1.8874586088176875</v>
       </c>
-      <c r="CT44">
+      <c r="CU44">
         <v>0</v>
       </c>
-      <c r="CU44">
+      <c r="CV44">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV44">
+      <c r="CW44">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>344</v>
       </c>
@@ -16065,31 +16110,31 @@
       <c r="CB45" t="s">
         <v>26</v>
       </c>
-      <c r="CQ45">
+      <c r="CR45">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CR45" s="18">
+      <c r="CS45" s="18">
         <f t="shared" si="6"/>
         <v>4.625</v>
       </c>
-      <c r="CS45">
+      <c r="CT45">
         <f t="shared" si="7"/>
         <v>1.4361406616345072</v>
       </c>
-      <c r="CT45">
+      <c r="CU45">
         <v>0</v>
       </c>
-      <c r="CU45">
+      <c r="CV45">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV45">
+      <c r="CW45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>361</v>
       </c>
@@ -16330,31 +16375,31 @@
       <c r="CB46" t="s">
         <v>26</v>
       </c>
-      <c r="CQ46">
+      <c r="CR46">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CR46" s="18">
+      <c r="CS46" s="18">
         <f t="shared" si="6"/>
         <v>6.25</v>
       </c>
-      <c r="CS46">
+      <c r="CT46">
         <f t="shared" si="7"/>
         <v>0.8660254037844386</v>
       </c>
-      <c r="CT46">
+      <c r="CU46">
         <v>0</v>
       </c>
-      <c r="CU46">
+      <c r="CV46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV46">
+      <c r="CW46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -16595,31 +16640,31 @@
       <c r="CB47" t="s">
         <v>26</v>
       </c>
-      <c r="CQ47">
+      <c r="CR47">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CR47" s="18">
+      <c r="CS47" s="18">
         <f t="shared" si="6"/>
         <v>2.875</v>
       </c>
-      <c r="CS47">
+      <c r="CT47">
         <f t="shared" si="7"/>
         <v>2.7801378862687129</v>
       </c>
-      <c r="CT47">
+      <c r="CU47">
         <v>0</v>
       </c>
-      <c r="CU47">
+      <c r="CV47">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV47">
+      <c r="CW47">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -16860,31 +16905,31 @@
       <c r="CB48" t="s">
         <v>26</v>
       </c>
-      <c r="CQ48">
+      <c r="CR48">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CR48" s="18">
+      <c r="CS48" s="18">
         <f t="shared" si="6"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="CS48">
+      <c r="CT48">
         <f t="shared" si="7"/>
         <v>1.4433756729740652</v>
       </c>
-      <c r="CT48">
+      <c r="CU48">
         <v>0</v>
       </c>
-      <c r="CU48">
+      <c r="CV48">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV48">
+      <c r="CW48">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -17125,31 +17170,31 @@
       <c r="CB49" t="s">
         <v>26</v>
       </c>
-      <c r="CQ49">
+      <c r="CR49">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CR49" s="18">
+      <c r="CS49" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CS49">
+      <c r="CT49">
         <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
-      <c r="CT49">
+      <c r="CU49">
         <v>0</v>
       </c>
-      <c r="CU49">
+      <c r="CV49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV49">
+      <c r="CW49">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -17390,31 +17435,31 @@
       <c r="CB50" t="s">
         <v>26</v>
       </c>
-      <c r="CQ50">
+      <c r="CR50">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CR50" s="18">
+      <c r="CS50" s="18">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="CS50">
+      <c r="CT50">
         <f t="shared" si="7"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT50">
+      <c r="CU50">
         <v>0</v>
       </c>
-      <c r="CU50">
+      <c r="CV50">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV50">
+      <c r="CW50">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -17658,31 +17703,31 @@
       <c r="CG51">
         <v>6</v>
       </c>
-      <c r="CQ51">
+      <c r="CR51">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CR51" s="18">
+      <c r="CS51" s="18">
         <f t="shared" si="6"/>
         <v>5.666666666666667</v>
       </c>
-      <c r="CS51">
+      <c r="CT51">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CT51">
+      <c r="CU51">
         <v>0</v>
       </c>
-      <c r="CU51">
+      <c r="CV51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV51">
+      <c r="CW51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>368</v>
       </c>
@@ -17926,31 +17971,31 @@
       <c r="CG52">
         <v>6</v>
       </c>
-      <c r="CQ52">
+      <c r="CR52">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CR52" s="18">
+      <c r="CS52" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CS52">
+      <c r="CT52">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CT52">
+      <c r="CU52">
         <v>0</v>
       </c>
-      <c r="CU52">
+      <c r="CV52">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV52">
+      <c r="CW52">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>362</v>
       </c>
@@ -18194,31 +18239,31 @@
       <c r="CD53">
         <v>5.5</v>
       </c>
-      <c r="CQ53">
+      <c r="CR53">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CR53" s="18">
+      <c r="CS53" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CS53">
+      <c r="CT53">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CT53">
+      <c r="CU53">
         <v>0</v>
       </c>
-      <c r="CU53">
+      <c r="CV53">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV53">
+      <c r="CW53">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>364</v>
       </c>
@@ -18468,31 +18513,31 @@
       <c r="CN54">
         <v>6</v>
       </c>
-      <c r="CQ54">
+      <c r="CR54">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CR54" s="18">
+      <c r="CS54" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="CS54">
+      <c r="CT54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CT54">
-        <v>1</v>
-      </c>
       <c r="CU54">
+        <v>1</v>
+      </c>
+      <c r="CV54">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CV54">
+      <c r="CW54">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -18733,31 +18778,31 @@
       <c r="CB55" t="s">
         <v>26</v>
       </c>
-      <c r="CQ55">
+      <c r="CR55">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CR55" s="18">
+      <c r="CS55" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CS55">
+      <c r="CT55">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CT55">
+      <c r="CU55">
         <v>0</v>
       </c>
-      <c r="CU55">
+      <c r="CV55">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV55">
+      <c r="CW55">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>339</v>
       </c>
@@ -18998,31 +19043,31 @@
       <c r="CB56" t="s">
         <v>26</v>
       </c>
-      <c r="CQ56">
+      <c r="CR56">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CR56" s="18">
+      <c r="CS56" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CS56">
+      <c r="CT56">
         <f t="shared" si="7"/>
         <v>2.4748737341529163</v>
       </c>
-      <c r="CT56">
+      <c r="CU56">
         <v>0</v>
       </c>
-      <c r="CU56">
+      <c r="CV56">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV56">
+      <c r="CW56">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>342</v>
       </c>
@@ -19269,31 +19314,31 @@
       <c r="CO57">
         <v>6</v>
       </c>
-      <c r="CQ57">
+      <c r="CR57">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CR57" s="18">
+      <c r="CS57" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CS57">
+      <c r="CT57">
         <f t="shared" si="7"/>
         <v>2.1213203435596424</v>
       </c>
-      <c r="CT57">
+      <c r="CU57">
         <v>0</v>
       </c>
-      <c r="CU57">
+      <c r="CV57">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV57">
+      <c r="CW57">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>369</v>
       </c>
@@ -19534,31 +19579,31 @@
       <c r="CB58" t="s">
         <v>26</v>
       </c>
-      <c r="CQ58">
+      <c r="CR58">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CR58" s="18">
+      <c r="CS58" s="18">
         <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
-      <c r="CS58">
+      <c r="CT58">
         <f t="shared" si="7"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="CT58">
+      <c r="CU58">
         <v>0</v>
       </c>
-      <c r="CU58">
+      <c r="CV58">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV58">
+      <c r="CW58">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>379</v>
       </c>
@@ -19799,31 +19844,31 @@
       <c r="CB59" t="s">
         <v>26</v>
       </c>
-      <c r="CQ59">
+      <c r="CR59">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CR59" s="18">
+      <c r="CS59" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CS59">
+      <c r="CT59">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CT59">
+      <c r="CU59">
         <v>0</v>
       </c>
-      <c r="CU59">
+      <c r="CV59">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV59">
+      <c r="CW59">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>390</v>
       </c>
@@ -20070,31 +20115,31 @@
       <c r="CH60">
         <v>7</v>
       </c>
-      <c r="CQ60">
+      <c r="CR60">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CR60" s="18">
+      <c r="CS60" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CS60" t="e">
+      <c r="CT60" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CT60">
+      <c r="CU60">
         <v>0</v>
       </c>
-      <c r="CU60">
+      <c r="CV60">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV60">
+      <c r="CW60">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>388</v>
       </c>
@@ -20338,31 +20383,31 @@
       <c r="CH61">
         <v>5</v>
       </c>
-      <c r="CQ61">
+      <c r="CR61">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CR61" s="18">
+      <c r="CS61" s="18">
         <f t="shared" si="6"/>
         <v>4.25</v>
       </c>
-      <c r="CS61" t="e">
+      <c r="CT61" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CT61">
+      <c r="CU61">
         <v>0</v>
       </c>
-      <c r="CU61">
+      <c r="CV61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV61">
+      <c r="CW61">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>345</v>
       </c>
@@ -20621,31 +20666,31 @@
       <c r="CO62">
         <v>4.5</v>
       </c>
-      <c r="CQ62">
+      <c r="CR62">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CR62" s="18">
+      <c r="CS62" s="18">
         <f t="shared" si="6"/>
         <v>4.25</v>
       </c>
-      <c r="CS62" t="e">
+      <c r="CT62" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CT62">
-        <v>1</v>
-      </c>
       <c r="CU62">
+        <v>1</v>
+      </c>
+      <c r="CV62">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CV62">
+      <c r="CW62">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>387</v>
       </c>
@@ -20895,31 +20940,31 @@
       <c r="CJ63">
         <v>7</v>
       </c>
-      <c r="CQ63">
+      <c r="CR63">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CR63" s="18">
+      <c r="CS63" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="CS63" t="e">
+      <c r="CT63" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CT63">
+      <c r="CU63">
         <v>0</v>
       </c>
-      <c r="CU63">
+      <c r="CV63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV63">
+      <c r="CW63">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>86</v>
       </c>
@@ -21160,31 +21205,31 @@
       <c r="CB64" t="s">
         <v>26</v>
       </c>
-      <c r="CQ64">
+      <c r="CR64">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CR64" s="18">
+      <c r="CS64" s="18">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="CS64" t="str">
+      <c r="CT64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="CT64">
+      <c r="CU64">
         <v>0</v>
       </c>
-      <c r="CU64">
+      <c r="CV64">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV64">
+      <c r="CW64">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -21425,31 +21470,31 @@
       <c r="CB65" t="s">
         <v>26</v>
       </c>
-      <c r="CQ65">
-        <f t="shared" ref="CQ65:CQ83" si="10">COUNT(B65:CI65)</f>
-        <v>1</v>
-      </c>
-      <c r="CR65" s="18">
-        <f t="shared" ref="CR65:CR83" si="11">AVERAGE(B65:CI65)</f>
+      <c r="CR65">
+        <f t="shared" ref="CR65:CR83" si="10">COUNT(B65:CI65)</f>
+        <v>1</v>
+      </c>
+      <c r="CS65" s="18">
+        <f t="shared" ref="CS65:CS83" si="11">AVERAGE(B65:CI65)</f>
         <v>7</v>
       </c>
-      <c r="CS65" t="str">
+      <c r="CT65" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="CT65">
+      <c r="CU65">
         <v>0</v>
       </c>
-      <c r="CU65">
+      <c r="CV65">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CV65">
+      <c r="CW65">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>353</v>
       </c>
@@ -21690,31 +21735,31 @@
       <c r="CB66" t="s">
         <v>26</v>
       </c>
-      <c r="CQ66">
+      <c r="CR66">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR66" s="18">
+      <c r="CS66" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CS66" t="str">
-        <f t="shared" ref="CS66:CS83" si="12">IF(CQ66&gt;1,_xlfn.STDEV.S(B66:CF66),"")</f>
+      <c r="CT66" t="str">
+        <f t="shared" ref="CT66:CT83" si="12">IF(CR66&gt;1,_xlfn.STDEV.S(B66:CF66),"")</f>
         <v/>
       </c>
-      <c r="CT66">
+      <c r="CU66">
         <v>0</v>
       </c>
-      <c r="CU66">
-        <f t="shared" ref="CU66:CU83" si="13">COUNT(CK66:CN66)</f>
+      <c r="CV66">
+        <f t="shared" ref="CV66:CV83" si="13">COUNT(CK66:CN66)</f>
         <v>0</v>
       </c>
-      <c r="CV66">
-        <f t="shared" ref="CV66:CV83" si="14">IF(CT66=0,CU66,0)</f>
+      <c r="CW66">
+        <f t="shared" ref="CW66:CW83" si="14">IF(CU66=0,CV66,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>80</v>
       </c>
@@ -21955,31 +22000,31 @@
       <c r="CB67" t="s">
         <v>26</v>
       </c>
-      <c r="CQ67">
+      <c r="CR67">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR67" s="18">
+      <c r="CS67" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CS67" t="str">
+      <c r="CT67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT67">
+      <c r="CU67">
         <v>0</v>
       </c>
-      <c r="CU67">
+      <c r="CV67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV67">
+      <c r="CW67">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>47</v>
       </c>
@@ -22220,31 +22265,31 @@
       <c r="CB68" t="s">
         <v>26</v>
       </c>
-      <c r="CQ68">
+      <c r="CR68">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR68" s="18">
+      <c r="CS68" s="18">
         <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
-      <c r="CS68" t="str">
+      <c r="CT68" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT68">
+      <c r="CU68">
         <v>0</v>
       </c>
-      <c r="CU68">
+      <c r="CV68">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV68">
+      <c r="CW68">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -22485,31 +22530,31 @@
       <c r="CB69" t="s">
         <v>26</v>
       </c>
-      <c r="CQ69">
+      <c r="CR69">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR69" s="18">
+      <c r="CS69" s="18">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="CS69" t="str">
+      <c r="CT69" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT69">
+      <c r="CU69">
         <v>0</v>
       </c>
-      <c r="CU69">
+      <c r="CV69">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV69">
+      <c r="CW69">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>347</v>
       </c>
@@ -22750,31 +22795,31 @@
       <c r="CB70" t="s">
         <v>26</v>
       </c>
-      <c r="CQ70">
+      <c r="CR70">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR70" s="18">
+      <c r="CS70" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="CS70" t="str">
+      <c r="CT70" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT70">
+      <c r="CU70">
         <v>0</v>
       </c>
-      <c r="CU70">
+      <c r="CV70">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV70">
+      <c r="CW70">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>350</v>
       </c>
@@ -23015,31 +23060,31 @@
       <c r="CB71" t="s">
         <v>26</v>
       </c>
-      <c r="CQ71">
+      <c r="CR71">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR71" s="18">
+      <c r="CS71" s="18">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="CS71" t="str">
+      <c r="CT71" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT71">
+      <c r="CU71">
         <v>0</v>
       </c>
-      <c r="CU71">
+      <c r="CV71">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV71">
+      <c r="CW71">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>351</v>
       </c>
@@ -23280,31 +23325,31 @@
       <c r="CB72" t="s">
         <v>26</v>
       </c>
-      <c r="CQ72">
+      <c r="CR72">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR72" s="18">
+      <c r="CS72" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="CS72" t="str">
+      <c r="CT72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT72">
+      <c r="CU72">
         <v>0</v>
       </c>
-      <c r="CU72">
+      <c r="CV72">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV72">
+      <c r="CW72">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>352</v>
       </c>
@@ -23545,31 +23590,31 @@
       <c r="CB73" t="s">
         <v>26</v>
       </c>
-      <c r="CQ73">
+      <c r="CR73">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR73" s="18">
+      <c r="CS73" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="CS73" t="str">
+      <c r="CT73" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT73">
+      <c r="CU73">
         <v>0</v>
       </c>
-      <c r="CU73">
+      <c r="CV73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV73">
+      <c r="CW73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>354</v>
       </c>
@@ -23810,31 +23855,31 @@
       <c r="CB74" t="s">
         <v>26</v>
       </c>
-      <c r="CQ74">
+      <c r="CR74">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR74" s="18">
+      <c r="CS74" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CS74" t="str">
+      <c r="CT74" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT74">
+      <c r="CU74">
         <v>0</v>
       </c>
-      <c r="CU74">
+      <c r="CV74">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV74">
+      <c r="CW74">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>365</v>
       </c>
@@ -24075,31 +24120,31 @@
       <c r="CB75" t="s">
         <v>26</v>
       </c>
-      <c r="CQ75">
+      <c r="CR75">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR75" s="18">
+      <c r="CS75" s="18">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
-      <c r="CS75" t="str">
+      <c r="CT75" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT75">
+      <c r="CU75">
         <v>0</v>
       </c>
-      <c r="CU75">
+      <c r="CV75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV75">
+      <c r="CW75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>366</v>
       </c>
@@ -24340,31 +24385,31 @@
       <c r="CB76" t="s">
         <v>26</v>
       </c>
-      <c r="CQ76">
+      <c r="CR76">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR76" s="18">
+      <c r="CS76" s="18">
         <f t="shared" si="11"/>
         <v>2.5</v>
       </c>
-      <c r="CS76" t="str">
+      <c r="CT76" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT76">
+      <c r="CU76">
         <v>0</v>
       </c>
-      <c r="CU76">
+      <c r="CV76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV76">
+      <c r="CW76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>374</v>
       </c>
@@ -24605,31 +24650,31 @@
       <c r="CB77" t="s">
         <v>26</v>
       </c>
-      <c r="CQ77">
+      <c r="CR77">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR77" s="18">
+      <c r="CS77" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CS77" t="str">
+      <c r="CT77" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT77">
+      <c r="CU77">
         <v>0</v>
       </c>
-      <c r="CU77">
+      <c r="CV77">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV77">
+      <c r="CW77">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>375</v>
       </c>
@@ -24870,31 +24915,31 @@
       <c r="CB78" t="s">
         <v>26</v>
       </c>
-      <c r="CQ78">
+      <c r="CR78">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR78" s="18">
+      <c r="CS78" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CS78" t="str">
+      <c r="CT78" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT78">
+      <c r="CU78">
         <v>0</v>
       </c>
-      <c r="CU78">
+      <c r="CV78">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV78">
+      <c r="CW78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>377</v>
       </c>
@@ -25135,31 +25180,31 @@
       <c r="CB79" t="s">
         <v>26</v>
       </c>
-      <c r="CQ79">
+      <c r="CR79">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR79" s="18">
+      <c r="CS79" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="CS79" t="str">
+      <c r="CT79" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT79">
+      <c r="CU79">
         <v>0</v>
       </c>
-      <c r="CU79">
+      <c r="CV79">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV79">
+      <c r="CW79">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>381</v>
       </c>
@@ -25400,31 +25445,31 @@
       <c r="CB80" t="s">
         <v>26</v>
       </c>
-      <c r="CQ80">
+      <c r="CR80">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR80" s="18">
+      <c r="CS80" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CS80" t="str">
+      <c r="CT80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT80">
+      <c r="CU80">
         <v>0</v>
       </c>
-      <c r="CU80">
+      <c r="CV80">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV80">
+      <c r="CW80">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>382</v>
       </c>
@@ -25665,31 +25710,31 @@
       <c r="CB81" t="s">
         <v>26</v>
       </c>
-      <c r="CQ81">
+      <c r="CR81">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR81" s="18">
+      <c r="CS81" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CS81" t="str">
+      <c r="CT81" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT81">
+      <c r="CU81">
         <v>0</v>
       </c>
-      <c r="CU81">
+      <c r="CV81">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV81">
+      <c r="CW81">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>389</v>
       </c>
@@ -25933,31 +25978,31 @@
       <c r="CH82">
         <v>7.5</v>
       </c>
-      <c r="CQ82">
+      <c r="CR82">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR82" s="18">
+      <c r="CS82" s="18">
         <f t="shared" si="11"/>
         <v>7.5</v>
       </c>
-      <c r="CS82" t="str">
+      <c r="CT82" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT82">
+      <c r="CU82">
         <v>0</v>
       </c>
-      <c r="CU82">
+      <c r="CV82">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV82">
+      <c r="CW82">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>391</v>
       </c>
@@ -26201,68 +26246,164 @@
       <c r="CI83">
         <v>7</v>
       </c>
-      <c r="CQ83">
+      <c r="CR83">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CR83" s="18">
+      <c r="CS83" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CS83" t="str">
+      <c r="CT83" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CT83">
+      <c r="CU83">
         <v>0</v>
       </c>
-      <c r="CU83">
+      <c r="CV83">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CV83">
+      <c r="CW83">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:100" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:101" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>393</v>
       </c>
       <c r="CO84">
         <v>6.5</v>
       </c>
-      <c r="CQ84">
-        <f t="shared" ref="CQ84" si="15">COUNT(B84:CI84)</f>
+      <c r="CP84">
+        <v>7</v>
+      </c>
+      <c r="CR84">
+        <f t="shared" ref="CR84:CR87" si="15">COUNT(B84:CI84)</f>
         <v>0</v>
       </c>
-      <c r="CR84" s="18" t="e">
-        <f t="shared" ref="CR84" si="16">AVERAGE(B84:CI84)</f>
+      <c r="CS84" s="18" t="e">
+        <f t="shared" ref="CS84:CS87" si="16">AVERAGE(B84:CI84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="CS84" t="str">
-        <f t="shared" ref="CS84" si="17">IF(CQ84&gt;1,_xlfn.STDEV.S(B84:CF84),"")</f>
+      <c r="CT84" t="str">
+        <f t="shared" ref="CT84:CT87" si="17">IF(CR84&gt;1,_xlfn.STDEV.S(B84:CF84),"")</f>
         <v/>
       </c>
-      <c r="CT84">
+      <c r="CU84">
         <v>0</v>
       </c>
-      <c r="CU84">
-        <f t="shared" ref="CU84" si="18">COUNT(CK84:CN84)</f>
+      <c r="CV84">
+        <f t="shared" ref="CV84:CV87" si="18">COUNT(CK84:CN84)</f>
         <v>0</v>
       </c>
-      <c r="CV84">
-        <f t="shared" ref="CV84" si="19">IF(CT84=0,CU84,0)</f>
+      <c r="CW84">
+        <f t="shared" ref="CW84:CW87" si="19">IF(CU84=0,CV84,0)</f>
         <v>0</v>
       </c>
     </row>
+    <row r="85" spans="1:101" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>394</v>
+      </c>
+      <c r="CP85">
+        <v>6</v>
+      </c>
+      <c r="CR85">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="CS85" s="18" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CT85" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="CU85">
+        <v>0</v>
+      </c>
+      <c r="CV85">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="CW85">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:101" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>395</v>
+      </c>
+      <c r="CP86">
+        <v>5.5</v>
+      </c>
+      <c r="CR86">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="CS86" s="18" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CT86" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="CU86">
+        <v>0</v>
+      </c>
+      <c r="CV86">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="CW86">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:101" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>396</v>
+      </c>
+      <c r="CP87">
+        <v>6.5</v>
+      </c>
+      <c r="CR87">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="CS87" s="18" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CT87" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="CU87">
+        <v>0</v>
+      </c>
+      <c r="CV87">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="CW87">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CV83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
-    <sortState ref="A2:CV83">
-      <sortCondition descending="1" ref="CQ1:CQ83"/>
+  <autoFilter ref="A1:CW83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
+    <sortState ref="A2:CW83">
+      <sortCondition descending="1" ref="CR1:CR83"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="CQ2:CQ84">
+  <conditionalFormatting sqref="CR2:CR87">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -26274,7 +26415,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS84">
+  <conditionalFormatting sqref="CT2:CT87">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -26286,7 +26427,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ84">
+  <conditionalFormatting sqref="CR2:CR87">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -26298,7 +26439,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR84">
+  <conditionalFormatting sqref="CS2:CS87">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
@@ -26310,7 +26451,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR84">
+  <conditionalFormatting sqref="CS2:CS87">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
@@ -26322,7 +26463,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ84">
+  <conditionalFormatting sqref="CR2:CR87">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -26334,7 +26475,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR84">
+  <conditionalFormatting sqref="CS2:CS87">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -26346,7 +26487,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP79">
+  <conditionalFormatting sqref="CQ2:CQ79">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -26358,7 +26499,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP67">
+  <conditionalFormatting sqref="CQ2:CQ67">
     <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
@@ -26370,7 +26511,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP67">
+  <conditionalFormatting sqref="CQ2:CQ67">
     <cfRule type="colorScale" priority="127">
       <colorScale>
         <cfvo type="min"/>
@@ -26382,7 +26523,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP67">
+  <conditionalFormatting sqref="CQ2:CQ67">
     <cfRule type="colorScale" priority="129">
       <colorScale>
         <cfvo type="min"/>
@@ -26394,7 +26535,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:CO83">
+  <conditionalFormatting sqref="B2:CP83">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -28615,7 +28756,7 @@
         <v>96.34</v>
       </c>
       <c r="AA2" s="1">
-        <v>46107</v>
+        <v>46116</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.35">
@@ -30199,7 +30340,7 @@
       <c r="V32" s="19">
         <v>78.34</v>
       </c>
-      <c r="W32" s="21">
+      <c r="W32" s="19">
         <v>96.34</v>
       </c>
     </row>
@@ -30675,7 +30816,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>80</v>
       </c>
@@ -30685,7 +30826,7 @@
       <c r="H49" s="19"/>
       <c r="I49" s="19"/>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>83</v>
       </c>
@@ -30695,7 +30836,7 @@
       </c>
       <c r="I50" s="19"/>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>86</v>
       </c>
@@ -30705,7 +30846,7 @@
       </c>
       <c r="I51" s="19"/>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>85</v>
       </c>
@@ -30717,7 +30858,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>84</v>
       </c>
@@ -30773,7 +30914,7 @@
         <v>96.34</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>340</v>
       </c>
@@ -30793,7 +30934,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>339</v>
       </c>
@@ -30807,7 +30948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>344</v>
       </c>
@@ -30824,7 +30965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>342</v>
       </c>
@@ -30846,7 +30987,7 @@
       </c>
       <c r="W57" s="19"/>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>345</v>
       </c>
@@ -30860,11 +31001,14 @@
       <c r="V58" s="19">
         <v>54</v>
       </c>
-      <c r="W58" s="21">
+      <c r="W58" s="19">
         <v>96.34</v>
       </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X58">
+        <v>-27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>346</v>
       </c>
@@ -30893,7 +31037,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>347</v>
       </c>
@@ -30905,7 +31049,7 @@
       </c>
       <c r="L60" s="19"/>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>354</v>
       </c>
@@ -30917,7 +31061,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>356</v>
       </c>
@@ -30925,7 +31069,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>352</v>
       </c>
@@ -30933,7 +31077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>350</v>
       </c>
@@ -31502,8 +31646,8 @@
         <v>1972.28</v>
       </c>
       <c r="W87" s="23">
-        <f>5*27+85.84*13.75</f>
-        <v>1315.3</v>
+        <f>5*27+85.84*15.75</f>
+        <v>1486.98</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.35">
@@ -31593,7 +31737,7 @@
       </c>
       <c r="W88" s="24">
         <f t="shared" ref="W88" si="9">W87/W86</f>
-        <v>0.70951941697819088</v>
+        <v>0.80212969106533138</v>
       </c>
     </row>
   </sheetData>
@@ -31604,7 +31748,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X270"/>
+  <dimension ref="A1:X273"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -45016,6 +45160,144 @@
         <v>393</v>
       </c>
     </row>
+    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A271" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B271" s="62">
+        <v>5</v>
+      </c>
+      <c r="C271" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D271" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E271" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F271" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="H271" s="8"/>
+      <c r="I271" s="9">
+        <v>4</v>
+      </c>
+      <c r="J271" s="10">
+        <v>5</v>
+      </c>
+      <c r="K271" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="L271" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="M271" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="N271" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="O271" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="P271" s="10"/>
+    </row>
+    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A272" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B272" s="62">
+        <v>5</v>
+      </c>
+      <c r="C272" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D272" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E272" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F272" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="G272" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H272" s="10"/>
+      <c r="I272" s="11">
+        <v>6</v>
+      </c>
+      <c r="J272" s="2">
+        <v>8</v>
+      </c>
+      <c r="K272" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L272" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M272" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N272" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="O272" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="P272" s="2"/>
+    </row>
+    <row r="273" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A273" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B273" s="62">
+        <v>4</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F273" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="G273" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="H273" s="2"/>
+      <c r="I273" s="5">
+        <v>3</v>
+      </c>
+      <c r="J273" s="8">
+        <v>6</v>
+      </c>
+      <c r="K273" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L273" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="M273" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N273" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="O273" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="P273" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -45023,7 +45305,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:BV84"/>
+  <dimension ref="A1:BW87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -45032,10 +45314,10 @@
     <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="74" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="75" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -45258,8 +45540,11 @@
       <c r="BV1" s="1">
         <v>46113</v>
       </c>
-    </row>
-    <row r="2" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="BW1" s="1">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -45314,8 +45599,11 @@
       <c r="BV2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="BW2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -45323,7 +45611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -45361,12 +45649,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -45374,12 +45662,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="8" spans="1:74" x14ac:dyDescent="0.35">
+      <c r="BW7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>364</v>
       </c>
@@ -45396,7 +45687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -45404,7 +45695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>353</v>
       </c>
@@ -45412,2732 +45703,2774 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="12" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="14" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>395</v>
+      </c>
+      <c r="BW14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>362</v>
       </c>
-      <c r="BK14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="BK15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="17" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="J16">
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="J17">
         <v>3</v>
       </c>
-      <c r="K16">
+      <c r="K17">
         <v>3</v>
       </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="R16">
-        <v>1</v>
-      </c>
-      <c r="V16">
-        <v>1</v>
-      </c>
-      <c r="AE16">
-        <v>1</v>
-      </c>
-      <c r="AF16">
-        <v>1</v>
-      </c>
-      <c r="AH16">
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="AE17">
+        <v>1</v>
+      </c>
+      <c r="AF17">
+        <v>1</v>
+      </c>
+      <c r="AH17">
         <v>2</v>
       </c>
-      <c r="AT16">
-        <v>1</v>
-      </c>
-      <c r="BA16">
-        <v>1</v>
-      </c>
-      <c r="BH16">
-        <v>1</v>
-      </c>
-      <c r="BM16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="AT17">
+        <v>1</v>
+      </c>
+      <c r="BA17">
+        <v>1</v>
+      </c>
+      <c r="BH17">
+        <v>1</v>
+      </c>
+      <c r="BM17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="P17">
-        <v>1</v>
-      </c>
-      <c r="S17">
-        <v>1</v>
-      </c>
-      <c r="W17">
-        <v>1</v>
-      </c>
-      <c r="Z17">
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="Z18">
         <v>2</v>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <v>0.5</v>
       </c>
-      <c r="AK17">
-        <v>1</v>
-      </c>
-      <c r="AR17">
+      <c r="AK18">
+        <v>1</v>
+      </c>
+      <c r="AR18">
         <v>2</v>
       </c>
-      <c r="AX17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="AX18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>378</v>
       </c>
-      <c r="BL18">
-        <v>1</v>
-      </c>
-      <c r="BR18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="BL19">
+        <v>1</v>
+      </c>
+      <c r="BR19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>54</v>
       </c>
-      <c r="C19">
+      <c r="C20">
         <v>2</v>
       </c>
-      <c r="D19">
+      <c r="D20">
         <v>3</v>
       </c>
-      <c r="V19">
+      <c r="V20">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="21" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>66</v>
       </c>
-      <c r="D20">
+      <c r="D21">
         <v>2</v>
       </c>
-      <c r="I20">
+      <c r="I21">
         <v>3</v>
       </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="T20">
-        <v>1</v>
-      </c>
-      <c r="W20">
-        <v>1</v>
-      </c>
-      <c r="X20">
-        <v>1</v>
-      </c>
-      <c r="Y20">
-        <v>1</v>
-      </c>
-      <c r="Z20">
-        <v>1</v>
-      </c>
-      <c r="AA20">
-        <v>1</v>
-      </c>
-      <c r="AC20">
-        <v>1</v>
-      </c>
-      <c r="AD20">
-        <v>1</v>
-      </c>
-      <c r="AH20">
-        <v>1</v>
-      </c>
-      <c r="AI20">
-        <v>1</v>
-      </c>
-      <c r="BA20">
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>1</v>
+      </c>
+      <c r="AA21">
+        <v>1</v>
+      </c>
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AD21">
+        <v>1</v>
+      </c>
+      <c r="AH21">
+        <v>1</v>
+      </c>
+      <c r="AI21">
+        <v>1</v>
+      </c>
+      <c r="BA21">
         <v>3</v>
       </c>
-      <c r="BG20">
-        <v>1</v>
-      </c>
-      <c r="BP20">
-        <v>1</v>
-      </c>
-      <c r="BU20">
+      <c r="BG21">
+        <v>1</v>
+      </c>
+      <c r="BP21">
+        <v>1</v>
+      </c>
+      <c r="BU21">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="22" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>84</v>
       </c>
-      <c r="I21">
+      <c r="I22">
         <v>2</v>
       </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="L21">
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="L22">
         <v>3</v>
       </c>
-      <c r="N21">
+      <c r="N22">
         <v>2</v>
       </c>
-      <c r="O21">
+      <c r="O22">
         <v>2</v>
       </c>
-      <c r="P21">
-        <v>1</v>
-      </c>
-      <c r="S21">
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="S22">
         <v>2</v>
       </c>
-      <c r="V21">
+      <c r="V22">
         <v>4</v>
       </c>
-      <c r="W21">
+      <c r="W22">
         <v>6</v>
       </c>
-      <c r="X21">
+      <c r="X22">
         <v>3</v>
       </c>
-      <c r="AB21">
-        <v>1</v>
-      </c>
-      <c r="AC21">
+      <c r="AB22">
+        <v>1</v>
+      </c>
+      <c r="AC22">
         <v>2</v>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <v>3</v>
       </c>
-      <c r="AE21">
-        <v>1</v>
-      </c>
-      <c r="AH21">
+      <c r="AE22">
+        <v>1</v>
+      </c>
+      <c r="AH22">
         <v>4</v>
       </c>
-      <c r="AI21">
-        <v>5</v>
-      </c>
-      <c r="AK21">
-        <v>1</v>
-      </c>
-      <c r="AL21">
-        <v>1</v>
-      </c>
-      <c r="AN21">
+      <c r="AI22">
+        <v>5</v>
+      </c>
+      <c r="AK22">
+        <v>1</v>
+      </c>
+      <c r="AL22">
+        <v>1</v>
+      </c>
+      <c r="AN22">
         <v>2</v>
       </c>
-      <c r="AU21">
+      <c r="AU22">
         <v>4</v>
       </c>
-      <c r="AV21">
-        <v>1</v>
-      </c>
-      <c r="AX21">
-        <v>1</v>
-      </c>
-      <c r="BH21">
-        <v>1</v>
-      </c>
-      <c r="BI21">
+      <c r="AV22">
+        <v>1</v>
+      </c>
+      <c r="AX22">
+        <v>1</v>
+      </c>
+      <c r="BH22">
+        <v>1</v>
+      </c>
+      <c r="BI22">
         <v>2</v>
       </c>
-      <c r="BK21">
+      <c r="BK22">
         <v>2</v>
       </c>
-      <c r="BQ21">
+      <c r="BQ22">
         <v>2</v>
       </c>
-      <c r="BR21">
+      <c r="BR22">
         <v>3</v>
       </c>
-      <c r="BU21">
-        <v>1</v>
-      </c>
-      <c r="BV21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="BU22">
+        <v>1</v>
+      </c>
+      <c r="BV22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>391</v>
       </c>
-      <c r="BP22">
+      <c r="BP23">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+    <row r="24" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>15</v>
       </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="H23">
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="H24">
         <v>2</v>
       </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="AK23">
-        <v>1</v>
-      </c>
-      <c r="AL23">
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="AK24">
+        <v>1</v>
+      </c>
+      <c r="AL24">
         <v>4</v>
       </c>
-      <c r="AO23">
+      <c r="AO24">
         <v>2</v>
       </c>
-      <c r="AR23">
+      <c r="AR24">
         <v>3</v>
       </c>
-      <c r="AS23">
+      <c r="AS24">
         <v>2</v>
       </c>
-      <c r="AT23">
-        <v>1</v>
-      </c>
-      <c r="AY23">
-        <v>1</v>
-      </c>
-      <c r="BE23">
+      <c r="AT24">
+        <v>1</v>
+      </c>
+      <c r="AY24">
+        <v>1</v>
+      </c>
+      <c r="BE24">
         <v>2</v>
       </c>
-      <c r="BF23">
-        <v>1</v>
-      </c>
-      <c r="BI23">
+      <c r="BF24">
+        <v>1</v>
+      </c>
+      <c r="BI24">
         <v>2</v>
       </c>
-      <c r="BR23">
-        <v>1</v>
-      </c>
-      <c r="BS23">
-        <v>1</v>
-      </c>
-      <c r="BT23">
+      <c r="BR24">
+        <v>1</v>
+      </c>
+      <c r="BS24">
+        <v>1</v>
+      </c>
+      <c r="BT24">
         <v>3</v>
       </c>
-      <c r="BU23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="BU24">
+        <v>1</v>
+      </c>
+      <c r="BW24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>375</v>
       </c>
-      <c r="AW24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="AW25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>6</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>3</v>
       </c>
-      <c r="E25">
+      <c r="E26">
         <v>2</v>
       </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="L25">
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="L26">
         <v>2</v>
       </c>
-      <c r="M25">
+      <c r="M26">
         <v>2</v>
       </c>
-      <c r="N25">
+      <c r="N26">
         <v>6</v>
       </c>
-      <c r="O25">
-        <v>1</v>
-      </c>
-      <c r="Q25">
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
         <v>3</v>
       </c>
-      <c r="R25">
-        <v>1</v>
-      </c>
-      <c r="S25">
-        <v>1</v>
-      </c>
-      <c r="T25">
+      <c r="R26">
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <v>1</v>
+      </c>
+      <c r="T26">
         <v>3</v>
       </c>
-      <c r="U25">
+      <c r="U26">
         <v>3</v>
       </c>
-      <c r="V25">
+      <c r="V26">
         <v>6</v>
       </c>
-      <c r="W25">
+      <c r="W26">
         <v>2</v>
       </c>
-      <c r="X25">
+      <c r="X26">
         <v>3</v>
       </c>
-      <c r="Y25">
-        <v>1</v>
-      </c>
-      <c r="Z25">
+      <c r="Y26">
+        <v>1</v>
+      </c>
+      <c r="Z26">
         <v>3.5</v>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <v>3.5</v>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <v>3</v>
       </c>
-      <c r="AC25">
-        <v>1</v>
-      </c>
-      <c r="AE25">
+      <c r="AC26">
+        <v>1</v>
+      </c>
+      <c r="AE26">
         <v>10</v>
       </c>
-      <c r="AF25">
+      <c r="AF26">
         <v>3</v>
       </c>
-      <c r="AG25">
+      <c r="AG26">
         <v>3</v>
       </c>
-      <c r="AH25">
+      <c r="AH26">
         <v>2</v>
       </c>
-      <c r="AJ25">
+      <c r="AJ26">
         <v>3</v>
       </c>
-      <c r="AK25">
+      <c r="AK26">
         <v>3</v>
       </c>
-      <c r="AL25">
-        <v>5</v>
-      </c>
-      <c r="AN25">
-        <v>1</v>
-      </c>
-      <c r="AO25">
+      <c r="AL26">
+        <v>5</v>
+      </c>
+      <c r="AN26">
+        <v>1</v>
+      </c>
+      <c r="AO26">
         <v>6</v>
       </c>
-      <c r="AP25">
+      <c r="AP26">
         <v>4</v>
       </c>
-      <c r="AQ25">
+      <c r="AQ26">
         <v>3</v>
       </c>
-      <c r="AR25">
+      <c r="AR26">
         <v>4</v>
       </c>
-      <c r="AS25">
+      <c r="AS26">
         <v>2</v>
       </c>
-      <c r="AT25">
+      <c r="AT26">
         <v>4</v>
       </c>
-      <c r="AU25">
+      <c r="AU26">
         <v>4</v>
       </c>
-      <c r="AV25">
+      <c r="AV26">
         <v>6</v>
       </c>
-      <c r="AW25">
-        <v>1</v>
-      </c>
-      <c r="AY25">
+      <c r="AW26">
+        <v>1</v>
+      </c>
+      <c r="AY26">
         <v>4</v>
       </c>
-      <c r="AZ25">
-        <v>1</v>
-      </c>
-      <c r="BA25">
+      <c r="AZ26">
+        <v>1</v>
+      </c>
+      <c r="BA26">
         <v>3</v>
       </c>
-      <c r="BC25">
-        <v>5</v>
-      </c>
-      <c r="BD25">
+      <c r="BC26">
+        <v>5</v>
+      </c>
+      <c r="BD26">
         <v>2</v>
       </c>
-      <c r="BE25">
+      <c r="BE26">
         <v>3</v>
       </c>
-      <c r="BF25">
+      <c r="BF26">
         <v>3</v>
       </c>
-      <c r="BG25">
+      <c r="BG26">
         <v>3</v>
       </c>
-      <c r="BH25">
-        <v>1</v>
-      </c>
-      <c r="BI25">
-        <v>5</v>
-      </c>
-      <c r="BJ25">
-        <v>1</v>
-      </c>
-      <c r="BK25">
-        <v>1</v>
-      </c>
-      <c r="BL25">
+      <c r="BH26">
+        <v>1</v>
+      </c>
+      <c r="BI26">
+        <v>5</v>
+      </c>
+      <c r="BJ26">
+        <v>1</v>
+      </c>
+      <c r="BK26">
+        <v>1</v>
+      </c>
+      <c r="BL26">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="27" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>342</v>
       </c>
-      <c r="T26">
+      <c r="T27">
         <v>4</v>
       </c>
-      <c r="AH26">
-        <v>1</v>
-      </c>
-      <c r="AK26">
-        <v>1</v>
-      </c>
-      <c r="BQ26">
+      <c r="AH27">
+        <v>1</v>
+      </c>
+      <c r="AK27">
+        <v>1</v>
+      </c>
+      <c r="BQ27">
         <v>2</v>
       </c>
-      <c r="BV26">
+      <c r="BV27">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="28" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="29" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="29" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+    <row r="30" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>12</v>
       </c>
-      <c r="N29">
+      <c r="N30">
         <v>2</v>
       </c>
-      <c r="U29">
-        <v>1</v>
-      </c>
-      <c r="AI29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="AI30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>4</v>
       </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30">
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
         <v>3</v>
       </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
         <v>3</v>
       </c>
-      <c r="P30">
+      <c r="P31">
         <v>3</v>
       </c>
-      <c r="U30">
+      <c r="U31">
         <v>3</v>
       </c>
-      <c r="W30">
-        <v>1</v>
-      </c>
-      <c r="AD30">
-        <v>1</v>
-      </c>
-      <c r="AF30">
-        <v>1</v>
-      </c>
-      <c r="AH30">
-        <v>1</v>
-      </c>
-      <c r="AI30">
-        <v>1</v>
-      </c>
-      <c r="AJ30">
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="AD31">
+        <v>1</v>
+      </c>
+      <c r="AF31">
+        <v>1</v>
+      </c>
+      <c r="AH31">
+        <v>1</v>
+      </c>
+      <c r="AI31">
+        <v>1</v>
+      </c>
+      <c r="AJ31">
         <v>2</v>
       </c>
-      <c r="AO30">
+      <c r="AO31">
         <v>2</v>
       </c>
-      <c r="AP30">
+      <c r="AP31">
         <v>2</v>
       </c>
-      <c r="AQ30">
+      <c r="AQ31">
         <v>4</v>
       </c>
-      <c r="AR30">
+      <c r="AR31">
         <v>2</v>
       </c>
-      <c r="AT30">
-        <v>1</v>
-      </c>
-      <c r="AU30">
+      <c r="AT31">
+        <v>1</v>
+      </c>
+      <c r="AU31">
         <v>2</v>
       </c>
-      <c r="AV30">
-        <v>1</v>
-      </c>
-      <c r="AW30">
-        <v>1</v>
-      </c>
-      <c r="AX30">
-        <v>1</v>
-      </c>
-      <c r="AZ30">
+      <c r="AV31">
+        <v>1</v>
+      </c>
+      <c r="AW31">
+        <v>1</v>
+      </c>
+      <c r="AX31">
+        <v>1</v>
+      </c>
+      <c r="AZ31">
         <v>2</v>
       </c>
-      <c r="BA30">
+      <c r="BA31">
         <v>2</v>
       </c>
-      <c r="BB30">
-        <v>1</v>
-      </c>
-      <c r="BD30">
+      <c r="BB31">
+        <v>1</v>
+      </c>
+      <c r="BD31">
         <v>2</v>
       </c>
-      <c r="BE30">
+      <c r="BE31">
         <v>3</v>
       </c>
-      <c r="BF30">
-        <v>1</v>
-      </c>
-      <c r="BG30">
-        <v>1</v>
-      </c>
-      <c r="BJ30">
-        <v>1</v>
-      </c>
-      <c r="BK30">
-        <v>1</v>
-      </c>
-      <c r="BL30">
-        <v>1</v>
-      </c>
-      <c r="BM30">
+      <c r="BF31">
+        <v>1</v>
+      </c>
+      <c r="BG31">
+        <v>1</v>
+      </c>
+      <c r="BJ31">
+        <v>1</v>
+      </c>
+      <c r="BK31">
+        <v>1</v>
+      </c>
+      <c r="BL31">
+        <v>1</v>
+      </c>
+      <c r="BM31">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    <row r="32" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>361</v>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <v>2</v>
       </c>
-      <c r="AM31">
-        <v>1</v>
-      </c>
-      <c r="AU31">
-        <v>1</v>
-      </c>
-      <c r="BF31">
+      <c r="AM32">
+        <v>1</v>
+      </c>
+      <c r="AU32">
+        <v>1</v>
+      </c>
+      <c r="BF32">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+    <row r="33" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>389</v>
       </c>
-      <c r="BO32">
+      <c r="BO33">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-      <c r="F33">
+    <row r="34" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
         <v>2</v>
       </c>
-      <c r="I33">
+      <c r="I34">
         <v>2</v>
       </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
-      <c r="K33">
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
         <v>2</v>
       </c>
-      <c r="L33">
-        <v>1</v>
-      </c>
-      <c r="M33">
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
         <v>2</v>
       </c>
-      <c r="N33">
-        <v>1</v>
-      </c>
-      <c r="O33">
-        <v>1</v>
-      </c>
-      <c r="P33">
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="P34">
         <v>2</v>
       </c>
-      <c r="R33">
-        <v>1</v>
-      </c>
-      <c r="T33">
-        <v>1</v>
-      </c>
-      <c r="U33">
+      <c r="R34">
+        <v>1</v>
+      </c>
+      <c r="T34">
+        <v>1</v>
+      </c>
+      <c r="U34">
         <v>2</v>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <v>2</v>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <v>2</v>
       </c>
-      <c r="AD33">
-        <v>1</v>
-      </c>
-      <c r="AH33">
-        <v>1</v>
-      </c>
-      <c r="AJ33">
-        <v>1</v>
-      </c>
-      <c r="AN33">
+      <c r="AD34">
+        <v>1</v>
+      </c>
+      <c r="AH34">
+        <v>1</v>
+      </c>
+      <c r="AJ34">
+        <v>1</v>
+      </c>
+      <c r="AN34">
         <v>2</v>
       </c>
-      <c r="AO33">
-        <v>1</v>
-      </c>
-      <c r="AP33">
+      <c r="AO34">
+        <v>1</v>
+      </c>
+      <c r="AP34">
         <v>2</v>
       </c>
-      <c r="AQ33">
-        <v>1</v>
-      </c>
-      <c r="AS33">
+      <c r="AQ34">
+        <v>1</v>
+      </c>
+      <c r="AS34">
         <v>2</v>
       </c>
-      <c r="AW33">
-        <v>1</v>
-      </c>
-      <c r="AX33">
-        <v>1</v>
-      </c>
-      <c r="AY33">
+      <c r="AW34">
+        <v>1</v>
+      </c>
+      <c r="AX34">
+        <v>1</v>
+      </c>
+      <c r="AY34">
         <v>2</v>
       </c>
-      <c r="AZ33">
+      <c r="AZ34">
         <v>2</v>
       </c>
-      <c r="BA33">
-        <v>1</v>
-      </c>
-      <c r="BB33">
+      <c r="BA34">
+        <v>1</v>
+      </c>
+      <c r="BB34">
         <v>2</v>
       </c>
-      <c r="BC33">
+      <c r="BC34">
         <v>4</v>
       </c>
-      <c r="BD33">
-        <v>1</v>
-      </c>
-      <c r="BE33">
-        <v>1</v>
-      </c>
-      <c r="BG33">
+      <c r="BD34">
+        <v>1</v>
+      </c>
+      <c r="BE34">
+        <v>1</v>
+      </c>
+      <c r="BG34">
         <v>2</v>
       </c>
-      <c r="BH33">
+      <c r="BH34">
         <v>3</v>
       </c>
-      <c r="BJ33">
-        <v>1</v>
-      </c>
-      <c r="BM33">
+      <c r="BJ34">
+        <v>1</v>
+      </c>
+      <c r="BM34">
         <v>3</v>
       </c>
-      <c r="BN33">
-        <v>1</v>
-      </c>
-      <c r="BP33">
-        <v>1</v>
-      </c>
-      <c r="BR33">
+      <c r="BN34">
+        <v>1</v>
+      </c>
+      <c r="BP34">
+        <v>1</v>
+      </c>
+      <c r="BR34">
         <v>3</v>
       </c>
-      <c r="BV33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="BV34">
+        <v>1</v>
+      </c>
+      <c r="BW34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>351</v>
       </c>
-      <c r="Z34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="Z35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>9</v>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="G35">
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="G36">
         <v>2</v>
       </c>
-      <c r="H35">
+      <c r="H36">
         <v>2</v>
       </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="K35">
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
         <v>2</v>
       </c>
-      <c r="L35">
-        <v>5</v>
-      </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
-      <c r="O35">
+      <c r="L36">
+        <v>5</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="O36">
         <v>4</v>
       </c>
-      <c r="P35">
-        <v>1</v>
-      </c>
-      <c r="Q35">
+      <c r="P36">
+        <v>1</v>
+      </c>
+      <c r="Q36">
         <v>2</v>
       </c>
-      <c r="T35">
+      <c r="T36">
         <v>6</v>
       </c>
-      <c r="X35">
+      <c r="X36">
         <v>2</v>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <v>2</v>
       </c>
-      <c r="Z35">
-        <v>1</v>
-      </c>
-      <c r="AA35">
-        <v>1</v>
-      </c>
-      <c r="AB35">
-        <v>1</v>
-      </c>
-      <c r="AC35">
+      <c r="Z36">
+        <v>1</v>
+      </c>
+      <c r="AA36">
+        <v>1</v>
+      </c>
+      <c r="AB36">
+        <v>1</v>
+      </c>
+      <c r="AC36">
         <v>3</v>
       </c>
-      <c r="AF35">
+      <c r="AF36">
         <v>4</v>
       </c>
-      <c r="AI35">
-        <v>1</v>
-      </c>
-      <c r="AL35">
-        <v>1</v>
-      </c>
-      <c r="AN35">
-        <v>1</v>
-      </c>
-      <c r="AR35">
+      <c r="AI36">
+        <v>1</v>
+      </c>
+      <c r="AL36">
+        <v>1</v>
+      </c>
+      <c r="AN36">
+        <v>1</v>
+      </c>
+      <c r="AR36">
         <v>2</v>
       </c>
-      <c r="AS35">
+      <c r="AS36">
         <v>3</v>
       </c>
-      <c r="AT35">
-        <v>1</v>
-      </c>
-      <c r="AW35">
+      <c r="AT36">
+        <v>1</v>
+      </c>
+      <c r="AW36">
         <v>2</v>
       </c>
-      <c r="AX35">
-        <v>5</v>
-      </c>
-      <c r="AY35">
+      <c r="AX36">
+        <v>5</v>
+      </c>
+      <c r="AY36">
         <v>3</v>
       </c>
-      <c r="AZ35">
-        <v>1</v>
-      </c>
-      <c r="BA35">
+      <c r="AZ36">
+        <v>1</v>
+      </c>
+      <c r="BA36">
         <v>3</v>
       </c>
-      <c r="BB35">
+      <c r="BB36">
         <v>2</v>
       </c>
-      <c r="BD35">
+      <c r="BD36">
         <v>3</v>
       </c>
-      <c r="BF35">
+      <c r="BF36">
         <v>3</v>
       </c>
-      <c r="BG35">
+      <c r="BG36">
         <v>4</v>
       </c>
-      <c r="BH35">
+      <c r="BH36">
         <v>3</v>
       </c>
-      <c r="BI35">
+      <c r="BI36">
         <v>2</v>
       </c>
-      <c r="BJ35">
-        <v>1</v>
-      </c>
-      <c r="BL35">
-        <v>1</v>
-      </c>
-      <c r="BM35">
+      <c r="BJ36">
+        <v>1</v>
+      </c>
+      <c r="BL36">
+        <v>1</v>
+      </c>
+      <c r="BM36">
         <v>2</v>
       </c>
-      <c r="BN35">
-        <v>1</v>
-      </c>
-      <c r="BP35">
-        <v>1</v>
-      </c>
-      <c r="BQ35">
+      <c r="BN36">
+        <v>1</v>
+      </c>
+      <c r="BP36">
+        <v>1</v>
+      </c>
+      <c r="BQ36">
         <v>2</v>
       </c>
-      <c r="BR35">
+      <c r="BR36">
         <v>3</v>
       </c>
-      <c r="BS35">
+      <c r="BS36">
         <v>2</v>
       </c>
-      <c r="BV35">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="BV36">
+        <v>5</v>
+      </c>
+      <c r="BW36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>394</v>
+      </c>
+      <c r="BW37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>381</v>
       </c>
-      <c r="BG36">
+      <c r="BG38">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+    <row r="39" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>20</v>
       </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="F37">
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="F39">
         <v>2</v>
       </c>
-      <c r="G37">
+      <c r="G39">
         <v>2</v>
       </c>
-      <c r="H37">
+      <c r="H39">
         <v>4</v>
       </c>
-      <c r="J37">
+      <c r="J39">
         <v>2</v>
       </c>
-      <c r="K37">
+      <c r="K39">
         <v>2</v>
       </c>
-      <c r="L37">
-        <v>1</v>
-      </c>
-      <c r="M37">
-        <v>1</v>
-      </c>
-      <c r="P37">
-        <v>1</v>
-      </c>
-      <c r="Q37">
-        <v>1</v>
-      </c>
-      <c r="R37">
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="P39">
+        <v>1</v>
+      </c>
+      <c r="Q39">
+        <v>1</v>
+      </c>
+      <c r="R39">
         <v>3</v>
       </c>
-      <c r="S37">
+      <c r="S39">
         <v>2</v>
       </c>
-      <c r="T37">
+      <c r="T39">
         <v>2</v>
       </c>
-      <c r="U37">
+      <c r="U39">
         <v>2</v>
       </c>
-      <c r="W37">
+      <c r="W39">
         <v>3</v>
       </c>
-      <c r="X37">
+      <c r="X39">
         <v>3</v>
       </c>
-      <c r="Y37">
+      <c r="Y39">
         <v>2</v>
       </c>
-      <c r="AA37">
+      <c r="AA39">
         <v>2</v>
       </c>
-      <c r="AB37">
+      <c r="AB39">
         <v>2</v>
       </c>
-      <c r="AC37">
+      <c r="AC39">
         <v>2</v>
       </c>
-      <c r="AE37">
+      <c r="AE39">
         <v>2</v>
       </c>
-      <c r="AF37">
-        <v>1</v>
-      </c>
-      <c r="AG37">
+      <c r="AF39">
+        <v>1</v>
+      </c>
+      <c r="AG39">
         <v>2</v>
       </c>
-      <c r="AJ37">
+      <c r="AJ39">
         <v>4</v>
       </c>
-      <c r="AK37">
+      <c r="AK39">
         <v>2</v>
       </c>
-      <c r="AM37">
-        <v>1</v>
-      </c>
-      <c r="AN37">
-        <v>1</v>
-      </c>
-      <c r="AO37">
-        <v>1</v>
-      </c>
-      <c r="AP37">
-        <v>1</v>
-      </c>
-      <c r="AU37">
-        <v>1</v>
-      </c>
-      <c r="AV37">
-        <v>1</v>
-      </c>
-      <c r="AW37">
+      <c r="AM39">
+        <v>1</v>
+      </c>
+      <c r="AN39">
+        <v>1</v>
+      </c>
+      <c r="AO39">
+        <v>1</v>
+      </c>
+      <c r="AP39">
+        <v>1</v>
+      </c>
+      <c r="AU39">
+        <v>1</v>
+      </c>
+      <c r="AV39">
+        <v>1</v>
+      </c>
+      <c r="AW39">
         <v>2</v>
       </c>
-      <c r="BA37">
-        <v>1</v>
-      </c>
-      <c r="BH37">
+      <c r="BA39">
+        <v>1</v>
+      </c>
+      <c r="BH39">
         <v>2</v>
       </c>
-      <c r="BJ37">
+      <c r="BJ39">
         <v>2</v>
       </c>
-      <c r="BK37">
+      <c r="BK39">
         <v>3</v>
       </c>
-      <c r="BP37">
+      <c r="BP39">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+    <row r="40" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="41" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>80</v>
       </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="F41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>61</v>
       </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>374</v>
       </c>
-      <c r="AW40">
+      <c r="AW43">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+    <row r="44" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>19</v>
       </c>
-      <c r="B41">
+      <c r="B44">
         <v>2</v>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="F41">
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="F44">
         <v>4</v>
       </c>
-      <c r="G41">
+      <c r="G44">
         <v>3</v>
       </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="M41">
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="M44">
         <v>2</v>
       </c>
-      <c r="N41">
+      <c r="N44">
         <v>3</v>
       </c>
-      <c r="T41">
-        <v>1</v>
-      </c>
-      <c r="X41">
-        <v>1</v>
-      </c>
-      <c r="AA41">
+      <c r="T44">
+        <v>1</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="AA44">
         <v>2</v>
       </c>
-      <c r="AB41">
+      <c r="AB44">
         <v>2</v>
       </c>
-      <c r="AC41">
-        <v>1</v>
-      </c>
-      <c r="AD41">
+      <c r="AC44">
+        <v>1</v>
+      </c>
+      <c r="AD44">
         <v>2</v>
       </c>
-      <c r="AE41">
-        <v>1</v>
-      </c>
-      <c r="AG41">
-        <v>1</v>
-      </c>
-      <c r="AH41">
+      <c r="AE44">
+        <v>1</v>
+      </c>
+      <c r="AG44">
+        <v>1</v>
+      </c>
+      <c r="AH44">
         <v>2</v>
       </c>
-      <c r="AJ41">
-        <v>1</v>
-      </c>
-      <c r="AM41">
+      <c r="AJ44">
+        <v>1</v>
+      </c>
+      <c r="AM44">
         <v>4</v>
       </c>
-      <c r="AN41">
-        <v>1</v>
-      </c>
-      <c r="AP41">
-        <v>1</v>
-      </c>
-      <c r="AR41">
-        <v>1</v>
-      </c>
-      <c r="AS41">
-        <v>1</v>
-      </c>
-      <c r="AT41">
-        <v>1</v>
-      </c>
-      <c r="AV41">
-        <v>1</v>
-      </c>
-      <c r="AZ41">
+      <c r="AN44">
+        <v>1</v>
+      </c>
+      <c r="AP44">
+        <v>1</v>
+      </c>
+      <c r="AR44">
+        <v>1</v>
+      </c>
+      <c r="AS44">
+        <v>1</v>
+      </c>
+      <c r="AT44">
+        <v>1</v>
+      </c>
+      <c r="AV44">
+        <v>1</v>
+      </c>
+      <c r="AZ44">
         <v>2</v>
       </c>
-      <c r="BA41">
-        <v>1</v>
-      </c>
-      <c r="BC41">
+      <c r="BA44">
+        <v>1</v>
+      </c>
+      <c r="BC44">
         <v>3</v>
       </c>
-      <c r="BD41">
-        <v>1</v>
-      </c>
-      <c r="BI41">
-        <v>1</v>
-      </c>
-      <c r="BJ41">
-        <v>1</v>
-      </c>
-      <c r="BK41">
+      <c r="BD44">
+        <v>1</v>
+      </c>
+      <c r="BI44">
+        <v>1</v>
+      </c>
+      <c r="BJ44">
+        <v>1</v>
+      </c>
+      <c r="BK44">
         <v>3</v>
       </c>
-      <c r="BL41">
+      <c r="BL44">
         <v>2</v>
       </c>
-      <c r="BM41">
-        <v>5</v>
-      </c>
-      <c r="BO41">
-        <v>1</v>
-      </c>
-      <c r="BP41">
+      <c r="BM44">
+        <v>5</v>
+      </c>
+      <c r="BO44">
+        <v>1</v>
+      </c>
+      <c r="BP44">
         <v>3</v>
       </c>
-      <c r="BQ41">
+      <c r="BQ44">
         <v>3</v>
       </c>
-      <c r="BS41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="BS44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>43</v>
       </c>
-      <c r="AQ42">
+      <c r="AQ45">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+    <row r="46" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>68</v>
       </c>
-      <c r="E43">
-        <v>1</v>
-      </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-      <c r="N43">
-        <v>1</v>
-      </c>
-      <c r="W43">
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+      <c r="W46">
         <v>2</v>
       </c>
-      <c r="AQ43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="AQ46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>53</v>
       </c>
-      <c r="N44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="N47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>368</v>
       </c>
-      <c r="AM45">
-        <v>5</v>
-      </c>
-      <c r="BB45">
+      <c r="AM48">
+        <v>5</v>
+      </c>
+      <c r="BB48">
         <v>9</v>
       </c>
-      <c r="BN45">
+      <c r="BN48">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+    <row r="49" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>345</v>
       </c>
-      <c r="U46">
-        <v>1</v>
-      </c>
-      <c r="BR46">
-        <v>1</v>
-      </c>
-      <c r="BS46">
-        <v>1</v>
-      </c>
-      <c r="BT46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="U49">
+        <v>1</v>
+      </c>
+      <c r="BR49">
+        <v>1</v>
+      </c>
+      <c r="BS49">
+        <v>1</v>
+      </c>
+      <c r="BT49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>343</v>
       </c>
-      <c r="AN47">
-        <v>1</v>
-      </c>
-      <c r="BR47">
-        <v>1</v>
-      </c>
-      <c r="BS47">
-        <v>1</v>
-      </c>
-      <c r="BT47">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>344</v>
-      </c>
-      <c r="X48">
-        <v>1</v>
-      </c>
-      <c r="Y48">
-        <v>2</v>
-      </c>
-      <c r="AF48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49">
-        <v>2</v>
-      </c>
-      <c r="C49">
-        <v>3</v>
-      </c>
-      <c r="F49">
-        <v>2</v>
-      </c>
-      <c r="I49">
-        <v>2</v>
-      </c>
-      <c r="J49">
-        <v>2</v>
-      </c>
-      <c r="K49">
-        <v>1</v>
-      </c>
-      <c r="L49">
-        <v>1</v>
-      </c>
-      <c r="M49">
-        <v>1</v>
-      </c>
-      <c r="O49">
-        <v>2</v>
-      </c>
-      <c r="R49">
-        <v>3</v>
-      </c>
-      <c r="S49">
-        <v>1</v>
-      </c>
-      <c r="T49">
-        <v>1</v>
-      </c>
-      <c r="V49">
-        <v>1</v>
-      </c>
-      <c r="W49">
-        <v>3</v>
-      </c>
-      <c r="X49">
-        <v>1</v>
-      </c>
-      <c r="Y49">
-        <v>1</v>
-      </c>
-      <c r="Z49">
-        <v>1.5</v>
-      </c>
-      <c r="AC49">
-        <v>1</v>
-      </c>
-      <c r="AD49">
-        <v>2</v>
-      </c>
-      <c r="AE49">
-        <v>1</v>
-      </c>
-      <c r="AF49">
-        <v>2</v>
-      </c>
-      <c r="AH49">
-        <v>2</v>
-      </c>
-      <c r="AL49">
-        <v>3</v>
-      </c>
-      <c r="AP49">
-        <v>2</v>
-      </c>
-      <c r="AQ49">
-        <v>4</v>
-      </c>
-      <c r="AR49">
-        <v>3</v>
-      </c>
-      <c r="AS49">
-        <v>0.5</v>
-      </c>
-      <c r="AU49">
-        <v>2</v>
-      </c>
-      <c r="AV49">
-        <v>1</v>
-      </c>
-      <c r="BC49">
-        <v>1</v>
-      </c>
-      <c r="BD49">
-        <v>1</v>
-      </c>
-      <c r="BE49">
-        <v>7</v>
-      </c>
-      <c r="BH49">
-        <v>1</v>
-      </c>
-      <c r="BI49">
-        <v>1</v>
-      </c>
-      <c r="BJ49">
-        <v>3</v>
-      </c>
-      <c r="BK49">
-        <v>3</v>
-      </c>
-      <c r="BL49">
-        <v>1</v>
-      </c>
-      <c r="BM49">
-        <v>1</v>
-      </c>
-      <c r="BN49">
-        <v>4</v>
-      </c>
-      <c r="BP49">
-        <v>1</v>
-      </c>
-      <c r="BQ49">
-        <v>3</v>
-      </c>
-      <c r="BR49">
-        <v>1</v>
-      </c>
-      <c r="BT49">
-        <v>1</v>
-      </c>
-      <c r="BV49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="O50">
-        <v>3</v>
-      </c>
-      <c r="P50">
-        <v>1</v>
-      </c>
-      <c r="Q50">
-        <v>2</v>
-      </c>
-      <c r="AM50">
-        <v>1</v>
-      </c>
       <c r="AN50">
         <v>1</v>
       </c>
-      <c r="AP50">
-        <v>1</v>
-      </c>
-      <c r="AS50">
-        <v>1</v>
-      </c>
-      <c r="AV50">
-        <v>1</v>
-      </c>
-      <c r="AX50">
-        <v>5</v>
-      </c>
-      <c r="AY50">
-        <v>1</v>
-      </c>
-      <c r="BA50">
-        <v>2</v>
-      </c>
-      <c r="BB50">
-        <v>4</v>
-      </c>
-      <c r="BE50">
-        <v>3</v>
-      </c>
-      <c r="BF50">
-        <v>2</v>
-      </c>
-      <c r="BH50">
-        <v>3</v>
-      </c>
-      <c r="BK50">
+      <c r="BR50">
+        <v>1</v>
+      </c>
+      <c r="BS50">
         <v>1</v>
       </c>
       <c r="BT50">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>344</v>
+      </c>
+      <c r="X51">
+        <v>1</v>
+      </c>
+      <c r="Y51">
+        <v>2</v>
+      </c>
+      <c r="AF51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="I52">
+        <v>2</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+      <c r="O52">
+        <v>2</v>
+      </c>
+      <c r="R52">
+        <v>3</v>
+      </c>
+      <c r="S52">
+        <v>1</v>
+      </c>
+      <c r="T52">
+        <v>1</v>
+      </c>
+      <c r="V52">
+        <v>1</v>
+      </c>
+      <c r="W52">
+        <v>3</v>
+      </c>
+      <c r="X52">
+        <v>1</v>
+      </c>
+      <c r="Y52">
+        <v>1</v>
+      </c>
+      <c r="Z52">
+        <v>1.5</v>
+      </c>
+      <c r="AC52">
+        <v>1</v>
+      </c>
+      <c r="AD52">
+        <v>2</v>
+      </c>
+      <c r="AE52">
+        <v>1</v>
+      </c>
+      <c r="AF52">
+        <v>2</v>
+      </c>
+      <c r="AH52">
+        <v>2</v>
+      </c>
+      <c r="AL52">
+        <v>3</v>
+      </c>
+      <c r="AP52">
+        <v>2</v>
+      </c>
+      <c r="AQ52">
+        <v>4</v>
+      </c>
+      <c r="AR52">
+        <v>3</v>
+      </c>
+      <c r="AS52">
+        <v>0.5</v>
+      </c>
+      <c r="AU52">
+        <v>2</v>
+      </c>
+      <c r="AV52">
+        <v>1</v>
+      </c>
+      <c r="BC52">
+        <v>1</v>
+      </c>
+      <c r="BD52">
+        <v>1</v>
+      </c>
+      <c r="BE52">
+        <v>7</v>
+      </c>
+      <c r="BH52">
+        <v>1</v>
+      </c>
+      <c r="BI52">
+        <v>1</v>
+      </c>
+      <c r="BJ52">
+        <v>3</v>
+      </c>
+      <c r="BK52">
+        <v>3</v>
+      </c>
+      <c r="BL52">
+        <v>1</v>
+      </c>
+      <c r="BM52">
+        <v>1</v>
+      </c>
+      <c r="BN52">
+        <v>4</v>
+      </c>
+      <c r="BP52">
+        <v>1</v>
+      </c>
+      <c r="BQ52">
+        <v>3</v>
+      </c>
+      <c r="BR52">
+        <v>1</v>
+      </c>
+      <c r="BT52">
+        <v>1</v>
+      </c>
+      <c r="BV52">
+        <v>1</v>
+      </c>
+      <c r="BW52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <v>3</v>
+      </c>
+      <c r="P53">
+        <v>1</v>
+      </c>
+      <c r="Q53">
+        <v>2</v>
+      </c>
+      <c r="AM53">
+        <v>1</v>
+      </c>
+      <c r="AN53">
+        <v>1</v>
+      </c>
+      <c r="AP53">
+        <v>1</v>
+      </c>
+      <c r="AS53">
+        <v>1</v>
+      </c>
+      <c r="AV53">
+        <v>1</v>
+      </c>
+      <c r="AX53">
+        <v>5</v>
+      </c>
+      <c r="AY53">
+        <v>1</v>
+      </c>
+      <c r="BA53">
+        <v>2</v>
+      </c>
+      <c r="BB53">
+        <v>4</v>
+      </c>
+      <c r="BE53">
+        <v>3</v>
+      </c>
+      <c r="BF53">
+        <v>2</v>
+      </c>
+      <c r="BH53">
+        <v>3</v>
+      </c>
+      <c r="BK53">
+        <v>1</v>
+      </c>
+      <c r="BT53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="52" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+    <row r="55" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>3</v>
       </c>
-      <c r="F52">
+      <c r="F55">
         <v>3</v>
       </c>
-      <c r="L52">
-        <v>1</v>
-      </c>
-      <c r="S52">
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="S55">
         <v>3</v>
       </c>
-      <c r="AH52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="AH55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="54" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+    <row r="57" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>56</v>
       </c>
-      <c r="C54">
+      <c r="C57">
         <v>3</v>
       </c>
-      <c r="E54">
+      <c r="E57">
         <v>2</v>
       </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-      <c r="G54">
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
         <v>2</v>
       </c>
-      <c r="I54">
-        <v>1</v>
-      </c>
-      <c r="J54">
-        <v>1</v>
-      </c>
-      <c r="K54">
-        <v>1</v>
-      </c>
-      <c r="L54">
-        <v>1</v>
-      </c>
-      <c r="M54">
-        <v>1</v>
-      </c>
-      <c r="P54">
-        <v>1</v>
-      </c>
-      <c r="R54">
-        <v>1</v>
-      </c>
-      <c r="S54">
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57">
+        <v>1</v>
+      </c>
+      <c r="P57">
+        <v>1</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
+      </c>
+      <c r="S57">
         <v>4</v>
       </c>
-      <c r="T54">
-        <v>1</v>
-      </c>
-      <c r="V54">
-        <v>1</v>
-      </c>
-      <c r="W54">
+      <c r="T57">
+        <v>1</v>
+      </c>
+      <c r="V57">
+        <v>1</v>
+      </c>
+      <c r="W57">
         <v>2</v>
       </c>
-      <c r="Z54">
+      <c r="Z57">
         <v>2</v>
       </c>
-      <c r="AA54">
-        <v>1</v>
-      </c>
-      <c r="AB54">
+      <c r="AA57">
+        <v>1</v>
+      </c>
+      <c r="AB57">
         <v>4</v>
       </c>
-      <c r="AC54">
-        <v>1</v>
-      </c>
-      <c r="AD54">
-        <v>1</v>
-      </c>
-      <c r="AX54">
-        <v>1</v>
-      </c>
-      <c r="AY54">
-        <v>1</v>
-      </c>
-      <c r="AZ54">
+      <c r="AC57">
+        <v>1</v>
+      </c>
+      <c r="AD57">
+        <v>1</v>
+      </c>
+      <c r="AX57">
+        <v>1</v>
+      </c>
+      <c r="AY57">
+        <v>1</v>
+      </c>
+      <c r="AZ57">
         <v>2</v>
       </c>
-      <c r="BD54">
-        <v>1</v>
-      </c>
-      <c r="BF54">
-        <v>1</v>
-      </c>
-      <c r="BH54">
-        <v>1</v>
-      </c>
-      <c r="BI54">
-        <v>1</v>
-      </c>
-      <c r="BJ54">
+      <c r="BD57">
+        <v>1</v>
+      </c>
+      <c r="BF57">
+        <v>1</v>
+      </c>
+      <c r="BH57">
+        <v>1</v>
+      </c>
+      <c r="BI57">
+        <v>1</v>
+      </c>
+      <c r="BJ57">
         <v>2</v>
       </c>
-      <c r="BK54">
-        <v>1</v>
-      </c>
-      <c r="BL54">
+      <c r="BK57">
+        <v>1</v>
+      </c>
+      <c r="BL57">
         <v>2</v>
       </c>
-      <c r="BM54">
+      <c r="BM57">
         <v>2</v>
       </c>
-      <c r="BN54">
+      <c r="BN57">
         <v>2</v>
       </c>
-      <c r="BO54">
-        <v>1</v>
-      </c>
-      <c r="BP54">
-        <v>1</v>
-      </c>
-      <c r="BR54">
-        <v>1</v>
-      </c>
-      <c r="BS54">
+      <c r="BO57">
+        <v>1</v>
+      </c>
+      <c r="BP57">
+        <v>1</v>
+      </c>
+      <c r="BR57">
+        <v>1</v>
+      </c>
+      <c r="BS57">
         <v>2</v>
       </c>
-      <c r="BU54">
+      <c r="BU57">
         <v>2</v>
       </c>
-      <c r="BV54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="BV57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>369</v>
       </c>
-      <c r="AN55">
+      <c r="AN58">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+    <row r="59" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>387</v>
       </c>
-      <c r="BN56">
+      <c r="BN59">
         <v>3</v>
       </c>
-      <c r="BO56">
+      <c r="BO59">
         <v>2</v>
       </c>
-      <c r="BQ56">
+      <c r="BQ59">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+    <row r="60" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>60</v>
       </c>
-      <c r="B57">
+      <c r="B60">
         <v>2</v>
       </c>
-      <c r="BF57">
-        <v>1</v>
-      </c>
-      <c r="BT57">
+      <c r="BF60">
+        <v>1</v>
+      </c>
+      <c r="BT60">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+    <row r="61" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>340</v>
       </c>
-      <c r="Q58">
-        <v>1</v>
-      </c>
-      <c r="U58">
-        <v>1</v>
-      </c>
-      <c r="W58">
-        <v>1</v>
-      </c>
-      <c r="X58">
+      <c r="Q61">
+        <v>1</v>
+      </c>
+      <c r="U61">
+        <v>1</v>
+      </c>
+      <c r="W61">
+        <v>1</v>
+      </c>
+      <c r="X61">
         <v>3</v>
       </c>
-      <c r="Y58">
-        <v>1</v>
-      </c>
-      <c r="Z58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+      <c r="Y61">
+        <v>1</v>
+      </c>
+      <c r="Z61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="60" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+    <row r="63" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+    <row r="64" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>55</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61">
-        <v>1</v>
-      </c>
-      <c r="F61">
-        <v>3</v>
-      </c>
-      <c r="G61">
-        <v>2</v>
-      </c>
-      <c r="H61">
-        <v>3</v>
-      </c>
-      <c r="J61">
-        <v>1</v>
-      </c>
-      <c r="K61">
-        <v>1</v>
-      </c>
-      <c r="M61">
-        <v>3</v>
-      </c>
-      <c r="N61">
-        <v>4</v>
-      </c>
-      <c r="X61">
-        <v>6</v>
-      </c>
-      <c r="Y61">
-        <v>5</v>
-      </c>
-      <c r="Z61">
-        <v>1</v>
-      </c>
-      <c r="AD61">
-        <v>2</v>
-      </c>
-      <c r="AG61">
-        <v>3</v>
-      </c>
-      <c r="AJ61">
-        <v>2</v>
-      </c>
-      <c r="AM61">
-        <v>2</v>
-      </c>
-      <c r="AO61">
-        <v>3</v>
-      </c>
-      <c r="AQ61">
-        <v>2</v>
-      </c>
-      <c r="AT61">
-        <v>1</v>
-      </c>
-      <c r="AU61">
-        <v>4</v>
-      </c>
-      <c r="AV61">
-        <v>2</v>
-      </c>
-      <c r="AX61">
-        <v>1</v>
-      </c>
-      <c r="AY61">
-        <v>2</v>
-      </c>
-      <c r="AZ61">
-        <v>1</v>
-      </c>
-      <c r="BA61">
-        <v>4</v>
-      </c>
-      <c r="BB61">
-        <v>2</v>
-      </c>
-      <c r="BH61">
-        <v>1</v>
-      </c>
-      <c r="BR61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="63" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>81</v>
-      </c>
-      <c r="G63">
-        <v>3</v>
-      </c>
-      <c r="K63">
-        <v>1</v>
-      </c>
-      <c r="BG63">
-        <v>2</v>
-      </c>
-      <c r="BN63">
-        <v>4</v>
-      </c>
-      <c r="BP63">
-        <v>1</v>
-      </c>
-      <c r="BR63">
-        <v>2</v>
-      </c>
-      <c r="BS63">
-        <v>3</v>
-      </c>
-      <c r="BU63">
-        <v>3</v>
-      </c>
-      <c r="BV63">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>63</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
       <c r="D64">
         <v>1</v>
       </c>
-      <c r="AF64">
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64">
         <v>2</v>
       </c>
+      <c r="H64">
+        <v>3</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>3</v>
+      </c>
+      <c r="N64">
+        <v>4</v>
+      </c>
+      <c r="X64">
+        <v>6</v>
+      </c>
+      <c r="Y64">
+        <v>5</v>
+      </c>
+      <c r="Z64">
+        <v>1</v>
+      </c>
+      <c r="AD64">
+        <v>2</v>
+      </c>
+      <c r="AG64">
+        <v>3</v>
+      </c>
+      <c r="AJ64">
+        <v>2</v>
+      </c>
+      <c r="AM64">
+        <v>2</v>
+      </c>
+      <c r="AO64">
+        <v>3</v>
+      </c>
       <c r="AQ64">
+        <v>2</v>
+      </c>
+      <c r="AT64">
+        <v>1</v>
+      </c>
+      <c r="AU64">
+        <v>4</v>
+      </c>
+      <c r="AV64">
+        <v>2</v>
+      </c>
+      <c r="AX64">
+        <v>1</v>
+      </c>
+      <c r="AY64">
+        <v>2</v>
+      </c>
+      <c r="AZ64">
+        <v>1</v>
+      </c>
+      <c r="BA64">
+        <v>4</v>
+      </c>
+      <c r="BB64">
+        <v>2</v>
+      </c>
+      <c r="BH64">
+        <v>1</v>
+      </c>
+      <c r="BR64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>81</v>
+      </c>
+      <c r="G66">
         <v>3</v>
       </c>
-      <c r="BF64">
-        <v>1</v>
-      </c>
-      <c r="BM64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="BG66">
+        <v>2</v>
+      </c>
+      <c r="BN66">
+        <v>4</v>
+      </c>
+      <c r="BP66">
+        <v>1</v>
+      </c>
+      <c r="BR66">
+        <v>2</v>
+      </c>
+      <c r="BS66">
+        <v>3</v>
+      </c>
+      <c r="BU66">
+        <v>3</v>
+      </c>
+      <c r="BV66">
+        <v>2</v>
+      </c>
+      <c r="BW66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>63</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="AF67">
+        <v>2</v>
+      </c>
+      <c r="AQ67">
+        <v>3</v>
+      </c>
+      <c r="BF67">
+        <v>1</v>
+      </c>
+      <c r="BM67">
+        <v>1</v>
+      </c>
+      <c r="BW67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="66" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+    <row r="69" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>22</v>
       </c>
-      <c r="Y66">
-        <v>1</v>
-      </c>
-      <c r="AB66">
+      <c r="Y69">
+        <v>1</v>
+      </c>
+      <c r="AB69">
         <v>2</v>
       </c>
-      <c r="AD66">
+      <c r="AD69">
         <v>3</v>
       </c>
-      <c r="AI66">
-        <v>1</v>
-      </c>
-      <c r="AR66">
+      <c r="AI69">
+        <v>1</v>
+      </c>
+      <c r="AR69">
         <v>4</v>
       </c>
-      <c r="AV66">
+      <c r="AV69">
         <v>3</v>
       </c>
-      <c r="BA66">
+      <c r="BA69">
         <v>2</v>
       </c>
-      <c r="BB66">
-        <v>5</v>
-      </c>
-      <c r="BE66">
+      <c r="BB69">
+        <v>5</v>
+      </c>
+      <c r="BE69">
         <v>6</v>
       </c>
-      <c r="BS66">
-        <v>1</v>
-      </c>
-      <c r="BT66">
-        <v>1</v>
-      </c>
-      <c r="BU66">
+      <c r="BS69">
+        <v>1</v>
+      </c>
+      <c r="BT69">
+        <v>1</v>
+      </c>
+      <c r="BU69">
         <v>2</v>
       </c>
-      <c r="BV66">
+      <c r="BV69">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+    <row r="70" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>376</v>
       </c>
-      <c r="AU67">
-        <v>1</v>
-      </c>
-      <c r="AV67">
-        <v>1</v>
-      </c>
-      <c r="AW67">
+      <c r="AU70">
+        <v>1</v>
+      </c>
+      <c r="AV70">
+        <v>1</v>
+      </c>
+      <c r="AW70">
         <v>3</v>
       </c>
-      <c r="AX67">
-        <v>1</v>
-      </c>
-      <c r="AZ67">
-        <v>1</v>
-      </c>
-      <c r="BC67">
+      <c r="AX70">
+        <v>1</v>
+      </c>
+      <c r="AZ70">
+        <v>1</v>
+      </c>
+      <c r="BC70">
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+    <row r="71" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>44</v>
       </c>
-      <c r="N68">
+      <c r="N71">
         <v>3</v>
       </c>
-      <c r="S68">
+      <c r="S71">
         <v>2</v>
       </c>
-      <c r="AG68">
+      <c r="AG71">
         <v>2</v>
       </c>
-      <c r="AI68">
-        <v>1</v>
-      </c>
-      <c r="AP68">
+      <c r="AI71">
+        <v>1</v>
+      </c>
+      <c r="AP71">
         <v>2</v>
       </c>
-      <c r="AQ68">
-        <v>1</v>
-      </c>
-      <c r="AR68">
+      <c r="AQ71">
+        <v>1</v>
+      </c>
+      <c r="AR71">
         <v>3</v>
       </c>
-      <c r="AW68">
-        <v>1</v>
-      </c>
-      <c r="BA68">
-        <v>1</v>
-      </c>
-      <c r="BE68">
-        <v>1</v>
-      </c>
-      <c r="BI68">
+      <c r="AW71">
+        <v>1</v>
+      </c>
+      <c r="BA71">
+        <v>1</v>
+      </c>
+      <c r="BE71">
+        <v>1</v>
+      </c>
+      <c r="BI71">
         <v>2</v>
       </c>
-      <c r="BL68">
+      <c r="BL71">
         <v>2</v>
       </c>
-      <c r="BN68">
+      <c r="BN71">
         <v>2</v>
       </c>
-      <c r="BO68">
-        <v>1</v>
-      </c>
-      <c r="BP68">
-        <v>1</v>
-      </c>
-      <c r="BR68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="BO71">
+        <v>1</v>
+      </c>
+      <c r="BP71">
+        <v>1</v>
+      </c>
+      <c r="BR71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>379</v>
       </c>
-      <c r="BF69">
-        <v>1</v>
-      </c>
-      <c r="BG69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+      <c r="BF72">
+        <v>1</v>
+      </c>
+      <c r="BG72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>8</v>
       </c>
-      <c r="B70">
-        <v>1</v>
-      </c>
-      <c r="H70">
-        <v>1</v>
-      </c>
-      <c r="J70">
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="J73">
         <v>2</v>
       </c>
-      <c r="Q70">
+      <c r="Q73">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+    <row r="74" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="72" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+    <row r="75" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>82</v>
       </c>
-      <c r="B72">
+      <c r="B75">
         <v>2</v>
       </c>
-      <c r="C72">
+      <c r="C75">
         <v>2</v>
       </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72">
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
         <v>2</v>
       </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-      <c r="G72">
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
         <v>2</v>
       </c>
-      <c r="H72">
+      <c r="H75">
         <v>2</v>
       </c>
-      <c r="I72">
+      <c r="I75">
         <v>3</v>
       </c>
-      <c r="J72">
+      <c r="J75">
         <v>4</v>
       </c>
-      <c r="L72">
+      <c r="L75">
         <v>4</v>
       </c>
-      <c r="M72">
-        <v>1</v>
-      </c>
-      <c r="N72">
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
         <v>2</v>
       </c>
-      <c r="O72">
-        <v>1</v>
-      </c>
-      <c r="P72">
-        <v>1</v>
-      </c>
-      <c r="Q72">
-        <v>1</v>
-      </c>
-      <c r="R72">
+      <c r="O75">
+        <v>1</v>
+      </c>
+      <c r="P75">
+        <v>1</v>
+      </c>
+      <c r="Q75">
+        <v>1</v>
+      </c>
+      <c r="R75">
         <v>3</v>
       </c>
-      <c r="S72">
+      <c r="S75">
         <v>3</v>
       </c>
-      <c r="U72">
+      <c r="U75">
         <v>3</v>
       </c>
-      <c r="V72">
-        <v>1</v>
-      </c>
-      <c r="W72">
+      <c r="V75">
+        <v>1</v>
+      </c>
+      <c r="W75">
         <v>3</v>
       </c>
-      <c r="AC72">
-        <v>1</v>
-      </c>
-      <c r="AF72">
-        <v>1</v>
-      </c>
-      <c r="AH72">
+      <c r="AC75">
+        <v>1</v>
+      </c>
+      <c r="AF75">
+        <v>1</v>
+      </c>
+      <c r="AH75">
         <v>2</v>
       </c>
-      <c r="AI72">
+      <c r="AI75">
         <v>3</v>
       </c>
-      <c r="AJ72">
-        <v>1</v>
-      </c>
-      <c r="AK72">
+      <c r="AJ75">
+        <v>1</v>
+      </c>
+      <c r="AK75">
         <v>4</v>
       </c>
-      <c r="AL72">
+      <c r="AL75">
         <v>3</v>
       </c>
-      <c r="AN72">
-        <v>1</v>
-      </c>
-      <c r="AP72">
+      <c r="AN75">
+        <v>1</v>
+      </c>
+      <c r="AP75">
         <v>2</v>
       </c>
-      <c r="AT72">
+      <c r="AT75">
         <v>2</v>
       </c>
-      <c r="AU72">
+      <c r="AU75">
         <v>3</v>
       </c>
-      <c r="AV72">
-        <v>1</v>
-      </c>
-      <c r="AW72">
-        <v>1</v>
-      </c>
-      <c r="AX72">
-        <v>1</v>
-      </c>
-      <c r="AY72">
-        <v>1</v>
-      </c>
-      <c r="AZ72">
+      <c r="AV75">
+        <v>1</v>
+      </c>
+      <c r="AW75">
+        <v>1</v>
+      </c>
+      <c r="AX75">
+        <v>1</v>
+      </c>
+      <c r="AY75">
+        <v>1</v>
+      </c>
+      <c r="AZ75">
         <v>2</v>
       </c>
-      <c r="BC72">
+      <c r="BC75">
         <v>2</v>
       </c>
-      <c r="BD72">
-        <v>1</v>
-      </c>
-      <c r="BF72">
+      <c r="BD75">
+        <v>1</v>
+      </c>
+      <c r="BF75">
         <v>2</v>
       </c>
-      <c r="BH72">
+      <c r="BH75">
         <v>3</v>
       </c>
-      <c r="BI72">
-        <v>1</v>
-      </c>
-      <c r="BJ72">
+      <c r="BI75">
+        <v>1</v>
+      </c>
+      <c r="BJ75">
         <v>2</v>
       </c>
-      <c r="BK72">
+      <c r="BK75">
         <v>3</v>
       </c>
-      <c r="BM72">
+      <c r="BM75">
         <v>2</v>
       </c>
-      <c r="BN72">
+      <c r="BN75">
         <v>3</v>
       </c>
-      <c r="BU72">
-        <v>1</v>
-      </c>
-      <c r="BV72">
+      <c r="BU75">
+        <v>1</v>
+      </c>
+      <c r="BV75">
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+    <row r="76" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>49</v>
       </c>
-      <c r="G73">
+      <c r="G76">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+    <row r="77" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="75" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+    <row r="78" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>85</v>
       </c>
-      <c r="K75">
+      <c r="K78">
         <v>4</v>
       </c>
-      <c r="L75">
+      <c r="L78">
         <v>2</v>
       </c>
-      <c r="M75">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>5</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76">
+      <c r="M78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79">
         <v>2</v>
       </c>
-      <c r="D76">
+      <c r="D79">
         <v>2</v>
       </c>
-      <c r="E76">
+      <c r="E79">
         <v>3</v>
       </c>
-      <c r="F76">
+      <c r="F79">
         <v>2</v>
       </c>
-      <c r="G76">
+      <c r="G79">
         <v>3</v>
       </c>
-      <c r="H76">
-        <v>1</v>
-      </c>
-      <c r="M76">
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="M79">
         <v>4</v>
       </c>
-      <c r="N76">
+      <c r="N79">
         <v>6</v>
       </c>
-      <c r="P76">
+      <c r="P79">
         <v>2</v>
       </c>
-      <c r="Q76">
-        <v>1</v>
-      </c>
-      <c r="R76">
+      <c r="Q79">
+        <v>1</v>
+      </c>
+      <c r="R79">
         <v>2</v>
       </c>
-      <c r="S76">
+      <c r="S79">
         <v>3</v>
       </c>
-      <c r="V76">
+      <c r="V79">
         <v>2</v>
       </c>
-      <c r="W76">
-        <v>1</v>
-      </c>
-      <c r="X76">
-        <v>1</v>
-      </c>
-      <c r="Y76">
+      <c r="W79">
+        <v>1</v>
+      </c>
+      <c r="X79">
+        <v>1</v>
+      </c>
+      <c r="Y79">
         <v>4</v>
       </c>
-      <c r="Z76">
-        <v>5</v>
-      </c>
-      <c r="AA76">
-        <v>1</v>
-      </c>
-      <c r="AB76">
+      <c r="Z79">
+        <v>5</v>
+      </c>
+      <c r="AA79">
+        <v>1</v>
+      </c>
+      <c r="AB79">
         <v>3</v>
       </c>
-      <c r="AC76">
+      <c r="AC79">
         <v>4</v>
       </c>
-      <c r="AD76">
+      <c r="AD79">
         <v>3</v>
       </c>
-      <c r="AE76">
+      <c r="AE79">
         <v>3</v>
       </c>
-      <c r="AF76">
+      <c r="AF79">
         <v>2</v>
       </c>
-      <c r="AG76">
-        <v>5</v>
-      </c>
-      <c r="AH76">
+      <c r="AG79">
+        <v>5</v>
+      </c>
+      <c r="AH79">
         <v>7</v>
       </c>
-      <c r="AI76">
+      <c r="AI79">
         <v>3</v>
       </c>
-      <c r="AJ76">
-        <v>1</v>
-      </c>
-      <c r="AK76">
-        <v>1</v>
-      </c>
-      <c r="AL76">
+      <c r="AJ79">
+        <v>1</v>
+      </c>
+      <c r="AK79">
+        <v>1</v>
+      </c>
+      <c r="AL79">
         <v>6</v>
       </c>
-      <c r="AR76">
+      <c r="AR79">
         <v>3</v>
       </c>
-      <c r="AS76">
+      <c r="AS79">
         <v>2</v>
       </c>
-      <c r="AV76">
+      <c r="AV79">
         <v>2</v>
       </c>
-      <c r="AW76">
-        <v>1</v>
-      </c>
-      <c r="AX76">
+      <c r="AW79">
+        <v>1</v>
+      </c>
+      <c r="AX79">
         <v>4</v>
       </c>
-      <c r="AY76">
+      <c r="AY79">
         <v>3</v>
       </c>
-      <c r="AZ76">
+      <c r="AZ79">
         <v>4</v>
       </c>
-      <c r="BA76">
-        <v>5</v>
-      </c>
-      <c r="BB76">
+      <c r="BA79">
+        <v>5</v>
+      </c>
+      <c r="BB79">
         <v>6</v>
       </c>
-      <c r="BC76">
+      <c r="BC79">
         <v>2</v>
       </c>
-      <c r="BD76">
+      <c r="BD79">
         <v>2</v>
       </c>
-      <c r="BE76">
+      <c r="BE79">
         <v>7</v>
       </c>
-      <c r="BG76">
+      <c r="BG79">
         <v>4</v>
       </c>
-      <c r="BH76">
+      <c r="BH79">
         <v>3</v>
       </c>
-      <c r="BI76">
+      <c r="BI79">
         <v>4</v>
       </c>
-      <c r="BK76">
-        <v>1</v>
-      </c>
-      <c r="BL76">
+      <c r="BK79">
+        <v>1</v>
+      </c>
+      <c r="BL79">
         <v>8</v>
       </c>
-      <c r="BM76">
+      <c r="BM79">
         <v>4</v>
       </c>
-      <c r="BN76">
-        <v>5</v>
-      </c>
-      <c r="BO76">
+      <c r="BN79">
+        <v>5</v>
+      </c>
+      <c r="BO79">
         <v>3</v>
       </c>
-      <c r="BP76">
-        <v>1</v>
-      </c>
-      <c r="BQ76">
-        <v>1</v>
-      </c>
-      <c r="BR76">
+      <c r="BP79">
+        <v>1</v>
+      </c>
+      <c r="BQ79">
+        <v>1</v>
+      </c>
+      <c r="BR79">
         <v>3</v>
       </c>
-      <c r="BS76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+      <c r="BS79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>45</v>
       </c>
-      <c r="K77">
-        <v>1</v>
-      </c>
-      <c r="BJ77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+      <c r="K80">
+        <v>1</v>
+      </c>
+      <c r="BJ80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>367</v>
       </c>
-      <c r="B78">
-        <v>1</v>
-      </c>
-      <c r="D78">
-        <v>1</v>
-      </c>
-      <c r="E78">
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
         <v>3</v>
       </c>
-      <c r="O78">
+      <c r="O81">
         <v>2</v>
       </c>
-      <c r="P78">
+      <c r="P81">
         <v>2</v>
       </c>
-      <c r="Q78">
-        <v>1</v>
-      </c>
-      <c r="R78">
-        <v>1</v>
-      </c>
-      <c r="AD78">
-        <v>1</v>
-      </c>
-      <c r="AE78">
-        <v>1</v>
-      </c>
-      <c r="AG78">
-        <v>1</v>
-      </c>
-      <c r="AH78">
+      <c r="Q81">
+        <v>1</v>
+      </c>
+      <c r="R81">
+        <v>1</v>
+      </c>
+      <c r="AD81">
+        <v>1</v>
+      </c>
+      <c r="AE81">
+        <v>1</v>
+      </c>
+      <c r="AG81">
+        <v>1</v>
+      </c>
+      <c r="AH81">
         <v>2</v>
       </c>
-      <c r="AL78">
+      <c r="AL81">
         <v>3</v>
       </c>
-      <c r="AM78">
+      <c r="AM81">
         <v>2</v>
       </c>
-      <c r="AN78">
-        <v>1</v>
-      </c>
-      <c r="AO78">
-        <v>1</v>
-      </c>
-      <c r="AR78">
-        <v>1</v>
-      </c>
-      <c r="AS78">
-        <v>1</v>
-      </c>
-      <c r="AT78">
-        <v>1</v>
-      </c>
-      <c r="AV78">
-        <v>1</v>
-      </c>
-      <c r="AW78">
+      <c r="AN81">
+        <v>1</v>
+      </c>
+      <c r="AO81">
+        <v>1</v>
+      </c>
+      <c r="AR81">
+        <v>1</v>
+      </c>
+      <c r="AS81">
+        <v>1</v>
+      </c>
+      <c r="AT81">
+        <v>1</v>
+      </c>
+      <c r="AV81">
+        <v>1</v>
+      </c>
+      <c r="AW81">
         <v>2</v>
       </c>
-      <c r="BD78">
-        <v>1</v>
-      </c>
-      <c r="BF78">
-        <v>1</v>
-      </c>
-      <c r="BI78">
-        <v>1</v>
-      </c>
-      <c r="BU78">
+      <c r="BD81">
+        <v>1</v>
+      </c>
+      <c r="BF81">
+        <v>1</v>
+      </c>
+      <c r="BI81">
+        <v>1</v>
+      </c>
+      <c r="BU81">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+      <c r="BW81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>352</v>
       </c>
-      <c r="Z79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="Z82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="81" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+    <row r="84" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>17</v>
       </c>
-      <c r="F81">
+      <c r="F84">
         <v>2</v>
       </c>
-      <c r="J81">
-        <v>1</v>
-      </c>
-      <c r="K81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>86</v>
       </c>
-      <c r="K82">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="K85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>16</v>
       </c>
-      <c r="C83">
+      <c r="C86">
         <v>4</v>
       </c>
-      <c r="D83">
+      <c r="D86">
         <v>3</v>
       </c>
-      <c r="F83">
+      <c r="F86">
         <v>2</v>
       </c>
-      <c r="G83">
-        <v>5</v>
-      </c>
-      <c r="H83">
+      <c r="G86">
+        <v>5</v>
+      </c>
+      <c r="H86">
         <v>3</v>
       </c>
-      <c r="I83">
+      <c r="I86">
         <v>2</v>
       </c>
-      <c r="J83">
-        <v>5</v>
-      </c>
-      <c r="K83">
+      <c r="J86">
+        <v>5</v>
+      </c>
+      <c r="K86">
         <v>3</v>
       </c>
-      <c r="L83">
+      <c r="L86">
         <v>2</v>
       </c>
-      <c r="M83">
+      <c r="M86">
         <v>3</v>
       </c>
-      <c r="O83">
-        <v>5</v>
-      </c>
-      <c r="P83">
-        <v>5</v>
-      </c>
-      <c r="Q83">
+      <c r="O86">
+        <v>5</v>
+      </c>
+      <c r="P86">
+        <v>5</v>
+      </c>
+      <c r="Q86">
         <v>3</v>
       </c>
-      <c r="R83">
+      <c r="R86">
         <v>2</v>
       </c>
-      <c r="S83">
+      <c r="S86">
         <v>3</v>
       </c>
-      <c r="T83">
-        <v>1</v>
-      </c>
-      <c r="U83">
-        <v>1</v>
-      </c>
-      <c r="V83">
+      <c r="T86">
+        <v>1</v>
+      </c>
+      <c r="U86">
+        <v>1</v>
+      </c>
+      <c r="V86">
         <v>3</v>
       </c>
-      <c r="W83">
+      <c r="W86">
         <v>3</v>
       </c>
-      <c r="X83">
-        <v>5</v>
-      </c>
-      <c r="Y83">
+      <c r="X86">
+        <v>5</v>
+      </c>
+      <c r="Y86">
         <v>4</v>
       </c>
-      <c r="Z83">
-        <v>1</v>
-      </c>
-      <c r="AA83">
+      <c r="Z86">
+        <v>1</v>
+      </c>
+      <c r="AA86">
         <v>3</v>
       </c>
-      <c r="AC83">
-        <v>1</v>
-      </c>
-      <c r="AE83">
+      <c r="AC86">
+        <v>1</v>
+      </c>
+      <c r="AE86">
         <v>4</v>
       </c>
-      <c r="AF83">
+      <c r="AF86">
         <v>2</v>
       </c>
-      <c r="AG83">
+      <c r="AG86">
         <v>3</v>
       </c>
-      <c r="AH83">
+      <c r="AH86">
         <v>2</v>
       </c>
-      <c r="AI83">
+      <c r="AI86">
         <v>2</v>
       </c>
-      <c r="AJ83">
+      <c r="AJ86">
         <v>7</v>
       </c>
-      <c r="AK83">
+      <c r="AK86">
         <v>3</v>
       </c>
-      <c r="AL83">
-        <v>5</v>
-      </c>
-      <c r="AM83">
-        <v>1</v>
-      </c>
-      <c r="AN83">
+      <c r="AL86">
+        <v>5</v>
+      </c>
+      <c r="AM86">
+        <v>1</v>
+      </c>
+      <c r="AN86">
         <v>4</v>
       </c>
-      <c r="AO83">
+      <c r="AO86">
         <v>3</v>
       </c>
-      <c r="AP83">
+      <c r="AP86">
         <v>6</v>
       </c>
-      <c r="AQ83">
+      <c r="AQ86">
         <v>4</v>
       </c>
-      <c r="AR83">
-        <v>5</v>
-      </c>
-      <c r="AS83">
+      <c r="AR86">
+        <v>5</v>
+      </c>
+      <c r="AS86">
         <v>3</v>
       </c>
-      <c r="AT83">
+      <c r="AT86">
         <v>2</v>
       </c>
-      <c r="AU83">
+      <c r="AU86">
         <v>2</v>
       </c>
-      <c r="AW83">
+      <c r="AW86">
         <v>3</v>
       </c>
-      <c r="AY83">
-        <v>1</v>
-      </c>
-      <c r="AZ83">
+      <c r="AY86">
+        <v>1</v>
+      </c>
+      <c r="AZ86">
         <v>3</v>
       </c>
-      <c r="BB83">
+      <c r="BB86">
         <v>4</v>
       </c>
-      <c r="BC83">
+      <c r="BC86">
         <v>4</v>
       </c>
-      <c r="BD83">
+      <c r="BD86">
         <v>3</v>
       </c>
-      <c r="BF83">
+      <c r="BF86">
         <v>2</v>
       </c>
-      <c r="BG83">
+      <c r="BG86">
         <v>4</v>
       </c>
-      <c r="BH83">
-        <v>5</v>
-      </c>
-      <c r="BJ83">
+      <c r="BH86">
+        <v>5</v>
+      </c>
+      <c r="BJ86">
         <v>4</v>
       </c>
-      <c r="BK83">
+      <c r="BK86">
         <v>2</v>
       </c>
-      <c r="BL83">
+      <c r="BL86">
         <v>4</v>
       </c>
-      <c r="BM83">
-        <v>1</v>
-      </c>
-      <c r="BN83">
+      <c r="BM86">
+        <v>1</v>
+      </c>
+      <c r="BN86">
         <v>2</v>
       </c>
-      <c r="BO83">
+      <c r="BO86">
         <v>3</v>
       </c>
-      <c r="BS83">
+      <c r="BS86">
         <v>3</v>
       </c>
-      <c r="BT83">
+      <c r="BT86">
         <v>4</v>
       </c>
-      <c r="BU83">
+      <c r="BU86">
         <v>4</v>
       </c>
-      <c r="BV83">
+      <c r="BV86">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:74" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+    <row r="87" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB84" xr:uid="{130C2564-D265-4C41-A3E0-02A62EDAC91D}">
-    <sortState ref="A2:AB84">
-      <sortCondition ref="A1:A84"/>
+  <autoFilter ref="A1:AB87" xr:uid="{130C2564-D265-4C41-A3E0-02A62EDAC91D}">
+    <sortState ref="A2:AB87">
+      <sortCondition ref="A1:A87"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3C1165B0-6E15-482B-A397-DF951961618B}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6CE4F743-8EB4-4866-A2D5-A7A1DD10CF79}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,17 +23,17 @@
     <sheet name="artilharia total" sheetId="3" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'extrato 2024'!$A$1:$C$187</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CW$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CX$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9290" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9328" uniqueCount="398">
   <si>
     <t>Jogador</t>
   </si>
@@ -1224,6 +1224,9 @@
   </si>
   <si>
     <t>Leo MJ</t>
+  </si>
+  <si>
+    <t>Caio Brandão</t>
   </si>
 </sst>
 </file>
@@ -3492,7 +3495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CW87"/>
+  <dimension ref="A1:CX88"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
@@ -3517,10 +3520,10 @@
     <col min="50" max="58" width="9.54296875" customWidth="1"/>
     <col min="59" max="65" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
-    <col min="67" max="95" width="11" customWidth="1"/>
+    <col min="67" max="96" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3803,27 +3806,30 @@
       <c r="CP1" s="1">
         <v>46120</v>
       </c>
-      <c r="CQ1" s="1"/>
-      <c r="CR1" t="s">
+      <c r="CQ1" s="1">
+        <v>46127</v>
+      </c>
+      <c r="CR1" s="1"/>
+      <c r="CS1" t="s">
         <v>57</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>58</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>59</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>62</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>392</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4103,31 +4109,34 @@
       <c r="CP2">
         <v>7</v>
       </c>
-      <c r="CR2">
-        <f>COUNT(B2:CP2)</f>
-        <v>87</v>
-      </c>
-      <c r="CS2" s="18">
-        <f>AVERAGE(B2:CP2)</f>
-        <v>6.0402298850574709</v>
-      </c>
-      <c r="CT2">
-        <f t="shared" ref="CT2:CT33" si="0">IF(CR2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
+      <c r="CQ2">
+        <v>6</v>
+      </c>
+      <c r="CS2">
+        <f>COUNT(B2:CQ2)</f>
+        <v>88</v>
+      </c>
+      <c r="CT2" s="18">
+        <f>AVERAGE(B2:CQ2)</f>
+        <v>6.0397727272727275</v>
+      </c>
+      <c r="CU2">
+        <f t="shared" ref="CU2:CU33" si="0">IF(CS2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
         <v>1.2512468149547391</v>
       </c>
-      <c r="CU2">
-        <v>1</v>
-      </c>
       <c r="CV2">
-        <f t="shared" ref="CV2:CV33" si="1">COUNT(CK2:CN2)</f>
+        <v>1</v>
+      </c>
+      <c r="CW2">
+        <f t="shared" ref="CW2:CW33" si="1">COUNT(CK2:CN2)</f>
         <v>4</v>
       </c>
-      <c r="CW2">
-        <f t="shared" ref="CW2:CW33" si="2">IF(CU2=0,CV2,0)</f>
+      <c r="CX2">
+        <f t="shared" ref="CX2:CX33" si="2">IF(CV2=0,CW2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4407,31 +4416,34 @@
       <c r="CP3">
         <v>6</v>
       </c>
-      <c r="CR3">
+      <c r="CQ3">
+        <v>5.5</v>
+      </c>
+      <c r="CS3">
         <f>COUNT(B3:CK3)</f>
         <v>79</v>
       </c>
-      <c r="CS3" s="18">
+      <c r="CT3" s="18">
         <f>AVERAGE(B3:CK3)</f>
         <v>5.6518987341772151</v>
       </c>
-      <c r="CT3">
+      <c r="CU3">
         <f t="shared" si="0"/>
         <v>1.0518094984498128</v>
       </c>
-      <c r="CU3">
-        <v>1</v>
-      </c>
       <c r="CV3">
+        <v>1</v>
+      </c>
+      <c r="CW3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CW3">
+      <c r="CX3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4693,31 +4705,31 @@
       <c r="CI4">
         <v>5.5</v>
       </c>
-      <c r="CR4">
+      <c r="CS4">
         <f>COUNT(B4:CI4)</f>
         <v>72</v>
       </c>
-      <c r="CS4" s="18">
+      <c r="CT4" s="18">
         <f>AVERAGE(B4:CI4)</f>
         <v>5.708333333333333</v>
       </c>
-      <c r="CT4">
+      <c r="CU4">
         <f t="shared" si="0"/>
         <v>0.96435844595057774</v>
       </c>
-      <c r="CU4">
+      <c r="CV4">
         <v>0</v>
       </c>
-      <c r="CV4">
+      <c r="CW4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CW4">
+      <c r="CX4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -4985,31 +4997,31 @@
       <c r="CL5">
         <v>5.5</v>
       </c>
-      <c r="CR5">
+      <c r="CS5">
         <f>COUNT(B5:CL5)</f>
         <v>71</v>
       </c>
-      <c r="CS5" s="18">
+      <c r="CT5" s="18">
         <f>AVERAGE(B5:CL5)</f>
         <v>7.267605633802817</v>
       </c>
-      <c r="CT5">
+      <c r="CU5">
         <f t="shared" si="0"/>
         <v>1.1294250579557983</v>
       </c>
-      <c r="CU5">
-        <v>1</v>
-      </c>
       <c r="CV5">
+        <v>1</v>
+      </c>
+      <c r="CW5">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CW5">
+      <c r="CX5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -5280,31 +5292,34 @@
       <c r="CO6">
         <v>6.5</v>
       </c>
-      <c r="CR6">
+      <c r="CQ6">
+        <v>6</v>
+      </c>
+      <c r="CS6">
         <f>COUNT(B6:CL6)</f>
         <v>70</v>
       </c>
-      <c r="CS6" s="18">
+      <c r="CT6" s="18">
         <f>AVERAGE(B6:CL6)</f>
         <v>6.6142857142857139</v>
       </c>
-      <c r="CT6">
+      <c r="CU6">
         <f t="shared" si="0"/>
         <v>0.9419445925236869</v>
       </c>
-      <c r="CU6">
-        <v>1</v>
-      </c>
       <c r="CV6">
+        <v>1</v>
+      </c>
+      <c r="CW6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CW6">
+      <c r="CX6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5578,31 +5593,31 @@
       <c r="CP7">
         <v>6.5</v>
       </c>
-      <c r="CR7">
+      <c r="CS7">
         <f>COUNT(B7:CL7)</f>
         <v>70</v>
       </c>
-      <c r="CS7" s="18">
+      <c r="CT7" s="18">
         <f>AVERAGE(B7:CL7)</f>
         <v>6.6071428571428568</v>
       </c>
-      <c r="CT7">
+      <c r="CU7">
         <f t="shared" si="0"/>
         <v>1.0570846156365068</v>
       </c>
-      <c r="CU7">
-        <v>1</v>
-      </c>
       <c r="CV7">
+        <v>1</v>
+      </c>
+      <c r="CW7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CW7">
+      <c r="CX7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5852,31 +5867,31 @@
       <c r="CE8">
         <v>5</v>
       </c>
-      <c r="CR8">
+      <c r="CS8">
         <f>COUNT(B8:CI8)</f>
         <v>68</v>
       </c>
-      <c r="CS8" s="18">
+      <c r="CT8" s="18">
         <f>AVERAGE(B8:CI8)</f>
         <v>6.4191176470588234</v>
       </c>
-      <c r="CT8">
+      <c r="CU8">
         <f t="shared" si="0"/>
         <v>1.1769245721961776</v>
       </c>
-      <c r="CU8">
+      <c r="CV8">
         <v>0</v>
       </c>
-      <c r="CV8">
+      <c r="CW8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CW8">
+      <c r="CX8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -6129,31 +6144,31 @@
       <c r="CI9">
         <v>5.5</v>
       </c>
-      <c r="CR9">
+      <c r="CS9">
         <f>COUNT(B9:CI9)</f>
         <v>67</v>
       </c>
-      <c r="CS9" s="18">
+      <c r="CT9" s="18">
         <f>AVERAGE(B9:CI9)</f>
         <v>5.9701492537313436</v>
       </c>
-      <c r="CT9">
+      <c r="CU9">
         <f t="shared" si="0"/>
         <v>0.96648378625350351</v>
       </c>
-      <c r="CU9">
+      <c r="CV9">
         <v>0</v>
       </c>
-      <c r="CV9">
+      <c r="CW9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CW9">
+      <c r="CX9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -6424,31 +6439,34 @@
       <c r="CP10">
         <v>5.5</v>
       </c>
-      <c r="CR10">
+      <c r="CQ10">
+        <v>6</v>
+      </c>
+      <c r="CS10">
         <f>COUNT(B10:CI10)</f>
         <v>62</v>
       </c>
-      <c r="CS10" s="18">
+      <c r="CT10" s="18">
         <f>AVERAGE(B10:CI10)</f>
         <v>5.717741935483871</v>
       </c>
-      <c r="CT10">
+      <c r="CU10">
         <f t="shared" si="0"/>
         <v>1.3617531291315086</v>
       </c>
-      <c r="CU10">
-        <v>1</v>
-      </c>
       <c r="CV10">
+        <v>1</v>
+      </c>
+      <c r="CW10">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CW10">
+      <c r="CX10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6719,31 +6737,34 @@
       <c r="CO11">
         <v>6.5</v>
       </c>
-      <c r="CR11">
+      <c r="CQ11">
+        <v>7</v>
+      </c>
+      <c r="CS11">
         <f>COUNT(B11:CI11)</f>
         <v>59</v>
       </c>
-      <c r="CS11" s="18">
+      <c r="CT11" s="18">
         <f>AVERAGE(B11:CI11)</f>
         <v>6.6779661016949152</v>
       </c>
-      <c r="CT11">
+      <c r="CU11">
         <f t="shared" si="0"/>
         <v>1.0072574989410263</v>
       </c>
-      <c r="CU11">
-        <v>1</v>
-      </c>
       <c r="CV11">
+        <v>1</v>
+      </c>
+      <c r="CW11">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CW11">
+      <c r="CX11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -7020,31 +7041,34 @@
       <c r="CP12">
         <v>6</v>
       </c>
-      <c r="CR12">
-        <f>COUNT(B12:CP12)</f>
-        <v>60</v>
-      </c>
-      <c r="CS12" s="18">
-        <f>AVERAGE(B12:CP12)</f>
-        <v>5.5250000000000004</v>
-      </c>
-      <c r="CT12">
+      <c r="CQ12">
+        <v>6</v>
+      </c>
+      <c r="CS12">
+        <f>COUNT(B12:CQ12)</f>
+        <v>61</v>
+      </c>
+      <c r="CT12" s="18">
+        <f>AVERAGE(B12:CQ12)</f>
+        <v>5.5327868852459012</v>
+      </c>
+      <c r="CU12">
         <f t="shared" si="0"/>
         <v>1.0254583642020354</v>
       </c>
-      <c r="CU12">
-        <v>1</v>
-      </c>
       <c r="CV12">
+        <v>1</v>
+      </c>
+      <c r="CW12">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CW12">
+      <c r="CX12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -7318,31 +7342,34 @@
       <c r="CN13">
         <v>5.5</v>
       </c>
-      <c r="CR13">
+      <c r="CQ13">
+        <v>6.5</v>
+      </c>
+      <c r="CS13">
         <f>COUNT(B13:CN13)</f>
         <v>56</v>
       </c>
-      <c r="CS13" s="18">
+      <c r="CT13" s="18">
         <f>AVERAGE(B13:CN13)</f>
         <v>6.3571428571428568</v>
       </c>
-      <c r="CT13">
+      <c r="CU13">
         <f t="shared" si="0"/>
         <v>1.1769469323774333</v>
       </c>
-      <c r="CU13">
-        <v>1</v>
-      </c>
       <c r="CV13">
+        <v>1</v>
+      </c>
+      <c r="CW13">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CW13">
+      <c r="CX13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>367</v>
       </c>
@@ -7595,31 +7622,31 @@
       <c r="CP14">
         <v>5.5</v>
       </c>
-      <c r="CR14">
+      <c r="CS14">
         <f>COUNT(B14:CI14)</f>
         <v>55</v>
       </c>
-      <c r="CS14" s="18">
+      <c r="CT14" s="18">
         <f>AVERAGE(B14:CI14)</f>
         <v>6.3181818181818183</v>
       </c>
-      <c r="CT14">
+      <c r="CU14">
         <f t="shared" si="0"/>
         <v>1.1213885273224193</v>
       </c>
-      <c r="CU14">
+      <c r="CV14">
         <v>0</v>
       </c>
-      <c r="CV14">
+      <c r="CW14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CW14">
+      <c r="CX14">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -7863,31 +7890,31 @@
       <c r="CF15">
         <v>5.5</v>
       </c>
-      <c r="CR15">
+      <c r="CS15">
         <f>COUNT(B15:CI15)</f>
         <v>52</v>
       </c>
-      <c r="CS15" s="18">
+      <c r="CT15" s="18">
         <f>AVERAGE(B15:CI15)</f>
         <v>5.6923076923076925</v>
       </c>
-      <c r="CT15">
+      <c r="CU15">
         <f t="shared" si="0"/>
         <v>0.84687340856573534</v>
       </c>
-      <c r="CU15">
+      <c r="CV15">
         <v>0</v>
       </c>
-      <c r="CV15">
+      <c r="CW15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CW15">
+      <c r="CX15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -8137,31 +8164,31 @@
       <c r="CF16">
         <v>5.5</v>
       </c>
-      <c r="CR16">
+      <c r="CS16">
         <f>COUNT(B16:CI16)</f>
         <v>47</v>
       </c>
-      <c r="CS16" s="18">
+      <c r="CT16" s="18">
         <f>AVERAGE(B16:CI16)</f>
         <v>4.4255319148936172</v>
       </c>
-      <c r="CT16">
+      <c r="CU16">
         <f t="shared" si="0"/>
         <v>1.3391217246854428</v>
       </c>
-      <c r="CU16">
+      <c r="CV16">
         <v>0</v>
       </c>
-      <c r="CV16">
+      <c r="CW16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CW16">
+      <c r="CX16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>56</v>
       </c>
@@ -8441,31 +8468,34 @@
       <c r="CP17">
         <v>5.5</v>
       </c>
-      <c r="CR17">
+      <c r="CQ17">
+        <v>5.5</v>
+      </c>
+      <c r="CS17">
         <f>COUNT(B17:CL17)</f>
         <v>46</v>
       </c>
-      <c r="CS17" s="18">
+      <c r="CT17" s="18">
         <f>AVERAGE(B17:CL17)</f>
         <v>6.0652173913043477</v>
       </c>
-      <c r="CT17">
+      <c r="CU17">
         <f t="shared" si="0"/>
         <v>0.9573434129174403</v>
       </c>
-      <c r="CU17">
-        <v>1</v>
-      </c>
       <c r="CV17">
+        <v>1</v>
+      </c>
+      <c r="CW17">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CW17">
+      <c r="CX17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -8733,31 +8763,31 @@
       <c r="CL18">
         <v>6</v>
       </c>
-      <c r="CR18">
+      <c r="CS18">
         <f>COUNT(B18:CL18)</f>
         <v>44</v>
       </c>
-      <c r="CS18" s="18">
+      <c r="CT18" s="18">
         <f>AVERAGE(B18:CL18)</f>
         <v>5.0113636363636367</v>
       </c>
-      <c r="CT18">
+      <c r="CU18">
         <f t="shared" si="0"/>
         <v>1.0645089158214895</v>
       </c>
-      <c r="CU18">
-        <v>1</v>
-      </c>
       <c r="CV18">
+        <v>1</v>
+      </c>
+      <c r="CW18">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CW18">
+      <c r="CX18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -9001,31 +9031,31 @@
       <c r="CK19">
         <v>5.5</v>
       </c>
-      <c r="CR19">
+      <c r="CS19">
         <f>COUNT(B19:CI19)</f>
         <v>38</v>
       </c>
-      <c r="CS19" s="18">
+      <c r="CT19" s="18">
         <f>AVERAGE(B19:CI19)</f>
         <v>6.1578947368421053</v>
       </c>
-      <c r="CT19">
+      <c r="CU19">
         <f t="shared" si="0"/>
         <v>1.0973263770680928</v>
       </c>
-      <c r="CU19">
+      <c r="CV19">
         <v>0</v>
       </c>
-      <c r="CV19">
+      <c r="CW19">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CW19">
+      <c r="CX19">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -9290,31 +9320,31 @@
       <c r="CM20">
         <v>5.5</v>
       </c>
-      <c r="CR20">
+      <c r="CS20">
         <f>COUNT(B20:CJ20)</f>
         <v>37</v>
       </c>
-      <c r="CS20" s="18">
+      <c r="CT20" s="18">
         <f>AVERAGE(B20:CJ20)</f>
         <v>5.2027027027027026</v>
       </c>
-      <c r="CT20">
+      <c r="CU20">
         <f t="shared" si="0"/>
         <v>1.3241383031954423</v>
       </c>
-      <c r="CU20">
+      <c r="CV20">
         <v>0</v>
       </c>
-      <c r="CV20">
+      <c r="CW20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CW20">
+      <c r="CX20">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -9573,31 +9603,31 @@
       <c r="CO21">
         <v>5.5</v>
       </c>
-      <c r="CR21">
+      <c r="CS21">
         <f>COUNT(B21:CI21)</f>
         <v>36</v>
       </c>
-      <c r="CS21" s="18">
+      <c r="CT21" s="18">
         <f>AVERAGE(B21:CI21)</f>
         <v>5.7361111111111107</v>
       </c>
-      <c r="CT21">
+      <c r="CU21">
         <f t="shared" si="0"/>
         <v>0.92956296268047622</v>
       </c>
-      <c r="CU21">
-        <v>1</v>
-      </c>
       <c r="CV21">
+        <v>1</v>
+      </c>
+      <c r="CW21">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CW21">
+      <c r="CX21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -9865,31 +9895,34 @@
       <c r="CP22">
         <v>5.5</v>
       </c>
-      <c r="CR22">
+      <c r="CQ22">
+        <v>6.5</v>
+      </c>
+      <c r="CS22">
         <f>COUNT(B22:CI22)</f>
         <v>36</v>
       </c>
-      <c r="CS22" s="18">
+      <c r="CT22" s="18">
         <f>AVERAGE(B22:CI22)</f>
         <v>5.6111111111111107</v>
       </c>
-      <c r="CT22">
+      <c r="CU22">
         <f t="shared" si="0"/>
         <v>1.0098256776095882</v>
       </c>
-      <c r="CU22">
-        <v>1</v>
-      </c>
       <c r="CV22">
+        <v>1</v>
+      </c>
+      <c r="CW22">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CW22">
+      <c r="CX22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -10160,31 +10193,31 @@
       <c r="CN23">
         <v>6</v>
       </c>
-      <c r="CR23">
+      <c r="CS23">
         <f>COUNT(B23:CN23)</f>
         <v>30</v>
       </c>
-      <c r="CS23" s="18">
+      <c r="CT23" s="18">
         <f>AVERAGE(B23:CN23)</f>
         <v>6.4</v>
       </c>
-      <c r="CT23">
+      <c r="CU23">
         <f t="shared" si="0"/>
         <v>0.90960483309014595</v>
       </c>
-      <c r="CU23">
-        <v>1</v>
-      </c>
       <c r="CV23">
+        <v>1</v>
+      </c>
+      <c r="CW23">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CW23">
+      <c r="CX23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -10434,31 +10467,31 @@
       <c r="CN24">
         <v>6</v>
       </c>
-      <c r="CR24">
-        <f t="shared" ref="CR24:CR31" si="3">COUNT(B24:CI24)</f>
+      <c r="CS24">
+        <f t="shared" ref="CS24:CS31" si="3">COUNT(B24:CI24)</f>
         <v>25</v>
       </c>
-      <c r="CS24" s="18">
-        <f t="shared" ref="CS24:CS31" si="4">AVERAGE(B24:CI24)</f>
+      <c r="CT24" s="18">
+        <f t="shared" ref="CT24:CT31" si="4">AVERAGE(B24:CI24)</f>
         <v>5.4</v>
       </c>
-      <c r="CT24">
+      <c r="CU24">
         <f t="shared" si="0"/>
         <v>0.71728150235677346</v>
       </c>
-      <c r="CU24">
+      <c r="CV24">
         <v>0</v>
       </c>
-      <c r="CV24">
+      <c r="CW24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CW24">
+      <c r="CX24">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -10699,31 +10732,31 @@
       <c r="CB25" t="s">
         <v>26</v>
       </c>
-      <c r="CR25">
+      <c r="CS25">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="CS25" s="18">
+      <c r="CT25" s="18">
         <f t="shared" si="4"/>
         <v>5.7894736842105265</v>
       </c>
-      <c r="CT25">
+      <c r="CU25">
         <f t="shared" si="0"/>
         <v>1.3674366679797902</v>
       </c>
-      <c r="CU25">
+      <c r="CV25">
         <v>0</v>
       </c>
-      <c r="CV25">
+      <c r="CW25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CW25">
+      <c r="CX25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>346</v>
       </c>
@@ -10964,31 +10997,31 @@
       <c r="CB26" t="s">
         <v>26</v>
       </c>
-      <c r="CR26">
+      <c r="CS26">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="CS26" s="18">
+      <c r="CT26" s="18">
         <f t="shared" si="4"/>
         <v>5.9444444444444446</v>
       </c>
-      <c r="CT26">
+      <c r="CU26">
         <f t="shared" si="0"/>
         <v>0.72535769855270305</v>
       </c>
-      <c r="CU26">
+      <c r="CV26">
         <v>0</v>
       </c>
-      <c r="CV26">
+      <c r="CW26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CW26">
+      <c r="CX26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -11229,31 +11262,31 @@
       <c r="CB27" t="s">
         <v>26</v>
       </c>
-      <c r="CR27">
+      <c r="CS27">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="CS27" s="18">
+      <c r="CT27" s="18">
         <f t="shared" si="4"/>
         <v>5.3235294117647056</v>
       </c>
-      <c r="CT27">
+      <c r="CU27">
         <f t="shared" si="0"/>
         <v>1.3456083251473603</v>
       </c>
-      <c r="CU27">
+      <c r="CV27">
         <v>0</v>
       </c>
-      <c r="CV27">
+      <c r="CW27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CW27">
+      <c r="CX27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -11494,31 +11527,31 @@
       <c r="CB28" t="s">
         <v>26</v>
       </c>
-      <c r="CR28">
+      <c r="CS28">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="CS28" s="18">
+      <c r="CT28" s="18">
         <f t="shared" si="4"/>
         <v>4.53125</v>
       </c>
-      <c r="CT28">
+      <c r="CU28">
         <f t="shared" si="0"/>
         <v>1.5434674167816653</v>
       </c>
-      <c r="CU28">
+      <c r="CV28">
         <v>0</v>
       </c>
-      <c r="CV28">
+      <c r="CW28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CW28">
+      <c r="CX28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -11771,31 +11804,34 @@
       <c r="CO29">
         <v>6.5</v>
       </c>
-      <c r="CR29">
+      <c r="CQ29">
+        <v>6.5</v>
+      </c>
+      <c r="CS29">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="CS29" s="18">
+      <c r="CT29" s="18">
         <f t="shared" si="4"/>
         <v>6.65625</v>
       </c>
-      <c r="CT29">
+      <c r="CU29">
         <f t="shared" si="0"/>
         <v>0.74651970279870483</v>
       </c>
-      <c r="CU29">
-        <v>1</v>
-      </c>
       <c r="CV29">
+        <v>1</v>
+      </c>
+      <c r="CW29">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CW29">
+      <c r="CX29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -12036,31 +12072,31 @@
       <c r="CB30">
         <v>5.5</v>
       </c>
-      <c r="CR30">
+      <c r="CS30">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="CS30" s="18">
+      <c r="CT30" s="18">
         <f t="shared" si="4"/>
         <v>3.8666666666666667</v>
       </c>
-      <c r="CT30">
+      <c r="CU30">
         <f t="shared" si="0"/>
         <v>2.3563490726929555</v>
       </c>
-      <c r="CU30">
+      <c r="CV30">
         <v>0</v>
       </c>
-      <c r="CV30">
+      <c r="CW30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CW30">
+      <c r="CX30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -12313,31 +12349,31 @@
       <c r="CP31">
         <v>6</v>
       </c>
-      <c r="CR31">
+      <c r="CS31">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="CS31" s="18">
+      <c r="CT31" s="18">
         <f t="shared" si="4"/>
         <v>4.8214285714285712</v>
       </c>
-      <c r="CT31">
+      <c r="CU31">
         <f t="shared" si="0"/>
         <v>0.89335151148745728</v>
       </c>
-      <c r="CU31">
+      <c r="CV31">
         <v>0</v>
       </c>
-      <c r="CV31">
+      <c r="CW31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CW31">
+      <c r="CX31">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -12611,31 +12647,34 @@
       <c r="CP32">
         <v>6</v>
       </c>
-      <c r="CR32">
-        <f>COUNT(B32:CP32)</f>
-        <v>15</v>
-      </c>
-      <c r="CS32" s="18">
-        <f>AVERAGE(B32:CP32)</f>
-        <v>6.3666666666666663</v>
-      </c>
-      <c r="CT32">
+      <c r="CQ32">
+        <v>6</v>
+      </c>
+      <c r="CS32">
+        <f>COUNT(B32:CQ32)</f>
+        <v>16</v>
+      </c>
+      <c r="CT32" s="18">
+        <f>AVERAGE(B32:CQ32)</f>
+        <v>6.34375</v>
+      </c>
+      <c r="CU32">
         <f t="shared" si="0"/>
         <v>0.90829510622924903</v>
       </c>
-      <c r="CU32">
-        <v>1</v>
-      </c>
       <c r="CV32">
+        <v>1</v>
+      </c>
+      <c r="CW32">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CW32">
+      <c r="CX32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -12876,31 +12915,31 @@
       <c r="CB33" t="s">
         <v>26</v>
       </c>
-      <c r="CR33">
-        <f t="shared" ref="CR33:CR64" si="5">COUNT(B33:CI33)</f>
+      <c r="CS33">
+        <f t="shared" ref="CS33:CS64" si="5">COUNT(B33:CI33)</f>
         <v>13</v>
       </c>
-      <c r="CS33" s="18">
-        <f t="shared" ref="CS33:CS64" si="6">AVERAGE(B33:CI33)</f>
+      <c r="CT33" s="18">
+        <f t="shared" ref="CT33:CT64" si="6">AVERAGE(B33:CI33)</f>
         <v>7.3461538461538458</v>
       </c>
-      <c r="CT33">
+      <c r="CU33">
         <f t="shared" si="0"/>
         <v>1.5191090506255012</v>
       </c>
-      <c r="CU33">
+      <c r="CV33">
         <v>0</v>
       </c>
-      <c r="CV33">
+      <c r="CW33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CW33">
+      <c r="CX33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -13141,31 +13180,31 @@
       <c r="CB34" t="s">
         <v>26</v>
       </c>
-      <c r="CR34">
+      <c r="CS34">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="CS34" s="18">
+      <c r="CT34" s="18">
         <f t="shared" si="6"/>
         <v>4.6818181818181817</v>
       </c>
-      <c r="CT34">
-        <f t="shared" ref="CT34:CT65" si="7">IF(CR34&gt;1,_xlfn.STDEV.S(B34:CF34),"")</f>
+      <c r="CU34">
+        <f t="shared" ref="CU34:CU65" si="7">IF(CS34&gt;1,_xlfn.STDEV.S(B34:CF34),"")</f>
         <v>0.81463879335344846</v>
       </c>
-      <c r="CU34">
+      <c r="CV34">
         <v>0</v>
       </c>
-      <c r="CV34">
-        <f t="shared" ref="CV34:CV65" si="8">COUNT(CK34:CN34)</f>
+      <c r="CW34">
+        <f t="shared" ref="CW34:CW65" si="8">COUNT(CK34:CN34)</f>
         <v>0</v>
       </c>
-      <c r="CW34">
-        <f t="shared" ref="CW34:CW65" si="9">IF(CU34=0,CV34,0)</f>
+      <c r="CX34">
+        <f t="shared" ref="CX34:CX65" si="9">IF(CV34=0,CW34,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>45</v>
       </c>
@@ -13409,31 +13448,31 @@
       <c r="CC35">
         <v>6</v>
       </c>
-      <c r="CR35">
+      <c r="CS35">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="CS35" s="18">
+      <c r="CT35" s="18">
         <f t="shared" si="6"/>
         <v>8.4499999999999993</v>
       </c>
-      <c r="CT35">
+      <c r="CU35">
         <f t="shared" si="7"/>
         <v>1.1890705987824657</v>
       </c>
-      <c r="CU35">
+      <c r="CV35">
         <v>0</v>
       </c>
-      <c r="CV35">
+      <c r="CW35">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW35">
+      <c r="CX35">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>343</v>
       </c>
@@ -13686,31 +13725,34 @@
       <c r="CO36">
         <v>6</v>
       </c>
-      <c r="CR36">
+      <c r="CQ36">
+        <v>6</v>
+      </c>
+      <c r="CS36">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="CS36" s="18">
+      <c r="CT36" s="18">
         <f t="shared" si="6"/>
         <v>4.125</v>
       </c>
-      <c r="CT36">
+      <c r="CU36">
         <f t="shared" si="7"/>
         <v>1.7677669529663689</v>
       </c>
-      <c r="CU36">
-        <v>1</v>
-      </c>
       <c r="CV36">
+        <v>1</v>
+      </c>
+      <c r="CW36">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CW36">
+      <c r="CX36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>340</v>
       </c>
@@ -13954,31 +13996,31 @@
       <c r="CL37">
         <v>6</v>
       </c>
-      <c r="CR37">
+      <c r="CS37">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CS37" s="18">
+      <c r="CT37" s="18">
         <f t="shared" si="6"/>
         <v>5.7142857142857144</v>
       </c>
-      <c r="CT37">
+      <c r="CU37">
         <f t="shared" si="7"/>
         <v>0.56694670951384085</v>
       </c>
-      <c r="CU37">
+      <c r="CV37">
         <v>0</v>
       </c>
-      <c r="CV37">
+      <c r="CW37">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CW37">
+      <c r="CX37">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>376</v>
       </c>
@@ -14225,31 +14267,34 @@
       <c r="CO38">
         <v>5.5</v>
       </c>
-      <c r="CR38">
+      <c r="CQ38">
+        <v>7.5</v>
+      </c>
+      <c r="CS38">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CS38" s="18">
+      <c r="CT38" s="18">
         <f t="shared" si="6"/>
         <v>5.7857142857142856</v>
       </c>
-      <c r="CT38">
+      <c r="CU38">
         <f t="shared" si="7"/>
         <v>0.4879500364742666</v>
       </c>
-      <c r="CU38">
+      <c r="CV38">
         <v>0</v>
       </c>
-      <c r="CV38">
+      <c r="CW38">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CW38">
+      <c r="CX38">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>378</v>
       </c>
@@ -14514,31 +14559,34 @@
       <c r="CP39">
         <v>6</v>
       </c>
-      <c r="CR39">
+      <c r="CQ39">
+        <v>5.5</v>
+      </c>
+      <c r="CS39">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="CS39" s="18">
+      <c r="CT39" s="18">
         <f t="shared" si="6"/>
         <v>5.166666666666667</v>
       </c>
-      <c r="CT39">
+      <c r="CU39">
         <f t="shared" si="7"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="CU39">
-        <v>1</v>
-      </c>
       <c r="CV39">
+        <v>1</v>
+      </c>
+      <c r="CW39">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CW39">
+      <c r="CX39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -14782,31 +14830,31 @@
       <c r="CH40">
         <v>6.5</v>
       </c>
-      <c r="CR40">
+      <c r="CS40">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CS40" s="18">
+      <c r="CT40" s="18">
         <f t="shared" si="6"/>
         <v>7.8</v>
       </c>
-      <c r="CT40">
+      <c r="CU40">
         <f t="shared" si="7"/>
         <v>1.0307764064044151</v>
       </c>
-      <c r="CU40">
+      <c r="CV40">
         <v>0</v>
       </c>
-      <c r="CV40">
+      <c r="CW40">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW40">
+      <c r="CX40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>60</v>
       </c>
@@ -15050,31 +15098,31 @@
       <c r="CM41">
         <v>5.5</v>
       </c>
-      <c r="CR41">
+      <c r="CS41">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CS41" s="18">
+      <c r="CT41" s="18">
         <f t="shared" si="6"/>
         <v>3.375</v>
       </c>
-      <c r="CT41">
+      <c r="CU41">
         <f t="shared" si="7"/>
         <v>0.47871355387816905</v>
       </c>
-      <c r="CU41">
+      <c r="CV41">
         <v>0</v>
       </c>
-      <c r="CV41">
+      <c r="CW41">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CW41">
+      <c r="CX41">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -15315,31 +15363,31 @@
       <c r="CB42" t="s">
         <v>26</v>
       </c>
-      <c r="CR42">
+      <c r="CS42">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CS42" s="18">
+      <c r="CT42" s="18">
         <f t="shared" si="6"/>
         <v>5.625</v>
       </c>
-      <c r="CT42">
+      <c r="CU42">
         <f t="shared" si="7"/>
         <v>0.9464847243000456</v>
       </c>
-      <c r="CU42">
+      <c r="CV42">
         <v>0</v>
       </c>
-      <c r="CV42">
+      <c r="CW42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW42">
+      <c r="CX42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -15580,31 +15628,31 @@
       <c r="CB43" t="s">
         <v>26</v>
       </c>
-      <c r="CR43">
+      <c r="CS43">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CS43" s="18">
+      <c r="CT43" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CT43">
+      <c r="CU43">
         <f t="shared" si="7"/>
         <v>1.0408329997330663</v>
       </c>
-      <c r="CU43">
+      <c r="CV43">
         <v>0</v>
       </c>
-      <c r="CV43">
+      <c r="CW43">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW43">
+      <c r="CX43">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -15845,31 +15893,31 @@
       <c r="CB44" t="s">
         <v>26</v>
       </c>
-      <c r="CR44">
+      <c r="CS44">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CS44" s="18">
+      <c r="CT44" s="18">
         <f t="shared" si="6"/>
         <v>1.375</v>
       </c>
-      <c r="CT44">
+      <c r="CU44">
         <f t="shared" si="7"/>
         <v>1.8874586088176875</v>
       </c>
-      <c r="CU44">
+      <c r="CV44">
         <v>0</v>
       </c>
-      <c r="CV44">
+      <c r="CW44">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW44">
+      <c r="CX44">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>344</v>
       </c>
@@ -16110,31 +16158,31 @@
       <c r="CB45" t="s">
         <v>26</v>
       </c>
-      <c r="CR45">
+      <c r="CS45">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CS45" s="18">
+      <c r="CT45" s="18">
         <f t="shared" si="6"/>
         <v>4.625</v>
       </c>
-      <c r="CT45">
+      <c r="CU45">
         <f t="shared" si="7"/>
         <v>1.4361406616345072</v>
       </c>
-      <c r="CU45">
+      <c r="CV45">
         <v>0</v>
       </c>
-      <c r="CV45">
+      <c r="CW45">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW45">
+      <c r="CX45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>361</v>
       </c>
@@ -16375,31 +16423,31 @@
       <c r="CB46" t="s">
         <v>26</v>
       </c>
-      <c r="CR46">
+      <c r="CS46">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CS46" s="18">
+      <c r="CT46" s="18">
         <f t="shared" si="6"/>
         <v>6.25</v>
       </c>
-      <c r="CT46">
+      <c r="CU46">
         <f t="shared" si="7"/>
         <v>0.8660254037844386</v>
       </c>
-      <c r="CU46">
+      <c r="CV46">
         <v>0</v>
       </c>
-      <c r="CV46">
+      <c r="CW46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW46">
+      <c r="CX46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -16640,31 +16688,31 @@
       <c r="CB47" t="s">
         <v>26</v>
       </c>
-      <c r="CR47">
+      <c r="CS47">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CS47" s="18">
+      <c r="CT47" s="18">
         <f t="shared" si="6"/>
         <v>2.875</v>
       </c>
-      <c r="CT47">
+      <c r="CU47">
         <f t="shared" si="7"/>
         <v>2.7801378862687129</v>
       </c>
-      <c r="CU47">
+      <c r="CV47">
         <v>0</v>
       </c>
-      <c r="CV47">
+      <c r="CW47">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW47">
+      <c r="CX47">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -16905,31 +16953,31 @@
       <c r="CB48" t="s">
         <v>26</v>
       </c>
-      <c r="CR48">
+      <c r="CS48">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CS48" s="18">
+      <c r="CT48" s="18">
         <f t="shared" si="6"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="CT48">
+      <c r="CU48">
         <f t="shared" si="7"/>
         <v>1.4433756729740652</v>
       </c>
-      <c r="CU48">
+      <c r="CV48">
         <v>0</v>
       </c>
-      <c r="CV48">
+      <c r="CW48">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW48">
+      <c r="CX48">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -17170,31 +17218,31 @@
       <c r="CB49" t="s">
         <v>26</v>
       </c>
-      <c r="CR49">
+      <c r="CS49">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CS49" s="18">
+      <c r="CT49" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CT49">
+      <c r="CU49">
         <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
-      <c r="CU49">
+      <c r="CV49">
         <v>0</v>
       </c>
-      <c r="CV49">
+      <c r="CW49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW49">
+      <c r="CX49">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -17435,31 +17483,31 @@
       <c r="CB50" t="s">
         <v>26</v>
       </c>
-      <c r="CR50">
+      <c r="CS50">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CS50" s="18">
+      <c r="CT50" s="18">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="CT50">
+      <c r="CU50">
         <f t="shared" si="7"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CU50">
+      <c r="CV50">
         <v>0</v>
       </c>
-      <c r="CV50">
+      <c r="CW50">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW50">
+      <c r="CX50">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -17703,31 +17751,31 @@
       <c r="CG51">
         <v>6</v>
       </c>
-      <c r="CR51">
+      <c r="CS51">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CS51" s="18">
+      <c r="CT51" s="18">
         <f t="shared" si="6"/>
         <v>5.666666666666667</v>
       </c>
-      <c r="CT51">
+      <c r="CU51">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CU51">
+      <c r="CV51">
         <v>0</v>
       </c>
-      <c r="CV51">
+      <c r="CW51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW51">
+      <c r="CX51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>368</v>
       </c>
@@ -17971,31 +18019,31 @@
       <c r="CG52">
         <v>6</v>
       </c>
-      <c r="CR52">
+      <c r="CS52">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CS52" s="18">
+      <c r="CT52" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CT52">
+      <c r="CU52">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CU52">
+      <c r="CV52">
         <v>0</v>
       </c>
-      <c r="CV52">
+      <c r="CW52">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW52">
+      <c r="CX52">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>362</v>
       </c>
@@ -18239,31 +18287,31 @@
       <c r="CD53">
         <v>5.5</v>
       </c>
-      <c r="CR53">
+      <c r="CS53">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CS53" s="18">
+      <c r="CT53" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CT53">
+      <c r="CU53">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CU53">
+      <c r="CV53">
         <v>0</v>
       </c>
-      <c r="CV53">
+      <c r="CW53">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW53">
+      <c r="CX53">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>364</v>
       </c>
@@ -18513,31 +18561,31 @@
       <c r="CN54">
         <v>6</v>
       </c>
-      <c r="CR54">
+      <c r="CS54">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CS54" s="18">
+      <c r="CT54" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="CT54">
+      <c r="CU54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CU54">
-        <v>1</v>
-      </c>
       <c r="CV54">
+        <v>1</v>
+      </c>
+      <c r="CW54">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CW54">
+      <c r="CX54">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -18778,31 +18826,31 @@
       <c r="CB55" t="s">
         <v>26</v>
       </c>
-      <c r="CR55">
+      <c r="CS55">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CS55" s="18">
+      <c r="CT55" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CT55">
+      <c r="CU55">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CU55">
+      <c r="CV55">
         <v>0</v>
       </c>
-      <c r="CV55">
+      <c r="CW55">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW55">
+      <c r="CX55">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>339</v>
       </c>
@@ -19043,31 +19091,31 @@
       <c r="CB56" t="s">
         <v>26</v>
       </c>
-      <c r="CR56">
+      <c r="CS56">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CS56" s="18">
+      <c r="CT56" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CT56">
+      <c r="CU56">
         <f t="shared" si="7"/>
         <v>2.4748737341529163</v>
       </c>
-      <c r="CU56">
+      <c r="CV56">
         <v>0</v>
       </c>
-      <c r="CV56">
+      <c r="CW56">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW56">
+      <c r="CX56">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>342</v>
       </c>
@@ -19314,31 +19362,31 @@
       <c r="CO57">
         <v>6</v>
       </c>
-      <c r="CR57">
+      <c r="CS57">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CS57" s="18">
+      <c r="CT57" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CT57">
+      <c r="CU57">
         <f t="shared" si="7"/>
         <v>2.1213203435596424</v>
       </c>
-      <c r="CU57">
+      <c r="CV57">
         <v>0</v>
       </c>
-      <c r="CV57">
+      <c r="CW57">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW57">
+      <c r="CX57">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>369</v>
       </c>
@@ -19579,31 +19627,31 @@
       <c r="CB58" t="s">
         <v>26</v>
       </c>
-      <c r="CR58">
+      <c r="CS58">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CS58" s="18">
+      <c r="CT58" s="18">
         <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
-      <c r="CT58">
+      <c r="CU58">
         <f t="shared" si="7"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="CU58">
+      <c r="CV58">
         <v>0</v>
       </c>
-      <c r="CV58">
+      <c r="CW58">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW58">
+      <c r="CX58">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>379</v>
       </c>
@@ -19844,31 +19892,31 @@
       <c r="CB59" t="s">
         <v>26</v>
       </c>
-      <c r="CR59">
+      <c r="CS59">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CS59" s="18">
+      <c r="CT59" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CT59">
+      <c r="CU59">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CU59">
+      <c r="CV59">
         <v>0</v>
       </c>
-      <c r="CV59">
+      <c r="CW59">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW59">
+      <c r="CX59">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>390</v>
       </c>
@@ -20115,31 +20163,31 @@
       <c r="CH60">
         <v>7</v>
       </c>
-      <c r="CR60">
+      <c r="CS60">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CS60" s="18">
+      <c r="CT60" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CT60" t="e">
+      <c r="CU60" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CU60">
+      <c r="CV60">
         <v>0</v>
       </c>
-      <c r="CV60">
+      <c r="CW60">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW60">
+      <c r="CX60">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>388</v>
       </c>
@@ -20383,31 +20431,31 @@
       <c r="CH61">
         <v>5</v>
       </c>
-      <c r="CR61">
+      <c r="CS61">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CS61" s="18">
+      <c r="CT61" s="18">
         <f t="shared" si="6"/>
         <v>4.25</v>
       </c>
-      <c r="CT61" t="e">
+      <c r="CU61" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CU61">
+      <c r="CV61">
         <v>0</v>
       </c>
-      <c r="CV61">
+      <c r="CW61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW61">
+      <c r="CX61">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>345</v>
       </c>
@@ -20666,31 +20714,31 @@
       <c r="CO62">
         <v>4.5</v>
       </c>
-      <c r="CR62">
+      <c r="CS62">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CS62" s="18">
+      <c r="CT62" s="18">
         <f t="shared" si="6"/>
         <v>4.25</v>
       </c>
-      <c r="CT62" t="e">
+      <c r="CU62" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CU62">
-        <v>1</v>
-      </c>
       <c r="CV62">
+        <v>1</v>
+      </c>
+      <c r="CW62">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CW62">
+      <c r="CX62">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>387</v>
       </c>
@@ -20940,31 +20988,31 @@
       <c r="CJ63">
         <v>7</v>
       </c>
-      <c r="CR63">
+      <c r="CS63">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CS63" s="18">
+      <c r="CT63" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="CT63" t="e">
+      <c r="CU63" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CU63">
+      <c r="CV63">
         <v>0</v>
       </c>
-      <c r="CV63">
+      <c r="CW63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW63">
+      <c r="CX63">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>86</v>
       </c>
@@ -21205,31 +21253,31 @@
       <c r="CB64" t="s">
         <v>26</v>
       </c>
-      <c r="CR64">
+      <c r="CS64">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CS64" s="18">
+      <c r="CT64" s="18">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="CT64" t="str">
+      <c r="CU64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="CU64">
+      <c r="CV64">
         <v>0</v>
       </c>
-      <c r="CV64">
+      <c r="CW64">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW64">
+      <c r="CX64">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -21470,31 +21518,31 @@
       <c r="CB65" t="s">
         <v>26</v>
       </c>
-      <c r="CR65">
-        <f t="shared" ref="CR65:CR83" si="10">COUNT(B65:CI65)</f>
-        <v>1</v>
-      </c>
-      <c r="CS65" s="18">
-        <f t="shared" ref="CS65:CS83" si="11">AVERAGE(B65:CI65)</f>
+      <c r="CS65">
+        <f t="shared" ref="CS65:CS83" si="10">COUNT(B65:CI65)</f>
+        <v>1</v>
+      </c>
+      <c r="CT65" s="18">
+        <f t="shared" ref="CT65:CT83" si="11">AVERAGE(B65:CI65)</f>
         <v>7</v>
       </c>
-      <c r="CT65" t="str">
+      <c r="CU65" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="CU65">
+      <c r="CV65">
         <v>0</v>
       </c>
-      <c r="CV65">
+      <c r="CW65">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW65">
+      <c r="CX65">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>353</v>
       </c>
@@ -21735,31 +21783,31 @@
       <c r="CB66" t="s">
         <v>26</v>
       </c>
-      <c r="CR66">
+      <c r="CS66">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS66" s="18">
+      <c r="CT66" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CT66" t="str">
-        <f t="shared" ref="CT66:CT83" si="12">IF(CR66&gt;1,_xlfn.STDEV.S(B66:CF66),"")</f>
+      <c r="CU66" t="str">
+        <f t="shared" ref="CU66:CU83" si="12">IF(CS66&gt;1,_xlfn.STDEV.S(B66:CF66),"")</f>
         <v/>
       </c>
-      <c r="CU66">
+      <c r="CV66">
         <v>0</v>
       </c>
-      <c r="CV66">
-        <f t="shared" ref="CV66:CV83" si="13">COUNT(CK66:CN66)</f>
+      <c r="CW66">
+        <f t="shared" ref="CW66:CW83" si="13">COUNT(CK66:CN66)</f>
         <v>0</v>
       </c>
-      <c r="CW66">
-        <f t="shared" ref="CW66:CW83" si="14">IF(CU66=0,CV66,0)</f>
+      <c r="CX66">
+        <f t="shared" ref="CX66:CX83" si="14">IF(CV66=0,CW66,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>80</v>
       </c>
@@ -22000,31 +22048,31 @@
       <c r="CB67" t="s">
         <v>26</v>
       </c>
-      <c r="CR67">
+      <c r="CS67">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS67" s="18">
+      <c r="CT67" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CT67" t="str">
+      <c r="CU67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU67">
+      <c r="CV67">
         <v>0</v>
       </c>
-      <c r="CV67">
+      <c r="CW67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW67">
+      <c r="CX67">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>47</v>
       </c>
@@ -22265,31 +22313,31 @@
       <c r="CB68" t="s">
         <v>26</v>
       </c>
-      <c r="CR68">
+      <c r="CS68">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS68" s="18">
+      <c r="CT68" s="18">
         <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
-      <c r="CT68" t="str">
+      <c r="CU68" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU68">
+      <c r="CV68">
         <v>0</v>
       </c>
-      <c r="CV68">
+      <c r="CW68">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW68">
+      <c r="CX68">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -22530,31 +22578,31 @@
       <c r="CB69" t="s">
         <v>26</v>
       </c>
-      <c r="CR69">
+      <c r="CS69">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS69" s="18">
+      <c r="CT69" s="18">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="CT69" t="str">
+      <c r="CU69" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU69">
+      <c r="CV69">
         <v>0</v>
       </c>
-      <c r="CV69">
+      <c r="CW69">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW69">
+      <c r="CX69">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>347</v>
       </c>
@@ -22795,31 +22843,31 @@
       <c r="CB70" t="s">
         <v>26</v>
       </c>
-      <c r="CR70">
+      <c r="CS70">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS70" s="18">
+      <c r="CT70" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="CT70" t="str">
+      <c r="CU70" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU70">
+      <c r="CV70">
         <v>0</v>
       </c>
-      <c r="CV70">
+      <c r="CW70">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW70">
+      <c r="CX70">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>350</v>
       </c>
@@ -23060,31 +23108,31 @@
       <c r="CB71" t="s">
         <v>26</v>
       </c>
-      <c r="CR71">
+      <c r="CS71">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS71" s="18">
+      <c r="CT71" s="18">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="CT71" t="str">
+      <c r="CU71" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU71">
+      <c r="CV71">
         <v>0</v>
       </c>
-      <c r="CV71">
+      <c r="CW71">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW71">
+      <c r="CX71">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>351</v>
       </c>
@@ -23325,31 +23373,31 @@
       <c r="CB72" t="s">
         <v>26</v>
       </c>
-      <c r="CR72">
+      <c r="CS72">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS72" s="18">
+      <c r="CT72" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="CT72" t="str">
+      <c r="CU72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU72">
+      <c r="CV72">
         <v>0</v>
       </c>
-      <c r="CV72">
+      <c r="CW72">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW72">
+      <c r="CX72">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>352</v>
       </c>
@@ -23590,31 +23638,31 @@
       <c r="CB73" t="s">
         <v>26</v>
       </c>
-      <c r="CR73">
+      <c r="CS73">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS73" s="18">
+      <c r="CT73" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="CT73" t="str">
+      <c r="CU73" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU73">
+      <c r="CV73">
         <v>0</v>
       </c>
-      <c r="CV73">
+      <c r="CW73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW73">
+      <c r="CX73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>354</v>
       </c>
@@ -23855,31 +23903,31 @@
       <c r="CB74" t="s">
         <v>26</v>
       </c>
-      <c r="CR74">
+      <c r="CS74">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS74" s="18">
+      <c r="CT74" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CT74" t="str">
+      <c r="CU74" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU74">
+      <c r="CV74">
         <v>0</v>
       </c>
-      <c r="CV74">
+      <c r="CW74">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW74">
+      <c r="CX74">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>365</v>
       </c>
@@ -24120,31 +24168,31 @@
       <c r="CB75" t="s">
         <v>26</v>
       </c>
-      <c r="CR75">
+      <c r="CS75">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS75" s="18">
+      <c r="CT75" s="18">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
-      <c r="CT75" t="str">
+      <c r="CU75" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU75">
+      <c r="CV75">
         <v>0</v>
       </c>
-      <c r="CV75">
+      <c r="CW75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW75">
+      <c r="CX75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>366</v>
       </c>
@@ -24385,31 +24433,31 @@
       <c r="CB76" t="s">
         <v>26</v>
       </c>
-      <c r="CR76">
+      <c r="CS76">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS76" s="18">
+      <c r="CT76" s="18">
         <f t="shared" si="11"/>
         <v>2.5</v>
       </c>
-      <c r="CT76" t="str">
+      <c r="CU76" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU76">
+      <c r="CV76">
         <v>0</v>
       </c>
-      <c r="CV76">
+      <c r="CW76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW76">
+      <c r="CX76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>374</v>
       </c>
@@ -24650,31 +24698,31 @@
       <c r="CB77" t="s">
         <v>26</v>
       </c>
-      <c r="CR77">
+      <c r="CS77">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS77" s="18">
+      <c r="CT77" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CT77" t="str">
+      <c r="CU77" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU77">
+      <c r="CV77">
         <v>0</v>
       </c>
-      <c r="CV77">
+      <c r="CW77">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW77">
+      <c r="CX77">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>375</v>
       </c>
@@ -24915,31 +24963,31 @@
       <c r="CB78" t="s">
         <v>26</v>
       </c>
-      <c r="CR78">
+      <c r="CS78">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS78" s="18">
+      <c r="CT78" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CT78" t="str">
+      <c r="CU78" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU78">
+      <c r="CV78">
         <v>0</v>
       </c>
-      <c r="CV78">
+      <c r="CW78">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW78">
+      <c r="CX78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>377</v>
       </c>
@@ -25180,31 +25228,31 @@
       <c r="CB79" t="s">
         <v>26</v>
       </c>
-      <c r="CR79">
+      <c r="CS79">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS79" s="18">
+      <c r="CT79" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="CT79" t="str">
+      <c r="CU79" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU79">
+      <c r="CV79">
         <v>0</v>
       </c>
-      <c r="CV79">
+      <c r="CW79">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW79">
+      <c r="CX79">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>381</v>
       </c>
@@ -25445,31 +25493,31 @@
       <c r="CB80" t="s">
         <v>26</v>
       </c>
-      <c r="CR80">
+      <c r="CS80">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS80" s="18">
+      <c r="CT80" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CT80" t="str">
+      <c r="CU80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU80">
+      <c r="CV80">
         <v>0</v>
       </c>
-      <c r="CV80">
+      <c r="CW80">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW80">
+      <c r="CX80">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>382</v>
       </c>
@@ -25710,31 +25758,31 @@
       <c r="CB81" t="s">
         <v>26</v>
       </c>
-      <c r="CR81">
+      <c r="CS81">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS81" s="18">
+      <c r="CT81" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CT81" t="str">
+      <c r="CU81" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU81">
+      <c r="CV81">
         <v>0</v>
       </c>
-      <c r="CV81">
+      <c r="CW81">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW81">
+      <c r="CX81">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>389</v>
       </c>
@@ -25978,31 +26026,31 @@
       <c r="CH82">
         <v>7.5</v>
       </c>
-      <c r="CR82">
+      <c r="CS82">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS82" s="18">
+      <c r="CT82" s="18">
         <f t="shared" si="11"/>
         <v>7.5</v>
       </c>
-      <c r="CT82" t="str">
+      <c r="CU82" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU82">
+      <c r="CV82">
         <v>0</v>
       </c>
-      <c r="CV82">
+      <c r="CW82">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW82">
+      <c r="CX82">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>391</v>
       </c>
@@ -26246,31 +26294,31 @@
       <c r="CI83">
         <v>7</v>
       </c>
-      <c r="CR83">
+      <c r="CS83">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CS83" s="18">
+      <c r="CT83" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CT83" t="str">
+      <c r="CU83" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CU83">
+      <c r="CV83">
         <v>0</v>
       </c>
-      <c r="CV83">
+      <c r="CW83">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CW83">
+      <c r="CX83">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>393</v>
       </c>
@@ -26280,130 +26328,170 @@
       <c r="CP84">
         <v>7</v>
       </c>
-      <c r="CR84">
-        <f t="shared" ref="CR84:CR87" si="15">COUNT(B84:CI84)</f>
+      <c r="CQ84">
+        <v>9</v>
+      </c>
+      <c r="CS84">
+        <f t="shared" ref="CS84:CS88" si="15">COUNT(B84:CI84)</f>
         <v>0</v>
       </c>
-      <c r="CS84" s="18" t="e">
-        <f t="shared" ref="CS84:CS87" si="16">AVERAGE(B84:CI84)</f>
+      <c r="CT84" s="18" t="e">
+        <f t="shared" ref="CT84:CT88" si="16">AVERAGE(B84:CI84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="CT84" t="str">
-        <f t="shared" ref="CT84:CT87" si="17">IF(CR84&gt;1,_xlfn.STDEV.S(B84:CF84),"")</f>
+      <c r="CU84" t="str">
+        <f t="shared" ref="CU84:CU88" si="17">IF(CS84&gt;1,_xlfn.STDEV.S(B84:CF84),"")</f>
         <v/>
       </c>
-      <c r="CU84">
+      <c r="CV84">
         <v>0</v>
       </c>
-      <c r="CV84">
-        <f t="shared" ref="CV84:CV87" si="18">COUNT(CK84:CN84)</f>
+      <c r="CW84">
+        <f t="shared" ref="CW84:CW88" si="18">COUNT(CK84:CN84)</f>
         <v>0</v>
       </c>
-      <c r="CW84">
-        <f t="shared" ref="CW84:CW87" si="19">IF(CU84=0,CV84,0)</f>
+      <c r="CX84">
+        <f t="shared" ref="CX84:CX88" si="19">IF(CV84=0,CW84,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>394</v>
       </c>
       <c r="CP85">
         <v>6</v>
       </c>
-      <c r="CR85">
+      <c r="CQ85">
+        <v>6.5</v>
+      </c>
+      <c r="CS85">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="CS85" s="18" t="e">
+      <c r="CT85" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CT85" t="str">
+      <c r="CU85" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="CU85">
+      <c r="CV85">
         <v>0</v>
       </c>
-      <c r="CV85">
+      <c r="CW85">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="CW85">
+      <c r="CX85">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>395</v>
       </c>
       <c r="CP86">
         <v>5.5</v>
       </c>
-      <c r="CR86">
+      <c r="CQ86">
+        <v>6</v>
+      </c>
+      <c r="CS86">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="CS86" s="18" t="e">
+      <c r="CT86" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CT86" t="str">
+      <c r="CU86" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="CU86">
+      <c r="CV86">
         <v>0</v>
       </c>
-      <c r="CV86">
+      <c r="CW86">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="CW86">
+      <c r="CX86">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>396</v>
       </c>
       <c r="CP87">
         <v>6.5</v>
       </c>
-      <c r="CR87">
+      <c r="CS87">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="CS87" s="18" t="e">
+      <c r="CT87" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CT87" t="str">
+      <c r="CU87" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="CU87">
+      <c r="CV87">
         <v>0</v>
       </c>
-      <c r="CV87">
+      <c r="CW87">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="CW87">
+      <c r="CX87">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
+    <row r="88" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>397</v>
+      </c>
+      <c r="CQ88">
+        <v>6.5</v>
+      </c>
+      <c r="CS88">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="CT88" s="18" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CU88" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="CV88">
+        <v>0</v>
+      </c>
+      <c r="CW88">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="CX88">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CW83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
-    <sortState ref="A2:CW83">
-      <sortCondition descending="1" ref="CR1:CR83"/>
+  <autoFilter ref="A1:CX83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
+    <sortState ref="A2:CX83">
+      <sortCondition descending="1" ref="CS1:CS83"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="CR2:CR87">
+  <conditionalFormatting sqref="CS2:CS88">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -26415,7 +26503,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CT2:CT87">
+  <conditionalFormatting sqref="CU2:CU88">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -26427,7 +26515,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR87">
+  <conditionalFormatting sqref="CS2:CS88">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -26439,7 +26527,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS87">
+  <conditionalFormatting sqref="CT2:CT88">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
@@ -26451,7 +26539,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS87">
+  <conditionalFormatting sqref="CT2:CT88">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
@@ -26463,7 +26551,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR87">
+  <conditionalFormatting sqref="CS2:CS88">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -26475,7 +26563,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS87">
+  <conditionalFormatting sqref="CT2:CT88">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -26487,7 +26575,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ79">
+  <conditionalFormatting sqref="CR2:CR79">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -26499,7 +26587,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ67">
+  <conditionalFormatting sqref="CR2:CR67">
     <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
@@ -26511,7 +26599,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ67">
+  <conditionalFormatting sqref="CR2:CR67">
     <cfRule type="colorScale" priority="127">
       <colorScale>
         <cfvo type="min"/>
@@ -26523,7 +26611,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ67">
+  <conditionalFormatting sqref="CR2:CR67">
     <cfRule type="colorScale" priority="129">
       <colorScale>
         <cfvo type="min"/>
@@ -26535,7 +26623,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:CP83">
+  <conditionalFormatting sqref="B2:CQ83">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -31748,7 +31836,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X273"/>
+  <dimension ref="A1:X276"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -45298,6 +45386,156 @@
       </c>
       <c r="P273" s="8"/>
     </row>
+    <row r="274" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A274" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B274" s="62">
+        <v>4</v>
+      </c>
+      <c r="C274" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="E274" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F274" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G274" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="H274" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="I274" s="9">
+        <v>4</v>
+      </c>
+      <c r="J274" s="10">
+        <v>5</v>
+      </c>
+      <c r="K274" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L274" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="M274" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N274" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O274" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="P274" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A275" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B275" s="62">
+        <v>7</v>
+      </c>
+      <c r="C275" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D275" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E275" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F275" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G275" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H275" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I275" s="11">
+        <v>9</v>
+      </c>
+      <c r="J275" s="2">
+        <v>5</v>
+      </c>
+      <c r="K275" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L275" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M275" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="N275" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="O275" s="61" t="s">
+        <v>394</v>
+      </c>
+      <c r="P275" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A276" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B276" s="62">
+        <v>4</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F276" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="G276" s="61" t="s">
+        <v>394</v>
+      </c>
+      <c r="H276" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="I276" s="5">
+        <v>7</v>
+      </c>
+      <c r="J276" s="8">
+        <v>4</v>
+      </c>
+      <c r="K276" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L276" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="M276" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="N276" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="O276" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="P276" s="8" t="s">
+        <v>397</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -45305,7 +45543,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:BW87"/>
+  <dimension ref="A1:BX88"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -45314,10 +45552,10 @@
     <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="75" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="76" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:76" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -45543,8 +45781,11 @@
       <c r="BW1" s="1">
         <v>46120</v>
       </c>
-    </row>
-    <row r="2" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="BX1" s="1">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:76" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -45602,8 +45843,11 @@
       <c r="BW2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="BX2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:76" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -45611,7 +45855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:76" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -45649,12 +45893,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:76" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -45662,15 +45906,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:76" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>393</v>
       </c>
       <c r="BW7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:75" x14ac:dyDescent="0.35">
+      <c r="BX7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:76" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>364</v>
       </c>
@@ -45687,7 +45934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:76" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -45695,7 +45942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:76" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>353</v>
       </c>
@@ -45703,2774 +45950,2815 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="12" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:76" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:76" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>397</v>
+      </c>
+      <c r="BX13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="14" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="15" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>395</v>
       </c>
-      <c r="BW14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="BW15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>362</v>
       </c>
-      <c r="BK15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="BK16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="18" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>25</v>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="J17">
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="J18">
         <v>3</v>
       </c>
-      <c r="K17">
+      <c r="K18">
         <v>3</v>
       </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="V17">
-        <v>1</v>
-      </c>
-      <c r="AE17">
-        <v>1</v>
-      </c>
-      <c r="AF17">
-        <v>1</v>
-      </c>
-      <c r="AH17">
-        <v>2</v>
-      </c>
-      <c r="AT17">
-        <v>1</v>
-      </c>
-      <c r="BA17">
-        <v>1</v>
-      </c>
-      <c r="BH17">
-        <v>1</v>
-      </c>
-      <c r="BM17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="AE18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>1</v>
+      </c>
+      <c r="AH18">
+        <v>2</v>
+      </c>
+      <c r="AT18">
+        <v>1</v>
+      </c>
+      <c r="BA18">
+        <v>1</v>
+      </c>
+      <c r="BH18">
+        <v>1</v>
+      </c>
+      <c r="BM18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="P18">
-        <v>1</v>
-      </c>
-      <c r="S18">
-        <v>1</v>
-      </c>
-      <c r="W18">
-        <v>1</v>
-      </c>
-      <c r="Z18">
-        <v>2</v>
-      </c>
-      <c r="AA18">
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>2</v>
+      </c>
+      <c r="AA19">
         <v>0.5</v>
       </c>
-      <c r="AK18">
-        <v>1</v>
-      </c>
-      <c r="AR18">
-        <v>2</v>
-      </c>
-      <c r="AX18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="AK19">
+        <v>1</v>
+      </c>
+      <c r="AR19">
+        <v>2</v>
+      </c>
+      <c r="AX19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>378</v>
       </c>
-      <c r="BL19">
-        <v>1</v>
-      </c>
-      <c r="BR19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="BL20">
+        <v>1</v>
+      </c>
+      <c r="BR20">
+        <v>1</v>
+      </c>
+      <c r="BX20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>54</v>
       </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
         <v>3</v>
       </c>
-      <c r="V20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="V21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>66</v>
       </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="I21">
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="I22">
         <v>3</v>
       </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="T21">
-        <v>1</v>
-      </c>
-      <c r="W21">
-        <v>1</v>
-      </c>
-      <c r="X21">
-        <v>1</v>
-      </c>
-      <c r="Y21">
-        <v>1</v>
-      </c>
-      <c r="Z21">
-        <v>1</v>
-      </c>
-      <c r="AA21">
-        <v>1</v>
-      </c>
-      <c r="AC21">
-        <v>1</v>
-      </c>
-      <c r="AD21">
-        <v>1</v>
-      </c>
-      <c r="AH21">
-        <v>1</v>
-      </c>
-      <c r="AI21">
-        <v>1</v>
-      </c>
-      <c r="BA21">
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="Z22">
+        <v>1</v>
+      </c>
+      <c r="AA22">
+        <v>1</v>
+      </c>
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AH22">
+        <v>1</v>
+      </c>
+      <c r="AI22">
+        <v>1</v>
+      </c>
+      <c r="BA22">
         <v>3</v>
       </c>
-      <c r="BG21">
-        <v>1</v>
-      </c>
-      <c r="BP21">
-        <v>1</v>
-      </c>
-      <c r="BU21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="BG22">
+        <v>1</v>
+      </c>
+      <c r="BP22">
+        <v>1</v>
+      </c>
+      <c r="BU22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>84</v>
       </c>
-      <c r="I22">
-        <v>2</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="L22">
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="L23">
         <v>3</v>
       </c>
-      <c r="N22">
-        <v>2</v>
-      </c>
-      <c r="O22">
-        <v>2</v>
-      </c>
-      <c r="P22">
-        <v>1</v>
-      </c>
-      <c r="S22">
-        <v>2</v>
-      </c>
-      <c r="V22">
+      <c r="N23">
+        <v>2</v>
+      </c>
+      <c r="O23">
+        <v>2</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>2</v>
+      </c>
+      <c r="V23">
         <v>4</v>
       </c>
-      <c r="W22">
+      <c r="W23">
         <v>6</v>
       </c>
-      <c r="X22">
+      <c r="X23">
         <v>3</v>
       </c>
-      <c r="AB22">
-        <v>1</v>
-      </c>
-      <c r="AC22">
-        <v>2</v>
-      </c>
-      <c r="AD22">
+      <c r="AB23">
+        <v>1</v>
+      </c>
+      <c r="AC23">
+        <v>2</v>
+      </c>
+      <c r="AD23">
         <v>3</v>
       </c>
-      <c r="AE22">
-        <v>1</v>
-      </c>
-      <c r="AH22">
+      <c r="AE23">
+        <v>1</v>
+      </c>
+      <c r="AH23">
         <v>4</v>
       </c>
-      <c r="AI22">
-        <v>5</v>
-      </c>
-      <c r="AK22">
-        <v>1</v>
-      </c>
-      <c r="AL22">
-        <v>1</v>
-      </c>
-      <c r="AN22">
-        <v>2</v>
-      </c>
-      <c r="AU22">
+      <c r="AI23">
+        <v>5</v>
+      </c>
+      <c r="AK23">
+        <v>1</v>
+      </c>
+      <c r="AL23">
+        <v>1</v>
+      </c>
+      <c r="AN23">
+        <v>2</v>
+      </c>
+      <c r="AU23">
         <v>4</v>
       </c>
-      <c r="AV22">
-        <v>1</v>
-      </c>
-      <c r="AX22">
-        <v>1</v>
-      </c>
-      <c r="BH22">
-        <v>1</v>
-      </c>
-      <c r="BI22">
-        <v>2</v>
-      </c>
-      <c r="BK22">
-        <v>2</v>
-      </c>
-      <c r="BQ22">
-        <v>2</v>
-      </c>
-      <c r="BR22">
+      <c r="AV23">
+        <v>1</v>
+      </c>
+      <c r="AX23">
+        <v>1</v>
+      </c>
+      <c r="BH23">
+        <v>1</v>
+      </c>
+      <c r="BI23">
+        <v>2</v>
+      </c>
+      <c r="BK23">
+        <v>2</v>
+      </c>
+      <c r="BQ23">
+        <v>2</v>
+      </c>
+      <c r="BR23">
         <v>3</v>
       </c>
-      <c r="BU22">
-        <v>1</v>
-      </c>
-      <c r="BV22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="BU23">
+        <v>1</v>
+      </c>
+      <c r="BV23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>391</v>
       </c>
-      <c r="BP23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="BP24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>15</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>2</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="AK24">
-        <v>1</v>
-      </c>
-      <c r="AL24">
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="AK25">
+        <v>1</v>
+      </c>
+      <c r="AL25">
         <v>4</v>
       </c>
-      <c r="AO24">
-        <v>2</v>
-      </c>
-      <c r="AR24">
+      <c r="AO25">
+        <v>2</v>
+      </c>
+      <c r="AR25">
         <v>3</v>
       </c>
-      <c r="AS24">
-        <v>2</v>
-      </c>
-      <c r="AT24">
-        <v>1</v>
-      </c>
-      <c r="AY24">
-        <v>1</v>
-      </c>
-      <c r="BE24">
-        <v>2</v>
-      </c>
-      <c r="BF24">
-        <v>1</v>
-      </c>
-      <c r="BI24">
-        <v>2</v>
-      </c>
-      <c r="BR24">
-        <v>1</v>
-      </c>
-      <c r="BS24">
-        <v>1</v>
-      </c>
-      <c r="BT24">
+      <c r="AS25">
+        <v>2</v>
+      </c>
+      <c r="AT25">
+        <v>1</v>
+      </c>
+      <c r="AY25">
+        <v>1</v>
+      </c>
+      <c r="BE25">
+        <v>2</v>
+      </c>
+      <c r="BF25">
+        <v>1</v>
+      </c>
+      <c r="BI25">
+        <v>2</v>
+      </c>
+      <c r="BR25">
+        <v>1</v>
+      </c>
+      <c r="BS25">
+        <v>1</v>
+      </c>
+      <c r="BT25">
         <v>3</v>
       </c>
-      <c r="BU24">
-        <v>1</v>
-      </c>
-      <c r="BW24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="BU25">
+        <v>1</v>
+      </c>
+      <c r="BW25">
+        <v>1</v>
+      </c>
+      <c r="BX25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>375</v>
       </c>
-      <c r="AW25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="AW26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>6</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>3</v>
       </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="L26">
-        <v>2</v>
-      </c>
-      <c r="M26">
-        <v>2</v>
-      </c>
-      <c r="N26">
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>2</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+      <c r="N27">
         <v>6</v>
       </c>
-      <c r="O26">
-        <v>1</v>
-      </c>
-      <c r="Q26">
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
         <v>3</v>
       </c>
-      <c r="R26">
-        <v>1</v>
-      </c>
-      <c r="S26">
-        <v>1</v>
-      </c>
-      <c r="T26">
+      <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <v>1</v>
+      </c>
+      <c r="T27">
         <v>3</v>
       </c>
-      <c r="U26">
+      <c r="U27">
         <v>3</v>
       </c>
-      <c r="V26">
+      <c r="V27">
         <v>6</v>
       </c>
-      <c r="W26">
-        <v>2</v>
-      </c>
-      <c r="X26">
+      <c r="W27">
+        <v>2</v>
+      </c>
+      <c r="X27">
         <v>3</v>
       </c>
-      <c r="Y26">
-        <v>1</v>
-      </c>
-      <c r="Z26">
+      <c r="Y27">
+        <v>1</v>
+      </c>
+      <c r="Z27">
         <v>3.5</v>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <v>3.5</v>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <v>3</v>
       </c>
-      <c r="AC26">
-        <v>1</v>
-      </c>
-      <c r="AE26">
+      <c r="AC27">
+        <v>1</v>
+      </c>
+      <c r="AE27">
         <v>10</v>
       </c>
-      <c r="AF26">
+      <c r="AF27">
         <v>3</v>
       </c>
-      <c r="AG26">
+      <c r="AG27">
         <v>3</v>
       </c>
-      <c r="AH26">
-        <v>2</v>
-      </c>
-      <c r="AJ26">
+      <c r="AH27">
+        <v>2</v>
+      </c>
+      <c r="AJ27">
         <v>3</v>
       </c>
-      <c r="AK26">
+      <c r="AK27">
         <v>3</v>
       </c>
-      <c r="AL26">
-        <v>5</v>
-      </c>
-      <c r="AN26">
-        <v>1</v>
-      </c>
-      <c r="AO26">
+      <c r="AL27">
+        <v>5</v>
+      </c>
+      <c r="AN27">
+        <v>1</v>
+      </c>
+      <c r="AO27">
         <v>6</v>
       </c>
-      <c r="AP26">
+      <c r="AP27">
         <v>4</v>
       </c>
-      <c r="AQ26">
+      <c r="AQ27">
         <v>3</v>
       </c>
-      <c r="AR26">
+      <c r="AR27">
         <v>4</v>
       </c>
-      <c r="AS26">
-        <v>2</v>
-      </c>
-      <c r="AT26">
+      <c r="AS27">
+        <v>2</v>
+      </c>
+      <c r="AT27">
         <v>4</v>
       </c>
-      <c r="AU26">
+      <c r="AU27">
         <v>4</v>
       </c>
-      <c r="AV26">
+      <c r="AV27">
         <v>6</v>
       </c>
-      <c r="AW26">
-        <v>1</v>
-      </c>
-      <c r="AY26">
+      <c r="AW27">
+        <v>1</v>
+      </c>
+      <c r="AY27">
         <v>4</v>
       </c>
-      <c r="AZ26">
-        <v>1</v>
-      </c>
-      <c r="BA26">
+      <c r="AZ27">
+        <v>1</v>
+      </c>
+      <c r="BA27">
         <v>3</v>
       </c>
-      <c r="BC26">
-        <v>5</v>
-      </c>
-      <c r="BD26">
-        <v>2</v>
-      </c>
-      <c r="BE26">
+      <c r="BC27">
+        <v>5</v>
+      </c>
+      <c r="BD27">
+        <v>2</v>
+      </c>
+      <c r="BE27">
         <v>3</v>
       </c>
-      <c r="BF26">
+      <c r="BF27">
         <v>3</v>
       </c>
-      <c r="BG26">
+      <c r="BG27">
         <v>3</v>
       </c>
-      <c r="BH26">
-        <v>1</v>
-      </c>
-      <c r="BI26">
-        <v>5</v>
-      </c>
-      <c r="BJ26">
-        <v>1</v>
-      </c>
-      <c r="BK26">
-        <v>1</v>
-      </c>
-      <c r="BL26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="BH27">
+        <v>1</v>
+      </c>
+      <c r="BI27">
+        <v>5</v>
+      </c>
+      <c r="BJ27">
+        <v>1</v>
+      </c>
+      <c r="BK27">
+        <v>1</v>
+      </c>
+      <c r="BL27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>342</v>
       </c>
-      <c r="T27">
+      <c r="T28">
         <v>4</v>
       </c>
-      <c r="AH27">
-        <v>1</v>
-      </c>
-      <c r="AK27">
-        <v>1</v>
-      </c>
-      <c r="BQ27">
-        <v>2</v>
-      </c>
-      <c r="BV27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="AH28">
+        <v>1</v>
+      </c>
+      <c r="AK28">
+        <v>1</v>
+      </c>
+      <c r="BQ28">
+        <v>2</v>
+      </c>
+      <c r="BV28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+    <row r="30" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="30" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+    <row r="31" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>12</v>
       </c>
-      <c r="N30">
-        <v>2</v>
-      </c>
-      <c r="U30">
-        <v>1</v>
-      </c>
-      <c r="AI30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="N31">
+        <v>2</v>
+      </c>
+      <c r="U31">
+        <v>1</v>
+      </c>
+      <c r="AI31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>4</v>
       </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
         <v>3</v>
       </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
         <v>3</v>
       </c>
-      <c r="P31">
+      <c r="P32">
         <v>3</v>
       </c>
-      <c r="U31">
+      <c r="U32">
         <v>3</v>
       </c>
-      <c r="W31">
-        <v>1</v>
-      </c>
-      <c r="AD31">
-        <v>1</v>
-      </c>
-      <c r="AF31">
-        <v>1</v>
-      </c>
-      <c r="AH31">
-        <v>1</v>
-      </c>
-      <c r="AI31">
-        <v>1</v>
-      </c>
-      <c r="AJ31">
-        <v>2</v>
-      </c>
-      <c r="AO31">
-        <v>2</v>
-      </c>
-      <c r="AP31">
-        <v>2</v>
-      </c>
-      <c r="AQ31">
+      <c r="W32">
+        <v>1</v>
+      </c>
+      <c r="AD32">
+        <v>1</v>
+      </c>
+      <c r="AF32">
+        <v>1</v>
+      </c>
+      <c r="AH32">
+        <v>1</v>
+      </c>
+      <c r="AI32">
+        <v>1</v>
+      </c>
+      <c r="AJ32">
+        <v>2</v>
+      </c>
+      <c r="AO32">
+        <v>2</v>
+      </c>
+      <c r="AP32">
+        <v>2</v>
+      </c>
+      <c r="AQ32">
         <v>4</v>
       </c>
-      <c r="AR31">
-        <v>2</v>
-      </c>
-      <c r="AT31">
-        <v>1</v>
-      </c>
-      <c r="AU31">
-        <v>2</v>
-      </c>
-      <c r="AV31">
-        <v>1</v>
-      </c>
-      <c r="AW31">
-        <v>1</v>
-      </c>
-      <c r="AX31">
-        <v>1</v>
-      </c>
-      <c r="AZ31">
-        <v>2</v>
-      </c>
-      <c r="BA31">
-        <v>2</v>
-      </c>
-      <c r="BB31">
-        <v>1</v>
-      </c>
-      <c r="BD31">
-        <v>2</v>
-      </c>
-      <c r="BE31">
+      <c r="AR32">
+        <v>2</v>
+      </c>
+      <c r="AT32">
+        <v>1</v>
+      </c>
+      <c r="AU32">
+        <v>2</v>
+      </c>
+      <c r="AV32">
+        <v>1</v>
+      </c>
+      <c r="AW32">
+        <v>1</v>
+      </c>
+      <c r="AX32">
+        <v>1</v>
+      </c>
+      <c r="AZ32">
+        <v>2</v>
+      </c>
+      <c r="BA32">
+        <v>2</v>
+      </c>
+      <c r="BB32">
+        <v>1</v>
+      </c>
+      <c r="BD32">
+        <v>2</v>
+      </c>
+      <c r="BE32">
         <v>3</v>
       </c>
-      <c r="BF31">
-        <v>1</v>
-      </c>
-      <c r="BG31">
-        <v>1</v>
-      </c>
-      <c r="BJ31">
-        <v>1</v>
-      </c>
-      <c r="BK31">
-        <v>1</v>
-      </c>
-      <c r="BL31">
-        <v>1</v>
-      </c>
-      <c r="BM31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="BF32">
+        <v>1</v>
+      </c>
+      <c r="BG32">
+        <v>1</v>
+      </c>
+      <c r="BJ32">
+        <v>1</v>
+      </c>
+      <c r="BK32">
+        <v>1</v>
+      </c>
+      <c r="BL32">
+        <v>1</v>
+      </c>
+      <c r="BM32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>361</v>
       </c>
-      <c r="AD32">
-        <v>2</v>
-      </c>
-      <c r="AM32">
-        <v>1</v>
-      </c>
-      <c r="AU32">
-        <v>1</v>
-      </c>
-      <c r="BF32">
+      <c r="AD33">
+        <v>2</v>
+      </c>
+      <c r="AM33">
+        <v>1</v>
+      </c>
+      <c r="AU33">
+        <v>1</v>
+      </c>
+      <c r="BF33">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+    <row r="34" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>389</v>
       </c>
-      <c r="BO33">
+      <c r="BO34">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34">
-        <v>2</v>
-      </c>
-      <c r="I34">
-        <v>2</v>
-      </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-      <c r="K34">
-        <v>2</v>
-      </c>
-      <c r="L34">
-        <v>1</v>
-      </c>
-      <c r="M34">
-        <v>2</v>
-      </c>
-      <c r="N34">
-        <v>1</v>
-      </c>
-      <c r="O34">
-        <v>1</v>
-      </c>
-      <c r="P34">
-        <v>2</v>
-      </c>
-      <c r="R34">
-        <v>1</v>
-      </c>
-      <c r="T34">
-        <v>1</v>
-      </c>
-      <c r="U34">
-        <v>2</v>
-      </c>
-      <c r="Y34">
-        <v>2</v>
-      </c>
-      <c r="AB34">
-        <v>2</v>
-      </c>
-      <c r="AD34">
-        <v>1</v>
-      </c>
-      <c r="AH34">
-        <v>1</v>
-      </c>
-      <c r="AJ34">
-        <v>1</v>
-      </c>
-      <c r="AN34">
-        <v>2</v>
-      </c>
-      <c r="AO34">
-        <v>1</v>
-      </c>
-      <c r="AP34">
-        <v>2</v>
-      </c>
-      <c r="AQ34">
-        <v>1</v>
-      </c>
-      <c r="AS34">
-        <v>2</v>
-      </c>
-      <c r="AW34">
-        <v>1</v>
-      </c>
-      <c r="AX34">
-        <v>1</v>
-      </c>
-      <c r="AY34">
-        <v>2</v>
-      </c>
-      <c r="AZ34">
-        <v>2</v>
-      </c>
-      <c r="BA34">
-        <v>1</v>
-      </c>
-      <c r="BB34">
-        <v>2</v>
-      </c>
-      <c r="BC34">
+    <row r="35" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>2</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>2</v>
+      </c>
+      <c r="R35">
+        <v>1</v>
+      </c>
+      <c r="T35">
+        <v>1</v>
+      </c>
+      <c r="U35">
+        <v>2</v>
+      </c>
+      <c r="Y35">
+        <v>2</v>
+      </c>
+      <c r="AB35">
+        <v>2</v>
+      </c>
+      <c r="AD35">
+        <v>1</v>
+      </c>
+      <c r="AH35">
+        <v>1</v>
+      </c>
+      <c r="AJ35">
+        <v>1</v>
+      </c>
+      <c r="AN35">
+        <v>2</v>
+      </c>
+      <c r="AO35">
+        <v>1</v>
+      </c>
+      <c r="AP35">
+        <v>2</v>
+      </c>
+      <c r="AQ35">
+        <v>1</v>
+      </c>
+      <c r="AS35">
+        <v>2</v>
+      </c>
+      <c r="AW35">
+        <v>1</v>
+      </c>
+      <c r="AX35">
+        <v>1</v>
+      </c>
+      <c r="AY35">
+        <v>2</v>
+      </c>
+      <c r="AZ35">
+        <v>2</v>
+      </c>
+      <c r="BA35">
+        <v>1</v>
+      </c>
+      <c r="BB35">
+        <v>2</v>
+      </c>
+      <c r="BC35">
         <v>4</v>
       </c>
-      <c r="BD34">
-        <v>1</v>
-      </c>
-      <c r="BE34">
-        <v>1</v>
-      </c>
-      <c r="BG34">
-        <v>2</v>
-      </c>
-      <c r="BH34">
+      <c r="BD35">
+        <v>1</v>
+      </c>
+      <c r="BE35">
+        <v>1</v>
+      </c>
+      <c r="BG35">
+        <v>2</v>
+      </c>
+      <c r="BH35">
         <v>3</v>
       </c>
-      <c r="BJ34">
-        <v>1</v>
-      </c>
-      <c r="BM34">
+      <c r="BJ35">
+        <v>1</v>
+      </c>
+      <c r="BM35">
         <v>3</v>
       </c>
-      <c r="BN34">
-        <v>1</v>
-      </c>
-      <c r="BP34">
-        <v>1</v>
-      </c>
-      <c r="BR34">
+      <c r="BN35">
+        <v>1</v>
+      </c>
+      <c r="BP35">
+        <v>1</v>
+      </c>
+      <c r="BR35">
         <v>3</v>
       </c>
-      <c r="BV34">
-        <v>1</v>
-      </c>
-      <c r="BW34">
+      <c r="BV35">
+        <v>1</v>
+      </c>
+      <c r="BW35">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="BX35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>351</v>
       </c>
-      <c r="Z35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="Z36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>9</v>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="G36">
-        <v>2</v>
-      </c>
-      <c r="H36">
-        <v>2</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-      <c r="K36">
-        <v>2</v>
-      </c>
-      <c r="L36">
-        <v>5</v>
-      </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-      <c r="O36">
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37">
+        <v>2</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>2</v>
+      </c>
+      <c r="L37">
+        <v>5</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="O37">
         <v>4</v>
       </c>
-      <c r="P36">
-        <v>1</v>
-      </c>
-      <c r="Q36">
-        <v>2</v>
-      </c>
-      <c r="T36">
+      <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="Q37">
+        <v>2</v>
+      </c>
+      <c r="T37">
         <v>6</v>
       </c>
-      <c r="X36">
-        <v>2</v>
-      </c>
-      <c r="Y36">
-        <v>2</v>
-      </c>
-      <c r="Z36">
-        <v>1</v>
-      </c>
-      <c r="AA36">
-        <v>1</v>
-      </c>
-      <c r="AB36">
-        <v>1</v>
-      </c>
-      <c r="AC36">
+      <c r="X37">
+        <v>2</v>
+      </c>
+      <c r="Y37">
+        <v>2</v>
+      </c>
+      <c r="Z37">
+        <v>1</v>
+      </c>
+      <c r="AA37">
+        <v>1</v>
+      </c>
+      <c r="AB37">
+        <v>1</v>
+      </c>
+      <c r="AC37">
         <v>3</v>
       </c>
-      <c r="AF36">
+      <c r="AF37">
         <v>4</v>
       </c>
-      <c r="AI36">
-        <v>1</v>
-      </c>
-      <c r="AL36">
-        <v>1</v>
-      </c>
-      <c r="AN36">
-        <v>1</v>
-      </c>
-      <c r="AR36">
-        <v>2</v>
-      </c>
-      <c r="AS36">
+      <c r="AI37">
+        <v>1</v>
+      </c>
+      <c r="AL37">
+        <v>1</v>
+      </c>
+      <c r="AN37">
+        <v>1</v>
+      </c>
+      <c r="AR37">
+        <v>2</v>
+      </c>
+      <c r="AS37">
         <v>3</v>
       </c>
-      <c r="AT36">
-        <v>1</v>
-      </c>
-      <c r="AW36">
-        <v>2</v>
-      </c>
-      <c r="AX36">
-        <v>5</v>
-      </c>
-      <c r="AY36">
+      <c r="AT37">
+        <v>1</v>
+      </c>
+      <c r="AW37">
+        <v>2</v>
+      </c>
+      <c r="AX37">
+        <v>5</v>
+      </c>
+      <c r="AY37">
         <v>3</v>
       </c>
-      <c r="AZ36">
-        <v>1</v>
-      </c>
-      <c r="BA36">
+      <c r="AZ37">
+        <v>1</v>
+      </c>
+      <c r="BA37">
         <v>3</v>
       </c>
-      <c r="BB36">
-        <v>2</v>
-      </c>
-      <c r="BD36">
+      <c r="BB37">
+        <v>2</v>
+      </c>
+      <c r="BD37">
         <v>3</v>
       </c>
-      <c r="BF36">
+      <c r="BF37">
         <v>3</v>
       </c>
-      <c r="BG36">
+      <c r="BG37">
         <v>4</v>
       </c>
-      <c r="BH36">
+      <c r="BH37">
         <v>3</v>
       </c>
-      <c r="BI36">
-        <v>2</v>
-      </c>
-      <c r="BJ36">
-        <v>1</v>
-      </c>
-      <c r="BL36">
-        <v>1</v>
-      </c>
-      <c r="BM36">
-        <v>2</v>
-      </c>
-      <c r="BN36">
-        <v>1</v>
-      </c>
-      <c r="BP36">
-        <v>1</v>
-      </c>
-      <c r="BQ36">
-        <v>2</v>
-      </c>
-      <c r="BR36">
+      <c r="BI37">
+        <v>2</v>
+      </c>
+      <c r="BJ37">
+        <v>1</v>
+      </c>
+      <c r="BL37">
+        <v>1</v>
+      </c>
+      <c r="BM37">
+        <v>2</v>
+      </c>
+      <c r="BN37">
+        <v>1</v>
+      </c>
+      <c r="BP37">
+        <v>1</v>
+      </c>
+      <c r="BQ37">
+        <v>2</v>
+      </c>
+      <c r="BR37">
         <v>3</v>
       </c>
-      <c r="BS36">
-        <v>2</v>
-      </c>
-      <c r="BV36">
-        <v>5</v>
-      </c>
-      <c r="BW36">
+      <c r="BS37">
+        <v>2</v>
+      </c>
+      <c r="BV37">
+        <v>5</v>
+      </c>
+      <c r="BW37">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+    <row r="38" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>394</v>
       </c>
-      <c r="BW37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="BW38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>381</v>
       </c>
-      <c r="BG38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="BG39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>20</v>
       </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="F39">
-        <v>2</v>
-      </c>
-      <c r="G39">
-        <v>2</v>
-      </c>
-      <c r="H39">
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40">
         <v>4</v>
       </c>
-      <c r="J39">
-        <v>2</v>
-      </c>
-      <c r="K39">
-        <v>2</v>
-      </c>
-      <c r="L39">
-        <v>1</v>
-      </c>
-      <c r="M39">
-        <v>1</v>
-      </c>
-      <c r="P39">
-        <v>1</v>
-      </c>
-      <c r="Q39">
-        <v>1</v>
-      </c>
-      <c r="R39">
+      <c r="J40">
+        <v>2</v>
+      </c>
+      <c r="K40">
+        <v>2</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="P40">
+        <v>1</v>
+      </c>
+      <c r="Q40">
+        <v>1</v>
+      </c>
+      <c r="R40">
         <v>3</v>
       </c>
-      <c r="S39">
-        <v>2</v>
-      </c>
-      <c r="T39">
-        <v>2</v>
-      </c>
-      <c r="U39">
-        <v>2</v>
-      </c>
-      <c r="W39">
+      <c r="S40">
+        <v>2</v>
+      </c>
+      <c r="T40">
+        <v>2</v>
+      </c>
+      <c r="U40">
+        <v>2</v>
+      </c>
+      <c r="W40">
         <v>3</v>
       </c>
-      <c r="X39">
+      <c r="X40">
         <v>3</v>
       </c>
-      <c r="Y39">
-        <v>2</v>
-      </c>
-      <c r="AA39">
-        <v>2</v>
-      </c>
-      <c r="AB39">
-        <v>2</v>
-      </c>
-      <c r="AC39">
-        <v>2</v>
-      </c>
-      <c r="AE39">
-        <v>2</v>
-      </c>
-      <c r="AF39">
-        <v>1</v>
-      </c>
-      <c r="AG39">
-        <v>2</v>
-      </c>
-      <c r="AJ39">
+      <c r="Y40">
+        <v>2</v>
+      </c>
+      <c r="AA40">
+        <v>2</v>
+      </c>
+      <c r="AB40">
+        <v>2</v>
+      </c>
+      <c r="AC40">
+        <v>2</v>
+      </c>
+      <c r="AE40">
+        <v>2</v>
+      </c>
+      <c r="AF40">
+        <v>1</v>
+      </c>
+      <c r="AG40">
+        <v>2</v>
+      </c>
+      <c r="AJ40">
         <v>4</v>
       </c>
-      <c r="AK39">
-        <v>2</v>
-      </c>
-      <c r="AM39">
-        <v>1</v>
-      </c>
-      <c r="AN39">
-        <v>1</v>
-      </c>
-      <c r="AO39">
-        <v>1</v>
-      </c>
-      <c r="AP39">
-        <v>1</v>
-      </c>
-      <c r="AU39">
-        <v>1</v>
-      </c>
-      <c r="AV39">
-        <v>1</v>
-      </c>
-      <c r="AW39">
-        <v>2</v>
-      </c>
-      <c r="BA39">
-        <v>1</v>
-      </c>
-      <c r="BH39">
-        <v>2</v>
-      </c>
-      <c r="BJ39">
-        <v>2</v>
-      </c>
-      <c r="BK39">
+      <c r="AK40">
+        <v>2</v>
+      </c>
+      <c r="AM40">
+        <v>1</v>
+      </c>
+      <c r="AN40">
+        <v>1</v>
+      </c>
+      <c r="AO40">
+        <v>1</v>
+      </c>
+      <c r="AP40">
+        <v>1</v>
+      </c>
+      <c r="AU40">
+        <v>1</v>
+      </c>
+      <c r="AV40">
+        <v>1</v>
+      </c>
+      <c r="AW40">
+        <v>2</v>
+      </c>
+      <c r="BA40">
+        <v>1</v>
+      </c>
+      <c r="BH40">
+        <v>2</v>
+      </c>
+      <c r="BJ40">
+        <v>2</v>
+      </c>
+      <c r="BK40">
         <v>3</v>
       </c>
-      <c r="BP39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="BP40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="41" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+    <row r="42" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>80</v>
       </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="F42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>61</v>
       </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="D43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>374</v>
       </c>
-      <c r="AW43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="AW44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>19</v>
       </c>
-      <c r="B44">
-        <v>2</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="F44">
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="F45">
         <v>4</v>
       </c>
-      <c r="G44">
+      <c r="G45">
         <v>3</v>
       </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="M44">
-        <v>2</v>
-      </c>
-      <c r="N44">
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>2</v>
+      </c>
+      <c r="N45">
         <v>3</v>
       </c>
-      <c r="T44">
-        <v>1</v>
-      </c>
-      <c r="X44">
-        <v>1</v>
-      </c>
-      <c r="AA44">
-        <v>2</v>
-      </c>
-      <c r="AB44">
-        <v>2</v>
-      </c>
-      <c r="AC44">
-        <v>1</v>
-      </c>
-      <c r="AD44">
-        <v>2</v>
-      </c>
-      <c r="AE44">
-        <v>1</v>
-      </c>
-      <c r="AG44">
-        <v>1</v>
-      </c>
-      <c r="AH44">
-        <v>2</v>
-      </c>
-      <c r="AJ44">
-        <v>1</v>
-      </c>
-      <c r="AM44">
+      <c r="T45">
+        <v>1</v>
+      </c>
+      <c r="X45">
+        <v>1</v>
+      </c>
+      <c r="AA45">
+        <v>2</v>
+      </c>
+      <c r="AB45">
+        <v>2</v>
+      </c>
+      <c r="AC45">
+        <v>1</v>
+      </c>
+      <c r="AD45">
+        <v>2</v>
+      </c>
+      <c r="AE45">
+        <v>1</v>
+      </c>
+      <c r="AG45">
+        <v>1</v>
+      </c>
+      <c r="AH45">
+        <v>2</v>
+      </c>
+      <c r="AJ45">
+        <v>1</v>
+      </c>
+      <c r="AM45">
         <v>4</v>
       </c>
-      <c r="AN44">
-        <v>1</v>
-      </c>
-      <c r="AP44">
-        <v>1</v>
-      </c>
-      <c r="AR44">
-        <v>1</v>
-      </c>
-      <c r="AS44">
-        <v>1</v>
-      </c>
-      <c r="AT44">
-        <v>1</v>
-      </c>
-      <c r="AV44">
-        <v>1</v>
-      </c>
-      <c r="AZ44">
-        <v>2</v>
-      </c>
-      <c r="BA44">
-        <v>1</v>
-      </c>
-      <c r="BC44">
+      <c r="AN45">
+        <v>1</v>
+      </c>
+      <c r="AP45">
+        <v>1</v>
+      </c>
+      <c r="AR45">
+        <v>1</v>
+      </c>
+      <c r="AS45">
+        <v>1</v>
+      </c>
+      <c r="AT45">
+        <v>1</v>
+      </c>
+      <c r="AV45">
+        <v>1</v>
+      </c>
+      <c r="AZ45">
+        <v>2</v>
+      </c>
+      <c r="BA45">
+        <v>1</v>
+      </c>
+      <c r="BC45">
         <v>3</v>
       </c>
-      <c r="BD44">
-        <v>1</v>
-      </c>
-      <c r="BI44">
-        <v>1</v>
-      </c>
-      <c r="BJ44">
-        <v>1</v>
-      </c>
-      <c r="BK44">
+      <c r="BD45">
+        <v>1</v>
+      </c>
+      <c r="BI45">
+        <v>1</v>
+      </c>
+      <c r="BJ45">
+        <v>1</v>
+      </c>
+      <c r="BK45">
         <v>3</v>
       </c>
-      <c r="BL44">
-        <v>2</v>
-      </c>
-      <c r="BM44">
-        <v>5</v>
-      </c>
-      <c r="BO44">
-        <v>1</v>
-      </c>
-      <c r="BP44">
+      <c r="BL45">
+        <v>2</v>
+      </c>
+      <c r="BM45">
+        <v>5</v>
+      </c>
+      <c r="BO45">
+        <v>1</v>
+      </c>
+      <c r="BP45">
         <v>3</v>
       </c>
-      <c r="BQ44">
+      <c r="BQ45">
         <v>3</v>
       </c>
-      <c r="BS44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="BS45">
+        <v>1</v>
+      </c>
+      <c r="BX45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>43</v>
       </c>
-      <c r="AQ45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+      <c r="AQ46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>68</v>
       </c>
-      <c r="E46">
-        <v>1</v>
-      </c>
-      <c r="I46">
-        <v>1</v>
-      </c>
-      <c r="N46">
-        <v>1</v>
-      </c>
-      <c r="W46">
-        <v>2</v>
-      </c>
-      <c r="AQ46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+      <c r="W47">
+        <v>2</v>
+      </c>
+      <c r="AQ47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>53</v>
       </c>
-      <c r="N47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="N48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>368</v>
       </c>
-      <c r="AM48">
-        <v>5</v>
-      </c>
-      <c r="BB48">
+      <c r="AM49">
+        <v>5</v>
+      </c>
+      <c r="BB49">
         <v>9</v>
       </c>
-      <c r="BN48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="BN49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>345</v>
       </c>
-      <c r="U49">
-        <v>1</v>
-      </c>
-      <c r="BR49">
-        <v>1</v>
-      </c>
-      <c r="BS49">
-        <v>1</v>
-      </c>
-      <c r="BT49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="U50">
+        <v>1</v>
+      </c>
+      <c r="BR50">
+        <v>1</v>
+      </c>
+      <c r="BS50">
+        <v>1</v>
+      </c>
+      <c r="BT50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>343</v>
       </c>
-      <c r="AN50">
-        <v>1</v>
-      </c>
-      <c r="BR50">
-        <v>1</v>
-      </c>
-      <c r="BS50">
-        <v>1</v>
-      </c>
-      <c r="BT50">
+      <c r="AN51">
+        <v>1</v>
+      </c>
+      <c r="BR51">
+        <v>1</v>
+      </c>
+      <c r="BS51">
+        <v>1</v>
+      </c>
+      <c r="BT51">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+    <row r="52" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>344</v>
       </c>
-      <c r="X51">
-        <v>1</v>
-      </c>
-      <c r="Y51">
-        <v>2</v>
-      </c>
-      <c r="AF51">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="X52">
+        <v>1</v>
+      </c>
+      <c r="Y52">
+        <v>2</v>
+      </c>
+      <c r="AF52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>10</v>
       </c>
-      <c r="B52">
-        <v>2</v>
-      </c>
-      <c r="C52">
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53">
         <v>3</v>
       </c>
-      <c r="F52">
-        <v>2</v>
-      </c>
-      <c r="I52">
-        <v>2</v>
-      </c>
-      <c r="J52">
-        <v>2</v>
-      </c>
-      <c r="K52">
-        <v>1</v>
-      </c>
-      <c r="L52">
-        <v>1</v>
-      </c>
-      <c r="M52">
-        <v>1</v>
-      </c>
-      <c r="O52">
-        <v>2</v>
-      </c>
-      <c r="R52">
+      <c r="F53">
+        <v>2</v>
+      </c>
+      <c r="I53">
+        <v>2</v>
+      </c>
+      <c r="J53">
+        <v>2</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <v>2</v>
+      </c>
+      <c r="R53">
         <v>3</v>
       </c>
-      <c r="S52">
-        <v>1</v>
-      </c>
-      <c r="T52">
-        <v>1</v>
-      </c>
-      <c r="V52">
-        <v>1</v>
-      </c>
-      <c r="W52">
+      <c r="S53">
+        <v>1</v>
+      </c>
+      <c r="T53">
+        <v>1</v>
+      </c>
+      <c r="V53">
+        <v>1</v>
+      </c>
+      <c r="W53">
         <v>3</v>
       </c>
-      <c r="X52">
-        <v>1</v>
-      </c>
-      <c r="Y52">
-        <v>1</v>
-      </c>
-      <c r="Z52">
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53">
+        <v>1</v>
+      </c>
+      <c r="Z53">
         <v>1.5</v>
       </c>
-      <c r="AC52">
-        <v>1</v>
-      </c>
-      <c r="AD52">
-        <v>2</v>
-      </c>
-      <c r="AE52">
-        <v>1</v>
-      </c>
-      <c r="AF52">
-        <v>2</v>
-      </c>
-      <c r="AH52">
-        <v>2</v>
-      </c>
-      <c r="AL52">
+      <c r="AC53">
+        <v>1</v>
+      </c>
+      <c r="AD53">
+        <v>2</v>
+      </c>
+      <c r="AE53">
+        <v>1</v>
+      </c>
+      <c r="AF53">
+        <v>2</v>
+      </c>
+      <c r="AH53">
+        <v>2</v>
+      </c>
+      <c r="AL53">
         <v>3</v>
       </c>
-      <c r="AP52">
-        <v>2</v>
-      </c>
-      <c r="AQ52">
+      <c r="AP53">
+        <v>2</v>
+      </c>
+      <c r="AQ53">
         <v>4</v>
       </c>
-      <c r="AR52">
+      <c r="AR53">
         <v>3</v>
       </c>
-      <c r="AS52">
+      <c r="AS53">
         <v>0.5</v>
       </c>
-      <c r="AU52">
-        <v>2</v>
-      </c>
-      <c r="AV52">
-        <v>1</v>
-      </c>
-      <c r="BC52">
-        <v>1</v>
-      </c>
-      <c r="BD52">
-        <v>1</v>
-      </c>
-      <c r="BE52">
+      <c r="AU53">
+        <v>2</v>
+      </c>
+      <c r="AV53">
+        <v>1</v>
+      </c>
+      <c r="BC53">
+        <v>1</v>
+      </c>
+      <c r="BD53">
+        <v>1</v>
+      </c>
+      <c r="BE53">
         <v>7</v>
       </c>
-      <c r="BH52">
-        <v>1</v>
-      </c>
-      <c r="BI52">
-        <v>1</v>
-      </c>
-      <c r="BJ52">
+      <c r="BH53">
+        <v>1</v>
+      </c>
+      <c r="BI53">
+        <v>1</v>
+      </c>
+      <c r="BJ53">
         <v>3</v>
       </c>
-      <c r="BK52">
+      <c r="BK53">
         <v>3</v>
       </c>
-      <c r="BL52">
-        <v>1</v>
-      </c>
-      <c r="BM52">
-        <v>1</v>
-      </c>
-      <c r="BN52">
+      <c r="BL53">
+        <v>1</v>
+      </c>
+      <c r="BM53">
+        <v>1</v>
+      </c>
+      <c r="BN53">
         <v>4</v>
       </c>
-      <c r="BP52">
-        <v>1</v>
-      </c>
-      <c r="BQ52">
+      <c r="BP53">
+        <v>1</v>
+      </c>
+      <c r="BQ53">
         <v>3</v>
       </c>
-      <c r="BR52">
-        <v>1</v>
-      </c>
-      <c r="BT52">
-        <v>1</v>
-      </c>
-      <c r="BV52">
-        <v>1</v>
-      </c>
-      <c r="BW52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="BR53">
+        <v>1</v>
+      </c>
+      <c r="BT53">
+        <v>1</v>
+      </c>
+      <c r="BV53">
+        <v>1</v>
+      </c>
+      <c r="BW53">
+        <v>2</v>
+      </c>
+      <c r="BX53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>46</v>
       </c>
-      <c r="B53">
-        <v>1</v>
-      </c>
-      <c r="O53">
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="O54">
         <v>3</v>
       </c>
-      <c r="P53">
-        <v>1</v>
-      </c>
-      <c r="Q53">
-        <v>2</v>
-      </c>
-      <c r="AM53">
-        <v>1</v>
-      </c>
-      <c r="AN53">
-        <v>1</v>
-      </c>
-      <c r="AP53">
-        <v>1</v>
-      </c>
-      <c r="AS53">
-        <v>1</v>
-      </c>
-      <c r="AV53">
-        <v>1</v>
-      </c>
-      <c r="AX53">
-        <v>5</v>
-      </c>
-      <c r="AY53">
-        <v>1</v>
-      </c>
-      <c r="BA53">
-        <v>2</v>
-      </c>
-      <c r="BB53">
+      <c r="P54">
+        <v>1</v>
+      </c>
+      <c r="Q54">
+        <v>2</v>
+      </c>
+      <c r="AM54">
+        <v>1</v>
+      </c>
+      <c r="AN54">
+        <v>1</v>
+      </c>
+      <c r="AP54">
+        <v>1</v>
+      </c>
+      <c r="AS54">
+        <v>1</v>
+      </c>
+      <c r="AV54">
+        <v>1</v>
+      </c>
+      <c r="AX54">
+        <v>5</v>
+      </c>
+      <c r="AY54">
+        <v>1</v>
+      </c>
+      <c r="BA54">
+        <v>2</v>
+      </c>
+      <c r="BB54">
         <v>4</v>
       </c>
-      <c r="BE53">
+      <c r="BE54">
         <v>3</v>
       </c>
-      <c r="BF53">
-        <v>2</v>
-      </c>
-      <c r="BH53">
+      <c r="BF54">
+        <v>2</v>
+      </c>
+      <c r="BH54">
         <v>3</v>
       </c>
-      <c r="BK53">
-        <v>1</v>
-      </c>
-      <c r="BT53">
+      <c r="BK54">
+        <v>1</v>
+      </c>
+      <c r="BT54">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+    <row r="55" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="55" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+    <row r="56" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>3</v>
       </c>
-      <c r="F55">
+      <c r="F56">
         <v>3</v>
       </c>
-      <c r="L55">
-        <v>1</v>
-      </c>
-      <c r="S55">
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="S56">
         <v>3</v>
       </c>
-      <c r="AH55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+      <c r="AH56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="57" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+    <row r="58" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>56</v>
       </c>
-      <c r="C57">
+      <c r="C58">
         <v>3</v>
       </c>
-      <c r="E57">
-        <v>2</v>
-      </c>
-      <c r="F57">
-        <v>1</v>
-      </c>
-      <c r="G57">
-        <v>2</v>
-      </c>
-      <c r="I57">
-        <v>1</v>
-      </c>
-      <c r="J57">
-        <v>1</v>
-      </c>
-      <c r="K57">
-        <v>1</v>
-      </c>
-      <c r="L57">
-        <v>1</v>
-      </c>
-      <c r="M57">
-        <v>1</v>
-      </c>
-      <c r="P57">
-        <v>1</v>
-      </c>
-      <c r="R57">
-        <v>1</v>
-      </c>
-      <c r="S57">
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>2</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58">
+        <v>1</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+      <c r="P58">
+        <v>1</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="S58">
         <v>4</v>
       </c>
-      <c r="T57">
-        <v>1</v>
-      </c>
-      <c r="V57">
-        <v>1</v>
-      </c>
-      <c r="W57">
-        <v>2</v>
-      </c>
-      <c r="Z57">
-        <v>2</v>
-      </c>
-      <c r="AA57">
-        <v>1</v>
-      </c>
-      <c r="AB57">
+      <c r="T58">
+        <v>1</v>
+      </c>
+      <c r="V58">
+        <v>1</v>
+      </c>
+      <c r="W58">
+        <v>2</v>
+      </c>
+      <c r="Z58">
+        <v>2</v>
+      </c>
+      <c r="AA58">
+        <v>1</v>
+      </c>
+      <c r="AB58">
         <v>4</v>
       </c>
-      <c r="AC57">
-        <v>1</v>
-      </c>
-      <c r="AD57">
-        <v>1</v>
-      </c>
-      <c r="AX57">
-        <v>1</v>
-      </c>
-      <c r="AY57">
-        <v>1</v>
-      </c>
-      <c r="AZ57">
-        <v>2</v>
-      </c>
-      <c r="BD57">
-        <v>1</v>
-      </c>
-      <c r="BF57">
-        <v>1</v>
-      </c>
-      <c r="BH57">
-        <v>1</v>
-      </c>
-      <c r="BI57">
-        <v>1</v>
-      </c>
-      <c r="BJ57">
-        <v>2</v>
-      </c>
-      <c r="BK57">
-        <v>1</v>
-      </c>
-      <c r="BL57">
-        <v>2</v>
-      </c>
-      <c r="BM57">
-        <v>2</v>
-      </c>
-      <c r="BN57">
-        <v>2</v>
-      </c>
-      <c r="BO57">
-        <v>1</v>
-      </c>
-      <c r="BP57">
-        <v>1</v>
-      </c>
-      <c r="BR57">
-        <v>1</v>
-      </c>
-      <c r="BS57">
-        <v>2</v>
-      </c>
-      <c r="BU57">
-        <v>2</v>
-      </c>
-      <c r="BV57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+      <c r="AC58">
+        <v>1</v>
+      </c>
+      <c r="AD58">
+        <v>1</v>
+      </c>
+      <c r="AX58">
+        <v>1</v>
+      </c>
+      <c r="AY58">
+        <v>1</v>
+      </c>
+      <c r="AZ58">
+        <v>2</v>
+      </c>
+      <c r="BD58">
+        <v>1</v>
+      </c>
+      <c r="BF58">
+        <v>1</v>
+      </c>
+      <c r="BH58">
+        <v>1</v>
+      </c>
+      <c r="BI58">
+        <v>1</v>
+      </c>
+      <c r="BJ58">
+        <v>2</v>
+      </c>
+      <c r="BK58">
+        <v>1</v>
+      </c>
+      <c r="BL58">
+        <v>2</v>
+      </c>
+      <c r="BM58">
+        <v>2</v>
+      </c>
+      <c r="BN58">
+        <v>2</v>
+      </c>
+      <c r="BO58">
+        <v>1</v>
+      </c>
+      <c r="BP58">
+        <v>1</v>
+      </c>
+      <c r="BR58">
+        <v>1</v>
+      </c>
+      <c r="BS58">
+        <v>2</v>
+      </c>
+      <c r="BU58">
+        <v>2</v>
+      </c>
+      <c r="BV58">
+        <v>1</v>
+      </c>
+      <c r="BX58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>369</v>
       </c>
-      <c r="AN58">
+      <c r="AN59">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+    <row r="60" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>387</v>
       </c>
-      <c r="BN59">
+      <c r="BN60">
         <v>3</v>
       </c>
-      <c r="BO59">
-        <v>2</v>
-      </c>
-      <c r="BQ59">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="BO60">
+        <v>2</v>
+      </c>
+      <c r="BQ60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>60</v>
       </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="BF60">
-        <v>1</v>
-      </c>
-      <c r="BT60">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="BF61">
+        <v>1</v>
+      </c>
+      <c r="BT61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>340</v>
       </c>
-      <c r="Q61">
-        <v>1</v>
-      </c>
-      <c r="U61">
-        <v>1</v>
-      </c>
-      <c r="W61">
-        <v>1</v>
-      </c>
-      <c r="X61">
+      <c r="Q62">
+        <v>1</v>
+      </c>
+      <c r="U62">
+        <v>1</v>
+      </c>
+      <c r="W62">
+        <v>1</v>
+      </c>
+      <c r="X62">
         <v>3</v>
       </c>
-      <c r="Y61">
-        <v>1</v>
-      </c>
-      <c r="Z61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="Y62">
+        <v>1</v>
+      </c>
+      <c r="Z62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="63" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+    <row r="64" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+    <row r="65" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>55</v>
       </c>
-      <c r="B64">
-        <v>2</v>
-      </c>
-      <c r="C64">
-        <v>1</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64">
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
         <v>3</v>
       </c>
-      <c r="G64">
-        <v>2</v>
-      </c>
-      <c r="H64">
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65">
         <v>3</v>
       </c>
-      <c r="J64">
-        <v>1</v>
-      </c>
-      <c r="K64">
-        <v>1</v>
-      </c>
-      <c r="M64">
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="M65">
         <v>3</v>
       </c>
-      <c r="N64">
+      <c r="N65">
         <v>4</v>
       </c>
-      <c r="X64">
+      <c r="X65">
         <v>6</v>
       </c>
-      <c r="Y64">
-        <v>5</v>
-      </c>
-      <c r="Z64">
-        <v>1</v>
-      </c>
-      <c r="AD64">
-        <v>2</v>
-      </c>
-      <c r="AG64">
+      <c r="Y65">
+        <v>5</v>
+      </c>
+      <c r="Z65">
+        <v>1</v>
+      </c>
+      <c r="AD65">
+        <v>2</v>
+      </c>
+      <c r="AG65">
         <v>3</v>
       </c>
-      <c r="AJ64">
-        <v>2</v>
-      </c>
-      <c r="AM64">
-        <v>2</v>
-      </c>
-      <c r="AO64">
+      <c r="AJ65">
+        <v>2</v>
+      </c>
+      <c r="AM65">
+        <v>2</v>
+      </c>
+      <c r="AO65">
         <v>3</v>
       </c>
-      <c r="AQ64">
-        <v>2</v>
-      </c>
-      <c r="AT64">
-        <v>1</v>
-      </c>
-      <c r="AU64">
+      <c r="AQ65">
+        <v>2</v>
+      </c>
+      <c r="AT65">
+        <v>1</v>
+      </c>
+      <c r="AU65">
         <v>4</v>
       </c>
-      <c r="AV64">
-        <v>2</v>
-      </c>
-      <c r="AX64">
-        <v>1</v>
-      </c>
-      <c r="AY64">
-        <v>2</v>
-      </c>
-      <c r="AZ64">
-        <v>1</v>
-      </c>
-      <c r="BA64">
+      <c r="AV65">
+        <v>2</v>
+      </c>
+      <c r="AX65">
+        <v>1</v>
+      </c>
+      <c r="AY65">
+        <v>2</v>
+      </c>
+      <c r="AZ65">
+        <v>1</v>
+      </c>
+      <c r="BA65">
         <v>4</v>
       </c>
-      <c r="BB64">
-        <v>2</v>
-      </c>
-      <c r="BH64">
-        <v>1</v>
-      </c>
-      <c r="BR64">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="BB65">
+        <v>2</v>
+      </c>
+      <c r="BH65">
+        <v>1</v>
+      </c>
+      <c r="BR65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+    <row r="67" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>81</v>
       </c>
-      <c r="G66">
+      <c r="G67">
         <v>3</v>
       </c>
-      <c r="K66">
-        <v>1</v>
-      </c>
-      <c r="BG66">
-        <v>2</v>
-      </c>
-      <c r="BN66">
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="BG67">
+        <v>2</v>
+      </c>
+      <c r="BN67">
         <v>4</v>
       </c>
-      <c r="BP66">
-        <v>1</v>
-      </c>
-      <c r="BR66">
-        <v>2</v>
-      </c>
-      <c r="BS66">
+      <c r="BP67">
+        <v>1</v>
+      </c>
+      <c r="BR67">
+        <v>2</v>
+      </c>
+      <c r="BS67">
         <v>3</v>
       </c>
-      <c r="BU66">
+      <c r="BU67">
         <v>3</v>
       </c>
-      <c r="BV66">
-        <v>2</v>
-      </c>
-      <c r="BW66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+      <c r="BV67">
+        <v>2</v>
+      </c>
+      <c r="BW67">
+        <v>2</v>
+      </c>
+      <c r="BX67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>63</v>
       </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="AF67">
-        <v>2</v>
-      </c>
-      <c r="AQ67">
+      <c r="B68">
+        <v>2</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="AF68">
+        <v>2</v>
+      </c>
+      <c r="AQ68">
         <v>3</v>
       </c>
-      <c r="BF67">
-        <v>1</v>
-      </c>
-      <c r="BM67">
-        <v>1</v>
-      </c>
-      <c r="BW67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="BF68">
+        <v>1</v>
+      </c>
+      <c r="BM68">
+        <v>1</v>
+      </c>
+      <c r="BW68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="69" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+    <row r="70" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>22</v>
       </c>
-      <c r="Y69">
-        <v>1</v>
-      </c>
-      <c r="AB69">
-        <v>2</v>
-      </c>
-      <c r="AD69">
+      <c r="Y70">
+        <v>1</v>
+      </c>
+      <c r="AB70">
+        <v>2</v>
+      </c>
+      <c r="AD70">
         <v>3</v>
       </c>
-      <c r="AI69">
-        <v>1</v>
-      </c>
-      <c r="AR69">
+      <c r="AI70">
+        <v>1</v>
+      </c>
+      <c r="AR70">
         <v>4</v>
       </c>
-      <c r="AV69">
+      <c r="AV70">
         <v>3</v>
       </c>
-      <c r="BA69">
-        <v>2</v>
-      </c>
-      <c r="BB69">
-        <v>5</v>
-      </c>
-      <c r="BE69">
+      <c r="BA70">
+        <v>2</v>
+      </c>
+      <c r="BB70">
+        <v>5</v>
+      </c>
+      <c r="BE70">
         <v>6</v>
       </c>
-      <c r="BS69">
-        <v>1</v>
-      </c>
-      <c r="BT69">
-        <v>1</v>
-      </c>
-      <c r="BU69">
-        <v>2</v>
-      </c>
-      <c r="BV69">
+      <c r="BS70">
+        <v>1</v>
+      </c>
+      <c r="BT70">
+        <v>1</v>
+      </c>
+      <c r="BU70">
+        <v>2</v>
+      </c>
+      <c r="BV70">
         <v>3</v>
       </c>
-    </row>
-    <row r="70" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+      <c r="BX70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>376</v>
       </c>
-      <c r="AU70">
-        <v>1</v>
-      </c>
-      <c r="AV70">
-        <v>1</v>
-      </c>
-      <c r="AW70">
+      <c r="AU71">
+        <v>1</v>
+      </c>
+      <c r="AV71">
+        <v>1</v>
+      </c>
+      <c r="AW71">
         <v>3</v>
       </c>
-      <c r="AX70">
-        <v>1</v>
-      </c>
-      <c r="AZ70">
-        <v>1</v>
-      </c>
-      <c r="BC70">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+      <c r="AX71">
+        <v>1</v>
+      </c>
+      <c r="AZ71">
+        <v>1</v>
+      </c>
+      <c r="BC71">
+        <v>2</v>
+      </c>
+      <c r="BX71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>44</v>
       </c>
-      <c r="N71">
+      <c r="N72">
         <v>3</v>
       </c>
-      <c r="S71">
-        <v>2</v>
-      </c>
-      <c r="AG71">
-        <v>2</v>
-      </c>
-      <c r="AI71">
-        <v>1</v>
-      </c>
-      <c r="AP71">
-        <v>2</v>
-      </c>
-      <c r="AQ71">
-        <v>1</v>
-      </c>
-      <c r="AR71">
+      <c r="S72">
+        <v>2</v>
+      </c>
+      <c r="AG72">
+        <v>2</v>
+      </c>
+      <c r="AI72">
+        <v>1</v>
+      </c>
+      <c r="AP72">
+        <v>2</v>
+      </c>
+      <c r="AQ72">
+        <v>1</v>
+      </c>
+      <c r="AR72">
         <v>3</v>
       </c>
-      <c r="AW71">
-        <v>1</v>
-      </c>
-      <c r="BA71">
-        <v>1</v>
-      </c>
-      <c r="BE71">
-        <v>1</v>
-      </c>
-      <c r="BI71">
-        <v>2</v>
-      </c>
-      <c r="BL71">
-        <v>2</v>
-      </c>
-      <c r="BN71">
-        <v>2</v>
-      </c>
-      <c r="BO71">
-        <v>1</v>
-      </c>
-      <c r="BP71">
-        <v>1</v>
-      </c>
-      <c r="BR71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+      <c r="AW72">
+        <v>1</v>
+      </c>
+      <c r="BA72">
+        <v>1</v>
+      </c>
+      <c r="BE72">
+        <v>1</v>
+      </c>
+      <c r="BI72">
+        <v>2</v>
+      </c>
+      <c r="BL72">
+        <v>2</v>
+      </c>
+      <c r="BN72">
+        <v>2</v>
+      </c>
+      <c r="BO72">
+        <v>1</v>
+      </c>
+      <c r="BP72">
+        <v>1</v>
+      </c>
+      <c r="BR72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>379</v>
       </c>
-      <c r="BF72">
-        <v>1</v>
-      </c>
-      <c r="BG72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+      <c r="BF73">
+        <v>1</v>
+      </c>
+      <c r="BG73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>8</v>
       </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="H73">
-        <v>1</v>
-      </c>
-      <c r="J73">
-        <v>2</v>
-      </c>
-      <c r="Q73">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>2</v>
+      </c>
+      <c r="Q74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="75" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+    <row r="76" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>82</v>
       </c>
-      <c r="B75">
-        <v>2</v>
-      </c>
-      <c r="C75">
-        <v>2</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="E75">
-        <v>2</v>
-      </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
-      <c r="G75">
-        <v>2</v>
-      </c>
-      <c r="H75">
-        <v>2</v>
-      </c>
-      <c r="I75">
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+      <c r="H76">
+        <v>2</v>
+      </c>
+      <c r="I76">
         <v>3</v>
       </c>
-      <c r="J75">
+      <c r="J76">
         <v>4</v>
       </c>
-      <c r="L75">
+      <c r="L76">
         <v>4</v>
       </c>
-      <c r="M75">
-        <v>1</v>
-      </c>
-      <c r="N75">
-        <v>2</v>
-      </c>
-      <c r="O75">
-        <v>1</v>
-      </c>
-      <c r="P75">
-        <v>1</v>
-      </c>
-      <c r="Q75">
-        <v>1</v>
-      </c>
-      <c r="R75">
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76">
+        <v>2</v>
+      </c>
+      <c r="O76">
+        <v>1</v>
+      </c>
+      <c r="P76">
+        <v>1</v>
+      </c>
+      <c r="Q76">
+        <v>1</v>
+      </c>
+      <c r="R76">
         <v>3</v>
       </c>
-      <c r="S75">
+      <c r="S76">
         <v>3</v>
       </c>
-      <c r="U75">
+      <c r="U76">
         <v>3</v>
       </c>
-      <c r="V75">
-        <v>1</v>
-      </c>
-      <c r="W75">
+      <c r="V76">
+        <v>1</v>
+      </c>
+      <c r="W76">
         <v>3</v>
       </c>
-      <c r="AC75">
-        <v>1</v>
-      </c>
-      <c r="AF75">
-        <v>1</v>
-      </c>
-      <c r="AH75">
-        <v>2</v>
-      </c>
-      <c r="AI75">
+      <c r="AC76">
+        <v>1</v>
+      </c>
+      <c r="AF76">
+        <v>1</v>
+      </c>
+      <c r="AH76">
+        <v>2</v>
+      </c>
+      <c r="AI76">
         <v>3</v>
       </c>
-      <c r="AJ75">
-        <v>1</v>
-      </c>
-      <c r="AK75">
+      <c r="AJ76">
+        <v>1</v>
+      </c>
+      <c r="AK76">
         <v>4</v>
       </c>
-      <c r="AL75">
+      <c r="AL76">
         <v>3</v>
       </c>
-      <c r="AN75">
-        <v>1</v>
-      </c>
-      <c r="AP75">
-        <v>2</v>
-      </c>
-      <c r="AT75">
-        <v>2</v>
-      </c>
-      <c r="AU75">
+      <c r="AN76">
+        <v>1</v>
+      </c>
+      <c r="AP76">
+        <v>2</v>
+      </c>
+      <c r="AT76">
+        <v>2</v>
+      </c>
+      <c r="AU76">
         <v>3</v>
       </c>
-      <c r="AV75">
-        <v>1</v>
-      </c>
-      <c r="AW75">
-        <v>1</v>
-      </c>
-      <c r="AX75">
-        <v>1</v>
-      </c>
-      <c r="AY75">
-        <v>1</v>
-      </c>
-      <c r="AZ75">
-        <v>2</v>
-      </c>
-      <c r="BC75">
-        <v>2</v>
-      </c>
-      <c r="BD75">
-        <v>1</v>
-      </c>
-      <c r="BF75">
-        <v>2</v>
-      </c>
-      <c r="BH75">
+      <c r="AV76">
+        <v>1</v>
+      </c>
+      <c r="AW76">
+        <v>1</v>
+      </c>
+      <c r="AX76">
+        <v>1</v>
+      </c>
+      <c r="AY76">
+        <v>1</v>
+      </c>
+      <c r="AZ76">
+        <v>2</v>
+      </c>
+      <c r="BC76">
+        <v>2</v>
+      </c>
+      <c r="BD76">
+        <v>1</v>
+      </c>
+      <c r="BF76">
+        <v>2</v>
+      </c>
+      <c r="BH76">
         <v>3</v>
       </c>
-      <c r="BI75">
-        <v>1</v>
-      </c>
-      <c r="BJ75">
-        <v>2</v>
-      </c>
-      <c r="BK75">
+      <c r="BI76">
+        <v>1</v>
+      </c>
+      <c r="BJ76">
+        <v>2</v>
+      </c>
+      <c r="BK76">
         <v>3</v>
       </c>
-      <c r="BM75">
-        <v>2</v>
-      </c>
-      <c r="BN75">
+      <c r="BM76">
+        <v>2</v>
+      </c>
+      <c r="BN76">
         <v>3</v>
       </c>
-      <c r="BU75">
-        <v>1</v>
-      </c>
-      <c r="BV75">
+      <c r="BU76">
+        <v>1</v>
+      </c>
+      <c r="BV76">
         <v>3</v>
       </c>
-    </row>
-    <row r="76" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+      <c r="BX76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>49</v>
       </c>
-      <c r="G76">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+      <c r="G77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="78" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+    <row r="79" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>85</v>
       </c>
-      <c r="K78">
+      <c r="K79">
         <v>4</v>
       </c>
-      <c r="L78">
-        <v>2</v>
-      </c>
-      <c r="M78">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>5</v>
-      </c>
-      <c r="B79">
-        <v>1</v>
-      </c>
-      <c r="C79">
-        <v>2</v>
-      </c>
-      <c r="D79">
-        <v>2</v>
-      </c>
-      <c r="E79">
+      <c r="L79">
+        <v>2</v>
+      </c>
+      <c r="M79">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+      <c r="E80">
         <v>3</v>
       </c>
-      <c r="F79">
-        <v>2</v>
-      </c>
-      <c r="G79">
+      <c r="F80">
+        <v>2</v>
+      </c>
+      <c r="G80">
         <v>3</v>
       </c>
-      <c r="H79">
-        <v>1</v>
-      </c>
-      <c r="M79">
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="M80">
         <v>4</v>
       </c>
-      <c r="N79">
+      <c r="N80">
         <v>6</v>
       </c>
-      <c r="P79">
-        <v>2</v>
-      </c>
-      <c r="Q79">
-        <v>1</v>
-      </c>
-      <c r="R79">
-        <v>2</v>
-      </c>
-      <c r="S79">
+      <c r="P80">
+        <v>2</v>
+      </c>
+      <c r="Q80">
+        <v>1</v>
+      </c>
+      <c r="R80">
+        <v>2</v>
+      </c>
+      <c r="S80">
         <v>3</v>
       </c>
-      <c r="V79">
-        <v>2</v>
-      </c>
-      <c r="W79">
-        <v>1</v>
-      </c>
-      <c r="X79">
-        <v>1</v>
-      </c>
-      <c r="Y79">
+      <c r="V80">
+        <v>2</v>
+      </c>
+      <c r="W80">
+        <v>1</v>
+      </c>
+      <c r="X80">
+        <v>1</v>
+      </c>
+      <c r="Y80">
         <v>4</v>
       </c>
-      <c r="Z79">
-        <v>5</v>
-      </c>
-      <c r="AA79">
-        <v>1</v>
-      </c>
-      <c r="AB79">
+      <c r="Z80">
+        <v>5</v>
+      </c>
+      <c r="AA80">
+        <v>1</v>
+      </c>
+      <c r="AB80">
         <v>3</v>
       </c>
-      <c r="AC79">
+      <c r="AC80">
         <v>4</v>
       </c>
-      <c r="AD79">
+      <c r="AD80">
         <v>3</v>
       </c>
-      <c r="AE79">
+      <c r="AE80">
         <v>3</v>
       </c>
-      <c r="AF79">
-        <v>2</v>
-      </c>
-      <c r="AG79">
-        <v>5</v>
-      </c>
-      <c r="AH79">
+      <c r="AF80">
+        <v>2</v>
+      </c>
+      <c r="AG80">
+        <v>5</v>
+      </c>
+      <c r="AH80">
         <v>7</v>
       </c>
-      <c r="AI79">
+      <c r="AI80">
         <v>3</v>
       </c>
-      <c r="AJ79">
-        <v>1</v>
-      </c>
-      <c r="AK79">
-        <v>1</v>
-      </c>
-      <c r="AL79">
+      <c r="AJ80">
+        <v>1</v>
+      </c>
+      <c r="AK80">
+        <v>1</v>
+      </c>
+      <c r="AL80">
         <v>6</v>
       </c>
-      <c r="AR79">
+      <c r="AR80">
         <v>3</v>
       </c>
-      <c r="AS79">
-        <v>2</v>
-      </c>
-      <c r="AV79">
-        <v>2</v>
-      </c>
-      <c r="AW79">
-        <v>1</v>
-      </c>
-      <c r="AX79">
+      <c r="AS80">
+        <v>2</v>
+      </c>
+      <c r="AV80">
+        <v>2</v>
+      </c>
+      <c r="AW80">
+        <v>1</v>
+      </c>
+      <c r="AX80">
         <v>4</v>
       </c>
-      <c r="AY79">
+      <c r="AY80">
         <v>3</v>
       </c>
-      <c r="AZ79">
+      <c r="AZ80">
         <v>4</v>
       </c>
-      <c r="BA79">
-        <v>5</v>
-      </c>
-      <c r="BB79">
+      <c r="BA80">
+        <v>5</v>
+      </c>
+      <c r="BB80">
         <v>6</v>
       </c>
-      <c r="BC79">
-        <v>2</v>
-      </c>
-      <c r="BD79">
-        <v>2</v>
-      </c>
-      <c r="BE79">
+      <c r="BC80">
+        <v>2</v>
+      </c>
+      <c r="BD80">
+        <v>2</v>
+      </c>
+      <c r="BE80">
         <v>7</v>
       </c>
-      <c r="BG79">
+      <c r="BG80">
         <v>4</v>
       </c>
-      <c r="BH79">
+      <c r="BH80">
         <v>3</v>
       </c>
-      <c r="BI79">
+      <c r="BI80">
         <v>4</v>
       </c>
-      <c r="BK79">
-        <v>1</v>
-      </c>
-      <c r="BL79">
+      <c r="BK80">
+        <v>1</v>
+      </c>
+      <c r="BL80">
         <v>8</v>
       </c>
-      <c r="BM79">
+      <c r="BM80">
         <v>4</v>
       </c>
-      <c r="BN79">
-        <v>5</v>
-      </c>
-      <c r="BO79">
+      <c r="BN80">
+        <v>5</v>
+      </c>
+      <c r="BO80">
         <v>3</v>
       </c>
-      <c r="BP79">
-        <v>1</v>
-      </c>
-      <c r="BQ79">
-        <v>1</v>
-      </c>
-      <c r="BR79">
+      <c r="BP80">
+        <v>1</v>
+      </c>
+      <c r="BQ80">
+        <v>1</v>
+      </c>
+      <c r="BR80">
         <v>3</v>
       </c>
-      <c r="BS79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="BS80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>45</v>
       </c>
-      <c r="K80">
-        <v>1</v>
-      </c>
-      <c r="BJ80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="BJ81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>367</v>
       </c>
-      <c r="B81">
-        <v>1</v>
-      </c>
-      <c r="D81">
-        <v>1</v>
-      </c>
-      <c r="E81">
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
         <v>3</v>
       </c>
-      <c r="O81">
-        <v>2</v>
-      </c>
-      <c r="P81">
-        <v>2</v>
-      </c>
-      <c r="Q81">
-        <v>1</v>
-      </c>
-      <c r="R81">
-        <v>1</v>
-      </c>
-      <c r="AD81">
-        <v>1</v>
-      </c>
-      <c r="AE81">
-        <v>1</v>
-      </c>
-      <c r="AG81">
-        <v>1</v>
-      </c>
-      <c r="AH81">
-        <v>2</v>
-      </c>
-      <c r="AL81">
+      <c r="O82">
+        <v>2</v>
+      </c>
+      <c r="P82">
+        <v>2</v>
+      </c>
+      <c r="Q82">
+        <v>1</v>
+      </c>
+      <c r="R82">
+        <v>1</v>
+      </c>
+      <c r="AD82">
+        <v>1</v>
+      </c>
+      <c r="AE82">
+        <v>1</v>
+      </c>
+      <c r="AG82">
+        <v>1</v>
+      </c>
+      <c r="AH82">
+        <v>2</v>
+      </c>
+      <c r="AL82">
         <v>3</v>
       </c>
-      <c r="AM81">
-        <v>2</v>
-      </c>
-      <c r="AN81">
-        <v>1</v>
-      </c>
-      <c r="AO81">
-        <v>1</v>
-      </c>
-      <c r="AR81">
-        <v>1</v>
-      </c>
-      <c r="AS81">
-        <v>1</v>
-      </c>
-      <c r="AT81">
-        <v>1</v>
-      </c>
-      <c r="AV81">
-        <v>1</v>
-      </c>
-      <c r="AW81">
-        <v>2</v>
-      </c>
-      <c r="BD81">
-        <v>1</v>
-      </c>
-      <c r="BF81">
-        <v>1</v>
-      </c>
-      <c r="BI81">
-        <v>1</v>
-      </c>
-      <c r="BU81">
-        <v>2</v>
-      </c>
-      <c r="BW81">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="AM82">
+        <v>2</v>
+      </c>
+      <c r="AN82">
+        <v>1</v>
+      </c>
+      <c r="AO82">
+        <v>1</v>
+      </c>
+      <c r="AR82">
+        <v>1</v>
+      </c>
+      <c r="AS82">
+        <v>1</v>
+      </c>
+      <c r="AT82">
+        <v>1</v>
+      </c>
+      <c r="AV82">
+        <v>1</v>
+      </c>
+      <c r="AW82">
+        <v>2</v>
+      </c>
+      <c r="BD82">
+        <v>1</v>
+      </c>
+      <c r="BF82">
+        <v>1</v>
+      </c>
+      <c r="BI82">
+        <v>1</v>
+      </c>
+      <c r="BU82">
+        <v>2</v>
+      </c>
+      <c r="BW82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>352</v>
       </c>
-      <c r="Z82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="Z83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="84" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+    <row r="85" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>17</v>
       </c>
-      <c r="F84">
-        <v>2</v>
-      </c>
-      <c r="J84">
-        <v>1</v>
-      </c>
-      <c r="K84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="F85">
+        <v>2</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>86</v>
       </c>
-      <c r="K85">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="K86">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>16</v>
       </c>
-      <c r="C86">
+      <c r="C87">
         <v>4</v>
       </c>
-      <c r="D86">
+      <c r="D87">
         <v>3</v>
       </c>
-      <c r="F86">
-        <v>2</v>
-      </c>
-      <c r="G86">
-        <v>5</v>
-      </c>
-      <c r="H86">
+      <c r="F87">
+        <v>2</v>
+      </c>
+      <c r="G87">
+        <v>5</v>
+      </c>
+      <c r="H87">
         <v>3</v>
       </c>
-      <c r="I86">
-        <v>2</v>
-      </c>
-      <c r="J86">
-        <v>5</v>
-      </c>
-      <c r="K86">
+      <c r="I87">
+        <v>2</v>
+      </c>
+      <c r="J87">
+        <v>5</v>
+      </c>
+      <c r="K87">
         <v>3</v>
       </c>
-      <c r="L86">
-        <v>2</v>
-      </c>
-      <c r="M86">
+      <c r="L87">
+        <v>2</v>
+      </c>
+      <c r="M87">
         <v>3</v>
       </c>
-      <c r="O86">
-        <v>5</v>
-      </c>
-      <c r="P86">
-        <v>5</v>
-      </c>
-      <c r="Q86">
+      <c r="O87">
+        <v>5</v>
+      </c>
+      <c r="P87">
+        <v>5</v>
+      </c>
+      <c r="Q87">
         <v>3</v>
       </c>
-      <c r="R86">
-        <v>2</v>
-      </c>
-      <c r="S86">
+      <c r="R87">
+        <v>2</v>
+      </c>
+      <c r="S87">
         <v>3</v>
       </c>
-      <c r="T86">
-        <v>1</v>
-      </c>
-      <c r="U86">
-        <v>1</v>
-      </c>
-      <c r="V86">
+      <c r="T87">
+        <v>1</v>
+      </c>
+      <c r="U87">
+        <v>1</v>
+      </c>
+      <c r="V87">
         <v>3</v>
       </c>
-      <c r="W86">
+      <c r="W87">
         <v>3</v>
       </c>
-      <c r="X86">
-        <v>5</v>
-      </c>
-      <c r="Y86">
+      <c r="X87">
+        <v>5</v>
+      </c>
+      <c r="Y87">
         <v>4</v>
       </c>
-      <c r="Z86">
-        <v>1</v>
-      </c>
-      <c r="AA86">
+      <c r="Z87">
+        <v>1</v>
+      </c>
+      <c r="AA87">
         <v>3</v>
       </c>
-      <c r="AC86">
-        <v>1</v>
-      </c>
-      <c r="AE86">
+      <c r="AC87">
+        <v>1</v>
+      </c>
+      <c r="AE87">
         <v>4</v>
       </c>
-      <c r="AF86">
-        <v>2</v>
-      </c>
-      <c r="AG86">
+      <c r="AF87">
+        <v>2</v>
+      </c>
+      <c r="AG87">
         <v>3</v>
       </c>
-      <c r="AH86">
-        <v>2</v>
-      </c>
-      <c r="AI86">
-        <v>2</v>
-      </c>
-      <c r="AJ86">
+      <c r="AH87">
+        <v>2</v>
+      </c>
+      <c r="AI87">
+        <v>2</v>
+      </c>
+      <c r="AJ87">
         <v>7</v>
       </c>
-      <c r="AK86">
+      <c r="AK87">
         <v>3</v>
       </c>
-      <c r="AL86">
-        <v>5</v>
-      </c>
-      <c r="AM86">
-        <v>1</v>
-      </c>
-      <c r="AN86">
+      <c r="AL87">
+        <v>5</v>
+      </c>
+      <c r="AM87">
+        <v>1</v>
+      </c>
+      <c r="AN87">
         <v>4</v>
       </c>
-      <c r="AO86">
+      <c r="AO87">
         <v>3</v>
       </c>
-      <c r="AP86">
+      <c r="AP87">
         <v>6</v>
       </c>
-      <c r="AQ86">
+      <c r="AQ87">
         <v>4</v>
       </c>
-      <c r="AR86">
-        <v>5</v>
-      </c>
-      <c r="AS86">
+      <c r="AR87">
+        <v>5</v>
+      </c>
+      <c r="AS87">
         <v>3</v>
       </c>
-      <c r="AT86">
-        <v>2</v>
-      </c>
-      <c r="AU86">
-        <v>2</v>
-      </c>
-      <c r="AW86">
+      <c r="AT87">
+        <v>2</v>
+      </c>
+      <c r="AU87">
+        <v>2</v>
+      </c>
+      <c r="AW87">
         <v>3</v>
       </c>
-      <c r="AY86">
-        <v>1</v>
-      </c>
-      <c r="AZ86">
+      <c r="AY87">
+        <v>1</v>
+      </c>
+      <c r="AZ87">
         <v>3</v>
       </c>
-      <c r="BB86">
+      <c r="BB87">
         <v>4</v>
       </c>
-      <c r="BC86">
+      <c r="BC87">
         <v>4</v>
       </c>
-      <c r="BD86">
+      <c r="BD87">
         <v>3</v>
       </c>
-      <c r="BF86">
-        <v>2</v>
-      </c>
-      <c r="BG86">
+      <c r="BF87">
+        <v>2</v>
+      </c>
+      <c r="BG87">
         <v>4</v>
       </c>
-      <c r="BH86">
-        <v>5</v>
-      </c>
-      <c r="BJ86">
+      <c r="BH87">
+        <v>5</v>
+      </c>
+      <c r="BJ87">
         <v>4</v>
       </c>
-      <c r="BK86">
-        <v>2</v>
-      </c>
-      <c r="BL86">
+      <c r="BK87">
+        <v>2</v>
+      </c>
+      <c r="BL87">
         <v>4</v>
       </c>
-      <c r="BM86">
-        <v>1</v>
-      </c>
-      <c r="BN86">
-        <v>2</v>
-      </c>
-      <c r="BO86">
+      <c r="BM87">
+        <v>1</v>
+      </c>
+      <c r="BN87">
+        <v>2</v>
+      </c>
+      <c r="BO87">
         <v>3</v>
       </c>
-      <c r="BS86">
+      <c r="BS87">
         <v>3</v>
       </c>
-      <c r="BT86">
+      <c r="BT87">
         <v>4</v>
       </c>
-      <c r="BU86">
+      <c r="BU87">
         <v>4</v>
       </c>
-      <c r="BV86">
+      <c r="BV87">
         <v>3</v>
       </c>
-    </row>
-    <row r="87" spans="1:75" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="BX87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB87" xr:uid="{130C2564-D265-4C41-A3E0-02A62EDAC91D}">
-    <sortState ref="A2:AB87">
-      <sortCondition ref="A1:A87"/>
+  <autoFilter ref="A1:AB88" xr:uid="{130C2564-D265-4C41-A3E0-02A62EDAC91D}">
+    <sortState ref="A2:AB88">
+      <sortCondition ref="A1:A88"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6CE4F743-8EB4-4866-A2D5-A7A1DD10CF79}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D811F9F1-E84B-46AF-87AE-06188FBDC290}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notas" sheetId="1" r:id="rId1"/>
@@ -26,14 +26,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'extrato 2024'!$A$1:$C$187</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CX$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CY$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9328" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9364" uniqueCount="398">
   <si>
     <t>Jogador</t>
   </si>
@@ -3495,7 +3495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CX88"/>
+  <dimension ref="A1:CY88"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
@@ -3520,10 +3520,10 @@
     <col min="50" max="58" width="9.54296875" customWidth="1"/>
     <col min="59" max="65" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
-    <col min="67" max="96" width="11" customWidth="1"/>
+    <col min="67" max="97" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3809,27 +3809,30 @@
       <c r="CQ1" s="1">
         <v>46127</v>
       </c>
-      <c r="CR1" s="1"/>
-      <c r="CS1" t="s">
+      <c r="CR1" s="1">
+        <v>46134</v>
+      </c>
+      <c r="CS1" s="1"/>
+      <c r="CT1" t="s">
         <v>57</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>58</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>59</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>62</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>392</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4112,31 +4115,34 @@
       <c r="CQ2">
         <v>6</v>
       </c>
-      <c r="CS2">
-        <f>COUNT(B2:CQ2)</f>
-        <v>88</v>
-      </c>
-      <c r="CT2" s="18">
-        <f>AVERAGE(B2:CQ2)</f>
-        <v>6.0397727272727275</v>
-      </c>
-      <c r="CU2">
-        <f t="shared" ref="CU2:CU33" si="0">IF(CS2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
+      <c r="CR2">
+        <v>5.5</v>
+      </c>
+      <c r="CT2">
+        <f>COUNT(B2:CR2)</f>
+        <v>89</v>
+      </c>
+      <c r="CU2" s="18">
+        <f>AVERAGE(B2:CR2)</f>
+        <v>6.0337078651685392</v>
+      </c>
+      <c r="CV2">
+        <f t="shared" ref="CV2:CV33" si="0">IF(CT2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
         <v>1.2512468149547391</v>
       </c>
-      <c r="CV2">
-        <v>1</v>
-      </c>
       <c r="CW2">
-        <f t="shared" ref="CW2:CW33" si="1">COUNT(CK2:CN2)</f>
+        <v>1</v>
+      </c>
+      <c r="CX2">
+        <f t="shared" ref="CX2:CX33" si="1">COUNT(CK2:CN2)</f>
         <v>4</v>
       </c>
-      <c r="CX2">
-        <f t="shared" ref="CX2:CX33" si="2">IF(CV2=0,CW2,0)</f>
+      <c r="CY2">
+        <f t="shared" ref="CY2:CY33" si="2">IF(CW2=0,CX2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4419,31 +4425,34 @@
       <c r="CQ3">
         <v>5.5</v>
       </c>
-      <c r="CS3">
+      <c r="CR3">
+        <v>5.5</v>
+      </c>
+      <c r="CT3">
         <f>COUNT(B3:CK3)</f>
         <v>79</v>
       </c>
-      <c r="CT3" s="18">
+      <c r="CU3" s="18">
         <f>AVERAGE(B3:CK3)</f>
         <v>5.6518987341772151</v>
       </c>
-      <c r="CU3">
+      <c r="CV3">
         <f t="shared" si="0"/>
         <v>1.0518094984498128</v>
       </c>
-      <c r="CV3">
-        <v>1</v>
-      </c>
       <c r="CW3">
+        <v>1</v>
+      </c>
+      <c r="CX3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CX3">
+      <c r="CY3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4705,31 +4714,31 @@
       <c r="CI4">
         <v>5.5</v>
       </c>
-      <c r="CS4">
+      <c r="CT4">
         <f>COUNT(B4:CI4)</f>
         <v>72</v>
       </c>
-      <c r="CT4" s="18">
+      <c r="CU4" s="18">
         <f>AVERAGE(B4:CI4)</f>
         <v>5.708333333333333</v>
       </c>
-      <c r="CU4">
+      <c r="CV4">
         <f t="shared" si="0"/>
         <v>0.96435844595057774</v>
       </c>
-      <c r="CV4">
+      <c r="CW4">
         <v>0</v>
       </c>
-      <c r="CW4">
+      <c r="CX4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CX4">
+      <c r="CY4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -4997,31 +5006,34 @@
       <c r="CL5">
         <v>5.5</v>
       </c>
-      <c r="CS5">
+      <c r="CR5">
+        <v>5.5</v>
+      </c>
+      <c r="CT5">
         <f>COUNT(B5:CL5)</f>
         <v>71</v>
       </c>
-      <c r="CT5" s="18">
+      <c r="CU5" s="18">
         <f>AVERAGE(B5:CL5)</f>
         <v>7.267605633802817</v>
       </c>
-      <c r="CU5">
+      <c r="CV5">
         <f t="shared" si="0"/>
         <v>1.1294250579557983</v>
       </c>
-      <c r="CV5">
-        <v>1</v>
-      </c>
       <c r="CW5">
+        <v>1</v>
+      </c>
+      <c r="CX5">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CX5">
+      <c r="CY5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -5295,31 +5307,34 @@
       <c r="CQ6">
         <v>6</v>
       </c>
-      <c r="CS6">
+      <c r="CR6">
+        <v>5.5</v>
+      </c>
+      <c r="CT6">
         <f>COUNT(B6:CL6)</f>
         <v>70</v>
       </c>
-      <c r="CT6" s="18">
+      <c r="CU6" s="18">
         <f>AVERAGE(B6:CL6)</f>
         <v>6.6142857142857139</v>
       </c>
-      <c r="CU6">
+      <c r="CV6">
         <f t="shared" si="0"/>
         <v>0.9419445925236869</v>
       </c>
-      <c r="CV6">
-        <v>1</v>
-      </c>
       <c r="CW6">
+        <v>1</v>
+      </c>
+      <c r="CX6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CX6">
+      <c r="CY6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5593,31 +5608,34 @@
       <c r="CP7">
         <v>6.5</v>
       </c>
-      <c r="CS7">
+      <c r="CR7">
+        <v>6.5</v>
+      </c>
+      <c r="CT7">
         <f>COUNT(B7:CL7)</f>
         <v>70</v>
       </c>
-      <c r="CT7" s="18">
+      <c r="CU7" s="18">
         <f>AVERAGE(B7:CL7)</f>
         <v>6.6071428571428568</v>
       </c>
-      <c r="CU7">
+      <c r="CV7">
         <f t="shared" si="0"/>
         <v>1.0570846156365068</v>
       </c>
-      <c r="CV7">
-        <v>1</v>
-      </c>
       <c r="CW7">
+        <v>1</v>
+      </c>
+      <c r="CX7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CX7">
+      <c r="CY7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5867,31 +5885,31 @@
       <c r="CE8">
         <v>5</v>
       </c>
-      <c r="CS8">
+      <c r="CT8">
         <f>COUNT(B8:CI8)</f>
         <v>68</v>
       </c>
-      <c r="CT8" s="18">
+      <c r="CU8" s="18">
         <f>AVERAGE(B8:CI8)</f>
         <v>6.4191176470588234</v>
       </c>
-      <c r="CU8">
+      <c r="CV8">
         <f t="shared" si="0"/>
         <v>1.1769245721961776</v>
       </c>
-      <c r="CV8">
+      <c r="CW8">
         <v>0</v>
       </c>
-      <c r="CW8">
+      <c r="CX8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CX8">
+      <c r="CY8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -6144,31 +6162,34 @@
       <c r="CI9">
         <v>5.5</v>
       </c>
-      <c r="CS9">
+      <c r="CR9">
+        <v>5.5</v>
+      </c>
+      <c r="CT9">
         <f>COUNT(B9:CI9)</f>
         <v>67</v>
       </c>
-      <c r="CT9" s="18">
+      <c r="CU9" s="18">
         <f>AVERAGE(B9:CI9)</f>
         <v>5.9701492537313436</v>
       </c>
-      <c r="CU9">
+      <c r="CV9">
         <f t="shared" si="0"/>
         <v>0.96648378625350351</v>
       </c>
-      <c r="CV9">
+      <c r="CW9">
         <v>0</v>
       </c>
-      <c r="CW9">
+      <c r="CX9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CX9">
+      <c r="CY9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -6442,31 +6463,34 @@
       <c r="CQ10">
         <v>6</v>
       </c>
-      <c r="CS10">
+      <c r="CR10">
+        <v>6</v>
+      </c>
+      <c r="CT10">
         <f>COUNT(B10:CI10)</f>
         <v>62</v>
       </c>
-      <c r="CT10" s="18">
+      <c r="CU10" s="18">
         <f>AVERAGE(B10:CI10)</f>
         <v>5.717741935483871</v>
       </c>
-      <c r="CU10">
+      <c r="CV10">
         <f t="shared" si="0"/>
         <v>1.3617531291315086</v>
       </c>
-      <c r="CV10">
-        <v>1</v>
-      </c>
       <c r="CW10">
+        <v>1</v>
+      </c>
+      <c r="CX10">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CX10">
+      <c r="CY10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6740,31 +6764,34 @@
       <c r="CQ11">
         <v>7</v>
       </c>
-      <c r="CS11">
+      <c r="CR11">
+        <v>6</v>
+      </c>
+      <c r="CT11">
         <f>COUNT(B11:CI11)</f>
         <v>59</v>
       </c>
-      <c r="CT11" s="18">
+      <c r="CU11" s="18">
         <f>AVERAGE(B11:CI11)</f>
         <v>6.6779661016949152</v>
       </c>
-      <c r="CU11">
+      <c r="CV11">
         <f t="shared" si="0"/>
         <v>1.0072574989410263</v>
       </c>
-      <c r="CV11">
-        <v>1</v>
-      </c>
       <c r="CW11">
+        <v>1</v>
+      </c>
+      <c r="CX11">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CX11">
+      <c r="CY11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -7044,31 +7071,34 @@
       <c r="CQ12">
         <v>6</v>
       </c>
-      <c r="CS12">
-        <f>COUNT(B12:CQ12)</f>
-        <v>61</v>
-      </c>
-      <c r="CT12" s="18">
-        <f>AVERAGE(B12:CQ12)</f>
-        <v>5.5327868852459012</v>
-      </c>
-      <c r="CU12">
+      <c r="CR12">
+        <v>6</v>
+      </c>
+      <c r="CT12">
+        <f>COUNT(B12:CR12)</f>
+        <v>62</v>
+      </c>
+      <c r="CU12" s="18">
+        <f>AVERAGE(B12:CR12)</f>
+        <v>5.540322580645161</v>
+      </c>
+      <c r="CV12">
         <f t="shared" si="0"/>
         <v>1.0254583642020354</v>
       </c>
-      <c r="CV12">
-        <v>1</v>
-      </c>
       <c r="CW12">
+        <v>1</v>
+      </c>
+      <c r="CX12">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CX12">
+      <c r="CY12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -7345,31 +7375,34 @@
       <c r="CQ13">
         <v>6.5</v>
       </c>
-      <c r="CS13">
+      <c r="CR13">
+        <v>7.5</v>
+      </c>
+      <c r="CT13">
         <f>COUNT(B13:CN13)</f>
         <v>56</v>
       </c>
-      <c r="CT13" s="18">
+      <c r="CU13" s="18">
         <f>AVERAGE(B13:CN13)</f>
         <v>6.3571428571428568</v>
       </c>
-      <c r="CU13">
+      <c r="CV13">
         <f t="shared" si="0"/>
         <v>1.1769469323774333</v>
       </c>
-      <c r="CV13">
-        <v>1</v>
-      </c>
       <c r="CW13">
+        <v>1</v>
+      </c>
+      <c r="CX13">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CX13">
+      <c r="CY13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>367</v>
       </c>
@@ -7622,31 +7655,34 @@
       <c r="CP14">
         <v>5.5</v>
       </c>
-      <c r="CS14">
+      <c r="CR14">
+        <v>6</v>
+      </c>
+      <c r="CT14">
         <f>COUNT(B14:CI14)</f>
         <v>55</v>
       </c>
-      <c r="CT14" s="18">
+      <c r="CU14" s="18">
         <f>AVERAGE(B14:CI14)</f>
         <v>6.3181818181818183</v>
       </c>
-      <c r="CU14">
+      <c r="CV14">
         <f t="shared" si="0"/>
         <v>1.1213885273224193</v>
       </c>
-      <c r="CV14">
+      <c r="CW14">
         <v>0</v>
       </c>
-      <c r="CW14">
+      <c r="CX14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CX14">
+      <c r="CY14">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -7890,31 +7926,31 @@
       <c r="CF15">
         <v>5.5</v>
       </c>
-      <c r="CS15">
+      <c r="CT15">
         <f>COUNT(B15:CI15)</f>
         <v>52</v>
       </c>
-      <c r="CT15" s="18">
+      <c r="CU15" s="18">
         <f>AVERAGE(B15:CI15)</f>
         <v>5.6923076923076925</v>
       </c>
-      <c r="CU15">
+      <c r="CV15">
         <f t="shared" si="0"/>
         <v>0.84687340856573534</v>
       </c>
-      <c r="CV15">
+      <c r="CW15">
         <v>0</v>
       </c>
-      <c r="CW15">
+      <c r="CX15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CX15">
+      <c r="CY15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -8164,31 +8200,31 @@
       <c r="CF16">
         <v>5.5</v>
       </c>
-      <c r="CS16">
+      <c r="CT16">
         <f>COUNT(B16:CI16)</f>
         <v>47</v>
       </c>
-      <c r="CT16" s="18">
+      <c r="CU16" s="18">
         <f>AVERAGE(B16:CI16)</f>
         <v>4.4255319148936172</v>
       </c>
-      <c r="CU16">
+      <c r="CV16">
         <f t="shared" si="0"/>
         <v>1.3391217246854428</v>
       </c>
-      <c r="CV16">
+      <c r="CW16">
         <v>0</v>
       </c>
-      <c r="CW16">
+      <c r="CX16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CX16">
+      <c r="CY16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>56</v>
       </c>
@@ -8471,31 +8507,34 @@
       <c r="CQ17">
         <v>5.5</v>
       </c>
-      <c r="CS17">
+      <c r="CR17">
+        <v>6</v>
+      </c>
+      <c r="CT17">
         <f>COUNT(B17:CL17)</f>
         <v>46</v>
       </c>
-      <c r="CT17" s="18">
+      <c r="CU17" s="18">
         <f>AVERAGE(B17:CL17)</f>
         <v>6.0652173913043477</v>
       </c>
-      <c r="CU17">
+      <c r="CV17">
         <f t="shared" si="0"/>
         <v>0.9573434129174403</v>
       </c>
-      <c r="CV17">
-        <v>1</v>
-      </c>
       <c r="CW17">
+        <v>1</v>
+      </c>
+      <c r="CX17">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CX17">
+      <c r="CY17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -8763,31 +8802,31 @@
       <c r="CL18">
         <v>6</v>
       </c>
-      <c r="CS18">
+      <c r="CT18">
         <f>COUNT(B18:CL18)</f>
         <v>44</v>
       </c>
-      <c r="CT18" s="18">
+      <c r="CU18" s="18">
         <f>AVERAGE(B18:CL18)</f>
         <v>5.0113636363636367</v>
       </c>
-      <c r="CU18">
+      <c r="CV18">
         <f t="shared" si="0"/>
         <v>1.0645089158214895</v>
       </c>
-      <c r="CV18">
-        <v>1</v>
-      </c>
       <c r="CW18">
+        <v>1</v>
+      </c>
+      <c r="CX18">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CX18">
+      <c r="CY18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -9031,31 +9070,31 @@
       <c r="CK19">
         <v>5.5</v>
       </c>
-      <c r="CS19">
+      <c r="CT19">
         <f>COUNT(B19:CI19)</f>
         <v>38</v>
       </c>
-      <c r="CT19" s="18">
+      <c r="CU19" s="18">
         <f>AVERAGE(B19:CI19)</f>
         <v>6.1578947368421053</v>
       </c>
-      <c r="CU19">
+      <c r="CV19">
         <f t="shared" si="0"/>
         <v>1.0973263770680928</v>
       </c>
-      <c r="CV19">
+      <c r="CW19">
         <v>0</v>
       </c>
-      <c r="CW19">
+      <c r="CX19">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CX19">
+      <c r="CY19">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -9320,31 +9359,31 @@
       <c r="CM20">
         <v>5.5</v>
       </c>
-      <c r="CS20">
+      <c r="CT20">
         <f>COUNT(B20:CJ20)</f>
         <v>37</v>
       </c>
-      <c r="CT20" s="18">
+      <c r="CU20" s="18">
         <f>AVERAGE(B20:CJ20)</f>
         <v>5.2027027027027026</v>
       </c>
-      <c r="CU20">
+      <c r="CV20">
         <f t="shared" si="0"/>
         <v>1.3241383031954423</v>
       </c>
-      <c r="CV20">
+      <c r="CW20">
         <v>0</v>
       </c>
-      <c r="CW20">
+      <c r="CX20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CX20">
+      <c r="CY20">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -9603,31 +9642,34 @@
       <c r="CO21">
         <v>5.5</v>
       </c>
-      <c r="CS21">
+      <c r="CR21">
+        <v>5.5</v>
+      </c>
+      <c r="CT21">
         <f>COUNT(B21:CI21)</f>
         <v>36</v>
       </c>
-      <c r="CT21" s="18">
+      <c r="CU21" s="18">
         <f>AVERAGE(B21:CI21)</f>
         <v>5.7361111111111107</v>
       </c>
-      <c r="CU21">
+      <c r="CV21">
         <f t="shared" si="0"/>
         <v>0.92956296268047622</v>
       </c>
-      <c r="CV21">
-        <v>1</v>
-      </c>
       <c r="CW21">
+        <v>1</v>
+      </c>
+      <c r="CX21">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CX21">
+      <c r="CY21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -9898,31 +9940,34 @@
       <c r="CQ22">
         <v>6.5</v>
       </c>
-      <c r="CS22">
+      <c r="CR22">
+        <v>5.5</v>
+      </c>
+      <c r="CT22">
         <f>COUNT(B22:CI22)</f>
         <v>36</v>
       </c>
-      <c r="CT22" s="18">
+      <c r="CU22" s="18">
         <f>AVERAGE(B22:CI22)</f>
         <v>5.6111111111111107</v>
       </c>
-      <c r="CU22">
+      <c r="CV22">
         <f t="shared" si="0"/>
         <v>1.0098256776095882</v>
       </c>
-      <c r="CV22">
-        <v>1</v>
-      </c>
       <c r="CW22">
+        <v>1</v>
+      </c>
+      <c r="CX22">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CX22">
+      <c r="CY22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -10193,31 +10238,31 @@
       <c r="CN23">
         <v>6</v>
       </c>
-      <c r="CS23">
+      <c r="CT23">
         <f>COUNT(B23:CN23)</f>
         <v>30</v>
       </c>
-      <c r="CT23" s="18">
+      <c r="CU23" s="18">
         <f>AVERAGE(B23:CN23)</f>
         <v>6.4</v>
       </c>
-      <c r="CU23">
+      <c r="CV23">
         <f t="shared" si="0"/>
         <v>0.90960483309014595</v>
       </c>
-      <c r="CV23">
-        <v>1</v>
-      </c>
       <c r="CW23">
+        <v>1</v>
+      </c>
+      <c r="CX23">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CX23">
+      <c r="CY23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -10467,31 +10512,34 @@
       <c r="CN24">
         <v>6</v>
       </c>
-      <c r="CS24">
-        <f t="shared" ref="CS24:CS31" si="3">COUNT(B24:CI24)</f>
+      <c r="CR24">
+        <v>6</v>
+      </c>
+      <c r="CT24">
+        <f t="shared" ref="CT24:CT31" si="3">COUNT(B24:CI24)</f>
         <v>25</v>
       </c>
-      <c r="CT24" s="18">
-        <f t="shared" ref="CT24:CT31" si="4">AVERAGE(B24:CI24)</f>
+      <c r="CU24" s="18">
+        <f t="shared" ref="CU24:CU31" si="4">AVERAGE(B24:CI24)</f>
         <v>5.4</v>
       </c>
-      <c r="CU24">
+      <c r="CV24">
         <f t="shared" si="0"/>
         <v>0.71728150235677346</v>
       </c>
-      <c r="CV24">
+      <c r="CW24">
         <v>0</v>
       </c>
-      <c r="CW24">
+      <c r="CX24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CX24">
+      <c r="CY24">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -10732,31 +10780,31 @@
       <c r="CB25" t="s">
         <v>26</v>
       </c>
-      <c r="CS25">
+      <c r="CT25">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="CT25" s="18">
+      <c r="CU25" s="18">
         <f t="shared" si="4"/>
         <v>5.7894736842105265</v>
       </c>
-      <c r="CU25">
+      <c r="CV25">
         <f t="shared" si="0"/>
         <v>1.3674366679797902</v>
       </c>
-      <c r="CV25">
+      <c r="CW25">
         <v>0</v>
       </c>
-      <c r="CW25">
+      <c r="CX25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CX25">
+      <c r="CY25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>346</v>
       </c>
@@ -10997,31 +11045,31 @@
       <c r="CB26" t="s">
         <v>26</v>
       </c>
-      <c r="CS26">
+      <c r="CT26">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="CT26" s="18">
+      <c r="CU26" s="18">
         <f t="shared" si="4"/>
         <v>5.9444444444444446</v>
       </c>
-      <c r="CU26">
+      <c r="CV26">
         <f t="shared" si="0"/>
         <v>0.72535769855270305</v>
       </c>
-      <c r="CV26">
+      <c r="CW26">
         <v>0</v>
       </c>
-      <c r="CW26">
+      <c r="CX26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CX26">
+      <c r="CY26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -11262,31 +11310,31 @@
       <c r="CB27" t="s">
         <v>26</v>
       </c>
-      <c r="CS27">
+      <c r="CT27">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="CT27" s="18">
+      <c r="CU27" s="18">
         <f t="shared" si="4"/>
         <v>5.3235294117647056</v>
       </c>
-      <c r="CU27">
+      <c r="CV27">
         <f t="shared" si="0"/>
         <v>1.3456083251473603</v>
       </c>
-      <c r="CV27">
+      <c r="CW27">
         <v>0</v>
       </c>
-      <c r="CW27">
+      <c r="CX27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CX27">
+      <c r="CY27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -11527,31 +11575,31 @@
       <c r="CB28" t="s">
         <v>26</v>
       </c>
-      <c r="CS28">
+      <c r="CT28">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="CT28" s="18">
+      <c r="CU28" s="18">
         <f t="shared" si="4"/>
         <v>4.53125</v>
       </c>
-      <c r="CU28">
+      <c r="CV28">
         <f t="shared" si="0"/>
         <v>1.5434674167816653</v>
       </c>
-      <c r="CV28">
+      <c r="CW28">
         <v>0</v>
       </c>
-      <c r="CW28">
+      <c r="CX28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CX28">
+      <c r="CY28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -11807,31 +11855,31 @@
       <c r="CQ29">
         <v>6.5</v>
       </c>
-      <c r="CS29">
+      <c r="CT29">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="CT29" s="18">
+      <c r="CU29" s="18">
         <f t="shared" si="4"/>
         <v>6.65625</v>
       </c>
-      <c r="CU29">
+      <c r="CV29">
         <f t="shared" si="0"/>
         <v>0.74651970279870483</v>
       </c>
-      <c r="CV29">
-        <v>1</v>
-      </c>
       <c r="CW29">
+        <v>1</v>
+      </c>
+      <c r="CX29">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CX29">
+      <c r="CY29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -12072,31 +12120,31 @@
       <c r="CB30">
         <v>5.5</v>
       </c>
-      <c r="CS30">
+      <c r="CT30">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="CT30" s="18">
+      <c r="CU30" s="18">
         <f t="shared" si="4"/>
         <v>3.8666666666666667</v>
       </c>
-      <c r="CU30">
+      <c r="CV30">
         <f t="shared" si="0"/>
         <v>2.3563490726929555</v>
       </c>
-      <c r="CV30">
+      <c r="CW30">
         <v>0</v>
       </c>
-      <c r="CW30">
+      <c r="CX30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CX30">
+      <c r="CY30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -12349,31 +12397,31 @@
       <c r="CP31">
         <v>6</v>
       </c>
-      <c r="CS31">
+      <c r="CT31">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="CT31" s="18">
+      <c r="CU31" s="18">
         <f t="shared" si="4"/>
         <v>4.8214285714285712</v>
       </c>
-      <c r="CU31">
+      <c r="CV31">
         <f t="shared" si="0"/>
         <v>0.89335151148745728</v>
       </c>
-      <c r="CV31">
+      <c r="CW31">
         <v>0</v>
       </c>
-      <c r="CW31">
+      <c r="CX31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CX31">
+      <c r="CY31">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -12650,31 +12698,34 @@
       <c r="CQ32">
         <v>6</v>
       </c>
-      <c r="CS32">
-        <f>COUNT(B32:CQ32)</f>
-        <v>16</v>
-      </c>
-      <c r="CT32" s="18">
-        <f>AVERAGE(B32:CQ32)</f>
-        <v>6.34375</v>
-      </c>
-      <c r="CU32">
+      <c r="CR32">
+        <v>6.5</v>
+      </c>
+      <c r="CT32">
+        <f>COUNT(B32:CR32)</f>
+        <v>17</v>
+      </c>
+      <c r="CU32" s="18">
+        <f>AVERAGE(B32:CR32)</f>
+        <v>6.3529411764705879</v>
+      </c>
+      <c r="CV32">
         <f t="shared" si="0"/>
         <v>0.90829510622924903</v>
       </c>
-      <c r="CV32">
-        <v>1</v>
-      </c>
       <c r="CW32">
+        <v>1</v>
+      </c>
+      <c r="CX32">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CX32">
+      <c r="CY32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -12915,31 +12966,31 @@
       <c r="CB33" t="s">
         <v>26</v>
       </c>
-      <c r="CS33">
-        <f t="shared" ref="CS33:CS64" si="5">COUNT(B33:CI33)</f>
+      <c r="CT33">
+        <f t="shared" ref="CT33:CT64" si="5">COUNT(B33:CI33)</f>
         <v>13</v>
       </c>
-      <c r="CT33" s="18">
-        <f t="shared" ref="CT33:CT64" si="6">AVERAGE(B33:CI33)</f>
+      <c r="CU33" s="18">
+        <f t="shared" ref="CU33:CU64" si="6">AVERAGE(B33:CI33)</f>
         <v>7.3461538461538458</v>
       </c>
-      <c r="CU33">
+      <c r="CV33">
         <f t="shared" si="0"/>
         <v>1.5191090506255012</v>
       </c>
-      <c r="CV33">
+      <c r="CW33">
         <v>0</v>
       </c>
-      <c r="CW33">
+      <c r="CX33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CX33">
+      <c r="CY33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -13180,31 +13231,31 @@
       <c r="CB34" t="s">
         <v>26</v>
       </c>
-      <c r="CS34">
+      <c r="CT34">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="CT34" s="18">
+      <c r="CU34" s="18">
         <f t="shared" si="6"/>
         <v>4.6818181818181817</v>
       </c>
-      <c r="CU34">
-        <f t="shared" ref="CU34:CU65" si="7">IF(CS34&gt;1,_xlfn.STDEV.S(B34:CF34),"")</f>
+      <c r="CV34">
+        <f t="shared" ref="CV34:CV65" si="7">IF(CT34&gt;1,_xlfn.STDEV.S(B34:CF34),"")</f>
         <v>0.81463879335344846</v>
       </c>
-      <c r="CV34">
+      <c r="CW34">
         <v>0</v>
       </c>
-      <c r="CW34">
-        <f t="shared" ref="CW34:CW65" si="8">COUNT(CK34:CN34)</f>
+      <c r="CX34">
+        <f t="shared" ref="CX34:CX65" si="8">COUNT(CK34:CN34)</f>
         <v>0</v>
       </c>
-      <c r="CX34">
-        <f t="shared" ref="CX34:CX65" si="9">IF(CV34=0,CW34,0)</f>
+      <c r="CY34">
+        <f t="shared" ref="CY34:CY65" si="9">IF(CW34=0,CX34,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>45</v>
       </c>
@@ -13448,31 +13499,31 @@
       <c r="CC35">
         <v>6</v>
       </c>
-      <c r="CS35">
+      <c r="CT35">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="CT35" s="18">
+      <c r="CU35" s="18">
         <f t="shared" si="6"/>
         <v>8.4499999999999993</v>
       </c>
-      <c r="CU35">
+      <c r="CV35">
         <f t="shared" si="7"/>
         <v>1.1890705987824657</v>
       </c>
-      <c r="CV35">
+      <c r="CW35">
         <v>0</v>
       </c>
-      <c r="CW35">
+      <c r="CX35">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX35">
+      <c r="CY35">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>343</v>
       </c>
@@ -13728,31 +13779,34 @@
       <c r="CQ36">
         <v>6</v>
       </c>
-      <c r="CS36">
+      <c r="CR36">
+        <v>6</v>
+      </c>
+      <c r="CT36">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="CT36" s="18">
+      <c r="CU36" s="18">
         <f t="shared" si="6"/>
         <v>4.125</v>
       </c>
-      <c r="CU36">
+      <c r="CV36">
         <f t="shared" si="7"/>
         <v>1.7677669529663689</v>
       </c>
-      <c r="CV36">
-        <v>1</v>
-      </c>
       <c r="CW36">
+        <v>1</v>
+      </c>
+      <c r="CX36">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CX36">
+      <c r="CY36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>340</v>
       </c>
@@ -13996,31 +14050,31 @@
       <c r="CL37">
         <v>6</v>
       </c>
-      <c r="CS37">
+      <c r="CT37">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CT37" s="18">
+      <c r="CU37" s="18">
         <f t="shared" si="6"/>
         <v>5.7142857142857144</v>
       </c>
-      <c r="CU37">
+      <c r="CV37">
         <f t="shared" si="7"/>
         <v>0.56694670951384085</v>
       </c>
-      <c r="CV37">
+      <c r="CW37">
         <v>0</v>
       </c>
-      <c r="CW37">
+      <c r="CX37">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CX37">
+      <c r="CY37">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>376</v>
       </c>
@@ -14270,31 +14324,31 @@
       <c r="CQ38">
         <v>7.5</v>
       </c>
-      <c r="CS38">
+      <c r="CT38">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CT38" s="18">
+      <c r="CU38" s="18">
         <f t="shared" si="6"/>
         <v>5.7857142857142856</v>
       </c>
-      <c r="CU38">
+      <c r="CV38">
         <f t="shared" si="7"/>
         <v>0.4879500364742666</v>
       </c>
-      <c r="CV38">
+      <c r="CW38">
         <v>0</v>
       </c>
-      <c r="CW38">
+      <c r="CX38">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CX38">
+      <c r="CY38">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>378</v>
       </c>
@@ -14562,31 +14616,31 @@
       <c r="CQ39">
         <v>5.5</v>
       </c>
-      <c r="CS39">
+      <c r="CT39">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="CT39" s="18">
+      <c r="CU39" s="18">
         <f t="shared" si="6"/>
         <v>5.166666666666667</v>
       </c>
-      <c r="CU39">
+      <c r="CV39">
         <f t="shared" si="7"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="CV39">
-        <v>1</v>
-      </c>
       <c r="CW39">
+        <v>1</v>
+      </c>
+      <c r="CX39">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CX39">
+      <c r="CY39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -14830,31 +14884,31 @@
       <c r="CH40">
         <v>6.5</v>
       </c>
-      <c r="CS40">
+      <c r="CT40">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CT40" s="18">
+      <c r="CU40" s="18">
         <f t="shared" si="6"/>
         <v>7.8</v>
       </c>
-      <c r="CU40">
+      <c r="CV40">
         <f t="shared" si="7"/>
         <v>1.0307764064044151</v>
       </c>
-      <c r="CV40">
+      <c r="CW40">
         <v>0</v>
       </c>
-      <c r="CW40">
+      <c r="CX40">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX40">
+      <c r="CY40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>60</v>
       </c>
@@ -15098,31 +15152,31 @@
       <c r="CM41">
         <v>5.5</v>
       </c>
-      <c r="CS41">
+      <c r="CT41">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CT41" s="18">
+      <c r="CU41" s="18">
         <f t="shared" si="6"/>
         <v>3.375</v>
       </c>
-      <c r="CU41">
+      <c r="CV41">
         <f t="shared" si="7"/>
         <v>0.47871355387816905</v>
       </c>
-      <c r="CV41">
+      <c r="CW41">
         <v>0</v>
       </c>
-      <c r="CW41">
+      <c r="CX41">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CX41">
+      <c r="CY41">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -15363,31 +15417,31 @@
       <c r="CB42" t="s">
         <v>26</v>
       </c>
-      <c r="CS42">
+      <c r="CT42">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CT42" s="18">
+      <c r="CU42" s="18">
         <f t="shared" si="6"/>
         <v>5.625</v>
       </c>
-      <c r="CU42">
+      <c r="CV42">
         <f t="shared" si="7"/>
         <v>0.9464847243000456</v>
       </c>
-      <c r="CV42">
+      <c r="CW42">
         <v>0</v>
       </c>
-      <c r="CW42">
+      <c r="CX42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX42">
+      <c r="CY42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -15628,31 +15682,31 @@
       <c r="CB43" t="s">
         <v>26</v>
       </c>
-      <c r="CS43">
+      <c r="CT43">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CT43" s="18">
+      <c r="CU43" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CU43">
+      <c r="CV43">
         <f t="shared" si="7"/>
         <v>1.0408329997330663</v>
       </c>
-      <c r="CV43">
+      <c r="CW43">
         <v>0</v>
       </c>
-      <c r="CW43">
+      <c r="CX43">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX43">
+      <c r="CY43">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -15893,31 +15947,31 @@
       <c r="CB44" t="s">
         <v>26</v>
       </c>
-      <c r="CS44">
+      <c r="CT44">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CT44" s="18">
+      <c r="CU44" s="18">
         <f t="shared" si="6"/>
         <v>1.375</v>
       </c>
-      <c r="CU44">
+      <c r="CV44">
         <f t="shared" si="7"/>
         <v>1.8874586088176875</v>
       </c>
-      <c r="CV44">
+      <c r="CW44">
         <v>0</v>
       </c>
-      <c r="CW44">
+      <c r="CX44">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX44">
+      <c r="CY44">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>344</v>
       </c>
@@ -16158,31 +16212,31 @@
       <c r="CB45" t="s">
         <v>26</v>
       </c>
-      <c r="CS45">
+      <c r="CT45">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CT45" s="18">
+      <c r="CU45" s="18">
         <f t="shared" si="6"/>
         <v>4.625</v>
       </c>
-      <c r="CU45">
+      <c r="CV45">
         <f t="shared" si="7"/>
         <v>1.4361406616345072</v>
       </c>
-      <c r="CV45">
+      <c r="CW45">
         <v>0</v>
       </c>
-      <c r="CW45">
+      <c r="CX45">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX45">
+      <c r="CY45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>361</v>
       </c>
@@ -16423,31 +16477,31 @@
       <c r="CB46" t="s">
         <v>26</v>
       </c>
-      <c r="CS46">
+      <c r="CT46">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CT46" s="18">
+      <c r="CU46" s="18">
         <f t="shared" si="6"/>
         <v>6.25</v>
       </c>
-      <c r="CU46">
+      <c r="CV46">
         <f t="shared" si="7"/>
         <v>0.8660254037844386</v>
       </c>
-      <c r="CV46">
+      <c r="CW46">
         <v>0</v>
       </c>
-      <c r="CW46">
+      <c r="CX46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX46">
+      <c r="CY46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -16688,31 +16742,31 @@
       <c r="CB47" t="s">
         <v>26</v>
       </c>
-      <c r="CS47">
+      <c r="CT47">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CT47" s="18">
+      <c r="CU47" s="18">
         <f t="shared" si="6"/>
         <v>2.875</v>
       </c>
-      <c r="CU47">
+      <c r="CV47">
         <f t="shared" si="7"/>
         <v>2.7801378862687129</v>
       </c>
-      <c r="CV47">
+      <c r="CW47">
         <v>0</v>
       </c>
-      <c r="CW47">
+      <c r="CX47">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX47">
+      <c r="CY47">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -16953,31 +17007,31 @@
       <c r="CB48" t="s">
         <v>26</v>
       </c>
-      <c r="CS48">
+      <c r="CT48">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CT48" s="18">
+      <c r="CU48" s="18">
         <f t="shared" si="6"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="CU48">
+      <c r="CV48">
         <f t="shared" si="7"/>
         <v>1.4433756729740652</v>
       </c>
-      <c r="CV48">
+      <c r="CW48">
         <v>0</v>
       </c>
-      <c r="CW48">
+      <c r="CX48">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX48">
+      <c r="CY48">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -17218,31 +17272,31 @@
       <c r="CB49" t="s">
         <v>26</v>
       </c>
-      <c r="CS49">
+      <c r="CT49">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CT49" s="18">
+      <c r="CU49" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CU49">
+      <c r="CV49">
         <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
-      <c r="CV49">
+      <c r="CW49">
         <v>0</v>
       </c>
-      <c r="CW49">
+      <c r="CX49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX49">
+      <c r="CY49">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -17483,31 +17537,31 @@
       <c r="CB50" t="s">
         <v>26</v>
       </c>
-      <c r="CS50">
+      <c r="CT50">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CT50" s="18">
+      <c r="CU50" s="18">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="CU50">
+      <c r="CV50">
         <f t="shared" si="7"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CV50">
+      <c r="CW50">
         <v>0</v>
       </c>
-      <c r="CW50">
+      <c r="CX50">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX50">
+      <c r="CY50">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -17751,31 +17805,31 @@
       <c r="CG51">
         <v>6</v>
       </c>
-      <c r="CS51">
+      <c r="CT51">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CT51" s="18">
+      <c r="CU51" s="18">
         <f t="shared" si="6"/>
         <v>5.666666666666667</v>
       </c>
-      <c r="CU51">
+      <c r="CV51">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CV51">
+      <c r="CW51">
         <v>0</v>
       </c>
-      <c r="CW51">
+      <c r="CX51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX51">
+      <c r="CY51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>368</v>
       </c>
@@ -18019,31 +18073,31 @@
       <c r="CG52">
         <v>6</v>
       </c>
-      <c r="CS52">
+      <c r="CT52">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CT52" s="18">
+      <c r="CU52" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CU52">
+      <c r="CV52">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CV52">
+      <c r="CW52">
         <v>0</v>
       </c>
-      <c r="CW52">
+      <c r="CX52">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX52">
+      <c r="CY52">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>362</v>
       </c>
@@ -18287,31 +18341,31 @@
       <c r="CD53">
         <v>5.5</v>
       </c>
-      <c r="CS53">
+      <c r="CT53">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CT53" s="18">
+      <c r="CU53" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CU53">
+      <c r="CV53">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CV53">
+      <c r="CW53">
         <v>0</v>
       </c>
-      <c r="CW53">
+      <c r="CX53">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX53">
+      <c r="CY53">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>364</v>
       </c>
@@ -18561,31 +18615,31 @@
       <c r="CN54">
         <v>6</v>
       </c>
-      <c r="CS54">
+      <c r="CT54">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CT54" s="18">
+      <c r="CU54" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="CU54">
+      <c r="CV54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CV54">
-        <v>1</v>
-      </c>
       <c r="CW54">
+        <v>1</v>
+      </c>
+      <c r="CX54">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CX54">
+      <c r="CY54">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -18826,31 +18880,31 @@
       <c r="CB55" t="s">
         <v>26</v>
       </c>
-      <c r="CS55">
+      <c r="CT55">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CT55" s="18">
+      <c r="CU55" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CU55">
+      <c r="CV55">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CV55">
+      <c r="CW55">
         <v>0</v>
       </c>
-      <c r="CW55">
+      <c r="CX55">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX55">
+      <c r="CY55">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>339</v>
       </c>
@@ -19091,31 +19145,31 @@
       <c r="CB56" t="s">
         <v>26</v>
       </c>
-      <c r="CS56">
+      <c r="CT56">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CT56" s="18">
+      <c r="CU56" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CU56">
+      <c r="CV56">
         <f t="shared" si="7"/>
         <v>2.4748737341529163</v>
       </c>
-      <c r="CV56">
+      <c r="CW56">
         <v>0</v>
       </c>
-      <c r="CW56">
+      <c r="CX56">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX56">
+      <c r="CY56">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>342</v>
       </c>
@@ -19362,31 +19416,31 @@
       <c r="CO57">
         <v>6</v>
       </c>
-      <c r="CS57">
+      <c r="CT57">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CT57" s="18">
+      <c r="CU57" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CU57">
+      <c r="CV57">
         <f t="shared" si="7"/>
         <v>2.1213203435596424</v>
       </c>
-      <c r="CV57">
+      <c r="CW57">
         <v>0</v>
       </c>
-      <c r="CW57">
+      <c r="CX57">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX57">
+      <c r="CY57">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>369</v>
       </c>
@@ -19627,31 +19681,31 @@
       <c r="CB58" t="s">
         <v>26</v>
       </c>
-      <c r="CS58">
+      <c r="CT58">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CT58" s="18">
+      <c r="CU58" s="18">
         <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
-      <c r="CU58">
+      <c r="CV58">
         <f t="shared" si="7"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="CV58">
+      <c r="CW58">
         <v>0</v>
       </c>
-      <c r="CW58">
+      <c r="CX58">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX58">
+      <c r="CY58">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>379</v>
       </c>
@@ -19892,31 +19946,31 @@
       <c r="CB59" t="s">
         <v>26</v>
       </c>
-      <c r="CS59">
+      <c r="CT59">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CT59" s="18">
+      <c r="CU59" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CU59">
+      <c r="CV59">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CV59">
+      <c r="CW59">
         <v>0</v>
       </c>
-      <c r="CW59">
+      <c r="CX59">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX59">
+      <c r="CY59">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>390</v>
       </c>
@@ -20163,31 +20217,31 @@
       <c r="CH60">
         <v>7</v>
       </c>
-      <c r="CS60">
+      <c r="CT60">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CT60" s="18">
+      <c r="CU60" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CU60" t="e">
+      <c r="CV60" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CV60">
+      <c r="CW60">
         <v>0</v>
       </c>
-      <c r="CW60">
+      <c r="CX60">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX60">
+      <c r="CY60">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>388</v>
       </c>
@@ -20431,31 +20485,31 @@
       <c r="CH61">
         <v>5</v>
       </c>
-      <c r="CS61">
+      <c r="CT61">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CT61" s="18">
+      <c r="CU61" s="18">
         <f t="shared" si="6"/>
         <v>4.25</v>
       </c>
-      <c r="CU61" t="e">
+      <c r="CV61" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CV61">
+      <c r="CW61">
         <v>0</v>
       </c>
-      <c r="CW61">
+      <c r="CX61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX61">
+      <c r="CY61">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>345</v>
       </c>
@@ -20714,31 +20768,31 @@
       <c r="CO62">
         <v>4.5</v>
       </c>
-      <c r="CS62">
+      <c r="CT62">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CT62" s="18">
+      <c r="CU62" s="18">
         <f t="shared" si="6"/>
         <v>4.25</v>
       </c>
-      <c r="CU62" t="e">
+      <c r="CV62" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CV62">
-        <v>1</v>
-      </c>
       <c r="CW62">
+        <v>1</v>
+      </c>
+      <c r="CX62">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CX62">
+      <c r="CY62">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>387</v>
       </c>
@@ -20988,31 +21042,31 @@
       <c r="CJ63">
         <v>7</v>
       </c>
-      <c r="CS63">
+      <c r="CT63">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CT63" s="18">
+      <c r="CU63" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="CU63" t="e">
+      <c r="CV63" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CV63">
+      <c r="CW63">
         <v>0</v>
       </c>
-      <c r="CW63">
+      <c r="CX63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX63">
+      <c r="CY63">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>86</v>
       </c>
@@ -21253,31 +21307,31 @@
       <c r="CB64" t="s">
         <v>26</v>
       </c>
-      <c r="CS64">
+      <c r="CT64">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CT64" s="18">
+      <c r="CU64" s="18">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="CU64" t="str">
+      <c r="CV64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="CV64">
+      <c r="CW64">
         <v>0</v>
       </c>
-      <c r="CW64">
+      <c r="CX64">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX64">
+      <c r="CY64">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -21518,31 +21572,31 @@
       <c r="CB65" t="s">
         <v>26</v>
       </c>
-      <c r="CS65">
-        <f t="shared" ref="CS65:CS83" si="10">COUNT(B65:CI65)</f>
-        <v>1</v>
-      </c>
-      <c r="CT65" s="18">
-        <f t="shared" ref="CT65:CT83" si="11">AVERAGE(B65:CI65)</f>
+      <c r="CT65">
+        <f t="shared" ref="CT65:CT83" si="10">COUNT(B65:CI65)</f>
+        <v>1</v>
+      </c>
+      <c r="CU65" s="18">
+        <f t="shared" ref="CU65:CU83" si="11">AVERAGE(B65:CI65)</f>
         <v>7</v>
       </c>
-      <c r="CU65" t="str">
+      <c r="CV65" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="CV65">
+      <c r="CW65">
         <v>0</v>
       </c>
-      <c r="CW65">
+      <c r="CX65">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CX65">
+      <c r="CY65">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>353</v>
       </c>
@@ -21783,31 +21837,31 @@
       <c r="CB66" t="s">
         <v>26</v>
       </c>
-      <c r="CS66">
+      <c r="CT66">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT66" s="18">
+      <c r="CU66" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CU66" t="str">
-        <f t="shared" ref="CU66:CU83" si="12">IF(CS66&gt;1,_xlfn.STDEV.S(B66:CF66),"")</f>
+      <c r="CV66" t="str">
+        <f t="shared" ref="CV66:CV83" si="12">IF(CT66&gt;1,_xlfn.STDEV.S(B66:CF66),"")</f>
         <v/>
       </c>
-      <c r="CV66">
+      <c r="CW66">
         <v>0</v>
       </c>
-      <c r="CW66">
-        <f t="shared" ref="CW66:CW83" si="13">COUNT(CK66:CN66)</f>
+      <c r="CX66">
+        <f t="shared" ref="CX66:CX83" si="13">COUNT(CK66:CN66)</f>
         <v>0</v>
       </c>
-      <c r="CX66">
-        <f t="shared" ref="CX66:CX83" si="14">IF(CV66=0,CW66,0)</f>
+      <c r="CY66">
+        <f t="shared" ref="CY66:CY83" si="14">IF(CW66=0,CX66,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>80</v>
       </c>
@@ -22048,31 +22102,31 @@
       <c r="CB67" t="s">
         <v>26</v>
       </c>
-      <c r="CS67">
+      <c r="CT67">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT67" s="18">
+      <c r="CU67" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CU67" t="str">
+      <c r="CV67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV67">
+      <c r="CW67">
         <v>0</v>
       </c>
-      <c r="CW67">
+      <c r="CX67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX67">
+      <c r="CY67">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>47</v>
       </c>
@@ -22313,31 +22367,31 @@
       <c r="CB68" t="s">
         <v>26</v>
       </c>
-      <c r="CS68">
+      <c r="CT68">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT68" s="18">
+      <c r="CU68" s="18">
         <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
-      <c r="CU68" t="str">
+      <c r="CV68" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV68">
+      <c r="CW68">
         <v>0</v>
       </c>
-      <c r="CW68">
+      <c r="CX68">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX68">
+      <c r="CY68">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -22578,31 +22632,31 @@
       <c r="CB69" t="s">
         <v>26</v>
       </c>
-      <c r="CS69">
+      <c r="CT69">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT69" s="18">
+      <c r="CU69" s="18">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="CU69" t="str">
+      <c r="CV69" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV69">
+      <c r="CW69">
         <v>0</v>
       </c>
-      <c r="CW69">
+      <c r="CX69">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX69">
+      <c r="CY69">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>347</v>
       </c>
@@ -22843,31 +22897,31 @@
       <c r="CB70" t="s">
         <v>26</v>
       </c>
-      <c r="CS70">
+      <c r="CT70">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT70" s="18">
+      <c r="CU70" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="CU70" t="str">
+      <c r="CV70" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV70">
+      <c r="CW70">
         <v>0</v>
       </c>
-      <c r="CW70">
+      <c r="CX70">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX70">
+      <c r="CY70">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>350</v>
       </c>
@@ -23108,31 +23162,31 @@
       <c r="CB71" t="s">
         <v>26</v>
       </c>
-      <c r="CS71">
+      <c r="CT71">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT71" s="18">
+      <c r="CU71" s="18">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="CU71" t="str">
+      <c r="CV71" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV71">
+      <c r="CW71">
         <v>0</v>
       </c>
-      <c r="CW71">
+      <c r="CX71">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX71">
+      <c r="CY71">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>351</v>
       </c>
@@ -23373,31 +23427,31 @@
       <c r="CB72" t="s">
         <v>26</v>
       </c>
-      <c r="CS72">
+      <c r="CT72">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT72" s="18">
+      <c r="CU72" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="CU72" t="str">
+      <c r="CV72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV72">
+      <c r="CW72">
         <v>0</v>
       </c>
-      <c r="CW72">
+      <c r="CX72">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX72">
+      <c r="CY72">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>352</v>
       </c>
@@ -23638,31 +23692,31 @@
       <c r="CB73" t="s">
         <v>26</v>
       </c>
-      <c r="CS73">
+      <c r="CT73">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT73" s="18">
+      <c r="CU73" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="CU73" t="str">
+      <c r="CV73" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV73">
+      <c r="CW73">
         <v>0</v>
       </c>
-      <c r="CW73">
+      <c r="CX73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX73">
+      <c r="CY73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>354</v>
       </c>
@@ -23903,31 +23957,31 @@
       <c r="CB74" t="s">
         <v>26</v>
       </c>
-      <c r="CS74">
+      <c r="CT74">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT74" s="18">
+      <c r="CU74" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CU74" t="str">
+      <c r="CV74" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV74">
+      <c r="CW74">
         <v>0</v>
       </c>
-      <c r="CW74">
+      <c r="CX74">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX74">
+      <c r="CY74">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>365</v>
       </c>
@@ -24168,31 +24222,31 @@
       <c r="CB75" t="s">
         <v>26</v>
       </c>
-      <c r="CS75">
+      <c r="CT75">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT75" s="18">
+      <c r="CU75" s="18">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
-      <c r="CU75" t="str">
+      <c r="CV75" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV75">
+      <c r="CW75">
         <v>0</v>
       </c>
-      <c r="CW75">
+      <c r="CX75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX75">
+      <c r="CY75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>366</v>
       </c>
@@ -24433,31 +24487,31 @@
       <c r="CB76" t="s">
         <v>26</v>
       </c>
-      <c r="CS76">
+      <c r="CT76">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT76" s="18">
+      <c r="CU76" s="18">
         <f t="shared" si="11"/>
         <v>2.5</v>
       </c>
-      <c r="CU76" t="str">
+      <c r="CV76" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV76">
+      <c r="CW76">
         <v>0</v>
       </c>
-      <c r="CW76">
+      <c r="CX76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX76">
+      <c r="CY76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>374</v>
       </c>
@@ -24698,31 +24752,31 @@
       <c r="CB77" t="s">
         <v>26</v>
       </c>
-      <c r="CS77">
+      <c r="CT77">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT77" s="18">
+      <c r="CU77" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CU77" t="str">
+      <c r="CV77" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV77">
+      <c r="CW77">
         <v>0</v>
       </c>
-      <c r="CW77">
+      <c r="CX77">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX77">
+      <c r="CY77">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>375</v>
       </c>
@@ -24963,31 +25017,31 @@
       <c r="CB78" t="s">
         <v>26</v>
       </c>
-      <c r="CS78">
+      <c r="CT78">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT78" s="18">
+      <c r="CU78" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CU78" t="str">
+      <c r="CV78" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV78">
+      <c r="CW78">
         <v>0</v>
       </c>
-      <c r="CW78">
+      <c r="CX78">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX78">
+      <c r="CY78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>377</v>
       </c>
@@ -25228,31 +25282,31 @@
       <c r="CB79" t="s">
         <v>26</v>
       </c>
-      <c r="CS79">
+      <c r="CT79">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT79" s="18">
+      <c r="CU79" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="CU79" t="str">
+      <c r="CV79" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV79">
+      <c r="CW79">
         <v>0</v>
       </c>
-      <c r="CW79">
+      <c r="CX79">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX79">
+      <c r="CY79">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>381</v>
       </c>
@@ -25493,31 +25547,31 @@
       <c r="CB80" t="s">
         <v>26</v>
       </c>
-      <c r="CS80">
+      <c r="CT80">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT80" s="18">
+      <c r="CU80" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CU80" t="str">
+      <c r="CV80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV80">
+      <c r="CW80">
         <v>0</v>
       </c>
-      <c r="CW80">
+      <c r="CX80">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX80">
+      <c r="CY80">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>382</v>
       </c>
@@ -25758,31 +25812,31 @@
       <c r="CB81" t="s">
         <v>26</v>
       </c>
-      <c r="CS81">
+      <c r="CT81">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT81" s="18">
+      <c r="CU81" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CU81" t="str">
+      <c r="CV81" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV81">
+      <c r="CW81">
         <v>0</v>
       </c>
-      <c r="CW81">
+      <c r="CX81">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX81">
+      <c r="CY81">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>389</v>
       </c>
@@ -26026,31 +26080,31 @@
       <c r="CH82">
         <v>7.5</v>
       </c>
-      <c r="CS82">
+      <c r="CT82">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT82" s="18">
+      <c r="CU82" s="18">
         <f t="shared" si="11"/>
         <v>7.5</v>
       </c>
-      <c r="CU82" t="str">
+      <c r="CV82" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV82">
+      <c r="CW82">
         <v>0</v>
       </c>
-      <c r="CW82">
+      <c r="CX82">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX82">
+      <c r="CY82">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>391</v>
       </c>
@@ -26294,31 +26348,31 @@
       <c r="CI83">
         <v>7</v>
       </c>
-      <c r="CS83">
+      <c r="CT83">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CT83" s="18">
+      <c r="CU83" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CU83" t="str">
+      <c r="CV83" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CV83">
+      <c r="CW83">
         <v>0</v>
       </c>
-      <c r="CW83">
+      <c r="CX83">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CX83">
+      <c r="CY83">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>393</v>
       </c>
@@ -26331,31 +26385,34 @@
       <c r="CQ84">
         <v>9</v>
       </c>
-      <c r="CS84">
-        <f t="shared" ref="CS84:CS88" si="15">COUNT(B84:CI84)</f>
+      <c r="CR84">
+        <v>6.5</v>
+      </c>
+      <c r="CT84">
+        <f t="shared" ref="CT84:CT88" si="15">COUNT(B84:CI84)</f>
         <v>0</v>
       </c>
-      <c r="CT84" s="18" t="e">
-        <f t="shared" ref="CT84:CT88" si="16">AVERAGE(B84:CI84)</f>
+      <c r="CU84" s="18" t="e">
+        <f t="shared" ref="CU84:CU88" si="16">AVERAGE(B84:CI84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="CU84" t="str">
-        <f t="shared" ref="CU84:CU88" si="17">IF(CS84&gt;1,_xlfn.STDEV.S(B84:CF84),"")</f>
+      <c r="CV84" t="str">
+        <f t="shared" ref="CV84:CV88" si="17">IF(CT84&gt;1,_xlfn.STDEV.S(B84:CF84),"")</f>
         <v/>
       </c>
-      <c r="CV84">
+      <c r="CW84">
         <v>0</v>
       </c>
-      <c r="CW84">
-        <f t="shared" ref="CW84:CW88" si="18">COUNT(CK84:CN84)</f>
+      <c r="CX84">
+        <f t="shared" ref="CX84:CX88" si="18">COUNT(CK84:CN84)</f>
         <v>0</v>
       </c>
-      <c r="CX84">
-        <f t="shared" ref="CX84:CX88" si="19">IF(CV84=0,CW84,0)</f>
+      <c r="CY84">
+        <f t="shared" ref="CY84:CY88" si="19">IF(CW84=0,CX84,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>394</v>
       </c>
@@ -26365,31 +26422,31 @@
       <c r="CQ85">
         <v>6.5</v>
       </c>
-      <c r="CS85">
+      <c r="CT85">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="CT85" s="18" t="e">
+      <c r="CU85" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CU85" t="str">
+      <c r="CV85" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="CV85">
+      <c r="CW85">
         <v>0</v>
       </c>
-      <c r="CW85">
+      <c r="CX85">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="CX85">
+      <c r="CY85">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>395</v>
       </c>
@@ -26399,99 +26456,99 @@
       <c r="CQ86">
         <v>6</v>
       </c>
-      <c r="CS86">
+      <c r="CT86">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="CT86" s="18" t="e">
+      <c r="CU86" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CU86" t="str">
+      <c r="CV86" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="CV86">
+      <c r="CW86">
         <v>0</v>
       </c>
-      <c r="CW86">
+      <c r="CX86">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="CX86">
+      <c r="CY86">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>396</v>
       </c>
       <c r="CP87">
         <v>6.5</v>
       </c>
-      <c r="CS87">
+      <c r="CT87">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="CT87" s="18" t="e">
+      <c r="CU87" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CU87" t="str">
+      <c r="CV87" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="CV87">
+      <c r="CW87">
         <v>0</v>
       </c>
-      <c r="CW87">
+      <c r="CX87">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="CX87">
+      <c r="CY87">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:103" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>397</v>
       </c>
       <c r="CQ88">
         <v>6.5</v>
       </c>
-      <c r="CS88">
+      <c r="CT88">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="CT88" s="18" t="e">
+      <c r="CU88" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CU88" t="str">
+      <c r="CV88" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="CV88">
+      <c r="CW88">
         <v>0</v>
       </c>
-      <c r="CW88">
+      <c r="CX88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="CX88">
+      <c r="CY88">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CX83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
-    <sortState ref="A2:CX83">
-      <sortCondition descending="1" ref="CS1:CS83"/>
+  <autoFilter ref="A1:CY83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
+    <sortState ref="A2:CY83">
+      <sortCondition descending="1" ref="CT1:CT83"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="CS2:CS88">
+  <conditionalFormatting sqref="CT2:CT88">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -26503,7 +26560,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CU2:CU88">
+  <conditionalFormatting sqref="CV2:CV88">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -26515,7 +26572,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS88">
+  <conditionalFormatting sqref="CT2:CT88">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -26527,7 +26584,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CT2:CT88">
+  <conditionalFormatting sqref="CU2:CU88">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
@@ -26539,7 +26596,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CT2:CT88">
+  <conditionalFormatting sqref="CU2:CU88">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
@@ -26551,7 +26608,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS88">
+  <conditionalFormatting sqref="CT2:CT88">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -26563,7 +26620,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CT2:CT88">
+  <conditionalFormatting sqref="CU2:CU88">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -26575,7 +26632,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR79">
+  <conditionalFormatting sqref="CS2:CS79">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -26587,7 +26644,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR67">
+  <conditionalFormatting sqref="CS2:CS67">
     <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
@@ -26599,7 +26656,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR67">
+  <conditionalFormatting sqref="CS2:CS67">
     <cfRule type="colorScale" priority="127">
       <colorScale>
         <cfvo type="min"/>
@@ -26611,7 +26668,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR67">
+  <conditionalFormatting sqref="CS2:CS67">
     <cfRule type="colorScale" priority="129">
       <colorScale>
         <cfvo type="min"/>
@@ -26623,7 +26680,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:CQ83">
+  <conditionalFormatting sqref="B2:CR83">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -31836,7 +31893,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X276"/>
+  <dimension ref="A1:X279"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -45536,6 +45593,156 @@
         <v>397</v>
       </c>
     </row>
+    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A277" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B277" s="62">
+        <v>3</v>
+      </c>
+      <c r="C277" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D277" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E277" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F277" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G277" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H277" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="I277" s="9">
+        <v>3</v>
+      </c>
+      <c r="J277" s="10">
+        <v>3</v>
+      </c>
+      <c r="K277" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L277" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="M277" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="N277" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O277" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="P277" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A278" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B278" s="62">
+        <v>4</v>
+      </c>
+      <c r="C278" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D278" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E278" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F278" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G278" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="H278" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I278" s="11">
+        <v>3</v>
+      </c>
+      <c r="J278" s="2">
+        <v>5</v>
+      </c>
+      <c r="K278" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L278" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M278" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N278" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="O278" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="P278" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A279" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B279" s="62">
+        <v>4</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F279" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="G279" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="H279" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I279" s="5">
+        <v>3</v>
+      </c>
+      <c r="J279" s="8">
+        <v>2</v>
+      </c>
+      <c r="K279" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L279" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M279" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="N279" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="O279" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="P279" s="8" t="s">
+        <v>343</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -45543,19 +45750,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:BX88"/>
+  <dimension ref="A1:BY88"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="76" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="77" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -45784,8 +45992,11 @@
       <c r="BX1" s="1">
         <v>46127</v>
       </c>
-    </row>
-    <row r="2" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="BY1" s="1">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -45846,8 +46057,11 @@
       <c r="BX2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="BY2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -45855,7 +46069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -45893,12 +46107,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -45906,7 +46120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>393</v>
       </c>
@@ -45916,8 +46130,11 @@
       <c r="BX7">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="BY7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>364</v>
       </c>
@@ -45934,7 +46151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -45942,7 +46159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>353</v>
       </c>
@@ -45950,17 +46167,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="12" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>397</v>
       </c>
@@ -45968,12 +46185,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="15" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>395</v>
       </c>
@@ -45981,7 +46198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>362</v>
       </c>
@@ -46639,7 +46856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>361</v>
       </c>
@@ -46656,7 +46873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>389</v>
       </c>
@@ -46664,7 +46881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>1</v>
       </c>
@@ -46804,7 +47021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>351</v>
       </c>
@@ -46812,7 +47029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -46957,8 +47174,11 @@
       <c r="BW37">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="BY37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>394</v>
       </c>
@@ -46966,7 +47186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>381</v>
       </c>
@@ -46974,7 +47194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -47093,12 +47313,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="42" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -47106,7 +47326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -47114,7 +47334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>374</v>
       </c>
@@ -47122,7 +47342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -47246,8 +47466,11 @@
       <c r="BX45">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="BY45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>43</v>
       </c>
@@ -47255,7 +47478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>68</v>
       </c>
@@ -47275,7 +47498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -47283,7 +47506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>368</v>
       </c>
@@ -47297,7 +47520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>345</v>
       </c>
@@ -47314,7 +47537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>343</v>
       </c>
@@ -47331,7 +47554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>344</v>
       </c>
@@ -47345,7 +47568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>10</v>
       </c>
@@ -47488,7 +47711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>46</v>
       </c>
@@ -47547,12 +47770,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="56" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -47569,12 +47792,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="58" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -47695,8 +47918,11 @@
       <c r="BX58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="BY58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>369</v>
       </c>
@@ -47704,7 +47930,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>387</v>
       </c>
@@ -47718,7 +47944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -47732,7 +47958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>340</v>
       </c>
@@ -47755,17 +47981,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="64" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>55</v>
       </c>
@@ -47860,12 +48086,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>81</v>
       </c>
@@ -47902,8 +48128,11 @@
       <c r="BX67">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="BY67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>63</v>
       </c>
@@ -47929,12 +48158,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>22</v>
       </c>
@@ -47981,7 +48210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>376</v>
       </c>
@@ -48007,7 +48236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>44</v>
       </c>
@@ -48060,7 +48289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>379</v>
       </c>
@@ -48071,7 +48300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -48088,12 +48317,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="76" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>82</v>
       </c>
@@ -48241,8 +48470,11 @@
       <c r="BX76">
         <v>2</v>
       </c>
-    </row>
-    <row r="77" spans="1:76" x14ac:dyDescent="0.35">
+      <c r="BY76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>49</v>
       </c>
@@ -48250,12 +48482,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="79" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>85</v>
       </c>
@@ -48269,7 +48501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -48436,7 +48668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>45</v>
       </c>
@@ -48447,7 +48679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>367</v>
       </c>
@@ -48527,7 +48759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>352</v>
       </c>
@@ -48535,12 +48767,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="85" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -48554,7 +48786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>86</v>
       </c>
@@ -48562,7 +48794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:76" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:77" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -48749,8 +48981,11 @@
       <c r="BX87">
         <v>5</v>
       </c>
-    </row>
-    <row r="88" spans="1:76" hidden="1" x14ac:dyDescent="0.35">
+      <c r="BY87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>47</v>
       </c>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D811F9F1-E84B-46AF-87AE-06188FBDC290}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{93108692-A4D1-48D4-A27C-577B4BAD3F0E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notas" sheetId="1" r:id="rId1"/>
@@ -26,14 +26,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'extrato 2024'!$A$1:$C$187</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CY$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$CZ$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9364" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9400" uniqueCount="398">
   <si>
     <t>Jogador</t>
   </si>
@@ -3495,7 +3495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CY88"/>
+  <dimension ref="A1:CZ88"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
@@ -3520,10 +3520,10 @@
     <col min="50" max="58" width="9.54296875" customWidth="1"/>
     <col min="59" max="65" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
-    <col min="67" max="97" width="11" customWidth="1"/>
+    <col min="67" max="98" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3812,27 +3812,30 @@
       <c r="CR1" s="1">
         <v>46134</v>
       </c>
-      <c r="CS1" s="1"/>
-      <c r="CT1" t="s">
+      <c r="CS1" s="1">
+        <v>46141</v>
+      </c>
+      <c r="CT1" s="1"/>
+      <c r="CU1" t="s">
         <v>57</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>58</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>59</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>62</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>392</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4118,31 +4121,34 @@
       <c r="CR2">
         <v>5.5</v>
       </c>
-      <c r="CT2">
-        <f>COUNT(B2:CR2)</f>
-        <v>89</v>
-      </c>
-      <c r="CU2" s="18">
-        <f>AVERAGE(B2:CR2)</f>
-        <v>6.0337078651685392</v>
-      </c>
-      <c r="CV2">
-        <f t="shared" ref="CV2:CV33" si="0">IF(CT2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
+      <c r="CS2">
+        <v>5.5</v>
+      </c>
+      <c r="CU2">
+        <f>COUNT(B2:CS2)</f>
+        <v>90</v>
+      </c>
+      <c r="CV2" s="18">
+        <f>AVERAGE(B2:CS2)</f>
+        <v>6.0277777777777777</v>
+      </c>
+      <c r="CW2">
+        <f t="shared" ref="CW2:CW33" si="0">IF(CU2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
         <v>1.2512468149547391</v>
       </c>
-      <c r="CW2">
-        <v>1</v>
-      </c>
       <c r="CX2">
-        <f t="shared" ref="CX2:CX33" si="1">COUNT(CK2:CN2)</f>
+        <v>1</v>
+      </c>
+      <c r="CY2">
+        <f t="shared" ref="CY2:CY33" si="1">COUNT(CK2:CN2)</f>
         <v>4</v>
       </c>
-      <c r="CY2">
-        <f t="shared" ref="CY2:CY33" si="2">IF(CW2=0,CX2,0)</f>
+      <c r="CZ2">
+        <f t="shared" ref="CZ2:CZ33" si="2">IF(CX2=0,CY2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4428,31 +4434,34 @@
       <c r="CR3">
         <v>5.5</v>
       </c>
-      <c r="CT3">
+      <c r="CS3">
+        <v>5.5</v>
+      </c>
+      <c r="CU3">
         <f>COUNT(B3:CK3)</f>
         <v>79</v>
       </c>
-      <c r="CU3" s="18">
+      <c r="CV3" s="18">
         <f>AVERAGE(B3:CK3)</f>
         <v>5.6518987341772151</v>
       </c>
-      <c r="CV3">
+      <c r="CW3">
         <f t="shared" si="0"/>
         <v>1.0518094984498128</v>
       </c>
-      <c r="CW3">
-        <v>1</v>
-      </c>
       <c r="CX3">
+        <v>1</v>
+      </c>
+      <c r="CY3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CY3">
+      <c r="CZ3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4714,31 +4723,31 @@
       <c r="CI4">
         <v>5.5</v>
       </c>
-      <c r="CT4">
+      <c r="CU4">
         <f>COUNT(B4:CI4)</f>
         <v>72</v>
       </c>
-      <c r="CU4" s="18">
+      <c r="CV4" s="18">
         <f>AVERAGE(B4:CI4)</f>
         <v>5.708333333333333</v>
       </c>
-      <c r="CV4">
+      <c r="CW4">
         <f t="shared" si="0"/>
         <v>0.96435844595057774</v>
       </c>
-      <c r="CW4">
+      <c r="CX4">
         <v>0</v>
       </c>
-      <c r="CX4">
+      <c r="CY4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CY4">
+      <c r="CZ4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -5009,31 +5018,31 @@
       <c r="CR5">
         <v>5.5</v>
       </c>
-      <c r="CT5">
+      <c r="CU5">
         <f>COUNT(B5:CL5)</f>
         <v>71</v>
       </c>
-      <c r="CU5" s="18">
+      <c r="CV5" s="18">
         <f>AVERAGE(B5:CL5)</f>
         <v>7.267605633802817</v>
       </c>
-      <c r="CV5">
+      <c r="CW5">
         <f t="shared" si="0"/>
         <v>1.1294250579557983</v>
       </c>
-      <c r="CW5">
-        <v>1</v>
-      </c>
       <c r="CX5">
+        <v>1</v>
+      </c>
+      <c r="CY5">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CY5">
+      <c r="CZ5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -5310,31 +5319,34 @@
       <c r="CR6">
         <v>5.5</v>
       </c>
-      <c r="CT6">
+      <c r="CS6">
+        <v>5.5</v>
+      </c>
+      <c r="CU6">
         <f>COUNT(B6:CL6)</f>
         <v>70</v>
       </c>
-      <c r="CU6" s="18">
+      <c r="CV6" s="18">
         <f>AVERAGE(B6:CL6)</f>
         <v>6.6142857142857139</v>
       </c>
-      <c r="CV6">
+      <c r="CW6">
         <f t="shared" si="0"/>
         <v>0.9419445925236869</v>
       </c>
-      <c r="CW6">
-        <v>1</v>
-      </c>
       <c r="CX6">
+        <v>1</v>
+      </c>
+      <c r="CY6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CY6">
+      <c r="CZ6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5611,31 +5623,34 @@
       <c r="CR7">
         <v>6.5</v>
       </c>
-      <c r="CT7">
+      <c r="CS7">
+        <v>6.5</v>
+      </c>
+      <c r="CU7">
         <f>COUNT(B7:CL7)</f>
         <v>70</v>
       </c>
-      <c r="CU7" s="18">
+      <c r="CV7" s="18">
         <f>AVERAGE(B7:CL7)</f>
         <v>6.6071428571428568</v>
       </c>
-      <c r="CV7">
+      <c r="CW7">
         <f t="shared" si="0"/>
         <v>1.0570846156365068</v>
       </c>
-      <c r="CW7">
-        <v>1</v>
-      </c>
       <c r="CX7">
+        <v>1</v>
+      </c>
+      <c r="CY7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CY7">
+      <c r="CZ7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5885,31 +5900,31 @@
       <c r="CE8">
         <v>5</v>
       </c>
-      <c r="CT8">
+      <c r="CU8">
         <f>COUNT(B8:CI8)</f>
         <v>68</v>
       </c>
-      <c r="CU8" s="18">
+      <c r="CV8" s="18">
         <f>AVERAGE(B8:CI8)</f>
         <v>6.4191176470588234</v>
       </c>
-      <c r="CV8">
+      <c r="CW8">
         <f t="shared" si="0"/>
         <v>1.1769245721961776</v>
       </c>
-      <c r="CW8">
+      <c r="CX8">
         <v>0</v>
       </c>
-      <c r="CX8">
+      <c r="CY8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CY8">
+      <c r="CZ8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -6165,31 +6180,34 @@
       <c r="CR9">
         <v>5.5</v>
       </c>
-      <c r="CT9">
+      <c r="CS9">
+        <v>5.5</v>
+      </c>
+      <c r="CU9">
         <f>COUNT(B9:CI9)</f>
         <v>67</v>
       </c>
-      <c r="CU9" s="18">
+      <c r="CV9" s="18">
         <f>AVERAGE(B9:CI9)</f>
         <v>5.9701492537313436</v>
       </c>
-      <c r="CV9">
+      <c r="CW9">
         <f t="shared" si="0"/>
         <v>0.96648378625350351</v>
       </c>
-      <c r="CW9">
+      <c r="CX9">
         <v>0</v>
       </c>
-      <c r="CX9">
+      <c r="CY9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CY9">
+      <c r="CZ9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -6466,31 +6484,31 @@
       <c r="CR10">
         <v>6</v>
       </c>
-      <c r="CT10">
+      <c r="CU10">
         <f>COUNT(B10:CI10)</f>
         <v>62</v>
       </c>
-      <c r="CU10" s="18">
+      <c r="CV10" s="18">
         <f>AVERAGE(B10:CI10)</f>
         <v>5.717741935483871</v>
       </c>
-      <c r="CV10">
+      <c r="CW10">
         <f t="shared" si="0"/>
         <v>1.3617531291315086</v>
       </c>
-      <c r="CW10">
-        <v>1</v>
-      </c>
       <c r="CX10">
+        <v>1</v>
+      </c>
+      <c r="CY10">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CY10">
+      <c r="CZ10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6767,31 +6785,34 @@
       <c r="CR11">
         <v>6</v>
       </c>
-      <c r="CT11">
+      <c r="CS11">
+        <v>6</v>
+      </c>
+      <c r="CU11">
         <f>COUNT(B11:CI11)</f>
         <v>59</v>
       </c>
-      <c r="CU11" s="18">
+      <c r="CV11" s="18">
         <f>AVERAGE(B11:CI11)</f>
         <v>6.6779661016949152</v>
       </c>
-      <c r="CV11">
+      <c r="CW11">
         <f t="shared" si="0"/>
         <v>1.0072574989410263</v>
       </c>
-      <c r="CW11">
-        <v>1</v>
-      </c>
       <c r="CX11">
+        <v>1</v>
+      </c>
+      <c r="CY11">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CY11">
+      <c r="CZ11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -7074,31 +7095,31 @@
       <c r="CR12">
         <v>6</v>
       </c>
-      <c r="CT12">
+      <c r="CU12">
         <f>COUNT(B12:CR12)</f>
         <v>62</v>
       </c>
-      <c r="CU12" s="18">
+      <c r="CV12" s="18">
         <f>AVERAGE(B12:CR12)</f>
         <v>5.540322580645161</v>
       </c>
-      <c r="CV12">
+      <c r="CW12">
         <f t="shared" si="0"/>
         <v>1.0254583642020354</v>
       </c>
-      <c r="CW12">
-        <v>1</v>
-      </c>
       <c r="CX12">
+        <v>1</v>
+      </c>
+      <c r="CY12">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CY12">
+      <c r="CZ12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -7378,31 +7399,34 @@
       <c r="CR13">
         <v>7.5</v>
       </c>
-      <c r="CT13">
+      <c r="CS13">
+        <v>5.5</v>
+      </c>
+      <c r="CU13">
         <f>COUNT(B13:CN13)</f>
         <v>56</v>
       </c>
-      <c r="CU13" s="18">
+      <c r="CV13" s="18">
         <f>AVERAGE(B13:CN13)</f>
         <v>6.3571428571428568</v>
       </c>
-      <c r="CV13">
+      <c r="CW13">
         <f t="shared" si="0"/>
         <v>1.1769469323774333</v>
       </c>
-      <c r="CW13">
-        <v>1</v>
-      </c>
       <c r="CX13">
+        <v>1</v>
+      </c>
+      <c r="CY13">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CY13">
+      <c r="CZ13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>367</v>
       </c>
@@ -7658,31 +7682,34 @@
       <c r="CR14">
         <v>6</v>
       </c>
-      <c r="CT14">
+      <c r="CS14">
+        <v>5.5</v>
+      </c>
+      <c r="CU14">
         <f>COUNT(B14:CI14)</f>
         <v>55</v>
       </c>
-      <c r="CU14" s="18">
+      <c r="CV14" s="18">
         <f>AVERAGE(B14:CI14)</f>
         <v>6.3181818181818183</v>
       </c>
-      <c r="CV14">
+      <c r="CW14">
         <f t="shared" si="0"/>
         <v>1.1213885273224193</v>
       </c>
-      <c r="CW14">
+      <c r="CX14">
         <v>0</v>
       </c>
-      <c r="CX14">
+      <c r="CY14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CY14">
+      <c r="CZ14">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -7926,31 +7953,31 @@
       <c r="CF15">
         <v>5.5</v>
       </c>
-      <c r="CT15">
+      <c r="CU15">
         <f>COUNT(B15:CI15)</f>
         <v>52</v>
       </c>
-      <c r="CU15" s="18">
+      <c r="CV15" s="18">
         <f>AVERAGE(B15:CI15)</f>
         <v>5.6923076923076925</v>
       </c>
-      <c r="CV15">
+      <c r="CW15">
         <f t="shared" si="0"/>
         <v>0.84687340856573534</v>
       </c>
-      <c r="CW15">
+      <c r="CX15">
         <v>0</v>
       </c>
-      <c r="CX15">
+      <c r="CY15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CY15">
+      <c r="CZ15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -8200,31 +8227,31 @@
       <c r="CF16">
         <v>5.5</v>
       </c>
-      <c r="CT16">
+      <c r="CU16">
         <f>COUNT(B16:CI16)</f>
         <v>47</v>
       </c>
-      <c r="CU16" s="18">
+      <c r="CV16" s="18">
         <f>AVERAGE(B16:CI16)</f>
         <v>4.4255319148936172</v>
       </c>
-      <c r="CV16">
+      <c r="CW16">
         <f t="shared" si="0"/>
         <v>1.3391217246854428</v>
       </c>
-      <c r="CW16">
+      <c r="CX16">
         <v>0</v>
       </c>
-      <c r="CX16">
+      <c r="CY16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CY16">
+      <c r="CZ16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>56</v>
       </c>
@@ -8510,31 +8537,34 @@
       <c r="CR17">
         <v>6</v>
       </c>
-      <c r="CT17">
+      <c r="CS17">
+        <v>5.5</v>
+      </c>
+      <c r="CU17">
         <f>COUNT(B17:CL17)</f>
         <v>46</v>
       </c>
-      <c r="CU17" s="18">
+      <c r="CV17" s="18">
         <f>AVERAGE(B17:CL17)</f>
         <v>6.0652173913043477</v>
       </c>
-      <c r="CV17">
+      <c r="CW17">
         <f t="shared" si="0"/>
         <v>0.9573434129174403</v>
       </c>
-      <c r="CW17">
-        <v>1</v>
-      </c>
       <c r="CX17">
+        <v>1</v>
+      </c>
+      <c r="CY17">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CY17">
+      <c r="CZ17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -8802,31 +8832,31 @@
       <c r="CL18">
         <v>6</v>
       </c>
-      <c r="CT18">
+      <c r="CU18">
         <f>COUNT(B18:CL18)</f>
         <v>44</v>
       </c>
-      <c r="CU18" s="18">
+      <c r="CV18" s="18">
         <f>AVERAGE(B18:CL18)</f>
         <v>5.0113636363636367</v>
       </c>
-      <c r="CV18">
+      <c r="CW18">
         <f t="shared" si="0"/>
         <v>1.0645089158214895</v>
       </c>
-      <c r="CW18">
-        <v>1</v>
-      </c>
       <c r="CX18">
+        <v>1</v>
+      </c>
+      <c r="CY18">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CY18">
+      <c r="CZ18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -9070,31 +9100,31 @@
       <c r="CK19">
         <v>5.5</v>
       </c>
-      <c r="CT19">
+      <c r="CU19">
         <f>COUNT(B19:CI19)</f>
         <v>38</v>
       </c>
-      <c r="CU19" s="18">
+      <c r="CV19" s="18">
         <f>AVERAGE(B19:CI19)</f>
         <v>6.1578947368421053</v>
       </c>
-      <c r="CV19">
+      <c r="CW19">
         <f t="shared" si="0"/>
         <v>1.0973263770680928</v>
       </c>
-      <c r="CW19">
+      <c r="CX19">
         <v>0</v>
       </c>
-      <c r="CX19">
+      <c r="CY19">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CY19">
+      <c r="CZ19">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -9359,31 +9389,34 @@
       <c r="CM20">
         <v>5.5</v>
       </c>
-      <c r="CT20">
+      <c r="CS20">
+        <v>6</v>
+      </c>
+      <c r="CU20">
         <f>COUNT(B20:CJ20)</f>
         <v>37</v>
       </c>
-      <c r="CU20" s="18">
+      <c r="CV20" s="18">
         <f>AVERAGE(B20:CJ20)</f>
         <v>5.2027027027027026</v>
       </c>
-      <c r="CV20">
+      <c r="CW20">
         <f t="shared" si="0"/>
         <v>1.3241383031954423</v>
       </c>
-      <c r="CW20">
+      <c r="CX20">
         <v>0</v>
       </c>
-      <c r="CX20">
+      <c r="CY20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CY20">
+      <c r="CZ20">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -9645,31 +9678,31 @@
       <c r="CR21">
         <v>5.5</v>
       </c>
-      <c r="CT21">
+      <c r="CU21">
         <f>COUNT(B21:CI21)</f>
         <v>36</v>
       </c>
-      <c r="CU21" s="18">
+      <c r="CV21" s="18">
         <f>AVERAGE(B21:CI21)</f>
         <v>5.7361111111111107</v>
       </c>
-      <c r="CV21">
+      <c r="CW21">
         <f t="shared" si="0"/>
         <v>0.92956296268047622</v>
       </c>
-      <c r="CW21">
-        <v>1</v>
-      </c>
       <c r="CX21">
+        <v>1</v>
+      </c>
+      <c r="CY21">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="CY21">
+      <c r="CZ21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -9943,31 +9976,34 @@
       <c r="CR22">
         <v>5.5</v>
       </c>
-      <c r="CT22">
+      <c r="CS22">
+        <v>5.5</v>
+      </c>
+      <c r="CU22">
         <f>COUNT(B22:CI22)</f>
         <v>36</v>
       </c>
-      <c r="CU22" s="18">
+      <c r="CV22" s="18">
         <f>AVERAGE(B22:CI22)</f>
         <v>5.6111111111111107</v>
       </c>
-      <c r="CV22">
+      <c r="CW22">
         <f t="shared" si="0"/>
         <v>1.0098256776095882</v>
       </c>
-      <c r="CW22">
-        <v>1</v>
-      </c>
       <c r="CX22">
+        <v>1</v>
+      </c>
+      <c r="CY22">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CY22">
+      <c r="CZ22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -10238,31 +10274,31 @@
       <c r="CN23">
         <v>6</v>
       </c>
-      <c r="CT23">
+      <c r="CU23">
         <f>COUNT(B23:CN23)</f>
         <v>30</v>
       </c>
-      <c r="CU23" s="18">
+      <c r="CV23" s="18">
         <f>AVERAGE(B23:CN23)</f>
         <v>6.4</v>
       </c>
-      <c r="CV23">
+      <c r="CW23">
         <f t="shared" si="0"/>
         <v>0.90960483309014595</v>
       </c>
-      <c r="CW23">
-        <v>1</v>
-      </c>
       <c r="CX23">
+        <v>1</v>
+      </c>
+      <c r="CY23">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CY23">
+      <c r="CZ23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -10515,31 +10551,31 @@
       <c r="CR24">
         <v>6</v>
       </c>
-      <c r="CT24">
-        <f t="shared" ref="CT24:CT31" si="3">COUNT(B24:CI24)</f>
+      <c r="CU24">
+        <f t="shared" ref="CU24:CU31" si="3">COUNT(B24:CI24)</f>
         <v>25</v>
       </c>
-      <c r="CU24" s="18">
-        <f t="shared" ref="CU24:CU31" si="4">AVERAGE(B24:CI24)</f>
+      <c r="CV24" s="18">
+        <f t="shared" ref="CV24:CV31" si="4">AVERAGE(B24:CI24)</f>
         <v>5.4</v>
       </c>
-      <c r="CV24">
+      <c r="CW24">
         <f t="shared" si="0"/>
         <v>0.71728150235677346</v>
       </c>
-      <c r="CW24">
+      <c r="CX24">
         <v>0</v>
       </c>
-      <c r="CX24">
+      <c r="CY24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CY24">
+      <c r="CZ24">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -10780,31 +10816,31 @@
       <c r="CB25" t="s">
         <v>26</v>
       </c>
-      <c r="CT25">
+      <c r="CU25">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="CU25" s="18">
+      <c r="CV25" s="18">
         <f t="shared" si="4"/>
         <v>5.7894736842105265</v>
       </c>
-      <c r="CV25">
+      <c r="CW25">
         <f t="shared" si="0"/>
         <v>1.3674366679797902</v>
       </c>
-      <c r="CW25">
+      <c r="CX25">
         <v>0</v>
       </c>
-      <c r="CX25">
+      <c r="CY25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CY25">
+      <c r="CZ25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>346</v>
       </c>
@@ -11045,31 +11081,31 @@
       <c r="CB26" t="s">
         <v>26</v>
       </c>
-      <c r="CT26">
+      <c r="CU26">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="CU26" s="18">
+      <c r="CV26" s="18">
         <f t="shared" si="4"/>
         <v>5.9444444444444446</v>
       </c>
-      <c r="CV26">
+      <c r="CW26">
         <f t="shared" si="0"/>
         <v>0.72535769855270305</v>
       </c>
-      <c r="CW26">
+      <c r="CX26">
         <v>0</v>
       </c>
-      <c r="CX26">
+      <c r="CY26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CY26">
+      <c r="CZ26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -11310,31 +11346,31 @@
       <c r="CB27" t="s">
         <v>26</v>
       </c>
-      <c r="CT27">
+      <c r="CU27">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="CU27" s="18">
+      <c r="CV27" s="18">
         <f t="shared" si="4"/>
         <v>5.3235294117647056</v>
       </c>
-      <c r="CV27">
+      <c r="CW27">
         <f t="shared" si="0"/>
         <v>1.3456083251473603</v>
       </c>
-      <c r="CW27">
+      <c r="CX27">
         <v>0</v>
       </c>
-      <c r="CX27">
+      <c r="CY27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CY27">
+      <c r="CZ27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -11575,31 +11611,31 @@
       <c r="CB28" t="s">
         <v>26</v>
       </c>
-      <c r="CT28">
+      <c r="CU28">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="CU28" s="18">
+      <c r="CV28" s="18">
         <f t="shared" si="4"/>
         <v>4.53125</v>
       </c>
-      <c r="CV28">
+      <c r="CW28">
         <f t="shared" si="0"/>
         <v>1.5434674167816653</v>
       </c>
-      <c r="CW28">
+      <c r="CX28">
         <v>0</v>
       </c>
-      <c r="CX28">
+      <c r="CY28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CY28">
+      <c r="CZ28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -11855,31 +11891,31 @@
       <c r="CQ29">
         <v>6.5</v>
       </c>
-      <c r="CT29">
+      <c r="CU29">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="CU29" s="18">
+      <c r="CV29" s="18">
         <f t="shared" si="4"/>
         <v>6.65625</v>
       </c>
-      <c r="CV29">
+      <c r="CW29">
         <f t="shared" si="0"/>
         <v>0.74651970279870483</v>
       </c>
-      <c r="CW29">
-        <v>1</v>
-      </c>
       <c r="CX29">
+        <v>1</v>
+      </c>
+      <c r="CY29">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="CY29">
+      <c r="CZ29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -12120,31 +12156,31 @@
       <c r="CB30">
         <v>5.5</v>
       </c>
-      <c r="CT30">
+      <c r="CU30">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="CU30" s="18">
+      <c r="CV30" s="18">
         <f t="shared" si="4"/>
         <v>3.8666666666666667</v>
       </c>
-      <c r="CV30">
+      <c r="CW30">
         <f t="shared" si="0"/>
         <v>2.3563490726929555</v>
       </c>
-      <c r="CW30">
+      <c r="CX30">
         <v>0</v>
       </c>
-      <c r="CX30">
+      <c r="CY30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CY30">
+      <c r="CZ30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -12397,31 +12433,31 @@
       <c r="CP31">
         <v>6</v>
       </c>
-      <c r="CT31">
+      <c r="CU31">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="CU31" s="18">
+      <c r="CV31" s="18">
         <f t="shared" si="4"/>
         <v>4.8214285714285712</v>
       </c>
-      <c r="CV31">
+      <c r="CW31">
         <f t="shared" si="0"/>
         <v>0.89335151148745728</v>
       </c>
-      <c r="CW31">
+      <c r="CX31">
         <v>0</v>
       </c>
-      <c r="CX31">
+      <c r="CY31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="CY31">
+      <c r="CZ31">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -12701,31 +12737,34 @@
       <c r="CR32">
         <v>6.5</v>
       </c>
-      <c r="CT32">
-        <f>COUNT(B32:CR32)</f>
-        <v>17</v>
-      </c>
-      <c r="CU32" s="18">
-        <f>AVERAGE(B32:CR32)</f>
-        <v>6.3529411764705879</v>
-      </c>
-      <c r="CV32">
+      <c r="CS32">
+        <v>5.5</v>
+      </c>
+      <c r="CU32">
+        <f>COUNT(B32:CS32)</f>
+        <v>18</v>
+      </c>
+      <c r="CV32" s="18">
+        <f>AVERAGE(B32:CS32)</f>
+        <v>6.3055555555555554</v>
+      </c>
+      <c r="CW32">
         <f t="shared" si="0"/>
         <v>0.90829510622924903</v>
       </c>
-      <c r="CW32">
-        <v>1</v>
-      </c>
       <c r="CX32">
+        <v>1</v>
+      </c>
+      <c r="CY32">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="CY32">
+      <c r="CZ32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -12966,31 +13005,31 @@
       <c r="CB33" t="s">
         <v>26</v>
       </c>
-      <c r="CT33">
-        <f t="shared" ref="CT33:CT64" si="5">COUNT(B33:CI33)</f>
+      <c r="CU33">
+        <f t="shared" ref="CU33:CU64" si="5">COUNT(B33:CI33)</f>
         <v>13</v>
       </c>
-      <c r="CU33" s="18">
-        <f t="shared" ref="CU33:CU64" si="6">AVERAGE(B33:CI33)</f>
+      <c r="CV33" s="18">
+        <f t="shared" ref="CV33:CV64" si="6">AVERAGE(B33:CI33)</f>
         <v>7.3461538461538458</v>
       </c>
-      <c r="CV33">
+      <c r="CW33">
         <f t="shared" si="0"/>
         <v>1.5191090506255012</v>
       </c>
-      <c r="CW33">
+      <c r="CX33">
         <v>0</v>
       </c>
-      <c r="CX33">
+      <c r="CY33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CY33">
+      <c r="CZ33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -13231,31 +13270,31 @@
       <c r="CB34" t="s">
         <v>26</v>
       </c>
-      <c r="CT34">
+      <c r="CU34">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="CU34" s="18">
+      <c r="CV34" s="18">
         <f t="shared" si="6"/>
         <v>4.6818181818181817</v>
       </c>
-      <c r="CV34">
-        <f t="shared" ref="CV34:CV65" si="7">IF(CT34&gt;1,_xlfn.STDEV.S(B34:CF34),"")</f>
+      <c r="CW34">
+        <f t="shared" ref="CW34:CW65" si="7">IF(CU34&gt;1,_xlfn.STDEV.S(B34:CF34),"")</f>
         <v>0.81463879335344846</v>
       </c>
-      <c r="CW34">
+      <c r="CX34">
         <v>0</v>
       </c>
-      <c r="CX34">
-        <f t="shared" ref="CX34:CX65" si="8">COUNT(CK34:CN34)</f>
+      <c r="CY34">
+        <f t="shared" ref="CY34:CY65" si="8">COUNT(CK34:CN34)</f>
         <v>0</v>
       </c>
-      <c r="CY34">
-        <f t="shared" ref="CY34:CY65" si="9">IF(CW34=0,CX34,0)</f>
+      <c r="CZ34">
+        <f t="shared" ref="CZ34:CZ65" si="9">IF(CX34=0,CY34,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>45</v>
       </c>
@@ -13499,31 +13538,31 @@
       <c r="CC35">
         <v>6</v>
       </c>
-      <c r="CT35">
+      <c r="CU35">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="CU35" s="18">
+      <c r="CV35" s="18">
         <f t="shared" si="6"/>
         <v>8.4499999999999993</v>
       </c>
-      <c r="CV35">
+      <c r="CW35">
         <f t="shared" si="7"/>
         <v>1.1890705987824657</v>
       </c>
-      <c r="CW35">
+      <c r="CX35">
         <v>0</v>
       </c>
-      <c r="CX35">
+      <c r="CY35">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY35">
+      <c r="CZ35">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>343</v>
       </c>
@@ -13782,31 +13821,31 @@
       <c r="CR36">
         <v>6</v>
       </c>
-      <c r="CT36">
+      <c r="CU36">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="CU36" s="18">
+      <c r="CV36" s="18">
         <f t="shared" si="6"/>
         <v>4.125</v>
       </c>
-      <c r="CV36">
+      <c r="CW36">
         <f t="shared" si="7"/>
         <v>1.7677669529663689</v>
       </c>
-      <c r="CW36">
-        <v>1</v>
-      </c>
       <c r="CX36">
+        <v>1</v>
+      </c>
+      <c r="CY36">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CY36">
+      <c r="CZ36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>340</v>
       </c>
@@ -14050,31 +14089,31 @@
       <c r="CL37">
         <v>6</v>
       </c>
-      <c r="CT37">
+      <c r="CU37">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CU37" s="18">
+      <c r="CV37" s="18">
         <f t="shared" si="6"/>
         <v>5.7142857142857144</v>
       </c>
-      <c r="CV37">
+      <c r="CW37">
         <f t="shared" si="7"/>
         <v>0.56694670951384085</v>
       </c>
-      <c r="CW37">
+      <c r="CX37">
         <v>0</v>
       </c>
-      <c r="CX37">
+      <c r="CY37">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CY37">
+      <c r="CZ37">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>376</v>
       </c>
@@ -14324,31 +14363,34 @@
       <c r="CQ38">
         <v>7.5</v>
       </c>
-      <c r="CT38">
+      <c r="CS38">
+        <v>6</v>
+      </c>
+      <c r="CU38">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="CU38" s="18">
+      <c r="CV38" s="18">
         <f t="shared" si="6"/>
         <v>5.7857142857142856</v>
       </c>
-      <c r="CV38">
+      <c r="CW38">
         <f t="shared" si="7"/>
         <v>0.4879500364742666</v>
       </c>
-      <c r="CW38">
+      <c r="CX38">
         <v>0</v>
       </c>
-      <c r="CX38">
+      <c r="CY38">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CY38">
+      <c r="CZ38">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>378</v>
       </c>
@@ -14616,31 +14658,31 @@
       <c r="CQ39">
         <v>5.5</v>
       </c>
-      <c r="CT39">
+      <c r="CU39">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="CU39" s="18">
+      <c r="CV39" s="18">
         <f t="shared" si="6"/>
         <v>5.166666666666667</v>
       </c>
-      <c r="CV39">
+      <c r="CW39">
         <f t="shared" si="7"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="CW39">
-        <v>1</v>
-      </c>
       <c r="CX39">
+        <v>1</v>
+      </c>
+      <c r="CY39">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CY39">
+      <c r="CZ39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -14884,31 +14926,31 @@
       <c r="CH40">
         <v>6.5</v>
       </c>
-      <c r="CT40">
+      <c r="CU40">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CU40" s="18">
+      <c r="CV40" s="18">
         <f t="shared" si="6"/>
         <v>7.8</v>
       </c>
-      <c r="CV40">
+      <c r="CW40">
         <f t="shared" si="7"/>
         <v>1.0307764064044151</v>
       </c>
-      <c r="CW40">
+      <c r="CX40">
         <v>0</v>
       </c>
-      <c r="CX40">
+      <c r="CY40">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY40">
+      <c r="CZ40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>60</v>
       </c>
@@ -15152,31 +15194,31 @@
       <c r="CM41">
         <v>5.5</v>
       </c>
-      <c r="CT41">
+      <c r="CU41">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CU41" s="18">
+      <c r="CV41" s="18">
         <f t="shared" si="6"/>
         <v>3.375</v>
       </c>
-      <c r="CV41">
+      <c r="CW41">
         <f t="shared" si="7"/>
         <v>0.47871355387816905</v>
       </c>
-      <c r="CW41">
+      <c r="CX41">
         <v>0</v>
       </c>
-      <c r="CX41">
+      <c r="CY41">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="CY41">
+      <c r="CZ41">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -15417,31 +15459,31 @@
       <c r="CB42" t="s">
         <v>26</v>
       </c>
-      <c r="CT42">
+      <c r="CU42">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CU42" s="18">
+      <c r="CV42" s="18">
         <f t="shared" si="6"/>
         <v>5.625</v>
       </c>
-      <c r="CV42">
+      <c r="CW42">
         <f t="shared" si="7"/>
         <v>0.9464847243000456</v>
       </c>
-      <c r="CW42">
+      <c r="CX42">
         <v>0</v>
       </c>
-      <c r="CX42">
+      <c r="CY42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY42">
+      <c r="CZ42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -15682,31 +15724,31 @@
       <c r="CB43" t="s">
         <v>26</v>
       </c>
-      <c r="CT43">
+      <c r="CU43">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CU43" s="18">
+      <c r="CV43" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CV43">
+      <c r="CW43">
         <f t="shared" si="7"/>
         <v>1.0408329997330663</v>
       </c>
-      <c r="CW43">
+      <c r="CX43">
         <v>0</v>
       </c>
-      <c r="CX43">
+      <c r="CY43">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY43">
+      <c r="CZ43">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -15947,31 +15989,31 @@
       <c r="CB44" t="s">
         <v>26</v>
       </c>
-      <c r="CT44">
+      <c r="CU44">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CU44" s="18">
+      <c r="CV44" s="18">
         <f t="shared" si="6"/>
         <v>1.375</v>
       </c>
-      <c r="CV44">
+      <c r="CW44">
         <f t="shared" si="7"/>
         <v>1.8874586088176875</v>
       </c>
-      <c r="CW44">
+      <c r="CX44">
         <v>0</v>
       </c>
-      <c r="CX44">
+      <c r="CY44">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY44">
+      <c r="CZ44">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>344</v>
       </c>
@@ -16212,31 +16254,31 @@
       <c r="CB45" t="s">
         <v>26</v>
       </c>
-      <c r="CT45">
+      <c r="CU45">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CU45" s="18">
+      <c r="CV45" s="18">
         <f t="shared" si="6"/>
         <v>4.625</v>
       </c>
-      <c r="CV45">
+      <c r="CW45">
         <f t="shared" si="7"/>
         <v>1.4361406616345072</v>
       </c>
-      <c r="CW45">
+      <c r="CX45">
         <v>0</v>
       </c>
-      <c r="CX45">
+      <c r="CY45">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY45">
+      <c r="CZ45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>361</v>
       </c>
@@ -16477,31 +16519,31 @@
       <c r="CB46" t="s">
         <v>26</v>
       </c>
-      <c r="CT46">
+      <c r="CU46">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CU46" s="18">
+      <c r="CV46" s="18">
         <f t="shared" si="6"/>
         <v>6.25</v>
       </c>
-      <c r="CV46">
+      <c r="CW46">
         <f t="shared" si="7"/>
         <v>0.8660254037844386</v>
       </c>
-      <c r="CW46">
+      <c r="CX46">
         <v>0</v>
       </c>
-      <c r="CX46">
+      <c r="CY46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY46">
+      <c r="CZ46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -16742,31 +16784,31 @@
       <c r="CB47" t="s">
         <v>26</v>
       </c>
-      <c r="CT47">
+      <c r="CU47">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CU47" s="18">
+      <c r="CV47" s="18">
         <f t="shared" si="6"/>
         <v>2.875</v>
       </c>
-      <c r="CV47">
+      <c r="CW47">
         <f t="shared" si="7"/>
         <v>2.7801378862687129</v>
       </c>
-      <c r="CW47">
+      <c r="CX47">
         <v>0</v>
       </c>
-      <c r="CX47">
+      <c r="CY47">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY47">
+      <c r="CZ47">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -17007,31 +17049,31 @@
       <c r="CB48" t="s">
         <v>26</v>
       </c>
-      <c r="CT48">
+      <c r="CU48">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CU48" s="18">
+      <c r="CV48" s="18">
         <f t="shared" si="6"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="CV48">
+      <c r="CW48">
         <f t="shared" si="7"/>
         <v>1.4433756729740652</v>
       </c>
-      <c r="CW48">
+      <c r="CX48">
         <v>0</v>
       </c>
-      <c r="CX48">
+      <c r="CY48">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY48">
+      <c r="CZ48">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -17272,31 +17314,31 @@
       <c r="CB49" t="s">
         <v>26</v>
       </c>
-      <c r="CT49">
+      <c r="CU49">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CU49" s="18">
+      <c r="CV49" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CV49">
+      <c r="CW49">
         <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
-      <c r="CW49">
+      <c r="CX49">
         <v>0</v>
       </c>
-      <c r="CX49">
+      <c r="CY49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY49">
+      <c r="CZ49">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -17537,31 +17579,31 @@
       <c r="CB50" t="s">
         <v>26</v>
       </c>
-      <c r="CT50">
+      <c r="CU50">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CU50" s="18">
+      <c r="CV50" s="18">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="CV50">
+      <c r="CW50">
         <f t="shared" si="7"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CW50">
+      <c r="CX50">
         <v>0</v>
       </c>
-      <c r="CX50">
+      <c r="CY50">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY50">
+      <c r="CZ50">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -17805,31 +17847,31 @@
       <c r="CG51">
         <v>6</v>
       </c>
-      <c r="CT51">
+      <c r="CU51">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CU51" s="18">
+      <c r="CV51" s="18">
         <f t="shared" si="6"/>
         <v>5.666666666666667</v>
       </c>
-      <c r="CV51">
+      <c r="CW51">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CW51">
+      <c r="CX51">
         <v>0</v>
       </c>
-      <c r="CX51">
+      <c r="CY51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY51">
+      <c r="CZ51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>368</v>
       </c>
@@ -18073,31 +18115,31 @@
       <c r="CG52">
         <v>6</v>
       </c>
-      <c r="CT52">
+      <c r="CU52">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CU52" s="18">
+      <c r="CV52" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="CV52">
+      <c r="CW52">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CW52">
+      <c r="CX52">
         <v>0</v>
       </c>
-      <c r="CX52">
+      <c r="CY52">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY52">
+      <c r="CZ52">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>362</v>
       </c>
@@ -18341,31 +18383,31 @@
       <c r="CD53">
         <v>5.5</v>
       </c>
-      <c r="CT53">
+      <c r="CU53">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CU53" s="18">
+      <c r="CV53" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CV53">
+      <c r="CW53">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CW53">
+      <c r="CX53">
         <v>0</v>
       </c>
-      <c r="CX53">
+      <c r="CY53">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY53">
+      <c r="CZ53">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>364</v>
       </c>
@@ -18615,31 +18657,31 @@
       <c r="CN54">
         <v>6</v>
       </c>
-      <c r="CT54">
+      <c r="CU54">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CU54" s="18">
+      <c r="CV54" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="CV54">
+      <c r="CW54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CW54">
-        <v>1</v>
-      </c>
       <c r="CX54">
+        <v>1</v>
+      </c>
+      <c r="CY54">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CY54">
+      <c r="CZ54">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -18880,31 +18922,34 @@
       <c r="CB55" t="s">
         <v>26</v>
       </c>
-      <c r="CT55">
+      <c r="CS55">
+        <v>5.5</v>
+      </c>
+      <c r="CU55">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CU55" s="18">
+      <c r="CV55" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="CV55">
+      <c r="CW55">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CW55">
+      <c r="CX55">
         <v>0</v>
       </c>
-      <c r="CX55">
+      <c r="CY55">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY55">
+      <c r="CZ55">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>339</v>
       </c>
@@ -19145,31 +19190,31 @@
       <c r="CB56" t="s">
         <v>26</v>
       </c>
-      <c r="CT56">
+      <c r="CU56">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CU56" s="18">
+      <c r="CV56" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="CV56">
+      <c r="CW56">
         <f t="shared" si="7"/>
         <v>2.4748737341529163</v>
       </c>
-      <c r="CW56">
+      <c r="CX56">
         <v>0</v>
       </c>
-      <c r="CX56">
+      <c r="CY56">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY56">
+      <c r="CZ56">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>342</v>
       </c>
@@ -19416,31 +19461,31 @@
       <c r="CO57">
         <v>6</v>
       </c>
-      <c r="CT57">
+      <c r="CU57">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CU57" s="18">
+      <c r="CV57" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CV57">
+      <c r="CW57">
         <f t="shared" si="7"/>
         <v>2.1213203435596424</v>
       </c>
-      <c r="CW57">
+      <c r="CX57">
         <v>0</v>
       </c>
-      <c r="CX57">
+      <c r="CY57">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY57">
+      <c r="CZ57">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>369</v>
       </c>
@@ -19681,31 +19726,31 @@
       <c r="CB58" t="s">
         <v>26</v>
       </c>
-      <c r="CT58">
+      <c r="CU58">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CU58" s="18">
+      <c r="CV58" s="18">
         <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
-      <c r="CV58">
+      <c r="CW58">
         <f t="shared" si="7"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="CW58">
+      <c r="CX58">
         <v>0</v>
       </c>
-      <c r="CX58">
+      <c r="CY58">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY58">
+      <c r="CZ58">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>379</v>
       </c>
@@ -19946,31 +19991,31 @@
       <c r="CB59" t="s">
         <v>26</v>
       </c>
-      <c r="CT59">
+      <c r="CU59">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CU59" s="18">
+      <c r="CV59" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="CV59">
+      <c r="CW59">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CW59">
+      <c r="CX59">
         <v>0</v>
       </c>
-      <c r="CX59">
+      <c r="CY59">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY59">
+      <c r="CZ59">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>390</v>
       </c>
@@ -20217,31 +20262,34 @@
       <c r="CH60">
         <v>7</v>
       </c>
-      <c r="CT60">
+      <c r="CS60">
+        <v>6.5</v>
+      </c>
+      <c r="CU60">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CU60" s="18">
+      <c r="CV60" s="18">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="CV60" t="e">
+      <c r="CW60" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CW60">
+      <c r="CX60">
         <v>0</v>
       </c>
-      <c r="CX60">
+      <c r="CY60">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY60">
+      <c r="CZ60">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>388</v>
       </c>
@@ -20485,31 +20533,31 @@
       <c r="CH61">
         <v>5</v>
       </c>
-      <c r="CT61">
+      <c r="CU61">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CU61" s="18">
+      <c r="CV61" s="18">
         <f t="shared" si="6"/>
         <v>4.25</v>
       </c>
-      <c r="CV61" t="e">
+      <c r="CW61" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CW61">
+      <c r="CX61">
         <v>0</v>
       </c>
-      <c r="CX61">
+      <c r="CY61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY61">
+      <c r="CZ61">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>345</v>
       </c>
@@ -20768,31 +20816,31 @@
       <c r="CO62">
         <v>4.5</v>
       </c>
-      <c r="CT62">
+      <c r="CU62">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CU62" s="18">
+      <c r="CV62" s="18">
         <f t="shared" si="6"/>
         <v>4.25</v>
       </c>
-      <c r="CV62" t="e">
+      <c r="CW62" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CW62">
-        <v>1</v>
-      </c>
       <c r="CX62">
+        <v>1</v>
+      </c>
+      <c r="CY62">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="CY62">
+      <c r="CZ62">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>387</v>
       </c>
@@ -21042,31 +21090,31 @@
       <c r="CJ63">
         <v>7</v>
       </c>
-      <c r="CT63">
+      <c r="CU63">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="CU63" s="18">
+      <c r="CV63" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="CV63" t="e">
+      <c r="CW63" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CW63">
+      <c r="CX63">
         <v>0</v>
       </c>
-      <c r="CX63">
+      <c r="CY63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY63">
+      <c r="CZ63">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>86</v>
       </c>
@@ -21307,31 +21355,31 @@
       <c r="CB64" t="s">
         <v>26</v>
       </c>
-      <c r="CT64">
+      <c r="CU64">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="CU64" s="18">
+      <c r="CV64" s="18">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="CV64" t="str">
+      <c r="CW64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="CW64">
+      <c r="CX64">
         <v>0</v>
       </c>
-      <c r="CX64">
+      <c r="CY64">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY64">
+      <c r="CZ64">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -21572,31 +21620,31 @@
       <c r="CB65" t="s">
         <v>26</v>
       </c>
-      <c r="CT65">
-        <f t="shared" ref="CT65:CT83" si="10">COUNT(B65:CI65)</f>
-        <v>1</v>
-      </c>
-      <c r="CU65" s="18">
-        <f t="shared" ref="CU65:CU83" si="11">AVERAGE(B65:CI65)</f>
+      <c r="CU65">
+        <f t="shared" ref="CU65:CU83" si="10">COUNT(B65:CI65)</f>
+        <v>1</v>
+      </c>
+      <c r="CV65" s="18">
+        <f t="shared" ref="CV65:CV83" si="11">AVERAGE(B65:CI65)</f>
         <v>7</v>
       </c>
-      <c r="CV65" t="str">
+      <c r="CW65" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="CW65">
+      <c r="CX65">
         <v>0</v>
       </c>
-      <c r="CX65">
+      <c r="CY65">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CY65">
+      <c r="CZ65">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>353</v>
       </c>
@@ -21837,31 +21885,31 @@
       <c r="CB66" t="s">
         <v>26</v>
       </c>
-      <c r="CT66">
+      <c r="CU66">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU66" s="18">
+      <c r="CV66" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CV66" t="str">
-        <f t="shared" ref="CV66:CV83" si="12">IF(CT66&gt;1,_xlfn.STDEV.S(B66:CF66),"")</f>
+      <c r="CW66" t="str">
+        <f t="shared" ref="CW66:CW83" si="12">IF(CU66&gt;1,_xlfn.STDEV.S(B66:CF66),"")</f>
         <v/>
       </c>
-      <c r="CW66">
+      <c r="CX66">
         <v>0</v>
       </c>
-      <c r="CX66">
-        <f t="shared" ref="CX66:CX83" si="13">COUNT(CK66:CN66)</f>
+      <c r="CY66">
+        <f t="shared" ref="CY66:CY83" si="13">COUNT(CK66:CN66)</f>
         <v>0</v>
       </c>
-      <c r="CY66">
-        <f t="shared" ref="CY66:CY83" si="14">IF(CW66=0,CX66,0)</f>
+      <c r="CZ66">
+        <f t="shared" ref="CZ66:CZ83" si="14">IF(CX66=0,CY66,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>80</v>
       </c>
@@ -22102,31 +22150,31 @@
       <c r="CB67" t="s">
         <v>26</v>
       </c>
-      <c r="CT67">
+      <c r="CU67">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU67" s="18">
+      <c r="CV67" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CV67" t="str">
+      <c r="CW67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW67">
+      <c r="CX67">
         <v>0</v>
       </c>
-      <c r="CX67">
+      <c r="CY67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY67">
+      <c r="CZ67">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>47</v>
       </c>
@@ -22367,31 +22415,31 @@
       <c r="CB68" t="s">
         <v>26</v>
       </c>
-      <c r="CT68">
+      <c r="CU68">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU68" s="18">
+      <c r="CV68" s="18">
         <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
-      <c r="CV68" t="str">
+      <c r="CW68" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW68">
+      <c r="CX68">
         <v>0</v>
       </c>
-      <c r="CX68">
+      <c r="CY68">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY68">
+      <c r="CZ68">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -22632,31 +22680,31 @@
       <c r="CB69" t="s">
         <v>26</v>
       </c>
-      <c r="CT69">
+      <c r="CU69">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU69" s="18">
+      <c r="CV69" s="18">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="CV69" t="str">
+      <c r="CW69" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW69">
+      <c r="CX69">
         <v>0</v>
       </c>
-      <c r="CX69">
+      <c r="CY69">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY69">
+      <c r="CZ69">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>347</v>
       </c>
@@ -22897,31 +22945,31 @@
       <c r="CB70" t="s">
         <v>26</v>
       </c>
-      <c r="CT70">
+      <c r="CU70">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU70" s="18">
+      <c r="CV70" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="CV70" t="str">
+      <c r="CW70" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW70">
+      <c r="CX70">
         <v>0</v>
       </c>
-      <c r="CX70">
+      <c r="CY70">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY70">
+      <c r="CZ70">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>350</v>
       </c>
@@ -23162,31 +23210,31 @@
       <c r="CB71" t="s">
         <v>26</v>
       </c>
-      <c r="CT71">
+      <c r="CU71">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU71" s="18">
+      <c r="CV71" s="18">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="CV71" t="str">
+      <c r="CW71" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW71">
+      <c r="CX71">
         <v>0</v>
       </c>
-      <c r="CX71">
+      <c r="CY71">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY71">
+      <c r="CZ71">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>351</v>
       </c>
@@ -23427,31 +23475,31 @@
       <c r="CB72" t="s">
         <v>26</v>
       </c>
-      <c r="CT72">
+      <c r="CU72">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU72" s="18">
+      <c r="CV72" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="CV72" t="str">
+      <c r="CW72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW72">
+      <c r="CX72">
         <v>0</v>
       </c>
-      <c r="CX72">
+      <c r="CY72">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY72">
+      <c r="CZ72">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>352</v>
       </c>
@@ -23692,31 +23740,31 @@
       <c r="CB73" t="s">
         <v>26</v>
       </c>
-      <c r="CT73">
+      <c r="CU73">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU73" s="18">
+      <c r="CV73" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="CV73" t="str">
+      <c r="CW73" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW73">
+      <c r="CX73">
         <v>0</v>
       </c>
-      <c r="CX73">
+      <c r="CY73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY73">
+      <c r="CZ73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>354</v>
       </c>
@@ -23957,31 +24005,31 @@
       <c r="CB74" t="s">
         <v>26</v>
       </c>
-      <c r="CT74">
+      <c r="CU74">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU74" s="18">
+      <c r="CV74" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CV74" t="str">
+      <c r="CW74" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW74">
+      <c r="CX74">
         <v>0</v>
       </c>
-      <c r="CX74">
+      <c r="CY74">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY74">
+      <c r="CZ74">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>365</v>
       </c>
@@ -24222,31 +24270,31 @@
       <c r="CB75" t="s">
         <v>26</v>
       </c>
-      <c r="CT75">
+      <c r="CU75">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU75" s="18">
+      <c r="CV75" s="18">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
-      <c r="CV75" t="str">
+      <c r="CW75" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW75">
+      <c r="CX75">
         <v>0</v>
       </c>
-      <c r="CX75">
+      <c r="CY75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY75">
+      <c r="CZ75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>366</v>
       </c>
@@ -24487,31 +24535,31 @@
       <c r="CB76" t="s">
         <v>26</v>
       </c>
-      <c r="CT76">
+      <c r="CU76">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU76" s="18">
+      <c r="CV76" s="18">
         <f t="shared" si="11"/>
         <v>2.5</v>
       </c>
-      <c r="CV76" t="str">
+      <c r="CW76" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW76">
+      <c r="CX76">
         <v>0</v>
       </c>
-      <c r="CX76">
+      <c r="CY76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY76">
+      <c r="CZ76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>374</v>
       </c>
@@ -24752,31 +24800,31 @@
       <c r="CB77" t="s">
         <v>26</v>
       </c>
-      <c r="CT77">
+      <c r="CU77">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU77" s="18">
+      <c r="CV77" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CV77" t="str">
+      <c r="CW77" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW77">
+      <c r="CX77">
         <v>0</v>
       </c>
-      <c r="CX77">
+      <c r="CY77">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY77">
+      <c r="CZ77">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>375</v>
       </c>
@@ -25017,31 +25065,31 @@
       <c r="CB78" t="s">
         <v>26</v>
       </c>
-      <c r="CT78">
+      <c r="CU78">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU78" s="18">
+      <c r="CV78" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CV78" t="str">
+      <c r="CW78" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW78">
+      <c r="CX78">
         <v>0</v>
       </c>
-      <c r="CX78">
+      <c r="CY78">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY78">
+      <c r="CZ78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>377</v>
       </c>
@@ -25282,31 +25330,31 @@
       <c r="CB79" t="s">
         <v>26</v>
       </c>
-      <c r="CT79">
+      <c r="CU79">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU79" s="18">
+      <c r="CV79" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="CV79" t="str">
+      <c r="CW79" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW79">
+      <c r="CX79">
         <v>0</v>
       </c>
-      <c r="CX79">
+      <c r="CY79">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY79">
+      <c r="CZ79">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>381</v>
       </c>
@@ -25547,31 +25595,31 @@
       <c r="CB80" t="s">
         <v>26</v>
       </c>
-      <c r="CT80">
+      <c r="CU80">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU80" s="18">
+      <c r="CV80" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CV80" t="str">
+      <c r="CW80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW80">
+      <c r="CX80">
         <v>0</v>
       </c>
-      <c r="CX80">
+      <c r="CY80">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY80">
+      <c r="CZ80">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>382</v>
       </c>
@@ -25812,31 +25860,31 @@
       <c r="CB81" t="s">
         <v>26</v>
       </c>
-      <c r="CT81">
+      <c r="CU81">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU81" s="18">
+      <c r="CV81" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="CV81" t="str">
+      <c r="CW81" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW81">
+      <c r="CX81">
         <v>0</v>
       </c>
-      <c r="CX81">
+      <c r="CY81">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY81">
+      <c r="CZ81">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>389</v>
       </c>
@@ -26080,31 +26128,31 @@
       <c r="CH82">
         <v>7.5</v>
       </c>
-      <c r="CT82">
+      <c r="CU82">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU82" s="18">
+      <c r="CV82" s="18">
         <f t="shared" si="11"/>
         <v>7.5</v>
       </c>
-      <c r="CV82" t="str">
+      <c r="CW82" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW82">
+      <c r="CX82">
         <v>0</v>
       </c>
-      <c r="CX82">
+      <c r="CY82">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY82">
+      <c r="CZ82">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>391</v>
       </c>
@@ -26348,31 +26396,31 @@
       <c r="CI83">
         <v>7</v>
       </c>
-      <c r="CT83">
+      <c r="CU83">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="CU83" s="18">
+      <c r="CV83" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="CV83" t="str">
+      <c r="CW83" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="CW83">
+      <c r="CX83">
         <v>0</v>
       </c>
-      <c r="CX83">
+      <c r="CY83">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="CY83">
+      <c r="CZ83">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>393</v>
       </c>
@@ -26388,31 +26436,34 @@
       <c r="CR84">
         <v>6.5</v>
       </c>
-      <c r="CT84">
-        <f t="shared" ref="CT84:CT88" si="15">COUNT(B84:CI84)</f>
+      <c r="CS84">
+        <v>5.5</v>
+      </c>
+      <c r="CU84">
+        <f t="shared" ref="CU84:CU88" si="15">COUNT(B84:CI84)</f>
         <v>0</v>
       </c>
-      <c r="CU84" s="18" t="e">
-        <f t="shared" ref="CU84:CU88" si="16">AVERAGE(B84:CI84)</f>
+      <c r="CV84" s="18" t="e">
+        <f t="shared" ref="CV84:CV88" si="16">AVERAGE(B84:CI84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="CV84" t="str">
-        <f t="shared" ref="CV84:CV88" si="17">IF(CT84&gt;1,_xlfn.STDEV.S(B84:CF84),"")</f>
+      <c r="CW84" t="str">
+        <f t="shared" ref="CW84:CW88" si="17">IF(CU84&gt;1,_xlfn.STDEV.S(B84:CF84),"")</f>
         <v/>
       </c>
-      <c r="CW84">
+      <c r="CX84">
         <v>0</v>
       </c>
-      <c r="CX84">
-        <f t="shared" ref="CX84:CX88" si="18">COUNT(CK84:CN84)</f>
+      <c r="CY84">
+        <f t="shared" ref="CY84:CY88" si="18">COUNT(CK84:CN84)</f>
         <v>0</v>
       </c>
-      <c r="CY84">
-        <f t="shared" ref="CY84:CY88" si="19">IF(CW84=0,CX84,0)</f>
+      <c r="CZ84">
+        <f t="shared" ref="CZ84:CZ88" si="19">IF(CX84=0,CY84,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>394</v>
       </c>
@@ -26422,31 +26473,34 @@
       <c r="CQ85">
         <v>6.5</v>
       </c>
-      <c r="CT85">
+      <c r="CS85">
+        <v>6.5</v>
+      </c>
+      <c r="CU85">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="CU85" s="18" t="e">
+      <c r="CV85" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CV85" t="str">
+      <c r="CW85" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="CW85">
+      <c r="CX85">
         <v>0</v>
       </c>
-      <c r="CX85">
+      <c r="CY85">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="CY85">
+      <c r="CZ85">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>395</v>
       </c>
@@ -26456,99 +26510,102 @@
       <c r="CQ86">
         <v>6</v>
       </c>
-      <c r="CT86">
+      <c r="CS86">
+        <v>6</v>
+      </c>
+      <c r="CU86">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="CU86" s="18" t="e">
+      <c r="CV86" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CV86" t="str">
+      <c r="CW86" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="CW86">
+      <c r="CX86">
         <v>0</v>
       </c>
-      <c r="CX86">
+      <c r="CY86">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="CY86">
+      <c r="CZ86">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>396</v>
       </c>
       <c r="CP87">
         <v>6.5</v>
       </c>
-      <c r="CT87">
+      <c r="CU87">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="CU87" s="18" t="e">
+      <c r="CV87" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CV87" t="str">
+      <c r="CW87" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="CW87">
+      <c r="CX87">
         <v>0</v>
       </c>
-      <c r="CX87">
+      <c r="CY87">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="CY87">
+      <c r="CZ87">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:103" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:104" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>397</v>
       </c>
       <c r="CQ88">
         <v>6.5</v>
       </c>
-      <c r="CT88">
+      <c r="CU88">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="CU88" s="18" t="e">
+      <c r="CV88" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CV88" t="str">
+      <c r="CW88" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="CW88">
+      <c r="CX88">
         <v>0</v>
       </c>
-      <c r="CX88">
+      <c r="CY88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="CY88">
+      <c r="CZ88">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CY83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
-    <sortState ref="A2:CY83">
-      <sortCondition descending="1" ref="CT1:CT83"/>
+  <autoFilter ref="A1:CZ83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
+    <sortState ref="A2:CZ83">
+      <sortCondition descending="1" ref="CU1:CU83"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="CT2:CT88">
+  <conditionalFormatting sqref="CU2:CU88">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -26560,7 +26617,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CV2:CV88">
+  <conditionalFormatting sqref="CW2:CW88">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -26572,7 +26629,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CT2:CT88">
+  <conditionalFormatting sqref="CU2:CU88">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -26584,7 +26641,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CU2:CU88">
+  <conditionalFormatting sqref="CV2:CV88">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
@@ -26596,7 +26653,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CU2:CU88">
+  <conditionalFormatting sqref="CV2:CV88">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
@@ -26608,7 +26665,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CT2:CT88">
+  <conditionalFormatting sqref="CU2:CU88">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -26620,7 +26677,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CU2:CU88">
+  <conditionalFormatting sqref="CV2:CV88">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -26632,7 +26689,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS79">
+  <conditionalFormatting sqref="CT2:CT79">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -26644,7 +26701,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS67">
+  <conditionalFormatting sqref="CT2:CT67">
     <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
@@ -26656,7 +26713,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS67">
+  <conditionalFormatting sqref="CT2:CT67">
     <cfRule type="colorScale" priority="127">
       <colorScale>
         <cfvo type="min"/>
@@ -26668,7 +26725,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS67">
+  <conditionalFormatting sqref="CT2:CT67">
     <cfRule type="colorScale" priority="129">
       <colorScale>
         <cfvo type="min"/>
@@ -26680,7 +26737,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:CR83">
+  <conditionalFormatting sqref="B2:CS83">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -31893,7 +31950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X279"/>
+  <dimension ref="A1:X282"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -43719,7 +43776,7 @@
         <v>81</v>
       </c>
       <c r="G238" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="H238" s="8"/>
       <c r="I238" s="9">
@@ -43833,7 +43890,7 @@
         <v>81</v>
       </c>
       <c r="O240" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="P240" s="8"/>
     </row>
@@ -44157,7 +44214,7 @@
         <v>388</v>
       </c>
       <c r="O247" s="10" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="P247" s="10" t="s">
         <v>389</v>
@@ -44183,7 +44240,7 @@
         <v>388</v>
       </c>
       <c r="G248" s="10" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="H248" s="10" t="s">
         <v>389</v>
@@ -45741,6 +45798,156 @@
       </c>
       <c r="P279" s="8" t="s">
         <v>343</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A280" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B280" s="62">
+        <v>5</v>
+      </c>
+      <c r="C280" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D280" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E280" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F280" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H280" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="I280" s="9">
+        <v>4</v>
+      </c>
+      <c r="J280" s="10">
+        <v>6</v>
+      </c>
+      <c r="K280" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="L280" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="M280" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N280" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="O280" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="P280" s="10" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A281" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B281" s="62">
+        <v>3</v>
+      </c>
+      <c r="C281" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D281" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="E281" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F281" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G281" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H281" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="I281" s="11">
+        <v>3</v>
+      </c>
+      <c r="J281" s="2">
+        <v>2</v>
+      </c>
+      <c r="K281" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L281" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M281" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N281" s="61" t="s">
+        <v>376</v>
+      </c>
+      <c r="O281" s="61" t="s">
+        <v>390</v>
+      </c>
+      <c r="P281" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A282" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B282" s="62">
+        <v>4</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F282" s="61" t="s">
+        <v>376</v>
+      </c>
+      <c r="G282" s="61" t="s">
+        <v>390</v>
+      </c>
+      <c r="H282" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="I282" s="5">
+        <v>6</v>
+      </c>
+      <c r="J282" s="8">
+        <v>6</v>
+      </c>
+      <c r="K282" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L282" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M282" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N282" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="O282" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="P282" s="8" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -45750,7 +45957,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:BY88"/>
+  <dimension ref="A1:BZ88"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
@@ -45760,10 +45967,10 @@
     <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="77" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="78" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -45995,8 +46202,11 @@
       <c r="BY1" s="1">
         <v>46134</v>
       </c>
-    </row>
-    <row r="2" spans="1:77" x14ac:dyDescent="0.35">
+      <c r="BZ1" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -46061,7 +46271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -46069,7 +46279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -46107,12 +46317,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:78" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -46120,7 +46330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>393</v>
       </c>
@@ -46133,8 +46343,11 @@
       <c r="BY7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:77" x14ac:dyDescent="0.35">
+      <c r="BZ7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>364</v>
       </c>
@@ -46151,7 +46364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -46159,7 +46372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>353</v>
       </c>
@@ -46167,17 +46380,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:78" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="12" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>397</v>
       </c>
@@ -46185,12 +46398,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="15" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>395</v>
       </c>
@@ -46198,7 +46411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>362</v>
       </c>
@@ -46856,7 +47069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>361</v>
       </c>
@@ -46873,7 +47086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>389</v>
       </c>
@@ -46881,7 +47094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>1</v>
       </c>
@@ -47021,7 +47234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:78" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>351</v>
       </c>
@@ -47029,7 +47242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -47177,16 +47390,22 @@
       <c r="BY37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:77" x14ac:dyDescent="0.35">
+      <c r="BZ37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>394</v>
       </c>
       <c r="BW38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:77" x14ac:dyDescent="0.35">
+      <c r="BZ38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>381</v>
       </c>
@@ -47194,7 +47413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -47313,12 +47532,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="42" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -47326,7 +47545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:78" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -47334,7 +47553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>374</v>
       </c>
@@ -47342,7 +47561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -47469,8 +47688,11 @@
       <c r="BY45">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:77" x14ac:dyDescent="0.35">
+      <c r="BZ45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>43</v>
       </c>
@@ -47478,7 +47700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>68</v>
       </c>
@@ -47498,15 +47720,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>53</v>
       </c>
       <c r="N48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:77" x14ac:dyDescent="0.35">
+      <c r="BZ48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>368</v>
       </c>
@@ -47520,7 +47745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>345</v>
       </c>
@@ -47537,7 +47762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>343</v>
       </c>
@@ -47554,7 +47779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>344</v>
       </c>
@@ -47568,7 +47793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>10</v>
       </c>
@@ -47710,8 +47935,11 @@
       <c r="BX53">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:77" x14ac:dyDescent="0.35">
+      <c r="BZ53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>46</v>
       </c>
@@ -47769,13 +47997,16 @@
       <c r="BT54">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="1:77" x14ac:dyDescent="0.35">
+      <c r="BZ54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="56" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -47792,12 +48023,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:78" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="58" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -47921,8 +48152,11 @@
       <c r="BY58">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" spans="1:77" x14ac:dyDescent="0.35">
+      <c r="BZ58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>369</v>
       </c>
@@ -47930,7 +48164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>387</v>
       </c>
@@ -47944,7 +48178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -47958,7 +48192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>340</v>
       </c>
@@ -47981,17 +48215,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="64" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>55</v>
       </c>
@@ -48086,12 +48320,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>81</v>
       </c>
@@ -48132,7 +48366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>63</v>
       </c>
@@ -48158,12 +48392,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:78" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>22</v>
       </c>
@@ -48210,7 +48444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>376</v>
       </c>
@@ -48236,7 +48470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>44</v>
       </c>
@@ -48289,7 +48523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>379</v>
       </c>
@@ -48300,7 +48534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -48317,12 +48551,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:78" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="76" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>82</v>
       </c>
@@ -48473,8 +48707,11 @@
       <c r="BY76">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:77" x14ac:dyDescent="0.35">
+      <c r="BZ76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>49</v>
       </c>
@@ -48482,12 +48719,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="79" spans="1:77" x14ac:dyDescent="0.35">
+        <v>390</v>
+      </c>
+      <c r="BZ78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>85</v>
       </c>
@@ -48501,7 +48741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -48668,7 +48908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>45</v>
       </c>
@@ -48679,7 +48919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>367</v>
       </c>
@@ -48759,7 +48999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:78" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>352</v>
       </c>
@@ -48767,12 +49007,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:78" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="85" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -48786,7 +49026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:78" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>86</v>
       </c>
@@ -48794,7 +49034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:77" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:78" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -48984,8 +49224,11 @@
       <c r="BY87">
         <v>2</v>
       </c>
-    </row>
-    <row r="88" spans="1:77" hidden="1" x14ac:dyDescent="0.35">
+      <c r="BZ87">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:78" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>47</v>
       </c>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{397AD17F-F7C1-49A1-BA33-AADCB3C4FEDE}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="14_{0C1905BB-B4B8-4F5B-9F29-FEFBC7ECF02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{5A659540-24C7-49CF-A019-BD8AFA929904}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="3780" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,17 +23,17 @@
     <sheet name="artilharia total" sheetId="3" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'extrato 2024'!$A$1:$C$187</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$DA$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$DB$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9436" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9474" uniqueCount="400">
   <si>
     <t>Jogador</t>
   </si>
@@ -1230,6 +1230,9 @@
   </si>
   <si>
     <t>Bernardo (Impactus)</t>
+  </si>
+  <si>
+    <t>Max</t>
   </si>
 </sst>
 </file>
@@ -3498,7 +3501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DA88"/>
+  <dimension ref="A1:DB89"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
@@ -3523,10 +3526,10 @@
     <col min="50" max="58" width="9.54296875" customWidth="1"/>
     <col min="59" max="65" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
-    <col min="67" max="99" width="11" customWidth="1"/>
+    <col min="67" max="100" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3821,27 +3824,30 @@
       <c r="CT1" s="1">
         <v>46148</v>
       </c>
-      <c r="CU1" s="1"/>
-      <c r="CV1" t="s">
+      <c r="CU1" s="1">
+        <v>46155</v>
+      </c>
+      <c r="CV1" s="1"/>
+      <c r="CW1" t="s">
         <v>57</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>58</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>59</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>62</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>397</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4133,31 +4139,34 @@
       <c r="CT2">
         <v>5.5</v>
       </c>
-      <c r="CV2">
-        <f>COUNT(B2:CT2)</f>
-        <v>91</v>
-      </c>
-      <c r="CW2" s="18">
-        <f>AVERAGE(B2:CT2)</f>
-        <v>6.0219780219780219</v>
-      </c>
-      <c r="CX2">
-        <f>IF(CV2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
+      <c r="CU2">
+        <v>5.5</v>
+      </c>
+      <c r="CW2">
+        <f>COUNT(B2:CU2)</f>
+        <v>92</v>
+      </c>
+      <c r="CX2" s="18">
+        <f>AVERAGE(B2:CU2)</f>
+        <v>6.0163043478260869</v>
+      </c>
+      <c r="CY2">
+        <f t="shared" ref="CY2:CY33" si="0">IF(CW2&gt;1,_xlfn.STDEV.S(B2:CF2),"")</f>
         <v>1.2512468149547391</v>
       </c>
-      <c r="CY2">
-        <v>1</v>
-      </c>
       <c r="CZ2">
-        <f>COUNT(CO2:CS2)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="DA2">
-        <f>IF(CY2=0,CZ2,0)</f>
+        <f t="shared" ref="DA2:DA33" si="1">COUNT(CO2:CS2)</f>
+        <v>5</v>
+      </c>
+      <c r="DB2">
+        <f t="shared" ref="DB2:DB33" si="2">IF(CZ2=0,DA2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4446,31 +4455,31 @@
       <c r="CS3">
         <v>5.5</v>
       </c>
-      <c r="CV3">
+      <c r="CW3">
         <f>COUNT(B3:CK3)</f>
         <v>79</v>
       </c>
-      <c r="CW3" s="18">
+      <c r="CX3" s="18">
         <f>AVERAGE(B3:CK3)</f>
         <v>5.6518987341772151</v>
       </c>
-      <c r="CX3">
-        <f>IF(CV3&gt;1,_xlfn.STDEV.S(B3:CF3),"")</f>
+      <c r="CY3">
+        <f t="shared" si="0"/>
         <v>1.0518094984498128</v>
       </c>
-      <c r="CY3">
-        <v>1</v>
-      </c>
       <c r="CZ3">
-        <f>COUNT(CO3:CS3)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="DA3">
-        <f>IF(CY3=0,CZ3,0)</f>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="DB3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4732,31 +4741,31 @@
       <c r="CI4">
         <v>5.5</v>
       </c>
-      <c r="CV4">
+      <c r="CW4">
         <f>COUNT(B4:CI4)</f>
         <v>72</v>
       </c>
-      <c r="CW4" s="18">
+      <c r="CX4" s="18">
         <f>AVERAGE(B4:CI4)</f>
         <v>5.708333333333333</v>
       </c>
-      <c r="CX4">
-        <f>IF(CV4&gt;1,_xlfn.STDEV.S(B4:CF4),"")</f>
+      <c r="CY4">
+        <f t="shared" si="0"/>
         <v>0.96435844595057774</v>
       </c>
-      <c r="CY4">
+      <c r="CZ4">
         <v>0</v>
       </c>
-      <c r="CZ4">
-        <f>COUNT(CO4:CS4)</f>
+      <c r="DA4">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA4">
-        <f>IF(CY4=0,CZ4,0)</f>
+      <c r="DB4">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -5027,31 +5036,31 @@
       <c r="CR5">
         <v>5.5</v>
       </c>
-      <c r="CV5">
+      <c r="CW5">
         <f>COUNT(B5:CL5)</f>
         <v>71</v>
       </c>
-      <c r="CW5" s="18">
+      <c r="CX5" s="18">
         <f>AVERAGE(B5:CL5)</f>
         <v>7.267605633802817</v>
       </c>
-      <c r="CX5">
-        <f>IF(CV5&gt;1,_xlfn.STDEV.S(B5:CF5),"")</f>
+      <c r="CY5">
+        <f t="shared" si="0"/>
         <v>1.1294250579557983</v>
       </c>
-      <c r="CY5">
+      <c r="CZ5">
         <v>0</v>
       </c>
-      <c r="CZ5">
-        <f>COUNT(CO5:CS5)</f>
-        <v>1</v>
-      </c>
       <c r="DA5">
-        <f>IF(CY5=0,CZ5,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:105" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="DB5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -5334,31 +5343,34 @@
       <c r="CT6">
         <v>6.5</v>
       </c>
-      <c r="CV6">
+      <c r="CU6">
+        <v>6.5</v>
+      </c>
+      <c r="CW6">
         <f>COUNT(B6:CL6)</f>
         <v>70</v>
       </c>
-      <c r="CW6" s="18">
+      <c r="CX6" s="18">
         <f>AVERAGE(B6:CL6)</f>
         <v>6.6142857142857139</v>
       </c>
-      <c r="CX6">
-        <f>IF(CV6&gt;1,_xlfn.STDEV.S(B6:CF6),"")</f>
+      <c r="CY6">
+        <f t="shared" si="0"/>
         <v>0.9419445925236869</v>
       </c>
-      <c r="CY6">
-        <v>1</v>
-      </c>
       <c r="CZ6">
-        <f>COUNT(CO6:CS6)</f>
+        <v>1</v>
+      </c>
+      <c r="DA6">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="DA6">
-        <f>IF(CY6=0,CZ6,0)</f>
+      <c r="DB6">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5638,31 +5650,34 @@
       <c r="CS7">
         <v>6.5</v>
       </c>
-      <c r="CV7">
+      <c r="CU7">
+        <v>7.5</v>
+      </c>
+      <c r="CW7">
         <f>COUNT(B7:CL7)</f>
         <v>70</v>
       </c>
-      <c r="CW7" s="18">
+      <c r="CX7" s="18">
         <f>AVERAGE(B7:CL7)</f>
         <v>6.6071428571428568</v>
       </c>
-      <c r="CX7">
-        <f>IF(CV7&gt;1,_xlfn.STDEV.S(B7:CF7),"")</f>
+      <c r="CY7">
+        <f t="shared" si="0"/>
         <v>1.0570846156365068</v>
       </c>
-      <c r="CY7">
-        <v>1</v>
-      </c>
       <c r="CZ7">
-        <f>COUNT(CO7:CS7)</f>
+        <v>1</v>
+      </c>
+      <c r="DA7">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="DA7">
-        <f>IF(CY7=0,CZ7,0)</f>
+      <c r="DB7">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5912,31 +5927,31 @@
       <c r="CE8">
         <v>5</v>
       </c>
-      <c r="CV8">
+      <c r="CW8">
         <f>COUNT(B8:CI8)</f>
         <v>68</v>
       </c>
-      <c r="CW8" s="18">
+      <c r="CX8" s="18">
         <f>AVERAGE(B8:CI8)</f>
         <v>6.4191176470588234</v>
       </c>
-      <c r="CX8">
-        <f>IF(CV8&gt;1,_xlfn.STDEV.S(B8:CF8),"")</f>
+      <c r="CY8">
+        <f t="shared" si="0"/>
         <v>1.1769245721961776</v>
       </c>
-      <c r="CY8">
+      <c r="CZ8">
         <v>0</v>
       </c>
-      <c r="CZ8">
-        <f>COUNT(CO8:CS8)</f>
+      <c r="DA8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA8">
-        <f>IF(CY8=0,CZ8,0)</f>
+      <c r="DB8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -6195,31 +6210,31 @@
       <c r="CS9">
         <v>5.5</v>
       </c>
-      <c r="CV9">
+      <c r="CW9">
         <f>COUNT(B9:CI9)</f>
         <v>67</v>
       </c>
-      <c r="CW9" s="18">
+      <c r="CX9" s="18">
         <f>AVERAGE(B9:CI9)</f>
         <v>5.9701492537313436</v>
       </c>
-      <c r="CX9">
-        <f>IF(CV9&gt;1,_xlfn.STDEV.S(B9:CF9),"")</f>
+      <c r="CY9">
+        <f t="shared" si="0"/>
         <v>0.96648378625350351</v>
       </c>
-      <c r="CY9">
+      <c r="CZ9">
         <v>0</v>
       </c>
-      <c r="CZ9">
-        <f>COUNT(CO9:CS9)</f>
-        <v>2</v>
-      </c>
       <c r="DA9">
-        <f>IF(CY9=0,CZ9,0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:105" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="DB9">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -6496,31 +6511,31 @@
       <c r="CR10">
         <v>6</v>
       </c>
-      <c r="CV10">
+      <c r="CW10">
         <f>COUNT(B10:CI10)</f>
         <v>62</v>
       </c>
-      <c r="CW10" s="18">
+      <c r="CX10" s="18">
         <f>AVERAGE(B10:CI10)</f>
         <v>5.717741935483871</v>
       </c>
-      <c r="CX10">
-        <f>IF(CV10&gt;1,_xlfn.STDEV.S(B10:CF10),"")</f>
+      <c r="CY10">
+        <f t="shared" si="0"/>
         <v>1.3617531291315086</v>
       </c>
-      <c r="CY10">
-        <v>1</v>
-      </c>
       <c r="CZ10">
-        <f>COUNT(CO10:CS10)</f>
+        <v>1</v>
+      </c>
+      <c r="DA10">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="DA10">
-        <f>IF(CY10=0,CZ10,0)</f>
+      <c r="DB10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -6803,31 +6818,31 @@
       <c r="CR11">
         <v>6</v>
       </c>
-      <c r="CV11">
+      <c r="CW11">
         <f>COUNT(B11:CR11)</f>
         <v>62</v>
       </c>
-      <c r="CW11" s="18">
+      <c r="CX11" s="18">
         <f>AVERAGE(B11:CR11)</f>
         <v>5.540322580645161</v>
       </c>
-      <c r="CX11">
-        <f>IF(CV11&gt;1,_xlfn.STDEV.S(B11:CF11),"")</f>
+      <c r="CY11">
+        <f t="shared" si="0"/>
         <v>1.0254583642020354</v>
       </c>
-      <c r="CY11">
-        <v>1</v>
-      </c>
       <c r="CZ11">
-        <f>COUNT(CO11:CS11)</f>
+        <v>1</v>
+      </c>
+      <c r="DA11">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="DA11">
-        <f>IF(CY11=0,CZ11,0)</f>
+      <c r="DB11">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -7110,31 +7125,31 @@
       <c r="CT12">
         <v>6</v>
       </c>
-      <c r="CV12">
+      <c r="CW12">
         <f>COUNT(B12:CI12)</f>
         <v>59</v>
       </c>
-      <c r="CW12" s="18">
+      <c r="CX12" s="18">
         <f>AVERAGE(B12:CI12)</f>
         <v>6.6779661016949152</v>
       </c>
-      <c r="CX12">
-        <f>IF(CV12&gt;1,_xlfn.STDEV.S(B12:CF12),"")</f>
+      <c r="CY12">
+        <f t="shared" si="0"/>
         <v>1.0072574989410263</v>
       </c>
-      <c r="CY12">
-        <v>1</v>
-      </c>
       <c r="CZ12">
-        <f>COUNT(CO12:CS12)</f>
+        <v>1</v>
+      </c>
+      <c r="DA12">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="DA12">
-        <f>IF(CY12=0,CZ12,0)</f>
+      <c r="DB12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -7420,31 +7435,34 @@
       <c r="CT13">
         <v>5</v>
       </c>
-      <c r="CV13">
+      <c r="CU13">
+        <v>5.5</v>
+      </c>
+      <c r="CW13">
         <f>COUNT(B13:CN13)</f>
         <v>56</v>
       </c>
-      <c r="CW13" s="18">
+      <c r="CX13" s="18">
         <f>AVERAGE(B13:CN13)</f>
         <v>6.3571428571428568</v>
       </c>
-      <c r="CX13">
-        <f>IF(CV13&gt;1,_xlfn.STDEV.S(B13:CF13),"")</f>
+      <c r="CY13">
+        <f t="shared" si="0"/>
         <v>1.1769469323774333</v>
       </c>
-      <c r="CY13">
-        <v>1</v>
-      </c>
       <c r="CZ13">
-        <f>COUNT(CO13:CS13)</f>
+        <v>1</v>
+      </c>
+      <c r="DA13">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="DA13">
-        <f>IF(CY13=0,CZ13,0)</f>
+      <c r="DB13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>367</v>
       </c>
@@ -7706,31 +7724,34 @@
       <c r="CT14">
         <v>6</v>
       </c>
-      <c r="CV14">
+      <c r="CU14">
+        <v>6</v>
+      </c>
+      <c r="CW14">
         <f>COUNT(B14:CI14)</f>
         <v>55</v>
       </c>
-      <c r="CW14" s="18">
+      <c r="CX14" s="18">
         <f>AVERAGE(B14:CI14)</f>
         <v>6.3181818181818183</v>
       </c>
-      <c r="CX14">
-        <f>IF(CV14&gt;1,_xlfn.STDEV.S(B14:CF14),"")</f>
+      <c r="CY14">
+        <f t="shared" si="0"/>
         <v>1.1213885273224193</v>
       </c>
-      <c r="CY14">
-        <v>1</v>
-      </c>
       <c r="CZ14">
-        <f>COUNT(CO14:CS14)</f>
+        <v>1</v>
+      </c>
+      <c r="DA14">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="DA14">
-        <f>IF(CY14=0,CZ14,0)</f>
+      <c r="DB14">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -7974,31 +7995,31 @@
       <c r="CF15">
         <v>5.5</v>
       </c>
-      <c r="CV15">
+      <c r="CW15">
         <f>COUNT(B15:CI15)</f>
         <v>52</v>
       </c>
-      <c r="CW15" s="18">
+      <c r="CX15" s="18">
         <f>AVERAGE(B15:CI15)</f>
         <v>5.6923076923076925</v>
       </c>
-      <c r="CX15">
-        <f>IF(CV15&gt;1,_xlfn.STDEV.S(B15:CF15),"")</f>
+      <c r="CY15">
+        <f t="shared" si="0"/>
         <v>0.84687340856573534</v>
       </c>
-      <c r="CY15">
+      <c r="CZ15">
         <v>0</v>
       </c>
-      <c r="CZ15">
-        <f>COUNT(CO15:CS15)</f>
+      <c r="DA15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA15">
-        <f>IF(CY15=0,CZ15,0)</f>
+      <c r="DB15">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -8248,31 +8269,31 @@
       <c r="CF16">
         <v>5.5</v>
       </c>
-      <c r="CV16">
+      <c r="CW16">
         <f>COUNT(B16:CI16)</f>
         <v>47</v>
       </c>
-      <c r="CW16" s="18">
+      <c r="CX16" s="18">
         <f>AVERAGE(B16:CI16)</f>
         <v>4.4255319148936172</v>
       </c>
-      <c r="CX16">
-        <f>IF(CV16&gt;1,_xlfn.STDEV.S(B16:CF16),"")</f>
+      <c r="CY16">
+        <f t="shared" si="0"/>
         <v>1.3391217246854428</v>
       </c>
-      <c r="CY16">
+      <c r="CZ16">
         <v>0</v>
       </c>
-      <c r="CZ16">
-        <f>COUNT(CO16:CS16)</f>
+      <c r="DA16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA16">
-        <f>IF(CY16=0,CZ16,0)</f>
+      <c r="DB16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>56</v>
       </c>
@@ -8564,31 +8585,34 @@
       <c r="CT17">
         <v>6</v>
       </c>
-      <c r="CV17">
+      <c r="CU17">
+        <v>6</v>
+      </c>
+      <c r="CW17">
         <f>COUNT(B17:CL17)</f>
         <v>46</v>
       </c>
-      <c r="CW17" s="18">
+      <c r="CX17" s="18">
         <f>AVERAGE(B17:CL17)</f>
         <v>6.0652173913043477</v>
       </c>
-      <c r="CX17">
-        <f>IF(CV17&gt;1,_xlfn.STDEV.S(B17:CF17),"")</f>
+      <c r="CY17">
+        <f t="shared" si="0"/>
         <v>0.9573434129174403</v>
       </c>
-      <c r="CY17">
-        <v>1</v>
-      </c>
       <c r="CZ17">
-        <f>COUNT(CO17:CS17)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="DA17">
-        <f>IF(CY17=0,CZ17,0)</f>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="DB17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -8856,31 +8880,31 @@
       <c r="CL18">
         <v>6</v>
       </c>
-      <c r="CV18">
+      <c r="CW18">
         <f>COUNT(B18:CL18)</f>
         <v>44</v>
       </c>
-      <c r="CW18" s="18">
+      <c r="CX18" s="18">
         <f>AVERAGE(B18:CL18)</f>
         <v>5.0113636363636367</v>
       </c>
-      <c r="CX18">
-        <f>IF(CV18&gt;1,_xlfn.STDEV.S(B18:CF18),"")</f>
+      <c r="CY18">
+        <f t="shared" si="0"/>
         <v>1.0645089158214895</v>
       </c>
-      <c r="CY18">
+      <c r="CZ18">
         <v>0</v>
       </c>
-      <c r="CZ18">
-        <f>COUNT(CO18:CS18)</f>
+      <c r="DA18">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA18">
-        <f>IF(CY18=0,CZ18,0)</f>
+      <c r="DB18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -9124,31 +9148,31 @@
       <c r="CK19">
         <v>5.5</v>
       </c>
-      <c r="CV19">
+      <c r="CW19">
         <f>COUNT(B19:CI19)</f>
         <v>38</v>
       </c>
-      <c r="CW19" s="18">
+      <c r="CX19" s="18">
         <f>AVERAGE(B19:CI19)</f>
         <v>6.1578947368421053</v>
       </c>
-      <c r="CX19">
-        <f>IF(CV19&gt;1,_xlfn.STDEV.S(B19:CF19),"")</f>
+      <c r="CY19">
+        <f t="shared" si="0"/>
         <v>1.0973263770680928</v>
       </c>
-      <c r="CY19">
+      <c r="CZ19">
         <v>0</v>
       </c>
-      <c r="CZ19">
-        <f>COUNT(CO19:CS19)</f>
+      <c r="DA19">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA19">
-        <f>IF(CY19=0,CZ19,0)</f>
+      <c r="DB19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -9419,31 +9443,34 @@
       <c r="CT20">
         <v>5.5</v>
       </c>
-      <c r="CV20">
+      <c r="CU20">
+        <v>5.5</v>
+      </c>
+      <c r="CW20">
         <f>COUNT(B20:CJ20)</f>
         <v>37</v>
       </c>
-      <c r="CW20" s="18">
+      <c r="CX20" s="18">
         <f>AVERAGE(B20:CJ20)</f>
         <v>5.2027027027027026</v>
       </c>
-      <c r="CX20">
-        <f>IF(CV20&gt;1,_xlfn.STDEV.S(B20:CF20),"")</f>
+      <c r="CY20">
+        <f t="shared" si="0"/>
         <v>1.3241383031954423</v>
       </c>
-      <c r="CY20">
+      <c r="CZ20">
         <v>0</v>
       </c>
-      <c r="CZ20">
-        <f>COUNT(CO20:CS20)</f>
-        <v>1</v>
-      </c>
       <c r="DA20">
-        <f>IF(CY20=0,CZ20,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:105" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="DB20">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -9708,31 +9735,34 @@
       <c r="CT21">
         <v>6</v>
       </c>
-      <c r="CV21">
+      <c r="CU21">
+        <v>5.5</v>
+      </c>
+      <c r="CW21">
         <f>COUNT(B21:CI21)</f>
         <v>36</v>
       </c>
-      <c r="CW21" s="18">
+      <c r="CX21" s="18">
         <f>AVERAGE(B21:CI21)</f>
         <v>5.7361111111111107</v>
       </c>
-      <c r="CX21">
-        <f>IF(CV21&gt;1,_xlfn.STDEV.S(B21:CF21),"")</f>
+      <c r="CY21">
+        <f t="shared" si="0"/>
         <v>0.92956296268047622</v>
       </c>
-      <c r="CY21">
-        <v>1</v>
-      </c>
       <c r="CZ21">
-        <f>COUNT(CO21:CS21)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DA21">
-        <f>IF(CY21=0,CZ21,0)</f>
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="DB21">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -10012,31 +10042,34 @@
       <c r="CT22">
         <v>6</v>
       </c>
-      <c r="CV22">
+      <c r="CU22">
+        <v>6.5</v>
+      </c>
+      <c r="CW22">
         <f>COUNT(B22:CI22)</f>
         <v>36</v>
       </c>
-      <c r="CW22" s="18">
+      <c r="CX22" s="18">
         <f>AVERAGE(B22:CI22)</f>
         <v>5.6111111111111107</v>
       </c>
-      <c r="CX22">
-        <f>IF(CV22&gt;1,_xlfn.STDEV.S(B22:CF22),"")</f>
+      <c r="CY22">
+        <f t="shared" si="0"/>
         <v>1.0098256776095882</v>
       </c>
-      <c r="CY22">
-        <v>1</v>
-      </c>
       <c r="CZ22">
-        <f>COUNT(CO22:CS22)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="DA22">
-        <f>IF(CY22=0,CZ22,0)</f>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="DB22">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -10310,31 +10343,31 @@
       <c r="CT23">
         <v>6.5</v>
       </c>
-      <c r="CV23">
+      <c r="CW23">
         <f>COUNT(B23:CN23)</f>
         <v>30</v>
       </c>
-      <c r="CW23" s="18">
+      <c r="CX23" s="18">
         <f>AVERAGE(B23:CN23)</f>
         <v>6.4</v>
       </c>
-      <c r="CX23">
-        <f>IF(CV23&gt;1,_xlfn.STDEV.S(B23:CF23),"")</f>
+      <c r="CY23">
+        <f t="shared" si="0"/>
         <v>0.90960483309014595</v>
       </c>
-      <c r="CY23">
+      <c r="CZ23">
         <v>0</v>
       </c>
-      <c r="CZ23">
-        <f>COUNT(CO23:CS23)</f>
+      <c r="DA23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA23">
-        <f>IF(CY23=0,CZ23,0)</f>
+      <c r="DB23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -10587,31 +10620,34 @@
       <c r="CR24">
         <v>6</v>
       </c>
-      <c r="CV24">
+      <c r="CU24">
+        <v>6</v>
+      </c>
+      <c r="CW24">
         <f>COUNT(B24:CI24)</f>
         <v>25</v>
       </c>
-      <c r="CW24" s="18">
+      <c r="CX24" s="18">
         <f>AVERAGE(B24:CI24)</f>
         <v>5.4</v>
       </c>
-      <c r="CX24">
-        <f>IF(CV24&gt;1,_xlfn.STDEV.S(B24:CF24),"")</f>
+      <c r="CY24">
+        <f t="shared" si="0"/>
         <v>0.71728150235677346</v>
       </c>
-      <c r="CY24">
+      <c r="CZ24">
         <v>0</v>
       </c>
-      <c r="CZ24">
-        <f>COUNT(CO24:CS24)</f>
-        <v>1</v>
-      </c>
       <c r="DA24">
-        <f>IF(CY24=0,CZ24,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:105" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="DB24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -10852,31 +10888,31 @@
       <c r="CB25" t="s">
         <v>26</v>
       </c>
-      <c r="CV25">
+      <c r="CW25">
         <f>COUNT(B25:CI25)</f>
         <v>19</v>
       </c>
-      <c r="CW25" s="18">
+      <c r="CX25" s="18">
         <f>AVERAGE(B25:CI25)</f>
         <v>5.7894736842105265</v>
       </c>
-      <c r="CX25">
-        <f>IF(CV25&gt;1,_xlfn.STDEV.S(B25:CF25),"")</f>
+      <c r="CY25">
+        <f t="shared" si="0"/>
         <v>1.3674366679797902</v>
       </c>
-      <c r="CY25">
+      <c r="CZ25">
         <v>0</v>
       </c>
-      <c r="CZ25">
-        <f>COUNT(CO25:CS25)</f>
+      <c r="DA25">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA25">
-        <f>IF(CY25=0,CZ25,0)</f>
+      <c r="DB25">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>81</v>
       </c>
@@ -11162,31 +11198,31 @@
       <c r="CT26">
         <v>5</v>
       </c>
-      <c r="CV26">
+      <c r="CW26">
         <f>COUNT(B26:CT26)</f>
         <v>19</v>
       </c>
-      <c r="CW26" s="18">
+      <c r="CX26" s="18">
         <f>AVERAGE(B26:CT26)</f>
         <v>6.2368421052631575</v>
       </c>
-      <c r="CX26">
-        <f>IF(CV26&gt;1,_xlfn.STDEV.S(B26:CF26),"")</f>
+      <c r="CY26">
+        <f t="shared" si="0"/>
         <v>0.90829510622924903</v>
       </c>
-      <c r="CY26">
-        <v>1</v>
-      </c>
       <c r="CZ26">
-        <f>COUNT(CO26:CS26)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="DA26">
-        <f>IF(CY26=0,CZ26,0)</f>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="DB26">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>346</v>
       </c>
@@ -11427,31 +11463,31 @@
       <c r="CB27" t="s">
         <v>26</v>
       </c>
-      <c r="CV27">
-        <f>COUNT(B27:CI27)</f>
+      <c r="CW27">
+        <f t="shared" ref="CW27:CW58" si="3">COUNT(B27:CI27)</f>
         <v>18</v>
       </c>
-      <c r="CW27" s="18">
-        <f>AVERAGE(B27:CI27)</f>
+      <c r="CX27" s="18">
+        <f t="shared" ref="CX27:CX58" si="4">AVERAGE(B27:CI27)</f>
         <v>5.9444444444444446</v>
       </c>
-      <c r="CX27">
-        <f>IF(CV27&gt;1,_xlfn.STDEV.S(B27:CF27),"")</f>
+      <c r="CY27">
+        <f t="shared" si="0"/>
         <v>0.72535769855270305</v>
       </c>
-      <c r="CY27">
+      <c r="CZ27">
         <v>0</v>
       </c>
-      <c r="CZ27">
-        <f>COUNT(CO27:CS27)</f>
+      <c r="DA27">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA27">
-        <f>IF(CY27=0,CZ27,0)</f>
+      <c r="DB27">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -11692,31 +11728,31 @@
       <c r="CB28" t="s">
         <v>26</v>
       </c>
-      <c r="CV28">
-        <f>COUNT(B28:CI28)</f>
+      <c r="CW28">
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="CW28" s="18">
-        <f>AVERAGE(B28:CI28)</f>
+      <c r="CX28" s="18">
+        <f t="shared" si="4"/>
         <v>5.3235294117647056</v>
       </c>
-      <c r="CX28">
-        <f>IF(CV28&gt;1,_xlfn.STDEV.S(B28:CF28),"")</f>
+      <c r="CY28">
+        <f t="shared" si="0"/>
         <v>1.3456083251473603</v>
       </c>
-      <c r="CY28">
+      <c r="CZ28">
         <v>0</v>
       </c>
-      <c r="CZ28">
-        <f>COUNT(CO28:CS28)</f>
+      <c r="DA28">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA28">
-        <f>IF(CY28=0,CZ28,0)</f>
+      <c r="DB28">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -11972,31 +12008,31 @@
       <c r="CQ29">
         <v>6.5</v>
       </c>
-      <c r="CV29">
-        <f>COUNT(B29:CI29)</f>
+      <c r="CW29">
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="CW29" s="18">
-        <f>AVERAGE(B29:CI29)</f>
+      <c r="CX29" s="18">
+        <f t="shared" si="4"/>
         <v>6.65625</v>
       </c>
-      <c r="CX29">
-        <f>IF(CV29&gt;1,_xlfn.STDEV.S(B29:CF29),"")</f>
+      <c r="CY29">
+        <f t="shared" si="0"/>
         <v>0.74651970279870483</v>
       </c>
-      <c r="CY29">
-        <v>1</v>
-      </c>
       <c r="CZ29">
-        <f>COUNT(CO29:CS29)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DA29">
-        <f>IF(CY29=0,CZ29,0)</f>
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="DB29">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -12237,31 +12273,31 @@
       <c r="CB30" t="s">
         <v>26</v>
       </c>
-      <c r="CV30">
-        <f>COUNT(B30:CI30)</f>
+      <c r="CW30">
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="CW30" s="18">
-        <f>AVERAGE(B30:CI30)</f>
+      <c r="CX30" s="18">
+        <f t="shared" si="4"/>
         <v>4.53125</v>
       </c>
-      <c r="CX30">
-        <f>IF(CV30&gt;1,_xlfn.STDEV.S(B30:CF30),"")</f>
+      <c r="CY30">
+        <f t="shared" si="0"/>
         <v>1.5434674167816653</v>
       </c>
-      <c r="CY30">
+      <c r="CZ30">
         <v>0</v>
       </c>
-      <c r="CZ30">
-        <f>COUNT(CO30:CS30)</f>
+      <c r="DA30">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA30">
-        <f>IF(CY30=0,CZ30,0)</f>
+      <c r="DB30">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -12502,31 +12538,31 @@
       <c r="CB31">
         <v>5.5</v>
       </c>
-      <c r="CV31">
-        <f>COUNT(B31:CI31)</f>
+      <c r="CW31">
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="CW31" s="18">
-        <f>AVERAGE(B31:CI31)</f>
+      <c r="CX31" s="18">
+        <f t="shared" si="4"/>
         <v>3.8666666666666667</v>
       </c>
-      <c r="CX31">
-        <f>IF(CV31&gt;1,_xlfn.STDEV.S(B31:CF31),"")</f>
+      <c r="CY31">
+        <f t="shared" si="0"/>
         <v>2.3563490726929555</v>
       </c>
-      <c r="CY31">
+      <c r="CZ31">
         <v>0</v>
       </c>
-      <c r="CZ31">
-        <f>COUNT(CO31:CS31)</f>
+      <c r="DA31">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA31">
-        <f>IF(CY31=0,CZ31,0)</f>
+      <c r="DB31">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -12779,31 +12815,34 @@
       <c r="CP32">
         <v>6</v>
       </c>
-      <c r="CV32">
-        <f>COUNT(B32:CI32)</f>
+      <c r="CU32">
+        <v>5.5</v>
+      </c>
+      <c r="CW32">
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="CW32" s="18">
-        <f>AVERAGE(B32:CI32)</f>
+      <c r="CX32" s="18">
+        <f t="shared" si="4"/>
         <v>4.8214285714285712</v>
       </c>
-      <c r="CX32">
-        <f>IF(CV32&gt;1,_xlfn.STDEV.S(B32:CF32),"")</f>
+      <c r="CY32">
+        <f t="shared" si="0"/>
         <v>0.89335151148745728</v>
       </c>
-      <c r="CY32">
+      <c r="CZ32">
         <v>0</v>
       </c>
-      <c r="CZ32">
-        <f>COUNT(CO32:CS32)</f>
-        <v>1</v>
-      </c>
       <c r="DA32">
-        <f>IF(CY32=0,CZ32,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:105" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="DB32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -13044,31 +13083,34 @@
       <c r="CB33" t="s">
         <v>26</v>
       </c>
-      <c r="CV33">
-        <f>COUNT(B33:CI33)</f>
+      <c r="CU33">
+        <v>6</v>
+      </c>
+      <c r="CW33">
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
-      <c r="CW33" s="18">
-        <f>AVERAGE(B33:CI33)</f>
+      <c r="CX33" s="18">
+        <f t="shared" si="4"/>
         <v>7.3461538461538458</v>
       </c>
-      <c r="CX33">
-        <f>IF(CV33&gt;1,_xlfn.STDEV.S(B33:CF33),"")</f>
+      <c r="CY33">
+        <f t="shared" si="0"/>
         <v>1.5191090506255012</v>
       </c>
-      <c r="CY33">
+      <c r="CZ33">
         <v>0</v>
       </c>
-      <c r="CZ33">
-        <f>COUNT(CO33:CS33)</f>
+      <c r="DA33">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="DA33">
-        <f>IF(CY33=0,CZ33,0)</f>
+      <c r="DB33">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -13309,31 +13351,31 @@
       <c r="CB34" t="s">
         <v>26</v>
       </c>
-      <c r="CV34">
-        <f>COUNT(B34:CI34)</f>
+      <c r="CW34">
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="CW34" s="18">
-        <f>AVERAGE(B34:CI34)</f>
+      <c r="CX34" s="18">
+        <f t="shared" si="4"/>
         <v>4.6818181818181817</v>
       </c>
-      <c r="CX34">
-        <f>IF(CV34&gt;1,_xlfn.STDEV.S(B34:CF34),"")</f>
+      <c r="CY34">
+        <f t="shared" ref="CY34:CY65" si="5">IF(CW34&gt;1,_xlfn.STDEV.S(B34:CF34),"")</f>
         <v>0.81463879335344846</v>
       </c>
-      <c r="CY34">
+      <c r="CZ34">
         <v>0</v>
       </c>
-      <c r="CZ34">
-        <f>COUNT(CO34:CS34)</f>
+      <c r="DA34">
+        <f t="shared" ref="DA34:DA65" si="6">COUNT(CO34:CS34)</f>
         <v>0</v>
       </c>
-      <c r="DA34">
-        <f>IF(CY34=0,CZ34,0)</f>
+      <c r="DB34">
+        <f t="shared" ref="DB34:DB65" si="7">IF(CZ34=0,DA34,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>45</v>
       </c>
@@ -13577,31 +13619,31 @@
       <c r="CC35">
         <v>6</v>
       </c>
-      <c r="CV35">
-        <f>COUNT(B35:CI35)</f>
+      <c r="CW35">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="CW35" s="18">
-        <f>AVERAGE(B35:CI35)</f>
+      <c r="CX35" s="18">
+        <f t="shared" si="4"/>
         <v>8.4499999999999993</v>
       </c>
-      <c r="CX35">
-        <f>IF(CV35&gt;1,_xlfn.STDEV.S(B35:CF35),"")</f>
+      <c r="CY35">
+        <f t="shared" si="5"/>
         <v>1.1890705987824657</v>
       </c>
-      <c r="CY35">
+      <c r="CZ35">
         <v>0</v>
       </c>
-      <c r="CZ35">
-        <f>COUNT(CO35:CS35)</f>
+      <c r="DA35">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA35">
-        <f>IF(CY35=0,CZ35,0)</f>
+      <c r="DB35">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>343</v>
       </c>
@@ -13860,31 +13902,34 @@
       <c r="CR36">
         <v>6</v>
       </c>
-      <c r="CV36">
-        <f>COUNT(B36:CI36)</f>
+      <c r="CU36">
+        <v>6</v>
+      </c>
+      <c r="CW36">
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="CW36" s="18">
-        <f>AVERAGE(B36:CI36)</f>
+      <c r="CX36" s="18">
+        <f t="shared" si="4"/>
         <v>4.125</v>
       </c>
-      <c r="CX36">
-        <f>IF(CV36&gt;1,_xlfn.STDEV.S(B36:CF36),"")</f>
+      <c r="CY36">
+        <f t="shared" si="5"/>
         <v>1.7677669529663689</v>
       </c>
-      <c r="CY36">
-        <v>1</v>
-      </c>
       <c r="CZ36">
-        <f>COUNT(CO36:CS36)</f>
+        <v>1</v>
+      </c>
+      <c r="DA36">
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="DA36">
-        <f>IF(CY36=0,CZ36,0)</f>
+      <c r="DB36">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>376</v>
       </c>
@@ -14140,31 +14185,34 @@
       <c r="CT37">
         <v>6</v>
       </c>
-      <c r="CV37">
-        <f>COUNT(B37:CI37)</f>
+      <c r="CU37">
+        <v>6.5</v>
+      </c>
+      <c r="CW37">
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="CW37" s="18">
-        <f>AVERAGE(B37:CI37)</f>
+      <c r="CX37" s="18">
+        <f t="shared" si="4"/>
         <v>5.7857142857142856</v>
       </c>
-      <c r="CX37">
-        <f>IF(CV37&gt;1,_xlfn.STDEV.S(B37:CF37),"")</f>
+      <c r="CY37">
+        <f t="shared" si="5"/>
         <v>0.4879500364742666</v>
       </c>
-      <c r="CY37">
-        <v>1</v>
-      </c>
       <c r="CZ37">
-        <f>COUNT(CO37:CS37)</f>
+        <v>1</v>
+      </c>
+      <c r="DA37">
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="DA37">
-        <f>IF(CY37=0,CZ37,0)</f>
+      <c r="DB37">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>340</v>
       </c>
@@ -14408,31 +14456,31 @@
       <c r="CL38">
         <v>6</v>
       </c>
-      <c r="CV38">
-        <f>COUNT(B38:CI38)</f>
+      <c r="CW38">
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="CW38" s="18">
-        <f>AVERAGE(B38:CI38)</f>
+      <c r="CX38" s="18">
+        <f t="shared" si="4"/>
         <v>5.7142857142857144</v>
       </c>
-      <c r="CX38">
-        <f>IF(CV38&gt;1,_xlfn.STDEV.S(B38:CF38),"")</f>
+      <c r="CY38">
+        <f t="shared" si="5"/>
         <v>0.56694670951384085</v>
       </c>
-      <c r="CY38">
+      <c r="CZ38">
         <v>0</v>
       </c>
-      <c r="CZ38">
-        <f>COUNT(CO38:CS38)</f>
+      <c r="DA38">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA38">
-        <f>IF(CY38=0,CZ38,0)</f>
+      <c r="DB38">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>378</v>
       </c>
@@ -14700,31 +14748,31 @@
       <c r="CQ39">
         <v>5.5</v>
       </c>
-      <c r="CV39">
-        <f>COUNT(B39:CI39)</f>
+      <c r="CW39">
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="CW39" s="18">
-        <f>AVERAGE(B39:CI39)</f>
+      <c r="CX39" s="18">
+        <f t="shared" si="4"/>
         <v>5.166666666666667</v>
       </c>
-      <c r="CX39">
-        <f>IF(CV39&gt;1,_xlfn.STDEV.S(B39:CF39),"")</f>
+      <c r="CY39">
+        <f t="shared" si="5"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="CY39">
-        <v>1</v>
-      </c>
       <c r="CZ39">
-        <f>COUNT(CO39:CS39)</f>
+        <v>1</v>
+      </c>
+      <c r="DA39">
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="DA39">
-        <f>IF(CY39=0,CZ39,0)</f>
+      <c r="DB39">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -14968,31 +15016,31 @@
       <c r="CH40">
         <v>6.5</v>
       </c>
-      <c r="CV40">
-        <f>COUNT(B40:CI40)</f>
-        <v>5</v>
-      </c>
-      <c r="CW40" s="18">
-        <f>AVERAGE(B40:CI40)</f>
+      <c r="CW40">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="CX40" s="18">
+        <f t="shared" si="4"/>
         <v>7.8</v>
       </c>
-      <c r="CX40">
-        <f>IF(CV40&gt;1,_xlfn.STDEV.S(B40:CF40),"")</f>
+      <c r="CY40">
+        <f t="shared" si="5"/>
         <v>1.0307764064044151</v>
       </c>
-      <c r="CY40">
+      <c r="CZ40">
         <v>0</v>
       </c>
-      <c r="CZ40">
-        <f>COUNT(CO40:CS40)</f>
+      <c r="DA40">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA40">
-        <f>IF(CY40=0,CZ40,0)</f>
+      <c r="DB40">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>60</v>
       </c>
@@ -15236,31 +15284,31 @@
       <c r="CM41">
         <v>5.5</v>
       </c>
-      <c r="CV41">
-        <f>COUNT(B41:CI41)</f>
+      <c r="CW41">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CW41" s="18">
-        <f>AVERAGE(B41:CI41)</f>
+      <c r="CX41" s="18">
+        <f t="shared" si="4"/>
         <v>3.375</v>
       </c>
-      <c r="CX41">
-        <f>IF(CV41&gt;1,_xlfn.STDEV.S(B41:CF41),"")</f>
+      <c r="CY41">
+        <f t="shared" si="5"/>
         <v>0.47871355387816905</v>
       </c>
-      <c r="CY41">
+      <c r="CZ41">
         <v>0</v>
       </c>
-      <c r="CZ41">
-        <f>COUNT(CO41:CS41)</f>
+      <c r="DA41">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA41">
-        <f>IF(CY41=0,CZ41,0)</f>
+      <c r="DB41">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -15501,31 +15549,31 @@
       <c r="CB42" t="s">
         <v>26</v>
       </c>
-      <c r="CV42">
-        <f>COUNT(B42:CI42)</f>
+      <c r="CW42">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CW42" s="18">
-        <f>AVERAGE(B42:CI42)</f>
+      <c r="CX42" s="18">
+        <f t="shared" si="4"/>
         <v>5.625</v>
       </c>
-      <c r="CX42">
-        <f>IF(CV42&gt;1,_xlfn.STDEV.S(B42:CF42),"")</f>
+      <c r="CY42">
+        <f t="shared" si="5"/>
         <v>0.9464847243000456</v>
       </c>
-      <c r="CY42">
+      <c r="CZ42">
         <v>0</v>
       </c>
-      <c r="CZ42">
-        <f>COUNT(CO42:CS42)</f>
+      <c r="DA42">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA42">
-        <f>IF(CY42=0,CZ42,0)</f>
+      <c r="DB42">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -15766,31 +15814,31 @@
       <c r="CB43" t="s">
         <v>26</v>
       </c>
-      <c r="CV43">
-        <f>COUNT(B43:CI43)</f>
+      <c r="CW43">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CW43" s="18">
-        <f>AVERAGE(B43:CI43)</f>
+      <c r="CX43" s="18">
+        <f t="shared" si="4"/>
         <v>6.75</v>
       </c>
-      <c r="CX43">
-        <f>IF(CV43&gt;1,_xlfn.STDEV.S(B43:CF43),"")</f>
+      <c r="CY43">
+        <f t="shared" si="5"/>
         <v>1.0408329997330663</v>
       </c>
-      <c r="CY43">
+      <c r="CZ43">
         <v>0</v>
       </c>
-      <c r="CZ43">
-        <f>COUNT(CO43:CS43)</f>
+      <c r="DA43">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA43">
-        <f>IF(CY43=0,CZ43,0)</f>
+      <c r="DB43">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -16031,31 +16079,31 @@
       <c r="CB44" t="s">
         <v>26</v>
       </c>
-      <c r="CV44">
-        <f>COUNT(B44:CI44)</f>
+      <c r="CW44">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CW44" s="18">
-        <f>AVERAGE(B44:CI44)</f>
+      <c r="CX44" s="18">
+        <f t="shared" si="4"/>
         <v>1.375</v>
       </c>
-      <c r="CX44">
-        <f>IF(CV44&gt;1,_xlfn.STDEV.S(B44:CF44),"")</f>
+      <c r="CY44">
+        <f t="shared" si="5"/>
         <v>1.8874586088176875</v>
       </c>
-      <c r="CY44">
+      <c r="CZ44">
         <v>0</v>
       </c>
-      <c r="CZ44">
-        <f>COUNT(CO44:CS44)</f>
+      <c r="DA44">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA44">
-        <f>IF(CY44=0,CZ44,0)</f>
+      <c r="DB44">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>344</v>
       </c>
@@ -16296,31 +16344,31 @@
       <c r="CB45" t="s">
         <v>26</v>
       </c>
-      <c r="CV45">
-        <f>COUNT(B45:CI45)</f>
+      <c r="CW45">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CW45" s="18">
-        <f>AVERAGE(B45:CI45)</f>
+      <c r="CX45" s="18">
+        <f t="shared" si="4"/>
         <v>4.625</v>
       </c>
-      <c r="CX45">
-        <f>IF(CV45&gt;1,_xlfn.STDEV.S(B45:CF45),"")</f>
+      <c r="CY45">
+        <f t="shared" si="5"/>
         <v>1.4361406616345072</v>
       </c>
-      <c r="CY45">
+      <c r="CZ45">
         <v>0</v>
       </c>
-      <c r="CZ45">
-        <f>COUNT(CO45:CS45)</f>
+      <c r="DA45">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA45">
-        <f>IF(CY45=0,CZ45,0)</f>
+      <c r="DB45">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>361</v>
       </c>
@@ -16561,31 +16609,31 @@
       <c r="CB46" t="s">
         <v>26</v>
       </c>
-      <c r="CV46">
-        <f>COUNT(B46:CI46)</f>
+      <c r="CW46">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CW46" s="18">
-        <f>AVERAGE(B46:CI46)</f>
+      <c r="CX46" s="18">
+        <f t="shared" si="4"/>
         <v>6.25</v>
       </c>
-      <c r="CX46">
-        <f>IF(CV46&gt;1,_xlfn.STDEV.S(B46:CF46),"")</f>
+      <c r="CY46">
+        <f t="shared" si="5"/>
         <v>0.8660254037844386</v>
       </c>
-      <c r="CY46">
+      <c r="CZ46">
         <v>0</v>
       </c>
-      <c r="CZ46">
-        <f>COUNT(CO46:CS46)</f>
+      <c r="DA46">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA46">
-        <f>IF(CY46=0,CZ46,0)</f>
+      <c r="DB46">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -16826,31 +16874,31 @@
       <c r="CB47" t="s">
         <v>26</v>
       </c>
-      <c r="CV47">
-        <f>COUNT(B47:CI47)</f>
+      <c r="CW47">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CW47" s="18">
-        <f>AVERAGE(B47:CI47)</f>
+      <c r="CX47" s="18">
+        <f t="shared" si="4"/>
         <v>2.875</v>
       </c>
-      <c r="CX47">
-        <f>IF(CV47&gt;1,_xlfn.STDEV.S(B47:CF47),"")</f>
+      <c r="CY47">
+        <f t="shared" si="5"/>
         <v>2.7801378862687129</v>
       </c>
-      <c r="CY47">
+      <c r="CZ47">
         <v>0</v>
       </c>
-      <c r="CZ47">
-        <f>COUNT(CO47:CS47)</f>
+      <c r="DA47">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA47">
-        <f>IF(CY47=0,CZ47,0)</f>
+      <c r="DB47">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -17091,31 +17139,31 @@
       <c r="CB48" t="s">
         <v>26</v>
       </c>
-      <c r="CV48">
-        <f>COUNT(B48:CI48)</f>
+      <c r="CW48">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CW48" s="18">
-        <f>AVERAGE(B48:CI48)</f>
+      <c r="CX48" s="18">
+        <f t="shared" si="4"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="CX48">
-        <f>IF(CV48&gt;1,_xlfn.STDEV.S(B48:CF48),"")</f>
+      <c r="CY48">
+        <f t="shared" si="5"/>
         <v>1.4433756729740652</v>
       </c>
-      <c r="CY48">
+      <c r="CZ48">
         <v>0</v>
       </c>
-      <c r="CZ48">
-        <f>COUNT(CO48:CS48)</f>
+      <c r="DA48">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA48">
-        <f>IF(CY48=0,CZ48,0)</f>
+      <c r="DB48">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -17356,31 +17404,31 @@
       <c r="CB49" t="s">
         <v>26</v>
       </c>
-      <c r="CV49">
-        <f>COUNT(B49:CI49)</f>
+      <c r="CW49">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CW49" s="18">
-        <f>AVERAGE(B49:CI49)</f>
+      <c r="CX49" s="18">
+        <f t="shared" si="4"/>
         <v>8.5</v>
       </c>
-      <c r="CX49">
-        <f>IF(CV49&gt;1,_xlfn.STDEV.S(B49:CF49),"")</f>
+      <c r="CY49">
+        <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
-      <c r="CY49">
+      <c r="CZ49">
         <v>0</v>
       </c>
-      <c r="CZ49">
-        <f>COUNT(CO49:CS49)</f>
+      <c r="DA49">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA49">
-        <f>IF(CY49=0,CZ49,0)</f>
+      <c r="DB49">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -17621,31 +17669,31 @@
       <c r="CB50" t="s">
         <v>26</v>
       </c>
-      <c r="CV50">
-        <f>COUNT(B50:CI50)</f>
+      <c r="CW50">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CW50" s="18">
-        <f>AVERAGE(B50:CI50)</f>
+      <c r="CX50" s="18">
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="CX50">
-        <f>IF(CV50&gt;1,_xlfn.STDEV.S(B50:CF50),"")</f>
+      <c r="CY50">
+        <f t="shared" si="5"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CY50">
+      <c r="CZ50">
         <v>0</v>
       </c>
-      <c r="CZ50">
-        <f>COUNT(CO50:CS50)</f>
+      <c r="DA50">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA50">
-        <f>IF(CY50=0,CZ50,0)</f>
+      <c r="DB50">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -17889,31 +17937,31 @@
       <c r="CG51">
         <v>6</v>
       </c>
-      <c r="CV51">
-        <f>COUNT(B51:CI51)</f>
+      <c r="CW51">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CW51" s="18">
-        <f>AVERAGE(B51:CI51)</f>
+      <c r="CX51" s="18">
+        <f t="shared" si="4"/>
         <v>5.666666666666667</v>
       </c>
-      <c r="CX51">
-        <f>IF(CV51&gt;1,_xlfn.STDEV.S(B51:CF51),"")</f>
+      <c r="CY51">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="CY51">
+      <c r="CZ51">
         <v>0</v>
       </c>
-      <c r="CZ51">
-        <f>COUNT(CO51:CS51)</f>
+      <c r="DA51">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA51">
-        <f>IF(CY51=0,CZ51,0)</f>
+      <c r="DB51">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>368</v>
       </c>
@@ -18157,31 +18205,31 @@
       <c r="CG52">
         <v>6</v>
       </c>
-      <c r="CV52">
-        <f>COUNT(B52:CI52)</f>
+      <c r="CW52">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CW52" s="18">
-        <f>AVERAGE(B52:CI52)</f>
+      <c r="CX52" s="18">
+        <f t="shared" si="4"/>
         <v>8.5</v>
       </c>
-      <c r="CX52">
-        <f>IF(CV52&gt;1,_xlfn.STDEV.S(B52:CF52),"")</f>
+      <c r="CY52">
+        <f t="shared" si="5"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CY52">
+      <c r="CZ52">
         <v>0</v>
       </c>
-      <c r="CZ52">
-        <f>COUNT(CO52:CS52)</f>
+      <c r="DA52">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA52">
-        <f>IF(CY52=0,CZ52,0)</f>
+      <c r="DB52">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>345</v>
       </c>
@@ -18440,31 +18488,31 @@
       <c r="CO53">
         <v>4.5</v>
       </c>
-      <c r="CV53">
-        <f>COUNT(B53:CI53)</f>
-        <v>2</v>
-      </c>
-      <c r="CW53" s="18">
-        <f>AVERAGE(B53:CI53)</f>
+      <c r="CW53">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="CX53" s="18">
+        <f t="shared" si="4"/>
         <v>4.25</v>
       </c>
-      <c r="CX53" t="e">
-        <f>IF(CV53&gt;1,_xlfn.STDEV.S(B53:CF53),"")</f>
+      <c r="CY53" t="e">
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CY53">
+      <c r="CZ53">
         <v>0</v>
       </c>
-      <c r="CZ53">
-        <f>COUNT(CO53:CS53)</f>
-        <v>1</v>
-      </c>
       <c r="DA53">
-        <f>IF(CY53=0,CZ53,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:105" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="DB53">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -18708,31 +18756,31 @@
       <c r="CS54">
         <v>5.5</v>
       </c>
-      <c r="CV54">
-        <f>COUNT(B54:CI54)</f>
-        <v>2</v>
-      </c>
-      <c r="CW54" s="18">
-        <f>AVERAGE(B54:CI54)</f>
+      <c r="CW54">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="CX54" s="18">
+        <f t="shared" si="4"/>
         <v>5.25</v>
       </c>
-      <c r="CX54">
-        <f>IF(CV54&gt;1,_xlfn.STDEV.S(B54:CF54),"")</f>
+      <c r="CY54">
+        <f t="shared" si="5"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CY54">
+      <c r="CZ54">
         <v>0</v>
       </c>
-      <c r="CZ54">
-        <f>COUNT(CO54:CS54)</f>
-        <v>1</v>
-      </c>
       <c r="DA54">
-        <f>IF(CY54=0,CZ54,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:105" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="DB54">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>342</v>
       </c>
@@ -18979,31 +19027,34 @@
       <c r="CO55">
         <v>6</v>
       </c>
-      <c r="CV55">
-        <f>COUNT(B55:CI55)</f>
-        <v>2</v>
-      </c>
-      <c r="CW55" s="18">
-        <f>AVERAGE(B55:CI55)</f>
-        <v>5.5</v>
-      </c>
-      <c r="CX55">
-        <f>IF(CV55&gt;1,_xlfn.STDEV.S(B55:CF55),"")</f>
+      <c r="CU55">
+        <v>5.5</v>
+      </c>
+      <c r="CW55">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="CX55" s="18">
+        <f t="shared" si="4"/>
+        <v>5.5</v>
+      </c>
+      <c r="CY55">
+        <f t="shared" si="5"/>
         <v>2.1213203435596424</v>
       </c>
-      <c r="CY55">
+      <c r="CZ55">
         <v>0</v>
       </c>
-      <c r="CZ55">
-        <f>COUNT(CO55:CS55)</f>
-        <v>1</v>
-      </c>
       <c r="DA55">
-        <f>IF(CY55=0,CZ55,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:105" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="DB55">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>390</v>
       </c>
@@ -19256,31 +19307,34 @@
       <c r="CT56">
         <v>6</v>
       </c>
-      <c r="CV56">
-        <f>COUNT(B56:CI56)</f>
-        <v>2</v>
-      </c>
-      <c r="CW56" s="18">
-        <f>AVERAGE(B56:CI56)</f>
+      <c r="CU56">
+        <v>6</v>
+      </c>
+      <c r="CW56">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="CX56" s="18">
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="CX56" t="e">
-        <f>IF(CV56&gt;1,_xlfn.STDEV.S(B56:CF56),"")</f>
+      <c r="CY56" t="e">
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CY56">
+      <c r="CZ56">
         <v>0</v>
       </c>
-      <c r="CZ56">
-        <f>COUNT(CO56:CS56)</f>
-        <v>1</v>
-      </c>
       <c r="DA56">
-        <f>IF(CY56=0,CZ56,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:105" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="DB56">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>364</v>
       </c>
@@ -19530,31 +19584,31 @@
       <c r="CN57">
         <v>6</v>
       </c>
-      <c r="CV57">
-        <f>COUNT(B57:CI57)</f>
-        <v>2</v>
-      </c>
-      <c r="CW57" s="18">
-        <f>AVERAGE(B57:CI57)</f>
+      <c r="CW57">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="CX57" s="18">
+        <f t="shared" si="4"/>
         <v>6.5</v>
       </c>
-      <c r="CX57">
-        <f>IF(CV57&gt;1,_xlfn.STDEV.S(B57:CF57),"")</f>
+      <c r="CY57">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="CY57">
+      <c r="CZ57">
         <v>0</v>
       </c>
-      <c r="CZ57">
-        <f>COUNT(CO57:CS57)</f>
+      <c r="DA57">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA57">
-        <f>IF(CY57=0,CZ57,0)</f>
+      <c r="DB57">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>362</v>
       </c>
@@ -19798,31 +19852,31 @@
       <c r="CD58">
         <v>5.5</v>
       </c>
-      <c r="CV58">
-        <f>COUNT(B58:CI58)</f>
-        <v>2</v>
-      </c>
-      <c r="CW58" s="18">
-        <f>AVERAGE(B58:CI58)</f>
+      <c r="CW58">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="CX58" s="18">
+        <f t="shared" si="4"/>
         <v>5.25</v>
       </c>
-      <c r="CX58">
-        <f>IF(CV58&gt;1,_xlfn.STDEV.S(B58:CF58),"")</f>
+      <c r="CY58">
+        <f t="shared" si="5"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="CY58">
+      <c r="CZ58">
         <v>0</v>
       </c>
-      <c r="CZ58">
-        <f>COUNT(CO58:CS58)</f>
+      <c r="DA58">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA58">
-        <f>IF(CY58=0,CZ58,0)</f>
+      <c r="DB58">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>339</v>
       </c>
@@ -20063,31 +20117,31 @@
       <c r="CB59" t="s">
         <v>26</v>
       </c>
-      <c r="CV59">
-        <f>COUNT(B59:CI59)</f>
-        <v>2</v>
-      </c>
-      <c r="CW59" s="18">
-        <f>AVERAGE(B59:CI59)</f>
+      <c r="CW59">
+        <f t="shared" ref="CW59:CW88" si="8">COUNT(B59:CI59)</f>
+        <v>2</v>
+      </c>
+      <c r="CX59" s="18">
+        <f t="shared" ref="CX59:CX88" si="9">AVERAGE(B59:CI59)</f>
         <v>6.75</v>
       </c>
-      <c r="CX59">
-        <f>IF(CV59&gt;1,_xlfn.STDEV.S(B59:CF59),"")</f>
+      <c r="CY59">
+        <f t="shared" si="5"/>
         <v>2.4748737341529163</v>
       </c>
-      <c r="CY59">
+      <c r="CZ59">
         <v>0</v>
       </c>
-      <c r="CZ59">
-        <f>COUNT(CO59:CS59)</f>
+      <c r="DA59">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA59">
-        <f>IF(CY59=0,CZ59,0)</f>
+      <c r="DB59">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>369</v>
       </c>
@@ -20328,31 +20382,31 @@
       <c r="CB60" t="s">
         <v>26</v>
       </c>
-      <c r="CV60">
-        <f>COUNT(B60:CI60)</f>
-        <v>2</v>
-      </c>
-      <c r="CW60" s="18">
-        <f>AVERAGE(B60:CI60)</f>
+      <c r="CW60">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="CX60" s="18">
+        <f t="shared" si="9"/>
         <v>5.75</v>
       </c>
-      <c r="CX60">
-        <f>IF(CV60&gt;1,_xlfn.STDEV.S(B60:CF60),"")</f>
+      <c r="CY60">
+        <f t="shared" si="5"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="CY60">
+      <c r="CZ60">
         <v>0</v>
       </c>
-      <c r="CZ60">
-        <f>COUNT(CO60:CS60)</f>
+      <c r="DA60">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA60">
-        <f>IF(CY60=0,CZ60,0)</f>
+      <c r="DB60">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>379</v>
       </c>
@@ -20593,31 +20647,31 @@
       <c r="CB61" t="s">
         <v>26</v>
       </c>
-      <c r="CV61">
-        <f>COUNT(B61:CI61)</f>
-        <v>2</v>
-      </c>
-      <c r="CW61" s="18">
-        <f>AVERAGE(B61:CI61)</f>
-        <v>5.5</v>
-      </c>
-      <c r="CX61">
-        <f>IF(CV61&gt;1,_xlfn.STDEV.S(B61:CF61),"")</f>
+      <c r="CW61">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="CX61" s="18">
+        <f t="shared" si="9"/>
+        <v>5.5</v>
+      </c>
+      <c r="CY61">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="CY61">
+      <c r="CZ61">
         <v>0</v>
       </c>
-      <c r="CZ61">
-        <f>COUNT(CO61:CS61)</f>
+      <c r="DA61">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA61">
-        <f>IF(CY61=0,CZ61,0)</f>
+      <c r="DB61">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>388</v>
       </c>
@@ -20861,31 +20915,31 @@
       <c r="CH62">
         <v>5</v>
       </c>
-      <c r="CV62">
-        <f>COUNT(B62:CI62)</f>
-        <v>2</v>
-      </c>
-      <c r="CW62" s="18">
-        <f>AVERAGE(B62:CI62)</f>
+      <c r="CW62">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="CX62" s="18">
+        <f t="shared" si="9"/>
         <v>4.25</v>
       </c>
-      <c r="CX62" t="e">
-        <f>IF(CV62&gt;1,_xlfn.STDEV.S(B62:CF62),"")</f>
+      <c r="CY62" t="e">
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CY62">
+      <c r="CZ62">
         <v>0</v>
       </c>
-      <c r="CZ62">
-        <f>COUNT(CO62:CS62)</f>
+      <c r="DA62">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA62">
-        <f>IF(CY62=0,CZ62,0)</f>
+      <c r="DB62">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>387</v>
       </c>
@@ -21135,31 +21189,31 @@
       <c r="CJ63">
         <v>7</v>
       </c>
-      <c r="CV63">
-        <f>COUNT(B63:CI63)</f>
-        <v>2</v>
-      </c>
-      <c r="CW63" s="18">
-        <f>AVERAGE(B63:CI63)</f>
+      <c r="CW63">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="CX63" s="18">
+        <f t="shared" si="9"/>
         <v>6.5</v>
       </c>
-      <c r="CX63" t="e">
-        <f>IF(CV63&gt;1,_xlfn.STDEV.S(B63:CF63),"")</f>
+      <c r="CY63" t="e">
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CY63">
+      <c r="CZ63">
         <v>0</v>
       </c>
-      <c r="CZ63">
-        <f>COUNT(CO63:CS63)</f>
+      <c r="DA63">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA63">
-        <f>IF(CY63=0,CZ63,0)</f>
+      <c r="DB63">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>86</v>
       </c>
@@ -21400,31 +21454,31 @@
       <c r="CB64" t="s">
         <v>26</v>
       </c>
-      <c r="CV64">
-        <f>COUNT(B64:CI64)</f>
-        <v>1</v>
-      </c>
-      <c r="CW64" s="18">
-        <f>AVERAGE(B64:CI64)</f>
+      <c r="CW64">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX64" s="18">
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="CX64" t="str">
-        <f>IF(CV64&gt;1,_xlfn.STDEV.S(B64:CF64),"")</f>
+      <c r="CY64" t="str">
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="CY64">
+      <c r="CZ64">
         <v>0</v>
       </c>
-      <c r="CZ64">
-        <f>COUNT(CO64:CS64)</f>
+      <c r="DA64">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA64">
-        <f>IF(CY64=0,CZ64,0)</f>
+      <c r="DB64">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -21665,31 +21719,31 @@
       <c r="CB65" t="s">
         <v>26</v>
       </c>
-      <c r="CV65">
-        <f>COUNT(B65:CI65)</f>
-        <v>1</v>
-      </c>
-      <c r="CW65" s="18">
-        <f>AVERAGE(B65:CI65)</f>
+      <c r="CW65">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX65" s="18">
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="CX65" t="str">
-        <f>IF(CV65&gt;1,_xlfn.STDEV.S(B65:CF65),"")</f>
+      <c r="CY65" t="str">
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="CY65">
+      <c r="CZ65">
         <v>0</v>
       </c>
-      <c r="CZ65">
-        <f>COUNT(CO65:CS65)</f>
+      <c r="DA65">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="DA65">
-        <f>IF(CY65=0,CZ65,0)</f>
+      <c r="DB65">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>353</v>
       </c>
@@ -21930,31 +21984,31 @@
       <c r="CB66" t="s">
         <v>26</v>
       </c>
-      <c r="CV66">
-        <f>COUNT(B66:CI66)</f>
-        <v>1</v>
-      </c>
-      <c r="CW66" s="18">
-        <f>AVERAGE(B66:CI66)</f>
+      <c r="CW66">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX66" s="18">
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="CX66" t="str">
-        <f>IF(CV66&gt;1,_xlfn.STDEV.S(B66:CF66),"")</f>
+      <c r="CY66" t="str">
+        <f t="shared" ref="CY66:CY88" si="10">IF(CW66&gt;1,_xlfn.STDEV.S(B66:CF66),"")</f>
         <v/>
       </c>
-      <c r="CY66">
+      <c r="CZ66">
         <v>0</v>
       </c>
-      <c r="CZ66">
-        <f>COUNT(CO66:CS66)</f>
+      <c r="DA66">
+        <f t="shared" ref="DA66:DA88" si="11">COUNT(CO66:CS66)</f>
         <v>0</v>
       </c>
-      <c r="DA66">
-        <f>IF(CY66=0,CZ66,0)</f>
+      <c r="DB66">
+        <f t="shared" ref="DB66:DB88" si="12">IF(CZ66=0,DA66,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>80</v>
       </c>
@@ -22195,31 +22249,31 @@
       <c r="CB67" t="s">
         <v>26</v>
       </c>
-      <c r="CV67">
-        <f>COUNT(B67:CI67)</f>
-        <v>1</v>
-      </c>
-      <c r="CW67" s="18">
-        <f>AVERAGE(B67:CI67)</f>
+      <c r="CW67">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX67" s="18">
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="CX67" t="str">
-        <f>IF(CV67&gt;1,_xlfn.STDEV.S(B67:CF67),"")</f>
+      <c r="CY67" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY67">
+      <c r="CZ67">
         <v>0</v>
       </c>
-      <c r="CZ67">
-        <f>COUNT(CO67:CS67)</f>
+      <c r="DA67">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA67">
-        <f>IF(CY67=0,CZ67,0)</f>
+      <c r="DB67">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>47</v>
       </c>
@@ -22460,31 +22514,31 @@
       <c r="CB68" t="s">
         <v>26</v>
       </c>
-      <c r="CV68">
-        <f>COUNT(B68:CI68)</f>
-        <v>1</v>
-      </c>
-      <c r="CW68" s="18">
-        <f>AVERAGE(B68:CI68)</f>
+      <c r="CW68">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX68" s="18">
+        <f t="shared" si="9"/>
         <v>3.5</v>
       </c>
-      <c r="CX68" t="str">
-        <f>IF(CV68&gt;1,_xlfn.STDEV.S(B68:CF68),"")</f>
+      <c r="CY68" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY68">
+      <c r="CZ68">
         <v>0</v>
       </c>
-      <c r="CZ68">
-        <f>COUNT(CO68:CS68)</f>
+      <c r="DA68">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA68">
-        <f>IF(CY68=0,CZ68,0)</f>
+      <c r="DB68">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -22725,31 +22779,31 @@
       <c r="CB69" t="s">
         <v>26</v>
       </c>
-      <c r="CV69">
-        <f>COUNT(B69:CI69)</f>
-        <v>1</v>
-      </c>
-      <c r="CW69" s="18">
-        <f>AVERAGE(B69:CI69)</f>
+      <c r="CW69">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX69" s="18">
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="CX69" t="str">
-        <f>IF(CV69&gt;1,_xlfn.STDEV.S(B69:CF69),"")</f>
+      <c r="CY69" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY69">
+      <c r="CZ69">
         <v>0</v>
       </c>
-      <c r="CZ69">
-        <f>COUNT(CO69:CS69)</f>
+      <c r="DA69">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA69">
-        <f>IF(CY69=0,CZ69,0)</f>
+      <c r="DB69">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>347</v>
       </c>
@@ -22990,31 +23044,31 @@
       <c r="CB70" t="s">
         <v>26</v>
       </c>
-      <c r="CV70">
-        <f>COUNT(B70:CI70)</f>
-        <v>1</v>
-      </c>
-      <c r="CW70" s="18">
-        <f>AVERAGE(B70:CI70)</f>
+      <c r="CW70">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX70" s="18">
+        <f t="shared" si="9"/>
         <v>6.5</v>
       </c>
-      <c r="CX70" t="str">
-        <f>IF(CV70&gt;1,_xlfn.STDEV.S(B70:CF70),"")</f>
+      <c r="CY70" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY70">
+      <c r="CZ70">
         <v>0</v>
       </c>
-      <c r="CZ70">
-        <f>COUNT(CO70:CS70)</f>
+      <c r="DA70">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA70">
-        <f>IF(CY70=0,CZ70,0)</f>
+      <c r="DB70">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>350</v>
       </c>
@@ -23255,31 +23309,31 @@
       <c r="CB71" t="s">
         <v>26</v>
       </c>
-      <c r="CV71">
-        <f>COUNT(B71:CI71)</f>
-        <v>1</v>
-      </c>
-      <c r="CW71" s="18">
-        <f>AVERAGE(B71:CI71)</f>
+      <c r="CW71">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX71" s="18">
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="CX71" t="str">
-        <f>IF(CV71&gt;1,_xlfn.STDEV.S(B71:CF71),"")</f>
+      <c r="CY71" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY71">
+      <c r="CZ71">
         <v>0</v>
       </c>
-      <c r="CZ71">
-        <f>COUNT(CO71:CS71)</f>
+      <c r="DA71">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA71">
-        <f>IF(CY71=0,CZ71,0)</f>
+      <c r="DB71">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>351</v>
       </c>
@@ -23520,31 +23574,31 @@
       <c r="CB72" t="s">
         <v>26</v>
       </c>
-      <c r="CV72">
-        <f>COUNT(B72:CI72)</f>
-        <v>1</v>
-      </c>
-      <c r="CW72" s="18">
-        <f>AVERAGE(B72:CI72)</f>
+      <c r="CW72">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX72" s="18">
+        <f t="shared" si="9"/>
         <v>6.5</v>
       </c>
-      <c r="CX72" t="str">
-        <f>IF(CV72&gt;1,_xlfn.STDEV.S(B72:CF72),"")</f>
+      <c r="CY72" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY72">
+      <c r="CZ72">
         <v>0</v>
       </c>
-      <c r="CZ72">
-        <f>COUNT(CO72:CS72)</f>
+      <c r="DA72">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA72">
-        <f>IF(CY72=0,CZ72,0)</f>
+      <c r="DB72">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>352</v>
       </c>
@@ -23785,31 +23839,31 @@
       <c r="CB73" t="s">
         <v>26</v>
       </c>
-      <c r="CV73">
-        <f>COUNT(B73:CI73)</f>
-        <v>1</v>
-      </c>
-      <c r="CW73" s="18">
-        <f>AVERAGE(B73:CI73)</f>
-        <v>5</v>
-      </c>
-      <c r="CX73" t="str">
-        <f>IF(CV73&gt;1,_xlfn.STDEV.S(B73:CF73),"")</f>
+      <c r="CW73">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX73" s="18">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="CY73" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY73">
+      <c r="CZ73">
         <v>0</v>
       </c>
-      <c r="CZ73">
-        <f>COUNT(CO73:CS73)</f>
+      <c r="DA73">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA73">
-        <f>IF(CY73=0,CZ73,0)</f>
+      <c r="DB73">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>354</v>
       </c>
@@ -24050,31 +24104,31 @@
       <c r="CB74" t="s">
         <v>26</v>
       </c>
-      <c r="CV74">
-        <f>COUNT(B74:CI74)</f>
-        <v>1</v>
-      </c>
-      <c r="CW74" s="18">
-        <f>AVERAGE(B74:CI74)</f>
-        <v>5.5</v>
-      </c>
-      <c r="CX74" t="str">
-        <f>IF(CV74&gt;1,_xlfn.STDEV.S(B74:CF74),"")</f>
+      <c r="CW74">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX74" s="18">
+        <f t="shared" si="9"/>
+        <v>5.5</v>
+      </c>
+      <c r="CY74" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY74">
+      <c r="CZ74">
         <v>0</v>
       </c>
-      <c r="CZ74">
-        <f>COUNT(CO74:CS74)</f>
+      <c r="DA74">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA74">
-        <f>IF(CY74=0,CZ74,0)</f>
+      <c r="DB74">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>365</v>
       </c>
@@ -24315,31 +24369,31 @@
       <c r="CB75" t="s">
         <v>26</v>
       </c>
-      <c r="CV75">
-        <f>COUNT(B75:CI75)</f>
-        <v>1</v>
-      </c>
-      <c r="CW75" s="18">
-        <f>AVERAGE(B75:CI75)</f>
-        <v>2</v>
-      </c>
-      <c r="CX75" t="str">
-        <f>IF(CV75&gt;1,_xlfn.STDEV.S(B75:CF75),"")</f>
+      <c r="CW75">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX75" s="18">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="CY75" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY75">
+      <c r="CZ75">
         <v>0</v>
       </c>
-      <c r="CZ75">
-        <f>COUNT(CO75:CS75)</f>
+      <c r="DA75">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA75">
-        <f>IF(CY75=0,CZ75,0)</f>
+      <c r="DB75">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>366</v>
       </c>
@@ -24580,31 +24634,31 @@
       <c r="CB76" t="s">
         <v>26</v>
       </c>
-      <c r="CV76">
-        <f>COUNT(B76:CI76)</f>
-        <v>1</v>
-      </c>
-      <c r="CW76" s="18">
-        <f>AVERAGE(B76:CI76)</f>
+      <c r="CW76">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX76" s="18">
+        <f t="shared" si="9"/>
         <v>2.5</v>
       </c>
-      <c r="CX76" t="str">
-        <f>IF(CV76&gt;1,_xlfn.STDEV.S(B76:CF76),"")</f>
+      <c r="CY76" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY76">
+      <c r="CZ76">
         <v>0</v>
       </c>
-      <c r="CZ76">
-        <f>COUNT(CO76:CS76)</f>
+      <c r="DA76">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA76">
-        <f>IF(CY76=0,CZ76,0)</f>
+      <c r="DB76">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>374</v>
       </c>
@@ -24845,31 +24899,31 @@
       <c r="CB77" t="s">
         <v>26</v>
       </c>
-      <c r="CV77">
-        <f>COUNT(B77:CI77)</f>
-        <v>1</v>
-      </c>
-      <c r="CW77" s="18">
-        <f>AVERAGE(B77:CI77)</f>
+      <c r="CW77">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX77" s="18">
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="CX77" t="str">
-        <f>IF(CV77&gt;1,_xlfn.STDEV.S(B77:CF77),"")</f>
+      <c r="CY77" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY77">
+      <c r="CZ77">
         <v>0</v>
       </c>
-      <c r="CZ77">
-        <f>COUNT(CO77:CS77)</f>
+      <c r="DA77">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA77">
-        <f>IF(CY77=0,CZ77,0)</f>
+      <c r="DB77">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>375</v>
       </c>
@@ -25110,31 +25164,31 @@
       <c r="CB78" t="s">
         <v>26</v>
       </c>
-      <c r="CV78">
-        <f>COUNT(B78:CI78)</f>
-        <v>1</v>
-      </c>
-      <c r="CW78" s="18">
-        <f>AVERAGE(B78:CI78)</f>
-        <v>5.5</v>
-      </c>
-      <c r="CX78" t="str">
-        <f>IF(CV78&gt;1,_xlfn.STDEV.S(B78:CF78),"")</f>
+      <c r="CW78">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX78" s="18">
+        <f t="shared" si="9"/>
+        <v>5.5</v>
+      </c>
+      <c r="CY78" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY78">
+      <c r="CZ78">
         <v>0</v>
       </c>
-      <c r="CZ78">
-        <f>COUNT(CO78:CS78)</f>
+      <c r="DA78">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA78">
-        <f>IF(CY78=0,CZ78,0)</f>
+      <c r="DB78">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>377</v>
       </c>
@@ -25375,31 +25429,31 @@
       <c r="CB79" t="s">
         <v>26</v>
       </c>
-      <c r="CV79">
-        <f>COUNT(B79:CI79)</f>
-        <v>1</v>
-      </c>
-      <c r="CW79" s="18">
-        <f>AVERAGE(B79:CI79)</f>
-        <v>5</v>
-      </c>
-      <c r="CX79" t="str">
-        <f>IF(CV79&gt;1,_xlfn.STDEV.S(B79:CF79),"")</f>
+      <c r="CW79">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX79" s="18">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="CY79" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY79">
+      <c r="CZ79">
         <v>0</v>
       </c>
-      <c r="CZ79">
-        <f>COUNT(CO79:CS79)</f>
+      <c r="DA79">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA79">
-        <f>IF(CY79=0,CZ79,0)</f>
+      <c r="DB79">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>381</v>
       </c>
@@ -25640,31 +25694,31 @@
       <c r="CB80" t="s">
         <v>26</v>
       </c>
-      <c r="CV80">
-        <f>COUNT(B80:CI80)</f>
-        <v>1</v>
-      </c>
-      <c r="CW80" s="18">
-        <f>AVERAGE(B80:CI80)</f>
-        <v>5.5</v>
-      </c>
-      <c r="CX80" t="str">
-        <f>IF(CV80&gt;1,_xlfn.STDEV.S(B80:CF80),"")</f>
+      <c r="CW80">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX80" s="18">
+        <f t="shared" si="9"/>
+        <v>5.5</v>
+      </c>
+      <c r="CY80" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY80">
+      <c r="CZ80">
         <v>0</v>
       </c>
-      <c r="CZ80">
-        <f>COUNT(CO80:CS80)</f>
+      <c r="DA80">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA80">
-        <f>IF(CY80=0,CZ80,0)</f>
+      <c r="DB80">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>382</v>
       </c>
@@ -25905,31 +25959,31 @@
       <c r="CB81" t="s">
         <v>26</v>
       </c>
-      <c r="CV81">
-        <f>COUNT(B81:CI81)</f>
-        <v>1</v>
-      </c>
-      <c r="CW81" s="18">
-        <f>AVERAGE(B81:CI81)</f>
-        <v>5.5</v>
-      </c>
-      <c r="CX81" t="str">
-        <f>IF(CV81&gt;1,_xlfn.STDEV.S(B81:CF81),"")</f>
+      <c r="CW81">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX81" s="18">
+        <f t="shared" si="9"/>
+        <v>5.5</v>
+      </c>
+      <c r="CY81" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY81">
+      <c r="CZ81">
         <v>0</v>
       </c>
-      <c r="CZ81">
-        <f>COUNT(CO81:CS81)</f>
+      <c r="DA81">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA81">
-        <f>IF(CY81=0,CZ81,0)</f>
+      <c r="DB81">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>389</v>
       </c>
@@ -26173,31 +26227,31 @@
       <c r="CH82">
         <v>7.5</v>
       </c>
-      <c r="CV82">
-        <f>COUNT(B82:CI82)</f>
-        <v>1</v>
-      </c>
-      <c r="CW82" s="18">
-        <f>AVERAGE(B82:CI82)</f>
+      <c r="CW82">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX82" s="18">
+        <f t="shared" si="9"/>
         <v>7.5</v>
       </c>
-      <c r="CX82" t="str">
-        <f>IF(CV82&gt;1,_xlfn.STDEV.S(B82:CF82),"")</f>
+      <c r="CY82" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY82">
+      <c r="CZ82">
         <v>0</v>
       </c>
-      <c r="CZ82">
-        <f>COUNT(CO82:CS82)</f>
+      <c r="DA82">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA82">
-        <f>IF(CY82=0,CZ82,0)</f>
+      <c r="DB82">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>391</v>
       </c>
@@ -26441,31 +26495,31 @@
       <c r="CI83">
         <v>7</v>
       </c>
-      <c r="CV83">
-        <f>COUNT(B83:CI83)</f>
-        <v>1</v>
-      </c>
-      <c r="CW83" s="18">
-        <f>AVERAGE(B83:CI83)</f>
+      <c r="CW83">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="CX83" s="18">
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="CX83" t="str">
-        <f>IF(CV83&gt;1,_xlfn.STDEV.S(B83:CF83),"")</f>
+      <c r="CY83" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY83">
+      <c r="CZ83">
         <v>0</v>
       </c>
-      <c r="CZ83">
-        <f>COUNT(CO83:CS83)</f>
+      <c r="DA83">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DA83">
-        <f>IF(CY83=0,CZ83,0)</f>
+      <c r="DB83">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>393</v>
       </c>
@@ -26481,31 +26535,34 @@
       <c r="CT84">
         <v>7</v>
       </c>
-      <c r="CV84">
-        <f>COUNT(B84:CI84)</f>
+      <c r="CU84">
+        <v>3.5</v>
+      </c>
+      <c r="CW84">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW84" s="18" t="e">
-        <f>AVERAGE(B84:CI84)</f>
+      <c r="CX84" s="18" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CX84" t="str">
-        <f>IF(CV84&gt;1,_xlfn.STDEV.S(B84:CF84),"")</f>
+      <c r="CY84" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY84">
+      <c r="CZ84">
         <v>0</v>
       </c>
-      <c r="CZ84">
-        <f>COUNT(CO84:CS84)</f>
+      <c r="DA84">
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="DA84">
-        <f>IF(CY84=0,CZ84,0)</f>
+      <c r="DB84">
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>394</v>
       </c>
@@ -26518,93 +26575,93 @@
       <c r="CS85">
         <v>6</v>
       </c>
-      <c r="CV85">
-        <f>COUNT(B85:CI85)</f>
+      <c r="CW85">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW85" s="18" t="e">
-        <f>AVERAGE(B85:CI85)</f>
+      <c r="CX85" s="18" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CX85" t="str">
-        <f>IF(CV85&gt;1,_xlfn.STDEV.S(B85:CF85),"")</f>
+      <c r="CY85" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY85">
+      <c r="CZ85">
         <v>0</v>
       </c>
-      <c r="CZ85">
-        <f>COUNT(CO85:CS85)</f>
+      <c r="DA85">
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="DA85">
-        <f>IF(CY85=0,CZ85,0)</f>
+      <c r="DB85">
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:105" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>395</v>
       </c>
       <c r="CP86">
         <v>6.5</v>
       </c>
-      <c r="CV86">
-        <f>COUNT(B86:CI86)</f>
+      <c r="CW86">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW86" s="18" t="e">
-        <f>AVERAGE(B86:CI86)</f>
+      <c r="CX86" s="18" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CX86" t="str">
-        <f>IF(CV86&gt;1,_xlfn.STDEV.S(B86:CF86),"")</f>
+      <c r="CY86" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY86">
+      <c r="CZ86">
         <v>0</v>
       </c>
-      <c r="CZ86">
-        <f>COUNT(CO86:CS86)</f>
-        <v>1</v>
-      </c>
       <c r="DA86">
-        <f>IF(CY86=0,CZ86,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:105" x14ac:dyDescent="0.35">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="DB86">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>396</v>
       </c>
       <c r="CQ87">
         <v>6.5</v>
       </c>
-      <c r="CV87">
-        <f>COUNT(B87:CI87)</f>
+      <c r="CW87">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW87" s="18" t="e">
-        <f>AVERAGE(B87:CI87)</f>
+      <c r="CX87" s="18" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CX87" t="str">
-        <f>IF(CV87&gt;1,_xlfn.STDEV.S(B87:CF87),"")</f>
+      <c r="CY87" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY87">
+      <c r="CZ87">
         <v>0</v>
       </c>
-      <c r="CZ87">
-        <f>COUNT(CO87:CS87)</f>
-        <v>1</v>
-      </c>
       <c r="DA87">
-        <f>IF(CY87=0,CZ87,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:105" x14ac:dyDescent="0.35">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="DB87">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:106" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>392</v>
       </c>
@@ -26626,37 +26683,68 @@
       <c r="CT88">
         <v>6.5</v>
       </c>
-      <c r="CV88">
-        <f>COUNT(B88:CI88)</f>
+      <c r="CW88">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="CW88" s="18" t="e">
-        <f>AVERAGE(B88:CI88)</f>
+      <c r="CX88" s="18" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CX88" t="str">
-        <f>IF(CV88&gt;1,_xlfn.STDEV.S(B88:CF88),"")</f>
+      <c r="CY88" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="CY88">
-        <v>1</v>
-      </c>
       <c r="CZ88">
-        <f>COUNT(CO88:CS88)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="DA88">
-        <f>IF(CY88=0,CZ88,0)</f>
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="DB88">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
+    <row r="89" spans="1:106" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>399</v>
+      </c>
+      <c r="CU89">
+        <v>7.5</v>
+      </c>
+      <c r="CW89">
+        <f t="shared" ref="CW89" si="13">COUNT(B89:CI89)</f>
+        <v>0</v>
+      </c>
+      <c r="CX89" s="18" t="e">
+        <f t="shared" ref="CX89" si="14">AVERAGE(B89:CI89)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY89" t="str">
+        <f t="shared" ref="CY89" si="15">IF(CW89&gt;1,_xlfn.STDEV.S(B89:CF89),"")</f>
+        <v/>
+      </c>
+      <c r="CZ89">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="DA89">
+        <f t="shared" ref="DA89" si="16">COUNT(CO89:CS89)</f>
+        <v>0</v>
+      </c>
+      <c r="DB89">
+        <f t="shared" ref="DB89" si="17">IF(CZ89=0,DA89,0)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:DA83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
-    <sortState ref="A2:DA88">
-      <sortCondition descending="1" ref="CV1:CV83"/>
+  <autoFilter ref="A1:DB83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
+    <sortState ref="A2:DB88">
+      <sortCondition descending="1" ref="CW1:CW83"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="CV2:CV88">
+  <conditionalFormatting sqref="CW2:CW89">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -26668,7 +26756,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CX2:CX88">
+  <conditionalFormatting sqref="CY2:CY89">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -26680,7 +26768,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CV2:CV88">
+  <conditionalFormatting sqref="CW2:CW89">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -26692,7 +26780,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CW2:CW88">
+  <conditionalFormatting sqref="CX2:CX89">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
@@ -26704,7 +26792,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CW2:CW88">
+  <conditionalFormatting sqref="CX2:CX89">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
@@ -26716,7 +26804,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CV2:CV88">
+  <conditionalFormatting sqref="CW2:CW89">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -26728,7 +26816,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CW2:CW88">
+  <conditionalFormatting sqref="CX2:CX89">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -26740,7 +26828,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CU2:CU79">
+  <conditionalFormatting sqref="CV2:CV79">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -26752,7 +26840,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CU2:CU67">
+  <conditionalFormatting sqref="CV2:CV67">
     <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
@@ -26764,7 +26852,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CU2:CU67">
+  <conditionalFormatting sqref="CV2:CV67">
     <cfRule type="colorScale" priority="127">
       <colorScale>
         <cfvo type="min"/>
@@ -26776,7 +26864,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CU2:CU67">
+  <conditionalFormatting sqref="CV2:CV67">
     <cfRule type="colorScale" priority="129">
       <colorScale>
         <cfvo type="min"/>
@@ -26788,7 +26876,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:CT83">
+  <conditionalFormatting sqref="B2:CU83">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -32185,7 +32273,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X285"/>
+  <dimension ref="A1:X288"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -46323,6 +46411,156 @@
       </c>
       <c r="P285" s="8"/>
     </row>
+    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A286" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B286" s="62">
+        <v>4</v>
+      </c>
+      <c r="C286" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E286" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F286" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="H286" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="I286" s="9">
+        <v>4</v>
+      </c>
+      <c r="J286" s="10">
+        <v>2</v>
+      </c>
+      <c r="K286" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L286" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M286" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N286" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="O286" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="P286" s="10" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A287" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B287" s="62">
+        <v>3</v>
+      </c>
+      <c r="C287" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D287" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E287" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F287" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="G287" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H287" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="I287" s="11">
+        <v>5</v>
+      </c>
+      <c r="J287" s="2">
+        <v>6</v>
+      </c>
+      <c r="K287" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L287" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M287" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N287" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="O287" s="61" t="s">
+        <v>343</v>
+      </c>
+      <c r="P287" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A288" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B288" s="62">
+        <v>4</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F288" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="G288" s="61" t="s">
+        <v>343</v>
+      </c>
+      <c r="H288" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I288" s="5">
+        <v>4</v>
+      </c>
+      <c r="J288" s="8">
+        <v>4</v>
+      </c>
+      <c r="K288" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L288" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M288" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="N288" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="O288" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="P288" s="8" t="s">
+        <v>390</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46330,7 +46568,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:CA88"/>
+  <dimension ref="A1:CB89"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
@@ -46340,10 +46578,10 @@
     <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="79" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="80" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -46581,8 +46819,11 @@
       <c r="CA1" s="1">
         <v>46148</v>
       </c>
-    </row>
-    <row r="2" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="CB1" s="1">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -46647,7 +46888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -46655,7 +46896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -46693,12 +46934,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -46706,7 +46947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>392</v>
       </c>
@@ -46726,7 +46967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>364</v>
       </c>
@@ -46743,7 +46984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -46751,7 +46992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>353</v>
       </c>
@@ -46759,17 +47000,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="12" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>396</v>
       </c>
@@ -46777,12 +47018,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="15" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>394</v>
       </c>
@@ -46790,7 +47031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>362</v>
       </c>
@@ -46798,12 +47039,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -46853,7 +47094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -46891,7 +47132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>378</v>
       </c>
@@ -46905,7 +47146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -46919,7 +47160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -46974,8 +47215,11 @@
       <c r="BU22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="CB22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>84</v>
       </c>
@@ -47070,7 +47314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>391</v>
       </c>
@@ -47078,7 +47322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -47139,8 +47383,11 @@
       <c r="BX25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="CB25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>375</v>
       </c>
@@ -47148,7 +47395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -47303,7 +47550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>342</v>
       </c>
@@ -47323,17 +47570,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="31" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -47347,7 +47594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -47451,7 +47698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>361</v>
       </c>
@@ -47468,7 +47715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>389</v>
       </c>
@@ -47476,7 +47723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>1</v>
       </c>
@@ -47615,16 +47862,22 @@
       <c r="BX35">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
+      <c r="CB35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>351</v>
       </c>
       <c r="Z36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="CB36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -47775,8 +48028,11 @@
       <c r="BZ37">
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="CB37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>393</v>
       </c>
@@ -47790,7 +48046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>381</v>
       </c>
@@ -47798,7 +48054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -47917,12 +48173,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -47930,7 +48186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -47938,7 +48194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>374</v>
       </c>
@@ -47946,7 +48202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -48076,8 +48332,11 @@
       <c r="BZ45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="CB45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>43</v>
       </c>
@@ -48085,7 +48344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>68</v>
       </c>
@@ -48105,7 +48364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -48116,7 +48375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>368</v>
       </c>
@@ -48130,7 +48389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>345</v>
       </c>
@@ -48147,7 +48406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>343</v>
       </c>
@@ -48164,7 +48423,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>344</v>
       </c>
@@ -48178,1462 +48437,1488 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>399</v>
+      </c>
+      <c r="CB53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>10</v>
       </c>
-      <c r="B53">
-        <v>2</v>
-      </c>
-      <c r="C53">
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54">
         <v>3</v>
       </c>
-      <c r="F53">
-        <v>2</v>
-      </c>
-      <c r="I53">
-        <v>2</v>
-      </c>
-      <c r="J53">
-        <v>2</v>
-      </c>
-      <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="L53">
-        <v>1</v>
-      </c>
-      <c r="M53">
-        <v>1</v>
-      </c>
-      <c r="O53">
-        <v>2</v>
-      </c>
-      <c r="R53">
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="I54">
+        <v>2</v>
+      </c>
+      <c r="J54">
+        <v>2</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="O54">
+        <v>2</v>
+      </c>
+      <c r="R54">
         <v>3</v>
       </c>
-      <c r="S53">
-        <v>1</v>
-      </c>
-      <c r="T53">
-        <v>1</v>
-      </c>
-      <c r="V53">
-        <v>1</v>
-      </c>
-      <c r="W53">
+      <c r="S54">
+        <v>1</v>
+      </c>
+      <c r="T54">
+        <v>1</v>
+      </c>
+      <c r="V54">
+        <v>1</v>
+      </c>
+      <c r="W54">
         <v>3</v>
       </c>
-      <c r="X53">
-        <v>1</v>
-      </c>
-      <c r="Y53">
-        <v>1</v>
-      </c>
-      <c r="Z53">
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
+        <v>1</v>
+      </c>
+      <c r="Z54">
         <v>1.5</v>
       </c>
-      <c r="AC53">
-        <v>1</v>
-      </c>
-      <c r="AD53">
-        <v>2</v>
-      </c>
-      <c r="AE53">
-        <v>1</v>
-      </c>
-      <c r="AF53">
-        <v>2</v>
-      </c>
-      <c r="AH53">
-        <v>2</v>
-      </c>
-      <c r="AL53">
+      <c r="AC54">
+        <v>1</v>
+      </c>
+      <c r="AD54">
+        <v>2</v>
+      </c>
+      <c r="AE54">
+        <v>1</v>
+      </c>
+      <c r="AF54">
+        <v>2</v>
+      </c>
+      <c r="AH54">
+        <v>2</v>
+      </c>
+      <c r="AL54">
         <v>3</v>
       </c>
-      <c r="AP53">
-        <v>2</v>
-      </c>
-      <c r="AQ53">
+      <c r="AP54">
+        <v>2</v>
+      </c>
+      <c r="AQ54">
         <v>4</v>
       </c>
-      <c r="AR53">
+      <c r="AR54">
         <v>3</v>
       </c>
-      <c r="AS53">
+      <c r="AS54">
         <v>0.5</v>
       </c>
-      <c r="AU53">
-        <v>2</v>
-      </c>
-      <c r="AV53">
-        <v>1</v>
-      </c>
-      <c r="BC53">
-        <v>1</v>
-      </c>
-      <c r="BD53">
-        <v>1</v>
-      </c>
-      <c r="BE53">
+      <c r="AU54">
+        <v>2</v>
+      </c>
+      <c r="AV54">
+        <v>1</v>
+      </c>
+      <c r="BC54">
+        <v>1</v>
+      </c>
+      <c r="BD54">
+        <v>1</v>
+      </c>
+      <c r="BE54">
         <v>7</v>
       </c>
-      <c r="BH53">
-        <v>1</v>
-      </c>
-      <c r="BI53">
-        <v>1</v>
-      </c>
-      <c r="BJ53">
+      <c r="BH54">
+        <v>1</v>
+      </c>
+      <c r="BI54">
+        <v>1</v>
+      </c>
+      <c r="BJ54">
         <v>3</v>
       </c>
-      <c r="BK53">
+      <c r="BK54">
         <v>3</v>
       </c>
-      <c r="BL53">
-        <v>1</v>
-      </c>
-      <c r="BM53">
-        <v>1</v>
-      </c>
-      <c r="BN53">
+      <c r="BL54">
+        <v>1</v>
+      </c>
+      <c r="BM54">
+        <v>1</v>
+      </c>
+      <c r="BN54">
         <v>4</v>
       </c>
-      <c r="BP53">
-        <v>1</v>
-      </c>
-      <c r="BQ53">
+      <c r="BP54">
+        <v>1</v>
+      </c>
+      <c r="BQ54">
         <v>3</v>
       </c>
-      <c r="BR53">
-        <v>1</v>
-      </c>
-      <c r="BT53">
-        <v>1</v>
-      </c>
-      <c r="BV53">
-        <v>1</v>
-      </c>
-      <c r="BW53">
-        <v>2</v>
-      </c>
-      <c r="BX53">
-        <v>2</v>
-      </c>
-      <c r="BZ53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+      <c r="BR54">
+        <v>1</v>
+      </c>
+      <c r="BT54">
+        <v>1</v>
+      </c>
+      <c r="BV54">
+        <v>1</v>
+      </c>
+      <c r="BW54">
+        <v>2</v>
+      </c>
+      <c r="BX54">
+        <v>2</v>
+      </c>
+      <c r="BZ54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>46</v>
       </c>
-      <c r="B54">
-        <v>1</v>
-      </c>
-      <c r="O54">
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="O55">
         <v>3</v>
       </c>
-      <c r="P54">
-        <v>1</v>
-      </c>
-      <c r="Q54">
-        <v>2</v>
-      </c>
-      <c r="AM54">
-        <v>1</v>
-      </c>
-      <c r="AN54">
-        <v>1</v>
-      </c>
-      <c r="AP54">
-        <v>1</v>
-      </c>
-      <c r="AS54">
-        <v>1</v>
-      </c>
-      <c r="AV54">
-        <v>1</v>
-      </c>
-      <c r="AX54">
-        <v>5</v>
-      </c>
-      <c r="AY54">
-        <v>1</v>
-      </c>
-      <c r="BA54">
-        <v>2</v>
-      </c>
-      <c r="BB54">
+      <c r="P55">
+        <v>1</v>
+      </c>
+      <c r="Q55">
+        <v>2</v>
+      </c>
+      <c r="AM55">
+        <v>1</v>
+      </c>
+      <c r="AN55">
+        <v>1</v>
+      </c>
+      <c r="AP55">
+        <v>1</v>
+      </c>
+      <c r="AS55">
+        <v>1</v>
+      </c>
+      <c r="AV55">
+        <v>1</v>
+      </c>
+      <c r="AX55">
+        <v>5</v>
+      </c>
+      <c r="AY55">
+        <v>1</v>
+      </c>
+      <c r="BA55">
+        <v>2</v>
+      </c>
+      <c r="BB55">
         <v>4</v>
       </c>
-      <c r="BE54">
+      <c r="BE55">
         <v>3</v>
       </c>
-      <c r="BF54">
-        <v>2</v>
-      </c>
-      <c r="BH54">
+      <c r="BF55">
+        <v>2</v>
+      </c>
+      <c r="BH55">
         <v>3</v>
       </c>
-      <c r="BK54">
-        <v>1</v>
-      </c>
-      <c r="BT54">
+      <c r="BK55">
+        <v>1</v>
+      </c>
+      <c r="BT55">
         <v>3</v>
       </c>
-      <c r="BZ54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="BZ55">
+        <v>1</v>
+      </c>
+      <c r="CB55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="56" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+    <row r="57" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>3</v>
       </c>
-      <c r="F56">
+      <c r="F57">
         <v>3</v>
       </c>
-      <c r="L56">
-        <v>1</v>
-      </c>
-      <c r="S56">
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="S57">
         <v>3</v>
       </c>
-      <c r="AH56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+      <c r="AH57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="58" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+    <row r="59" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>56</v>
       </c>
-      <c r="C58">
+      <c r="C59">
         <v>3</v>
       </c>
-      <c r="E58">
-        <v>2</v>
-      </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
-      <c r="G58">
-        <v>2</v>
-      </c>
-      <c r="I58">
-        <v>1</v>
-      </c>
-      <c r="J58">
-        <v>1</v>
-      </c>
-      <c r="K58">
-        <v>1</v>
-      </c>
-      <c r="L58">
-        <v>1</v>
-      </c>
-      <c r="M58">
-        <v>1</v>
-      </c>
-      <c r="P58">
-        <v>1</v>
-      </c>
-      <c r="R58">
-        <v>1</v>
-      </c>
-      <c r="S58">
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>2</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <v>1</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <v>1</v>
+      </c>
+      <c r="P59">
+        <v>1</v>
+      </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
+      <c r="S59">
         <v>4</v>
       </c>
-      <c r="T58">
-        <v>1</v>
-      </c>
-      <c r="V58">
-        <v>1</v>
-      </c>
-      <c r="W58">
-        <v>2</v>
-      </c>
-      <c r="Z58">
-        <v>2</v>
-      </c>
-      <c r="AA58">
-        <v>1</v>
-      </c>
-      <c r="AB58">
+      <c r="T59">
+        <v>1</v>
+      </c>
+      <c r="V59">
+        <v>1</v>
+      </c>
+      <c r="W59">
+        <v>2</v>
+      </c>
+      <c r="Z59">
+        <v>2</v>
+      </c>
+      <c r="AA59">
+        <v>1</v>
+      </c>
+      <c r="AB59">
         <v>4</v>
       </c>
-      <c r="AC58">
-        <v>1</v>
-      </c>
-      <c r="AD58">
-        <v>1</v>
-      </c>
-      <c r="AX58">
-        <v>1</v>
-      </c>
-      <c r="AY58">
-        <v>1</v>
-      </c>
-      <c r="AZ58">
-        <v>2</v>
-      </c>
-      <c r="BD58">
-        <v>1</v>
-      </c>
-      <c r="BF58">
-        <v>1</v>
-      </c>
-      <c r="BH58">
-        <v>1</v>
-      </c>
-      <c r="BI58">
-        <v>1</v>
-      </c>
-      <c r="BJ58">
-        <v>2</v>
-      </c>
-      <c r="BK58">
-        <v>1</v>
-      </c>
-      <c r="BL58">
-        <v>2</v>
-      </c>
-      <c r="BM58">
-        <v>2</v>
-      </c>
-      <c r="BN58">
-        <v>2</v>
-      </c>
-      <c r="BO58">
-        <v>1</v>
-      </c>
-      <c r="BP58">
-        <v>1</v>
-      </c>
-      <c r="BR58">
-        <v>1</v>
-      </c>
-      <c r="BS58">
-        <v>2</v>
-      </c>
-      <c r="BU58">
-        <v>2</v>
-      </c>
-      <c r="BV58">
-        <v>1</v>
-      </c>
-      <c r="BX58">
-        <v>1</v>
-      </c>
-      <c r="BY58">
-        <v>2</v>
-      </c>
-      <c r="BZ58">
-        <v>2</v>
-      </c>
-      <c r="CA58">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+      <c r="AC59">
+        <v>1</v>
+      </c>
+      <c r="AD59">
+        <v>1</v>
+      </c>
+      <c r="AX59">
+        <v>1</v>
+      </c>
+      <c r="AY59">
+        <v>1</v>
+      </c>
+      <c r="AZ59">
+        <v>2</v>
+      </c>
+      <c r="BD59">
+        <v>1</v>
+      </c>
+      <c r="BF59">
+        <v>1</v>
+      </c>
+      <c r="BH59">
+        <v>1</v>
+      </c>
+      <c r="BI59">
+        <v>1</v>
+      </c>
+      <c r="BJ59">
+        <v>2</v>
+      </c>
+      <c r="BK59">
+        <v>1</v>
+      </c>
+      <c r="BL59">
+        <v>2</v>
+      </c>
+      <c r="BM59">
+        <v>2</v>
+      </c>
+      <c r="BN59">
+        <v>2</v>
+      </c>
+      <c r="BO59">
+        <v>1</v>
+      </c>
+      <c r="BP59">
+        <v>1</v>
+      </c>
+      <c r="BR59">
+        <v>1</v>
+      </c>
+      <c r="BS59">
+        <v>2</v>
+      </c>
+      <c r="BU59">
+        <v>2</v>
+      </c>
+      <c r="BV59">
+        <v>1</v>
+      </c>
+      <c r="BX59">
+        <v>1</v>
+      </c>
+      <c r="BY59">
+        <v>2</v>
+      </c>
+      <c r="BZ59">
+        <v>2</v>
+      </c>
+      <c r="CA59">
+        <v>2</v>
+      </c>
+      <c r="CB59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>369</v>
       </c>
-      <c r="AN59">
+      <c r="AN60">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+    <row r="61" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>387</v>
       </c>
-      <c r="BN60">
+      <c r="BN61">
         <v>3</v>
       </c>
-      <c r="BO60">
-        <v>2</v>
-      </c>
-      <c r="BQ60">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="BO61">
+        <v>2</v>
+      </c>
+      <c r="BQ61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>60</v>
       </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
-      <c r="BF61">
-        <v>1</v>
-      </c>
-      <c r="BT61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="BF62">
+        <v>1</v>
+      </c>
+      <c r="BT62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>340</v>
       </c>
-      <c r="Q62">
-        <v>1</v>
-      </c>
-      <c r="U62">
-        <v>1</v>
-      </c>
-      <c r="W62">
-        <v>1</v>
-      </c>
-      <c r="X62">
+      <c r="Q63">
+        <v>1</v>
+      </c>
+      <c r="U63">
+        <v>1</v>
+      </c>
+      <c r="W63">
+        <v>1</v>
+      </c>
+      <c r="X63">
         <v>3</v>
       </c>
-      <c r="Y62">
-        <v>1</v>
-      </c>
-      <c r="Z62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="Y63">
+        <v>1</v>
+      </c>
+      <c r="Z63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="64" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+    <row r="65" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+    <row r="66" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>55</v>
       </c>
-      <c r="B65">
-        <v>2</v>
-      </c>
-      <c r="C65">
-        <v>1</v>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65">
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
         <v>3</v>
       </c>
-      <c r="G65">
-        <v>2</v>
-      </c>
-      <c r="H65">
+      <c r="G66">
+        <v>2</v>
+      </c>
+      <c r="H66">
         <v>3</v>
       </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-      <c r="K65">
-        <v>1</v>
-      </c>
-      <c r="M65">
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="M66">
         <v>3</v>
       </c>
-      <c r="N65">
+      <c r="N66">
         <v>4</v>
       </c>
-      <c r="X65">
+      <c r="X66">
         <v>6</v>
       </c>
-      <c r="Y65">
-        <v>5</v>
-      </c>
-      <c r="Z65">
-        <v>1</v>
-      </c>
-      <c r="AD65">
-        <v>2</v>
-      </c>
-      <c r="AG65">
+      <c r="Y66">
+        <v>5</v>
+      </c>
+      <c r="Z66">
+        <v>1</v>
+      </c>
+      <c r="AD66">
+        <v>2</v>
+      </c>
+      <c r="AG66">
         <v>3</v>
       </c>
-      <c r="AJ65">
-        <v>2</v>
-      </c>
-      <c r="AM65">
-        <v>2</v>
-      </c>
-      <c r="AO65">
+      <c r="AJ66">
+        <v>2</v>
+      </c>
+      <c r="AM66">
+        <v>2</v>
+      </c>
+      <c r="AO66">
         <v>3</v>
       </c>
-      <c r="AQ65">
-        <v>2</v>
-      </c>
-      <c r="AT65">
-        <v>1</v>
-      </c>
-      <c r="AU65">
+      <c r="AQ66">
+        <v>2</v>
+      </c>
+      <c r="AT66">
+        <v>1</v>
+      </c>
+      <c r="AU66">
         <v>4</v>
       </c>
-      <c r="AV65">
-        <v>2</v>
-      </c>
-      <c r="AX65">
-        <v>1</v>
-      </c>
-      <c r="AY65">
-        <v>2</v>
-      </c>
-      <c r="AZ65">
-        <v>1</v>
-      </c>
-      <c r="BA65">
+      <c r="AV66">
+        <v>2</v>
+      </c>
+      <c r="AX66">
+        <v>1</v>
+      </c>
+      <c r="AY66">
+        <v>2</v>
+      </c>
+      <c r="AZ66">
+        <v>1</v>
+      </c>
+      <c r="BA66">
         <v>4</v>
       </c>
-      <c r="BB65">
-        <v>2</v>
-      </c>
-      <c r="BH65">
-        <v>1</v>
-      </c>
-      <c r="BR65">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="BB66">
+        <v>2</v>
+      </c>
+      <c r="BH66">
+        <v>1</v>
+      </c>
+      <c r="BR66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+    <row r="68" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>81</v>
       </c>
-      <c r="G67">
+      <c r="G68">
         <v>3</v>
       </c>
-      <c r="K67">
-        <v>1</v>
-      </c>
-      <c r="BG67">
-        <v>2</v>
-      </c>
-      <c r="BN67">
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="BG68">
+        <v>2</v>
+      </c>
+      <c r="BN68">
         <v>4</v>
       </c>
-      <c r="BP67">
-        <v>1</v>
-      </c>
-      <c r="BR67">
-        <v>2</v>
-      </c>
-      <c r="BS67">
+      <c r="BP68">
+        <v>1</v>
+      </c>
+      <c r="BR68">
+        <v>2</v>
+      </c>
+      <c r="BS68">
         <v>3</v>
       </c>
-      <c r="BU67">
+      <c r="BU68">
         <v>3</v>
       </c>
-      <c r="BV67">
-        <v>2</v>
-      </c>
-      <c r="BW67">
-        <v>2</v>
-      </c>
-      <c r="BX67">
-        <v>2</v>
-      </c>
-      <c r="BY67">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="BV68">
+        <v>2</v>
+      </c>
+      <c r="BW68">
+        <v>2</v>
+      </c>
+      <c r="BX68">
+        <v>2</v>
+      </c>
+      <c r="BY68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>63</v>
       </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="AF68">
-        <v>2</v>
-      </c>
-      <c r="AQ68">
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="AF69">
+        <v>2</v>
+      </c>
+      <c r="AQ69">
         <v>3</v>
       </c>
-      <c r="BF68">
-        <v>1</v>
-      </c>
-      <c r="BM68">
-        <v>1</v>
-      </c>
-      <c r="BW68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="BF69">
+        <v>1</v>
+      </c>
+      <c r="BM69">
+        <v>1</v>
+      </c>
+      <c r="BW69">
+        <v>1</v>
+      </c>
+      <c r="CB69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+    <row r="71" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>22</v>
       </c>
-      <c r="Y70">
-        <v>1</v>
-      </c>
-      <c r="AB70">
-        <v>2</v>
-      </c>
-      <c r="AD70">
+      <c r="Y71">
+        <v>1</v>
+      </c>
+      <c r="AB71">
+        <v>2</v>
+      </c>
+      <c r="AD71">
         <v>3</v>
       </c>
-      <c r="AI70">
-        <v>1</v>
-      </c>
-      <c r="AR70">
+      <c r="AI71">
+        <v>1</v>
+      </c>
+      <c r="AR71">
         <v>4</v>
       </c>
-      <c r="AV70">
+      <c r="AV71">
         <v>3</v>
       </c>
-      <c r="BA70">
-        <v>2</v>
-      </c>
-      <c r="BB70">
-        <v>5</v>
-      </c>
-      <c r="BE70">
+      <c r="BA71">
+        <v>2</v>
+      </c>
+      <c r="BB71">
+        <v>5</v>
+      </c>
+      <c r="BE71">
         <v>6</v>
       </c>
-      <c r="BS70">
-        <v>1</v>
-      </c>
-      <c r="BT70">
-        <v>1</v>
-      </c>
-      <c r="BU70">
-        <v>2</v>
-      </c>
-      <c r="BV70">
+      <c r="BS71">
+        <v>1</v>
+      </c>
+      <c r="BT71">
+        <v>1</v>
+      </c>
+      <c r="BU71">
+        <v>2</v>
+      </c>
+      <c r="BV71">
         <v>3</v>
       </c>
-      <c r="BX70">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+      <c r="BX71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>376</v>
       </c>
-      <c r="AU71">
-        <v>1</v>
-      </c>
-      <c r="AV71">
-        <v>1</v>
-      </c>
-      <c r="AW71">
+      <c r="AU72">
+        <v>1</v>
+      </c>
+      <c r="AV72">
+        <v>1</v>
+      </c>
+      <c r="AW72">
         <v>3</v>
       </c>
-      <c r="AX71">
-        <v>1</v>
-      </c>
-      <c r="AZ71">
-        <v>1</v>
-      </c>
-      <c r="BC71">
-        <v>2</v>
-      </c>
-      <c r="BX71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+      <c r="AX72">
+        <v>1</v>
+      </c>
+      <c r="AZ72">
+        <v>1</v>
+      </c>
+      <c r="BC72">
+        <v>2</v>
+      </c>
+      <c r="BX72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>44</v>
       </c>
-      <c r="N72">
+      <c r="N73">
         <v>3</v>
       </c>
-      <c r="S72">
-        <v>2</v>
-      </c>
-      <c r="AG72">
-        <v>2</v>
-      </c>
-      <c r="AI72">
-        <v>1</v>
-      </c>
-      <c r="AP72">
-        <v>2</v>
-      </c>
-      <c r="AQ72">
-        <v>1</v>
-      </c>
-      <c r="AR72">
+      <c r="S73">
+        <v>2</v>
+      </c>
+      <c r="AG73">
+        <v>2</v>
+      </c>
+      <c r="AI73">
+        <v>1</v>
+      </c>
+      <c r="AP73">
+        <v>2</v>
+      </c>
+      <c r="AQ73">
+        <v>1</v>
+      </c>
+      <c r="AR73">
         <v>3</v>
       </c>
-      <c r="AW72">
-        <v>1</v>
-      </c>
-      <c r="BA72">
-        <v>1</v>
-      </c>
-      <c r="BE72">
-        <v>1</v>
-      </c>
-      <c r="BI72">
-        <v>2</v>
-      </c>
-      <c r="BL72">
-        <v>2</v>
-      </c>
-      <c r="BN72">
-        <v>2</v>
-      </c>
-      <c r="BO72">
-        <v>1</v>
-      </c>
-      <c r="BP72">
-        <v>1</v>
-      </c>
-      <c r="BR72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+      <c r="AW73">
+        <v>1</v>
+      </c>
+      <c r="BA73">
+        <v>1</v>
+      </c>
+      <c r="BE73">
+        <v>1</v>
+      </c>
+      <c r="BI73">
+        <v>2</v>
+      </c>
+      <c r="BL73">
+        <v>2</v>
+      </c>
+      <c r="BN73">
+        <v>2</v>
+      </c>
+      <c r="BO73">
+        <v>1</v>
+      </c>
+      <c r="BP73">
+        <v>1</v>
+      </c>
+      <c r="BR73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>379</v>
       </c>
-      <c r="BF73">
-        <v>1</v>
-      </c>
-      <c r="BG73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="BF74">
+        <v>1</v>
+      </c>
+      <c r="BG74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>8</v>
       </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="H74">
-        <v>1</v>
-      </c>
-      <c r="J74">
-        <v>2</v>
-      </c>
-      <c r="Q74">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="J75">
+        <v>2</v>
+      </c>
+      <c r="Q75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="76" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+    <row r="77" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>82</v>
       </c>
-      <c r="B76">
-        <v>2</v>
-      </c>
-      <c r="C76">
-        <v>2</v>
-      </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76">
-        <v>2</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="G76">
-        <v>2</v>
-      </c>
-      <c r="H76">
-        <v>2</v>
-      </c>
-      <c r="I76">
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+      <c r="H77">
+        <v>2</v>
+      </c>
+      <c r="I77">
         <v>3</v>
       </c>
-      <c r="J76">
+      <c r="J77">
         <v>4</v>
       </c>
-      <c r="L76">
+      <c r="L77">
         <v>4</v>
       </c>
-      <c r="M76">
-        <v>1</v>
-      </c>
-      <c r="N76">
-        <v>2</v>
-      </c>
-      <c r="O76">
-        <v>1</v>
-      </c>
-      <c r="P76">
-        <v>1</v>
-      </c>
-      <c r="Q76">
-        <v>1</v>
-      </c>
-      <c r="R76">
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77">
+        <v>2</v>
+      </c>
+      <c r="O77">
+        <v>1</v>
+      </c>
+      <c r="P77">
+        <v>1</v>
+      </c>
+      <c r="Q77">
+        <v>1</v>
+      </c>
+      <c r="R77">
         <v>3</v>
       </c>
-      <c r="S76">
+      <c r="S77">
         <v>3</v>
       </c>
-      <c r="U76">
+      <c r="U77">
         <v>3</v>
       </c>
-      <c r="V76">
-        <v>1</v>
-      </c>
-      <c r="W76">
+      <c r="V77">
+        <v>1</v>
+      </c>
+      <c r="W77">
         <v>3</v>
       </c>
-      <c r="AC76">
-        <v>1</v>
-      </c>
-      <c r="AF76">
-        <v>1</v>
-      </c>
-      <c r="AH76">
-        <v>2</v>
-      </c>
-      <c r="AI76">
+      <c r="AC77">
+        <v>1</v>
+      </c>
+      <c r="AF77">
+        <v>1</v>
+      </c>
+      <c r="AH77">
+        <v>2</v>
+      </c>
+      <c r="AI77">
         <v>3</v>
       </c>
-      <c r="AJ76">
-        <v>1</v>
-      </c>
-      <c r="AK76">
+      <c r="AJ77">
+        <v>1</v>
+      </c>
+      <c r="AK77">
         <v>4</v>
       </c>
-      <c r="AL76">
+      <c r="AL77">
         <v>3</v>
       </c>
-      <c r="AN76">
-        <v>1</v>
-      </c>
-      <c r="AP76">
-        <v>2</v>
-      </c>
-      <c r="AT76">
-        <v>2</v>
-      </c>
-      <c r="AU76">
+      <c r="AN77">
+        <v>1</v>
+      </c>
+      <c r="AP77">
+        <v>2</v>
+      </c>
+      <c r="AT77">
+        <v>2</v>
+      </c>
+      <c r="AU77">
         <v>3</v>
       </c>
-      <c r="AV76">
-        <v>1</v>
-      </c>
-      <c r="AW76">
-        <v>1</v>
-      </c>
-      <c r="AX76">
-        <v>1</v>
-      </c>
-      <c r="AY76">
-        <v>1</v>
-      </c>
-      <c r="AZ76">
-        <v>2</v>
-      </c>
-      <c r="BC76">
-        <v>2</v>
-      </c>
-      <c r="BD76">
-        <v>1</v>
-      </c>
-      <c r="BF76">
-        <v>2</v>
-      </c>
-      <c r="BH76">
+      <c r="AV77">
+        <v>1</v>
+      </c>
+      <c r="AW77">
+        <v>1</v>
+      </c>
+      <c r="AX77">
+        <v>1</v>
+      </c>
+      <c r="AY77">
+        <v>1</v>
+      </c>
+      <c r="AZ77">
+        <v>2</v>
+      </c>
+      <c r="BC77">
+        <v>2</v>
+      </c>
+      <c r="BD77">
+        <v>1</v>
+      </c>
+      <c r="BF77">
+        <v>2</v>
+      </c>
+      <c r="BH77">
         <v>3</v>
       </c>
-      <c r="BI76">
-        <v>1</v>
-      </c>
-      <c r="BJ76">
-        <v>2</v>
-      </c>
-      <c r="BK76">
+      <c r="BI77">
+        <v>1</v>
+      </c>
+      <c r="BJ77">
+        <v>2</v>
+      </c>
+      <c r="BK77">
         <v>3</v>
       </c>
-      <c r="BM76">
-        <v>2</v>
-      </c>
-      <c r="BN76">
+      <c r="BM77">
+        <v>2</v>
+      </c>
+      <c r="BN77">
         <v>3</v>
       </c>
-      <c r="BU76">
-        <v>1</v>
-      </c>
-      <c r="BV76">
+      <c r="BU77">
+        <v>1</v>
+      </c>
+      <c r="BV77">
         <v>3</v>
       </c>
-      <c r="BX76">
-        <v>2</v>
-      </c>
-      <c r="BY76">
-        <v>1</v>
-      </c>
-      <c r="BZ76">
-        <v>1</v>
-      </c>
-      <c r="CA76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+      <c r="BX77">
+        <v>2</v>
+      </c>
+      <c r="BY77">
+        <v>1</v>
+      </c>
+      <c r="BZ77">
+        <v>1</v>
+      </c>
+      <c r="CA77">
+        <v>1</v>
+      </c>
+      <c r="CB77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>49</v>
       </c>
-      <c r="G77">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+      <c r="G78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>390</v>
       </c>
-      <c r="BZ78">
-        <v>5</v>
-      </c>
-      <c r="CA78">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+      <c r="BZ79">
+        <v>5</v>
+      </c>
+      <c r="CA79">
+        <v>2</v>
+      </c>
+      <c r="CB79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>85</v>
       </c>
-      <c r="K79">
+      <c r="K80">
         <v>4</v>
       </c>
-      <c r="L79">
-        <v>2</v>
-      </c>
-      <c r="M79">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>5</v>
-      </c>
-      <c r="B80">
-        <v>1</v>
-      </c>
-      <c r="C80">
-        <v>2</v>
-      </c>
-      <c r="D80">
-        <v>2</v>
-      </c>
-      <c r="E80">
+      <c r="L80">
+        <v>2</v>
+      </c>
+      <c r="M80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>5</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+      <c r="E81">
         <v>3</v>
       </c>
-      <c r="F80">
-        <v>2</v>
-      </c>
-      <c r="G80">
+      <c r="F81">
+        <v>2</v>
+      </c>
+      <c r="G81">
         <v>3</v>
       </c>
-      <c r="H80">
-        <v>1</v>
-      </c>
-      <c r="M80">
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="M81">
         <v>4</v>
       </c>
-      <c r="N80">
+      <c r="N81">
         <v>6</v>
       </c>
-      <c r="P80">
-        <v>2</v>
-      </c>
-      <c r="Q80">
-        <v>1</v>
-      </c>
-      <c r="R80">
-        <v>2</v>
-      </c>
-      <c r="S80">
+      <c r="P81">
+        <v>2</v>
+      </c>
+      <c r="Q81">
+        <v>1</v>
+      </c>
+      <c r="R81">
+        <v>2</v>
+      </c>
+      <c r="S81">
         <v>3</v>
       </c>
-      <c r="V80">
-        <v>2</v>
-      </c>
-      <c r="W80">
-        <v>1</v>
-      </c>
-      <c r="X80">
-        <v>1</v>
-      </c>
-      <c r="Y80">
+      <c r="V81">
+        <v>2</v>
+      </c>
+      <c r="W81">
+        <v>1</v>
+      </c>
+      <c r="X81">
+        <v>1</v>
+      </c>
+      <c r="Y81">
         <v>4</v>
       </c>
-      <c r="Z80">
-        <v>5</v>
-      </c>
-      <c r="AA80">
-        <v>1</v>
-      </c>
-      <c r="AB80">
+      <c r="Z81">
+        <v>5</v>
+      </c>
+      <c r="AA81">
+        <v>1</v>
+      </c>
+      <c r="AB81">
         <v>3</v>
       </c>
-      <c r="AC80">
+      <c r="AC81">
         <v>4</v>
       </c>
-      <c r="AD80">
+      <c r="AD81">
         <v>3</v>
       </c>
-      <c r="AE80">
+      <c r="AE81">
         <v>3</v>
       </c>
-      <c r="AF80">
-        <v>2</v>
-      </c>
-      <c r="AG80">
-        <v>5</v>
-      </c>
-      <c r="AH80">
+      <c r="AF81">
+        <v>2</v>
+      </c>
+      <c r="AG81">
+        <v>5</v>
+      </c>
+      <c r="AH81">
         <v>7</v>
       </c>
-      <c r="AI80">
+      <c r="AI81">
         <v>3</v>
       </c>
-      <c r="AJ80">
-        <v>1</v>
-      </c>
-      <c r="AK80">
-        <v>1</v>
-      </c>
-      <c r="AL80">
+      <c r="AJ81">
+        <v>1</v>
+      </c>
+      <c r="AK81">
+        <v>1</v>
+      </c>
+      <c r="AL81">
         <v>6</v>
       </c>
-      <c r="AR80">
+      <c r="AR81">
         <v>3</v>
       </c>
-      <c r="AS80">
-        <v>2</v>
-      </c>
-      <c r="AV80">
-        <v>2</v>
-      </c>
-      <c r="AW80">
-        <v>1</v>
-      </c>
-      <c r="AX80">
+      <c r="AS81">
+        <v>2</v>
+      </c>
+      <c r="AV81">
+        <v>2</v>
+      </c>
+      <c r="AW81">
+        <v>1</v>
+      </c>
+      <c r="AX81">
         <v>4</v>
       </c>
-      <c r="AY80">
+      <c r="AY81">
         <v>3</v>
       </c>
-      <c r="AZ80">
+      <c r="AZ81">
         <v>4</v>
       </c>
-      <c r="BA80">
-        <v>5</v>
-      </c>
-      <c r="BB80">
+      <c r="BA81">
+        <v>5</v>
+      </c>
+      <c r="BB81">
         <v>6</v>
       </c>
-      <c r="BC80">
-        <v>2</v>
-      </c>
-      <c r="BD80">
-        <v>2</v>
-      </c>
-      <c r="BE80">
+      <c r="BC81">
+        <v>2</v>
+      </c>
+      <c r="BD81">
+        <v>2</v>
+      </c>
+      <c r="BE81">
         <v>7</v>
       </c>
-      <c r="BG80">
+      <c r="BG81">
         <v>4</v>
       </c>
-      <c r="BH80">
+      <c r="BH81">
         <v>3</v>
       </c>
-      <c r="BI80">
+      <c r="BI81">
         <v>4</v>
       </c>
-      <c r="BK80">
-        <v>1</v>
-      </c>
-      <c r="BL80">
+      <c r="BK81">
+        <v>1</v>
+      </c>
+      <c r="BL81">
         <v>8</v>
       </c>
-      <c r="BM80">
+      <c r="BM81">
         <v>4</v>
       </c>
-      <c r="BN80">
-        <v>5</v>
-      </c>
-      <c r="BO80">
+      <c r="BN81">
+        <v>5</v>
+      </c>
+      <c r="BO81">
         <v>3</v>
       </c>
-      <c r="BP80">
-        <v>1</v>
-      </c>
-      <c r="BQ80">
-        <v>1</v>
-      </c>
-      <c r="BR80">
+      <c r="BP81">
+        <v>1</v>
+      </c>
+      <c r="BQ81">
+        <v>1</v>
+      </c>
+      <c r="BR81">
         <v>3</v>
       </c>
-      <c r="BS80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="BS81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>45</v>
       </c>
-      <c r="K81">
-        <v>1</v>
-      </c>
-      <c r="BJ81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="BJ82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>367</v>
       </c>
-      <c r="B82">
-        <v>1</v>
-      </c>
-      <c r="D82">
-        <v>1</v>
-      </c>
-      <c r="E82">
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
         <v>3</v>
       </c>
-      <c r="O82">
-        <v>2</v>
-      </c>
-      <c r="P82">
-        <v>2</v>
-      </c>
-      <c r="Q82">
-        <v>1</v>
-      </c>
-      <c r="R82">
-        <v>1</v>
-      </c>
-      <c r="AD82">
-        <v>1</v>
-      </c>
-      <c r="AE82">
-        <v>1</v>
-      </c>
-      <c r="AG82">
-        <v>1</v>
-      </c>
-      <c r="AH82">
-        <v>2</v>
-      </c>
-      <c r="AL82">
+      <c r="O83">
+        <v>2</v>
+      </c>
+      <c r="P83">
+        <v>2</v>
+      </c>
+      <c r="Q83">
+        <v>1</v>
+      </c>
+      <c r="R83">
+        <v>1</v>
+      </c>
+      <c r="AD83">
+        <v>1</v>
+      </c>
+      <c r="AE83">
+        <v>1</v>
+      </c>
+      <c r="AG83">
+        <v>1</v>
+      </c>
+      <c r="AH83">
+        <v>2</v>
+      </c>
+      <c r="AL83">
         <v>3</v>
       </c>
-      <c r="AM82">
-        <v>2</v>
-      </c>
-      <c r="AN82">
-        <v>1</v>
-      </c>
-      <c r="AO82">
-        <v>1</v>
-      </c>
-      <c r="AR82">
-        <v>1</v>
-      </c>
-      <c r="AS82">
-        <v>1</v>
-      </c>
-      <c r="AT82">
-        <v>1</v>
-      </c>
-      <c r="AV82">
-        <v>1</v>
-      </c>
-      <c r="AW82">
-        <v>2</v>
-      </c>
-      <c r="BD82">
-        <v>1</v>
-      </c>
-      <c r="BF82">
-        <v>1</v>
-      </c>
-      <c r="BI82">
-        <v>1</v>
-      </c>
-      <c r="BU82">
-        <v>2</v>
-      </c>
-      <c r="BW82">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="AM83">
+        <v>2</v>
+      </c>
+      <c r="AN83">
+        <v>1</v>
+      </c>
+      <c r="AO83">
+        <v>1</v>
+      </c>
+      <c r="AR83">
+        <v>1</v>
+      </c>
+      <c r="AS83">
+        <v>1</v>
+      </c>
+      <c r="AT83">
+        <v>1</v>
+      </c>
+      <c r="AV83">
+        <v>1</v>
+      </c>
+      <c r="AW83">
+        <v>2</v>
+      </c>
+      <c r="BD83">
+        <v>1</v>
+      </c>
+      <c r="BF83">
+        <v>1</v>
+      </c>
+      <c r="BI83">
+        <v>1</v>
+      </c>
+      <c r="BU83">
+        <v>2</v>
+      </c>
+      <c r="BW83">
+        <v>2</v>
+      </c>
+      <c r="CB83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>352</v>
       </c>
-      <c r="Z83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="Z84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="85" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+    <row r="86" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>17</v>
       </c>
-      <c r="F85">
-        <v>2</v>
-      </c>
-      <c r="J85">
-        <v>1</v>
-      </c>
-      <c r="K85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+      <c r="K86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>86</v>
       </c>
-      <c r="K86">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="K87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>16</v>
       </c>
-      <c r="C87">
+      <c r="C88">
         <v>4</v>
       </c>
-      <c r="D87">
+      <c r="D88">
         <v>3</v>
       </c>
-      <c r="F87">
-        <v>2</v>
-      </c>
-      <c r="G87">
-        <v>5</v>
-      </c>
-      <c r="H87">
+      <c r="F88">
+        <v>2</v>
+      </c>
+      <c r="G88">
+        <v>5</v>
+      </c>
+      <c r="H88">
         <v>3</v>
       </c>
-      <c r="I87">
-        <v>2</v>
-      </c>
-      <c r="J87">
-        <v>5</v>
-      </c>
-      <c r="K87">
+      <c r="I88">
+        <v>2</v>
+      </c>
+      <c r="J88">
+        <v>5</v>
+      </c>
+      <c r="K88">
         <v>3</v>
       </c>
-      <c r="L87">
-        <v>2</v>
-      </c>
-      <c r="M87">
+      <c r="L88">
+        <v>2</v>
+      </c>
+      <c r="M88">
         <v>3</v>
       </c>
-      <c r="O87">
-        <v>5</v>
-      </c>
-      <c r="P87">
-        <v>5</v>
-      </c>
-      <c r="Q87">
+      <c r="O88">
+        <v>5</v>
+      </c>
+      <c r="P88">
+        <v>5</v>
+      </c>
+      <c r="Q88">
         <v>3</v>
       </c>
-      <c r="R87">
-        <v>2</v>
-      </c>
-      <c r="S87">
+      <c r="R88">
+        <v>2</v>
+      </c>
+      <c r="S88">
         <v>3</v>
       </c>
-      <c r="T87">
-        <v>1</v>
-      </c>
-      <c r="U87">
-        <v>1</v>
-      </c>
-      <c r="V87">
+      <c r="T88">
+        <v>1</v>
+      </c>
+      <c r="U88">
+        <v>1</v>
+      </c>
+      <c r="V88">
         <v>3</v>
       </c>
-      <c r="W87">
+      <c r="W88">
         <v>3</v>
       </c>
-      <c r="X87">
-        <v>5</v>
-      </c>
-      <c r="Y87">
+      <c r="X88">
+        <v>5</v>
+      </c>
+      <c r="Y88">
         <v>4</v>
       </c>
-      <c r="Z87">
-        <v>1</v>
-      </c>
-      <c r="AA87">
+      <c r="Z88">
+        <v>1</v>
+      </c>
+      <c r="AA88">
         <v>3</v>
       </c>
-      <c r="AC87">
-        <v>1</v>
-      </c>
-      <c r="AE87">
+      <c r="AC88">
+        <v>1</v>
+      </c>
+      <c r="AE88">
         <v>4</v>
       </c>
-      <c r="AF87">
-        <v>2</v>
-      </c>
-      <c r="AG87">
+      <c r="AF88">
+        <v>2</v>
+      </c>
+      <c r="AG88">
         <v>3</v>
       </c>
-      <c r="AH87">
-        <v>2</v>
-      </c>
-      <c r="AI87">
-        <v>2</v>
-      </c>
-      <c r="AJ87">
+      <c r="AH88">
+        <v>2</v>
+      </c>
+      <c r="AI88">
+        <v>2</v>
+      </c>
+      <c r="AJ88">
         <v>7</v>
       </c>
-      <c r="AK87">
+      <c r="AK88">
         <v>3</v>
       </c>
-      <c r="AL87">
-        <v>5</v>
-      </c>
-      <c r="AM87">
-        <v>1</v>
-      </c>
-      <c r="AN87">
+      <c r="AL88">
+        <v>5</v>
+      </c>
+      <c r="AM88">
+        <v>1</v>
+      </c>
+      <c r="AN88">
         <v>4</v>
       </c>
-      <c r="AO87">
+      <c r="AO88">
         <v>3</v>
       </c>
-      <c r="AP87">
+      <c r="AP88">
         <v>6</v>
       </c>
-      <c r="AQ87">
+      <c r="AQ88">
         <v>4</v>
       </c>
-      <c r="AR87">
-        <v>5</v>
-      </c>
-      <c r="AS87">
+      <c r="AR88">
+        <v>5</v>
+      </c>
+      <c r="AS88">
         <v>3</v>
       </c>
-      <c r="AT87">
-        <v>2</v>
-      </c>
-      <c r="AU87">
-        <v>2</v>
-      </c>
-      <c r="AW87">
+      <c r="AT88">
+        <v>2</v>
+      </c>
+      <c r="AU88">
+        <v>2</v>
+      </c>
+      <c r="AW88">
         <v>3</v>
       </c>
-      <c r="AY87">
-        <v>1</v>
-      </c>
-      <c r="AZ87">
+      <c r="AY88">
+        <v>1</v>
+      </c>
+      <c r="AZ88">
         <v>3</v>
       </c>
-      <c r="BB87">
+      <c r="BB88">
         <v>4</v>
       </c>
-      <c r="BC87">
+      <c r="BC88">
         <v>4</v>
       </c>
-      <c r="BD87">
+      <c r="BD88">
         <v>3</v>
       </c>
-      <c r="BF87">
-        <v>2</v>
-      </c>
-      <c r="BG87">
+      <c r="BF88">
+        <v>2</v>
+      </c>
+      <c r="BG88">
         <v>4</v>
       </c>
-      <c r="BH87">
-        <v>5</v>
-      </c>
-      <c r="BJ87">
+      <c r="BH88">
+        <v>5</v>
+      </c>
+      <c r="BJ88">
         <v>4</v>
       </c>
-      <c r="BK87">
-        <v>2</v>
-      </c>
-      <c r="BL87">
+      <c r="BK88">
+        <v>2</v>
+      </c>
+      <c r="BL88">
         <v>4</v>
       </c>
-      <c r="BM87">
-        <v>1</v>
-      </c>
-      <c r="BN87">
-        <v>2</v>
-      </c>
-      <c r="BO87">
+      <c r="BM88">
+        <v>1</v>
+      </c>
+      <c r="BN88">
+        <v>2</v>
+      </c>
+      <c r="BO88">
         <v>3</v>
       </c>
-      <c r="BS87">
+      <c r="BS88">
         <v>3</v>
       </c>
-      <c r="BT87">
+      <c r="BT88">
         <v>4</v>
       </c>
-      <c r="BU87">
+      <c r="BU88">
         <v>4</v>
       </c>
-      <c r="BV87">
+      <c r="BV88">
         <v>3</v>
       </c>
-      <c r="BX87">
-        <v>5</v>
-      </c>
-      <c r="BY87">
-        <v>2</v>
-      </c>
-      <c r="BZ87">
+      <c r="BX88">
+        <v>5</v>
+      </c>
+      <c r="BY88">
+        <v>2</v>
+      </c>
+      <c r="BZ88">
         <v>3</v>
       </c>
-      <c r="CA87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:79" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+      <c r="CA88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:80" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB88" xr:uid="{130C2564-D265-4C41-A3E0-02A62EDAC91D}">
-    <sortState ref="A2:AB88">
-      <sortCondition ref="A1:A88"/>
+  <autoFilter ref="A1:AB89" xr:uid="{130C2564-D265-4C41-A3E0-02A62EDAC91D}">
+    <sortState ref="A2:AB89">
+      <sortCondition ref="A1:A89"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="14_{CCCF2471-6899-4BEE-B69A-61EDE0174783}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{99989A48-6A86-496D-98FD-95C8B4F5248B}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="14_{CCCF2471-6899-4BEE-B69A-61EDE0174783}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{1FF58352-21FD-4CDD-AB1B-3891BF8C526A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7890" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notas" sheetId="1" r:id="rId1"/>
@@ -47684,7 +47684,9 @@
       <c r="A295" s="1">
         <v>46176</v>
       </c>
-      <c r="B295" s="62"/>
+      <c r="B295" s="62">
+        <v>1</v>
+      </c>
       <c r="C295" s="8" t="s">
         <v>1</v>
       </c>
@@ -47703,8 +47705,12 @@
       <c r="H295" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="I295" s="9"/>
-      <c r="J295" s="10"/>
+      <c r="I295" s="9">
+        <v>0</v>
+      </c>
+      <c r="J295" s="10">
+        <v>0</v>
+      </c>
       <c r="K295" s="10" t="s">
         <v>16</v>
       </c>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="14_{CCCF2471-6899-4BEE-B69A-61EDE0174783}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{1FF58352-21FD-4CDD-AB1B-3891BF8C526A}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="14_{CCCF2471-6899-4BEE-B69A-61EDE0174783}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{1830A4E2-765F-47E2-8AC0-FDF695CE3D23}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7890" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7890" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notas" sheetId="1" r:id="rId1"/>
@@ -49903,9 +49903,6 @@
       <c r="Z39">
         <v>1</v>
       </c>
-      <c r="CB39">
-        <v>4</v>
-      </c>
     </row>
     <row r="40" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A40" t="s">

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="14_{CCCF2471-6899-4BEE-B69A-61EDE0174783}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{1830A4E2-765F-47E2-8AC0-FDF695CE3D23}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="14_{CCCF2471-6899-4BEE-B69A-61EDE0174783}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{06CF8E01-0038-44E7-893A-E6758B390BD1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7890" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,17 +23,17 @@
     <sheet name="artilharia total" sheetId="3" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'extrato 2024'!$A$1:$C$187</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$DJ$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$DK$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9735" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9767" uniqueCount="407">
   <si>
     <t>Jogador</t>
   </si>
@@ -1251,6 +1251,9 @@
   </si>
   <si>
     <t>Thiago C.</t>
+  </si>
+  <si>
+    <t>Vitor</t>
   </si>
 </sst>
 </file>
@@ -3519,7 +3522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DJ95"/>
+  <dimension ref="A1:DK96"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
@@ -3544,10 +3547,10 @@
     <col min="50" max="58" width="9.54296875" customWidth="1"/>
     <col min="59" max="65" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
-    <col min="67" max="108" width="11" customWidth="1"/>
+    <col min="67" max="109" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3869,27 +3872,30 @@
       <c r="DC1" s="1">
         <v>46218</v>
       </c>
-      <c r="DD1" s="1"/>
-      <c r="DE1" t="s">
+      <c r="DD1" s="1">
+        <v>46225</v>
+      </c>
+      <c r="DE1" s="1"/>
+      <c r="DF1" t="s">
         <v>57</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>58</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DH1" t="s">
         <v>59</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DI1" t="s">
         <v>62</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DJ1" t="s">
         <v>400</v>
       </c>
-      <c r="DJ1" t="s">
+      <c r="DK1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4205,31 +4211,34 @@
       <c r="DC2">
         <v>6.5</v>
       </c>
-      <c r="DE2">
-        <f t="shared" ref="DE2:DE33" si="0">COUNT(B2:CW2)</f>
+      <c r="DD2">
+        <v>6.5</v>
+      </c>
+      <c r="DF2">
+        <f t="shared" ref="DF2:DF33" si="0">COUNT(B2:CW2)</f>
         <v>94</v>
       </c>
-      <c r="DF2" s="18">
-        <f t="shared" ref="DF2:DF33" si="1">AVERAGE(B2:CW2)</f>
+      <c r="DG2" s="18">
+        <f t="shared" ref="DG2:DG33" si="1">AVERAGE(B2:CW2)</f>
         <v>6.0106382978723403</v>
       </c>
-      <c r="DG2">
-        <f t="shared" ref="DG2:DG33" si="2">IF(DE2&gt;1,_xlfn.STDEV.S(B2:CW2),"")</f>
+      <c r="DH2">
+        <f t="shared" ref="DH2:DH33" si="2">IF(DF2&gt;1,_xlfn.STDEV.S(B2:CW2),"")</f>
         <v>1.1662335372744763</v>
       </c>
-      <c r="DH2">
-        <v>1</v>
-      </c>
       <c r="DI2">
-        <f t="shared" ref="DI2:DI33" si="3">COUNT(CX2:DA2)</f>
+        <v>1</v>
+      </c>
+      <c r="DJ2">
+        <f t="shared" ref="DJ2:DJ33" si="3">COUNT(CX2:DA2)</f>
         <v>3</v>
       </c>
-      <c r="DJ2">
-        <f t="shared" ref="DJ2:DJ33" si="4">IF(DH2=0,DI2,0)</f>
+      <c r="DK2">
+        <f t="shared" ref="DK2:DK33" si="4">IF(DI2=0,DJ2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4536,31 +4545,34 @@
       <c r="DC3">
         <v>5</v>
       </c>
-      <c r="DE3">
+      <c r="DD3">
+        <v>5.5</v>
+      </c>
+      <c r="DF3">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="DF3" s="18">
+      <c r="DG3" s="18">
         <f t="shared" si="1"/>
         <v>5.6590909090909092</v>
       </c>
-      <c r="DG3">
+      <c r="DH3">
         <f t="shared" si="2"/>
         <v>0.97540281848434929</v>
       </c>
-      <c r="DH3">
-        <v>1</v>
-      </c>
       <c r="DI3">
+        <v>1</v>
+      </c>
+      <c r="DJ3">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DJ3">
+      <c r="DK3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -4858,31 +4870,31 @@
       <c r="DA4">
         <v>6</v>
       </c>
-      <c r="DE4">
+      <c r="DF4">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="DF4" s="18">
+      <c r="DG4" s="18">
         <f t="shared" si="1"/>
         <v>6.5576923076923075</v>
       </c>
-      <c r="DG4">
+      <c r="DH4">
         <f t="shared" si="2"/>
         <v>0.9327405829087726</v>
       </c>
-      <c r="DH4">
-        <v>1</v>
-      </c>
       <c r="DI4">
+        <v>1</v>
+      </c>
+      <c r="DJ4">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DJ4">
+      <c r="DK4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -5180,31 +5192,34 @@
       <c r="DC5">
         <v>6.5</v>
       </c>
-      <c r="DE5">
+      <c r="DD5">
+        <v>5.5</v>
+      </c>
+      <c r="DF5">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="DF5" s="18">
+      <c r="DG5" s="18">
         <f t="shared" si="1"/>
         <v>6.625</v>
       </c>
-      <c r="DG5">
+      <c r="DH5">
         <f t="shared" si="2"/>
         <v>0.99037030111637203</v>
       </c>
-      <c r="DH5">
-        <v>1</v>
-      </c>
       <c r="DI5">
+        <v>1</v>
+      </c>
+      <c r="DJ5">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DJ5">
+      <c r="DK5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5490,31 +5505,31 @@
       <c r="DC6">
         <v>7.5</v>
       </c>
-      <c r="DE6">
+      <c r="DF6">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="DF6" s="18">
+      <c r="DG6" s="18">
         <f t="shared" si="1"/>
         <v>7.2430555555555554</v>
       </c>
-      <c r="DG6">
+      <c r="DH6">
         <f t="shared" si="2"/>
         <v>1.1444694187225961</v>
       </c>
-      <c r="DH6">
-        <v>1</v>
-      </c>
       <c r="DI6">
+        <v>1</v>
+      </c>
+      <c r="DJ6">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DJ6">
+      <c r="DK6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -5776,31 +5791,34 @@
       <c r="CI7">
         <v>5.5</v>
       </c>
-      <c r="DE7">
+      <c r="DD7">
+        <v>5.5</v>
+      </c>
+      <c r="DF7">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="DF7" s="18">
+      <c r="DG7" s="18">
         <f t="shared" si="1"/>
         <v>5.708333333333333</v>
       </c>
-      <c r="DG7">
+      <c r="DH7">
         <f t="shared" si="2"/>
         <v>0.94477808706744304</v>
       </c>
-      <c r="DH7">
+      <c r="DI7">
         <v>0</v>
       </c>
-      <c r="DI7">
+      <c r="DJ7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ7">
+      <c r="DK7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -6089,31 +6107,34 @@
       <c r="DC8">
         <v>6.5</v>
       </c>
-      <c r="DE8">
+      <c r="DD8">
+        <v>4.5</v>
+      </c>
+      <c r="DF8">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="DF8" s="18">
+      <c r="DG8" s="18">
         <f t="shared" si="1"/>
         <v>5.7642857142857142</v>
       </c>
-      <c r="DG8">
+      <c r="DH8">
         <f t="shared" si="2"/>
         <v>1.2986097040916795</v>
       </c>
-      <c r="DH8">
-        <v>1</v>
-      </c>
       <c r="DI8">
+        <v>1</v>
+      </c>
+      <c r="DJ8">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="DJ8">
+      <c r="DK8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -6378,31 +6399,34 @@
       <c r="DC9">
         <v>5.5</v>
       </c>
-      <c r="DE9">
+      <c r="DD9">
+        <v>5.5</v>
+      </c>
+      <c r="DF9">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="DF9" s="18">
+      <c r="DG9" s="18">
         <f t="shared" si="1"/>
         <v>5.95</v>
       </c>
-      <c r="DG9">
+      <c r="DH9">
         <f t="shared" si="2"/>
         <v>0.94466465179333525</v>
       </c>
-      <c r="DH9">
+      <c r="DI9">
         <v>0</v>
       </c>
-      <c r="DI9">
+      <c r="DJ9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ9">
+      <c r="DK9">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -6652,31 +6676,31 @@
       <c r="CE10">
         <v>5</v>
       </c>
-      <c r="DE10">
+      <c r="DF10">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="DF10" s="18">
+      <c r="DG10" s="18">
         <f t="shared" si="1"/>
         <v>6.4191176470588234</v>
       </c>
-      <c r="DG10">
+      <c r="DH10">
         <f t="shared" si="2"/>
         <v>1.1769245721961776</v>
       </c>
-      <c r="DH10">
+      <c r="DI10">
         <v>0</v>
       </c>
-      <c r="DI10">
+      <c r="DJ10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ10">
+      <c r="DK10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6971,31 +6995,34 @@
       <c r="DC11">
         <v>6</v>
       </c>
-      <c r="DE11">
+      <c r="DD11">
+        <v>6.5</v>
+      </c>
+      <c r="DF11">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="DF11" s="18">
+      <c r="DG11" s="18">
         <f t="shared" si="1"/>
         <v>6.6492537313432836</v>
       </c>
-      <c r="DG11">
+      <c r="DH11">
         <f t="shared" si="2"/>
         <v>0.94152892009339217</v>
       </c>
-      <c r="DH11">
-        <v>1</v>
-      </c>
       <c r="DI11">
+        <v>1</v>
+      </c>
+      <c r="DJ11">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="DJ11">
+      <c r="DK11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -7296,31 +7323,31 @@
       <c r="DC12">
         <v>5</v>
       </c>
-      <c r="DE12">
+      <c r="DF12">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="DF12" s="18">
+      <c r="DG12" s="18">
         <f t="shared" si="1"/>
         <v>5.5390625</v>
       </c>
-      <c r="DG12">
+      <c r="DH12">
         <f t="shared" si="2"/>
         <v>0.96075651202415768</v>
       </c>
-      <c r="DH12">
-        <v>1</v>
-      </c>
       <c r="DI12">
+        <v>1</v>
+      </c>
+      <c r="DJ12">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DJ12">
+      <c r="DK12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -7630,31 +7657,34 @@
       <c r="DC13">
         <v>5</v>
       </c>
-      <c r="DE13">
+      <c r="DD13">
+        <v>6.5</v>
+      </c>
+      <c r="DF13">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="DF13" s="18">
+      <c r="DG13" s="18">
         <f t="shared" si="1"/>
         <v>6.3174603174603172</v>
       </c>
-      <c r="DG13">
+      <c r="DH13">
         <f t="shared" si="2"/>
         <v>1.0862096991357946</v>
       </c>
-      <c r="DH13">
-        <v>1</v>
-      </c>
       <c r="DI13">
+        <v>1</v>
+      </c>
+      <c r="DJ13">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DJ13">
+      <c r="DK13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>367</v>
       </c>
@@ -7922,31 +7952,31 @@
       <c r="DB14">
         <v>6</v>
       </c>
-      <c r="DE14">
+      <c r="DF14">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="DF14" s="18">
+      <c r="DG14" s="18">
         <f t="shared" si="1"/>
         <v>6.2661290322580649</v>
       </c>
-      <c r="DG14">
+      <c r="DH14">
         <f t="shared" si="2"/>
         <v>1.0586015440095373</v>
       </c>
-      <c r="DH14">
+      <c r="DI14">
         <v>0</v>
       </c>
-      <c r="DI14">
+      <c r="DJ14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ14">
+      <c r="DK14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -8262,31 +8292,34 @@
       <c r="DC15">
         <v>7</v>
       </c>
-      <c r="DE15">
+      <c r="DD15">
+        <v>6</v>
+      </c>
+      <c r="DF15">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="DF15" s="18">
+      <c r="DG15" s="18">
         <f t="shared" si="1"/>
         <v>6.0535714285714288</v>
       </c>
-      <c r="DG15">
+      <c r="DH15">
         <f t="shared" si="2"/>
         <v>0.85108792104614583</v>
       </c>
-      <c r="DH15">
-        <v>1</v>
-      </c>
       <c r="DI15">
+        <v>1</v>
+      </c>
+      <c r="DJ15">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DJ15">
+      <c r="DK15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -8533,31 +8566,31 @@
       <c r="CW16">
         <v>6</v>
       </c>
-      <c r="DE16">
+      <c r="DF16">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="DF16" s="18">
+      <c r="DG16" s="18">
         <f t="shared" si="1"/>
         <v>5.6981132075471699</v>
       </c>
-      <c r="DG16">
+      <c r="DH16">
         <f t="shared" si="2"/>
         <v>0.83975513052632311</v>
       </c>
-      <c r="DH16">
+      <c r="DI16">
         <v>0</v>
       </c>
-      <c r="DI16">
+      <c r="DJ16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ16">
+      <c r="DK16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -8843,31 +8876,34 @@
       <c r="CV17">
         <v>6</v>
       </c>
-      <c r="DE17">
+      <c r="DD17">
+        <v>5.5</v>
+      </c>
+      <c r="DF17">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="DF17" s="18">
+      <c r="DG17" s="18">
         <f t="shared" si="1"/>
         <v>5.7244897959183669</v>
       </c>
-      <c r="DG17">
+      <c r="DH17">
         <f t="shared" si="2"/>
         <v>0.89594703439175261</v>
       </c>
-      <c r="DH17">
-        <v>1</v>
-      </c>
       <c r="DI17">
+        <v>1</v>
+      </c>
+      <c r="DJ17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ17">
+      <c r="DK17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -9117,31 +9153,31 @@
       <c r="CF18">
         <v>5.5</v>
       </c>
-      <c r="DE18">
+      <c r="DF18">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="DF18" s="18">
+      <c r="DG18" s="18">
         <f t="shared" si="1"/>
         <v>4.4255319148936172</v>
       </c>
-      <c r="DG18">
+      <c r="DH18">
         <f t="shared" si="2"/>
         <v>1.3391217246854428</v>
       </c>
-      <c r="DH18">
+      <c r="DI18">
         <v>0</v>
       </c>
-      <c r="DI18">
+      <c r="DJ18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ18">
+      <c r="DK18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -9424,31 +9460,31 @@
       <c r="DC19">
         <v>5.5</v>
       </c>
-      <c r="DE19">
+      <c r="DF19">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="DF19" s="18">
+      <c r="DG19" s="18">
         <f t="shared" si="1"/>
         <v>5.0113636363636367</v>
       </c>
-      <c r="DG19">
+      <c r="DH19">
         <f t="shared" si="2"/>
         <v>1.0481913346311222</v>
       </c>
-      <c r="DH19">
+      <c r="DI19">
         <v>0</v>
       </c>
-      <c r="DI19">
+      <c r="DJ19">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DJ19">
+      <c r="DK19">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -9731,31 +9767,31 @@
       <c r="DB20">
         <v>6</v>
       </c>
-      <c r="DE20">
+      <c r="DF20">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="DF20" s="18">
+      <c r="DG20" s="18">
         <f t="shared" si="1"/>
         <v>5.75</v>
       </c>
-      <c r="DG20">
+      <c r="DH20">
         <f t="shared" si="2"/>
         <v>0.85249292433809187</v>
       </c>
-      <c r="DH20">
-        <v>1</v>
-      </c>
       <c r="DI20">
+        <v>1</v>
+      </c>
+      <c r="DJ20">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DJ20">
+      <c r="DK20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -10041,31 +10077,31 @@
       <c r="CZ21">
         <v>5.5</v>
       </c>
-      <c r="DE21">
+      <c r="DF21">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="DF21" s="18">
+      <c r="DG21" s="18">
         <f t="shared" si="1"/>
         <v>5.2441860465116283</v>
       </c>
-      <c r="DG21">
+      <c r="DH21">
         <f t="shared" si="2"/>
         <v>1.1920974563830549</v>
       </c>
-      <c r="DH21">
-        <v>1</v>
-      </c>
       <c r="DI21">
+        <v>1</v>
+      </c>
+      <c r="DJ21">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="DJ21">
+      <c r="DK21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -10309,31 +10345,31 @@
       <c r="CK22">
         <v>5.5</v>
       </c>
-      <c r="DE22">
+      <c r="DF22">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="DF22" s="18">
+      <c r="DG22" s="18">
         <f t="shared" si="1"/>
         <v>6.1410256410256414</v>
       </c>
-      <c r="DG22">
+      <c r="DH22">
         <f t="shared" si="2"/>
         <v>1.0879042984027267</v>
       </c>
-      <c r="DH22">
+      <c r="DI22">
         <v>0</v>
       </c>
-      <c r="DI22">
+      <c r="DJ22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ22">
+      <c r="DK22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -10616,31 +10652,31 @@
       <c r="DB23">
         <v>5.5</v>
       </c>
-      <c r="DE23">
+      <c r="DF23">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="DF23" s="18">
+      <c r="DG23" s="18">
         <f t="shared" si="1"/>
         <v>6.3181818181818183</v>
       </c>
-      <c r="DG23">
+      <c r="DH23">
         <f t="shared" si="2"/>
         <v>0.9828067413836219</v>
       </c>
-      <c r="DH23">
+      <c r="DI23">
         <v>0</v>
       </c>
-      <c r="DI23">
+      <c r="DJ23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ23">
+      <c r="DK23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -10902,31 +10938,34 @@
       <c r="DC24">
         <v>5</v>
       </c>
-      <c r="DE24">
+      <c r="DD24">
+        <v>6</v>
+      </c>
+      <c r="DF24">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="DF24" s="18">
+      <c r="DG24" s="18">
         <f t="shared" si="1"/>
         <v>5.4827586206896548</v>
       </c>
-      <c r="DG24">
+      <c r="DH24">
         <f t="shared" si="2"/>
         <v>0.68768190607350477</v>
       </c>
-      <c r="DH24">
+      <c r="DI24">
         <v>0</v>
       </c>
-      <c r="DI24">
+      <c r="DJ24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ24">
+      <c r="DK24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -11197,31 +11236,31 @@
       <c r="DB25">
         <v>6</v>
       </c>
-      <c r="DE25">
+      <c r="DF25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="DF25" s="18">
+      <c r="DG25" s="18">
         <f t="shared" si="1"/>
         <v>6.6086956521739131</v>
       </c>
-      <c r="DG25">
+      <c r="DH25">
         <f t="shared" si="2"/>
         <v>0.67346663781731952</v>
       </c>
-      <c r="DH25">
-        <v>1</v>
-      </c>
       <c r="DI25">
+        <v>1</v>
+      </c>
+      <c r="DJ25">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="DJ25">
+      <c r="DK25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>81</v>
       </c>
@@ -11507,31 +11546,31 @@
       <c r="CT26">
         <v>5</v>
       </c>
-      <c r="DE26">
+      <c r="DF26">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="DF26" s="18">
+      <c r="DG26" s="18">
         <f t="shared" si="1"/>
         <v>6.2368421052631575</v>
       </c>
-      <c r="DG26">
+      <c r="DH26">
         <f t="shared" si="2"/>
         <v>0.63176166947476609</v>
       </c>
-      <c r="DH26">
+      <c r="DI26">
         <v>0</v>
       </c>
-      <c r="DI26">
+      <c r="DJ26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ26">
+      <c r="DK26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -11772,31 +11811,31 @@
       <c r="CB27" t="s">
         <v>26</v>
       </c>
-      <c r="DE27">
+      <c r="DF27">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="DF27" s="18">
+      <c r="DG27" s="18">
         <f t="shared" si="1"/>
         <v>5.7894736842105265</v>
       </c>
-      <c r="DG27">
+      <c r="DH27">
         <f t="shared" si="2"/>
         <v>1.3674366679797902</v>
       </c>
-      <c r="DH27">
+      <c r="DI27">
         <v>0</v>
       </c>
-      <c r="DI27">
+      <c r="DJ27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ27">
+      <c r="DK27">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -12055,31 +12094,31 @@
       <c r="CW28">
         <v>5.5</v>
       </c>
-      <c r="DE28">
+      <c r="DF28">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="DF28" s="18">
+      <c r="DG28" s="18">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="DG28">
+      <c r="DH28">
         <f t="shared" si="2"/>
         <v>0.85749292571254421</v>
       </c>
-      <c r="DH28">
+      <c r="DI28">
         <v>0</v>
       </c>
-      <c r="DI28">
+      <c r="DJ28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ28">
+      <c r="DK28">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>346</v>
       </c>
@@ -12320,31 +12359,31 @@
       <c r="CB29" t="s">
         <v>26</v>
       </c>
-      <c r="DE29">
+      <c r="DF29">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="DF29" s="18">
+      <c r="DG29" s="18">
         <f t="shared" si="1"/>
         <v>5.9444444444444446</v>
       </c>
-      <c r="DG29">
+      <c r="DH29">
         <f t="shared" si="2"/>
         <v>0.72535769855270305</v>
       </c>
-      <c r="DH29">
+      <c r="DI29">
         <v>0</v>
       </c>
-      <c r="DI29">
+      <c r="DJ29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ29">
+      <c r="DK29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -12585,31 +12624,34 @@
       <c r="CB30" t="s">
         <v>26</v>
       </c>
-      <c r="DE30">
+      <c r="DD30">
+        <v>5.5</v>
+      </c>
+      <c r="DF30">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="DF30" s="18">
+      <c r="DG30" s="18">
         <f t="shared" si="1"/>
         <v>5.3235294117647056</v>
       </c>
-      <c r="DG30">
+      <c r="DH30">
         <f t="shared" si="2"/>
         <v>1.3456083251473603</v>
       </c>
-      <c r="DH30">
+      <c r="DI30">
         <v>0</v>
       </c>
-      <c r="DI30">
+      <c r="DJ30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ30">
+      <c r="DK30">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -12856,31 +12898,31 @@
       <c r="DA31">
         <v>5.5</v>
       </c>
-      <c r="DE31">
+      <c r="DF31">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="DF31" s="18">
+      <c r="DG31" s="18">
         <f t="shared" si="1"/>
         <v>4.53125</v>
       </c>
-      <c r="DG31">
+      <c r="DH31">
         <f t="shared" si="2"/>
         <v>1.5434674167816653</v>
       </c>
-      <c r="DH31">
+      <c r="DI31">
         <v>0</v>
       </c>
-      <c r="DI31">
+      <c r="DJ31">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="DJ31">
+      <c r="DK31">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>343</v>
       </c>
@@ -13151,31 +13193,31 @@
       <c r="DC32">
         <v>5.5</v>
       </c>
-      <c r="DE32">
+      <c r="DF32">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="DF32" s="18">
+      <c r="DG32" s="18">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="DG32">
+      <c r="DH32">
         <f t="shared" si="2"/>
         <v>1.5383974345619102</v>
       </c>
-      <c r="DH32">
-        <v>1</v>
-      </c>
       <c r="DI32">
+        <v>1</v>
+      </c>
+      <c r="DJ32">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="DJ32">
+      <c r="DK32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -13416,31 +13458,31 @@
       <c r="CB33">
         <v>5.5</v>
       </c>
-      <c r="DE33">
+      <c r="DF33">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="DF33" s="18">
+      <c r="DG33" s="18">
         <f t="shared" si="1"/>
         <v>3.8666666666666667</v>
       </c>
-      <c r="DG33">
+      <c r="DH33">
         <f t="shared" si="2"/>
         <v>2.3563490726929555</v>
       </c>
-      <c r="DH33">
+      <c r="DI33">
         <v>0</v>
       </c>
-      <c r="DI33">
+      <c r="DJ33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DJ33">
+      <c r="DK33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -13690,31 +13732,31 @@
       <c r="DB34">
         <v>6.5</v>
       </c>
-      <c r="DE34">
-        <f t="shared" ref="DE34:DE65" si="5">COUNT(B34:CW34)</f>
+      <c r="DF34">
+        <f t="shared" ref="DF34:DF65" si="5">COUNT(B34:CW34)</f>
         <v>14</v>
       </c>
-      <c r="DF34" s="18">
-        <f t="shared" ref="DF34:DF65" si="6">AVERAGE(B34:CW34)</f>
+      <c r="DG34" s="18">
+        <f t="shared" ref="DG34:DG65" si="6">AVERAGE(B34:CW34)</f>
         <v>7.25</v>
       </c>
-      <c r="DG34">
-        <f t="shared" ref="DG34:DG65" si="7">IF(DE34&gt;1,_xlfn.STDEV.S(B34:CW34),"")</f>
+      <c r="DH34">
+        <f t="shared" ref="DH34:DH65" si="7">IF(DF34&gt;1,_xlfn.STDEV.S(B34:CW34),"")</f>
         <v>1.5032017112202156</v>
       </c>
-      <c r="DH34">
+      <c r="DI34">
         <v>0</v>
       </c>
-      <c r="DI34">
-        <f t="shared" ref="DI34:DI65" si="8">COUNT(CX34:DA34)</f>
-        <v>1</v>
-      </c>
       <c r="DJ34">
-        <f t="shared" ref="DJ34:DJ65" si="9">IF(DH34=0,DI34,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.35">
+        <f t="shared" ref="DJ34:DJ65" si="8">COUNT(CX34:DA34)</f>
+        <v>1</v>
+      </c>
+      <c r="DK34">
+        <f t="shared" ref="DK34:DK65" si="9">IF(DI34=0,DJ34,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>376</v>
       </c>
@@ -13991,31 +14033,34 @@
       <c r="DC35">
         <v>5.5</v>
       </c>
-      <c r="DE35">
+      <c r="DD35">
+        <v>7</v>
+      </c>
+      <c r="DF35">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="DF35" s="18">
+      <c r="DG35" s="18">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="DG35">
+      <c r="DH35">
         <f t="shared" si="7"/>
         <v>0.58834840541455213</v>
       </c>
-      <c r="DH35">
-        <v>1</v>
-      </c>
       <c r="DI35">
+        <v>1</v>
+      </c>
+      <c r="DJ35">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="DJ35">
+      <c r="DK35">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>378</v>
       </c>
@@ -14283,31 +14328,31 @@
       <c r="CQ36">
         <v>5.5</v>
       </c>
-      <c r="DE36">
+      <c r="DF36">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="DF36" s="18">
+      <c r="DG36" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="DG36">
+      <c r="DH36">
         <f t="shared" si="7"/>
         <v>0.3988620176087328</v>
       </c>
-      <c r="DH36">
+      <c r="DI36">
         <v>0</v>
       </c>
-      <c r="DI36">
+      <c r="DJ36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ36">
+      <c r="DK36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -14548,31 +14593,31 @@
       <c r="CB37" t="s">
         <v>26</v>
       </c>
-      <c r="DE37">
+      <c r="DF37">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="DF37" s="18">
+      <c r="DG37" s="18">
         <f t="shared" si="6"/>
         <v>4.6818181818181817</v>
       </c>
-      <c r="DG37">
+      <c r="DH37">
         <f t="shared" si="7"/>
         <v>0.81463879335344846</v>
       </c>
-      <c r="DH37">
+      <c r="DI37">
         <v>0</v>
       </c>
-      <c r="DI37">
+      <c r="DJ37">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ37">
+      <c r="DK37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -14816,31 +14861,31 @@
       <c r="CC38">
         <v>6</v>
       </c>
-      <c r="DE38">
+      <c r="DF38">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="DF38" s="18">
+      <c r="DG38" s="18">
         <f t="shared" si="6"/>
         <v>8.4499999999999993</v>
       </c>
-      <c r="DG38">
+      <c r="DH38">
         <f t="shared" si="7"/>
         <v>1.1890705987824657</v>
       </c>
-      <c r="DH38">
+      <c r="DI38">
         <v>0</v>
       </c>
-      <c r="DI38">
+      <c r="DJ38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ38">
+      <c r="DK38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>340</v>
       </c>
@@ -15084,31 +15129,31 @@
       <c r="CL39">
         <v>6</v>
       </c>
-      <c r="DE39">
+      <c r="DF39">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="DF39" s="18">
+      <c r="DG39" s="18">
         <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
-      <c r="DG39">
+      <c r="DH39">
         <f t="shared" si="7"/>
         <v>0.53452248382484879</v>
       </c>
-      <c r="DH39">
+      <c r="DI39">
         <v>0</v>
       </c>
-      <c r="DI39">
+      <c r="DJ39">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ39">
+      <c r="DK39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>401</v>
       </c>
@@ -15148,31 +15193,34 @@
       <c r="DC40">
         <v>7</v>
       </c>
-      <c r="DE40">
+      <c r="DD40">
+        <v>9</v>
+      </c>
+      <c r="DF40">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="DF40" s="18">
+      <c r="DG40" s="18">
         <f t="shared" si="6"/>
         <v>6.6428571428571432</v>
       </c>
-      <c r="DG40">
+      <c r="DH40">
         <f t="shared" si="7"/>
         <v>1.1801936887041631</v>
       </c>
-      <c r="DH40">
-        <v>1</v>
-      </c>
       <c r="DI40">
+        <v>1</v>
+      </c>
+      <c r="DJ40">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="DJ40">
+      <c r="DK40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>345</v>
       </c>
@@ -15431,31 +15479,31 @@
       <c r="CO41">
         <v>4.5</v>
       </c>
-      <c r="DE41">
+      <c r="DF41">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="DF41" s="18">
+      <c r="DG41" s="18">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="DG41">
+      <c r="DH41">
         <f t="shared" si="7"/>
         <v>1.2583057392117916</v>
       </c>
-      <c r="DH41">
+      <c r="DI41">
         <v>0</v>
       </c>
-      <c r="DI41">
+      <c r="DJ41">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ41">
+      <c r="DK41">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>392</v>
       </c>
@@ -15480,31 +15528,31 @@
       <c r="CY42">
         <v>4.5</v>
       </c>
-      <c r="DE42">
+      <c r="DF42">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="DF42" s="18">
+      <c r="DG42" s="18">
         <f t="shared" si="6"/>
         <v>5.833333333333333</v>
       </c>
-      <c r="DG42">
+      <c r="DH42">
         <f t="shared" si="7"/>
         <v>1.2516655570345734</v>
       </c>
-      <c r="DH42">
+      <c r="DI42">
         <v>0</v>
       </c>
-      <c r="DI42">
+      <c r="DJ42">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="DJ42">
+      <c r="DK42">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>398</v>
       </c>
@@ -15532,31 +15580,34 @@
       <c r="DC43">
         <v>5.5</v>
       </c>
-      <c r="DE43">
+      <c r="DD43">
+        <v>6.5</v>
+      </c>
+      <c r="DF43">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DF43" s="18">
+      <c r="DG43" s="18">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="DG43">
+      <c r="DH43">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DH43">
+      <c r="DI43">
         <v>0</v>
       </c>
-      <c r="DI43">
+      <c r="DJ43">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="DJ43">
+      <c r="DK43">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>342</v>
       </c>
@@ -15806,31 +15857,31 @@
       <c r="CU44">
         <v>5.5</v>
       </c>
-      <c r="DE44">
+      <c r="DF44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DF44" s="18">
+      <c r="DG44" s="18">
         <f t="shared" si="6"/>
         <v>5.6</v>
       </c>
-      <c r="DG44">
+      <c r="DH44">
         <f t="shared" si="7"/>
         <v>1.0839741694339387</v>
       </c>
-      <c r="DH44">
+      <c r="DI44">
         <v>0</v>
       </c>
-      <c r="DI44">
+      <c r="DJ44">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ44">
+      <c r="DK44">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>390</v>
       </c>
@@ -16086,31 +16137,31 @@
       <c r="CU45">
         <v>6</v>
       </c>
-      <c r="DE45">
+      <c r="DF45">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DF45" s="18">
+      <c r="DG45" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="DG45">
+      <c r="DH45">
         <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
-      <c r="DH45">
+      <c r="DI45">
         <v>0</v>
       </c>
-      <c r="DI45">
+      <c r="DJ45">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ45">
+      <c r="DK45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -16354,31 +16405,31 @@
       <c r="CH46">
         <v>6.5</v>
       </c>
-      <c r="DE46">
+      <c r="DF46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DF46" s="18">
+      <c r="DG46" s="18">
         <f t="shared" si="6"/>
         <v>7.8</v>
       </c>
-      <c r="DG46">
+      <c r="DH46">
         <f t="shared" si="7"/>
         <v>1.1510864433221351</v>
       </c>
-      <c r="DH46">
+      <c r="DI46">
         <v>0</v>
       </c>
-      <c r="DI46">
+      <c r="DJ46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ46">
+      <c r="DK46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -16622,31 +16673,31 @@
       <c r="CM47">
         <v>5.5</v>
       </c>
-      <c r="DE47">
+      <c r="DF47">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DF47" s="18">
+      <c r="DG47" s="18">
         <f t="shared" si="6"/>
         <v>3.8</v>
       </c>
-      <c r="DG47">
+      <c r="DH47">
         <f t="shared" si="7"/>
         <v>1.0368220676663857</v>
       </c>
-      <c r="DH47">
+      <c r="DI47">
         <v>0</v>
       </c>
-      <c r="DI47">
+      <c r="DJ47">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ47">
+      <c r="DK47">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>364</v>
       </c>
@@ -16896,31 +16947,31 @@
       <c r="CN48">
         <v>6</v>
       </c>
-      <c r="DE48">
+      <c r="DF48">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DF48" s="18">
+      <c r="DG48" s="18">
         <f t="shared" si="6"/>
         <v>6.2</v>
       </c>
-      <c r="DG48">
+      <c r="DH48">
         <f t="shared" si="7"/>
         <v>0.44721359549995793</v>
       </c>
-      <c r="DH48">
+      <c r="DI48">
         <v>0</v>
       </c>
-      <c r="DI48">
+      <c r="DJ48">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ48">
+      <c r="DK48">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -17164,31 +17215,31 @@
       <c r="CY49">
         <v>5.5</v>
       </c>
-      <c r="DE49">
+      <c r="DF49">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DF49" s="18">
+      <c r="DG49" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="DG49">
+      <c r="DH49">
         <f t="shared" si="7"/>
         <v>1.0408329997330663</v>
       </c>
-      <c r="DH49">
+      <c r="DI49">
         <v>0</v>
       </c>
-      <c r="DI49">
+      <c r="DJ49">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="DJ49">
+      <c r="DK49">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -17435,31 +17486,31 @@
       <c r="CV50">
         <v>5.5</v>
       </c>
-      <c r="DE50">
+      <c r="DF50">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DF50" s="18">
+      <c r="DG50" s="18">
         <f t="shared" si="6"/>
         <v>5.625</v>
       </c>
-      <c r="DG50">
+      <c r="DH50">
         <f t="shared" si="7"/>
         <v>0.25</v>
       </c>
-      <c r="DH50">
+      <c r="DI50">
         <v>0</v>
       </c>
-      <c r="DI50">
+      <c r="DJ50">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ50">
+      <c r="DK50">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -17700,31 +17751,31 @@
       <c r="CB51" t="s">
         <v>26</v>
       </c>
-      <c r="DE51">
+      <c r="DF51">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DF51" s="18">
+      <c r="DG51" s="18">
         <f t="shared" si="6"/>
         <v>5.625</v>
       </c>
-      <c r="DG51">
+      <c r="DH51">
         <f t="shared" si="7"/>
         <v>0.9464847243000456</v>
       </c>
-      <c r="DH51">
+      <c r="DI51">
         <v>0</v>
       </c>
-      <c r="DI51">
+      <c r="DJ51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ51">
+      <c r="DK51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>21</v>
       </c>
@@ -17965,31 +18016,31 @@
       <c r="CB52" t="s">
         <v>26</v>
       </c>
-      <c r="DE52">
+      <c r="DF52">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DF52" s="18">
+      <c r="DG52" s="18">
         <f t="shared" si="6"/>
         <v>1.375</v>
       </c>
-      <c r="DG52">
+      <c r="DH52">
         <f t="shared" si="7"/>
         <v>1.8874586088176875</v>
       </c>
-      <c r="DH52">
+      <c r="DI52">
         <v>0</v>
       </c>
-      <c r="DI52">
+      <c r="DJ52">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ52">
+      <c r="DK52">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>344</v>
       </c>
@@ -18230,31 +18281,31 @@
       <c r="CB53" t="s">
         <v>26</v>
       </c>
-      <c r="DE53">
+      <c r="DF53">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DF53" s="18">
+      <c r="DG53" s="18">
         <f t="shared" si="6"/>
         <v>4.625</v>
       </c>
-      <c r="DG53">
+      <c r="DH53">
         <f t="shared" si="7"/>
         <v>1.4361406616345072</v>
       </c>
-      <c r="DH53">
+      <c r="DI53">
         <v>0</v>
       </c>
-      <c r="DI53">
+      <c r="DJ53">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ53">
+      <c r="DK53">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>361</v>
       </c>
@@ -18495,31 +18546,31 @@
       <c r="CB54" t="s">
         <v>26</v>
       </c>
-      <c r="DE54">
+      <c r="DF54">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DF54" s="18">
+      <c r="DG54" s="18">
         <f t="shared" si="6"/>
         <v>6.25</v>
       </c>
-      <c r="DG54">
+      <c r="DH54">
         <f t="shared" si="7"/>
         <v>0.8660254037844386</v>
       </c>
-      <c r="DH54">
+      <c r="DI54">
         <v>0</v>
       </c>
-      <c r="DI54">
+      <c r="DJ54">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ54">
+      <c r="DK54">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>43</v>
       </c>
@@ -18760,31 +18811,31 @@
       <c r="CB55" t="s">
         <v>26</v>
       </c>
-      <c r="DE55">
+      <c r="DF55">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DF55" s="18">
+      <c r="DG55" s="18">
         <f t="shared" si="6"/>
         <v>2.875</v>
       </c>
-      <c r="DG55">
+      <c r="DH55">
         <f t="shared" si="7"/>
         <v>2.7801378862687129</v>
       </c>
-      <c r="DH55">
+      <c r="DI55">
         <v>0</v>
       </c>
-      <c r="DI55">
+      <c r="DJ55">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ55">
+      <c r="DK55">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -19025,31 +19076,31 @@
       <c r="CB56" t="s">
         <v>26</v>
       </c>
-      <c r="DE56">
+      <c r="DF56">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DF56" s="18">
+      <c r="DG56" s="18">
         <f t="shared" si="6"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="DG56">
+      <c r="DH56">
         <f t="shared" si="7"/>
         <v>1.4433756729740652</v>
       </c>
-      <c r="DH56">
+      <c r="DI56">
         <v>0</v>
       </c>
-      <c r="DI56">
+      <c r="DJ56">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ56">
+      <c r="DK56">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -19290,31 +19341,31 @@
       <c r="CB57" t="s">
         <v>26</v>
       </c>
-      <c r="DE57">
+      <c r="DF57">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DF57" s="18">
+      <c r="DG57" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="DG57">
+      <c r="DH57">
         <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
-      <c r="DH57">
+      <c r="DI57">
         <v>0</v>
       </c>
-      <c r="DI57">
+      <c r="DJ57">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ57">
+      <c r="DK57">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>49</v>
       </c>
@@ -19555,31 +19606,31 @@
       <c r="CB58" t="s">
         <v>26</v>
       </c>
-      <c r="DE58">
+      <c r="DF58">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DF58" s="18">
+      <c r="DG58" s="18">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="DG58">
+      <c r="DH58">
         <f t="shared" si="7"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="DH58">
+      <c r="DI58">
         <v>0</v>
       </c>
-      <c r="DI58">
+      <c r="DJ58">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ58">
+      <c r="DK58">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>368</v>
       </c>
@@ -19823,31 +19874,31 @@
       <c r="CG59">
         <v>6</v>
       </c>
-      <c r="DE59">
+      <c r="DF59">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DF59" s="18">
+      <c r="DG59" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="DG59">
+      <c r="DH59">
         <f t="shared" si="7"/>
         <v>2.179449471770337</v>
       </c>
-      <c r="DH59">
+      <c r="DI59">
         <v>0</v>
       </c>
-      <c r="DI59">
+      <c r="DJ59">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ59">
+      <c r="DK59">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>53</v>
       </c>
@@ -20091,31 +20142,31 @@
       <c r="CS60">
         <v>5.5</v>
       </c>
-      <c r="DE60">
+      <c r="DF60">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DF60" s="18">
+      <c r="DG60" s="18">
         <f t="shared" si="6"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="DG60">
+      <c r="DH60">
         <f t="shared" si="7"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="DH60">
+      <c r="DI60">
         <v>0</v>
       </c>
-      <c r="DI60">
+      <c r="DJ60">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ60">
+      <c r="DK60">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>387</v>
       </c>
@@ -20365,31 +20416,31 @@
       <c r="CJ61">
         <v>7</v>
       </c>
-      <c r="DE61">
+      <c r="DF61">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DF61" s="18">
+      <c r="DG61" s="18">
         <f t="shared" si="6"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="DG61">
+      <c r="DH61">
         <f t="shared" si="7"/>
         <v>0.57735026918962584</v>
       </c>
-      <c r="DH61">
+      <c r="DI61">
         <v>0</v>
       </c>
-      <c r="DI61">
+      <c r="DJ61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ61">
+      <c r="DK61">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>362</v>
       </c>
@@ -20633,31 +20684,31 @@
       <c r="CD62">
         <v>5.5</v>
       </c>
-      <c r="DE62">
+      <c r="DF62">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="DF62" s="18">
+      <c r="DG62" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="DG62">
+      <c r="DH62">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DH62">
+      <c r="DI62">
         <v>0</v>
       </c>
-      <c r="DI62">
+      <c r="DJ62">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ62">
+      <c r="DK62">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>339</v>
       </c>
@@ -20898,31 +20949,31 @@
       <c r="CB63" t="s">
         <v>26</v>
       </c>
-      <c r="DE63">
+      <c r="DF63">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="DF63" s="18">
+      <c r="DG63" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="DG63">
+      <c r="DH63">
         <f t="shared" si="7"/>
         <v>2.4748737341529163</v>
       </c>
-      <c r="DH63">
+      <c r="DI63">
         <v>0</v>
       </c>
-      <c r="DI63">
+      <c r="DJ63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ63">
+      <c r="DK63">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>369</v>
       </c>
@@ -21163,31 +21214,31 @@
       <c r="CB64" t="s">
         <v>26</v>
       </c>
-      <c r="DE64">
+      <c r="DF64">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="DF64" s="18">
+      <c r="DG64" s="18">
         <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
-      <c r="DG64">
+      <c r="DH64">
         <f t="shared" si="7"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="DH64">
+      <c r="DI64">
         <v>0</v>
       </c>
-      <c r="DI64">
+      <c r="DJ64">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ64">
+      <c r="DK64">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>379</v>
       </c>
@@ -21428,31 +21479,31 @@
       <c r="CB65" t="s">
         <v>26</v>
       </c>
-      <c r="DE65">
+      <c r="DF65">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="DF65" s="18">
+      <c r="DG65" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="DG65">
+      <c r="DH65">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DH65">
+      <c r="DI65">
         <v>0</v>
       </c>
-      <c r="DI65">
+      <c r="DJ65">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DJ65">
+      <c r="DK65">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>388</v>
       </c>
@@ -21696,31 +21747,31 @@
       <c r="CH66">
         <v>5</v>
       </c>
-      <c r="DE66">
-        <f t="shared" ref="DE66:DE91" si="10">COUNT(B66:CW66)</f>
-        <v>2</v>
-      </c>
-      <c r="DF66" s="18">
-        <f t="shared" ref="DF66:DF91" si="11">AVERAGE(B66:CW66)</f>
+      <c r="DF66">
+        <f t="shared" ref="DF66:DF91" si="10">COUNT(B66:CW66)</f>
+        <v>2</v>
+      </c>
+      <c r="DG66" s="18">
+        <f t="shared" ref="DG66:DG91" si="11">AVERAGE(B66:CW66)</f>
         <v>4.25</v>
       </c>
-      <c r="DG66">
-        <f t="shared" ref="DG66:DG91" si="12">IF(DE66&gt;1,_xlfn.STDEV.S(B66:CW66),"")</f>
+      <c r="DH66">
+        <f t="shared" ref="DH66:DH91" si="12">IF(DF66&gt;1,_xlfn.STDEV.S(B66:CW66),"")</f>
         <v>1.0606601717798212</v>
       </c>
-      <c r="DH66">
+      <c r="DI66">
         <v>0</v>
       </c>
-      <c r="DI66">
-        <f t="shared" ref="DI66:DI91" si="13">COUNT(CX66:DA66)</f>
+      <c r="DJ66">
+        <f t="shared" ref="DJ66:DJ91" si="13">COUNT(CX66:DA66)</f>
         <v>0</v>
       </c>
-      <c r="DJ66">
-        <f t="shared" ref="DJ66:DJ91" si="14">IF(DH66=0,DI66,0)</f>
+      <c r="DK66">
+        <f t="shared" ref="DK66:DK91" si="14">IF(DI66=0,DJ66,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>396</v>
       </c>
@@ -21730,62 +21781,62 @@
       <c r="DA67">
         <v>7</v>
       </c>
-      <c r="DE67">
+      <c r="DF67">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF67" s="18">
+      <c r="DG67" s="18">
         <f t="shared" si="11"/>
         <v>7.5</v>
       </c>
-      <c r="DG67" t="str">
+      <c r="DH67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH67">
+      <c r="DI67">
         <v>0</v>
       </c>
-      <c r="DI67">
+      <c r="DJ67">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="DJ67">
+      <c r="DK67">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>397</v>
       </c>
       <c r="CV68">
         <v>6</v>
       </c>
-      <c r="DE68">
+      <c r="DF68">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF68" s="18">
+      <c r="DG68" s="18">
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
-      <c r="DG68" t="str">
+      <c r="DH68" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH68">
+      <c r="DI68">
         <v>0</v>
       </c>
-      <c r="DI68">
+      <c r="DJ68">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ68">
+      <c r="DK68">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>86</v>
       </c>
@@ -22026,31 +22077,31 @@
       <c r="CB69" t="s">
         <v>26</v>
       </c>
-      <c r="DE69">
+      <c r="DF69">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF69" s="18">
+      <c r="DG69" s="18">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="DG69" t="str">
+      <c r="DH69" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH69">
+      <c r="DI69">
         <v>0</v>
       </c>
-      <c r="DI69">
+      <c r="DJ69">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ69">
+      <c r="DK69">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -22291,31 +22342,31 @@
       <c r="CB70" t="s">
         <v>26</v>
       </c>
-      <c r="DE70">
+      <c r="DF70">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF70" s="18">
+      <c r="DG70" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="DG70" t="str">
+      <c r="DH70" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH70">
+      <c r="DI70">
         <v>0</v>
       </c>
-      <c r="DI70">
+      <c r="DJ70">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ70">
+      <c r="DK70">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>353</v>
       </c>
@@ -22556,31 +22607,31 @@
       <c r="CB71" t="s">
         <v>26</v>
       </c>
-      <c r="DE71">
+      <c r="DF71">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF71" s="18">
+      <c r="DG71" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="DG71" t="str">
+      <c r="DH71" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH71">
+      <c r="DI71">
         <v>0</v>
       </c>
-      <c r="DI71">
+      <c r="DJ71">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ71">
+      <c r="DK71">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>80</v>
       </c>
@@ -22821,31 +22872,31 @@
       <c r="CB72" t="s">
         <v>26</v>
       </c>
-      <c r="DE72">
+      <c r="DF72">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF72" s="18">
+      <c r="DG72" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="DG72" t="str">
+      <c r="DH72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH72">
+      <c r="DI72">
         <v>0</v>
       </c>
-      <c r="DI72">
+      <c r="DJ72">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ72">
+      <c r="DK72">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>47</v>
       </c>
@@ -23086,31 +23137,31 @@
       <c r="CB73" t="s">
         <v>26</v>
       </c>
-      <c r="DE73">
+      <c r="DF73">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF73" s="18">
+      <c r="DG73" s="18">
         <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
-      <c r="DG73" t="str">
+      <c r="DH73" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH73">
+      <c r="DI73">
         <v>0</v>
       </c>
-      <c r="DI73">
+      <c r="DJ73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ73">
+      <c r="DK73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -23351,31 +23402,31 @@
       <c r="CB74" t="s">
         <v>26</v>
       </c>
-      <c r="DE74">
+      <c r="DF74">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF74" s="18">
+      <c r="DG74" s="18">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="DG74" t="str">
+      <c r="DH74" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH74">
+      <c r="DI74">
         <v>0</v>
       </c>
-      <c r="DI74">
+      <c r="DJ74">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ74">
+      <c r="DK74">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>347</v>
       </c>
@@ -23616,31 +23667,31 @@
       <c r="CB75" t="s">
         <v>26</v>
       </c>
-      <c r="DE75">
+      <c r="DF75">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF75" s="18">
+      <c r="DG75" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="DG75" t="str">
+      <c r="DH75" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH75">
+      <c r="DI75">
         <v>0</v>
       </c>
-      <c r="DI75">
+      <c r="DJ75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ75">
+      <c r="DK75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>350</v>
       </c>
@@ -23881,31 +23932,31 @@
       <c r="CB76" t="s">
         <v>26</v>
       </c>
-      <c r="DE76">
+      <c r="DF76">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF76" s="18">
+      <c r="DG76" s="18">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="DG76" t="str">
+      <c r="DH76" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH76">
+      <c r="DI76">
         <v>0</v>
       </c>
-      <c r="DI76">
+      <c r="DJ76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ76">
+      <c r="DK76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>351</v>
       </c>
@@ -24146,31 +24197,31 @@
       <c r="CB77" t="s">
         <v>26</v>
       </c>
-      <c r="DE77">
+      <c r="DF77">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF77" s="18">
+      <c r="DG77" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="DG77" t="str">
+      <c r="DH77" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH77">
+      <c r="DI77">
         <v>0</v>
       </c>
-      <c r="DI77">
+      <c r="DJ77">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ77">
+      <c r="DK77">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>352</v>
       </c>
@@ -24411,31 +24462,31 @@
       <c r="CB78" t="s">
         <v>26</v>
       </c>
-      <c r="DE78">
+      <c r="DF78">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF78" s="18">
+      <c r="DG78" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="DG78" t="str">
+      <c r="DH78" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH78">
+      <c r="DI78">
         <v>0</v>
       </c>
-      <c r="DI78">
+      <c r="DJ78">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ78">
+      <c r="DK78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>354</v>
       </c>
@@ -24676,31 +24727,31 @@
       <c r="CB79" t="s">
         <v>26</v>
       </c>
-      <c r="DE79">
+      <c r="DF79">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF79" s="18">
+      <c r="DG79" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="DG79" t="str">
+      <c r="DH79" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH79">
+      <c r="DI79">
         <v>0</v>
       </c>
-      <c r="DI79">
+      <c r="DJ79">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ79">
+      <c r="DK79">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>365</v>
       </c>
@@ -24941,31 +24992,31 @@
       <c r="CB80" t="s">
         <v>26</v>
       </c>
-      <c r="DE80">
+      <c r="DF80">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF80" s="18">
+      <c r="DG80" s="18">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
-      <c r="DG80" t="str">
+      <c r="DH80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH80">
+      <c r="DI80">
         <v>0</v>
       </c>
-      <c r="DI80">
+      <c r="DJ80">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ80">
+      <c r="DK80">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>366</v>
       </c>
@@ -25206,31 +25257,31 @@
       <c r="CB81" t="s">
         <v>26</v>
       </c>
-      <c r="DE81">
+      <c r="DF81">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF81" s="18">
+      <c r="DG81" s="18">
         <f t="shared" si="11"/>
         <v>2.5</v>
       </c>
-      <c r="DG81" t="str">
+      <c r="DH81" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH81">
+      <c r="DI81">
         <v>0</v>
       </c>
-      <c r="DI81">
+      <c r="DJ81">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ81">
+      <c r="DK81">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>374</v>
       </c>
@@ -25471,31 +25522,31 @@
       <c r="CB82" t="s">
         <v>26</v>
       </c>
-      <c r="DE82">
+      <c r="DF82">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF82" s="18">
+      <c r="DG82" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="DG82" t="str">
+      <c r="DH82" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH82">
+      <c r="DI82">
         <v>0</v>
       </c>
-      <c r="DI82">
+      <c r="DJ82">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ82">
+      <c r="DK82">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>375</v>
       </c>
@@ -25736,31 +25787,31 @@
       <c r="CB83" t="s">
         <v>26</v>
       </c>
-      <c r="DE83">
+      <c r="DF83">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF83" s="18">
+      <c r="DG83" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="DG83" t="str">
+      <c r="DH83" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH83">
+      <c r="DI83">
         <v>0</v>
       </c>
-      <c r="DI83">
+      <c r="DJ83">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ83">
+      <c r="DK83">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>377</v>
       </c>
@@ -26001,31 +26052,31 @@
       <c r="CB84" t="s">
         <v>26</v>
       </c>
-      <c r="DE84">
+      <c r="DF84">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF84" s="18">
+      <c r="DG84" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="DG84" t="str">
+      <c r="DH84" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH84">
+      <c r="DI84">
         <v>0</v>
       </c>
-      <c r="DI84">
+      <c r="DJ84">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ84">
+      <c r="DK84">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>381</v>
       </c>
@@ -26266,31 +26317,31 @@
       <c r="CB85" t="s">
         <v>26</v>
       </c>
-      <c r="DE85">
+      <c r="DF85">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF85" s="18">
+      <c r="DG85" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="DG85" t="str">
+      <c r="DH85" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH85">
+      <c r="DI85">
         <v>0</v>
       </c>
-      <c r="DI85">
+      <c r="DJ85">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ85">
+      <c r="DK85">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>382</v>
       </c>
@@ -26531,31 +26582,31 @@
       <c r="CB86" t="s">
         <v>26</v>
       </c>
-      <c r="DE86">
+      <c r="DF86">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF86" s="18">
+      <c r="DG86" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="DG86" t="str">
+      <c r="DH86" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH86">
+      <c r="DI86">
         <v>0</v>
       </c>
-      <c r="DI86">
+      <c r="DJ86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ86">
+      <c r="DK86">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>389</v>
       </c>
@@ -26799,31 +26850,31 @@
       <c r="CH87">
         <v>7.5</v>
       </c>
-      <c r="DE87">
+      <c r="DF87">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF87" s="18">
+      <c r="DG87" s="18">
         <f t="shared" si="11"/>
         <v>7.5</v>
       </c>
-      <c r="DG87" t="str">
+      <c r="DH87" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH87">
+      <c r="DI87">
         <v>0</v>
       </c>
-      <c r="DI87">
+      <c r="DJ87">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ87">
+      <c r="DK87">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>391</v>
       </c>
@@ -27067,93 +27118,93 @@
       <c r="CI88">
         <v>7</v>
       </c>
-      <c r="DE88">
+      <c r="DF88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF88" s="18">
+      <c r="DG88" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="DG88" t="str">
+      <c r="DH88" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH88">
+      <c r="DI88">
         <v>0</v>
       </c>
-      <c r="DI88">
+      <c r="DJ88">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ88">
+      <c r="DK88">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>394</v>
       </c>
       <c r="CP89">
         <v>6.5</v>
       </c>
-      <c r="DE89">
+      <c r="DF89">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF89" s="18">
+      <c r="DG89" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="DG89" t="str">
+      <c r="DH89" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH89">
+      <c r="DI89">
         <v>0</v>
       </c>
-      <c r="DI89">
+      <c r="DJ89">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ89">
+      <c r="DK89">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>395</v>
       </c>
       <c r="CQ90">
         <v>6.5</v>
       </c>
-      <c r="DE90">
+      <c r="DF90">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DF90" s="18">
+      <c r="DG90" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="DG90" t="str">
+      <c r="DH90" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH90">
+      <c r="DI90">
         <v>0</v>
       </c>
-      <c r="DI90">
+      <c r="DJ90">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DJ90">
+      <c r="DK90">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>399</v>
       </c>
@@ -27169,157 +27220,191 @@
       <c r="DC91">
         <v>8</v>
       </c>
-      <c r="DE91">
+      <c r="DD91">
+        <v>6</v>
+      </c>
+      <c r="DF91">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="DF91" s="18" t="e">
+      <c r="DG91" s="18" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="DG91" t="str">
+      <c r="DH91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DH91">
+      <c r="DI91">
         <v>0</v>
       </c>
-      <c r="DI91">
+      <c r="DJ91">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="DJ91">
+      <c r="DK91">
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>402</v>
       </c>
       <c r="DB92">
         <v>6</v>
       </c>
-      <c r="DE92">
-        <f t="shared" ref="DE92:DE95" si="15">COUNT(B92:CW92)</f>
+      <c r="DF92">
+        <f t="shared" ref="DF92:DF95" si="15">COUNT(B92:CW92)</f>
         <v>0</v>
       </c>
-      <c r="DF92" s="18" t="e">
-        <f t="shared" ref="DF92:DF95" si="16">AVERAGE(B92:CW92)</f>
+      <c r="DG92" s="18" t="e">
+        <f t="shared" ref="DG92:DG95" si="16">AVERAGE(B92:CW92)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="DG92" t="str">
-        <f t="shared" ref="DG92:DG95" si="17">IF(DE92&gt;1,_xlfn.STDEV.S(B92:CW92),"")</f>
+      <c r="DH92" t="str">
+        <f t="shared" ref="DH92:DH95" si="17">IF(DF92&gt;1,_xlfn.STDEV.S(B92:CW92),"")</f>
         <v/>
       </c>
-      <c r="DH92">
+      <c r="DI92">
         <v>0</v>
       </c>
-      <c r="DI92">
-        <f t="shared" ref="DI92:DI95" si="18">COUNT(CX92:DA92)</f>
+      <c r="DJ92">
+        <f t="shared" ref="DJ92:DJ95" si="18">COUNT(CX92:DA92)</f>
         <v>0</v>
       </c>
-      <c r="DJ92">
-        <f t="shared" ref="DJ92:DJ94" si="19">IF(DH92=0,DI92,0)</f>
+      <c r="DK92">
+        <f t="shared" ref="DK92:DK94" si="19">IF(DI92=0,DJ92,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>403</v>
       </c>
       <c r="DB93">
         <v>5.5</v>
       </c>
-      <c r="DE93">
+      <c r="DF93">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="DF93" s="18" t="e">
+      <c r="DG93" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="DG93" t="str">
+      <c r="DH93" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="DH93">
+      <c r="DI93">
         <v>0</v>
       </c>
-      <c r="DI93">
+      <c r="DJ93">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="DJ93">
+      <c r="DK93">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>404</v>
       </c>
       <c r="DB94">
         <v>5.5</v>
       </c>
-      <c r="DE94">
+      <c r="DF94">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="DF94" s="18" t="e">
+      <c r="DG94" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="DG94" t="str">
+      <c r="DH94" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="DH94">
+      <c r="DI94">
         <v>0</v>
       </c>
-      <c r="DI94">
+      <c r="DJ94">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="DJ94">
+      <c r="DK94">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:114" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:115" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>405</v>
       </c>
       <c r="DC95">
         <v>6</v>
       </c>
-      <c r="DE95">
+      <c r="DF95">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="DF95" s="18" t="e">
+      <c r="DG95" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="DG95" t="str">
+      <c r="DH95" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="DH95">
+      <c r="DI95">
         <v>0</v>
       </c>
-      <c r="DI95">
+      <c r="DJ95">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
+    <row r="96" spans="1:115" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>406</v>
+      </c>
+      <c r="DD96">
+        <v>6</v>
+      </c>
+      <c r="DF96">
+        <f t="shared" ref="DF96" si="20">COUNT(B96:CW96)</f>
+        <v>0</v>
+      </c>
+      <c r="DG96" s="18" t="e">
+        <f t="shared" ref="DG96" si="21">AVERAGE(B96:CW96)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="DH96" t="str">
+        <f t="shared" ref="DH96" si="22">IF(DF96&gt;1,_xlfn.STDEV.S(B96:CW96),"")</f>
+        <v/>
+      </c>
+      <c r="DI96">
+        <v>0</v>
+      </c>
+      <c r="DJ96">
+        <f t="shared" ref="DJ96" si="23">COUNT(CX96:DA96)</f>
+        <v>0</v>
+      </c>
+      <c r="DK96">
+        <f t="shared" ref="DK96" si="24">IF(DI96=0,DJ96,0)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:DJ83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
-    <sortState ref="A2:DJ91">
-      <sortCondition descending="1" ref="DE1:DE83"/>
+  <autoFilter ref="A1:DK83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
+    <sortState ref="A2:DK91">
+      <sortCondition descending="1" ref="DF1:DF83"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="DE2:DE95">
+  <conditionalFormatting sqref="DF2:DF96">
     <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
@@ -27331,7 +27416,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DG2:DG95">
+  <conditionalFormatting sqref="DH2:DH96">
     <cfRule type="colorScale" priority="89">
       <colorScale>
         <cfvo type="min"/>
@@ -27343,7 +27428,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE95">
+  <conditionalFormatting sqref="DF2:DF96">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -27355,7 +27440,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF95">
+  <conditionalFormatting sqref="DG2:DG96">
     <cfRule type="colorScale" priority="83">
       <colorScale>
         <cfvo type="min"/>
@@ -27367,7 +27452,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF95">
+  <conditionalFormatting sqref="DG2:DG96">
     <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
@@ -27379,7 +27464,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE95">
+  <conditionalFormatting sqref="DF2:DF96">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
@@ -27391,7 +27476,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF95">
+  <conditionalFormatting sqref="DG2:DG96">
     <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
@@ -27403,7 +27488,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DD2:DD79">
+  <conditionalFormatting sqref="DE2:DE79">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -27415,7 +27500,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DD2:DD67">
+  <conditionalFormatting sqref="DE2:DE67">
     <cfRule type="colorScale" priority="132">
       <colorScale>
         <cfvo type="min"/>
@@ -27427,7 +27512,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DD2:DD67">
+  <conditionalFormatting sqref="DE2:DE67">
     <cfRule type="colorScale" priority="134">
       <colorScale>
         <cfvo type="min"/>
@@ -27439,7 +27524,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DD2:DD67">
+  <conditionalFormatting sqref="DE2:DE67">
     <cfRule type="colorScale" priority="136">
       <colorScale>
         <cfvo type="min"/>
@@ -27451,7 +27536,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:DC83">
+  <conditionalFormatting sqref="B2:DD83">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -33120,7 +33205,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X310"/>
+  <dimension ref="A1:X313"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -48468,6 +48553,144 @@
         <v>398</v>
       </c>
     </row>
+    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A311" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B311" s="62">
+        <v>4</v>
+      </c>
+      <c r="C311" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D311" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E311" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F311" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G311" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="H311" s="8"/>
+      <c r="I311" s="9">
+        <v>2</v>
+      </c>
+      <c r="J311" s="10">
+        <v>5</v>
+      </c>
+      <c r="K311" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L311" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="M311" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N311" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="O311" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="P311" s="10"/>
+    </row>
+    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A312" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B312" s="62">
+        <v>5</v>
+      </c>
+      <c r="C312" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D312" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E312" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F312" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G312" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H312" s="10"/>
+      <c r="I312" s="11">
+        <v>5</v>
+      </c>
+      <c r="J312" s="2">
+        <v>5</v>
+      </c>
+      <c r="K312" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L312" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M312" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="N312" s="61" t="s">
+        <v>401</v>
+      </c>
+      <c r="O312" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="P312" s="2"/>
+    </row>
+    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A313" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B313" s="62">
+        <v>4</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E313" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="F313" s="61" t="s">
+        <v>401</v>
+      </c>
+      <c r="G313" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="H313" s="2"/>
+      <c r="I313" s="5">
+        <v>6</v>
+      </c>
+      <c r="J313" s="8">
+        <v>2</v>
+      </c>
+      <c r="K313" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L313" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="M313" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="N313" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="O313" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="P313" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -48475,7 +48698,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:CJ95"/>
+  <dimension ref="A1:CK96"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
@@ -48485,10 +48708,10 @@
     <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="88" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="89" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -48753,8 +48976,11 @@
       <c r="CJ1" s="1">
         <v>46218</v>
       </c>
-    </row>
-    <row r="2" spans="1:88" x14ac:dyDescent="0.35">
+      <c r="CK1" s="1">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -48825,7 +49051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -48833,7 +49059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -48871,7 +49097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>399</v>
       </c>
@@ -48887,13 +49113,16 @@
       <c r="CJ5">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:88" hidden="1" x14ac:dyDescent="0.35">
+      <c r="CK5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="7" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>77</v>
       </c>
@@ -48901,7 +49130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>364</v>
       </c>
@@ -48918,7 +49147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>401</v>
       </c>
@@ -48952,8 +49181,11 @@
       <c r="CJ9">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:88" x14ac:dyDescent="0.35">
+      <c r="CK9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -48961,7 +49193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>353</v>
       </c>
@@ -48969,17 +49201,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:88" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="13" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>395</v>
       </c>
@@ -48987,7 +49219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>398</v>
       </c>
@@ -49004,12 +49236,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="17" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>362</v>
       </c>
@@ -49017,12 +49249,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -49072,7 +49304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -49113,7 +49345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>378</v>
       </c>
@@ -49127,7 +49359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -49144,7 +49376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -49205,8 +49437,11 @@
       <c r="CC23">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:87" x14ac:dyDescent="0.35">
+      <c r="CK23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>84</v>
       </c>
@@ -49313,7 +49548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>391</v>
       </c>
@@ -49321,7 +49556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -49388,8 +49623,11 @@
       <c r="CC26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:87" x14ac:dyDescent="0.35">
+      <c r="CK26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>375</v>
       </c>
@@ -49397,7 +49635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -49552,7 +49790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>342</v>
       </c>
@@ -49572,12 +49810,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="31" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -49585,12 +49823,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:87" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="33" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>397</v>
       </c>
@@ -49598,7 +49836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -49618,7 +49856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -49722,7 +49960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>361</v>
       </c>
@@ -49739,7 +49977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>389</v>
       </c>
@@ -49747,7 +49985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>1</v>
       </c>
@@ -49895,8 +50133,11 @@
       <c r="CJ38">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:88" hidden="1" x14ac:dyDescent="0.35">
+      <c r="CK38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>351</v>
       </c>
@@ -49904,7 +50145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -50065,7 +50306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>392</v>
       </c>
@@ -50085,7 +50326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>381</v>
       </c>
@@ -50093,7 +50334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>20</v>
       </c>
@@ -50215,12 +50456,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="45" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>80</v>
       </c>
@@ -50228,7 +50469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:88" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -50236,7 +50477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>374</v>
       </c>
@@ -50244,7 +50485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -50392,8 +50633,11 @@
       <c r="CJ48">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="1:88" x14ac:dyDescent="0.35">
+      <c r="CK48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>43</v>
       </c>
@@ -50401,7 +50645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -50421,7 +50665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -50432,7 +50676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>368</v>
       </c>
@@ -50446,7 +50690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>345</v>
       </c>
@@ -50463,7 +50707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>343</v>
       </c>
@@ -50486,7 +50730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>344</v>
       </c>
@@ -50500,7 +50744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>396</v>
       </c>
@@ -50511,7 +50755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -50665,8 +50909,11 @@
       <c r="CJ57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:88" x14ac:dyDescent="0.35">
+      <c r="CK57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>46</v>
       </c>
@@ -50740,17 +50987,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="60" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="61" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>3</v>
       </c>
@@ -50767,12 +51014,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:88" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="63" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>56</v>
       </c>
@@ -50924,7 +51171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>369</v>
       </c>
@@ -51345,12 +51592,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:88" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>82</v>
       </c>
@@ -51520,7 +51767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>49</v>
       </c>
@@ -51528,12 +51775,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="85" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>390</v>
       </c>
@@ -51550,7 +51797,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -51564,7 +51811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -51746,7 +51993,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>45</v>
       </c>
@@ -51757,7 +52004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>367</v>
       </c>
@@ -51840,7 +52087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:88" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>352</v>
       </c>
@@ -51848,12 +52095,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:88" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="92" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -51867,232 +52114,240 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:88" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="94" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>86</v>
       </c>
-      <c r="K93">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:88" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+      <c r="K94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>16</v>
       </c>
-      <c r="C94">
+      <c r="C95">
         <v>4</v>
       </c>
-      <c r="D94">
+      <c r="D95">
         <v>3</v>
       </c>
-      <c r="F94">
-        <v>2</v>
-      </c>
-      <c r="G94">
-        <v>5</v>
-      </c>
-      <c r="H94">
+      <c r="F95">
+        <v>2</v>
+      </c>
+      <c r="G95">
+        <v>5</v>
+      </c>
+      <c r="H95">
         <v>3</v>
       </c>
-      <c r="I94">
-        <v>2</v>
-      </c>
-      <c r="J94">
-        <v>5</v>
-      </c>
-      <c r="K94">
+      <c r="I95">
+        <v>2</v>
+      </c>
+      <c r="J95">
+        <v>5</v>
+      </c>
+      <c r="K95">
         <v>3</v>
       </c>
-      <c r="L94">
-        <v>2</v>
-      </c>
-      <c r="M94">
+      <c r="L95">
+        <v>2</v>
+      </c>
+      <c r="M95">
         <v>3</v>
       </c>
-      <c r="O94">
-        <v>5</v>
-      </c>
-      <c r="P94">
-        <v>5</v>
-      </c>
-      <c r="Q94">
+      <c r="O95">
+        <v>5</v>
+      </c>
+      <c r="P95">
+        <v>5</v>
+      </c>
+      <c r="Q95">
         <v>3</v>
       </c>
-      <c r="R94">
-        <v>2</v>
-      </c>
-      <c r="S94">
+      <c r="R95">
+        <v>2</v>
+      </c>
+      <c r="S95">
         <v>3</v>
       </c>
-      <c r="T94">
-        <v>1</v>
-      </c>
-      <c r="U94">
-        <v>1</v>
-      </c>
-      <c r="V94">
+      <c r="T95">
+        <v>1</v>
+      </c>
+      <c r="U95">
+        <v>1</v>
+      </c>
+      <c r="V95">
         <v>3</v>
       </c>
-      <c r="W94">
+      <c r="W95">
         <v>3</v>
       </c>
-      <c r="X94">
-        <v>5</v>
-      </c>
-      <c r="Y94">
+      <c r="X95">
+        <v>5</v>
+      </c>
+      <c r="Y95">
         <v>4</v>
       </c>
-      <c r="Z94">
-        <v>1</v>
-      </c>
-      <c r="AA94">
+      <c r="Z95">
+        <v>1</v>
+      </c>
+      <c r="AA95">
         <v>3</v>
       </c>
-      <c r="AC94">
-        <v>1</v>
-      </c>
-      <c r="AE94">
+      <c r="AC95">
+        <v>1</v>
+      </c>
+      <c r="AE95">
         <v>4</v>
       </c>
-      <c r="AF94">
-        <v>2</v>
-      </c>
-      <c r="AG94">
+      <c r="AF95">
+        <v>2</v>
+      </c>
+      <c r="AG95">
         <v>3</v>
       </c>
-      <c r="AH94">
-        <v>2</v>
-      </c>
-      <c r="AI94">
-        <v>2</v>
-      </c>
-      <c r="AJ94">
+      <c r="AH95">
+        <v>2</v>
+      </c>
+      <c r="AI95">
+        <v>2</v>
+      </c>
+      <c r="AJ95">
         <v>7</v>
       </c>
-      <c r="AK94">
+      <c r="AK95">
         <v>3</v>
       </c>
-      <c r="AL94">
-        <v>5</v>
-      </c>
-      <c r="AM94">
-        <v>1</v>
-      </c>
-      <c r="AN94">
+      <c r="AL95">
+        <v>5</v>
+      </c>
+      <c r="AM95">
+        <v>1</v>
+      </c>
+      <c r="AN95">
         <v>4</v>
       </c>
-      <c r="AO94">
+      <c r="AO95">
         <v>3</v>
       </c>
-      <c r="AP94">
+      <c r="AP95">
         <v>6</v>
       </c>
-      <c r="AQ94">
+      <c r="AQ95">
         <v>4</v>
       </c>
-      <c r="AR94">
-        <v>5</v>
-      </c>
-      <c r="AS94">
+      <c r="AR95">
+        <v>5</v>
+      </c>
+      <c r="AS95">
         <v>3</v>
       </c>
-      <c r="AT94">
-        <v>2</v>
-      </c>
-      <c r="AU94">
-        <v>2</v>
-      </c>
-      <c r="AW94">
+      <c r="AT95">
+        <v>2</v>
+      </c>
+      <c r="AU95">
+        <v>2</v>
+      </c>
+      <c r="AW95">
         <v>3</v>
       </c>
-      <c r="AY94">
-        <v>1</v>
-      </c>
-      <c r="AZ94">
+      <c r="AY95">
+        <v>1</v>
+      </c>
+      <c r="AZ95">
         <v>3</v>
       </c>
-      <c r="BB94">
+      <c r="BB95">
         <v>4</v>
       </c>
-      <c r="BC94">
+      <c r="BC95">
         <v>4</v>
       </c>
-      <c r="BD94">
+      <c r="BD95">
         <v>3</v>
       </c>
-      <c r="BF94">
-        <v>2</v>
-      </c>
-      <c r="BG94">
+      <c r="BF95">
+        <v>2</v>
+      </c>
+      <c r="BG95">
         <v>4</v>
       </c>
-      <c r="BH94">
-        <v>5</v>
-      </c>
-      <c r="BJ94">
+      <c r="BH95">
+        <v>5</v>
+      </c>
+      <c r="BJ95">
         <v>4</v>
       </c>
-      <c r="BK94">
-        <v>2</v>
-      </c>
-      <c r="BL94">
+      <c r="BK95">
+        <v>2</v>
+      </c>
+      <c r="BL95">
         <v>4</v>
       </c>
-      <c r="BM94">
-        <v>1</v>
-      </c>
-      <c r="BN94">
-        <v>2</v>
-      </c>
-      <c r="BO94">
+      <c r="BM95">
+        <v>1</v>
+      </c>
+      <c r="BN95">
+        <v>2</v>
+      </c>
+      <c r="BO95">
         <v>3</v>
       </c>
-      <c r="BS94">
+      <c r="BS95">
         <v>3</v>
       </c>
-      <c r="BT94">
+      <c r="BT95">
         <v>4</v>
       </c>
-      <c r="BU94">
+      <c r="BU95">
         <v>4</v>
       </c>
-      <c r="BV94">
+      <c r="BV95">
         <v>3</v>
       </c>
-      <c r="BX94">
-        <v>5</v>
-      </c>
-      <c r="BY94">
-        <v>2</v>
-      </c>
-      <c r="BZ94">
+      <c r="BX95">
+        <v>5</v>
+      </c>
+      <c r="BY95">
+        <v>2</v>
+      </c>
+      <c r="BZ95">
         <v>3</v>
       </c>
-      <c r="CA94">
-        <v>1</v>
-      </c>
-      <c r="CG94">
+      <c r="CA95">
+        <v>1</v>
+      </c>
+      <c r="CG95">
         <v>3</v>
       </c>
-      <c r="CH94">
+      <c r="CH95">
         <v>6</v>
       </c>
-      <c r="CI94">
+      <c r="CI95">
         <v>3</v>
       </c>
-      <c r="CJ94">
+      <c r="CJ95">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="1:88" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+      <c r="CK95">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB95" xr:uid="{130C2564-D265-4C41-A3E0-02A62EDAC91D}">
-    <sortState ref="A2:AB95">
-      <sortCondition ref="A1:A95"/>
+  <autoFilter ref="A1:AB96" xr:uid="{130C2564-D265-4C41-A3E0-02A62EDAC91D}">
+    <sortState ref="A2:AB96">
+      <sortCondition ref="A1:A96"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="14_{CCCF2471-6899-4BEE-B69A-61EDE0174783}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{06CF8E01-0038-44E7-893A-E6758B390BD1}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="14_{CCCF2471-6899-4BEE-B69A-61EDE0174783}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{7F3F5EF3-6B1E-4132-9C8A-0A7F75662649}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7890" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notas" sheetId="1" r:id="rId1"/>
@@ -26,14 +26,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$AB$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'extrato 2024'!$A$1:$C$187</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$DK$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$DL$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9767" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9797" uniqueCount="407">
   <si>
     <t>Jogador</t>
   </si>
@@ -3522,7 +3522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DK96"/>
+  <dimension ref="A1:DL96"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
@@ -3547,10 +3547,10 @@
     <col min="50" max="58" width="9.54296875" customWidth="1"/>
     <col min="59" max="65" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
-    <col min="67" max="109" width="11" customWidth="1"/>
+    <col min="67" max="110" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3875,27 +3875,30 @@
       <c r="DD1" s="1">
         <v>46225</v>
       </c>
-      <c r="DE1" s="1"/>
-      <c r="DF1" t="s">
+      <c r="DE1" s="1">
+        <v>46232</v>
+      </c>
+      <c r="DF1" s="1"/>
+      <c r="DG1" t="s">
         <v>57</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DH1" t="s">
         <v>58</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DI1" t="s">
         <v>59</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DJ1" t="s">
         <v>62</v>
       </c>
-      <c r="DJ1" t="s">
+      <c r="DK1" t="s">
         <v>400</v>
       </c>
-      <c r="DK1" t="s">
+      <c r="DL1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4214,31 +4217,34 @@
       <c r="DD2">
         <v>6.5</v>
       </c>
-      <c r="DF2">
-        <f t="shared" ref="DF2:DF33" si="0">COUNT(B2:CW2)</f>
+      <c r="DE2">
+        <v>6</v>
+      </c>
+      <c r="DG2">
+        <f t="shared" ref="DG2:DG33" si="0">COUNT(B2:CW2)</f>
         <v>94</v>
       </c>
-      <c r="DG2" s="18">
-        <f t="shared" ref="DG2:DG33" si="1">AVERAGE(B2:CW2)</f>
+      <c r="DH2" s="18">
+        <f t="shared" ref="DH2:DH33" si="1">AVERAGE(B2:CW2)</f>
         <v>6.0106382978723403</v>
       </c>
-      <c r="DH2">
-        <f t="shared" ref="DH2:DH33" si="2">IF(DF2&gt;1,_xlfn.STDEV.S(B2:CW2),"")</f>
+      <c r="DI2">
+        <f t="shared" ref="DI2:DI33" si="2">IF(DG2&gt;1,_xlfn.STDEV.S(B2:CW2),"")</f>
         <v>1.1662335372744763</v>
       </c>
-      <c r="DI2">
-        <v>1</v>
-      </c>
       <c r="DJ2">
-        <f t="shared" ref="DJ2:DJ33" si="3">COUNT(CX2:DA2)</f>
+        <v>1</v>
+      </c>
+      <c r="DK2">
+        <f t="shared" ref="DK2:DK33" si="3">COUNT(CX2:DA2)</f>
         <v>3</v>
       </c>
-      <c r="DK2">
-        <f t="shared" ref="DK2:DK33" si="4">IF(DI2=0,DJ2,0)</f>
+      <c r="DL2">
+        <f t="shared" ref="DL2:DL33" si="4">IF(DJ2=0,DK2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4548,31 +4554,34 @@
       <c r="DD3">
         <v>5.5</v>
       </c>
-      <c r="DF3">
+      <c r="DE3">
+        <v>5.5</v>
+      </c>
+      <c r="DG3">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="DG3" s="18">
+      <c r="DH3" s="18">
         <f t="shared" si="1"/>
         <v>5.6590909090909092</v>
       </c>
-      <c r="DH3">
+      <c r="DI3">
         <f t="shared" si="2"/>
         <v>0.97540281848434929</v>
       </c>
-      <c r="DI3">
-        <v>1</v>
-      </c>
       <c r="DJ3">
+        <v>1</v>
+      </c>
+      <c r="DK3">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DK3">
+      <c r="DL3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -4870,31 +4879,34 @@
       <c r="DA4">
         <v>6</v>
       </c>
-      <c r="DF4">
+      <c r="DE4">
+        <v>6</v>
+      </c>
+      <c r="DG4">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="DG4" s="18">
+      <c r="DH4" s="18">
         <f t="shared" si="1"/>
         <v>6.5576923076923075</v>
       </c>
-      <c r="DH4">
+      <c r="DI4">
         <f t="shared" si="2"/>
         <v>0.9327405829087726</v>
       </c>
-      <c r="DI4">
-        <v>1</v>
-      </c>
       <c r="DJ4">
+        <v>1</v>
+      </c>
+      <c r="DK4">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DK4">
+      <c r="DL4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -5195,31 +5207,34 @@
       <c r="DD5">
         <v>5.5</v>
       </c>
-      <c r="DF5">
+      <c r="DE5">
+        <v>6.5</v>
+      </c>
+      <c r="DG5">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="DG5" s="18">
+      <c r="DH5" s="18">
         <f t="shared" si="1"/>
         <v>6.625</v>
       </c>
-      <c r="DH5">
+      <c r="DI5">
         <f t="shared" si="2"/>
         <v>0.99037030111637203</v>
       </c>
-      <c r="DI5">
-        <v>1</v>
-      </c>
       <c r="DJ5">
+        <v>1</v>
+      </c>
+      <c r="DK5">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DK5">
+      <c r="DL5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5505,31 +5520,34 @@
       <c r="DC6">
         <v>7.5</v>
       </c>
-      <c r="DF6">
+      <c r="DE6">
+        <v>6.5</v>
+      </c>
+      <c r="DG6">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="DG6" s="18">
+      <c r="DH6" s="18">
         <f t="shared" si="1"/>
         <v>7.2430555555555554</v>
       </c>
-      <c r="DH6">
+      <c r="DI6">
         <f t="shared" si="2"/>
         <v>1.1444694187225961</v>
       </c>
-      <c r="DI6">
-        <v>1</v>
-      </c>
       <c r="DJ6">
+        <v>1</v>
+      </c>
+      <c r="DK6">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DK6">
+      <c r="DL6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -5794,31 +5812,31 @@
       <c r="DD7">
         <v>5.5</v>
       </c>
-      <c r="DF7">
+      <c r="DG7">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="DG7" s="18">
+      <c r="DH7" s="18">
         <f t="shared" si="1"/>
         <v>5.708333333333333</v>
       </c>
-      <c r="DH7">
+      <c r="DI7">
         <f t="shared" si="2"/>
         <v>0.94477808706744304</v>
       </c>
-      <c r="DI7">
+      <c r="DJ7">
         <v>0</v>
       </c>
-      <c r="DJ7">
+      <c r="DK7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK7">
+      <c r="DL7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -6110,31 +6128,31 @@
       <c r="DD8">
         <v>4.5</v>
       </c>
-      <c r="DF8">
+      <c r="DG8">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="DG8" s="18">
+      <c r="DH8" s="18">
         <f t="shared" si="1"/>
         <v>5.7642857142857142</v>
       </c>
-      <c r="DH8">
+      <c r="DI8">
         <f t="shared" si="2"/>
         <v>1.2986097040916795</v>
       </c>
-      <c r="DI8">
-        <v>1</v>
-      </c>
       <c r="DJ8">
+        <v>1</v>
+      </c>
+      <c r="DK8">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="DK8">
+      <c r="DL8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -6402,31 +6420,31 @@
       <c r="DD9">
         <v>5.5</v>
       </c>
-      <c r="DF9">
+      <c r="DG9">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="DG9" s="18">
+      <c r="DH9" s="18">
         <f t="shared" si="1"/>
         <v>5.95</v>
       </c>
-      <c r="DH9">
+      <c r="DI9">
         <f t="shared" si="2"/>
         <v>0.94466465179333525</v>
       </c>
-      <c r="DI9">
+      <c r="DJ9">
         <v>0</v>
       </c>
-      <c r="DJ9">
+      <c r="DK9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK9">
+      <c r="DL9">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -6676,31 +6694,31 @@
       <c r="CE10">
         <v>5</v>
       </c>
-      <c r="DF10">
+      <c r="DG10">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="DG10" s="18">
+      <c r="DH10" s="18">
         <f t="shared" si="1"/>
         <v>6.4191176470588234</v>
       </c>
-      <c r="DH10">
+      <c r="DI10">
         <f t="shared" si="2"/>
         <v>1.1769245721961776</v>
       </c>
-      <c r="DI10">
+      <c r="DJ10">
         <v>0</v>
       </c>
-      <c r="DJ10">
+      <c r="DK10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK10">
+      <c r="DL10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6998,31 +7016,34 @@
       <c r="DD11">
         <v>6.5</v>
       </c>
-      <c r="DF11">
+      <c r="DE11">
+        <v>7.5</v>
+      </c>
+      <c r="DG11">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="DG11" s="18">
+      <c r="DH11" s="18">
         <f t="shared" si="1"/>
         <v>6.6492537313432836</v>
       </c>
-      <c r="DH11">
+      <c r="DI11">
         <f t="shared" si="2"/>
         <v>0.94152892009339217</v>
       </c>
-      <c r="DI11">
-        <v>1</v>
-      </c>
       <c r="DJ11">
+        <v>1</v>
+      </c>
+      <c r="DK11">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="DK11">
+      <c r="DL11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -7323,31 +7344,34 @@
       <c r="DC12">
         <v>5</v>
       </c>
-      <c r="DF12">
+      <c r="DE12">
+        <v>5.5</v>
+      </c>
+      <c r="DG12">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="DG12" s="18">
+      <c r="DH12" s="18">
         <f t="shared" si="1"/>
         <v>5.5390625</v>
       </c>
-      <c r="DH12">
+      <c r="DI12">
         <f t="shared" si="2"/>
         <v>0.96075651202415768</v>
       </c>
-      <c r="DI12">
-        <v>1</v>
-      </c>
       <c r="DJ12">
+        <v>1</v>
+      </c>
+      <c r="DK12">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DK12">
+      <c r="DL12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -7660,31 +7684,34 @@
       <c r="DD13">
         <v>6.5</v>
       </c>
-      <c r="DF13">
+      <c r="DE13">
+        <v>5.5</v>
+      </c>
+      <c r="DG13">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="DG13" s="18">
+      <c r="DH13" s="18">
         <f t="shared" si="1"/>
         <v>6.3174603174603172</v>
       </c>
-      <c r="DH13">
+      <c r="DI13">
         <f t="shared" si="2"/>
         <v>1.0862096991357946</v>
       </c>
-      <c r="DI13">
-        <v>1</v>
-      </c>
       <c r="DJ13">
+        <v>1</v>
+      </c>
+      <c r="DK13">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DK13">
+      <c r="DL13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>367</v>
       </c>
@@ -7952,31 +7979,34 @@
       <c r="DB14">
         <v>6</v>
       </c>
-      <c r="DF14">
+      <c r="DE14">
+        <v>5.5</v>
+      </c>
+      <c r="DG14">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="DG14" s="18">
+      <c r="DH14" s="18">
         <f t="shared" si="1"/>
         <v>6.2661290322580649</v>
       </c>
-      <c r="DH14">
+      <c r="DI14">
         <f t="shared" si="2"/>
         <v>1.0586015440095373</v>
       </c>
-      <c r="DI14">
+      <c r="DJ14">
         <v>0</v>
       </c>
-      <c r="DJ14">
+      <c r="DK14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK14">
+      <c r="DL14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -8295,31 +8325,34 @@
       <c r="DD15">
         <v>6</v>
       </c>
-      <c r="DF15">
+      <c r="DE15">
+        <v>6.5</v>
+      </c>
+      <c r="DG15">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="DG15" s="18">
+      <c r="DH15" s="18">
         <f t="shared" si="1"/>
         <v>6.0535714285714288</v>
       </c>
-      <c r="DH15">
+      <c r="DI15">
         <f t="shared" si="2"/>
         <v>0.85108792104614583</v>
       </c>
-      <c r="DI15">
-        <v>1</v>
-      </c>
       <c r="DJ15">
+        <v>1</v>
+      </c>
+      <c r="DK15">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DK15">
+      <c r="DL15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -8566,31 +8599,31 @@
       <c r="CW16">
         <v>6</v>
       </c>
-      <c r="DF16">
+      <c r="DG16">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="DG16" s="18">
+      <c r="DH16" s="18">
         <f t="shared" si="1"/>
         <v>5.6981132075471699</v>
       </c>
-      <c r="DH16">
+      <c r="DI16">
         <f t="shared" si="2"/>
         <v>0.83975513052632311</v>
       </c>
-      <c r="DI16">
+      <c r="DJ16">
         <v>0</v>
       </c>
-      <c r="DJ16">
+      <c r="DK16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK16">
+      <c r="DL16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -8879,31 +8912,31 @@
       <c r="DD17">
         <v>5.5</v>
       </c>
-      <c r="DF17">
+      <c r="DG17">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="DG17" s="18">
+      <c r="DH17" s="18">
         <f t="shared" si="1"/>
         <v>5.7244897959183669</v>
       </c>
-      <c r="DH17">
+      <c r="DI17">
         <f t="shared" si="2"/>
         <v>0.89594703439175261</v>
       </c>
-      <c r="DI17">
-        <v>1</v>
-      </c>
       <c r="DJ17">
+        <v>1</v>
+      </c>
+      <c r="DK17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK17">
+      <c r="DL17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -9153,31 +9186,31 @@
       <c r="CF18">
         <v>5.5</v>
       </c>
-      <c r="DF18">
+      <c r="DG18">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="DG18" s="18">
+      <c r="DH18" s="18">
         <f t="shared" si="1"/>
         <v>4.4255319148936172</v>
       </c>
-      <c r="DH18">
+      <c r="DI18">
         <f t="shared" si="2"/>
         <v>1.3391217246854428</v>
       </c>
-      <c r="DI18">
+      <c r="DJ18">
         <v>0</v>
       </c>
-      <c r="DJ18">
+      <c r="DK18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK18">
+      <c r="DL18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -9460,31 +9493,34 @@
       <c r="DC19">
         <v>5.5</v>
       </c>
-      <c r="DF19">
+      <c r="DE19">
+        <v>5.5</v>
+      </c>
+      <c r="DG19">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="DG19" s="18">
+      <c r="DH19" s="18">
         <f t="shared" si="1"/>
         <v>5.0113636363636367</v>
       </c>
-      <c r="DH19">
+      <c r="DI19">
         <f t="shared" si="2"/>
         <v>1.0481913346311222</v>
       </c>
-      <c r="DI19">
+      <c r="DJ19">
         <v>0</v>
       </c>
-      <c r="DJ19">
+      <c r="DK19">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DK19">
+      <c r="DL19">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -9767,31 +9803,34 @@
       <c r="DB20">
         <v>6</v>
       </c>
-      <c r="DF20">
+      <c r="DE20">
+        <v>6.5</v>
+      </c>
+      <c r="DG20">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="DG20" s="18">
+      <c r="DH20" s="18">
         <f t="shared" si="1"/>
         <v>5.75</v>
       </c>
-      <c r="DH20">
+      <c r="DI20">
         <f t="shared" si="2"/>
         <v>0.85249292433809187</v>
       </c>
-      <c r="DI20">
-        <v>1</v>
-      </c>
       <c r="DJ20">
+        <v>1</v>
+      </c>
+      <c r="DK20">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="DK20">
+      <c r="DL20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -10077,31 +10116,31 @@
       <c r="CZ21">
         <v>5.5</v>
       </c>
-      <c r="DF21">
+      <c r="DG21">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="DG21" s="18">
+      <c r="DH21" s="18">
         <f t="shared" si="1"/>
         <v>5.2441860465116283</v>
       </c>
-      <c r="DH21">
+      <c r="DI21">
         <f t="shared" si="2"/>
         <v>1.1920974563830549</v>
       </c>
-      <c r="DI21">
-        <v>1</v>
-      </c>
       <c r="DJ21">
+        <v>1</v>
+      </c>
+      <c r="DK21">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="DK21">
+      <c r="DL21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -10345,31 +10384,31 @@
       <c r="CK22">
         <v>5.5</v>
       </c>
-      <c r="DF22">
+      <c r="DG22">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="DG22" s="18">
+      <c r="DH22" s="18">
         <f t="shared" si="1"/>
         <v>6.1410256410256414</v>
       </c>
-      <c r="DH22">
+      <c r="DI22">
         <f t="shared" si="2"/>
         <v>1.0879042984027267</v>
       </c>
-      <c r="DI22">
+      <c r="DJ22">
         <v>0</v>
       </c>
-      <c r="DJ22">
+      <c r="DK22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK22">
+      <c r="DL22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -10652,31 +10691,31 @@
       <c r="DB23">
         <v>5.5</v>
       </c>
-      <c r="DF23">
+      <c r="DG23">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="DG23" s="18">
+      <c r="DH23" s="18">
         <f t="shared" si="1"/>
         <v>6.3181818181818183</v>
       </c>
-      <c r="DH23">
+      <c r="DI23">
         <f t="shared" si="2"/>
         <v>0.9828067413836219</v>
       </c>
-      <c r="DI23">
+      <c r="DJ23">
         <v>0</v>
       </c>
-      <c r="DJ23">
+      <c r="DK23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK23">
+      <c r="DL23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -10941,31 +10980,31 @@
       <c r="DD24">
         <v>6</v>
       </c>
-      <c r="DF24">
+      <c r="DG24">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="DG24" s="18">
+      <c r="DH24" s="18">
         <f t="shared" si="1"/>
         <v>5.4827586206896548</v>
       </c>
-      <c r="DH24">
+      <c r="DI24">
         <f t="shared" si="2"/>
         <v>0.68768190607350477</v>
       </c>
-      <c r="DI24">
+      <c r="DJ24">
         <v>0</v>
       </c>
-      <c r="DJ24">
+      <c r="DK24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK24">
+      <c r="DL24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -11236,31 +11275,31 @@
       <c r="DB25">
         <v>6</v>
       </c>
-      <c r="DF25">
+      <c r="DG25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="DG25" s="18">
+      <c r="DH25" s="18">
         <f t="shared" si="1"/>
         <v>6.6086956521739131</v>
       </c>
-      <c r="DH25">
+      <c r="DI25">
         <f t="shared" si="2"/>
         <v>0.67346663781731952</v>
       </c>
-      <c r="DI25">
-        <v>1</v>
-      </c>
       <c r="DJ25">
+        <v>1</v>
+      </c>
+      <c r="DK25">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="DK25">
+      <c r="DL25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>81</v>
       </c>
@@ -11546,31 +11585,31 @@
       <c r="CT26">
         <v>5</v>
       </c>
-      <c r="DF26">
+      <c r="DG26">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="DG26" s="18">
+      <c r="DH26" s="18">
         <f t="shared" si="1"/>
         <v>6.2368421052631575</v>
       </c>
-      <c r="DH26">
+      <c r="DI26">
         <f t="shared" si="2"/>
         <v>0.63176166947476609</v>
       </c>
-      <c r="DI26">
+      <c r="DJ26">
         <v>0</v>
       </c>
-      <c r="DJ26">
+      <c r="DK26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK26">
+      <c r="DL26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -11811,31 +11850,31 @@
       <c r="CB27" t="s">
         <v>26</v>
       </c>
-      <c r="DF27">
+      <c r="DG27">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="DG27" s="18">
+      <c r="DH27" s="18">
         <f t="shared" si="1"/>
         <v>5.7894736842105265</v>
       </c>
-      <c r="DH27">
+      <c r="DI27">
         <f t="shared" si="2"/>
         <v>1.3674366679797902</v>
       </c>
-      <c r="DI27">
+      <c r="DJ27">
         <v>0</v>
       </c>
-      <c r="DJ27">
+      <c r="DK27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK27">
+      <c r="DL27">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -12094,31 +12133,31 @@
       <c r="CW28">
         <v>5.5</v>
       </c>
-      <c r="DF28">
+      <c r="DG28">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="DG28" s="18">
+      <c r="DH28" s="18">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="DH28">
+      <c r="DI28">
         <f t="shared" si="2"/>
         <v>0.85749292571254421</v>
       </c>
-      <c r="DI28">
+      <c r="DJ28">
         <v>0</v>
       </c>
-      <c r="DJ28">
+      <c r="DK28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK28">
+      <c r="DL28">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>346</v>
       </c>
@@ -12359,31 +12398,31 @@
       <c r="CB29" t="s">
         <v>26</v>
       </c>
-      <c r="DF29">
+      <c r="DG29">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="DG29" s="18">
+      <c r="DH29" s="18">
         <f t="shared" si="1"/>
         <v>5.9444444444444446</v>
       </c>
-      <c r="DH29">
+      <c r="DI29">
         <f t="shared" si="2"/>
         <v>0.72535769855270305</v>
       </c>
-      <c r="DI29">
+      <c r="DJ29">
         <v>0</v>
       </c>
-      <c r="DJ29">
+      <c r="DK29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK29">
+      <c r="DL29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -12627,31 +12666,31 @@
       <c r="DD30">
         <v>5.5</v>
       </c>
-      <c r="DF30">
+      <c r="DG30">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="DG30" s="18">
+      <c r="DH30" s="18">
         <f t="shared" si="1"/>
         <v>5.3235294117647056</v>
       </c>
-      <c r="DH30">
+      <c r="DI30">
         <f t="shared" si="2"/>
         <v>1.3456083251473603</v>
       </c>
-      <c r="DI30">
+      <c r="DJ30">
         <v>0</v>
       </c>
-      <c r="DJ30">
+      <c r="DK30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK30">
+      <c r="DL30">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -12898,31 +12937,31 @@
       <c r="DA31">
         <v>5.5</v>
       </c>
-      <c r="DF31">
+      <c r="DG31">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="DG31" s="18">
+      <c r="DH31" s="18">
         <f t="shared" si="1"/>
         <v>4.53125</v>
       </c>
-      <c r="DH31">
+      <c r="DI31">
         <f t="shared" si="2"/>
         <v>1.5434674167816653</v>
       </c>
-      <c r="DI31">
+      <c r="DJ31">
         <v>0</v>
       </c>
-      <c r="DJ31">
+      <c r="DK31">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="DK31">
+      <c r="DL31">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>343</v>
       </c>
@@ -13193,31 +13232,31 @@
       <c r="DC32">
         <v>5.5</v>
       </c>
-      <c r="DF32">
+      <c r="DG32">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="DG32" s="18">
+      <c r="DH32" s="18">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="DH32">
+      <c r="DI32">
         <f t="shared" si="2"/>
         <v>1.5383974345619102</v>
       </c>
-      <c r="DI32">
-        <v>1</v>
-      </c>
       <c r="DJ32">
+        <v>1</v>
+      </c>
+      <c r="DK32">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="DK32">
+      <c r="DL32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -13458,31 +13497,31 @@
       <c r="CB33">
         <v>5.5</v>
       </c>
-      <c r="DF33">
+      <c r="DG33">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="DG33" s="18">
+      <c r="DH33" s="18">
         <f t="shared" si="1"/>
         <v>3.8666666666666667</v>
       </c>
-      <c r="DH33">
+      <c r="DI33">
         <f t="shared" si="2"/>
         <v>2.3563490726929555</v>
       </c>
-      <c r="DI33">
+      <c r="DJ33">
         <v>0</v>
       </c>
-      <c r="DJ33">
+      <c r="DK33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DK33">
+      <c r="DL33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -13732,31 +13771,31 @@
       <c r="DB34">
         <v>6.5</v>
       </c>
-      <c r="DF34">
-        <f t="shared" ref="DF34:DF65" si="5">COUNT(B34:CW34)</f>
+      <c r="DG34">
+        <f t="shared" ref="DG34:DG65" si="5">COUNT(B34:CW34)</f>
         <v>14</v>
       </c>
-      <c r="DG34" s="18">
-        <f t="shared" ref="DG34:DG65" si="6">AVERAGE(B34:CW34)</f>
+      <c r="DH34" s="18">
+        <f t="shared" ref="DH34:DH65" si="6">AVERAGE(B34:CW34)</f>
         <v>7.25</v>
       </c>
-      <c r="DH34">
-        <f t="shared" ref="DH34:DH65" si="7">IF(DF34&gt;1,_xlfn.STDEV.S(B34:CW34),"")</f>
+      <c r="DI34">
+        <f t="shared" ref="DI34:DI65" si="7">IF(DG34&gt;1,_xlfn.STDEV.S(B34:CW34),"")</f>
         <v>1.5032017112202156</v>
       </c>
-      <c r="DI34">
+      <c r="DJ34">
         <v>0</v>
       </c>
-      <c r="DJ34">
-        <f t="shared" ref="DJ34:DJ65" si="8">COUNT(CX34:DA34)</f>
-        <v>1</v>
-      </c>
       <c r="DK34">
-        <f t="shared" ref="DK34:DK65" si="9">IF(DI34=0,DJ34,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:115" x14ac:dyDescent="0.35">
+        <f t="shared" ref="DK34:DK65" si="8">COUNT(CX34:DA34)</f>
+        <v>1</v>
+      </c>
+      <c r="DL34">
+        <f t="shared" ref="DL34:DL65" si="9">IF(DJ34=0,DK34,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>376</v>
       </c>
@@ -14036,31 +14075,34 @@
       <c r="DD35">
         <v>7</v>
       </c>
-      <c r="DF35">
+      <c r="DE35">
+        <v>6.5</v>
+      </c>
+      <c r="DG35">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="DG35" s="18">
+      <c r="DH35" s="18">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="DH35">
+      <c r="DI35">
         <f t="shared" si="7"/>
         <v>0.58834840541455213</v>
       </c>
-      <c r="DI35">
-        <v>1</v>
-      </c>
       <c r="DJ35">
+        <v>1</v>
+      </c>
+      <c r="DK35">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="DK35">
+      <c r="DL35">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>378</v>
       </c>
@@ -14328,31 +14370,31 @@
       <c r="CQ36">
         <v>5.5</v>
       </c>
-      <c r="DF36">
+      <c r="DG36">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="DG36" s="18">
+      <c r="DH36" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="DH36">
+      <c r="DI36">
         <f t="shared" si="7"/>
         <v>0.3988620176087328</v>
       </c>
-      <c r="DI36">
+      <c r="DJ36">
         <v>0</v>
       </c>
-      <c r="DJ36">
+      <c r="DK36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK36">
+      <c r="DL36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -14593,31 +14635,31 @@
       <c r="CB37" t="s">
         <v>26</v>
       </c>
-      <c r="DF37">
+      <c r="DG37">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="DG37" s="18">
+      <c r="DH37" s="18">
         <f t="shared" si="6"/>
         <v>4.6818181818181817</v>
       </c>
-      <c r="DH37">
+      <c r="DI37">
         <f t="shared" si="7"/>
         <v>0.81463879335344846</v>
       </c>
-      <c r="DI37">
+      <c r="DJ37">
         <v>0</v>
       </c>
-      <c r="DJ37">
+      <c r="DK37">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK37">
+      <c r="DL37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -14861,31 +14903,31 @@
       <c r="CC38">
         <v>6</v>
       </c>
-      <c r="DF38">
+      <c r="DG38">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="DG38" s="18">
+      <c r="DH38" s="18">
         <f t="shared" si="6"/>
         <v>8.4499999999999993</v>
       </c>
-      <c r="DH38">
+      <c r="DI38">
         <f t="shared" si="7"/>
         <v>1.1890705987824657</v>
       </c>
-      <c r="DI38">
+      <c r="DJ38">
         <v>0</v>
       </c>
-      <c r="DJ38">
+      <c r="DK38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK38">
+      <c r="DL38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>340</v>
       </c>
@@ -15129,31 +15171,31 @@
       <c r="CL39">
         <v>6</v>
       </c>
-      <c r="DF39">
+      <c r="DG39">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="DG39" s="18">
+      <c r="DH39" s="18">
         <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
-      <c r="DH39">
+      <c r="DI39">
         <f t="shared" si="7"/>
         <v>0.53452248382484879</v>
       </c>
-      <c r="DI39">
+      <c r="DJ39">
         <v>0</v>
       </c>
-      <c r="DJ39">
+      <c r="DK39">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK39">
+      <c r="DL39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>401</v>
       </c>
@@ -15196,31 +15238,34 @@
       <c r="DD40">
         <v>9</v>
       </c>
-      <c r="DF40">
+      <c r="DE40">
+        <v>5.5</v>
+      </c>
+      <c r="DG40">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="DG40" s="18">
+      <c r="DH40" s="18">
         <f t="shared" si="6"/>
         <v>6.6428571428571432</v>
       </c>
-      <c r="DH40">
+      <c r="DI40">
         <f t="shared" si="7"/>
         <v>1.1801936887041631</v>
       </c>
-      <c r="DI40">
-        <v>1</v>
-      </c>
       <c r="DJ40">
+        <v>1</v>
+      </c>
+      <c r="DK40">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="DK40">
+      <c r="DL40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>345</v>
       </c>
@@ -15479,31 +15524,31 @@
       <c r="CO41">
         <v>4.5</v>
       </c>
-      <c r="DF41">
+      <c r="DG41">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="DG41" s="18">
+      <c r="DH41" s="18">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="DH41">
+      <c r="DI41">
         <f t="shared" si="7"/>
         <v>1.2583057392117916</v>
       </c>
-      <c r="DI41">
+      <c r="DJ41">
         <v>0</v>
       </c>
-      <c r="DJ41">
+      <c r="DK41">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK41">
+      <c r="DL41">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>392</v>
       </c>
@@ -15528,31 +15573,31 @@
       <c r="CY42">
         <v>4.5</v>
       </c>
-      <c r="DF42">
+      <c r="DG42">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="DG42" s="18">
+      <c r="DH42" s="18">
         <f t="shared" si="6"/>
         <v>5.833333333333333</v>
       </c>
-      <c r="DH42">
+      <c r="DI42">
         <f t="shared" si="7"/>
         <v>1.2516655570345734</v>
       </c>
-      <c r="DI42">
+      <c r="DJ42">
         <v>0</v>
       </c>
-      <c r="DJ42">
+      <c r="DK42">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="DK42">
+      <c r="DL42">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>398</v>
       </c>
@@ -15583,31 +15628,34 @@
       <c r="DD43">
         <v>6.5</v>
       </c>
-      <c r="DF43">
+      <c r="DE43">
+        <v>5.5</v>
+      </c>
+      <c r="DG43">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DG43" s="18">
+      <c r="DH43" s="18">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="DH43">
+      <c r="DI43">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DI43">
+      <c r="DJ43">
         <v>0</v>
       </c>
-      <c r="DJ43">
+      <c r="DK43">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="DK43">
+      <c r="DL43">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>342</v>
       </c>
@@ -15857,31 +15905,31 @@
       <c r="CU44">
         <v>5.5</v>
       </c>
-      <c r="DF44">
+      <c r="DG44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DG44" s="18">
+      <c r="DH44" s="18">
         <f t="shared" si="6"/>
         <v>5.6</v>
       </c>
-      <c r="DH44">
+      <c r="DI44">
         <f t="shared" si="7"/>
         <v>1.0839741694339387</v>
       </c>
-      <c r="DI44">
+      <c r="DJ44">
         <v>0</v>
       </c>
-      <c r="DJ44">
+      <c r="DK44">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK44">
+      <c r="DL44">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>390</v>
       </c>
@@ -16137,31 +16185,31 @@
       <c r="CU45">
         <v>6</v>
       </c>
-      <c r="DF45">
+      <c r="DG45">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DG45" s="18">
+      <c r="DH45" s="18">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="DH45">
+      <c r="DI45">
         <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
-      <c r="DI45">
+      <c r="DJ45">
         <v>0</v>
       </c>
-      <c r="DJ45">
+      <c r="DK45">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK45">
+      <c r="DL45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -16405,31 +16453,31 @@
       <c r="CH46">
         <v>6.5</v>
       </c>
-      <c r="DF46">
+      <c r="DG46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DG46" s="18">
+      <c r="DH46" s="18">
         <f t="shared" si="6"/>
         <v>7.8</v>
       </c>
-      <c r="DH46">
+      <c r="DI46">
         <f t="shared" si="7"/>
         <v>1.1510864433221351</v>
       </c>
-      <c r="DI46">
+      <c r="DJ46">
         <v>0</v>
       </c>
-      <c r="DJ46">
+      <c r="DK46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK46">
+      <c r="DL46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -16673,31 +16721,31 @@
       <c r="CM47">
         <v>5.5</v>
       </c>
-      <c r="DF47">
+      <c r="DG47">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DG47" s="18">
+      <c r="DH47" s="18">
         <f t="shared" si="6"/>
         <v>3.8</v>
       </c>
-      <c r="DH47">
+      <c r="DI47">
         <f t="shared" si="7"/>
         <v>1.0368220676663857</v>
       </c>
-      <c r="DI47">
+      <c r="DJ47">
         <v>0</v>
       </c>
-      <c r="DJ47">
+      <c r="DK47">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK47">
+      <c r="DL47">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>364</v>
       </c>
@@ -16947,31 +16995,31 @@
       <c r="CN48">
         <v>6</v>
       </c>
-      <c r="DF48">
+      <c r="DG48">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="DG48" s="18">
+      <c r="DH48" s="18">
         <f t="shared" si="6"/>
         <v>6.2</v>
       </c>
-      <c r="DH48">
+      <c r="DI48">
         <f t="shared" si="7"/>
         <v>0.44721359549995793</v>
       </c>
-      <c r="DI48">
+      <c r="DJ48">
         <v>0</v>
       </c>
-      <c r="DJ48">
+      <c r="DK48">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK48">
+      <c r="DL48">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -17215,31 +17263,31 @@
       <c r="CY49">
         <v>5.5</v>
       </c>
-      <c r="DF49">
+      <c r="DG49">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DG49" s="18">
+      <c r="DH49" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="DH49">
+      <c r="DI49">
         <f t="shared" si="7"/>
         <v>1.0408329997330663</v>
       </c>
-      <c r="DI49">
+      <c r="DJ49">
         <v>0</v>
       </c>
-      <c r="DJ49">
+      <c r="DK49">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="DK49">
+      <c r="DL49">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -17486,31 +17534,31 @@
       <c r="CV50">
         <v>5.5</v>
       </c>
-      <c r="DF50">
+      <c r="DG50">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DG50" s="18">
+      <c r="DH50" s="18">
         <f t="shared" si="6"/>
         <v>5.625</v>
       </c>
-      <c r="DH50">
+      <c r="DI50">
         <f t="shared" si="7"/>
         <v>0.25</v>
       </c>
-      <c r="DI50">
+      <c r="DJ50">
         <v>0</v>
       </c>
-      <c r="DJ50">
+      <c r="DK50">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK50">
+      <c r="DL50">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -17751,31 +17799,31 @@
       <c r="CB51" t="s">
         <v>26</v>
       </c>
-      <c r="DF51">
+      <c r="DG51">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DG51" s="18">
+      <c r="DH51" s="18">
         <f t="shared" si="6"/>
         <v>5.625</v>
       </c>
-      <c r="DH51">
+      <c r="DI51">
         <f t="shared" si="7"/>
         <v>0.9464847243000456</v>
       </c>
-      <c r="DI51">
+      <c r="DJ51">
         <v>0</v>
       </c>
-      <c r="DJ51">
+      <c r="DK51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK51">
+      <c r="DL51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>21</v>
       </c>
@@ -18016,31 +18064,31 @@
       <c r="CB52" t="s">
         <v>26</v>
       </c>
-      <c r="DF52">
+      <c r="DG52">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DG52" s="18">
+      <c r="DH52" s="18">
         <f t="shared" si="6"/>
         <v>1.375</v>
       </c>
-      <c r="DH52">
+      <c r="DI52">
         <f t="shared" si="7"/>
         <v>1.8874586088176875</v>
       </c>
-      <c r="DI52">
+      <c r="DJ52">
         <v>0</v>
       </c>
-      <c r="DJ52">
+      <c r="DK52">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK52">
+      <c r="DL52">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>344</v>
       </c>
@@ -18281,31 +18329,31 @@
       <c r="CB53" t="s">
         <v>26</v>
       </c>
-      <c r="DF53">
+      <c r="DG53">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DG53" s="18">
+      <c r="DH53" s="18">
         <f t="shared" si="6"/>
         <v>4.625</v>
       </c>
-      <c r="DH53">
+      <c r="DI53">
         <f t="shared" si="7"/>
         <v>1.4361406616345072</v>
       </c>
-      <c r="DI53">
+      <c r="DJ53">
         <v>0</v>
       </c>
-      <c r="DJ53">
+      <c r="DK53">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK53">
+      <c r="DL53">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>361</v>
       </c>
@@ -18546,31 +18594,31 @@
       <c r="CB54" t="s">
         <v>26</v>
       </c>
-      <c r="DF54">
+      <c r="DG54">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DG54" s="18">
+      <c r="DH54" s="18">
         <f t="shared" si="6"/>
         <v>6.25</v>
       </c>
-      <c r="DH54">
+      <c r="DI54">
         <f t="shared" si="7"/>
         <v>0.8660254037844386</v>
       </c>
-      <c r="DI54">
+      <c r="DJ54">
         <v>0</v>
       </c>
-      <c r="DJ54">
+      <c r="DK54">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK54">
+      <c r="DL54">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>43</v>
       </c>
@@ -18811,31 +18859,31 @@
       <c r="CB55" t="s">
         <v>26</v>
       </c>
-      <c r="DF55">
+      <c r="DG55">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="DG55" s="18">
+      <c r="DH55" s="18">
         <f t="shared" si="6"/>
         <v>2.875</v>
       </c>
-      <c r="DH55">
+      <c r="DI55">
         <f t="shared" si="7"/>
         <v>2.7801378862687129</v>
       </c>
-      <c r="DI55">
+      <c r="DJ55">
         <v>0</v>
       </c>
-      <c r="DJ55">
+      <c r="DK55">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK55">
+      <c r="DL55">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -19076,31 +19124,31 @@
       <c r="CB56" t="s">
         <v>26</v>
       </c>
-      <c r="DF56">
+      <c r="DG56">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DG56" s="18">
+      <c r="DH56" s="18">
         <f t="shared" si="6"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="DH56">
+      <c r="DI56">
         <f t="shared" si="7"/>
         <v>1.4433756729740652</v>
       </c>
-      <c r="DI56">
+      <c r="DJ56">
         <v>0</v>
       </c>
-      <c r="DJ56">
+      <c r="DK56">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK56">
+      <c r="DL56">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -19341,31 +19389,31 @@
       <c r="CB57" t="s">
         <v>26</v>
       </c>
-      <c r="DF57">
+      <c r="DG57">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DG57" s="18">
+      <c r="DH57" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="DH57">
+      <c r="DI57">
         <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
-      <c r="DI57">
+      <c r="DJ57">
         <v>0</v>
       </c>
-      <c r="DJ57">
+      <c r="DK57">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK57">
+      <c r="DL57">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>49</v>
       </c>
@@ -19606,31 +19654,31 @@
       <c r="CB58" t="s">
         <v>26</v>
       </c>
-      <c r="DF58">
+      <c r="DG58">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DG58" s="18">
+      <c r="DH58" s="18">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="DH58">
+      <c r="DI58">
         <f t="shared" si="7"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="DI58">
+      <c r="DJ58">
         <v>0</v>
       </c>
-      <c r="DJ58">
+      <c r="DK58">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK58">
+      <c r="DL58">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>368</v>
       </c>
@@ -19874,31 +19922,31 @@
       <c r="CG59">
         <v>6</v>
       </c>
-      <c r="DF59">
+      <c r="DG59">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DG59" s="18">
+      <c r="DH59" s="18">
         <f t="shared" si="6"/>
         <v>8.5</v>
       </c>
-      <c r="DH59">
+      <c r="DI59">
         <f t="shared" si="7"/>
         <v>2.179449471770337</v>
       </c>
-      <c r="DI59">
+      <c r="DJ59">
         <v>0</v>
       </c>
-      <c r="DJ59">
+      <c r="DK59">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK59">
+      <c r="DL59">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>53</v>
       </c>
@@ -20142,31 +20190,31 @@
       <c r="CS60">
         <v>5.5</v>
       </c>
-      <c r="DF60">
+      <c r="DG60">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DG60" s="18">
+      <c r="DH60" s="18">
         <f t="shared" si="6"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="DH60">
+      <c r="DI60">
         <f t="shared" si="7"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="DI60">
+      <c r="DJ60">
         <v>0</v>
       </c>
-      <c r="DJ60">
+      <c r="DK60">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK60">
+      <c r="DL60">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>387</v>
       </c>
@@ -20416,31 +20464,31 @@
       <c r="CJ61">
         <v>7</v>
       </c>
-      <c r="DF61">
+      <c r="DG61">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DG61" s="18">
+      <c r="DH61" s="18">
         <f t="shared" si="6"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="DH61">
+      <c r="DI61">
         <f t="shared" si="7"/>
         <v>0.57735026918962584</v>
       </c>
-      <c r="DI61">
+      <c r="DJ61">
         <v>0</v>
       </c>
-      <c r="DJ61">
+      <c r="DK61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK61">
+      <c r="DL61">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>362</v>
       </c>
@@ -20684,31 +20732,31 @@
       <c r="CD62">
         <v>5.5</v>
       </c>
-      <c r="DF62">
+      <c r="DG62">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="DG62" s="18">
+      <c r="DH62" s="18">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
-      <c r="DH62">
+      <c r="DI62">
         <f t="shared" si="7"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DI62">
+      <c r="DJ62">
         <v>0</v>
       </c>
-      <c r="DJ62">
+      <c r="DK62">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK62">
+      <c r="DL62">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>339</v>
       </c>
@@ -20949,31 +20997,31 @@
       <c r="CB63" t="s">
         <v>26</v>
       </c>
-      <c r="DF63">
+      <c r="DG63">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="DG63" s="18">
+      <c r="DH63" s="18">
         <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
-      <c r="DH63">
+      <c r="DI63">
         <f t="shared" si="7"/>
         <v>2.4748737341529163</v>
       </c>
-      <c r="DI63">
+      <c r="DJ63">
         <v>0</v>
       </c>
-      <c r="DJ63">
+      <c r="DK63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK63">
+      <c r="DL63">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>369</v>
       </c>
@@ -21214,31 +21262,31 @@
       <c r="CB64" t="s">
         <v>26</v>
       </c>
-      <c r="DF64">
+      <c r="DG64">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="DG64" s="18">
+      <c r="DH64" s="18">
         <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
-      <c r="DH64">
+      <c r="DI64">
         <f t="shared" si="7"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="DI64">
+      <c r="DJ64">
         <v>0</v>
       </c>
-      <c r="DJ64">
+      <c r="DK64">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK64">
+      <c r="DL64">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>379</v>
       </c>
@@ -21479,31 +21527,31 @@
       <c r="CB65" t="s">
         <v>26</v>
       </c>
-      <c r="DF65">
+      <c r="DG65">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="DG65" s="18">
+      <c r="DH65" s="18">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="DH65">
+      <c r="DI65">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DI65">
+      <c r="DJ65">
         <v>0</v>
       </c>
-      <c r="DJ65">
+      <c r="DK65">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DK65">
+      <c r="DL65">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>388</v>
       </c>
@@ -21747,31 +21795,31 @@
       <c r="CH66">
         <v>5</v>
       </c>
-      <c r="DF66">
-        <f t="shared" ref="DF66:DF91" si="10">COUNT(B66:CW66)</f>
-        <v>2</v>
-      </c>
-      <c r="DG66" s="18">
-        <f t="shared" ref="DG66:DG91" si="11">AVERAGE(B66:CW66)</f>
+      <c r="DG66">
+        <f t="shared" ref="DG66:DG91" si="10">COUNT(B66:CW66)</f>
+        <v>2</v>
+      </c>
+      <c r="DH66" s="18">
+        <f t="shared" ref="DH66:DH91" si="11">AVERAGE(B66:CW66)</f>
         <v>4.25</v>
       </c>
-      <c r="DH66">
-        <f t="shared" ref="DH66:DH91" si="12">IF(DF66&gt;1,_xlfn.STDEV.S(B66:CW66),"")</f>
+      <c r="DI66">
+        <f t="shared" ref="DI66:DI91" si="12">IF(DG66&gt;1,_xlfn.STDEV.S(B66:CW66),"")</f>
         <v>1.0606601717798212</v>
       </c>
-      <c r="DI66">
+      <c r="DJ66">
         <v>0</v>
       </c>
-      <c r="DJ66">
-        <f t="shared" ref="DJ66:DJ91" si="13">COUNT(CX66:DA66)</f>
+      <c r="DK66">
+        <f t="shared" ref="DK66:DK91" si="13">COUNT(CX66:DA66)</f>
         <v>0</v>
       </c>
-      <c r="DK66">
-        <f t="shared" ref="DK66:DK91" si="14">IF(DI66=0,DJ66,0)</f>
+      <c r="DL66">
+        <f t="shared" ref="DL66:DL91" si="14">IF(DJ66=0,DK66,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>396</v>
       </c>
@@ -21781,62 +21829,62 @@
       <c r="DA67">
         <v>7</v>
       </c>
-      <c r="DF67">
+      <c r="DG67">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG67" s="18">
+      <c r="DH67" s="18">
         <f t="shared" si="11"/>
         <v>7.5</v>
       </c>
-      <c r="DH67" t="str">
+      <c r="DI67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI67">
+      <c r="DJ67">
         <v>0</v>
       </c>
-      <c r="DJ67">
+      <c r="DK67">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="DK67">
+      <c r="DL67">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>397</v>
       </c>
       <c r="CV68">
         <v>6</v>
       </c>
-      <c r="DF68">
+      <c r="DG68">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG68" s="18">
+      <c r="DH68" s="18">
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
-      <c r="DH68" t="str">
+      <c r="DI68" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI68">
+      <c r="DJ68">
         <v>0</v>
       </c>
-      <c r="DJ68">
+      <c r="DK68">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK68">
+      <c r="DL68">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>86</v>
       </c>
@@ -22077,31 +22125,31 @@
       <c r="CB69" t="s">
         <v>26</v>
       </c>
-      <c r="DF69">
+      <c r="DG69">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG69" s="18">
+      <c r="DH69" s="18">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="DH69" t="str">
+      <c r="DI69" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI69">
+      <c r="DJ69">
         <v>0</v>
       </c>
-      <c r="DJ69">
+      <c r="DK69">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK69">
+      <c r="DL69">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -22342,31 +22390,31 @@
       <c r="CB70" t="s">
         <v>26</v>
       </c>
-      <c r="DF70">
+      <c r="DG70">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG70" s="18">
+      <c r="DH70" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="DH70" t="str">
+      <c r="DI70" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI70">
+      <c r="DJ70">
         <v>0</v>
       </c>
-      <c r="DJ70">
+      <c r="DK70">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK70">
+      <c r="DL70">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>353</v>
       </c>
@@ -22607,31 +22655,31 @@
       <c r="CB71" t="s">
         <v>26</v>
       </c>
-      <c r="DF71">
+      <c r="DG71">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG71" s="18">
+      <c r="DH71" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="DH71" t="str">
+      <c r="DI71" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI71">
+      <c r="DJ71">
         <v>0</v>
       </c>
-      <c r="DJ71">
+      <c r="DK71">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK71">
+      <c r="DL71">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>80</v>
       </c>
@@ -22872,31 +22920,31 @@
       <c r="CB72" t="s">
         <v>26</v>
       </c>
-      <c r="DF72">
+      <c r="DG72">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG72" s="18">
+      <c r="DH72" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="DH72" t="str">
+      <c r="DI72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI72">
+      <c r="DJ72">
         <v>0</v>
       </c>
-      <c r="DJ72">
+      <c r="DK72">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK72">
+      <c r="DL72">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>47</v>
       </c>
@@ -23137,31 +23185,31 @@
       <c r="CB73" t="s">
         <v>26</v>
       </c>
-      <c r="DF73">
+      <c r="DG73">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG73" s="18">
+      <c r="DH73" s="18">
         <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
-      <c r="DH73" t="str">
+      <c r="DI73" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI73">
+      <c r="DJ73">
         <v>0</v>
       </c>
-      <c r="DJ73">
+      <c r="DK73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK73">
+      <c r="DL73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -23402,31 +23450,31 @@
       <c r="CB74" t="s">
         <v>26</v>
       </c>
-      <c r="DF74">
+      <c r="DG74">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG74" s="18">
+      <c r="DH74" s="18">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="DH74" t="str">
+      <c r="DI74" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI74">
+      <c r="DJ74">
         <v>0</v>
       </c>
-      <c r="DJ74">
+      <c r="DK74">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK74">
+      <c r="DL74">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>347</v>
       </c>
@@ -23667,31 +23715,31 @@
       <c r="CB75" t="s">
         <v>26</v>
       </c>
-      <c r="DF75">
+      <c r="DG75">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG75" s="18">
+      <c r="DH75" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="DH75" t="str">
+      <c r="DI75" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI75">
+      <c r="DJ75">
         <v>0</v>
       </c>
-      <c r="DJ75">
+      <c r="DK75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK75">
+      <c r="DL75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>350</v>
       </c>
@@ -23932,31 +23980,31 @@
       <c r="CB76" t="s">
         <v>26</v>
       </c>
-      <c r="DF76">
+      <c r="DG76">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG76" s="18">
+      <c r="DH76" s="18">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="DH76" t="str">
+      <c r="DI76" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI76">
+      <c r="DJ76">
         <v>0</v>
       </c>
-      <c r="DJ76">
+      <c r="DK76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK76">
+      <c r="DL76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>351</v>
       </c>
@@ -24197,31 +24245,31 @@
       <c r="CB77" t="s">
         <v>26</v>
       </c>
-      <c r="DF77">
+      <c r="DG77">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG77" s="18">
+      <c r="DH77" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="DH77" t="str">
+      <c r="DI77" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI77">
+      <c r="DJ77">
         <v>0</v>
       </c>
-      <c r="DJ77">
+      <c r="DK77">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK77">
+      <c r="DL77">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>352</v>
       </c>
@@ -24462,31 +24510,31 @@
       <c r="CB78" t="s">
         <v>26</v>
       </c>
-      <c r="DF78">
+      <c r="DG78">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG78" s="18">
+      <c r="DH78" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="DH78" t="str">
+      <c r="DI78" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI78">
+      <c r="DJ78">
         <v>0</v>
       </c>
-      <c r="DJ78">
+      <c r="DK78">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK78">
+      <c r="DL78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>354</v>
       </c>
@@ -24727,31 +24775,31 @@
       <c r="CB79" t="s">
         <v>26</v>
       </c>
-      <c r="DF79">
+      <c r="DG79">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG79" s="18">
+      <c r="DH79" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="DH79" t="str">
+      <c r="DI79" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI79">
+      <c r="DJ79">
         <v>0</v>
       </c>
-      <c r="DJ79">
+      <c r="DK79">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK79">
+      <c r="DL79">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>365</v>
       </c>
@@ -24992,31 +25040,31 @@
       <c r="CB80" t="s">
         <v>26</v>
       </c>
-      <c r="DF80">
+      <c r="DG80">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG80" s="18">
+      <c r="DH80" s="18">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
-      <c r="DH80" t="str">
+      <c r="DI80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI80">
+      <c r="DJ80">
         <v>0</v>
       </c>
-      <c r="DJ80">
+      <c r="DK80">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK80">
+      <c r="DL80">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>366</v>
       </c>
@@ -25257,31 +25305,31 @@
       <c r="CB81" t="s">
         <v>26</v>
       </c>
-      <c r="DF81">
+      <c r="DG81">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG81" s="18">
+      <c r="DH81" s="18">
         <f t="shared" si="11"/>
         <v>2.5</v>
       </c>
-      <c r="DH81" t="str">
+      <c r="DI81" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI81">
+      <c r="DJ81">
         <v>0</v>
       </c>
-      <c r="DJ81">
+      <c r="DK81">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK81">
+      <c r="DL81">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>374</v>
       </c>
@@ -25522,31 +25570,31 @@
       <c r="CB82" t="s">
         <v>26</v>
       </c>
-      <c r="DF82">
+      <c r="DG82">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG82" s="18">
+      <c r="DH82" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="DH82" t="str">
+      <c r="DI82" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI82">
+      <c r="DJ82">
         <v>0</v>
       </c>
-      <c r="DJ82">
+      <c r="DK82">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK82">
+      <c r="DL82">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>375</v>
       </c>
@@ -25787,31 +25835,31 @@
       <c r="CB83" t="s">
         <v>26</v>
       </c>
-      <c r="DF83">
+      <c r="DG83">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG83" s="18">
+      <c r="DH83" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="DH83" t="str">
+      <c r="DI83" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI83">
+      <c r="DJ83">
         <v>0</v>
       </c>
-      <c r="DJ83">
+      <c r="DK83">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK83">
+      <c r="DL83">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>377</v>
       </c>
@@ -26052,31 +26100,31 @@
       <c r="CB84" t="s">
         <v>26</v>
       </c>
-      <c r="DF84">
+      <c r="DG84">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG84" s="18">
+      <c r="DH84" s="18">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="DH84" t="str">
+      <c r="DI84" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI84">
+      <c r="DJ84">
         <v>0</v>
       </c>
-      <c r="DJ84">
+      <c r="DK84">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK84">
+      <c r="DL84">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>381</v>
       </c>
@@ -26317,31 +26365,31 @@
       <c r="CB85" t="s">
         <v>26</v>
       </c>
-      <c r="DF85">
+      <c r="DG85">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG85" s="18">
+      <c r="DH85" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="DH85" t="str">
+      <c r="DI85" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI85">
+      <c r="DJ85">
         <v>0</v>
       </c>
-      <c r="DJ85">
+      <c r="DK85">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK85">
+      <c r="DL85">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>382</v>
       </c>
@@ -26582,31 +26630,31 @@
       <c r="CB86" t="s">
         <v>26</v>
       </c>
-      <c r="DF86">
+      <c r="DG86">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG86" s="18">
+      <c r="DH86" s="18">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="DH86" t="str">
+      <c r="DI86" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI86">
+      <c r="DJ86">
         <v>0</v>
       </c>
-      <c r="DJ86">
+      <c r="DK86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK86">
+      <c r="DL86">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>389</v>
       </c>
@@ -26850,31 +26898,31 @@
       <c r="CH87">
         <v>7.5</v>
       </c>
-      <c r="DF87">
+      <c r="DG87">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG87" s="18">
+      <c r="DH87" s="18">
         <f t="shared" si="11"/>
         <v>7.5</v>
       </c>
-      <c r="DH87" t="str">
+      <c r="DI87" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI87">
+      <c r="DJ87">
         <v>0</v>
       </c>
-      <c r="DJ87">
+      <c r="DK87">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK87">
+      <c r="DL87">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>391</v>
       </c>
@@ -27118,93 +27166,93 @@
       <c r="CI88">
         <v>7</v>
       </c>
-      <c r="DF88">
+      <c r="DG88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG88" s="18">
+      <c r="DH88" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="DH88" t="str">
+      <c r="DI88" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI88">
+      <c r="DJ88">
         <v>0</v>
       </c>
-      <c r="DJ88">
+      <c r="DK88">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK88">
+      <c r="DL88">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>394</v>
       </c>
       <c r="CP89">
         <v>6.5</v>
       </c>
-      <c r="DF89">
+      <c r="DG89">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG89" s="18">
+      <c r="DH89" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="DH89" t="str">
+      <c r="DI89" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI89">
+      <c r="DJ89">
         <v>0</v>
       </c>
-      <c r="DJ89">
+      <c r="DK89">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK89">
+      <c r="DL89">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>395</v>
       </c>
       <c r="CQ90">
         <v>6.5</v>
       </c>
-      <c r="DF90">
+      <c r="DG90">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="DG90" s="18">
+      <c r="DH90" s="18">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="DH90" t="str">
+      <c r="DI90" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI90">
+      <c r="DJ90">
         <v>0</v>
       </c>
-      <c r="DJ90">
+      <c r="DK90">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="DK90">
+      <c r="DL90">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>399</v>
       </c>
@@ -27223,188 +27271,188 @@
       <c r="DD91">
         <v>6</v>
       </c>
-      <c r="DF91">
+      <c r="DG91">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="DG91" s="18" t="e">
+      <c r="DH91" s="18" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="DH91" t="str">
+      <c r="DI91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="DI91">
+      <c r="DJ91">
         <v>0</v>
       </c>
-      <c r="DJ91">
+      <c r="DK91">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="DK91">
+      <c r="DL91">
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>402</v>
       </c>
       <c r="DB92">
         <v>6</v>
       </c>
-      <c r="DF92">
-        <f t="shared" ref="DF92:DF95" si="15">COUNT(B92:CW92)</f>
+      <c r="DG92">
+        <f t="shared" ref="DG92:DG95" si="15">COUNT(B92:CW92)</f>
         <v>0</v>
       </c>
-      <c r="DG92" s="18" t="e">
-        <f t="shared" ref="DG92:DG95" si="16">AVERAGE(B92:CW92)</f>
+      <c r="DH92" s="18" t="e">
+        <f t="shared" ref="DH92:DH95" si="16">AVERAGE(B92:CW92)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="DH92" t="str">
-        <f t="shared" ref="DH92:DH95" si="17">IF(DF92&gt;1,_xlfn.STDEV.S(B92:CW92),"")</f>
+      <c r="DI92" t="str">
+        <f t="shared" ref="DI92:DI95" si="17">IF(DG92&gt;1,_xlfn.STDEV.S(B92:CW92),"")</f>
         <v/>
       </c>
-      <c r="DI92">
+      <c r="DJ92">
         <v>0</v>
       </c>
-      <c r="DJ92">
-        <f t="shared" ref="DJ92:DJ95" si="18">COUNT(CX92:DA92)</f>
+      <c r="DK92">
+        <f t="shared" ref="DK92:DK95" si="18">COUNT(CX92:DA92)</f>
         <v>0</v>
       </c>
-      <c r="DK92">
-        <f t="shared" ref="DK92:DK94" si="19">IF(DI92=0,DJ92,0)</f>
+      <c r="DL92">
+        <f t="shared" ref="DL92:DL94" si="19">IF(DJ92=0,DK92,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>403</v>
       </c>
       <c r="DB93">
         <v>5.5</v>
       </c>
-      <c r="DF93">
+      <c r="DG93">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="DG93" s="18" t="e">
+      <c r="DH93" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="DH93" t="str">
+      <c r="DI93" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="DI93">
+      <c r="DJ93">
         <v>0</v>
       </c>
-      <c r="DJ93">
+      <c r="DK93">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="DK93">
+      <c r="DL93">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>404</v>
       </c>
       <c r="DB94">
         <v>5.5</v>
       </c>
-      <c r="DF94">
+      <c r="DG94">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="DG94" s="18" t="e">
+      <c r="DH94" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="DH94" t="str">
+      <c r="DI94" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="DI94">
+      <c r="DJ94">
         <v>0</v>
       </c>
-      <c r="DJ94">
+      <c r="DK94">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="DK94">
+      <c r="DL94">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>405</v>
       </c>
       <c r="DC95">
         <v>6</v>
       </c>
-      <c r="DF95">
+      <c r="DG95">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="DG95" s="18" t="e">
+      <c r="DH95" s="18" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="DH95" t="str">
+      <c r="DI95" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="DI95">
+      <c r="DJ95">
         <v>0</v>
       </c>
-      <c r="DJ95">
+      <c r="DK95">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>406</v>
       </c>
       <c r="DD96">
         <v>6</v>
       </c>
-      <c r="DF96">
-        <f t="shared" ref="DF96" si="20">COUNT(B96:CW96)</f>
+      <c r="DG96">
+        <f t="shared" ref="DG96" si="20">COUNT(B96:CW96)</f>
         <v>0</v>
       </c>
-      <c r="DG96" s="18" t="e">
-        <f t="shared" ref="DG96" si="21">AVERAGE(B96:CW96)</f>
+      <c r="DH96" s="18" t="e">
+        <f t="shared" ref="DH96" si="21">AVERAGE(B96:CW96)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="DH96" t="str">
-        <f t="shared" ref="DH96" si="22">IF(DF96&gt;1,_xlfn.STDEV.S(B96:CW96),"")</f>
+      <c r="DI96" t="str">
+        <f t="shared" ref="DI96" si="22">IF(DG96&gt;1,_xlfn.STDEV.S(B96:CW96),"")</f>
         <v/>
       </c>
-      <c r="DI96">
+      <c r="DJ96">
         <v>0</v>
       </c>
-      <c r="DJ96">
-        <f t="shared" ref="DJ96" si="23">COUNT(CX96:DA96)</f>
+      <c r="DK96">
+        <f t="shared" ref="DK96" si="23">COUNT(CX96:DA96)</f>
         <v>0</v>
       </c>
-      <c r="DK96">
-        <f t="shared" ref="DK96" si="24">IF(DI96=0,DJ96,0)</f>
+      <c r="DL96">
+        <f t="shared" ref="DL96" si="24">IF(DJ96=0,DK96,0)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:DK83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
-    <sortState ref="A2:DK91">
-      <sortCondition descending="1" ref="DF1:DF83"/>
+  <autoFilter ref="A1:DL83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
+    <sortState ref="A2:DL91">
+      <sortCondition descending="1" ref="DG1:DG83"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="DF2:DF96">
+  <conditionalFormatting sqref="DG2:DG96">
     <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
@@ -27416,7 +27464,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DH2:DH96">
+  <conditionalFormatting sqref="DI2:DI96">
     <cfRule type="colorScale" priority="89">
       <colorScale>
         <cfvo type="min"/>
@@ -27428,7 +27476,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF96">
+  <conditionalFormatting sqref="DG2:DG96">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -27440,7 +27488,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DG2:DG96">
+  <conditionalFormatting sqref="DH2:DH96">
     <cfRule type="colorScale" priority="83">
       <colorScale>
         <cfvo type="min"/>
@@ -27452,7 +27500,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DG2:DG96">
+  <conditionalFormatting sqref="DH2:DH96">
     <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
@@ -27464,7 +27512,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF96">
+  <conditionalFormatting sqref="DG2:DG96">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
@@ -27476,7 +27524,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DG2:DG96">
+  <conditionalFormatting sqref="DH2:DH96">
     <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
@@ -27488,7 +27536,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE79">
+  <conditionalFormatting sqref="DF2:DF79">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -27500,7 +27548,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE67">
+  <conditionalFormatting sqref="DF2:DF67">
     <cfRule type="colorScale" priority="132">
       <colorScale>
         <cfvo type="min"/>
@@ -27512,7 +27560,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE67">
+  <conditionalFormatting sqref="DF2:DF67">
     <cfRule type="colorScale" priority="134">
       <colorScale>
         <cfvo type="min"/>
@@ -27524,7 +27572,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE67">
+  <conditionalFormatting sqref="DF2:DF67">
     <cfRule type="colorScale" priority="136">
       <colorScale>
         <cfvo type="min"/>
@@ -27536,7 +27584,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:DD83">
+  <conditionalFormatting sqref="B2:DE83">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -33205,7 +33253,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X313"/>
+  <dimension ref="A1:X316"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -48691,6 +48739,144 @@
       </c>
       <c r="P313" s="8"/>
     </row>
+    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A314" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B314" s="62">
+        <v>4</v>
+      </c>
+      <c r="C314" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D314" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E314" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F314" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G314" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H314" s="8"/>
+      <c r="I314" s="9">
+        <v>6</v>
+      </c>
+      <c r="J314" s="10">
+        <v>3</v>
+      </c>
+      <c r="K314" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L314" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M314" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N314" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="O314" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="P314" s="10"/>
+    </row>
+    <row r="315" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A315" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B315" s="62">
+        <v>2</v>
+      </c>
+      <c r="C315" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D315" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E315" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F315" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G315" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="H315" s="10"/>
+      <c r="I315" s="11">
+        <v>3</v>
+      </c>
+      <c r="J315" s="2">
+        <v>2</v>
+      </c>
+      <c r="K315" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="L315" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M315" s="61" t="s">
+        <v>367</v>
+      </c>
+      <c r="N315" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="O315" s="61" t="s">
+        <v>376</v>
+      </c>
+      <c r="P315" s="2"/>
+    </row>
+    <row r="316" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A316" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B316" s="62">
+        <v>4</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E316" s="61" t="s">
+        <v>367</v>
+      </c>
+      <c r="F316" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="G316" s="61" t="s">
+        <v>376</v>
+      </c>
+      <c r="H316" s="2"/>
+      <c r="I316" s="5">
+        <v>0</v>
+      </c>
+      <c r="J316" s="8">
+        <v>5</v>
+      </c>
+      <c r="K316" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L316" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M316" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="N316" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="O316" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="P316" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -48698,7 +48884,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:CK96"/>
+  <dimension ref="A1:CL96"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
@@ -48708,10 +48894,10 @@
     <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="89" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="90" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -48979,8 +49165,11 @@
       <c r="CK1" s="1">
         <v>46225</v>
       </c>
-    </row>
-    <row r="2" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="CL1" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -49051,7 +49240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -49059,7 +49248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -49097,7 +49286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>399</v>
       </c>
@@ -49117,12 +49306,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="7" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>77</v>
       </c>
@@ -49130,7 +49319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>364</v>
       </c>
@@ -49147,7 +49336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>401</v>
       </c>
@@ -49185,7 +49374,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -49193,7 +49382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>353</v>
       </c>
@@ -49201,17 +49390,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="13" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>395</v>
       </c>
@@ -49219,7 +49408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>398</v>
       </c>
@@ -49236,12 +49425,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="17" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>362</v>
       </c>
@@ -49249,12 +49438,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -49304,7 +49493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -49345,7 +49534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>378</v>
       </c>
@@ -49359,7 +49548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -49376,7 +49565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -49441,7 +49630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>84</v>
       </c>
@@ -49547,8 +49736,11 @@
       <c r="CI24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="CL24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>391</v>
       </c>
@@ -49556,7 +49748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -49627,7 +49819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>375</v>
       </c>
@@ -49635,7 +49827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -49790,7 +49982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>342</v>
       </c>
@@ -49810,12 +50002,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="31" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -49823,12 +50015,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="33" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>397</v>
       </c>
@@ -49836,7 +50028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -49856,7 +50048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -49960,7 +50152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>361</v>
       </c>
@@ -49977,7 +50169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>389</v>
       </c>
@@ -49985,7 +50177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>1</v>
       </c>
@@ -50137,7 +50329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>351</v>
       </c>
@@ -50145,7 +50337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -50305,8 +50497,11 @@
       <c r="CG40">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="CL40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>392</v>
       </c>
@@ -50326,7 +50521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>381</v>
       </c>
@@ -50334,7 +50529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>20</v>
       </c>
@@ -50456,12 +50651,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="45" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>80</v>
       </c>
@@ -50469,7 +50664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -50477,7 +50672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>374</v>
       </c>
@@ -50485,7 +50680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -50636,8 +50831,11 @@
       <c r="CK48">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="CL48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>43</v>
       </c>
@@ -50645,7 +50843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -50665,7 +50863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -50676,7 +50874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>368</v>
       </c>
@@ -50690,7 +50888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>345</v>
       </c>
@@ -50707,7 +50905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>343</v>
       </c>
@@ -50730,7 +50928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>344</v>
       </c>
@@ -50744,7 +50942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>396</v>
       </c>
@@ -50755,7 +50953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -50912,8 +51110,11 @@
       <c r="CK57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="CL57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>46</v>
       </c>
@@ -50987,17 +51188,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="60" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="61" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>3</v>
       </c>
@@ -51014,12 +51215,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="63" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>56</v>
       </c>
@@ -51171,7 +51372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>369</v>
       </c>
@@ -51179,7 +51380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>387</v>
       </c>
@@ -51193,7 +51394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>60</v>
       </c>
@@ -51207,7 +51408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>340</v>
       </c>
@@ -51230,17 +51431,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="69" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>55</v>
       </c>
@@ -51335,12 +51536,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -51381,7 +51582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>63</v>
       </c>
@@ -51413,17 +51614,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="75" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="76" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>22</v>
       </c>
@@ -51479,7 +51680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>376</v>
       </c>
@@ -51505,7 +51706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>44</v>
       </c>
@@ -51563,8 +51764,11 @@
       <c r="CJ78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:88" x14ac:dyDescent="0.35">
+      <c r="CL78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>379</v>
       </c>
@@ -51575,7 +51779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:88" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -51592,12 +51796,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>82</v>
       </c>
@@ -51766,8 +51970,11 @@
       <c r="CH82">
         <v>2</v>
       </c>
-    </row>
-    <row r="83" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="CL82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>49</v>
       </c>
@@ -51775,12 +51982,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="85" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>390</v>
       </c>
@@ -51797,7 +52004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -51811,7 +52018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -51992,8 +52199,11 @@
       <c r="CJ87">
         <v>7</v>
       </c>
-    </row>
-    <row r="88" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="CL87">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>45</v>
       </c>
@@ -52004,7 +52214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>367</v>
       </c>
@@ -52086,8 +52296,11 @@
       <c r="CB89">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+      <c r="CL89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>352</v>
       </c>
@@ -52095,12 +52308,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="92" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -52114,12 +52327,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="94" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>86</v>
       </c>
@@ -52127,7 +52340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:90" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -52338,8 +52551,11 @@
       <c r="CK95">
         <v>4</v>
       </c>
-    </row>
-    <row r="96" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+      <c r="CL95">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>47</v>
       </c>
